--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4353,8 +4353,907 @@
       </c>
       <c r="R41" s="3" t="inlineStr"/>
     </row>
+    <row r="42" ht="45" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>314f5c90e2eca63ec5e4</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T03:55:59.132604+00:00</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17T14:48:23+00:00</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>NVIDIA Ignite Internship releases 10/5</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-dfw5-1.cdninstagram.com/v/t51.82787-15/814875022_18087172547678962_8331711395526830193_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4ODI1MDI4MjU4ODMyMjY1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=0lQzvtPz4T8Q7kNvwHCmzto&amp;_nc_oc=AdqbHkWTew8g-pvDOcQ7u7I9Zlgvh21KFC16yyZK0sq59Cll0pfbwzqE_5J3idcA5Ag&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQJSzB6lC_tMcAuut_QC3HvLF1mZaTfmuN3IGHFQy4ePSQ&amp;oe=6AB29450</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>NVIDIA Ignite Internship releases 10/5
+Turn on your notifications for my account!
+Hey there zero2sudo. | remember
+you mentioning that NVIDIA
+Ignite is going to be released in
+early October. | just got an email
+saying It will be on the 5th
+https://scontent-dfw5-1.cdninstagram.com/v/t51.82787-15/814875022_18087172547678962_8331711395526830193_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4ODI1MDI4MjU4ODMyMjY1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=0lQzvtPz4T8Q7kNvwHCmzto&amp;_nc_oc=AdqbHkWTew8g-pvDOcQ7u7I9Zlgvh21KFC16yyZK0sq59Cll0pfbwzqE_5J3idcA5Ag&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQJSzB6lC_tMcAuut_QC3HvLF1mZaTfmuN3IGHFQy4ePSQ&amp;oe=6AB29450
+https://scontent-dfw5-1.cdninstagram.com/v/t51.82787-15/814875022_18087172547678962_8331711395526830193_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4ODI1MDI4MjU4ODMyMjY1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=0lQzvtPz4T8Q7kNvwHCmzto&amp;_nc_oc=AdqbHkWTew8g-pvDOcQ7u7I9Zlgvh21KFC16yyZK0sq59Cll0pfbwzqE_5J3idcA5Ag&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQIhOBjuFed24yHd6OccDaCRbuDP_jK_Fxqa3avKaJPCjQ&amp;oe=6AB29450
+https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwEdRcyz&amp;_nc_oc=Adqw8M_x9B-a8shtOG5wRrb9an7G9olGpS9_wQd75NfCA1HGhLaideM0LC7_0tGzj_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKjZ8LuZIyQWmMhzZRTIIXPovMdv5VlfhbUe2vSoVvRTA&amp;oe=6AB27099</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43" ht="45" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>f76cd1342a4d1945eb27</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T03:56:06.101600+00:00</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17T15:14:38+00:00</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft SWE Intern Offer + Process!</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-dfw5-2.cdninstagram.com/v/t51.82787-15/813634716_18087176735678962_8479740632337180657_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4ODI2MzQ5NDczOTg1NTczOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=00WHMxCXizYQ7kNvwGQInUv&amp;_nc_oc=AdocJ6NuB8k-AoviUantdlwnmlMeE9r1u24mtpyK6Xw-RIzvM65J_qyjb1OnxhZb1yA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQIWpRoM3bL_hWlAaIG2tdSjAIMZ-Ktp5xgY_ZxExFGVYA&amp;oe=6AB2A380</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft SWE Intern Offer + Process!
+Intern Summer 2027, applied as
+soon as | saw your story!
+OA was a standard leetcode easy
+and medium similar to what
+everyone else has been saying
+with the second problem having
+that Al assistant
+v
+First interview had some system
+design, leetcode, and general
+trivia
+Ld
+Second interview was purely
+talking about past experiences
+along with some talk about how |
+use Al to code but it was a super
+chill convo, didn’t feel like an
+interview
+https://scontent-dfw5-2.cdninstagram.com/v/t51.82787-15/813634716_18087176735678962_8479740632337180657_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4ODI2MzQ5NDczOTg1NTczOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=00WHMxCXizYQ7kNvwGQInUv&amp;_nc_oc=AdocJ6NuB8k-AoviUantdlwnmlMeE9r1u24mtpyK6Xw-RIzvM65J_qyjb1OnxhZb1yA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQIWpRoM3bL_hWlAaIG2tdSjAIMZ-Ktp5xgY_ZxExFGVYA&amp;oe=6AB2A380
+https://scontent-dfw5-2.cdninstagram.com/v/t51.82787-15/813634716_18087176735678962_8479740632337180657_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4ODI2MzQ5NDczOTg1NTczOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=00WHMxCXizYQ7kNvwGQInUv&amp;_nc_oc=AdocJ6NuB8k-AoviUantdlwnmlMeE9r1u24mtpyK6Xw-RIzvM65J_qyjb1OnxhZb1yA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQINzKgI3MC1sdOucq-eP4llsOaq6g_uuvlLUpsWYlapgA&amp;oe=6AB2A380
+https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwEdRcyz&amp;_nc_oc=Adqw8M_x9B-a8shtOG5wRrb9an7G9olGpS9_wQd75NfCA1HGhLaideM0LC7_0tGzj_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKjZ8LuZIyQWmMhzZRTIIXPovMdv5VlfhbUe2vSoVvRTA&amp;oe=6AB27099</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="45" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>4bacd493ca4209df0e9b</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T03:56:17.935509+00:00</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17T16:33:16+00:00</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>(new grad swe) yet this year?</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-dfw5-2.cdninstagram.com/v/t51.82787-15/814453000_18087186893678962_2860711254553635645_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4ODMwMzA3MjYyMDM1NTkyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=Kqyif5gxD2UQ7kNvwGrQoN-&amp;_nc_oc=AdpXBVwHSn9OBSr59M00r-W0EnYqJyiF_aC1h_Lt4zXKuOptM0oys_UGzBpCeFAZu8Y&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQJYpGfIpiX0j3gyufnEUPSwujZF3lp8kRfx2-SfFf2fxw&amp;oe=6AB29044</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>More Cap1 TIP offers! Has anyone gotten TDP
+(new grad swe) yet this year?
+Replied to your story
+Yo | got ci TIP cuz of ur story.
+And the info u dropped was
+exactly what the process was
+like.
+Thank you
+~@
+LFG! im so happy when people
+read the stories and highlights
+and get offers ® there's def
+something about high agency ppl
+who consume info and apply it
+properly and landing roles!
+https://scontent-dfw5-2.cdninstagram.com/v/t51.82787-15/814453000_18087186893678962_2860711254553635645_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4ODMwMzA3MjYyMDM1NTkyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=Kqyif5gxD2UQ7kNvwGrQoN-&amp;_nc_oc=AdpXBVwHSn9OBSr59M00r-W0EnYqJyiF_aC1h_Lt4zXKuOptM0oys_UGzBpCeFAZu8Y&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQJYpGfIpiX0j3gyufnEUPSwujZF3lp8kRfx2-SfFf2fxw&amp;oe=6AB29044
+https://scontent-dfw5-2.cdninstagram.com/v/t51.82787-15/814453000_18087186893678962_2860711254553635645_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4ODMwMzA3MjYyMDM1NTkyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=Kqyif5gxD2UQ7kNvwGrQoN-&amp;_nc_oc=AdpXBVwHSn9OBSr59M00r-W0EnYqJyiF_aC1h_Lt4zXKuOptM0oys_UGzBpCeFAZu8Y&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQKzt6EFQ7rBlpyBBx_IwzIWSM_qcMutuHsAfaFz1Gi8_Q&amp;oe=6AB29044
+https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwEdRcyz&amp;_nc_oc=Adqw8M_x9B-a8shtOG5wRrb9an7G9olGpS9_wQd75NfCA1HGhLaideM0LC7_0tGzj_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKjZ8LuZIyQWmMhzZRTIIXPovMdv5VlfhbUe2vSoVvRTA&amp;oe=6AB27099</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45" ht="45" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>c716bcad601a9d9ab8ce</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T03:56:25.967828+00:00</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17T17:25:39+00:00</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>- Hiring happens 1-6 months</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Job / Hiring</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-dfw6-2.cdninstagram.com/v/t51.82787-15/788924699_18087195047678962_4065300646317777670_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4ODMyOTQzNjcxNjUxMDE3Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=r1KisgbLBN0Q7kNvwGpdCaD&amp;_nc_oc=AdodVmaXg5vc8Ho_zZ3Mm8rqJD-iYH7jVBG7_BHU3uVxfw2beh9I0a5PTOS__-FZ_kQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw6-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQLwhQl2VA-wUB3JfXqeF5a1-Fs-FM7v5Cvk9dys3ot-KA&amp;oe=6AB29B46</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Hey Sudo, recap from the Tesla
+event at Chapel Hill:
+- Tailor your resume to the
+specific role, have similar
+keywords/skills/projects as they
+mention in the role
+- WHO method (What, How,
+Outcome)
+- Hiring happens 1-6 months
+before role start
+- Be yourself as much as possible
+in interviews
+- Referrals help, even from
+interns (goes to same place)
+- Best of the Best - why are you
+the best person that we should
+hire? (goes all the way up
+command chain)
+https://scontent-dfw6-2.cdninstagram.com/v/t51.82787-15/788924699_18087195047678962_4065300646317777670_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4ODMyOTQzNjcxNjUxMDE3Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=r1KisgbLBN0Q7kNvwGpdCaD&amp;_nc_oc=AdodVmaXg5vc8Ho_zZ3Mm8rqJD-iYH7jVBG7_BHU3uVxfw2beh9I0a5PTOS__-FZ_kQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw6-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQLwhQl2VA-wUB3JfXqeF5a1-Fs-FM7v5Cvk9dys3ot-KA&amp;oe=6AB29B46
+https://scontent-dfw6-2.cdninstagram.com/v/t51.82787-15/788924699_18087195047678962_4065300646317777670_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4ODMyOTQzNjcxNjUxMDE3Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=r1KisgbLBN0Q7kNvwGpdCaD&amp;_nc_oc=AdodVmaXg5vc8Ho_zZ3Mm8rqJD-iYH7jVBG7_BHU3uVxfw2beh9I0a5PTOS__-FZ_kQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQLDnG6D0On1tMrP5sUTsdtW39-tpQq7PkNZHeviJSdYUg&amp;oe=6AB29B46
+https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwEdRcyz&amp;_nc_oc=Adqw8M_x9B-a8shtOG5wRrb9an7G9olGpS9_wQd75NfCA1HGhLaideM0LC7_0tGzj_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKjZ8LuZIyQWmMhzZRTIIXPovMdv5VlfhbUe2vSoVvRTA&amp;oe=6AB27099</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="45" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>d8f744b57e2f32c28c9b</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T03:56:28.030321+00:00</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17T17:37:26+00:00</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Google — webinar you posted JA, J,</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr"/>
+      <c r="I46" s="3" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-dfw5-2.cdninstagram.com/v/t51.82787-15/809209168_18087197012678962_1565929461932431535_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4ODMzNTM2NjgwNDgwMjc2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=hyMuw1kltl4Q7kNvwGDmDfE&amp;_nc_oc=AdqP3Ta2dI1g0FVH7QyEE7uEOkgbBa3Q4hKWXs3n0cE6DhBALl74f1QRyALqnOSfz6A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQIostWAzN_LeyMnpXj1RMvSP1_Q_e9HqHU6OvxXwXkAiA&amp;oe=6AB29612</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Google SWE New Grad RO!!!
+Got google return offer thank
+you for all you do for the cs
+students! Got my google
+interview last year because of a
+webinar you posted JA, J,
+| only know I'm matched to
+Youtube they said i won't be
+matched till 8 weeks b4 my start
+date
+https://scontent-dfw5-2.cdninstagram.com/v/t51.82787-15/809209168_18087197012678962_1565929461932431535_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4ODMzNTM2NjgwNDgwMjc2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=hyMuw1kltl4Q7kNvwGDmDfE&amp;_nc_oc=AdqP3Ta2dI1g0FVH7QyEE7uEOkgbBa3Q4hKWXs3n0cE6DhBALl74f1QRyALqnOSfz6A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQIostWAzN_LeyMnpXj1RMvSP1_Q_e9HqHU6OvxXwXkAiA&amp;oe=6AB29612
+https://scontent-dfw5-2.cdninstagram.com/v/t51.82787-15/809209168_18087197012678962_1565929461932431535_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4ODMzNTM2NjgwNDgwMjc2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=hyMuw1kltl4Q7kNvwGDmDfE&amp;_nc_oc=AdqP3Ta2dI1g0FVH7QyEE7uEOkgbBa3Q4hKWXs3n0cE6DhBALl74f1QRyALqnOSfz6A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQJzFWVHc5WeuM08e47_3LCv6Ija7-EHDaKsxGpsey7Cag&amp;oe=6AB29612
+https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwEdRcyz&amp;_nc_oc=Adqw8M_x9B-a8shtOG5wRrb9an7G9olGpS9_wQd75NfCA1HGhLaideM0LC7_0tGzj_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKjZ8LuZIyQWmMhzZRTIIXPovMdv5VlfhbUe2vSoVvRTA&amp;oe=6AB27099</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47" ht="45" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>5ec01f615ec61f7238aa</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T03:56:45.854899+00:00</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17T20:13:34+00:00</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Adobe — also no sign up form</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/813976257_18087212606678962_600677638285630895_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4ODQxMzk1MjcwNjYxNTUwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=mB7SsEg8mAcQ7kNvwH7ifI4&amp;_nc_oc=AdrgaQy7PBD-5nGixGfL9Zm9M9qCO-UwaBNx4BPlBGPKDnHMEuxIZR6RGEskG80WK3M&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQLcplPJMSsGcX-eInoBlbJjbtdXSHaxWs8IMJ0bNGTzjw&amp;oe=6AB27AB6</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Adobe Intern
+@ rolling bests)!
+epee matters more than referrals
+aa tor Adobe!
+in the adobe event they also said
+that referrals matter but speed
+matters more and for ai they said
+that they are only gonna use it in
+a few questions and not for all in
+the interviews and she said that
+they are gonna wrap up their
+hiring around march
+| wasn’t there for the first 20ish
+minutes for the event so idk what
+happened there but there was
+also no sign up form
+she also said that they don’t use
+Al to look through candidates
+https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/813976257_18087212606678962_600677638285630895_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4ODQxMzk1MjcwNjYxNTUwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=mB7SsEg8mAcQ7kNvwH7ifI4&amp;_nc_oc=AdrgaQy7PBD-5nGixGfL9Zm9M9qCO-UwaBNx4BPlBGPKDnHMEuxIZR6RGEskG80WK3M&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQLcplPJMSsGcX-eInoBlbJjbtdXSHaxWs8IMJ0bNGTzjw&amp;oe=6AB27AB6
+https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/813976257_18087212606678962_600677638285630895_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4ODQxMzk1MjcwNjYxNTUwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=mB7SsEg8mAcQ7kNvwH7ifI4&amp;_nc_oc=AdrgaQy7PBD-5nGixGfL9Zm9M9qCO-UwaBNx4BPlBGPKDnHMEuxIZR6RGEskG80WK3M&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQJmDHRanLsPRRuz018MKNgajUmLnPE_BRNLe2hAqyiJ5Q&amp;oe=6AB27AB6
+https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwEdRcyz&amp;_nc_oc=Adqw8M_x9B-a8shtOG5wRrb9an7G9olGpS9_wQd75NfCA1HGhLaideM0LC7_0tGzj_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKjZ8LuZIyQWmMhzZRTIIXPovMdv5VlfhbUe2vSoVvRTA&amp;oe=6AB27099</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="45" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>406eecd407d7e310c1bb</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T03:56:54.958591+00:00</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17T20:35:03+00:00</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr"/>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>So many Capi SWE Intern Offers!</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr"/>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/814768840_18087214964678962_300587807414299988_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4ODQyNDc2MjY2MTAyNzcwOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=pKt1LD4ViCkQ7kNvwGmc1Xt&amp;_nc_oc=AdoWWXXPfejqt7fr8TqU4wiOJQL5Kapkkj3oZVJYjGdMXzvek1-BVeQqoMxaOTP3aSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQLfVG2TXYuw4-wQ30d9xFs07gxCXJmKpbd9Zr-A8UPhHQ&amp;oe=6AB28EC4</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Replied to your story
+got c1tip as well, helpful info on
+the ai assist ty. litearlly heard
+back in less than 24 hours as well
+So many Capi SWE Intern Offers!
+https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/814768840_18087214964678962_300587807414299988_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4ODQyNDc2MjY2MTAyNzcwOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=pKt1LD4ViCkQ7kNvwGmc1Xt&amp;_nc_oc=AdoWWXXPfejqt7fr8TqU4wiOJQL5Kapkkj3oZVJYjGdMXzvek1-BVeQqoMxaOTP3aSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQLfVG2TXYuw4-wQ30d9xFs07gxCXJmKpbd9Zr-A8UPhHQ&amp;oe=6AB28EC4
+https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/814768840_18087214964678962_300587807414299988_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4ODQyNDc2MjY2MTAyNzcwOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=pKt1LD4ViCkQ7kNvwGmc1Xt&amp;_nc_oc=AdoWWXXPfejqt7fr8TqU4wiOJQL5Kapkkj3oZVJYjGdMXzvek1-BVeQqoMxaOTP3aSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQKK9OBBGgHLdlREGZEWhyBfKCkjYAZhPcMzTH2etxQsrg&amp;oe=6AB28EC4
+https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwEdRcyz&amp;_nc_oc=Adqw8M_x9B-a8shtOG5wRrb9an7G9olGpS9_wQd75NfCA1HGhLaideM0LC7_0tGzj_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKjZ8LuZIyQWmMhzZRTIIXPovMdv5VlfhbUe2vSoVvRTA&amp;oe=6AB27099</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49" ht="45" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>a99c75e25c9a557a5480</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T03:57:00.309434+00:00</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17T21:45:38+00:00</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>This is why | care so much about making opportunity</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr"/>
+      <c r="I49" s="3" t="inlineStr"/>
+      <c r="J49" s="3" t="inlineStr"/>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-dfw5-1.cdninstagram.com/v/t51.82787-15/814695558_18087220370678962_7673257959919455186_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4ODQ2MDI4NjYyNDg0MzIxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=cjWX3Z2jFwgQ7kNvwFQwL12&amp;_nc_oc=AdpT1A9Oi-S9coUbMd4aNFpXGgvavHvrRTkuWPbPVSiVxtBpWJNvyhWFrgSD_wWpd1k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQLt2FiRSa8REgSoEbK6HJbEM2xWYlfJE05brCM6MV0KZg&amp;oe=6AB299D1</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>So many non-target students made it to Bloomberg
+last year and crushed it. Never let anyone tell you
+what you deserve (unless it’s better than you
+expect), and never let where you start determine
+where you finish.
+This is why | care so much about making opportunity
+more accessible :)
+Same A, if you scroll up in
+our chat you can see | got
+headcounted initially, but
+persistence paid off
+Thanks for everything you do!
+| applied through your link last
+year.
+ae
+I'm the first ever intern at bb
+from my university purely
+because of your stories &amp;
+ae
+lets fkn go! it's super funny bc
+gatekeepers tried claiming
+people would be blacklisted for
+applying. in reality, multiple
+companies confirmed with us
+last year that they just want to
+hire competent candidates.
+good people exist anywhere,
+companies don't care about
+people "trying harder" to find an
+event link or some dumbass shit
+like that &amp; great job man :)
+https://scontent-dfw5-1.cdninstagram.com/v/t51.82787-15/814695558_18087220370678962_7673257959919455186_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4ODQ2MDI4NjYyNDg0MzIxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=cjWX3Z2jFwgQ7kNvwFQwL12&amp;_nc_oc=AdpT1A9Oi-S9coUbMd4aNFpXGgvavHvrRTkuWPbPVSiVxtBpWJNvyhWFrgSD_wWpd1k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQLt2FiRSa8REgSoEbK6HJbEM2xWYlfJE05brCM6MV0KZg&amp;oe=6AB299D1
+https://scontent-dfw5-1.cdninstagram.com/v/t51.82787-15/814695558_18087220370678962_7673257959919455186_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4ODQ2MDI4NjYyNDg0MzIxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=cjWX3Z2jFwgQ7kNvwFQwL12&amp;_nc_oc=AdpT1A9Oi-S9coUbMd4aNFpXGgvavHvrRTkuWPbPVSiVxtBpWJNvyhWFrgSD_wWpd1k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQKv6hKoYDUUuRWKaovEu-W_i3fy911SUhhyKWdW3GqDGw&amp;oe=6AB299D1
+https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwEdRcyz&amp;_nc_oc=Adqw8M_x9B-a8shtOG5wRrb9an7G9olGpS9_wQd75NfCA1HGhLaideM0LC7_0tGzj_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKjZ8LuZIyQWmMhzZRTIIXPovMdv5VlfhbUe2vSoVvRTA&amp;oe=6AB27099</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="45" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>b05a980a5e5c08b9287d</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T03:57:03.026869+00:00</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17T21:49:10+00:00</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr"/>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>career fair but we are definitely</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Recruiting / Career Event</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr"/>
+      <c r="I50" s="3" t="inlineStr"/>
+      <c r="J50" s="3" t="inlineStr"/>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-dfw5-1.cdninstagram.com/v/t51.82787-15/814229705_18087220610678962_85839488440364683_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4ODQ2MjA2ODY5MjM1ODkwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=8_nKWHMwEBkQ7kNvwFHtp7M&amp;_nc_oc=Adq8Vb2DwR7WFk4raII5dwO7zqnLZ11FjpaSySsL8C1v09BNzAjMd-OvEozUUr_GoqU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQJ0BfSD_GObVyneapxWhUFOmU8UAUXpUBpFC670fF8FPg&amp;oe=6AB2850B</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>ARM recruiter clarification on
+application consideration!
+Hey hey, someone flagged
+this for me, this is probably a
+misunderstanding from the
+career fair but we are definitely
+still considering applications
+from our original application
+window being open. We are
+no longer accepting new
+applications outside of career
+fair signups, that could be the
+confusion point from the fair.
+https://scontent-dfw5-1.cdninstagram.com/v/t51.82787-15/814229705_18087220610678962_85839488440364683_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4ODQ2MjA2ODY5MjM1ODkwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=8_nKWHMwEBkQ7kNvwFHtp7M&amp;_nc_oc=Adq8Vb2DwR7WFk4raII5dwO7zqnLZ11FjpaSySsL8C1v09BNzAjMd-OvEozUUr_GoqU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQJ0BfSD_GObVyneapxWhUFOmU8UAUXpUBpFC670fF8FPg&amp;oe=6AB2850B
+https://scontent-dfw5-1.cdninstagram.com/v/t51.82787-15/814229705_18087220610678962_85839488440364683_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4ODQ2MjA2ODY5MjM1ODkwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=8_nKWHMwEBkQ7kNvwFHtp7M&amp;_nc_oc=Adq8Vb2DwR7WFk4raII5dwO7zqnLZ11FjpaSySsL8C1v09BNzAjMd-OvEozUUr_GoqU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQIBe2RX7D6PQfZ5GpMe85mCb3lbJ-gRAPPbE_xN3rABGA&amp;oe=6AB2850B
+https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwEdRcyz&amp;_nc_oc=Adqw8M_x9B-a8shtOG5wRrb9an7G9olGpS9_wQd75NfCA1HGhLaideM0LC7_0tGzj_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKjZ8LuZIyQWmMhzZRTIIXPovMdv5VlfhbUe2vSoVvRTA&amp;oe=6AB27099</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51" ht="45" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>cb892eb20bb5e8bf02de</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T03:57:42.780142+00:00</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17T23:38:08+00:00</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Amazon — 1AZ0N SWE INTERN 2027 &amp;</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr"/>
+      <c r="J51" s="3" t="inlineStr"/>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/814779823_18087230822678962_7861859619461180195_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4ODUxNjkwOTI4NjA1MTY1Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=K22FdASUScsQ7kNvwEvHaFi&amp;_nc_oc=AdoQIek4FQMqLlmJYPzidfEr7oCV4F82zJCRax858_LfrkYKuBPCI8uXwqX7MkpngfU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQJni_oy7mNWkib4ab3OL8yIdviP21Y9xzY-Z58nUm0O7g&amp;oe=6AB28C0F</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Replied to your story
+Ask your Amazon questions!
+2027 (USA)
+Type something...
+1AZ0N SWE INTERN 2027 &amp;
+HUGE DROP @ @ @ gal
+interning at amazon rn Imk if | can
+provide any helpful info abt the
+process
+| think at this point you probbaly
+have heard it so many times but
+Leadership Principles are so so
+so important i think it helps to
+literally sit down and study them
+yessir! ty for sharing A.A.
+https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/814779823_18087230822678962_7861859619461180195_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4ODUxNjkwOTI4NjA1MTY1Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=K22FdASUScsQ7kNvwEvHaFi&amp;_nc_oc=AdoQIek4FQMqLlmJYPzidfEr7oCV4F82zJCRax858_LfrkYKuBPCI8uXwqX7MkpngfU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQJni_oy7mNWkib4ab3OL8yIdviP21Y9xzY-Z58nUm0O7g&amp;oe=6AB28C0F
+https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/814779823_18087230822678962_7861859619461180195_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4ODUxNjkwOTI4NjA1MTY1Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=K22FdASUScsQ7kNvwEvHaFi&amp;_nc_oc=AdoQIek4FQMqLlmJYPzidfEr7oCV4F82zJCRax858_LfrkYKuBPCI8uXwqX7MkpngfU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQI_SnA4LGBN9T2S09E-BZmktP92CboF4vixfqJC0UiyTA&amp;oe=6AB28C0F
+https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwEdRcyz&amp;_nc_oc=Adqw8M_x9B-a8shtOG5wRrb9an7G9olGpS9_wQd75NfCA1HGhLaideM0LC7_0tGzj_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKjZ8LuZIyQWmMhzZRTIIXPovMdv5VlfhbUe2vSoVvRTA&amp;oe=6AB27099</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R51" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R41"/>
+  <autoFilter ref="A1:R51"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -4436,6 +5335,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId100"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,9 +11,9 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$41</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -565,7 +565,7 @@
     <row r="2" ht="45" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>ba25d10856a4f31cf5ae</t>
+          <t>7b4825530649f17a0c19</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>(5) Posted Today iw Visa SWE New Grad!!!</t>
+          <t>Visa — Software Engineering</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -608,10 +608,10 @@
           <t>Bellevue</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="n"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/en-US/Visa_Early_Careers/job/US---Bellevue-WA/Software-Engineer--New-College-Grad--Bellevue---2027_REF088530W-2?fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeST7K82NONiITJFgPRoD7vqqZysLZI_Kz5DuYkh8mizAkeTVEkDyD4jJ-bCQ_aem_SzaD6pjjVhOnaIDGMRdSig&amp;utm_id=97760_v0_s00_e0_tv6_a1denngsc6gtwx</t>
+          <t>https://visa.wd5.myworkdayjobs.com/en-US/Visa_Early_Careers/job/US---Bellevue-WA/Software-Engineer--New-College-Grad--Bellevue---2027_REF088530W-2</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
@@ -661,12 +661,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="n"/>
     </row>
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>bb4bf87bb799bef31a9d</t>
+          <t>706ceee9c55c8a4451c0</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Visa — (APM) Intern - Summer 2027</t>
+          <t>Visa — Product Management</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -709,10 +709,10 @@
           <t>Austin</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="n"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/en-US/Visa_Early_Careers/job/US---Austin-TX/Job-Posting-Title-Associate-Product-Manager--APM--Intern---Summer-2027_REF088604W-2?fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafErXktmGYjgELrbXzuGr-4sHOy7HSCp1KP84X8ESQq1ZBQFe9uP9r58_xBXA_aem_YauQvUxAOSwNnF_Ca5r5pQ&amp;utm_id=97760_v0_s00_e0_tv6_a1denngsc6gtwx</t>
+          <t>https://visa.wd5.myworkdayjobs.com/en-US/Visa_Early_Careers/job/US---Austin-TX/Job-Posting-Title-Associate-Product-Manager--APM--Intern---Summer-2027_REF088604W-2</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -764,12 +764,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="n"/>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>41d04c2ffdee78e648cf</t>
+          <t>a4b39740d30b2b618009</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Visa — Finance Intern - Summer 2027</t>
+          <t>Visa — Internship</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -797,17 +797,17 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/en-US/Visa_Early_Careers/job/US---Foster-City-CA/Finance-Intern---Summer-2027_REF088568W?fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacrgdepGz4IJHft5p7SK4A3enB46rvIP87IwJLZ5kf-rM2jmzsofDfWU9h7mA_aem_XqzNR2ihyenUwHa6XT37lQ&amp;utm_id=97760_v0_s00_e0_tv6_a1denngsc6gtwx</t>
+          <t>https://visa.wd5.myworkdayjobs.com/en-US/Visa_Early_Careers/job/US---Foster-City-CA/Finance-Intern---Summer-2027_REF088568W</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -855,12 +855,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>e4ac01912369a33590d8</t>
+          <t>41c956ede1ac1dff5fc9</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -873,7 +873,7 @@
           <t>2026-09-17T12:03:07+00:00</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Show Control Software Intern, Spring</t>
@@ -884,17 +884,17 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Spring 2027</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.disneycareers.com/en/job/lake-buena-vista/wdi-show-control-software-intern-spring-2027/391/100746188400?fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadwEe5sctZcAP-EsdGnxw5qf9253ZYr28qgT5W43fCOdXtriPGh-ABTWVYNrQ_aem_I1zyxzuXuPXPFJyUZmZzNA</t>
+          <t>https://www.disneycareers.com/en/job/lake-buena-vista/wdi-show-control-software-intern-spring-2027/391/100746188400</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -935,12 +935,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="n"/>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>b46593350a917c25ed0c</t>
+          <t>9c4d0e23dd51c74d3e4d</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Withwaymo — Intern, BS/MS,</t>
+          <t>Withwaymo — Internship</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -968,17 +968,17 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://careers.withwaymo.com/jobs/2027-summer-intern-bs-ms-software-engineering-maneuvering-tech-san-francisco-california-united-states?gh_jid=8203200&amp;fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAac7NESXQ_ZBbGXP7JPPQlKEyZsxD271fGAncinplB6KCYADxnCtUuRWhGXKLg_aem_57W-a28xeCAUm05Wf09Jug</t>
+          <t>https://careers.withwaymo.com/jobs/2027-summer-intern-bs-ms-software-engineering-maneuvering-tech-san-francisco-california-united-states?gh_jid=8203200</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -1022,12 +1022,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>b7914b5fe87bf2b1e6d9</t>
+          <t>c35828f5f25cc7491cbd</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Apple — Submit Resume</t>
+          <t>Apple — Other Opportunity</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -1055,7 +1055,7 @@
           <t>Other Opportunity</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
           <t>2026</t>
@@ -1066,7 +1066,7 @@
           <t>Sunnyvale</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="n"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
           <t>https://jobs.apple.com/en-us/details/200684185/module-test-instrumentation-automation-engineer</t>
@@ -1120,12 +1120,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="n"/>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>c0ccd2d97d3e335259bf</t>
+          <t>256dc7c9740c905fd441</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn — Intern - Artificial Intelligence (Al)</t>
+          <t>LinkedIn — Product Management, Machine Learning / AI</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -1163,11 +1163,11 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://fa-exty-saasfaprod1.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/119494?fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaey1PtPQiYe5X7JAbRYjBMUbwF3JiTdE8MPS5qoCoqHmR9Em1VgGz1W8g--Qg_aem__X-JBPU8nXhPkia9VIWUIQ</t>
+          <t>https://fa-exty-saasfaprod1.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/119494</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -1217,12 +1217,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="n"/>
     </row>
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>0a42f7bbd79d29ae6052</t>
+          <t>68c75318e6ddaeafc89f</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA Ignite Internship releases 10/5</t>
+          <t>NVIDIA — Internship</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1250,15 +1250,11 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-lax3-2.cdninstagram.com/v/t51.82787-15/814875022_18087172547678962_8331711395526830193_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4ODI1MDI4MjU4ODMyMjY1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=0lQzvtPz4T8Q7kNvwGb64qW&amp;_nc_oc=AdrSMu6j2saVzvC8n6-INMidcq3jnNz2RsCMAfR-NTdoNnnUsjfAbwzIaLtqrDSfQKI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=8&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=57T-qu4SHiuDf3cdAqvPAQ&amp;_nc_ss=7e3ba&amp;oh=00_AQJLx5h2SxoTCuOxos4Ym6C9Jb9Qsd5UfZLd9XdcTVaPrw&amp;oe=6AB29450</t>
-        </is>
-      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -1303,7 +1299,7 @@
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>1aa86cda3b61178d4db4</t>
+          <t>c9cfc5e72765dc797466</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1323,7 +1319,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Microsoft SWE Intern Offer + Process!</t>
+          <t>Microsoft — Software Engineering</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1341,13 +1337,9 @@
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-lax3-2.cdninstagram.com/v/t51.82787-15/813634716_18087176735678962_8479740632337180657_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4ODI2MzQ5NDczOTg1NTczOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=00WHMxCXizYQ7kNvwEfhEBA&amp;_nc_oc=AdoSWVClbyaGKmL_LYJ0tjkWb639aA2YLznC6VoeLhdeVnZqe7FW7evBFEHIaMOWz94&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=8&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=57T-qu4SHiuDf3cdAqvPAQ&amp;_nc_ss=7e3ba&amp;oh=00_AQJwjlnqLL-Hs6ooI2cFzExFVSqH9U0UlYntRbkuj-GXWg&amp;oe=6AB26B40</t>
-        </is>
-      </c>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -1403,7 +1395,7 @@
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>dffb3574e3ae221f1a0b</t>
+          <t>27df51b2475d3caf749f</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1431,13 +1423,13 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://apply.corteva.com/careers/job/893397633254?domain=corteva.com&amp;hl=en&amp;fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacwttun-0wNDC5BX9MElJ91PBNW7MRlcRgKQx-eJxB6fRnIhQxMM9QO5iNH5A_aem_XWOcJtSqH4hHzbSJjUav1w</t>
+          <t>https://apply.corteva.com/careers/job/893397633254?domain=corteva.com&amp;hl=en</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1481,12 +1473,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="n"/>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>8e6595b74f21640d5db7</t>
+          <t>7eee43b02b5baab891f7</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1506,7 +1498,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Visa — 2027 Sophomore Internship Program - Software</t>
+          <t>Visa — Software Engineering</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1529,10 +1521,10 @@
           <t>Bellevue, Austin</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="n"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/en-US/Visa_Early_Careers?q=sophomore&amp;fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadqXWxlVc59UpVZ-qavclGHLIjRLxHIC8QzIrsgNWTg6ZrjWLxAilpPuro9ZQ_aem_Sni8W7aTuRQoJvB693kyFg&amp;utm_id=97760_v0_s00_e0_tv6_a1denngsc6gtwx</t>
+          <t>https://visa.wd5.myworkdayjobs.com/en-US/Visa_Early_Careers?q=sophomore</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1588,12 +1580,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="n"/>
     </row>
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>68fab5dd9163a70b2933</t>
+          <t>f2153ff3f291d141b2cf</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1613,7 +1605,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Visa — [ Intern x | United States of America x |</t>
+          <t>Visa — Software Engineering</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1636,10 +1628,10 @@
           <t>Bellevue</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="n"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/en-US/Visa_Early_Careers?fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafqtDCHtM4dD6sXASoqMNOxrRJUgZndaVPIML5twNk5hG_DZdboH3baMNsUxw_aem_IJkMMFwzZMCHeZt88nLJ-g&amp;utm_id=97760_v0_s00_e0_tv6_a1denngsc6gtwx</t>
+          <t>https://visa.wd5.myworkdayjobs.com/en-US/Visa_Early_Careers</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1683,12 +1675,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="n"/>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>f91ea23cff55c87fcd24</t>
+          <t>eae5a097203d5f8c02a8</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1701,10 +1693,10 @@
           <t>2026-09-17T16:33:16+00:00</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>(new grad swe) yet this year?</t>
+          <t>Software Engineering</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1717,14 +1709,10 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr"/>
-      <c r="J14" s="3" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-lax3-1.cdninstagram.com/v/t51.82787-15/814453000_18087186893678962_2860711254553635645_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4ODMwMzA3MjYyMDM1NTkyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=Kqyif5gxD2UQ7kNvwHJVLdN&amp;_nc_oc=AdoNHDEoWB6BKWzQhX0T7L7g6YKjxJdTLP2IKQKDsn1j2G0ND1PhxoH-z-EyPJq60BA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=8&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=57T-qu4SHiuDf3cdAqvPAQ&amp;_nc_ss=7e3ba&amp;oh=00_AQLb6ntW9dHc92zRlgQI5sfWKBvxiINa2vuMw2Ii4Gbh_A&amp;oe=6AB29044</t>
-        </is>
-      </c>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="inlineStr"/>
       <c r="L14" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -1777,7 +1765,7 @@
     <row r="15" ht="45" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>ad285a2cc189de0b9b00</t>
+          <t>c6b95c3fe9fbd547419f</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1790,10 +1778,10 @@
           <t>2026-09-17T17:25:39+00:00</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>- Hiring happens 1-6 months</t>
+          <t>Job / Hiring</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1801,15 +1789,11 @@
           <t>Job / Hiring</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="3" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-lax3-1.cdninstagram.com/v/t51.82787-15/788924699_18087195047678962_4065300646317777670_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4ODMyOTQzNjcxNjUxMDE3Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=r1KisgbLBN0Q7kNvwE3fA0k&amp;_nc_oc=AdrfxVJRMRwQd_SEW-50uwb_gTKV9bq-AvXL-gBeFK2QyzYe4MsDemMx1_UjSWK9Fkk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=8&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=57T-qu4SHiuDf3cdAqvPAQ&amp;_nc_ss=7e3ba&amp;oh=00_AQKRQJ9KbVIXNPvUFZuCCVLPuqzKOlD8gFaH3qGeTZ5jwQ&amp;oe=6AB29B46</t>
-        </is>
-      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="inlineStr"/>
       <c r="L15" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -1865,7 +1849,7 @@
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>c8a267405a5a2605f037</t>
+          <t>92438512a971c17dd06b</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1885,7 +1869,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Google — webinar you posted J J,</t>
+          <t>Google — Software Engineering</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1898,14 +1882,10 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-lax3-2.cdninstagram.com/v/t51.82787-15/809209168_18087197012678962_1565929461932431535_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4ODMzNTM2NjgwNDgwMjc2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=hyMuw1kltl4Q7kNvwHH6s5-&amp;_nc_oc=AdqRmJMnUSuie2BMPQ-aJNFrRLxyGSZF3DrsZt-50ZyfhhvDwI5yeatV-zfCNkNyPHM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=8&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=57T-qu4SHiuDf3cdAqvPAQ&amp;_nc_ss=7e3ba&amp;oh=00_AQKgPJdT-Wou9jGmQDqPmigan6YNEHefJMVtrJuOzifDNQ&amp;oe=6AB29612</t>
-        </is>
-      </c>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="inlineStr"/>
       <c r="L16" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -1953,7 +1933,7 @@
     <row r="17" ht="45" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>ac80776bfd29833aeb4b</t>
+          <t>74c276c16180d5c50fa2</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1973,7 +1953,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Amazon — Apply now</t>
+          <t>Amazon — Internship</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1981,17 +1961,17 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="n"/>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://www.amazon.jobs/en/jobs/10550494/solutions-architect-intern-awsi-2027?cmpid=SPLICX0248M&amp;ss=paid&amp;utm_content=job_posting&amp;utm_medium=zero2sudo&amp;utm_source=zero2sudo&amp;fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafr8EsnZGevTi78IsAHz9sobXtEmKEiH6UUMtCXzLNCIW0sR20czRLHrB5wlw_aem_z_MLDgU1BRYPYoXbhHc-sA</t>
+          <t>https://www.amazon.jobs/en/jobs/10550494/solutions-architect-intern-awsi-2027?cmpid=SPLICX0248M&amp;ss=paid</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -2042,12 +2022,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="n"/>
     </row>
     <row r="18" ht="45" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>b800e0fbc0382c3be18a</t>
+          <t>bf5ef4b5db8fb13f9ddc</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2067,7 +2047,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Q2ebanking — 2027 Summer Internship -</t>
+          <t>Q2ebanking — Software Engineering</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -2090,10 +2070,10 @@
           <t>Austin</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="n"/>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://q2ebanking.wd5.myworkdayjobs.com/Q2/job/Austin-Texas/XMLNAME-2027-Summer-Internship---Software-Engineer_REQ-12794?utm_id=97760_v0_s00_e0_tv4&amp;fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadm-5zDxHnUrJw5OmSWhsw33qDd0fJMQygYRr_CWdPTgpga-Sco0_jNVFyB-w_aem_XEKItE_5z4RYfO416W_Ebg</t>
+          <t>https://q2ebanking.wd5.myworkdayjobs.com/Q2/job/Austin-Texas/XMLNAME-2027-Summer-Internship---Software-Engineer_REQ-12794</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -2146,12 +2126,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="n"/>
     </row>
     <row r="19" ht="45" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>3e00a3bad38d576ffa82</t>
+          <t>02fedfa0d99db4731f48</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2164,10 +2144,10 @@
           <t>2026-09-17T18:59:03+00:00</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>been the driving idea for 240 years, across all of</t>
+          <t>Other Opportunity</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -2175,17 +2155,17 @@
           <t>Other Opportunity</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="n"/>
       <c r="H19" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://bankcampuscareers.tal.net/vx/lang-en-GB/candidate/postings/11722?fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafeDHmviMVR05IZSAB3tVEs3ROEfYrjpYEH7louQ8yFhhQFmPd1VsERDNMU9w_aem_N6TKx1NV2V5YW6HvFJCkUw</t>
+          <t>https://bankcampuscareers.tal.net/vx/lang-en-GB/candidate/postings/11722</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2241,12 +2221,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="n"/>
     </row>
     <row r="20" ht="45" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>15b2a2624f5223e15eaa</t>
+          <t>dc8cbc2121b163b30edf</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2266,7 +2246,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Google — Please fill out this brief form to RSVP for the</t>
+          <t>Google — Product Management</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -2284,8 +2264,8 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
       <c r="K20" s="4" t="inlineStr">
         <is>
           <t>https://docs.google.com/forms/d/e/1FAIpQLSdFK9CGBJkDUxjEq_ILISViHrG0cRyuXvor4BvuFyQHVidh-w/viewform</t>
@@ -2339,12 +2319,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="n"/>
     </row>
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>bd6fcaeaa66536d0b95f</t>
+          <t>7e684900440f149d9011</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -2364,7 +2344,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Adobe — also no sign up form</t>
+          <t>Adobe — Internship</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -2372,15 +2352,11 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-lax7-1.cdninstagram.com/v/t51.82787-15/813976257_18087212606678962_600677638285630895_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4ODQxMzk1MjcwNjYxNTUwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=mB7SsEg8mAcQ7kNvwGDESki&amp;_nc_oc=AdqwSy9lQdoQ7uWsjMrgq9SpYo-t7RKuO-8tfRJYIkguFhZhWBJaqsDbijFvkgiToOk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=8&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_gid=57T-qu4SHiuDf3cdAqvPAQ&amp;_nc_ss=7e3ba&amp;oh=00_AQISudedPTIfHr9XqqCjG8QPpz8oP1SqpqBAKn5ZnlIOlg&amp;oe=6AB27AB6</t>
-        </is>
-      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -2436,7 +2412,7 @@
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>8c0b721693b195be7216</t>
+          <t>ee8af5b3cf30cdbd333e</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2456,7 +2432,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA — =&gt; ONvODIA. Join Talent Network Sign In</t>
+          <t>NVIDIA — Referral / Talent Network</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -2464,7 +2440,7 @@
           <t>Referral / Talent Network</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="n"/>
       <c r="H22" s="3" t="inlineStr">
         <is>
           <t>2027</t>
@@ -2475,10 +2451,10 @@
           <t>Remote</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="n"/>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.nvidia.com/careers/job/893397738658?fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacwd4iWA6Kmt4fmWSXDNGjUf8gG9AYz_r0957yYx7bNqCcV7Ody7dwGG1XNGQ_aem_bGab7CLgQ3mbjGQji2QWZw</t>
+          <t>https://jobs.nvidia.com/careers/job/893397738658</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -2524,12 +2500,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="n"/>
     </row>
     <row r="23" ht="45" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>944f58df7bb90171bbcb</t>
+          <t>bf16b8d883cdedb2f926</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2549,7 +2525,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>| @ GOOGLE DS INTERN (MASTER'S)</t>
+          <t>Google — Data Science</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -2572,10 +2548,10 @@
           <t>Mountain View</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="n"/>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/about/careers/applications/jobs/results/119184035237765830-data-scientist-product-intern-ms-summer-2027?fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacK1MJPvTGidxzLP77EnMQ6VdWc0VM_93Ybe0gQiyPZ3iO8dXYYXEoofHw1Wg_aem_eLjzGtAKkIwP6ukiv2-bkg</t>
+          <t>https://www.google.com/about/careers/applications/jobs/results/119184035237765830-data-scientist-product-intern-ms-summer-2027</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2631,12 +2607,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="n"/>
     </row>
     <row r="24" ht="45" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>16d3b078f65f297c2711</t>
+          <t>4663d547ffead36088c0</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2656,7 +2632,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Google — Thanks for your interest! RSVP now to</t>
+          <t>Google — Product Management</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -2674,8 +2650,8 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr"/>
-      <c r="J24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="n"/>
+      <c r="J24" s="3" t="n"/>
       <c r="K24" s="4" t="inlineStr">
         <is>
           <t>https://docs.google.com/forms/d/1wd3Ye6ouR2G9mdhQkJDv8jI5WDs1UyhRLEa6j6lnCn8/viewform?edit_requested=true</t>
@@ -2730,12 +2706,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="n"/>
     </row>
     <row r="25" ht="45" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2d278256e08f52e7a8ad</t>
+          <t>0fe8808a7d439950ce28</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -2748,7 +2724,7 @@
           <t>2026-09-17T20:35:03+00:00</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="n"/>
       <c r="E25" s="3" t="inlineStr">
         <is>
           <t>So many Capi SWE Intern Offers!</t>
@@ -2764,14 +2740,10 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="3" t="inlineStr"/>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-lax3-1.cdninstagram.com/v/t51.82787-15/814768840_18087214964678962_300587807414299988_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4ODQyNDc2MjY2MTAyNzcwOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=pKt1LD4ViCkQ7kNvwHhUYXn&amp;_nc_oc=AdoZi4VEBt8BaXpB0z8F0TF3U5JeEdxHdA8NsWQJkRN6rlYTzjev8WeKUtvI-bYvE4Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=8&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=57T-qu4SHiuDf3cdAqvPAQ&amp;_nc_ss=7e3ba&amp;oh=00_AQLvf2PVnBzkD4XLel30rzSzlykJKRBEJNFkeZgZi9hLqw&amp;oe=6AB28EC4</t>
-        </is>
-      </c>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="n"/>
+      <c r="K25" s="3" t="inlineStr"/>
       <c r="L25" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -2814,7 +2786,7 @@
     <row r="26" ht="45" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>a9b64af528ee883ce2e6</t>
+          <t>501b0313e294a2fd2587</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2827,10 +2799,10 @@
           <t>2026-09-17T21:45:38+00:00</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr"/>
+      <c r="D26" s="3" t="n"/>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>This is why | care so much about making opportunity</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -2838,15 +2810,11 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr"/>
-      <c r="I26" s="3" t="inlineStr"/>
-      <c r="J26" s="3" t="inlineStr"/>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-lax7-1.cdninstagram.com/v/t51.82787-15/814695558_18087220370678962_7673257959919455186_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4ODQ2MDI4NjYyNDg0MzIxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=cjWX3Z2jFwgQ7kNvwH9pLS-&amp;_nc_oc=AdqgF0ddwV2dIw-1ayYY4qoYOUqWJAx1FiOj07Fx-aRtVpy5QP5yuaWa1cVmo5R4C2o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=8&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_gid=57T-qu4SHiuDf3cdAqvPAQ&amp;_nc_ss=7e3ba&amp;oh=00_AQJNhrc1ufjC65SBYeMchRTEc47y9jkI0LJ_GgMszMOBtg&amp;oe=6AB299D1</t>
-        </is>
-      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="n"/>
+      <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="inlineStr"/>
       <c r="L26" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -2914,7 +2882,7 @@
     <row r="27" ht="45" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>1b30f086603953353336</t>
+          <t>4837b3f99756fdf407bd</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2927,7 +2895,7 @@
           <t>2026-09-17T21:49:10+00:00</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="inlineStr">
         <is>
           <t>career fair but we are definitely</t>
@@ -2938,15 +2906,11 @@
           <t>Recruiting / Career Event</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="3" t="inlineStr"/>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-lax7-1.cdninstagram.com/v/t51.82787-15/814229705_18087220610678962_85839488440364683_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4ODQ2MjA2ODY5MjM1ODkwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=8_nKWHMwEBkQ7kNvwE5b4c3&amp;_nc_oc=AdpB0ezYJ4O4C44dy9AN2cWL--QsPKjT2fTj7lRnvjWm9oxeWz1KUB4as5GegKfz5C4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=8&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_gid=57T-qu4SHiuDf3cdAqvPAQ&amp;_nc_ss=7e3ba&amp;oh=00_AQIxDW1oPVRudABN4ygQHaiQEqwa1C0JJZJkTvYlrmU-hg&amp;oe=6AB2850B</t>
-        </is>
-      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="inlineStr"/>
       <c r="L27" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -2997,7 +2961,7 @@
     <row r="28" ht="45" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>e36f1d7bf2d9f8467ff2</t>
+          <t>d7c6eba27b4b38ca567d</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -3017,7 +2981,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Apple — Summary Fa your georgia tech friends to rsvp!</t>
+          <t>Apple — Internship</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -3025,14 +2989,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="n"/>
       <c r="H28" s="3" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr"/>
-      <c r="J28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="n"/>
       <c r="K28" s="4" t="inlineStr">
         <is>
           <t>https://jobs.apple.com/en-us/details/200674756/2026-fall-georgia-tech-intern-event</t>
@@ -3086,12 +3050,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="n"/>
     </row>
     <row r="29" ht="45" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>ffb84d4747fda0babf1a</t>
+          <t>d76907e49f6b13cc5bbe</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3111,7 +3075,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Google — internship opportunities. Below is the list</t>
+          <t>Google — Research</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -3129,13 +3093,9 @@
           <t>Summer 2027, Fall 2026</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="3" t="inlineStr"/>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-lax3-1.cdninstagram.com/v/t51.82787-15/813987078_18087223502678962_4329236367136784088_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk4ODQ4MDE4OTkzMjkyMjYzMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjExNzAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=5_VsXXxgyvgQ7kNvwEssCk8&amp;_nc_oc=Adr6BZMs2flNzN0j1d78Nwoy6OVocjXigeSa55pVgsI8W1ymvNEnUnd4djr4bNB4_ak&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=8&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=57T-qu4SHiuDf3cdAqvPAQ&amp;_nc_ss=7e3ba&amp;oh=00_AQL2VofTc-8xf8df7dQeU6rqj2HNpVYP2tolkUfgjTUvVw&amp;oe=6AB295D1</t>
-        </is>
-      </c>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="inlineStr"/>
       <c r="L29" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -3195,12 +3155,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="n"/>
     </row>
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>0a558af512ea4df66870</t>
+          <t>7f635d4a78692389282e</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -3213,7 +3173,7 @@
           <t>2026-09-17T22:28:11+00:00</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr"/>
+      <c r="D30" s="3" t="n"/>
       <c r="E30" s="3" t="inlineStr">
         <is>
           <t>you use etc. when you submit</t>
@@ -3224,15 +3184,11 @@
           <t>Job / Hiring</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr"/>
-      <c r="H30" s="3" t="inlineStr"/>
-      <c r="I30" s="3" t="inlineStr"/>
-      <c r="J30" s="3" t="inlineStr"/>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-lax7-1.cdninstagram.com/v/t51.82787-15/815037784_18087223682678962_2026450667892772629_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4ODQ4MTcwOTEzNDk0NTY0MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=XYnJtxn22t0Q7kNvwHHtjw_&amp;_nc_oc=Adr_rZrNbmkKJvc9bYKw4tPO06dwAufnM1Ys9_y3H0vvNfb1-W04myUxVraZxtx4yjg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=8&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_gid=57T-qu4SHiuDf3cdAqvPAQ&amp;_nc_ss=7e3ba&amp;oh=00_AQKlFL4-RwwZNk0CNOB4fOH5McCBCJdF0_fStTyfQuL3mw&amp;oe=6AB299A1</t>
-        </is>
-      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+      <c r="I30" s="3" t="n"/>
+      <c r="J30" s="3" t="n"/>
+      <c r="K30" s="3" t="inlineStr"/>
       <c r="L30" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -3290,12 +3246,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="n"/>
     </row>
     <row r="31" ht="45" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>cdf93a31b6975ceec194</t>
+          <t>c5900336a265064e119c</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -3315,7 +3271,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Jane Street — Internship, May-Augus</t>
+          <t>Jane Street — Internship</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -3323,17 +3279,17 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
       <c r="I31" s="3" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="n"/>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/position/8621552002/?fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacuafr6QJ-Ce3fYoovQx4RP3TEBCpYp9fFl91lkpN9kY9jzuLwu_U_Uy2yZLA_aem_GQnIJuAmSUwHrXWH9OMamA</t>
+          <t>https://www.janestreet.com/join-jane-street/position/8621552002</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3383,12 +3339,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="n"/>
     </row>
     <row r="32" ht="45" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2a604f0a8f72c26071ba</t>
+          <t>a442e48757ea792dbe08</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -3408,7 +3364,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Amazon — All intern roles require in-person work and are</t>
+          <t>Amazon — Software Engineering</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -3426,11 +3382,11 @@
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr"/>
-      <c r="J32" s="3" t="inlineStr"/>
+      <c r="I32" s="3" t="n"/>
+      <c r="J32" s="3" t="n"/>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://www.amazon.jobs/en/jobs/10552937/software-development-engineer-internship-summer-2027-usa?fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafKvJ-vOJ_8GtQixvwhpq6Ze0-xRf6cDJ1If08gQvDHOh0X7xdOnNomN0fvpg_aem_1bV3C5y6g_9Cs53941mPiw</t>
+          <t>https://www.amazon.jobs/en/jobs/10552937/software-development-engineer-internship-summer-2027-usa</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -3483,12 +3439,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="n"/>
     </row>
     <row r="33" ht="45" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>e446458b990486b6fc78</t>
+          <t>5ae56c54847025263c17</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -3501,10 +3457,10 @@
           <t>2026-09-17T23:15:52+00:00</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="n"/>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>@ JP MORGAN MLE INTERN</t>
+          <t>Product Management</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -3522,11 +3478,11 @@
           <t>2027, 2026</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr"/>
-      <c r="J33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="n"/>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>https://jpmc.fa.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1001/job/210790885/?utm_medium=zero2sudo&amp;utm_source=zero2sudo&amp;fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAae4SUrhvlIq7XohjPKQbjrUyLm-4fJX-2w-YoEHr5IEqmYtxYqaFOQR9EK7qA_aem_Su0FMgp0ZLrzh2Xp3uFWAw</t>
+          <t>https://jpmc.fa.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1001/job/210790885</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -3579,12 +3535,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="n"/>
     </row>
     <row r="34" ht="45" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>091b866a8ab4a371c44a</t>
+          <t>39cbe517a4c307e1e186</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -3597,7 +3553,7 @@
           <t>2026-09-17T23:17:36+00:00</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr"/>
+      <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="inlineStr">
         <is>
           <t>User Quant Firm SWE Intern semeliie</t>
@@ -3623,10 +3579,10 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr"/>
+      <c r="J34" s="3" t="n"/>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://tower-research.com/open-positions/?gh_jid=8212158&amp;fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafkpiE1ADEJgdro46AUukp4S1c7X6Tsknxj0BCtyH-1O0q_nYlkhaG5bqhLEQ_aem_33NobttIShHrjtrQIfyBcQ</t>
+          <t>https://tower-research.com/open-positions?gh_jid=8212158</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -3677,12 +3633,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="n"/>
     </row>
     <row r="35" ht="45" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>02c1e895979222046d1e</t>
+          <t>d21347488dc862530bdd</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -3702,7 +3658,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Genevatrading — (2) GENEVA TRADING SWE INTERN</t>
+          <t>Genevatrading — Software Engineering</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -3725,10 +3681,10 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="n"/>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/genevatrading/jobs/5240107007?fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafKOilFJANNgjAK8i5Xz60-zqba3vrG0B4_EaFJN_z668B4AZTmOuUr5QS-xA_aem_lusdNExhOfSmeiINBhwMXw</t>
+          <t>https://job-boards.greenhouse.io/genevatrading/jobs/5240107007</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -3778,12 +3734,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="n"/>
     </row>
     <row r="36" ht="45" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>db2508abdff47110838f</t>
+          <t>507e995a44fdc316f7af</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -3796,10 +3752,10 @@
           <t>2026-09-17T23:22:41+00:00</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr"/>
+      <c r="D36" s="3" t="n"/>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>As an Al-Enabled Full Stack Software Engineering Intern,</t>
+          <t>Software Engineering</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -3817,11 +3773,11 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr"/>
-      <c r="J36" s="3" t="inlineStr"/>
+      <c r="I36" s="3" t="n"/>
+      <c r="J36" s="3" t="n"/>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>https://uscareers-lennox.icims.com/jobs/54888/job?mobile=true&amp;needsRedirect=false&amp;fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafsRB0-BGwnQXsROGbgn90SEljPG-vI0pHX2pqjUloef2uJLpRyov12qnvbJA_aem_gZzmY_13u1vDHcZ5RfF9gQ</t>
+          <t>https://uscareers-lennox.icims.com/jobs/54888/job?mobile=true&amp;needsRedirect=false</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -3877,12 +3833,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="n"/>
     </row>
     <row r="37" ht="45" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>e8401f48ef4c6e2bb66b</t>
+          <t>14ef4ac48c575f1dd069</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -3902,7 +3858,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Amazon — Apply now</t>
+          <t>Amazon — Software Engineering</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -3920,11 +3876,11 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr"/>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="3" t="n"/>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>https://www.amazon.jobs/en/jobs/10550549/customer-solutions-manager-intern-awsi-2027?cmpid=SPLICX0248M&amp;ss=paid&amp;utm_campaign=cxro&amp;utm_content=job_posting&amp;utm_medium=social_media&amp;utm_source=zero2sudo&amp;fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadZNaBxhdV1zdgE5m487a6gxy0t_gZ6S162HYi7dcJ9s4pQKUttQIGr3LyHOA_aem_u_qKRfEy1SbqjuR4OkR-qw</t>
+          <t>https://www.amazon.jobs/en/jobs/10550549/customer-solutions-manager-intern-awsi-2027?cmpid=SPLICX0248M&amp;ss=paid</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -3981,12 +3937,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="n"/>
     </row>
     <row r="38" ht="45" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>105137d19244b8fa6f73</t>
+          <t>bc3c542ea0a3726b689e</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -4006,7 +3962,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Stripe New Grad SWE - CURRENT GRADS</t>
+          <t>Stripe — Software Engineering</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -4019,12 +3975,12 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr"/>
-      <c r="I38" s="3" t="inlineStr"/>
-      <c r="J38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="n"/>
+      <c r="I38" s="3" t="n"/>
+      <c r="J38" s="3" t="n"/>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>https://stripe.com/careers/listing/software-engineer-early-career-immediate-start/8212508?gh_jid=8212508&amp;fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeS9-3wMwEr2z4VUPiiOPIc-g9AOf3FmyuPiB5CcVBuDNH0dHZ_l0vZ9yveNQ_aem_nTbCzL3M4WI6fSEU0LfnDw</t>
+          <t>https://stripe.com/careers/listing/software-engineer-early-career-immediate-start/8212508?gh_jid=8212508</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -4071,12 +4027,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="n"/>
     </row>
     <row r="39" ht="45" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>31faafd7da662c6fa78c</t>
+          <t>3d0187e32613e4b67336</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -4096,7 +4052,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Amazon — 1A20N SWE INTERN 2027 &amp;</t>
+          <t>Amazon — Software Engineering</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -4114,13 +4070,9 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="3" t="inlineStr"/>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-lax3-2.cdninstagram.com/v/t51.82787-15/814779823_18087230822678962_7861859619461180195_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4ODUxNjkwOTI4NjA1MTY1Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=K22FdASUScsQ7kNvwFAXeWO&amp;_nc_oc=AdrlL8reucHrEu412ewuNWOmkwOel2sO03HaXr_4S_8GSzSFhj-MivzKX74nb5VDoEE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=8&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=57T-qu4SHiuDf3cdAqvPAQ&amp;_nc_ss=7e3ba&amp;oh=00_AQJkhH60oGUjxiKJnNPinigBUPa1QRnO_rCkvxaZHqwYxw&amp;oe=6AB28C0F</t>
-        </is>
-      </c>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="inlineStr"/>
       <c r="L39" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -4173,7 +4125,7 @@
     <row r="40" ht="45" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>5cad12d5263039d2a750</t>
+          <t>28bf99b5659b477321cd</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -4186,10 +4138,10 @@
           <t>2026-09-17T23:39:22+00:00</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr"/>
+      <c r="D40" s="3" t="n"/>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>if you intern here, pls put me on your</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -4197,17 +4149,17 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="n"/>
       <c r="H40" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr"/>
-      <c r="J40" s="3" t="inlineStr"/>
+      <c r="I40" s="3" t="n"/>
+      <c r="J40" s="3" t="n"/>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>https://fairlife.com/career-opportunities/?fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeE8foehH2yoTK--OZzqa4YoU4BpueplCO_FtI0TsWXTtiu9bZR-A1IdR9k8g_aem_oaGy81tBjDJPo8A428hDyA&amp;utm_id=97760_v0_s00_e0_tv6_a1denngsc6gtwx</t>
+          <t>https://fairlife.com/career-opportunities</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -4250,12 +4202,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="n"/>
     </row>
     <row r="41" ht="45" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>9b40f464b60cc33f1677</t>
+          <t>924e3906701a97e1ef33</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -4288,16 +4240,16 @@
           <t>Product Management</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="inlineStr">
         <is>
           <t>New York, NYC</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr"/>
+      <c r="J41" s="3" t="n"/>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>https://www.gem.com/form?formID=4928fae1-3247-4eb2-9752-e5dfc087a4c1&amp;fbclid=PAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaft9G-bfpRwmZTqGopgopd6uB8YSxuTCNDz40hW5CHv10Mhn8tBcO4_bIjI8w_aem_OkZn7yz3HDeH6jKZOFE8wA</t>
+          <t>https://www.gem.com/form?formID=4928fae1-3247-4eb2-9752-e5dfc087a4c1</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -4351,909 +4303,20 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="45" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>314f5c90e2eca63ec5e4</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T03:55:59.132604+00:00</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17T14:48:23+00:00</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>NVIDIA Ignite Internship releases 10/5</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="3" t="inlineStr"/>
-      <c r="I42" s="3" t="inlineStr"/>
-      <c r="J42" s="3" t="inlineStr"/>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dfw5-1.cdninstagram.com/v/t51.82787-15/814875022_18087172547678962_8331711395526830193_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4ODI1MDI4MjU4ODMyMjY1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=0lQzvtPz4T8Q7kNvwHCmzto&amp;_nc_oc=AdqbHkWTew8g-pvDOcQ7u7I9Zlgvh21KFC16yyZK0sq59Cll0pfbwzqE_5J3idcA5Ag&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQJSzB6lC_tMcAuut_QC3HvLF1mZaTfmuN3IGHFQy4ePSQ&amp;oe=6AB29450</t>
-        </is>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/stories/zero2sudo/</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t>NVIDIA Ignite Internship releases 10/5
-Turn on your notifications for my account!
-Hey there zero2sudo. | remember
-you mentioning that NVIDIA
-Ignite is going to be released in
-early October. | just got an email
-saying It will be on the 5th
-https://scontent-dfw5-1.cdninstagram.com/v/t51.82787-15/814875022_18087172547678962_8331711395526830193_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4ODI1MDI4MjU4ODMyMjY1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=0lQzvtPz4T8Q7kNvwHCmzto&amp;_nc_oc=AdqbHkWTew8g-pvDOcQ7u7I9Zlgvh21KFC16yyZK0sq59Cll0pfbwzqE_5J3idcA5Ag&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQJSzB6lC_tMcAuut_QC3HvLF1mZaTfmuN3IGHFQy4ePSQ&amp;oe=6AB29450
-https://scontent-dfw5-1.cdninstagram.com/v/t51.82787-15/814875022_18087172547678962_8331711395526830193_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk4ODI1MDI4MjU4ODMyMjY1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=0lQzvtPz4T8Q7kNvwHCmzto&amp;_nc_oc=AdqbHkWTew8g-pvDOcQ7u7I9Zlgvh21KFC16yyZK0sq59Cll0pfbwzqE_5J3idcA5Ag&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQIhOBjuFed24yHd6OccDaCRbuDP_jK_Fxqa3avKaJPCjQ&amp;oe=6AB29450
-https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwEdRcyz&amp;_nc_oc=Adqw8M_x9B-a8shtOG5wRrb9an7G9olGpS9_wQd75NfCA1HGhLaideM0LC7_0tGzj_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKjZ8LuZIyQWmMhzZRTIIXPovMdv5VlfhbUe2vSoVvRTA&amp;oe=6AB27099</t>
-        </is>
-      </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr"/>
-    </row>
-    <row r="43" ht="45" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>f76cd1342a4d1945eb27</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T03:56:06.101600+00:00</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17T15:14:38+00:00</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>Microsoft SWE Intern Offer + Process!</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>Software Engineering</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>Summer 2027</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr"/>
-      <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dfw5-2.cdninstagram.com/v/t51.82787-15/813634716_18087176735678962_8479740632337180657_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4ODI2MzQ5NDczOTg1NTczOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=00WHMxCXizYQ7kNvwGQInUv&amp;_nc_oc=AdocJ6NuB8k-AoviUantdlwnmlMeE9r1u24mtpyK6Xw-RIzvM65J_qyjb1OnxhZb1yA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQIWpRoM3bL_hWlAaIG2tdSjAIMZ-Ktp5xgY_ZxExFGVYA&amp;oe=6AB2A380</t>
-        </is>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/stories/zero2sudo/</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t>Microsoft SWE Intern Offer + Process!
-Intern Summer 2027, applied as
-soon as | saw your story!
-OA was a standard leetcode easy
-and medium similar to what
-everyone else has been saying
-with the second problem having
-that Al assistant
-v
-First interview had some system
-design, leetcode, and general
-trivia
-Ld
-Second interview was purely
-talking about past experiences
-along with some talk about how |
-use Al to code but it was a super
-chill convo, didn’t feel like an
-interview
-https://scontent-dfw5-2.cdninstagram.com/v/t51.82787-15/813634716_18087176735678962_8479740632337180657_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4ODI2MzQ5NDczOTg1NTczOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=00WHMxCXizYQ7kNvwGQInUv&amp;_nc_oc=AdocJ6NuB8k-AoviUantdlwnmlMeE9r1u24mtpyK6Xw-RIzvM65J_qyjb1OnxhZb1yA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQIWpRoM3bL_hWlAaIG2tdSjAIMZ-Ktp5xgY_ZxExFGVYA&amp;oe=6AB2A380
-https://scontent-dfw5-2.cdninstagram.com/v/t51.82787-15/813634716_18087176735678962_8479740632337180657_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk4ODI2MzQ5NDczOTg1NTczOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=00WHMxCXizYQ7kNvwGQInUv&amp;_nc_oc=AdocJ6NuB8k-AoviUantdlwnmlMeE9r1u24mtpyK6Xw-RIzvM65J_qyjb1OnxhZb1yA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQINzKgI3MC1sdOucq-eP4llsOaq6g_uuvlLUpsWYlapgA&amp;oe=6AB2A380
-https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwEdRcyz&amp;_nc_oc=Adqw8M_x9B-a8shtOG5wRrb9an7G9olGpS9_wQd75NfCA1HGhLaideM0LC7_0tGzj_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKjZ8LuZIyQWmMhzZRTIIXPovMdv5VlfhbUe2vSoVvRTA&amp;oe=6AB27099</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44" ht="45" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>4bacd493ca4209df0e9b</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T03:56:17.935509+00:00</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17T16:33:16+00:00</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>(new grad swe) yet this year?</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>New Grad / Early Career</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>Software Engineering</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="3" t="inlineStr"/>
-      <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dfw5-2.cdninstagram.com/v/t51.82787-15/814453000_18087186893678962_2860711254553635645_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4ODMwMzA3MjYyMDM1NTkyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=Kqyif5gxD2UQ7kNvwGrQoN-&amp;_nc_oc=AdpXBVwHSn9OBSr59M00r-W0EnYqJyiF_aC1h_Lt4zXKuOptM0oys_UGzBpCeFAZu8Y&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQJYpGfIpiX0j3gyufnEUPSwujZF3lp8kRfx2-SfFf2fxw&amp;oe=6AB29044</t>
-        </is>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/stories/zero2sudo/</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t>More Cap1 TIP offers! Has anyone gotten TDP
-(new grad swe) yet this year?
-Replied to your story
-Yo | got ci TIP cuz of ur story.
-And the info u dropped was
-exactly what the process was
-like.
-Thank you
-~@
-LFG! im so happy when people
-read the stories and highlights
-and get offers ® there's def
-something about high agency ppl
-who consume info and apply it
-properly and landing roles!
-https://scontent-dfw5-2.cdninstagram.com/v/t51.82787-15/814453000_18087186893678962_2860711254553635645_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4ODMwMzA3MjYyMDM1NTkyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=Kqyif5gxD2UQ7kNvwGrQoN-&amp;_nc_oc=AdpXBVwHSn9OBSr59M00r-W0EnYqJyiF_aC1h_Lt4zXKuOptM0oys_UGzBpCeFAZu8Y&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQJYpGfIpiX0j3gyufnEUPSwujZF3lp8kRfx2-SfFf2fxw&amp;oe=6AB29044
-https://scontent-dfw5-2.cdninstagram.com/v/t51.82787-15/814453000_18087186893678962_2860711254553635645_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk4ODMwMzA3MjYyMDM1NTkyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=Kqyif5gxD2UQ7kNvwGrQoN-&amp;_nc_oc=AdpXBVwHSn9OBSr59M00r-W0EnYqJyiF_aC1h_Lt4zXKuOptM0oys_UGzBpCeFAZu8Y&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQKzt6EFQ7rBlpyBBx_IwzIWSM_qcMutuHsAfaFz1Gi8_Q&amp;oe=6AB29044
-https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwEdRcyz&amp;_nc_oc=Adqw8M_x9B-a8shtOG5wRrb9an7G9olGpS9_wQd75NfCA1HGhLaideM0LC7_0tGzj_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKjZ8LuZIyQWmMhzZRTIIXPovMdv5VlfhbUe2vSoVvRTA&amp;oe=6AB27099</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr"/>
-    </row>
-    <row r="45" ht="45" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>c716bcad601a9d9ab8ce</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T03:56:25.967828+00:00</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17T17:25:39+00:00</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>- Hiring happens 1-6 months</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>Job / Hiring</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr"/>
-      <c r="I45" s="3" t="inlineStr"/>
-      <c r="J45" s="3" t="inlineStr"/>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dfw6-2.cdninstagram.com/v/t51.82787-15/788924699_18087195047678962_4065300646317777670_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4ODMyOTQzNjcxNjUxMDE3Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=r1KisgbLBN0Q7kNvwGpdCaD&amp;_nc_oc=AdodVmaXg5vc8Ho_zZ3Mm8rqJD-iYH7jVBG7_BHU3uVxfw2beh9I0a5PTOS__-FZ_kQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw6-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQLwhQl2VA-wUB3JfXqeF5a1-Fs-FM7v5Cvk9dys3ot-KA&amp;oe=6AB29B46</t>
-        </is>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/stories/zero2sudo/</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t>Hey Sudo, recap from the Tesla
-event at Chapel Hill:
-- Tailor your resume to the
-specific role, have similar
-keywords/skills/projects as they
-mention in the role
-- WHO method (What, How,
-Outcome)
-- Hiring happens 1-6 months
-before role start
-- Be yourself as much as possible
-in interviews
-- Referrals help, even from
-interns (goes to same place)
-- Best of the Best - why are you
-the best person that we should
-hire? (goes all the way up
-command chain)
-https://scontent-dfw6-2.cdninstagram.com/v/t51.82787-15/788924699_18087195047678962_4065300646317777670_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4ODMyOTQzNjcxNjUxMDE3Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=r1KisgbLBN0Q7kNvwGpdCaD&amp;_nc_oc=AdodVmaXg5vc8Ho_zZ3Mm8rqJD-iYH7jVBG7_BHU3uVxfw2beh9I0a5PTOS__-FZ_kQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw6-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQLwhQl2VA-wUB3JfXqeF5a1-Fs-FM7v5Cvk9dys3ot-KA&amp;oe=6AB29B46
-https://scontent-dfw6-2.cdninstagram.com/v/t51.82787-15/788924699_18087195047678962_4065300646317777670_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4ODMyOTQzNjcxNjUxMDE3Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=r1KisgbLBN0Q7kNvwGpdCaD&amp;_nc_oc=AdodVmaXg5vc8Ho_zZ3Mm8rqJD-iYH7jVBG7_BHU3uVxfw2beh9I0a5PTOS__-FZ_kQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQLDnG6D0On1tMrP5sUTsdtW39-tpQq7PkNZHeviJSdYUg&amp;oe=6AB29B46
-https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwEdRcyz&amp;_nc_oc=Adqw8M_x9B-a8shtOG5wRrb9an7G9olGpS9_wQd75NfCA1HGhLaideM0LC7_0tGzj_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKjZ8LuZIyQWmMhzZRTIIXPovMdv5VlfhbUe2vSoVvRTA&amp;oe=6AB27099</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q45" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46" ht="45" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>d8f744b57e2f32c28c9b</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T03:56:28.030321+00:00</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17T17:37:26+00:00</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>Google — webinar you posted JA, J,</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>New Grad / Early Career</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>Software Engineering</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr"/>
-      <c r="I46" s="3" t="inlineStr"/>
-      <c r="J46" s="3" t="inlineStr"/>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dfw5-2.cdninstagram.com/v/t51.82787-15/809209168_18087197012678962_1565929461932431535_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4ODMzNTM2NjgwNDgwMjc2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=hyMuw1kltl4Q7kNvwGDmDfE&amp;_nc_oc=AdqP3Ta2dI1g0FVH7QyEE7uEOkgbBa3Q4hKWXs3n0cE6DhBALl74f1QRyALqnOSfz6A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQIostWAzN_LeyMnpXj1RMvSP1_Q_e9HqHU6OvxXwXkAiA&amp;oe=6AB29612</t>
-        </is>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/stories/zero2sudo/</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t>Google SWE New Grad RO!!!
-Got google return offer thank
-you for all you do for the cs
-students! Got my google
-interview last year because of a
-webinar you posted JA, J,
-| only know I'm matched to
-Youtube they said i won't be
-matched till 8 weeks b4 my start
-date
-https://scontent-dfw5-2.cdninstagram.com/v/t51.82787-15/809209168_18087197012678962_1565929461932431535_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4ODMzNTM2NjgwNDgwMjc2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=hyMuw1kltl4Q7kNvwGDmDfE&amp;_nc_oc=AdqP3Ta2dI1g0FVH7QyEE7uEOkgbBa3Q4hKWXs3n0cE6DhBALl74f1QRyALqnOSfz6A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQIostWAzN_LeyMnpXj1RMvSP1_Q_e9HqHU6OvxXwXkAiA&amp;oe=6AB29612
-https://scontent-dfw5-2.cdninstagram.com/v/t51.82787-15/809209168_18087197012678962_1565929461932431535_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk4ODMzNTM2NjgwNDgwMjc2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=hyMuw1kltl4Q7kNvwGDmDfE&amp;_nc_oc=AdqP3Ta2dI1g0FVH7QyEE7uEOkgbBa3Q4hKWXs3n0cE6DhBALl74f1QRyALqnOSfz6A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQJzFWVHc5WeuM08e47_3LCv6Ija7-EHDaKsxGpsey7Cag&amp;oe=6AB29612
-https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwEdRcyz&amp;_nc_oc=Adqw8M_x9B-a8shtOG5wRrb9an7G9olGpS9_wQd75NfCA1HGhLaideM0LC7_0tGzj_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKjZ8LuZIyQWmMhzZRTIIXPovMdv5VlfhbUe2vSoVvRTA&amp;oe=6AB27099</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr"/>
-    </row>
-    <row r="47" ht="45" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>5ec01f615ec61f7238aa</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T03:56:45.854899+00:00</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17T20:13:34+00:00</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>Adobe — also no sign up form</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr"/>
-      <c r="H47" s="3" t="inlineStr"/>
-      <c r="I47" s="3" t="inlineStr"/>
-      <c r="J47" s="3" t="inlineStr"/>
-      <c r="K47" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/813976257_18087212606678962_600677638285630895_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4ODQxMzk1MjcwNjYxNTUwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=mB7SsEg8mAcQ7kNvwH7ifI4&amp;_nc_oc=AdrgaQy7PBD-5nGixGfL9Zm9M9qCO-UwaBNx4BPlBGPKDnHMEuxIZR6RGEskG80WK3M&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQLcplPJMSsGcX-eInoBlbJjbtdXSHaxWs8IMJ0bNGTzjw&amp;oe=6AB27AB6</t>
-        </is>
-      </c>
-      <c r="L47" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/stories/zero2sudo/</t>
-        </is>
-      </c>
-      <c r="M47" s="3" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="N47" s="3" t="inlineStr">
-        <is>
-          <t>Adobe Intern
-@ rolling bests)!
-epee matters more than referrals
-aa tor Adobe!
-in the adobe event they also said
-that referrals matter but speed
-matters more and for ai they said
-that they are only gonna use it in
-a few questions and not for all in
-the interviews and she said that
-they are gonna wrap up their
-hiring around march
-| wasn’t there for the first 20ish
-minutes for the event so idk what
-happened there but there was
-also no sign up form
-she also said that they don’t use
-Al to look through candidates
-https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/813976257_18087212606678962_600677638285630895_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4ODQxMzk1MjcwNjYxNTUwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=mB7SsEg8mAcQ7kNvwH7ifI4&amp;_nc_oc=AdrgaQy7PBD-5nGixGfL9Zm9M9qCO-UwaBNx4BPlBGPKDnHMEuxIZR6RGEskG80WK3M&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQLcplPJMSsGcX-eInoBlbJjbtdXSHaxWs8IMJ0bNGTzjw&amp;oe=6AB27AB6
-https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/813976257_18087212606678962_600677638285630895_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk4ODQxMzk1MjcwNjYxNTUwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=mB7SsEg8mAcQ7kNvwH7ifI4&amp;_nc_oc=AdrgaQy7PBD-5nGixGfL9Zm9M9qCO-UwaBNx4BPlBGPKDnHMEuxIZR6RGEskG80WK3M&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQJmDHRanLsPRRuz018MKNgajUmLnPE_BRNLe2hAqyiJ5Q&amp;oe=6AB27AB6
-https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwEdRcyz&amp;_nc_oc=Adqw8M_x9B-a8shtOG5wRrb9an7G9olGpS9_wQd75NfCA1HGhLaideM0LC7_0tGzj_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKjZ8LuZIyQWmMhzZRTIIXPovMdv5VlfhbUe2vSoVvRTA&amp;oe=6AB27099</t>
-        </is>
-      </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P47" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q47" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48" ht="45" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>406eecd407d7e310c1bb</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T03:56:54.958591+00:00</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17T20:35:03+00:00</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr"/>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>So many Capi SWE Intern Offers!</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>Software Engineering</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr"/>
-      <c r="I48" s="3" t="inlineStr"/>
-      <c r="J48" s="3" t="inlineStr"/>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/814768840_18087214964678962_300587807414299988_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4ODQyNDc2MjY2MTAyNzcwOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=pKt1LD4ViCkQ7kNvwGmc1Xt&amp;_nc_oc=AdoWWXXPfejqt7fr8TqU4wiOJQL5Kapkkj3oZVJYjGdMXzvek1-BVeQqoMxaOTP3aSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQLfVG2TXYuw4-wQ30d9xFs07gxCXJmKpbd9Zr-A8UPhHQ&amp;oe=6AB28EC4</t>
-        </is>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/stories/zero2sudo/</t>
-        </is>
-      </c>
-      <c r="M48" s="3" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="N48" s="3" t="inlineStr">
-        <is>
-          <t>Replied to your story
-got c1tip as well, helpful info on
-the ai assist ty. litearlly heard
-back in less than 24 hours as well
-So many Capi SWE Intern Offers!
-https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/814768840_18087214964678962_300587807414299988_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4ODQyNDc2MjY2MTAyNzcwOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=pKt1LD4ViCkQ7kNvwGmc1Xt&amp;_nc_oc=AdoWWXXPfejqt7fr8TqU4wiOJQL5Kapkkj3oZVJYjGdMXzvek1-BVeQqoMxaOTP3aSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQLfVG2TXYuw4-wQ30d9xFs07gxCXJmKpbd9Zr-A8UPhHQ&amp;oe=6AB28EC4
-https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/814768840_18087214964678962_300587807414299988_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk4ODQyNDc2MjY2MTAyNzcwOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=pKt1LD4ViCkQ7kNvwGmc1Xt&amp;_nc_oc=AdoWWXXPfejqt7fr8TqU4wiOJQL5Kapkkj3oZVJYjGdMXzvek1-BVeQqoMxaOTP3aSw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQKK9OBBGgHLdlREGZEWhyBfKCkjYAZhPcMzTH2etxQsrg&amp;oe=6AB28EC4
-https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwEdRcyz&amp;_nc_oc=Adqw8M_x9B-a8shtOG5wRrb9an7G9olGpS9_wQd75NfCA1HGhLaideM0LC7_0tGzj_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKjZ8LuZIyQWmMhzZRTIIXPovMdv5VlfhbUe2vSoVvRTA&amp;oe=6AB27099</t>
-        </is>
-      </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P48" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q48" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R48" s="3" t="inlineStr"/>
-    </row>
-    <row r="49" ht="45" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>a99c75e25c9a557a5480</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T03:57:00.309434+00:00</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17T21:45:38+00:00</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>This is why | care so much about making opportunity</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="3" t="inlineStr"/>
-      <c r="I49" s="3" t="inlineStr"/>
-      <c r="J49" s="3" t="inlineStr"/>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dfw5-1.cdninstagram.com/v/t51.82787-15/814695558_18087220370678962_7673257959919455186_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4ODQ2MDI4NjYyNDg0MzIxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=cjWX3Z2jFwgQ7kNvwFQwL12&amp;_nc_oc=AdpT1A9Oi-S9coUbMd4aNFpXGgvavHvrRTkuWPbPVSiVxtBpWJNvyhWFrgSD_wWpd1k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQLt2FiRSa8REgSoEbK6HJbEM2xWYlfJE05brCM6MV0KZg&amp;oe=6AB299D1</t>
-        </is>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/stories/zero2sudo/</t>
-        </is>
-      </c>
-      <c r="M49" s="3" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="N49" s="3" t="inlineStr">
-        <is>
-          <t>So many non-target students made it to Bloomberg
-last year and crushed it. Never let anyone tell you
-what you deserve (unless it’s better than you
-expect), and never let where you start determine
-where you finish.
-This is why | care so much about making opportunity
-more accessible :)
-Same A, if you scroll up in
-our chat you can see | got
-headcounted initially, but
-persistence paid off
-Thanks for everything you do!
-| applied through your link last
-year.
-ae
-I'm the first ever intern at bb
-from my university purely
-because of your stories &amp;
-ae
-lets fkn go! it's super funny bc
-gatekeepers tried claiming
-people would be blacklisted for
-applying. in reality, multiple
-companies confirmed with us
-last year that they just want to
-hire competent candidates.
-good people exist anywhere,
-companies don't care about
-people "trying harder" to find an
-event link or some dumbass shit
-like that &amp; great job man :)
-https://scontent-dfw5-1.cdninstagram.com/v/t51.82787-15/814695558_18087220370678962_7673257959919455186_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4ODQ2MDI4NjYyNDg0MzIxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=cjWX3Z2jFwgQ7kNvwFQwL12&amp;_nc_oc=AdpT1A9Oi-S9coUbMd4aNFpXGgvavHvrRTkuWPbPVSiVxtBpWJNvyhWFrgSD_wWpd1k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQLt2FiRSa8REgSoEbK6HJbEM2xWYlfJE05brCM6MV0KZg&amp;oe=6AB299D1
-https://scontent-dfw5-1.cdninstagram.com/v/t51.82787-15/814695558_18087220370678962_7673257959919455186_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4ODQ2MDI4NjYyNDg0MzIxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=cjWX3Z2jFwgQ7kNvwFQwL12&amp;_nc_oc=AdpT1A9Oi-S9coUbMd4aNFpXGgvavHvrRTkuWPbPVSiVxtBpWJNvyhWFrgSD_wWpd1k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQKv6hKoYDUUuRWKaovEu-W_i3fy911SUhhyKWdW3GqDGw&amp;oe=6AB299D1
-https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwEdRcyz&amp;_nc_oc=Adqw8M_x9B-a8shtOG5wRrb9an7G9olGpS9_wQd75NfCA1HGhLaideM0LC7_0tGzj_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKjZ8LuZIyQWmMhzZRTIIXPovMdv5VlfhbUe2vSoVvRTA&amp;oe=6AB27099</t>
-        </is>
-      </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P49" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q49" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50" ht="45" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>b05a980a5e5c08b9287d</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T03:57:03.026869+00:00</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17T21:49:10+00:00</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr"/>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>career fair but we are definitely</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>Recruiting / Career Event</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr"/>
-      <c r="H50" s="3" t="inlineStr"/>
-      <c r="I50" s="3" t="inlineStr"/>
-      <c r="J50" s="3" t="inlineStr"/>
-      <c r="K50" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dfw5-1.cdninstagram.com/v/t51.82787-15/814229705_18087220610678962_85839488440364683_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4ODQ2MjA2ODY5MjM1ODkwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=8_nKWHMwEBkQ7kNvwFHtp7M&amp;_nc_oc=Adq8Vb2DwR7WFk4raII5dwO7zqnLZ11FjpaSySsL8C1v09BNzAjMd-OvEozUUr_GoqU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQJ0BfSD_GObVyneapxWhUFOmU8UAUXpUBpFC670fF8FPg&amp;oe=6AB2850B</t>
-        </is>
-      </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/stories/zero2sudo/</t>
-        </is>
-      </c>
-      <c r="M50" s="3" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="N50" s="3" t="inlineStr">
-        <is>
-          <t>ARM recruiter clarification on
-application consideration!
-Hey hey, someone flagged
-this for me, this is probably a
-misunderstanding from the
-career fair but we are definitely
-still considering applications
-from our original application
-window being open. We are
-no longer accepting new
-applications outside of career
-fair signups, that could be the
-confusion point from the fair.
-https://scontent-dfw5-1.cdninstagram.com/v/t51.82787-15/814229705_18087220610678962_85839488440364683_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4ODQ2MjA2ODY5MjM1ODkwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=8_nKWHMwEBkQ7kNvwFHtp7M&amp;_nc_oc=Adq8Vb2DwR7WFk4raII5dwO7zqnLZ11FjpaSySsL8C1v09BNzAjMd-OvEozUUr_GoqU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQJ0BfSD_GObVyneapxWhUFOmU8UAUXpUBpFC670fF8FPg&amp;oe=6AB2850B
-https://scontent-dfw5-1.cdninstagram.com/v/t51.82787-15/814229705_18087220610678962_85839488440364683_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk4ODQ2MjA2ODY5MjM1ODkwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=8_nKWHMwEBkQ7kNvwFHtp7M&amp;_nc_oc=Adq8Vb2DwR7WFk4raII5dwO7zqnLZ11FjpaSySsL8C1v09BNzAjMd-OvEozUUr_GoqU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQIBe2RX7D6PQfZ5GpMe85mCb3lbJ-gRAPPbE_xN3rABGA&amp;oe=6AB2850B
-https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwEdRcyz&amp;_nc_oc=Adqw8M_x9B-a8shtOG5wRrb9an7G9olGpS9_wQd75NfCA1HGhLaideM0LC7_0tGzj_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKjZ8LuZIyQWmMhzZRTIIXPovMdv5VlfhbUe2vSoVvRTA&amp;oe=6AB27099</t>
-        </is>
-      </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="P50" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q50" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R50" s="3" t="inlineStr"/>
-    </row>
-    <row r="51" ht="45" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>cb892eb20bb5e8bf02de</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T03:57:42.780142+00:00</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17T23:38:08+00:00</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>Amazon — 1AZ0N SWE INTERN 2027 &amp;</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>Software Engineering</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr"/>
-      <c r="J51" s="3" t="inlineStr"/>
-      <c r="K51" s="4" t="inlineStr">
-        <is>
-          <t>https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/814779823_18087230822678962_7861859619461180195_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4ODUxNjkwOTI4NjA1MTY1Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=K22FdASUScsQ7kNvwEvHaFi&amp;_nc_oc=AdoQIek4FQMqLlmJYPzidfEr7oCV4F82zJCRax858_LfrkYKuBPCI8uXwqX7MkpngfU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQJni_oy7mNWkib4ab3OL8yIdviP21Y9xzY-Z58nUm0O7g&amp;oe=6AB28C0F</t>
-        </is>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/stories/zero2sudo/</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="N51" s="3" t="inlineStr">
-        <is>
-          <t>Replied to your story
-Ask your Amazon questions!
-2027 (USA)
-Type something...
-1AZ0N SWE INTERN 2027 &amp;
-HUGE DROP @ @ @ gal
-interning at amazon rn Imk if | can
-provide any helpful info abt the
-process
-| think at this point you probbaly
-have heard it so many times but
-Leadership Principles are so so
-so important i think it helps to
-literally sit down and study them
-yessir! ty for sharing A.A.
-https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/814779823_18087230822678962_7861859619461180195_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4ODUxNjkwOTI4NjA1MTY1Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=K22FdASUScsQ7kNvwEvHaFi&amp;_nc_oc=AdoQIek4FQMqLlmJYPzidfEr7oCV4F82zJCRax858_LfrkYKuBPCI8uXwqX7MkpngfU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQJni_oy7mNWkib4ab3OL8yIdviP21Y9xzY-Z58nUm0O7g&amp;oe=6AB28C0F
-https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/814779823_18087230822678962_7861859619461180195_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk4ODUxNjkwOTI4NjA1MTY1Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=K22FdASUScsQ7kNvwEvHaFi&amp;_nc_oc=AdoQIek4FQMqLlmJYPzidfEr7oCV4F82zJCRax858_LfrkYKuBPCI8uXwqX7MkpngfU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=eHz5TcyW0mp_pt15cJ6WDA&amp;_nc_ss=7e3ba&amp;oh=00_AQI_SnA4LGBN9T2S09E-BZmktP92CboF4vixfqJC0UiyTA&amp;oe=6AB28C0F
-https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwEdRcyz&amp;_nc_oc=Adqw8M_x9B-a8shtOG5wRrb9an7G9olGpS9_wQd75NfCA1HGhLaideM0LC7_0tGzj_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKjZ8LuZIyQWmMhzZRTIIXPovMdv5VlfhbUe2vSoVvRTA&amp;oe=6AB27099</t>
-        </is>
-      </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="P51" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q51" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R51" s="3" t="inlineStr"/>
-    </row>
+      <c r="R41" s="3" t="n"/>
+    </row>
+    <row r="42" ht="45" customHeight="1"/>
+    <row r="43" ht="45" customHeight="1"/>
+    <row r="44" ht="45" customHeight="1"/>
+    <row r="45" ht="45" customHeight="1"/>
+    <row r="46" ht="45" customHeight="1"/>
+    <row r="47" ht="45" customHeight="1"/>
+    <row r="48" ht="45" customHeight="1"/>
+    <row r="49" ht="45" customHeight="1"/>
+    <row r="50" ht="45" customHeight="1"/>
+    <row r="51" ht="45" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:R51"/>
+  <autoFilter ref="A1:R41"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -5269,92 +4332,60 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4305,7 +4305,101 @@
       </c>
       <c r="R41" s="3" t="n"/>
     </row>
-    <row r="42" ht="45" customHeight="1"/>
+    <row r="42" ht="45" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>f44dafd8793e1e534a16</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:41:22.870831+00:00</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:16:39+00:00</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>machines will challenge your ideas</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>https://bloomberg.avature.net/careers/Private?jobId=21414</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Bloomberg
+2027 Software Engineer - New
+York
+Description &amp; Requirements As a
+Bloomberg engineer, you will impact
+the real world by solving complex
+problems in an ever-evolving market.
+Our engineers sit at the center of
+finance and tech where people and
+machines will challenge your ideas
+and push your engineering skills to
+the next level.We wor...
+bloomberg new grad. not sure if
+its school specific tho https://
+Bloomberg NeWorad SWE kat
+https://scontent-ord5-1.cdninstagram.com/v/t51.71878-15/815798021_4451613878428518_3929229307797770943_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4ODg2ODUyNTQyMjMwNDc0MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=qDEjTy71bXQQ7kNvwFnVmCw&amp;_nc_oc=AdrpbUESQd5xBEccY9zHK3DSmHXZup46KpP0SbY7VFeRxvbOJEwSkq9Qm9wuPN4ME3c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-1.cdninstagram.com&amp;_nc_gid=FMuDcMCe2s70jKLbDFE5pA&amp;_nc_ss=7e3ba&amp;oh=00_AQJ0l-pR3og6SCPZVvrlOfMYZBjdnCComr8MT_sDLTwx6w&amp;oe=6AB31B99
+https://scontent-ord5-1.cdninstagram.com/v/t51.71878-15/815798021_4451613878428518_3929229307797770943_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk4ODg2ODUyNTQyMjMwNDc0MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=qDEjTy71bXQQ7kNvwFnVmCw&amp;_nc_oc=AdrpbUESQd5xBEccY9zHK3DSmHXZup46KpP0SbY7VFeRxvbOJEwSkq9Qm9wuPN4ME3c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-1.cdninstagram.com&amp;_nc_gid=FMuDcMCe2s70jKLbDFE5pA&amp;_nc_ss=7e3ba&amp;oh=00_AQIfxGTd1ZRtk3XkdlaK410Epce7GuRtHsm0veuYB1Qg1g&amp;oe=6AB31B99
+https://scontent-ord5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwE0Ou4K&amp;_nc_oc=AdpQk_kx2-OALlXOk3z_BJjOdFTAD7mXXcDqatOjjyy47sySzBOwXF41z0pFW7SJlWM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQK2GecX4iFYbRdS5UgPeZoCHU3Y3rq_Hy8g5NVXTgcv7Q&amp;oe=6AB31959
+https://l.instagram.com/?u=https%3A%2F%2Fbloomberg.avature.net%2Fcareers%2FPrivate%3FjobId%3D21414%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaevSyrh8_Kchlc5mvFDYVDYHHKuUNYugBViJu7IX37WR9MNlETYfY9u4XaITQ_aem_iK6Y-ACWBjGPnCiuu8Qq5g&amp;e=AUBEbFOLF7HCsH7ehirbLkoP2Qnp3qfgOI3fCWghEvZS5otrLfZHkG0e8SqGVYMqxGzJhjGqKXlhNtS6qcdTJj70O0Jq67Mtco79aAVMsg
+https://scontent-ord5-1.cdninstagram.com/o1/v/t2/f2/m78/AQOdfmt1SXR6ChchF3oQLqhudH7B8xQPihR8AuElu0_srZ5T2xbK0wIADut5Uq0CB_N9gePjEw3OnrUcC5F2O_uOeNSQllWbwpxp4QU.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-1.cdninstagram.com&amp;_nc_ohc=mzn9AMMaanYQ7kNvwFfn4ff&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODcyOTMwNDg2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=342d1379830a5cf6&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzdENDQ5MTYxMUUxNTYzMDM5MzU4RDUwREIxNTE5MUJFX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkqOvRgpOhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=FMuDcMCe2s70jKLbDFE5pA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKbLSG-34VdpYOqnipbxLh7MMfBjLdxSWFIMTp3qu-8Cw&amp;oe=6AAF2CE6</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr"/>
+    </row>
     <row r="43" ht="45" customHeight="1"/>
     <row r="44" ht="45" customHeight="1"/>
     <row r="45" ht="45" customHeight="1"/>
@@ -4316,7 +4410,7 @@
     <row r="50" ht="45" customHeight="1"/>
     <row r="51" ht="45" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:R41"/>
+  <autoFilter ref="A1:R42"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -4386,6 +4480,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R42"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1254,7 +1254,7 @@
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="n"/>
       <c r="L9" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -1294,7 +1294,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="n"/>
     </row>
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="n"/>
       <c r="L10" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -1390,7 +1390,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="n"/>
     </row>
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -1712,7 +1712,7 @@
       <c r="H14" s="3" t="n"/>
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="n"/>
       <c r="L14" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -1760,7 +1760,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="n"/>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -1793,7 +1793,7 @@
       <c r="H15" s="3" t="n"/>
       <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="n"/>
       <c r="L15" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -1844,7 +1844,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="n"/>
     </row>
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -1885,7 +1885,7 @@
       <c r="H16" s="3" t="n"/>
       <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="n"/>
       <c r="L16" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -1928,7 +1928,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="n"/>
     </row>
     <row r="17" ht="45" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -2356,7 +2356,7 @@
       <c r="H21" s="3" t="n"/>
       <c r="I21" s="3" t="n"/>
       <c r="J21" s="3" t="n"/>
-      <c r="K21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="n"/>
       <c r="L21" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -2407,7 +2407,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="n"/>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
@@ -2743,7 +2743,7 @@
       <c r="H25" s="3" t="n"/>
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="n"/>
       <c r="L25" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -2781,7 +2781,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="n"/>
     </row>
     <row r="26" ht="45" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
@@ -2814,7 +2814,7 @@
       <c r="H26" s="3" t="n"/>
       <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="n"/>
       <c r="L26" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -2877,7 +2877,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="n"/>
     </row>
     <row r="27" ht="45" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -2910,7 +2910,7 @@
       <c r="H27" s="3" t="n"/>
       <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="inlineStr"/>
+      <c r="K27" s="3" t="n"/>
       <c r="L27" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -2956,7 +2956,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="n"/>
     </row>
     <row r="28" ht="45" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="I29" s="3" t="n"/>
       <c r="J29" s="3" t="n"/>
-      <c r="K29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="n"/>
       <c r="L29" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -3188,7 +3188,7 @@
       <c r="H30" s="3" t="n"/>
       <c r="I30" s="3" t="n"/>
       <c r="J30" s="3" t="n"/>
-      <c r="K30" s="3" t="inlineStr"/>
+      <c r="K30" s="3" t="n"/>
       <c r="L30" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n"/>
-      <c r="K39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="n"/>
       <c r="L39" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -4120,7 +4120,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="n"/>
     </row>
     <row r="40" ht="45" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
@@ -4308,7 +4308,7 @@
     <row r="42" ht="45" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>f44dafd8793e1e534a16</t>
+          <t>0a2a76f27cd629337223</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -4321,7 +4321,7 @@
           <t>2026-09-18T11:16:39+00:00</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr"/>
+      <c r="D42" s="3" t="n"/>
       <c r="E42" s="3" t="inlineStr">
         <is>
           <t>machines will challenge your ideas</t>
@@ -4342,8 +4342,8 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr"/>
-      <c r="J42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="n"/>
+      <c r="J42" s="3" t="n"/>
       <c r="K42" s="4" t="inlineStr">
         <is>
           <t>https://bloomberg.avature.net/careers/Private?jobId=21414</t>
@@ -4398,9 +4398,101 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R42" s="3" t="inlineStr"/>
-    </row>
-    <row r="43" ht="45" customHeight="1"/>
+      <c r="R42" s="3" t="n"/>
+    </row>
+    <row r="43" ht="45" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>6e6be2c58f0b7438c75d</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T17:44:23.568155+00:00</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T14:48:40+00:00</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Two Sigma</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Two Sigma — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.twosigma.com/careers/JobDetail/Houston-Texas-United-States-Software-Engineering-Full-Time-Campus-Hire-Houston/14018</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>@ careers.twosigma.com C:
+Instagram :
+Careers Portal v
+Software Engineering Full-
+Time Campus Hire (Houston)
+TX Houston
+United States
+Function
+Engineering
+Experience Level
+Early Careers
+Share this job
+Apply &gt;
+https://scontent-dfw6-2.cdninstagram.com/v/t51.71878-15/814761768_2832500993789345_4138885630878849595_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4ODk3NTIxNjQwMzIxMTMwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=45z9YqwwmlsQ7kNvwEYD42n&amp;_nc_oc=AdrxxRlIEizNoc1O6B6Wm_TDH9PYn60d9qkq_qXf9I2DSv7k6pK_t90xshpiH82x2io&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-2.cdninstagram.com&amp;_nc_gid=_HJvXbB2iTBpEzEgYcxHhw&amp;_nc_ss=7e3ba&amp;oh=00_AQIupI8BK7pPUvevvplQK_o38VJh3xV8fSgEB8Ww2bjRUw&amp;oe=6AB34064
+https://scontent-dfw6-2.cdninstagram.com/v/t51.71878-15/814761768_2832500993789345_4138885630878849595_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk4ODk3NTIxNjQwMzIxMTMwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=45z9YqwwmlsQ7kNvwEYD42n&amp;_nc_oc=AdrxxRlIEizNoc1O6B6Wm_TDH9PYn60d9qkq_qXf9I2DSv7k6pK_t90xshpiH82x2io&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-2.cdninstagram.com&amp;_nc_gid=_HJvXbB2iTBpEzEgYcxHhw&amp;_nc_ss=7e3ba&amp;oh=00_AQJl3JQe7twtYLlcXofn1p82asW1KOVPf7QRtIoCyww3yQ&amp;oe=6AB34064
+https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwFEXube&amp;_nc_oc=Adpz_CyRQp18B6vrHtHd4s9becfDXtCVB4v0hL4EpdTXKjbHdPDR17cGb0e9h-L3EKk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKOPfxUiF90e2Q8NuYj_6nKAR34YYa0joHVpeFhzQ6Nsg&amp;oe=6AB35199
+https://l.instagram.com/?u=https%3A%2F%2Fcareers.twosigma.com%2Fcareers%2FJobDetail%2FHouston-Texas-United-States-Software-Engineering-Full-Time-Campus-Hire-Houston%2F14018%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafKIwCwfnJ9zAdoa8iKhYq_jY2VY1z5KxxCfQZoGY4j9i4HbVDFgy_myczb-w_aem_MdwdutW1wxw67SPMn8Zr9g&amp;e=AUDz2_WOW-arTotkdqRTL30bxhWf6Sj_k0LDV90r6ym_lDZe6D6iqEUN5mCowWo-3X1wRBlgD3B6nNy-dd9OS49Wf-h11Oa6V86MwmrTGA
+https://scontent-dfw5-2.cdninstagram.com/o1/v/t2/f2/m78/AQNBtWb44u-YIErHFp_1yBN2S26XT55Q_rTYPafI0qM7BV0HySQ1SB3rsVib0qJxiOdJxB-iXyzOcEye8FOYUfGDkPNch5T_g-QdoAA.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ohc=Xcan3PMr2GsQ7kNvwGkivtw&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODczMjEyMTI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=6a79a9efef48cb1&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0U4NDc0MTcwNTczNDhDOEIyQTNGNDQ0RDE4OUZEOUIwX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkzI-91JShQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=_HJvXbB2iTBpEzEgYcxHhw&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLOUu6y9qQ3gXg1KKXXxT93TBo0ezGR4hw85157gmv5Iw&amp;oe=6AAF5C29</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr"/>
+    </row>
     <row r="44" ht="45" customHeight="1"/>
     <row r="45" ht="45" customHeight="1"/>
     <row r="46" ht="45" customHeight="1"/>
@@ -4410,7 +4502,7 @@
     <row r="50" ht="45" customHeight="1"/>
     <row r="51" ht="45" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:R42"/>
+  <autoFilter ref="A1:R43"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -4482,6 +4574,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId72"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -4403,7 +4403,7 @@
     <row r="43" ht="45" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>6e6be2c58f0b7438c75d</t>
+          <t>4f757090c99da1f4029f</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -4436,9 +4436,9 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr"/>
-      <c r="I43" s="3" t="inlineStr"/>
-      <c r="J43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
+      <c r="J43" s="3" t="n"/>
       <c r="K43" s="4" t="inlineStr">
         <is>
           <t>https://careers.twosigma.com/careers/JobDetail/Houston-Texas-United-States-Software-Engineering-Full-Time-Campus-Hire-Houston/14018</t>
@@ -4491,7 +4491,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="n"/>
     </row>
     <row r="44" ht="45" customHeight="1"/>
     <row r="45" ht="45" customHeight="1"/>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R43"/>
+  <dimension ref="A1:R63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4493,16 +4493,1913 @@
       </c>
       <c r="R43" s="3" t="n"/>
     </row>
-    <row r="44" ht="45" customHeight="1"/>
-    <row r="45" ht="45" customHeight="1"/>
-    <row r="46" ht="45" customHeight="1"/>
-    <row r="47" ht="45" customHeight="1"/>
-    <row r="48" ht="45" customHeight="1"/>
-    <row r="49" ht="45" customHeight="1"/>
-    <row r="50" ht="45" customHeight="1"/>
-    <row r="51" ht="45" customHeight="1"/>
+    <row r="44" ht="45" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>bb4c73a1e31623b25741</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:31:11.640439+00:00</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T17:27:11+00:00</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Robinhood</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Robinhood — Internship</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Bellevue, Menlo Park</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/robinhood/jobs/8214142?t=gh_src%3D&amp;gh_jid=8214142</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>@ Robinhood
+&lt; Back to jobs
+Offensive Security
+Intern (Summer 2027)
+© Bellevue, WA; Menlo Park, CA
+Apply
+Join us in building the
+future of finance.
+(A?) JOB-BOARDS.GREENHOUSE.IO
+inherited by younger ions in the next
+two decades. The larg nsfer of wealth
+in human history. If you’re ready to be at the
+epice . .
+meee Robinhood Security Intern
+inanc
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/817540344_3365741493598513_7535366815332864767_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5MDUwNDU1OTU2NjQ0ODkxNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=vpcnoa8d6I8Q7kNvwEDLE9-&amp;_nc_oc=AdqyDZgsURJrVXwye9y_jpoSyoyrxy8jZ23UHNJy2xEWbngGFokamcGckKwAAnBhnp4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQJMuKiA1oA_p_edCSeeAz4eCYp9dciGFrJfKHxalZlgjw&amp;oe=6AB5FA86
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/817540344_3365741493598513_7535366815332864767_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5MDUwNDU1OTU2NjQ0ODkxNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=vpcnoa8d6I8Q7kNvwEDLE9-&amp;_nc_oc=AdqyDZgsURJrVXwye9y_jpoSyoyrxy8jZ23UHNJy2xEWbngGFokamcGckKwAAnBhnp4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQKnMv_fMuYGpsXL1b5CxcsxSHng8Zw_cRc41ryvk6VupA&amp;oe=6AB5FA86
+https://scontent-lax7-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwHaI_dS&amp;_nc_oc=Adq3LGJyNFrC9-EzezVyaOsWC-5zSCe28c6wHeqJ5VQu8HMR1zTDSheLtUNfpsIG7sg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQLMLr9A-7ja_0OMTP6yRJ_fAJhG7KaZt9cF9etcqieuAA&amp;oe=6AB5F499
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Frobinhood%2Fjobs%2F8214142%3Ft%3Dgh_src%253D%26gh_jid%3D8214142%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeps_P4o59Uh97t_hHxWiTx45y1JZBmGqOH1Ogfd0CqKRWBDvIyOUtkKTR9eg_aem_9UCaUq5NYQugYtQH14xQQQ&amp;e=AUAm8KNmF2SJpRGkbYqXSr4ppa1eMx8XAGMGUAhKOQwi6Sge665RHqLhAcfugZi5inqSE721BOx_8FtvuHI-C2X7ZyiJAayyTeXjTT7NzMSH7gAeOxnUxqtmL61U5vt-NBNzlI-rHjsYuw
+https://scontent-lax3-2.cdninstagram.com/o1/v/t2/f2/m78/AQNhCnLr-KBf_gq5sVjstO3HXZN6hjUom2l4F0sLyYDwCfopA6ZEwjLRVbofa1u1-rcRLLBTG843Gp3Uk-B1bhGHEJZqF527B84BU4g.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ohc=JyV3LW8XZZ4Q7kNvwEg7wqH&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NDMxMTI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=6181b9821a56cec8&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzdCNEYxMTRGMEIwRUU1RkM4MTAxRDdDMzhDQzUxMzhGX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkmPHosqehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJQhmEHk7aGpD8ZUOlY3g-QZvBRqzV9uIca0psWB89NOQ&amp;oe=6AB2184D</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45" ht="45" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>088edc02396f8c754958</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:31:13.411442+00:00</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T17:27:57+00:00</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Amazon — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>https://amazon.jobs/en/jobs/10553947/software-development-engineer-intern-summer-2027-can</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>—  amazonjobs
+—_ ——
+Software Development
+Engineer Intern -
+Summer 2027 (CAN)
+Job ID: 10553947 | Amazon Development Centre Canada
+ULC - KO3
+Apply now
+Description
+Shape what comes next | Discover careers in
+Tech
+st 2) AMAZON.JOBS *
+play . :
+systems, cloud servi customer-facing
+products that operate al scale. This is an
+environment where you learn by building.
+| Amazon Canada SWE Intern
+products that drive experiences for millions of
+customers around the globe, your work reaches
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/819130397_1607187461100495_3010312684693336791_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MDUwNDk0MjQ4OTU5NjkyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=tW-F3oa90vAQ7kNvwGEVP4N&amp;_nc_oc=AdpgQqKN_RXLMsvvhl3zka3WkSBlkYZPfbkAWit3M6QvtAek_0hrq3mXjhyOMWHgyS8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQJC8inxNGI4T-TWeAy9lrMrru0pyQLnBB4CbfMSGO4e-g&amp;oe=6AB60CC2
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/819130397_1607187461100495_3010312684693336791_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MDUwNDk0MjQ4OTU5NjkyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=tW-F3oa90vAQ7kNvwGEVP4N&amp;_nc_oc=AdpgQqKN_RXLMsvvhl3zka3WkSBlkYZPfbkAWit3M6QvtAek_0hrq3mXjhyOMWHgyS8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQL18rOmOuuSV8Eia78mV_gWmkTix2h6QZbXvswwOTg84Q&amp;oe=6AB60CC2
+https://scontent-lax7-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwHaI_dS&amp;_nc_oc=Adq3LGJyNFrC9-EzezVyaOsWC-5zSCe28c6wHeqJ5VQu8HMR1zTDSheLtUNfpsIG7sg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQLMLr9A-7ja_0OMTP6yRJ_fAJhG7KaZt9cF9etcqieuAA&amp;oe=6AB5F499
+https://l.instagram.com/?u=https%3A%2F%2Famazon.jobs%2Fen%2Fjobs%2F10553947%2Fsoftware-development-engineer-intern-summer-2027-can%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaejqX8KNavxlG8P1Ttjc4MYsdmPp4AXD01t-M2iNogTs2W9M-yPkFSSzaSOEw_aem_sTTN1nP36x-J-hTk8cgtQw&amp;e=AUBZOoQXAJM3wpijKmA04lZef3bRzLuPnTMywg-pE51SIFi9Xi2kWgn6gNk9E9tqbet1qhSAKXjigwkzJSUyviiGoXEqJMXBUkqEg1F9iztyNUBjhnoFCQSI7EwOa3egZvlTeUfpc3SvIg
+https://scontent-lax3-2.cdninstagram.com/o1/v/t2/f2/m78/AQNwj4wQ_MfVxzq33xaYt1rny-fJ6DBnpSMrACDqQ--uUqLdbLhY7f3PfaMUmfYPWToSw8RFqUBQoVx8HtSNIuZ-X35q1vK66WyvxGs.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ohc=bcKwrvB5FzEQ7kNvwH5DNUn&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NDMyMzU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=9884252187b26e1e&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzI2NENGODY4QjczQUI0OEYxRkI5OTFGOEI3Q0VCN0EyX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk65fes6ehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKo60EwGSBZ3slDTZmNeYdiMA5nlUFxvGNrcv68xotaBw&amp;oe=6AB211F4</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="45" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>7fbe5df77a220cad7844</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:31:15.004768+00:00</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T17:31:18+00:00</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Cmegroup</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Cmegroup — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>https://cmegroup.wd1.myworkdayjobs.com/en-US/cme_careers/job/Chicago---20-S-Wacker/Software-Engineering-Fellowship---Summer-2027_34824</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>CME Group
+WHERE FUTURES
+ARE MADE.
+BUILD A CAREER BY SHAPING TOMORROW.
+@ CME Group
+Software Engineering
+Fellowship - Summer 2027
+© Chicago - 20 S. Wacker |
+Fometikinceee (rst internship swe fellowship!
+Although students at all levels are welcome to
+apply, this program is targeted towards rising
+sophomore and junior students (class of 2028
+and 2029) who may not have previously held a
+software engineering internship.
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/818010896_1713259936407722_953205042217191111_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDUwNjYxNzY2OTQzMjA0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=IFBe8HFOGJ8Q7kNvwF6vtDw&amp;_nc_oc=AdonYrmx3Gxj07x5eT6aHQHFxL4eUDLHEN1ZZTGIiMT2RRCSrkqZavd8zpx-vzzKWDQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQKxBpGn5EaPSofDM4-ErccElsLtOVQwr8VLm5hPYMBDMQ&amp;oe=6AB61936
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/818010896_1713259936407722_953205042217191111_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDUwNjYxNzY2OTQzMjA0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=IFBe8HFOGJ8Q7kNvwF6vtDw&amp;_nc_oc=AdonYrmx3Gxj07x5eT6aHQHFxL4eUDLHEN1ZZTGIiMT2RRCSrkqZavd8zpx-vzzKWDQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQKZYwMcs1gNZYrmve4b6s3-mWPdrsnOmfcWXgWvcUeBWw&amp;oe=6AB61936
+https://scontent-lax7-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwHaI_dS&amp;_nc_oc=Adq3LGJyNFrC9-EzezVyaOsWC-5zSCe28c6wHeqJ5VQu8HMR1zTDSheLtUNfpsIG7sg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQLMLr9A-7ja_0OMTP6yRJ_fAJhG7KaZt9cF9etcqieuAA&amp;oe=6AB5F499
+https://l.instagram.com/?u=https%3A%2F%2Fcmegroup.wd1.myworkdayjobs.com%2Fen-US%2Fcme_careers%2Fjob%2FChicago---20-S-Wacker%2FSoftware-Engineering-Fellowship---Summer-2027_34824%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAae9t4AREWFoAr_mZGgWzTVxmN0a8S6UZgp9QpLcjKBxZ9medt57_4tCPmXjnw_aem_JX37q2y1a7OLLqiSqkladg%26utm_id%3D97760_v0_s00_e0_tv6&amp;e=AUCxTyMSRlzD44sHzsvvNOvkNrLlGwPmLKoYhI9Ra-dRrZIANopj2GYExOoHfRPMpo7wa3v-D-GAfyuX4mNci1LCTYNIHdlmVxhsRJzyDcC_OMMlueNIWU0AefF21rbyg_areeTt8OCfdw
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQOxS63sdnjv22X0Kwh5JspBS3sxcmgEZbhLUeFYmm9pPiRj1Nw-ur3CQgovsRanX0RvYMdtVWgDjvZlL7ZURo0wt5d6lIu4F_sqS8M.mp4?_nc_cat=104&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=jq5Pi70Lc-QQ7kNvwGlfDLJ&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NDM0OTY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=1744a88df862da27&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0NCNDZCNTIyMEM5OTBFN0Y5RTdENTIzRDc4Q0M0QzlCX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkmIzXtaehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLc_K3sHwmj82DJ6oHMASVhL1FaCpJRVZC2nvg1pgpemw&amp;oe=6AB208E1</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47" ht="45" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>8ad3c6d9e6121e96eff0</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:31:16.067122+00:00</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T17:33:12+00:00</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Tesla Summer 2027 SWE Intern</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tesla.com/careers/search/job/284004</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>TESLA Careers Menu
+Go to search
+Internship, Software
+Engineering, People
+Products (Summer
+Engineering &amp;
+Job Category Information
+Technology
+: PALO ALTO,
+Eenation California
+Req. ID 284004
+@ TESLA.COM
+w
+Tesla Summer 2027 SWE Intern
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/818598497_1114852041226290_2887109307819877843_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5MDUwNzU4NDEyOTM1NTc2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=_nGgvDeBiEUQ7kNvwEvQnaq&amp;_nc_oc=AdpU5tphkdHXg8FhOHEeQ8rf3efrB7smQ-Y4nZ1Ah8okLWvLiRmLdMI3Ko3ajojQDmw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQKsGkYKt4ZILSVGh-Wir2GeCqdfJsH-7W5yQY_JshN1Cw&amp;oe=6AB61E9B
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/818598497_1114852041226290_2887109307819877843_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5MDUwNzU4NDEyOTM1NTc2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=_nGgvDeBiEUQ7kNvwEvQnaq&amp;_nc_oc=AdpU5tphkdHXg8FhOHEeQ8rf3efrB7smQ-Y4nZ1Ah8okLWvLiRmLdMI3Ko3ajojQDmw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQL0uyDzGEWm3Dfluz6jSvSxESFG3wNIStA8Ox9D-NUHFw&amp;oe=6AB61E9B
+https://scontent-lax7-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwHaI_dS&amp;_nc_oc=Adq3LGJyNFrC9-EzezVyaOsWC-5zSCe28c6wHeqJ5VQu8HMR1zTDSheLtUNfpsIG7sg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQLMLr9A-7ja_0OMTP6yRJ_fAJhG7KaZt9cF9etcqieuAA&amp;oe=6AB5F499
+https://l.instagram.com/?u=https%3A%2F%2Fwww.tesla.com%2Fcareers%2Fsearch%2Fjob%2F284004%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadefy4xEUGOer1jbjDhm-Cny9I4ppC6q9mz9z4YgUO9FljzsMMSdtocHU4msA_aem_3qd4ZP4Oa6_wtYLjFtUSvA&amp;e=AUCKfp_D2Ekr8UdthYrtFCRf5ABnLbqUKaC7gYWS7rRlgg1M7wW8Bd31IGzvkgb0V8tqJ7myO0roAzjddQJbIRZKO04vGG8VFtS1AnGDaDtNVbKTNDRgZHif6p-MjXL-PrR-TAGjRiy3Ew
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQMutOWfoOmGukjJms5GSYo_OoD5Ho13C1glhzhtTUx5T3gt1nrRHzESEPzeLj47U0lSZo7WbrUnQcB1xAporPKu9-ldj1ZV-gXCpSQ.mp4?_nc_cat=102&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=Q9ubBPbzlfkQ7kNvwESfppO&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NDM3NDI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=1b171052b5052ddf&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzM4NDBFNzk2NTI4NTgzMTUyMUFDMTczMkNFQ0E5OEFCX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkvtnBt6ehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJViDOmyU7nEYB_OUza_1IAll6D_6ACrSXuaFkAiiGHgA&amp;oe=6AB20CD3</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="45" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>e780735abf15677b2046</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:31:17.374595+00:00</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T17:37:40+00:00</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Embed</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Embed — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Winter 2027</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr"/>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/embed/job_app?for=gemini&amp;token=8214272&amp;gh_jid=8214272</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>New
+Software Engineering
+Intern (Winter 2027)
+© New York, New York
+About the Company
+Gemini is a global crypto and Web platform
+founded by Cameron and Tyler Winklevoss in
+@ GEMINI SWE INTERN
+over /O countries. Our mission is to ck
+envision a world wherg@ Mato reshapes the
+Ask anything about Gemini
+Type something...
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/819031189_2329848987751124_4040444669564451376_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5MDUwOTgyOTM0MDMxOTMyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=6Mj43KIvKd4Q7kNvwEbuHmG&amp;_nc_oc=AdqazW7Ik3hhTUWaxGIXGGF8MD8MXSuZupgAfl1DEx8sJ0pTU2L7UvumpMSWQ7Aq_60&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQK6F-WgLiRo78QsFg6Hl45iuMoXVwUB4YLeuLWhXX0qMQ&amp;oe=6AB60EEB
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/819031189_2329848987751124_4040444669564451376_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5MDUwOTgyOTM0MDMxOTMyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=6Mj43KIvKd4Q7kNvwEbuHmG&amp;_nc_oc=AdqazW7Ik3hhTUWaxGIXGGF8MD8MXSuZupgAfl1DEx8sJ0pTU2L7UvumpMSWQ7Aq_60&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQKdd3PVaAjgVn1cWKGKmSxtUQPcFPufLxvdmQc46VbZ-A&amp;oe=6AB60EEB
+https://scontent-lax7-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwHaI_dS&amp;_nc_oc=Adq3LGJyNFrC9-EzezVyaOsWC-5zSCe28c6wHeqJ5VQu8HMR1zTDSheLtUNfpsIG7sg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQLMLr9A-7ja_0OMTP6yRJ_fAJhG7KaZt9cF9etcqieuAA&amp;oe=6AB5F499
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fembed%2Fjob_app%3Ffor%3Dgemini%26token%3D8214272%26gh_jid%3D8214272%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafZazY0YDQtD83QGRovZcwT8jEkDunF0czcCK6zP97FOHlQ5RtKVGHJs6e10Q_aem_yjO8zYXVKhrHACVaAA_Kgw&amp;e=AUBEDVtTBaIPQPy-XCoiRjTaFoznFOQoXJxakJ1u6ydJ57kOiTEVo5KAdhIQbD87jUN6SS0zgZWjRi-GsZl_AQBBrNegZX08bdSTjz4qhMphg0qUptMUVjHHFQr6mw7po4xNmgow3FApeQ
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQPYmc6B5Qvp412xxk6YkCaaI0UJZSWfatwE1XM2hZxF2mPxeB6XvyBqzG_hJwMUKECzjZqd2i2Kdi6lSL9MnDhi7sZwR7EH9V4p_vc.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=y1wQTE1Mdo4Q7kNvwHJa3qW&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NDQxMTQ2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=f7d94d32e2468a19&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzQ3NEFGRjE0MUY5MzlDMUQ5MTFENUZCMDkzQzFBNjhGX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk0rukuqehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKn24uqdIzYPXMjyK82G6EQiNsbtzRg8xEWQa3AMJby9Q&amp;oe=6AB1F69E</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49" ht="45" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>7abe95aedc3b735601be</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:31:19.060980+00:00</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T17:38:51+00:00</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Internship Dates: January 11, 2027 -</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Winter 2027</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr"/>
+      <c r="J49" s="3" t="inlineStr"/>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>https://www.rubrik.com/company/careers/departments/job.8171088?gh_jid=8171088</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>$°¢ rubrik
+Job Summary
+Software Engineering
+Internship, Winter 2027
+Internship Dates: January 11, 2027 -
+May 7, 2027
+About Rubrik &amp; About Role
+Rubrik (NYSE: RBRK) is on a mission to
+secure the world’s data. With Zero Trust
+Data Security™, we help organizations
+(2) RUBRIK WINTER SWE INTERN
+operational disrup ubrik Security
+Cloud, powered by ine learning,
+secures data across enterprise, cloud,
+and SaaS applications. We help
+https://scontent-lax7-1.cdninstagram.com/v/t51.71878-15/818941400_4402798683194240_8290839601004444363_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MDUxMDQzMDgxMTg2NDQ5Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=W2ilAq7iKhUQ7kNvwFb7H3L&amp;_nc_oc=AdrFGDLsGnK4V2pssPQfffayi80TjuErzXah-3i0TREvmpWNIyRjMAI5N2f28SnmEE4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQLO7sfAG2NrRGy7FrhpIWqjmMexayabZfAllVytS4WHjQ&amp;oe=6AB6149C
+https://scontent-lax7-1.cdninstagram.com/v/t51.71878-15/818941400_4402798683194240_8290839601004444363_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MDUxMDQzMDgxMTg2NDQ5Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=W2ilAq7iKhUQ7kNvwFb7H3L&amp;_nc_oc=AdrFGDLsGnK4V2pssPQfffayi80TjuErzXah-3i0TREvmpWNIyRjMAI5N2f28SnmEE4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQIZDmeRRzp4EbKeOCq3aesItbUa__zthIXQm8ycKsy09Q&amp;oe=6AB6149C
+https://scontent-lax7-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwHaI_dS&amp;_nc_oc=Adq3LGJyNFrC9-EzezVyaOsWC-5zSCe28c6wHeqJ5VQu8HMR1zTDSheLtUNfpsIG7sg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQLMLr9A-7ja_0OMTP6yRJ_fAJhG7KaZt9cF9etcqieuAA&amp;oe=6AB5F499
+https://l.instagram.com/?u=https%3A%2F%2Fwww.rubrik.com%2Fcompany%2Fcareers%2Fdepartments%2Fjob.8171088%3Fgh_jid%3D8171088%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacMXvxkJskb2af6ELP7e8nTk_0L_xk_HX98FsuEbxZLthtKWsQ7dh0lezSIxA_aem_gVvNnzZ28Z1Wj6Osx7YhEw&amp;e=AUAEdhfjva2c-7P7RPHOKX4VlpHr0FLrvm_kruVi45TDsZYUQzWU7l4QZel-n-YcGOnG6gY1sqKV_ar8hMH1h8wCWiCKqzt3k-GnS2Pur78pY2qaXU1oVOIkVtScEzHzuePCpK5kSgRknw
+https://scontent-lax3-2.cdninstagram.com/o1/v/t2/f2/m78/AQOf5i2G38rr0MXvwKb5Ck24djXcdlKZa_AEUbh2fnnvPd-iaLxfeWRd7ApkNrbMlWZ7E_ICA4ZRj6CSWDSLTjdmAJrSL5ggl4JGaGI.mp4?_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ohc=QHYbJ101a9wQ7kNvwGgaV2x&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NDQyNjE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=1fd60f584135d2ff&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzA5NDc4RTg4MUVGRURBRDlCRkFDQTdEOEYzREE5MEE5X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk_dOwu6ehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLfzyXTgy72l9hjUsGgbIsz-yBxh4E7NXyePT4odmHADQ&amp;oe=6AB22173</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="45" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>7fd55cacb063b2ac27ab</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:31:21.745169+00:00</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T17:41:52+00:00</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft — Hardware</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr"/>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Redmond</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr"/>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>https://apply.careers.microsoft.com/careers/job/1970393557002608</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N50" s="3">
+        <f> 6 B® Microsoft Sign in
+Careers v
+€ View All Jobs
+Hardware Engineering
+Internship (6-Month
+Program)
+Q United States, Washington, Redmond
+Apply now | Add to cart |
+9 PA
+(7) MICROSOFT HARDWARE ENG COO!
+Ww)
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/797646789_1027516423666649_2262555117865925566_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MDUxMTk0NzA4NjMyMzYxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=53Q6GYROLUgQ7kNvwEcjqEG&amp;_nc_oc=AdqycfMBVwIJ-CX1sAKcYZzyMcheNbSpPJ4XlJbKKQ_AMhbQ6Ha5HSS9giMKc2LBffM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQKpVBa4tXKxkWmcLbEF1muyaDEWef1JU0Yez9c90d7L4A&amp;oe=6AB60FF5
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/797646789_1027516423666649_2262555117865925566_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MDUxMTk0NzA4NjMyMzYxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=53Q6GYROLUgQ7kNvwEcjqEG&amp;_nc_oc=AdqycfMBVwIJ-CX1sAKcYZzyMcheNbSpPJ4XlJbKKQ_AMhbQ6Ha5HSS9giMKc2LBffM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQINoz-EaRSmZtT0y7Q2BpbXR7dLXmZz9OsGd8m7M4AnkA&amp;oe=6AB60FF5
+https://scontent-lax7-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwHaI_dS&amp;_nc_oc=Adq3LGJyNFrC9-EzezVyaOsWC-5zSCe28c6wHeqJ5VQu8HMR1zTDSheLtUNfpsIG7sg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQLMLr9A-7ja_0OMTP6yRJ_fAJhG7KaZt9cF9etcqieuAA&amp;oe=6AB5F499
+https://l.instagram.com/?u=https%3A%2F%2Fapply.careers.microsoft.com%2Fcareers%2Fjob%2F1970393557002608%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAae439wp-0h4VOKNCMgdQp-ncoxJZ3X0ADDiLy44Rvod8nWeLoKFBOkI-F_d1A_aem_nKxBsHCZwtcQqG9dCNnK7Q&amp;e=AUClnlr6s8LUpZAw-S2lAtFDC7k6oFYzTPK8o0Mu1xW88V17v0u_tpIYglrxg3dBOm5zywhCl0_E8LKNUJOiDFeaA7A2G03bNc97TaYTXlU-wLMbCPK9diZHLrj6rPRcio4a4_qOG1uLLA
+https://scontent-lax3-2.cdninstagram.com/o1/v/t2/f2/m78/AQNmr82tK1ePiWLe4mRWq_zIg-uxqHD97DRsCppNY6VxUKe1-ZUGQyXwk6eHf13xASW5rZnjVjZGzlLjBNb3rNrq1BZMrxni6nAqHqw.mp4?_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ohc=-HSPyQX-rlMQ7kNvwEyIXyd&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NDQ3NDc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=c95a6e852bbda475&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzBENDBBOUUzQjRGMTg4RTA0REIwMTdDODM3NjJGM0FDX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkk5KAv6ehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKn2BoMi3DYPtvJYUMdlkJ9SWf3Q5Lb-G66ApXoxEN2yQ&amp;oe=6AB1FFAF</f>
+        <v/>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51" ht="45" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>07dd815ef7fe2ecde141</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:31:24.697753+00:00</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T17:44:25+00:00</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Togetherai</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Togetherai — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr"/>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/togetherai/jobs/5232036007</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>&lt; Back to jobs
+New
+Software Engineer
+Intern (Summer 2027)
+© San Francisco
+Role Overview
+As a Software Engineer Intern, you’ll have
+the opportunity to work on a variety of
+projects, from designing scalable systems,
+ TOGETHERAI SWE INTERN
+Witn cross-Tunctional #amMs to Dulld robust,
+user-focused sual ty contribute to our
+mission of delivering g-edge
+technology.
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/819236850_2189587084951541_448754701832988724_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MDUxMzIyNTc3MDI0MzUxOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=8tK-3q5zglIQ7kNvwH6F9QN&amp;_nc_oc=AdoTY_u8wsHdpzI_SbIrg3w9nG3Z-lBNp-8KDl3brvdp9LKJjgh9GV4_vYifWiZWlCg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQKkOItnr04Yl3dNBRyB7AoIk7kGgCP2_QzwcX-80WwfqQ&amp;oe=6AB616B8
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/819236850_2189587084951541_448754701832988724_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MDUxMzIyNTc3MDI0MzUxOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=8tK-3q5zglIQ7kNvwH6F9QN&amp;_nc_oc=AdoTY_u8wsHdpzI_SbIrg3w9nG3Z-lBNp-8KDl3brvdp9LKJjgh9GV4_vYifWiZWlCg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQJbvTzfYCKT3fd1SomodSl9qgwkrJBPAN9dRay6j0wZUQ&amp;oe=6AB616B8
+https://scontent-lax7-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwHaI_dS&amp;_nc_oc=Adq3LGJyNFrC9-EzezVyaOsWC-5zSCe28c6wHeqJ5VQu8HMR1zTDSheLtUNfpsIG7sg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQLMLr9A-7ja_0OMTP6yRJ_fAJhG7KaZt9cF9etcqieuAA&amp;oe=6AB5F499
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Ftogetherai%2Fjobs%2F5232036007%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadkoVOnPUeqcU6GTEVjyTUiTa0HSQxpGEdGavhXrNS5qO43OCHk4yPDxocJAA_aem_2yCW5G-sUzZ_RtMhNsSTiw&amp;e=AUBPbsrJ3Id1D4_UYsFQOMeHhGa0SIM9ELShHsFN107c9zmxrsX7Yh5VrENxBZC-fleWqTuTnJOHQp6zyu2GRRztTbNpy7JRDOI4yMGjvVaOSFq8cJb3BcH2VlnUnNf2t-xeLwmNKzgs8w
+https://scontent-lax3-2.cdninstagram.com/o1/v/t2/f2/m78/AQO4nZIVJqo0wnW1MRZxOLcVEnYx6DlNAvJ4DCbb2kfagSrgriAcMuTwL9WuU7gN-gi33roho0Ax5p47kUK_1IK_aGRVVRh6ll1qIkk.mp4?_nc_cat=107&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ohc=yinEtddBvzcQ7kNvwFSmLt-&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NDUzNjU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=ea450a84f64db01c&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0RFNDhDREMzODYxMERGQTFDNzZERjREQzRBQkZENDhCX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkzcHNw6ehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJ6j3f4Hi6cgYikWUztzJWKLPYK2wbYYsoqY6YO2M7Ctg&amp;oe=6AB20914</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="45" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>47ae3eeb80ba3c22e429</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:31:26.243552+00:00</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T17:45:57+00:00</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Jobvite</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Jobvite — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr"/>
+      <c r="J52" s="3" t="inlineStr"/>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.jobvite.com/tylertech/job/oAVOAfwD?nl=1&amp;fr=false</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>| 31 =
+Software Development Intern,
+Summer 2027
+Lawrenceville, Georgia
+Salary: USD 20.00 - 25.00 Hourly
+| Apply
+Description
+Tyler Technologies is seeking a Software
+Development Intern. Tyler has an agile, fun, fast-
+paced and stable environment.
+Tyler’s goal is find extremely strong developers
+tl
+h
+S
+natural affinity and abili velopment that can
+work in a team environ
+The ideg
+charact TylerTech SWE Intern tosis af |
+interviews historically)
+https://scontent-lax7-1.cdninstagram.com/v/t51.71878-15/797517894_1805880567497099_590590402248055749_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5MDUxNDAwMTgxNzE2ODQ4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=az4kemq6vKcQ7kNvwEwTckv&amp;_nc_oc=Ado_a7toRYhe5m_w3Dz6M5sWcwBISoB9vEE1E9hFMqo63WWKF5rDoz44ZJMy_G9W5oQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQJJkXIAvStNR_5ZEVODa9hUhV9cVaU7HKA33bkJNJ7_Ow&amp;oe=6AB5F758
+https://scontent-lax7-1.cdninstagram.com/v/t51.71878-15/797517894_1805880567497099_590590402248055749_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5MDUxNDAwMTgxNzE2ODQ4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=az4kemq6vKcQ7kNvwEwTckv&amp;_nc_oc=Ado_a7toRYhe5m_w3Dz6M5sWcwBISoB9vEE1E9hFMqo63WWKF5rDoz44ZJMy_G9W5oQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQKqH6zZvtJ-tavwdk1JWS6ar0QqoIL7M8-GhxnfmL36Xw&amp;oe=6AB5F758
+https://scontent-lax7-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwHaI_dS&amp;_nc_oc=Adq3LGJyNFrC9-EzezVyaOsWC-5zSCe28c6wHeqJ5VQu8HMR1zTDSheLtUNfpsIG7sg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQLMLr9A-7ja_0OMTP6yRJ_fAJhG7KaZt9cF9etcqieuAA&amp;oe=6AB5F499
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.jobvite.com%2Ftylertech%2Fjob%2FoAVOAfwD%3Fnl%3D1%26fr%3Dfalse%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAad9qStlGCpovQehSrjSJRatmmwcmg74LS8et6rDB0Ry12edswml96HY5Oe14Q_aem_my2jDTWDBDWkB8TeGywCdQ%26utm_id%3D97760_v0_s00_e0_tv6&amp;e=AUAyRXbhr9nZUWMZiJ892SpZJwyjRrj5p84o1HM0QXY_gpurYDeESewvuUunD_vbND7t2CbMMCVtd3vHHe8okvpae_IThAltc8VLQf4gL_NHzz--fqAenR44mQIZeIsKkmB_KyLRLRZHvA
+https://scontent-lax3-2.cdninstagram.com/o1/v/t2/f2/m78/AQOkXh9KQy32SBefA5ewY-3k0KWNXZeWWmc3MH3kL0pFYnDOeWmv22Wx0iF61pxTxRrfJNYa1QRI6H_K6LRKHS85Qt8K69z-sXnEFcE.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ohc=oq_vIhMJU1kQ7kNvwGET1B4&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NDU3MTY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=485ca7577e29d99f&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0FENDM3NjQxODM1RkIwRjE4RjFBQzYyQTQ3QkRBQUE0X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkpKCcxqehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJgwgHqxxlllgDs3ZFSOE3P-wWI5rlK1OS4JZK3-hrXXQ&amp;oe=6AB224D1</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53" ht="45" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>d73483fb3da3fa833398</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:31:27.223770+00:00</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T17:47:22+00:00</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Thrivent</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Thrivent — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr"/>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>https://thrivent.wd5.myworkdayjobs.com/external/job/Remote-Minnesota/Associate-Software-Engineer---Sophomore-Intern-Summer-2027_REQ-48457</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>2 Sign In
+thrivent:
+Thrivent Careers
+Associate Software Engineer -
+Sophomore Intern Summer
+2027
+© Remote-Minnesota
+Full time
+(2) THRIVENT SOPHOMORE SWE INTER
+w)
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/816953246_1899476797888074_3836302701042367753_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDUxNDcyMTQzMzg3NjY3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Fphw4e6XabEQ7kNvwFWPXyL&amp;_nc_oc=Adprxj23_Y1wNMecPIv4bybAweVbsdLpIp5DaxFQdedYzX3SfvpBnQh-C1rZE1RjJjs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQJuvxPf3ZELOkexsrAfWrJA8CJhwYv-qzo_YvHrGLycog&amp;oe=6AB5F456
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/816953246_1899476797888074_3836302701042367753_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MDUxNDcyMTQzMzg3NjY3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Fphw4e6XabEQ7kNvwFWPXyL&amp;_nc_oc=Adprxj23_Y1wNMecPIv4bybAweVbsdLpIp5DaxFQdedYzX3SfvpBnQh-C1rZE1RjJjs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQJu-dJC6hJE-WSmragn-z87BxoRb2GELDk9e38jdIVUoA&amp;oe=6AB5F456
+https://scontent-lax7-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwHaI_dS&amp;_nc_oc=Adq3LGJyNFrC9-EzezVyaOsWC-5zSCe28c6wHeqJ5VQu8HMR1zTDSheLtUNfpsIG7sg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQLMLr9A-7ja_0OMTP6yRJ_fAJhG7KaZt9cF9etcqieuAA&amp;oe=6AB5F499
+https://l.instagram.com/?u=https%3A%2F%2Fthrivent.wd5.myworkdayjobs.com%2Fexternal%2Fjob%2FRemote-Minnesota%2FAssociate-Software-Engineer---Sophomore-Intern-Summer-2027_REQ-48457%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacrKZMZ4cSJXpsYxApqVmvXVUPny_m4yhxIsqcJur2UzjMC4ZQalYvnsjJRGw_aem_PkMfEXZ_mulckLfPIPfNlg%26utm_id%3D97760_v0_s00_e0_tv6&amp;e=AUACdu9Ok3GOOLoPMpPjmF-Pl1s7lPhKOtLi4w8FRmcZw7bsadI6S2L-HNzeTytT1AmF9ah0XP2kYJEfdFA6nso9v8a5Rg8IZxzGx2LCkKJhnIe3UXMB3QJzuqNiQW9yKApEcCIWzaUhPQ
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQNIqyTE7-y1fHJW_jAKqV9cuHbygSQtQtAzClJGa3igLIbzIZdUujTcVYC_8Klb1J3zWGRPtCXa39bBH40ywpXBCd7qgaK4CFELkGI.mp4?_nc_cat=102&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=4_QV-F-LmvoQ7kNvwEERsWS&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NDU5MDU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=696d7a924098ba3f&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzFGNDdGMURCNEZEOURBQThGMDlCQUZCNEFEQjU1NUJBX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkyb_Qx6ehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKl4e_sYDT3YNGbPs7e8sBDurJSV2zyqzV-nEuRysAyYQ&amp;oe=6AB1FC1B</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54" ht="45" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>731b58b2665e61030985</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:31:31.669283+00:00</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T18:05:45+00:00</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr"/>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>contribute to as an intern within the</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr"/>
+      <c r="J54" s="3" t="inlineStr"/>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>https://recruitment.macquarie.com/en_US/careers/JobDetail?jobId=24234&amp;source=zero2sudo</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>© mMacauaricE
+2027 Commodities and Global
+Markets Summer Internship
+Program
+Today, as commodities continue to
+underpin the building of our cities, as
+our global energy needs continue to
+grow, and with technology changing
+the world, the projects you will
+contribute to as an intern within the
+Commodities and Global Markets
+business are helping to build a better
+future. We...
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/795288569_1678153260550851_171570055937635526_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MDUyMzk3MDk3MzEwMjMzMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=-r5DiJh9I48Q7kNvwGieXoX&amp;_nc_oc=Adraqjb2w5t9HnRw_mw1ZdimkulhnLR8nXgPC0LOHQGGnmh5gvrFNUvdeOhLyrXZ1-8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQIpVXVf6NTSupApWNFTPhSwUHY5iJPK02CbFNvY4LwvCA&amp;oe=6AB61DE4
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/795288569_1678153260550851_171570055937635526_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MDUyMzk3MDk3MzEwMjMzMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=-r5DiJh9I48Q7kNvwGieXoX&amp;_nc_oc=Adraqjb2w5t9HnRw_mw1ZdimkulhnLR8nXgPC0LOHQGGnmh5gvrFNUvdeOhLyrXZ1-8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQLGuK0LZFnvyYR8NX-T61HeBebIM4qQil4nIyquWOR1tQ&amp;oe=6AB61DE4
+https://scontent-lax7-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwHaI_dS&amp;_nc_oc=Adq3LGJyNFrC9-EzezVyaOsWC-5zSCe28c6wHeqJ5VQu8HMR1zTDSheLtUNfpsIG7sg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQLMLr9A-7ja_0OMTP6yRJ_fAJhG7KaZt9cF9etcqieuAA&amp;oe=6AB5F499
+https://l.instagram.com/?u=https%3A%2F%2Frecruitment.macquarie.com%2Fen_US%2Fcareers%2FJobDetail%3FjobId%3D24234%26source%3Dzero2sudo%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafQenRFJy8hBEfADInbTqAMxbzb8ZTTw8RWqVkKaPGnQnTgV7H6RKkgSPSQXw_aem_sGq6H1eimDMct3tIMt0t_Q&amp;e=AUBZpQms5Eaur8phpIk2WjqhYEShL5eGK8iQY_b_DGPyK5AvUQ9_xUS7CIrJLr3dGV0Kqd9RuAvt0h48h3YqR3fyNLcp7sk3YOFmBLELFQcsMOJlfRCgDKOTIaLuWzilwUBw41QTl3sX-w
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQOtsFGcAABp7P_Mzu_CD3J3_VqkxaI2yMcoy5lc7vXp0wJFe3GAdJ7t8l92CU5dBgBVpCKT7t1ZEO8882ayuSSepLlKaAp0zOrSWWA.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=lJ0R_aGSg-kQ7kNvwF8Bsa0&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NDgzODM2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=3f0c464967c9b34d&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0EwNEM4OUVBOTZEODgxNTIyNUE2Njc0MDUxNDMwNDk2X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk59mL2qehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIXZLYwziDSAa6jTICanDHWBFvQyIbzzF9hV7IJNEBeKA&amp;oe=6AB210CE</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55" ht="45" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>8bf6d9ccc1bfbc15f1be</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:31:32.659724+00:00</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T18:07:40+00:00</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Celestica</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Celestica — Data Science</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr"/>
+      <c r="I55" s="3" t="inlineStr"/>
+      <c r="J55" s="3" t="inlineStr"/>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.celestica.com/job/San-Jose-Student-Intern%2C-AI-Data-Science-CA-95101/1439115933</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Student Intern, Al / Data Science
+Student Intern, Al / Data Science
+‘CAREERS CELESTICA(
+/1439115933/ l |
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/818654773_2239103396936932_2875417659324531195_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MDUyNDkzNjYwMjU1ODA5OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=tYY-2vaMutcQ7kNvwHNFL96&amp;_nc_oc=Adq9Bpu82Uy9myQpv9oxBw0qlg13nIQOHRdC_sK87MGUIfHvfC7_b-XMwKHbasHrhQ4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQLIl2F9jiUVhQRQmFhEAiLx7na-9pRXuCbHZIGR_udy3A&amp;oe=6AB5EEAF
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/818654773_2239103396936932_2875417659324531195_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MDUyNDkzNjYwMjU1ODA5OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=tYY-2vaMutcQ7kNvwHNFL96&amp;_nc_oc=Adq9Bpu82Uy9myQpv9oxBw0qlg13nIQOHRdC_sK87MGUIfHvfC7_b-XMwKHbasHrhQ4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQK-A2n-lenpG57EXaF9xhImUTOXTJ-cgdP6V64QdFU32Q&amp;oe=6AB5EEAF
+https://scontent-lax7-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwHaI_dS&amp;_nc_oc=Adq3LGJyNFrC9-EzezVyaOsWC-5zSCe28c6wHeqJ5VQu8HMR1zTDSheLtUNfpsIG7sg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQLMLr9A-7ja_0OMTP6yRJ_fAJhG7KaZt9cF9etcqieuAA&amp;oe=6AB5F499
+https://l.instagram.com/?u=https%3A%2F%2Fcareers.celestica.com%2Fjob%2FSan-Jose-Student-Intern%252C-AI-Data-Science-CA-95101%2F1439115933%2F%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafgH-EM_-LCVJsDd6y6o3s86OYHY7O__84yUIYA0qTCq8c72QJuWn8LRN1YdA_aem_o9AYuqfbjYB_8o0zIgpkyg&amp;e=AUDgRKdbRcyR9iWKYbdyZGrXwZ9QZ2GYZKxjYvRmP_iycbQPbHCaThurzOmeFy2hy4II22E29OmZrGKPecMl4AwovkbQrGR8PU5SPZhsIvPjiz64lNosAj-aWxLwtnlgvlS7db8Bu436CQ
+https://scontent-lax7-1.cdninstagram.com/o1/v/t2/f2/m78/AQOMbhZoecM34o48SrSEd5_hMM7LTMVEAdUFMVBqEuVT_lhspnYdte8C1v9zukyLqtAamOPfuWj2eq3a76p7LhqdfUZaKKA9QopN6Cs.mp4?_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ohc=T-MJOhOt7uMQ7kNvwFpgxzQ&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NDg1Mzk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=f29dd1bb3435f5c3&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0IyNDVENTg4Mzg0MzQ0MzcwQkFGOUIyREJERjdBNkIzX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk47yg26ehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKMdsm4P_rnCxgDTxG0nUsg9WKAnfvQEnHnfioAXfFR6A&amp;oe=6AB1F6D2</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56" ht="45" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>a906527dc68d6e18c0a1</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:31:33.802602+00:00</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T18:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft — Internship</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr"/>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr"/>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>https://apply.careers.microsoft.com/careers/job/1970393556982262</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N56" s="3">
+        <f> 9 B® Microsoft Sign in
+Careers v
+€ View All Jobs
+Electrical Engineering
+Internship (6-Month
+Program)
+9 United States, Washington, Seattle +2 more
+PNeye)\aarevam | Add to cart |
+(2) APPLY.CAREERS.MICROSOFT.COM
+vw)
+Microsoft Electrical Engineering
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/819107299_941795338981640_7096675012911458198_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MDUyNjkwMTAyOTk4OTM3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=JKQuw4rU18gQ7kNvwE1n4zF&amp;_nc_oc=Adq6SMFi47Fn-6HKjEiTDg7KZqM0vBUd3QHbeBwrri9W82VWHGYYjX6QdIeHWa2i8F0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQKpQvNC52MGg2jL1IUX9eGE-JCdBXTIpwXT9zAjQkxAFA&amp;oe=6AB5FAD8
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/819107299_941795338981640_7096675012911458198_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MDUyNjkwMTAyOTk4OTM3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=JKQuw4rU18gQ7kNvwE1n4zF&amp;_nc_oc=Adq6SMFi47Fn-6HKjEiTDg7KZqM0vBUd3QHbeBwrri9W82VWHGYYjX6QdIeHWa2i8F0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQKXKcKnB8Fn0sCfwIpl3Wvbhto1G2fdTAPFHAmG9lvQpA&amp;oe=6AB5FAD8
+https://scontent-lax7-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwHaI_dS&amp;_nc_oc=Adq3LGJyNFrC9-EzezVyaOsWC-5zSCe28c6wHeqJ5VQu8HMR1zTDSheLtUNfpsIG7sg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQLMLr9A-7ja_0OMTP6yRJ_fAJhG7KaZt9cF9etcqieuAA&amp;oe=6AB5F499
+https://l.instagram.com/?u=https%3A%2F%2Fapply.careers.microsoft.com%2Fcareers%2Fjob%2F1970393556982262%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeBE_zBZXjPmffQvkwMgxV-K4yPo_bW86Qk2L3WOUkiK_TXGBMMWa9EGOCdHg_aem_1Sb-omkjHxffY5wcoDbNlw&amp;e=AUAlrzeB5hmCqozVmaFr7w6yHNygXBM64TtYa80t0IaDkAs_730BUjUYPGUihz9mV64OkwpjDWLOTOSgqNWYOoA_QzhJSQbsyF7Y5cjJupqwFtNshyrWfwTyw8d15KHSZ7WmqahpZGkMbQ
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQOrI1gGaK1ZM0pjJS1iVzwB4CRiexrlITozXtOGsWdEWXm97qLDplgCX00lNQ2PDgabRTBwdYdq9qVSfF6bxEj-ezMYdxUvNreoZZQ.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=VLHWRKlRrtAQ7kNvwGg2Ka4&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NDkyMjA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=88c07d553e076b&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0I0NDI1OTI5MEY5MjVCRTU1OUM3NzhDNjBCRTM2OTkyX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk1Pap4KehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKr_DORfOCKuTSg963S8IJ-zxdf1YUI-ND8wbACgbKpSQ&amp;oe=6AB22E9E</f>
+        <v/>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57" ht="45" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>206d81a1fa917e2d2884</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:31:34.845150+00:00</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T18:12:16+00:00</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft — Internship</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr"/>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr"/>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>https://apply.careers.microsoft.com/careers/job/1970393556982259</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N57" s="3">
+        <f> 9 BE Microsoft
+Sign in
+Careers v
+€ View All Jobs
+Silicon Engineering
+Internship (6-month
+Program)
+Q United States, California, Mountain View +1 more
+Apply now
+YO PA
+Add to cart |
+(2) MICROSOFT SILICON ENGINEERING
+w)
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/816615036_1078658781544141_8695390050669371685_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MDUyNzI1MjgzOTgyNzM1OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=uAqvsP51No8Q7kNvwFNfFSO&amp;_nc_oc=AdpVJE9z9URAFBZoXXCgIxRzGWT_oNSLM5N2RA0avALr6sAm1ZcgPjGJxdXk1JuwN3w&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQLcWV1OURH5XOmioif2SoN-50RkI3tazR8kRndV5D8goA&amp;oe=6AB61036
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/816615036_1078658781544141_8695390050669371685_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MDUyNzI1MjgzOTgyNzM1OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=uAqvsP51No8Q7kNvwFNfFSO&amp;_nc_oc=AdpVJE9z9URAFBZoXXCgIxRzGWT_oNSLM5N2RA0avALr6sAm1ZcgPjGJxdXk1JuwN3w&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQJ68kDfcvwtW1ZkmIJQ3F6yz9183mIv61JPn_6osHuUZQ&amp;oe=6AB61036
+https://scontent-lax7-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwHaI_dS&amp;_nc_oc=Adq3LGJyNFrC9-EzezVyaOsWC-5zSCe28c6wHeqJ5VQu8HMR1zTDSheLtUNfpsIG7sg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQLMLr9A-7ja_0OMTP6yRJ_fAJhG7KaZt9cF9etcqieuAA&amp;oe=6AB5F499
+https://l.instagram.com/?u=https%3A%2F%2Fapply.careers.microsoft.com%2Fcareers%2Fjob%2F1970393556982259%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaepIL6MANp_31fw6WSsib3gAnwhVadwQQ1Mma_tIE1NQYXejciKcWzzU8KnWQ_aem_KsaQ0f-F4P1ene93hhkhEQ&amp;e=AUDpPbE3pHV3Dzb2fO5KYFTy7lSswGfyMuwoYfnUkin2ZSxa61T1RxitPnacYwNB7bMJGUQwc_GU1IJf9hzAKMwQ2oegGiPAlMUun09vdDYkmFc_mBrCSRlVkvL7apxhlzFPe4mtA-qSCA
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQO0D97QzW59v0QglPDoXFaWuEODiXFkUbAHlWa8UrFVfooTkt0w3z5kp4FdqS2QFJOnV7Lihf6GUk2WcawV4a94hCZBPRWdMP2Adbw.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=vJs4VjpdMiEQ7kNvwEMrO8V&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NDkzNjE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=a095f4dc95966328&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0Y4NDYxMTJFQTFBNTQxODIxRDhBMzVGNDRBQjU4RUJEX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkybKw4aehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJyUZj5qZHNyele1L5GwfrT6hah4OlpsfGakkXBncpRDA&amp;oe=6AB20C76</f>
+        <v/>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58" ht="45" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>762cc629290d15c1c399</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:31:36.327258+00:00</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T18:13:22+00:00</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Metoxinternationalinc</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Metoxinternationalinc — Data Science</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Spring 2027</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr"/>
+      <c r="J58" s="3" t="inlineStr"/>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/metoxinternationalinc/jobs/5427064008</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>METO-&lt;
+&lt; Back to jobs
+New
+Data Science Intern
+(Spring 2027)
+© Houston, TX
+Empower Your Future: At MetOx
+International, we're pioneering the next era
+of energy security and abundance through
+(2 JOB-BOARDS. GREENHOUSE. 10
+ewes ear A cain
+more resilient, efficient and reliable.
+Data Science Intern
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/818685589_1440631781309045_621455048469772451_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MDUyNzc5NzYyMTE2NTc4NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=aNUXSSptDKIQ7kNvwGWFQAV&amp;_nc_oc=Adq1Q8bpvrXeMtnNXJjxFe5WDjoE4YIB8lojNXjWkHT1ojLOnwFr6BdAkGHS5sZ4epE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQKbYEM2U3lDtzGll1HiiPwt2G3QxqJvQUYU8ZqmpoWe_A&amp;oe=6AB6172B
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/818685589_1440631781309045_621455048469772451_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MDUyNzc5NzYyMTE2NTc4NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=aNUXSSptDKIQ7kNvwGWFQAV&amp;_nc_oc=Adq1Q8bpvrXeMtnNXJjxFe5WDjoE4YIB8lojNXjWkHT1ojLOnwFr6BdAkGHS5sZ4epE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQLFg3XxD4DpFYL3lk-hrHgrTGQRDYqmOMTBbZRfYpxtCg&amp;oe=6AB6172B
+https://scontent-lax7-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwHaI_dS&amp;_nc_oc=Adq3LGJyNFrC9-EzezVyaOsWC-5zSCe28c6wHeqJ5VQu8HMR1zTDSheLtUNfpsIG7sg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQLMLr9A-7ja_0OMTP6yRJ_fAJhG7KaZt9cF9etcqieuAA&amp;oe=6AB5F499
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fmetoxinternationalinc%2Fjobs%2F5427064008%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafAnfJEhUBUjLEZwazZB5-HpjHtGB4XQah6msKxiR735qzcoh1Dl4Jb-0V-LA_aem_eFvYmJNa3ZtwuKE2VAIVAw&amp;e=AUCEdud0_rfjOoftSpwt5iEc92zyCj4HCxjScx-NVl9sM3bB4xSlWybQhxEpxW_FkqKjus7k0AWw1BVysI7qQ3N_hC547cusIUSdraDXsKvhbWGIPn1mbE7xzuVUbF9Zpcc3G4ZqakqZiw
+https://scontent-lax7-1.cdninstagram.com/o1/v/t2/f2/m78/AQNia4NhiTsCq_R8gPiA8IpCYdycxW5SiPgaBc9dnaZ4p_d4N37FRtLBCxDZEP-4twRMtINQJWoP4RvbkAwmtbFF0VTjofz7FXT7bMM.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ohc=K29E6Os_1gAQ7kNvwF-ERDh&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NDk1NTM2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=586407a44edfc03a&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzczNEIyOUQyOTI1MDRGODdFNjZBMThDODFDRUY5NkEyX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkicDn4qehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQL1RjHdM0ARSKrSOax3T-TLZ10JjzVWiaEdbu7ILLiCuQ&amp;oe=6AB20346</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59" ht="45" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>ce4c166ea68390433278</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:31:44.047687+00:00</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T18:34:53+00:00</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Embed</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Embed — Other Opportunity</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr"/>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/embed/job_app?for=gemini&amp;token=8214332&amp;gh_jid=8214332</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>@ job-boards.greenhouse.io G
+Instagram
+© New York, New York
+Apply
+About the Company
+Gemini is a global crypto and Web3 platform
+ICHAVIC, AINU SSULUTS LIYVPLU PIUUULLS aIIU
+services to individu institutions in
+over 7O countries. O ion is to unlock
+the next era of financial, creative, and
+personal freedom by providing trusted
+access to the decentralized future. We
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/818553715_1094247189959185_7437255251207578059_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MDUzODYzOTgxMzE1MjUyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=nfnKuDVS7AkQ7kNvwGXsJOw&amp;_nc_oc=Adq2EponO1YmmM_sAqbuQ7b2gqGBdNzmZfnKMAD7LXcCkzW71_DD3NyqxR88421YaFQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQIxYQnL0SPhE85n9TT3cOiuXl6OfpkB4iA_OGUnOUTBgQ&amp;oe=6AB60307
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/818553715_1094247189959185_7437255251207578059_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MDUzODYzOTgxMzE1MjUyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=nfnKuDVS7AkQ7kNvwGXsJOw&amp;_nc_oc=Adq2EponO1YmmM_sAqbuQ7b2gqGBdNzmZfnKMAD7LXcCkzW71_DD3NyqxR88421YaFQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQK6ZSEga0pWXH-cCODrtecPd7Jzli9TbW6XPh-Bnwc5kg&amp;oe=6AB60307
+https://scontent-lax7-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwHaI_dS&amp;_nc_oc=Adq3LGJyNFrC9-EzezVyaOsWC-5zSCe28c6wHeqJ5VQu8HMR1zTDSheLtUNfpsIG7sg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQLMLr9A-7ja_0OMTP6yRJ_fAJhG7KaZt9cF9etcqieuAA&amp;oe=6AB5F499
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fembed%2Fjob_app%3Ffor%3Dgemini%26token%3D8214332%26gh_jid%3D8214332%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeSBzxNjtXfvmxX4HbFItwzvyNYDSeZ7IDF6bxVooxCTh1GKMeNd_vhcj7bCA_aem_WvZP0cSPbL0xBxop-6Ywiw&amp;e=AUAAaB_vBqJMRLW76cojHFmAqE9ifFJsXOc73qg7hx7iummjsyG2HE7Y8QzU9E1r_JIfqeryPa_QDKxn23WgUVMP2XnDpSpWEZpaoIKWsuDn7XLZfzVKTCER3oyqfMhAnAz5kY-IzzNr-g
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQOU2LU4EC3nZMC3geQwThjPHa5ycn7x0UNGx-9EOWaQ3eMwCUlW02SKsWUNo1vUQto991qFiKNOf1p8S-kV7DQ_y1aRnfBYvowFO-o.mp4?_nc_cat=102&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=pWJQPf-Okd4Q7kNvwGgjJ2d&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NTIwNDY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=9d882df02caeb57e&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0VFNDA2NDAxQjY5MEE2M0E0QTY2NEYxOTFFRjhGNTk3X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkroGx9aehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKWpBm_ylWjsPQrFTFLzFh5MWqZXT9Lb4MRrUSjcFDseA&amp;oe=6AB20073</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60" ht="45" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>76f65ccbff7a905576a9</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:31:45.256659+00:00</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T18:54:43+00:00</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr"/>
+      <c r="I60" s="3" t="inlineStr"/>
+      <c r="J60" s="3" t="inlineStr"/>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>https://apply.careers.microsoft.com/careers/job/1970393556982258?domain=microsoft.com&amp;hl=en</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>@ apply.careers.microsoft.com C:
+Instagram -
+€ View All Jobs
+Software Engineering
+Internship (6-month
+Program)
+2] United States, California, Santa Clara +1 more
+Apply now
+Add to cart
+9 PAP
+Microsoft 6 month SWE intern
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/818250663_2228590974386507_7756861971034096205_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5MDU0ODYxNTcxMzU1MzgxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=iH8InmR2DzEQ7kNvwE_GwZQ&amp;_nc_oc=AdpeMASCszpgktAV2kkwhPIyuCLxOzkESRPVH55WWqfIOK-2nk3QObOvfrW_aJVc21Y&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQK8y6yJcauXJVpmQgDQLxWnJb0AXKs2J1zWmvWXYwA-ZQ&amp;oe=6AB5F6F9
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/818250663_2228590974386507_7756861971034096205_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5MDU0ODYxNTcxMzU1MzgxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=iH8InmR2DzEQ7kNvwE_GwZQ&amp;_nc_oc=AdpeMASCszpgktAV2kkwhPIyuCLxOzkESRPVH55WWqfIOK-2nk3QObOvfrW_aJVc21Y&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQI34lHe9EDm0fnhJkO5XUUrNz3MVvTXgedpx1hsSmBoMw&amp;oe=6AB5F6F9
+https://scontent-lax7-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwHaI_dS&amp;_nc_oc=Adq3LGJyNFrC9-EzezVyaOsWC-5zSCe28c6wHeqJ5VQu8HMR1zTDSheLtUNfpsIG7sg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQLMLr9A-7ja_0OMTP6yRJ_fAJhG7KaZt9cF9etcqieuAA&amp;oe=6AB5F499
+https://l.instagram.com/?u=https%3A%2F%2Fapply.careers.microsoft.com%2Fcareers%2Fjob%2F1970393556982258%3Fdomain%3Dmicrosoft.com%26hl%3Den%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaecAl4PUxS3DJRk1-QquoTS9puRoucgEDm_-gG8NVXWm6VpBkVkBAtiDgUyvg_aem_XV2jT4a2WzuEmgL2hP6-Sg&amp;e=AUC_mAu5ZkM8DZJkxbaWeqvh_T4KH1iW11-fxXYW-2BLX_qrotJbnwDz7K3qyhNhHTQ3mmSJlBWoQUWq85AwGwdhUiVAyJIi_UrU4c2SILuSm5DZqWySYR3OmA0b94njfys732Vlxm5BzQ
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQN8s1on0D0qm7rNdzjDIhCBKsu6L3DBc_p2QiGx2Ep90t7MWQX-3YEmxHcvTdlGcZDm4bazQdec1b-0X_LotGuaxyeVxRGcFXS07RU.mp4?_nc_cat=110&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=4lTN07ErgasQ7kNvwFC_KtP&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NTQzNTk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=9900fa936e03aa45&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0QxNEI1QzQ4OTNFNzEwQ0VGNDgzQjhERDMyNDhGQjkyX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk_-3OhqihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKBRdPJipUHPVtYDwXaFTR1QzZ9b6ucspLExBbrL3ZwWw&amp;oe=6AB2095B</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61" ht="45" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>4e16d0d1cb76f8cb0143</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:31:49.147681+00:00</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:04:55+00:00</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr"/>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Summer Internship-.</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr"/>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>https://corporate.target.com/jobs/w10/82/software-engineering-summer-internship-minneapolis,-mn-starting-june-2027</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>(Il
+O
+&lt; Job Search
+Software Engineering
+Summer Internship-.
+Minneapolis, MN’ —
+(Starting June 2027)
+w
+Internships Full-time
+https://scontent-lax7-1.cdninstagram.com/v/t51.71878-15/818062750_1716197372810335_456094538637226437_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MDU1Mzc0OTAxMzE1MTI0OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=stf7Zk7_P8kQ7kNvwEZpiMz&amp;_nc_oc=Adpuwo5Lnvnn7B-6cXy77zHcDDC07XmI-TYnWNhkDpiCwQQbQ7kvEM6oyp0QEBIbiTo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQInmWSV4-7TOH8IzcfwJfklPCBUeKiIDKQ954YNP9RgZg&amp;oe=6AB60BA2
+https://scontent-lax7-1.cdninstagram.com/v/t51.71878-15/818062750_1716197372810335_456094538637226437_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MDU1Mzc0OTAxMzE1MTI0OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=stf7Zk7_P8kQ7kNvwEZpiMz&amp;_nc_oc=Adpuwo5Lnvnn7B-6cXy77zHcDDC07XmI-TYnWNhkDpiCwQQbQ7kvEM6oyp0QEBIbiTo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQJYNF5ekwoNCFwApbW-eFTvgTYs8BkFZ4EncXU3Cp8iIQ&amp;oe=6AB60BA2
+https://scontent-lax7-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwHaI_dS&amp;_nc_oc=Adq3LGJyNFrC9-EzezVyaOsWC-5zSCe28c6wHeqJ5VQu8HMR1zTDSheLtUNfpsIG7sg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQLMLr9A-7ja_0OMTP6yRJ_fAJhG7KaZt9cF9etcqieuAA&amp;oe=6AB5F499
+https://l.instagram.com/?u=https%3A%2F%2Fcorporate.target.com%2Fjobs%2Fw10%2F82%2Fsoftware-engineering-summer-internship-minneapolis%2C-mn-starting-june-2027%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAac83RepOX2DxDFaQYRzlg5P057vv73o3_usNCKujYBmVRsjvKEmqCV3gElpLQ_aem_qT4J1SfO5XP1JPTKSOBOzA&amp;e=AUAu34_JiEClC5qo8t08pfsZ9nJNN3PJNxoKA7--vK38zP3JF4_FE8-CgEuEU-raQHCnxjKiwhpIhitQdn-cnIgaiGG-t1EhnxX2OjPJ62zj_fI2noQ1PP1y4_0IX1B5a9hynwEjLJsIjA
+https://scontent-lax7-1.cdninstagram.com/o1/v/t2/f2/m78/AQM7ky4btPc3TQm2P4hl_vVqjKf00FmU75KQVKjTi27gyc_L9RZGHPbGb6wEIms1O0KnVQ4oxBJVu2AtvY1atTvuu1rrciLG7lcc0IY.mp4?_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ohc=YAAv0a6x3f0Q7kNvwGtOnO4&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NTU2MTA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=dbf67b1706ad0cb8&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzFDNEM1NUNGQTM5RjBCNEE3RDk0RTkxRjFBMzgzQUFEX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk-vP3j6ihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIZF9nAN9hox_qZt3qp4uT1uOjSOlpUvKz3sDVUY7CdPQ&amp;oe=6AB22162</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62" ht="45" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>c7a8b582c2c09622af10</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:31:50.522996+00:00</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:05:31+00:00</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr"/>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>UX Design Internship -</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr"/>
+      <c r="J62" s="3" t="inlineStr"/>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>https://corporate.target.com/jobs/w10/77/ux-design-internship-minneapolis,-mn-starting-summer,-2027</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>@ corporate.target.com C:
+Instagram
+&lt; JobSearch
+~~.
+UX Design Internship -
+Minneapolis, MN
+(Starting Sumroc tt
+2027)
+Internships oy
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/819051047_4225384054263146_2989809718136161509_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MDU1NDA1Njk1ODk5NjgxOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=mlO_3eSjwigQ7kNvwF5UP8K&amp;_nc_oc=AdqyRJbrMglkTZJwm7WIfSfHvvSunRdQt9NbgiBP1leL9KPPLMcHMq_ULfUj3W8Yujg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQLAzNwf3lYFJM1B95EXUI0X9jCyooMtmAGAGcygR00NhA&amp;oe=6AB60D05
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/819051047_4225384054263146_2989809718136161509_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MDU1NDA1Njk1ODk5NjgxOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=mlO_3eSjwigQ7kNvwF5UP8K&amp;_nc_oc=AdqyRJbrMglkTZJwm7WIfSfHvvSunRdQt9NbgiBP1leL9KPPLMcHMq_ULfUj3W8Yujg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQJFISyIP-VJPtXgQnNzqg2VshOp5CqRTBHEfNf8r83Fqw&amp;oe=6AB60D05
+https://scontent-lax7-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwHaI_dS&amp;_nc_oc=Adq3LGJyNFrC9-EzezVyaOsWC-5zSCe28c6wHeqJ5VQu8HMR1zTDSheLtUNfpsIG7sg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQLMLr9A-7ja_0OMTP6yRJ_fAJhG7KaZt9cF9etcqieuAA&amp;oe=6AB5F499
+https://l.instagram.com/?u=https%3A%2F%2Fcorporate.target.com%2Fjobs%2Fw10%2F77%2Fux-design-internship-minneapolis%2C-mn-starting-summer%2C-2027%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaf0gvghVyL3ghd9hKCT_lyirf5oKlnYn7e1X-eI9o-6tMv7O5ziQXZiQ7diHg_aem_8RTb6XxJnUGEigIhuwo_iQ&amp;e=AUBHlq_SgrCFI81Sw4qchCb_QR3gbBUTdD1oO6qHGNPSw4xIgZsWPmRVURZlXBtnlzyp2SUSznWMFfgFRm5rQDVKlLcx61RGZTYTTiDgIB8QCO5cqtM-Cvt1wQKsCdrqaaqR9OtoSARpWA
+https://scontent-lax3-2.cdninstagram.com/o1/v/t2/f2/m78/AQNJbzeJdDBTSAWyyj1sVIISC9Ywi27V71Fa3puaW7lxpCVTa1gOEYEagWNQUqiayZpE8UhYVSDiQYiqUxDeJePvth_TU294Ko6o6w4.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ohc=EaVc9fn7jlcQ7kNvwG2zXjJ&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NTU2OTc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=e4fe238398883b56&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0Y3NEE4QzBBRENDMTI1RTg3NEVGMDlCMkRFQUVCQzhGX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkifDKkKihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQI-Ih_o74sDBvSSdcmyKFSgvKVe8gHNdAKmrxd4G4lnWw&amp;oe=6AB209A4</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q62" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63" ht="45" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>40b7c3397dcd2e60ca3b</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:31:52.177981+00:00</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:11:22+00:00</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Cmegroup</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Cmegroup — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr"/>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>https://cmegroup.wd1.myworkdayjobs.com/en-US/cme_careers/job/Chicago---20-S-Wacker/Software-Engineering-Internship---Summer-2027_34821</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>@ CME Group
+BUILD A CAREER BY SHAPING TOMORROW
+@ CME Group
+Software Engineering
+Internship - Summer 2027
+© Chicago - 20 S. Wacker
+fc] Full time
+(7) CMEGROUP.WD1.MYWORKDAYJOBS.
+We are looking for mo and talented
+students who want to help us solve some of
+CME Group General SWE Internship
+write and maintain ultra low-latency electronic
+trading platforms, risk management systems,
+and front-end trading interfaces, all of which
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/819272073_1619500616228350_1370677816217657977_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MDU1Njk5MTAyNTYzMzA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=JliNYXAeWv0Q7kNvwH-dzWZ&amp;_nc_oc=AdrObPIUPIa3mx8bkH4stxKKEeqV4KNeNQCJNlsadLO_iBtLsNYqqdlJ9sKvGlc-8oE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQIryS6DRWpmkF6ETaP4JPqKTcG0MwO-Mqmbe-jshQMGcw&amp;oe=6AB610AE
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/819272073_1619500616228350_1370677816217657977_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MDU1Njk5MTAyNTYzMzA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=JliNYXAeWv0Q7kNvwH-dzWZ&amp;_nc_oc=AdrObPIUPIa3mx8bkH4stxKKEeqV4KNeNQCJNlsadLO_iBtLsNYqqdlJ9sKvGlc-8oE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;oh=00_AQJJEHb6BDc4_OAHpzfLDOjrzoxejjmL6n6H3ofm564kNQ&amp;oe=6AB610AE
+https://scontent-lax7-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwHaI_dS&amp;_nc_oc=Adq3LGJyNFrC9-EzezVyaOsWC-5zSCe28c6wHeqJ5VQu8HMR1zTDSheLtUNfpsIG7sg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQLMLr9A-7ja_0OMTP6yRJ_fAJhG7KaZt9cF9etcqieuAA&amp;oe=6AB5F499
+https://l.instagram.com/?u=https%3A%2F%2Fcmegroup.wd1.myworkdayjobs.com%2Fen-US%2Fcme_careers%2Fjob%2FChicago---20-S-Wacker%2FSoftware-Engineering-Internship---Summer-2027_34821%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadBOEVPZTKVv9NKjiry3T-dRtok15cRANTpBYO-62R_3A5bhegPR_R8sDrj3g_aem_oVwozUnkPnFJ6p3CfyfY5w%26utm_id%3D97760_v0_s00_e0_tv6&amp;e=AUDJKyw2rxpJeXK9gYYPjucXG7WRTub2kOpE8nhcOakgolrvt1X_bcyV3k7EqnjJJkjNdP4y3RFRyQL7tHU4N9NC5HRx_3bbPQACGhezfg4Ydh2dQ7Li9PRB9Cj5orMhE2FLQrjxxkSMkg
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQMQjVlNthOcwaCNdPV5xTc-19gpecml_70hZXZAcXcPQrCgqJw6f3BnLhbpdv_QRIoClAoiATdIXecKeuNe9gYF_G0TGbASysQBAmE.mp4?_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=oDa0ZW34AioQ7kNvwGJlZLi&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NTY4ODU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=ac0ac53d444e084e&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzg4NENFMDBFRjgyNzdBODE4MzZBRTgxNjQ0MzREMDkzX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkzeu3maihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=iRKYyKODeStU4Vu7SLjNog&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKbQtDyEIbYue_RA0-07YUK-WxkSnTF3o6uVBz-7cJuhA&amp;oe=6AB1FFCD</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R63" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R43"/>
+  <autoFilter ref="A1:R63"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -4576,6 +6473,46 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId112"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R63"/>
+  <dimension ref="A1:R68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4496,7 +4496,7 @@
     <row r="44" ht="45" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>bb4c73a1e31623b25741</t>
+          <t>4184e41d4d6579412bc5</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -4524,7 +4524,7 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="n"/>
       <c r="H44" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
@@ -4535,7 +4535,7 @@
           <t>Bellevue, Menlo Park</t>
         </is>
       </c>
-      <c r="J44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="n"/>
       <c r="K44" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/robinhood/jobs/8214142?t=gh_src%3D&amp;gh_jid=8214142</t>
@@ -4590,12 +4590,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="n"/>
     </row>
     <row r="45" ht="45" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>088edc02396f8c754958</t>
+          <t>2da5d9b33b6e8165b1f3</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -4633,8 +4633,8 @@
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr"/>
-      <c r="J45" s="3" t="inlineStr"/>
+      <c r="I45" s="3" t="n"/>
+      <c r="J45" s="3" t="n"/>
       <c r="K45" s="4" t="inlineStr">
         <is>
           <t>https://amazon.jobs/en/jobs/10553947/software-development-engineer-intern-summer-2027-can</t>
@@ -4693,12 +4693,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="n"/>
     </row>
     <row r="46" ht="45" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>7fbe5df77a220cad7844</t>
+          <t>8337ca7d5fbaa15764ea</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -4741,7 +4741,7 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr"/>
+      <c r="J46" s="3" t="n"/>
       <c r="K46" s="4" t="inlineStr">
         <is>
           <t>https://cmegroup.wd1.myworkdayjobs.com/en-US/cme_careers/job/Chicago---20-S-Wacker/Software-Engineering-Fellowship---Summer-2027_34824</t>
@@ -4795,12 +4795,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="n"/>
     </row>
     <row r="47" ht="45" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>8ad3c6d9e6121e96eff0</t>
+          <t>612acb144e9d92f3393e</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -4813,7 +4813,7 @@
           <t>2026-09-20T17:33:12+00:00</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="n"/>
       <c r="E47" s="3" t="inlineStr">
         <is>
           <t>Tesla Summer 2027 SWE Intern</t>
@@ -4834,8 +4834,8 @@
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr"/>
-      <c r="J47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="n"/>
+      <c r="J47" s="3" t="n"/>
       <c r="K47" s="4" t="inlineStr">
         <is>
           <t>https://www.tesla.com/careers/search/job/284004</t>
@@ -4889,12 +4889,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="n"/>
     </row>
     <row r="48" ht="45" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>e780735abf15677b2046</t>
+          <t>3637f74a13b08023145c</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -4937,7 +4937,7 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="J48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="n"/>
       <c r="K48" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/embed/job_app?for=gemini&amp;token=8214272&amp;gh_jid=8214272</t>
@@ -4989,12 +4989,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="n"/>
     </row>
     <row r="49" ht="45" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>7abe95aedc3b735601be</t>
+          <t>1081797658af10c36afd</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -5007,7 +5007,7 @@
           <t>2026-09-20T17:38:51+00:00</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="n"/>
       <c r="E49" s="3" t="inlineStr">
         <is>
           <t>Internship Dates: January 11, 2027 -</t>
@@ -5028,8 +5028,8 @@
           <t>Winter 2027</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr"/>
-      <c r="J49" s="3" t="inlineStr"/>
+      <c r="I49" s="3" t="n"/>
+      <c r="J49" s="3" t="n"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
           <t>https://www.rubrik.com/company/careers/departments/job.8171088?gh_jid=8171088</t>
@@ -5084,12 +5084,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="n"/>
     </row>
     <row r="50" ht="45" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>7fd55cacb063b2ac27ab</t>
+          <t>9715025cd1377607017a</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -5122,13 +5122,13 @@
           <t>Hardware</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="n"/>
       <c r="I50" s="3" t="inlineStr">
         <is>
           <t>Redmond</t>
         </is>
       </c>
-      <c r="J50" s="3" t="inlineStr"/>
+      <c r="J50" s="3" t="n"/>
       <c r="K50" s="4" t="inlineStr">
         <is>
           <t>https://apply.careers.microsoft.com/careers/job/1970393557002608</t>
@@ -5178,12 +5178,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="n"/>
     </row>
     <row r="51" ht="45" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>07dd815ef7fe2ecde141</t>
+          <t>bd98bd21c2b87a07c099</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -5226,7 +5226,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="J51" s="3" t="inlineStr"/>
+      <c r="J51" s="3" t="n"/>
       <c r="K51" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/togetherai/jobs/5232036007</t>
@@ -5280,12 +5280,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="n"/>
     </row>
     <row r="52" ht="45" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>47ae3eeb80ba3c22e429</t>
+          <t>088775cf79d9bb115fcd</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -5323,8 +5323,8 @@
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr"/>
-      <c r="J52" s="3" t="inlineStr"/>
+      <c r="I52" s="3" t="n"/>
+      <c r="J52" s="3" t="n"/>
       <c r="K52" s="4" t="inlineStr">
         <is>
           <t>https://jobs.jobvite.com/tylertech/job/oAVOAfwD?nl=1&amp;fr=false</t>
@@ -5383,12 +5383,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="n"/>
     </row>
     <row r="53" ht="45" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>d73483fb3da3fa833398</t>
+          <t>54fa735b813e0dba0cc2</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -5431,7 +5431,7 @@
           <t>Remote</t>
         </is>
       </c>
-      <c r="J53" s="3" t="inlineStr"/>
+      <c r="J53" s="3" t="n"/>
       <c r="K53" s="4" t="inlineStr">
         <is>
           <t>https://thrivent.wd5.myworkdayjobs.com/external/job/Remote-Minnesota/Associate-Software-Engineer---Sophomore-Intern-Summer-2027_REQ-48457</t>
@@ -5481,12 +5481,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="n"/>
     </row>
     <row r="54" ht="45" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>731b58b2665e61030985</t>
+          <t>2f526a7bb467d13b0d17</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -5499,10 +5499,10 @@
           <t>2026-09-20T18:05:45+00:00</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr"/>
+      <c r="D54" s="3" t="n"/>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>contribute to as an intern within the</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -5510,14 +5510,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr"/>
+      <c r="G54" s="3" t="n"/>
       <c r="H54" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="I54" s="3" t="inlineStr"/>
-      <c r="J54" s="3" t="inlineStr"/>
+      <c r="I54" s="3" t="n"/>
+      <c r="J54" s="3" t="n"/>
       <c r="K54" s="4" t="inlineStr">
         <is>
           <t>https://recruitment.macquarie.com/en_US/careers/JobDetail?jobId=24234&amp;source=zero2sudo</t>
@@ -5570,12 +5570,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="n"/>
     </row>
     <row r="55" ht="45" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>8bf6d9ccc1bfbc15f1be</t>
+          <t>583695f0ce2ed204aaa5</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -5608,9 +5608,9 @@
           <t>Data Science</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr"/>
-      <c r="I55" s="3" t="inlineStr"/>
-      <c r="J55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="n"/>
+      <c r="I55" s="3" t="n"/>
+      <c r="J55" s="3" t="n"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
           <t>https://careers.celestica.com/job/San-Jose-Student-Intern%2C-AI-Data-Science-CA-95101/1439115933</t>
@@ -5654,12 +5654,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="n"/>
     </row>
     <row r="56" ht="45" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>a906527dc68d6e18c0a1</t>
+          <t>40926ee53fcc07dc6c0e</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -5687,14 +5687,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G56" s="3" t="inlineStr"/>
-      <c r="H56" s="3" t="inlineStr"/>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
       <c r="I56" s="3" t="inlineStr">
         <is>
           <t>Seattle</t>
         </is>
       </c>
-      <c r="J56" s="3" t="inlineStr"/>
+      <c r="J56" s="3" t="n"/>
       <c r="K56" s="4" t="inlineStr">
         <is>
           <t>https://apply.careers.microsoft.com/careers/job/1970393556982262</t>
@@ -5744,12 +5744,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="n"/>
     </row>
     <row r="57" ht="45" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>206d81a1fa917e2d2884</t>
+          <t>f3e8318dd143ff719aaf</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -5777,14 +5777,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr"/>
-      <c r="H57" s="3" t="inlineStr"/>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
       <c r="I57" s="3" t="inlineStr">
         <is>
           <t>Mountain View</t>
         </is>
       </c>
-      <c r="J57" s="3" t="inlineStr"/>
+      <c r="J57" s="3" t="n"/>
       <c r="K57" s="4" t="inlineStr">
         <is>
           <t>https://apply.careers.microsoft.com/careers/job/1970393556982259</t>
@@ -5836,12 +5836,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="n"/>
     </row>
     <row r="58" ht="45" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>762cc629290d15c1c399</t>
+          <t>bc85339e2ffcc514913e</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -5879,8 +5879,8 @@
           <t>Spring 2027</t>
         </is>
       </c>
-      <c r="I58" s="3" t="inlineStr"/>
-      <c r="J58" s="3" t="inlineStr"/>
+      <c r="I58" s="3" t="n"/>
+      <c r="J58" s="3" t="n"/>
       <c r="K58" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/metoxinternationalinc/jobs/5427064008</t>
@@ -5933,12 +5933,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R58" s="3" t="inlineStr"/>
+      <c r="R58" s="3" t="n"/>
     </row>
     <row r="59" ht="45" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>ce4c166ea68390433278</t>
+          <t>8e81abd555ff2d671ab2</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -5966,14 +5966,14 @@
           <t>Other Opportunity</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr"/>
-      <c r="H59" s="3" t="inlineStr"/>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
       <c r="I59" s="3" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="J59" s="3" t="inlineStr"/>
+      <c r="J59" s="3" t="n"/>
       <c r="K59" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/embed/job_app?for=gemini&amp;token=8214332&amp;gh_jid=8214332</t>
@@ -6025,12 +6025,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R59" s="3" t="inlineStr"/>
+      <c r="R59" s="3" t="n"/>
     </row>
     <row r="60" ht="45" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>76f65ccbff7a905576a9</t>
+          <t>f1c6ac044d0d9a4579da</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -6063,9 +6063,9 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr"/>
-      <c r="I60" s="3" t="inlineStr"/>
-      <c r="J60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="n"/>
+      <c r="I60" s="3" t="n"/>
+      <c r="J60" s="3" t="n"/>
       <c r="K60" s="4" t="inlineStr">
         <is>
           <t>https://apply.careers.microsoft.com/careers/job/1970393556982258?domain=microsoft.com&amp;hl=en</t>
@@ -6116,12 +6116,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R60" s="3" t="inlineStr"/>
+      <c r="R60" s="3" t="n"/>
     </row>
     <row r="61" ht="45" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>4e16d0d1cb76f8cb0143</t>
+          <t>8b08e92afc97b31859db</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -6134,7 +6134,7 @@
           <t>2026-09-20T19:04:55+00:00</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr"/>
+      <c r="D61" s="3" t="n"/>
       <c r="E61" s="3" t="inlineStr">
         <is>
           <t>Summer Internship-.</t>
@@ -6155,8 +6155,8 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr"/>
-      <c r="J61" s="3" t="inlineStr"/>
+      <c r="I61" s="3" t="n"/>
+      <c r="J61" s="3" t="n"/>
       <c r="K61" s="4" t="inlineStr">
         <is>
           <t>https://corporate.target.com/jobs/w10/82/software-engineering-summer-internship-minneapolis,-mn-starting-june-2027</t>
@@ -6205,12 +6205,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R61" s="3" t="inlineStr"/>
+      <c r="R61" s="3" t="n"/>
     </row>
     <row r="62" ht="45" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>c7a8b582c2c09622af10</t>
+          <t>f3e5a017150e005467c5</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -6223,7 +6223,7 @@
           <t>2026-09-20T19:05:31+00:00</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr"/>
+      <c r="D62" s="3" t="n"/>
       <c r="E62" s="3" t="inlineStr">
         <is>
           <t>UX Design Internship -</t>
@@ -6244,8 +6244,8 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="I62" s="3" t="inlineStr"/>
-      <c r="J62" s="3" t="inlineStr"/>
+      <c r="I62" s="3" t="n"/>
+      <c r="J62" s="3" t="n"/>
       <c r="K62" s="4" t="inlineStr">
         <is>
           <t>https://corporate.target.com/jobs/w10/77/ux-design-internship-minneapolis,-mn-starting-summer,-2027</t>
@@ -6294,12 +6294,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R62" s="3" t="inlineStr"/>
+      <c r="R62" s="3" t="n"/>
     </row>
     <row r="63" ht="45" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>40b7c3397dcd2e60ca3b</t>
+          <t>ca2e3f51217c40373a1b</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -6342,7 +6342,7 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="J63" s="3" t="inlineStr"/>
+      <c r="J63" s="3" t="n"/>
       <c r="K63" s="4" t="inlineStr">
         <is>
           <t>https://cmegroup.wd1.myworkdayjobs.com/en-US/cme_careers/job/Chicago---20-S-Wacker/Software-Engineering-Internship---Summer-2027_34821</t>
@@ -6396,10 +6396,500 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R63" s="3" t="inlineStr"/>
+      <c r="R63" s="3" t="n"/>
+    </row>
+    <row r="64" ht="45" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>4d49af86ae200e4c6010</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:32:10.692651+00:00</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T20:20:06+00:00</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Google — Product Management</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Workshop / Info Session</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr"/>
+      <c r="J64" s="3" t="inlineStr"/>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>https://rsvp.withgoogle.com/events/uw-google-career-workshop-2026/forms/registration</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>@ rsvp.withgoogle.com C:
+oogle Sign In
+University of
+Wisconsin -
+Madison x Google
+Career Workshop
+Please RSVP to attend Google's Career Workshop
+taking place Tuesday Sept 22 | 4:30-6:00pm at
+WARF Centennial Seminar Hub - 7th Floor. Note:
+RSVP does not guarantee entry. Seating is first
+come, first served.
+September 22, 2026 at 4:30 PM -
+* September 22, 2026 at 6:00 PM CDT
+PSA Wisconsin students - share with
+your friends before it fills up!
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/797101964_2342389466569152_6976791631158622096_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MDU5MTU4NDUxMzE4OTMyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=daNiSu8njWQQ7kNvwFkyqT1&amp;_nc_oc=AdoOBNNe4tWUTNcHrZUkSx5C4ztx0dz9MfuzqBdR4ntHQWWTKjakumWW8WcOMAIwjvo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=PAIFeRD54Uy2jrTozMBDPA&amp;_nc_ss=7e3ba&amp;oh=00_AQJttRa2weHubRPeS_gScp83pQvIAoX3UekPOPJ3VtbV0g&amp;oe=6AB64805
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/797101964_2342389466569152_6976791631158622096_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MDU5MTU4NDUxMzE4OTMyNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=daNiSu8njWQQ7kNvwFkyqT1&amp;_nc_oc=AdoOBNNe4tWUTNcHrZUkSx5C4ztx0dz9MfuzqBdR4ntHQWWTKjakumWW8WcOMAIwjvo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=PAIFeRD54Uy2jrTozMBDPA&amp;_nc_ss=7e3ba&amp;oh=00_AQLZvKlmp4DUFyJKYGj4Rl7iDgdhh_DFi9gPKoO58aj1NA&amp;oe=6AB64805
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwE17_Nj&amp;_nc_oc=AdoaxT-oEqzqimewLLsjlgtPsx41LdjP8EQv0VZzMCVGFUvIkZMPGOHA6H_zPOaAQN0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIRy378DFED3lc-frZ8Zl3dq3tUnJLobQ4Doe1wWqPb4w&amp;oe=6AB62CD9
+https://l.instagram.com/?u=https%3A%2F%2Frsvp.withgoogle.com%2Fevents%2Fuw-google-career-workshop-2026%2Fforms%2Fregistration%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafnCf2LGHeknPZmOjAKmjfWLlcADGOqFpj75smuLoecuMJNQ261K4ECew_L7w_aem_XE739uK9f1PKz8-hsIxaAw&amp;e=AUBnCiEfGAo19Ptei4oJBrX04mfLscfuiIw_wIThMFgyiT68JLhA49mXTgaD00nAN9t3x-NsLwdce2Ce1H1iXTgUW7kRm_zVWxbaKQpciw
+https://scontent-sjc6-1.cdninstagram.com/o1/v/t2/f2/m78/AQOju9-l_D1DFWq3WjY0bPXmvOmPrs6Py9T_CYrDrs5ppGlfxbAIk9KZvar0ET9htMP06b5M7g1uwBMHuv5AUgeuIiMK77QMirqJawU.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ohc=s6fa8sssh0QQ7kNvwGxpCHi&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NjMyNjA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=b24cbf4723b8beae&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzA5NEY3RUVGNkI4MDU5OEFBM0ZFQkRENjZGNUU3MzhDX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk7MH3yKihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=PAIFeRD54Uy2jrTozMBDPA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIWziIqjYFvlja052yJcD33Re32OnTTFnTYCqLiBFpztg&amp;oe=6AB24B45</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q64" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65" ht="45" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>17ff3188b8937fef7110</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:32:12.911350+00:00</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T20:20:53+00:00</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Amazon — Machine Learning / AI</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Machine Learning / AI</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr"/>
+      <c r="J65" s="3" t="inlineStr"/>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>https://amazon.jobs/en/jobs/10394278/2026-fall-applied-science-internship-reinforcement-learning-optimization-machine-learning-united-states-phd-student-science-recruiting</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
+          <t>x @ amazon.jobs C:
+Instagram ps
+= amazonjobs Q
+| 2026 Fall Applied
+Science Internship -
+Reinforcement Learning
+&amp; Optimization
+(Machine Learning) -
+United States, PhD
+Student Science
+Recruiting
+Job ID: 10394278 | Amazon.com Services LLC
+@ AMAZON.JOBS
+Description Ny
+Unlock the Future with Amazon Science!
+Calling all visionary minds passionate about the
+transformative power of machine learning!
+Amazon is seeking boundary-pushing graduate
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/818909906_1255035160090612_829923498727900902_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDU5MTk3MzIwNzc0ODI1MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=kPd2jSg8Y8AQ7kNvwGVZOct&amp;_nc_oc=AdqS-5feXBfPGH5EVubX1KbNUMae4DK9KqJNwNwyoNkqPpUe5hSjvHPxJWKl_-SdTqQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=PAIFeRD54Uy2jrTozMBDPA&amp;_nc_ss=7e3ba&amp;oh=00_AQJoEI_fVNqbdZSZgriQ2iKaSwfs0jC-im6nIhLsgoifqQ&amp;oe=6AB629A7
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/818909906_1255035160090612_829923498727900902_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDU5MTk3MzIwNzc0ODI1MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=kPd2jSg8Y8AQ7kNvwGVZOct&amp;_nc_oc=AdqS-5feXBfPGH5EVubX1KbNUMae4DK9KqJNwNwyoNkqPpUe5hSjvHPxJWKl_-SdTqQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=PAIFeRD54Uy2jrTozMBDPA&amp;_nc_ss=7e3ba&amp;oh=00_AQJpkDNbXSuV679WjbXhEJ62yne8_xyJCEsT1mwz-BOl8w&amp;oe=6AB629A7
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwE17_Nj&amp;_nc_oc=AdoaxT-oEqzqimewLLsjlgtPsx41LdjP8EQv0VZzMCVGFUvIkZMPGOHA6H_zPOaAQN0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIRy378DFED3lc-frZ8Zl3dq3tUnJLobQ4Doe1wWqPb4w&amp;oe=6AB62CD9
+https://l.instagram.com/?u=https%3A%2F%2Famazon.jobs%2Fen%2Fjobs%2F10394278%2F2026-fall-applied-science-internship-reinforcement-learning-optimization-machine-learning-united-states-phd-student-science-recruiting%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeaaKWWRjHIv0BKw0VCVQdrtxgYuMe296fvSeJtPRbNgZq0NoiptCaD7IY_Ew_aem_-oO-jeRBP9V2RHFZzwoc0Q&amp;e=AUB93Mm8-G4pgxEpy0DQrZAOSq6uiVQsCoHw1KqyJhuvRh8UoZGTd6o1zIy5SYKXOY9N3wvCL_O6RpwyhHNKldM-f5YbnCm6YXg4ngS9KQ
+https://scontent-sjc3-1.cdninstagram.com/o1/v/t2/f2/m78/AQNQXj57iI1q8TTsR2f5GOsgvPbiaAm0B8JgAhjgVNq2v1y-jtsKvV-nZFUiHQTp0mM4ulOrqoO3L0vWcpCAX1n7VaiRSIW4SXAXgtE.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_ohc=aSXpIm7v38kQ7kNvwHsH-Ai&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NjMzNDc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=f0b06278f206d163&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0E4NDlBOTcxOTUxODgyNkRBOThDODMzREJGNEJDM0IzX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk-73KyaihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=PAIFeRD54Uy2jrTozMBDPA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJeYmG1GJHzZezlq7vpXQ-WUkjT1ip7OrkMJh1UTXPqhQ&amp;oe=6AB2459C</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66" ht="45" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>2979dff0c6ced716aeb9</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:32:18.881032+00:00</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T20:26:24+00:00</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft — Other Opportunity</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr"/>
+      <c r="J66" s="3" t="inlineStr"/>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>https://forms.cloud.microsoft/Pages/ResponsePage.aspx?id=v4j5cvGGr0GRqy180BHbR67drzZ_HMRKrjpUVBFkKE1UQ1JURDUySDk1REpJUk40WlY4UE5SNFdMSC4u</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
+          <t>@ forms.cloud.microsoft (Ex
+GitHub Universe 2026 Micro-
+Mentoring Application
+Apply to participate in a GitHub Universe micro-
+mentoring session! Share your background,
+interests, and mentoring goals to help us connect
+you with a skilled GitHub professional for a 30
+minute session where you can get support on your
+career path in tech.
+Applications are open September 8-22 and you will
+hear back by late September. Sessions will be
+scheduled between October 5-30.
+(2) FORMS.CLOUD.MICROSOFT
+* Required
+1. First Name *
+Enter your answer
+2. Last Name *
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/818479262_1758223018790141_6892203284407885337_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDU5NDc0NzIwMjk0MzIxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Wg2H4_krHewQ7kNvwHnn4ua&amp;_nc_oc=AdqPhp2XwIiCsoxm_Y_3vAQnWqPx6jx5EHAmlbiZy2D03ygwuRGrOeURR7octYoTUt0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=PAIFeRD54Uy2jrTozMBDPA&amp;_nc_ss=7e3ba&amp;oh=00_AQLMtaVuK4L3d9C_2p-0wmMI9RCV9G2pJw4a4MroPJ-WLw&amp;oe=6AB637B1
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/818479262_1758223018790141_6892203284407885337_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MDU5NDc0NzIwMjk0MzIxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Wg2H4_krHewQ7kNvwHnn4ua&amp;_nc_oc=AdqPhp2XwIiCsoxm_Y_3vAQnWqPx6jx5EHAmlbiZy2D03ygwuRGrOeURR7octYoTUt0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=PAIFeRD54Uy2jrTozMBDPA&amp;_nc_ss=7e3ba&amp;oh=00_AQJfDC6yCRqNJP__hzeVNtZ5btQzAIi9hD-ehbQga0arWA&amp;oe=6AB637B1
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwE17_Nj&amp;_nc_oc=AdoaxT-oEqzqimewLLsjlgtPsx41LdjP8EQv0VZzMCVGFUvIkZMPGOHA6H_zPOaAQN0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIRy378DFED3lc-frZ8Zl3dq3tUnJLobQ4Doe1wWqPb4w&amp;oe=6AB62CD9
+https://l.instagram.com/?u=https%3A%2F%2Fforms.cloud.microsoft%2FPages%2FResponsePage.aspx%3Fid%3Dv4j5cvGGr0GRqy180BHbR67drzZ_HMRKrjpUVBFkKE1UQ1JURDUySDk1REpJUk40WlY4UE5SNFdMSC4u%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeIT4zCkz26AKvUJJjWtk7yLDBa99Z_oVNe4dfuuwDE0csq9rgvVjFpdlIfLg_aem_tSHLF2Ul8PVR1IN16taF2A&amp;e=AUBP7n0QSOymRt_MHg11a5hzcnDlvorvEPq7Y3gvb49x7h2xk44uqGPZrdk3l9Qnt6s1GypighFhgCMYUnikerBTDC8ECcNQtr-37RM7Rg
+https://scontent-sjc3-1.cdninstagram.com/o1/v/t2/f2/m78/AQMZlnomK1xmG7u8EofndvN6rajQTgkARjt98HzNdn8dVIIKfPZ21smkqG5pOuNXE7dhoGouXzs5c1iXCjqfADxd6AsMMqHlcYhxJ3U.mp4?_nc_cat=110&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_ohc=Qja-pt5xFBoQ7kNvwFVggt4&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NjM3MDc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=4532c262589af2a6&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzU0NEIzNkJEMUEyRTIyQjY0RTg3NzVCQzRBQTUyM0ExX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbko-ehzKihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=PAIFeRD54Uy2jrTozMBDPA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLugXEmZs4SlFxsfyvwAB1U2kIkC_BvYkcbgHm0Nh0g3Q&amp;oe=6AB24BBB</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q66" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67" ht="45" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>4d68684836842a5003e8</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:32:20.397368+00:00</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T20:28:35+00:00</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr"/>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>is a DoW Scholarship Program for</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr"/>
+      <c r="I67" s="3" t="inlineStr"/>
+      <c r="J67" s="3" t="inlineStr"/>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>https://www.smartscholarship.org/smart/en</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
+          <t>Department of War (DoW)
+Scholarship-for-Service Program
+Scholarship. Stipend.
+Internship. Career.
+Build Your Future With
+SMART
+Science, Mathematics, and
+Research for Transformation
+(SMART)
+is a DoW Scholarship Program for
+STEM Students
+P SMARTSCHOLARSHIP.ORG
+oy oe
+O
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/818730189_1732357891152793_6717289823999387909_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MDU5NTg1MTczOTM4ODQ0MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=LAEzGvEKf9oQ7kNvwGbuksQ&amp;_nc_oc=Adq4446TbVMEkZBwjfHWEEaOG18eXpfcynlCftB81YhnIE1K3l-InLxuqgLXyl2_QC8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=PAIFeRD54Uy2jrTozMBDPA&amp;_nc_ss=7e3ba&amp;oh=00_AQL8vc7pi2QXSwy_QT9yQxvo-tER5wDCu1_VtgRKPpOdZA&amp;oe=6AB64016
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/818730189_1732357891152793_6717289823999387909_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MDU5NTg1MTczOTM4ODQ0MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=LAEzGvEKf9oQ7kNvwGbuksQ&amp;_nc_oc=Adq4446TbVMEkZBwjfHWEEaOG18eXpfcynlCftB81YhnIE1K3l-InLxuqgLXyl2_QC8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=PAIFeRD54Uy2jrTozMBDPA&amp;_nc_ss=7e3ba&amp;oh=00_AQLgIAh5QgIwRtCKCpMQmj20AVuhnCzL3OapmdDHAY8SGw&amp;oe=6AB64016
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwE17_Nj&amp;_nc_oc=AdoaxT-oEqzqimewLLsjlgtPsx41LdjP8EQv0VZzMCVGFUvIkZMPGOHA6H_zPOaAQN0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIRy378DFED3lc-frZ8Zl3dq3tUnJLobQ4Doe1wWqPb4w&amp;oe=6AB62CD9
+https://l.instagram.com/?u=https%3A%2F%2Fwww.smartscholarship.org%2Fsmart%2Fen%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafdRGHxHQhhWOTlrlrxYHi1kbWk7ywqnSBw-7Ba7kcOuOR_sBFcxlYxaJUjkg_aem_tLSCfpH3DiONtdfC3Kl2fg&amp;e=AUCSKrr3Xv_drPav5JDAIzNKsumLJ4YxHQTyW7OVRAnIWXzqojE1ZXzo_jWFKPGEKqnfoPf-gS_rHfjIfwnQvzzm_ARcvNL65YLkcQaiXg
+https://scontent-sjc6-1.cdninstagram.com/o1/v/t2/f2/m78/AQN2vudmj95UzxKULT0w3PBsh8MgC9amsdP4485rZpAI4O42LmDml9oIO69PEtMr0KY538RjDItnDjM52GPgNPI5ZTfmSgs3g_Hxhp4.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ohc=xbiu-Cck3FgQ7kNvwEU-V4s&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NjM4NDI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=9b379e697801028a&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzk2NEI5QzMxODQxNEZFMzNBRUJCRkJDOTI5QzFEQzk5X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk4saizaihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=PAIFeRD54Uy2jrTozMBDPA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIZLTn539rjVrUvibjJxf11wObpT7fRMbn7mLhOEqVFIQ&amp;oe=6AB23CE1</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q67" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68" ht="45" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>21bd1a5c0097c3708fff</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:32:23.674317+00:00</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T20:50:49+00:00</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr"/>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/greenboard/e5deef5b-8667-48d7-be48-a0b6616eaba5</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>@ jobs.ashbyhg.com C:
+Instagram
+Greenboard
+Software Engineer (2027 Grads)
+Location
+New York City
+Employment Type
+Full time
+Location Type
+On-site
+COM
+on Yr 6 = Vint
+A JOBS. ASHBYHO
+=" VUDV.AOIHDITT
+Cea
+Compensation
+$130K - $150K * Of quity
+Overview Application
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/808999994_947380958413430_9013007498583461760_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MDYwNzA0NTk0MjQ2MTg3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=W9M2I_MOHRYQ7kNvwEtYEbk&amp;_nc_oc=AdrhixYIYkkk0kHcYi2BeE9HXBufifO24lOXei6afgoRN2_8SX0ZSkGTgwm6XLOG_hM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=PAIFeRD54Uy2jrTozMBDPA&amp;_nc_ss=7e3ba&amp;oh=00_AQLmaBydnxBXiQCNVw-FLrdoi3EWVt0F3fZvA4kgNQd3kQ&amp;oe=6AB61C51
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/808999994_947380958413430_9013007498583461760_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MDYwNzA0NTk0MjQ2MTg3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=W9M2I_MOHRYQ7kNvwEtYEbk&amp;_nc_oc=AdrhixYIYkkk0kHcYi2BeE9HXBufifO24lOXei6afgoRN2_8SX0ZSkGTgwm6XLOG_hM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=PAIFeRD54Uy2jrTozMBDPA&amp;_nc_ss=7e3ba&amp;oh=00_AQIzieEkLUzmKuSnQ1FdhPahykZXtpgntFp7QOJTZ0Bvrg&amp;oe=6AB61C51
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=v_28DqPFYsAQ7kNvwE17_Nj&amp;_nc_oc=AdoaxT-oEqzqimewLLsjlgtPsx41LdjP8EQv0VZzMCVGFUvIkZMPGOHA6H_zPOaAQN0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIRy378DFED3lc-frZ8Zl3dq3tUnJLobQ4Doe1wWqPb4w&amp;oe=6AB62CD9
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.ashbyhq.com%2Fgreenboard%2Fe5deef5b-8667-48d7-be48-a0b6616eaba5%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafOFSCyMPpovs5tgA4xJMvtJid4FAUDF7RpxY-D2YBIsiR-yEE52-4sxYCFug_aem_YbCli8a0WVF90EY96GreFQ&amp;e=AUDYaTV0MZlyV3vMi-01nYRINxTI0Obwwwd76DqawAHppIwECv_egVql9Pl59gQQ8f5Pxf606Oa358OBCaHmiCyCaNB9pNsaxTbf7Z-B_Q
+https://scontent-sjc3-1.cdninstagram.com/o1/v/t2/f2/m78/AQPTk8dHILSJNhyasYZlTBYJ0xq5ux_aG_qOvjEcb39xArJg1QSU3-T-7xZ6hoKzMsOj6PL1fq5j04-K_7Fl4Qc3VLr1_VYH2c-9hgk.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_ohc=ntA2gtfLFKcQ7kNvwEtWj5L&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc2NjYwMTQ2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=2ae0f87e39c5d127&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzRGNEVGMTVBMDk4QkYyNTUxMEZCNjMxREU4OTI5OTkyX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkvve53aihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=PAIFeRD54Uy2jrTozMBDPA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQL_FeV0U3ceXQtpUQ7r1s-GsBc9iri_oh_Z9eA7kdaT3Q&amp;oe=6AB24138</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q68" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R68" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R63"/>
+  <autoFilter ref="A1:R68"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -6513,6 +7003,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId122"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -6401,7 +6401,7 @@
     <row r="64" ht="45" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>4d49af86ae200e4c6010</t>
+          <t>29ea1f14dbfb33b2cc09</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -6439,8 +6439,8 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="I64" s="3" t="inlineStr"/>
-      <c r="J64" s="3" t="inlineStr"/>
+      <c r="I64" s="3" t="n"/>
+      <c r="J64" s="3" t="n"/>
       <c r="K64" s="4" t="inlineStr">
         <is>
           <t>https://rsvp.withgoogle.com/events/uw-google-career-workshop-2026/forms/registration</t>
@@ -6495,12 +6495,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R64" s="3" t="inlineStr"/>
+      <c r="R64" s="3" t="n"/>
     </row>
     <row r="65" ht="45" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>17ff3188b8937fef7110</t>
+          <t>3dc1102277730e80cd7a</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -6538,8 +6538,8 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="I65" s="3" t="inlineStr"/>
-      <c r="J65" s="3" t="inlineStr"/>
+      <c r="I65" s="3" t="n"/>
+      <c r="J65" s="3" t="n"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
           <t>https://amazon.jobs/en/jobs/10394278/2026-fall-applied-science-internship-reinforcement-learning-optimization-machine-learning-united-states-phd-student-science-recruiting</t>
@@ -6597,12 +6597,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R65" s="3" t="inlineStr"/>
+      <c r="R65" s="3" t="n"/>
     </row>
     <row r="66" ht="45" customHeight="1">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2979dff0c6ced716aeb9</t>
+          <t>b8b1bdfaf4efa294a9ab</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -6630,14 +6630,14 @@
           <t>Other Opportunity</t>
         </is>
       </c>
-      <c r="G66" s="3" t="inlineStr"/>
+      <c r="G66" s="3" t="n"/>
       <c r="H66" s="3" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="I66" s="3" t="inlineStr"/>
-      <c r="J66" s="3" t="inlineStr"/>
+      <c r="I66" s="3" t="n"/>
+      <c r="J66" s="3" t="n"/>
       <c r="K66" s="4" t="inlineStr">
         <is>
           <t>https://forms.cloud.microsoft/Pages/ResponsePage.aspx?id=v4j5cvGGr0GRqy180BHbR67drzZ_HMRKrjpUVBFkKE1UQ1JURDUySDk1REpJUk40WlY4UE5SNFdMSC4u</t>
@@ -6694,12 +6694,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R66" s="3" t="inlineStr"/>
+      <c r="R66" s="3" t="n"/>
     </row>
     <row r="67" ht="45" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>4d68684836842a5003e8</t>
+          <t>5bc00a26a2e527162acf</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -6712,7 +6712,7 @@
           <t>2026-09-20T20:28:35+00:00</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr"/>
+      <c r="D67" s="3" t="n"/>
       <c r="E67" s="3" t="inlineStr">
         <is>
           <t>is a DoW Scholarship Program for</t>
@@ -6723,10 +6723,10 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G67" s="3" t="inlineStr"/>
-      <c r="H67" s="3" t="inlineStr"/>
-      <c r="I67" s="3" t="inlineStr"/>
-      <c r="J67" s="3" t="inlineStr"/>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+      <c r="I67" s="3" t="n"/>
+      <c r="J67" s="3" t="n"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
           <t>https://www.smartscholarship.org/smart/en</t>
@@ -6780,12 +6780,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R67" s="3" t="inlineStr"/>
+      <c r="R67" s="3" t="n"/>
     </row>
     <row r="68" ht="45" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>21bd1a5c0097c3708fff</t>
+          <t>faabbae8d9e229e2b26d</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -6828,7 +6828,7 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="J68" s="3" t="inlineStr"/>
+      <c r="J68" s="3" t="n"/>
       <c r="K68" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/greenboard/e5deef5b-8667-48d7-be48-a0b6616eaba5</t>
@@ -6886,7 +6886,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R68" s="3" t="inlineStr"/>
+      <c r="R68" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:R68"/>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R68"/>
+  <dimension ref="A1:R71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6888,8 +6888,266 @@
       </c>
       <c r="R68" s="3" t="n"/>
     </row>
+    <row r="69" ht="45" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>3a9542daa2d64f226608</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:18:23.862514+00:00</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T07:56:15+00:00</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr"/>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>AutoZone's Top 100 Internship Program is</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr"/>
+      <c r="J69" s="3" t="inlineStr"/>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>https://egud.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/155461</t>
+        </is>
+      </c>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
+          <t>“ WW +t View More Jobs
+AUTOZONE 2027
+INTERNSHIP =
+Memphis, TN, United States
+(2? AUTOZONE 2027 DS INTERN
+= :
+autozone why tf u opening at midnight
+es
+JOB DESCRIPTION
+AutoZone's Top 100 Internship Program is
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/819571867_27994706156897800_4967386248258520862_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MDk0MTk2Mjk2MTczMjI3Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=TpqDh9iVW1oQ7kNvwH__1vP&amp;_nc_oc=Adp9XxmQc8qWLoShR_11mDPOC_p2vdoi093kUQycPtWQBdpIv7AFmZOFg1QWiIKU7sU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=Cn4PepwDyqnKTj0fwmV0Jg&amp;_nc_ss=7e3ba&amp;oh=00_AQIxz92fXSOofjs7xaFsHBe4mqeC75kWGV6k7CVOQonaYQ&amp;oe=6AB70D2F
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/819571867_27994706156897800_4967386248258520862_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MDk0MTk2Mjk2MTczMjI3Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=TpqDh9iVW1oQ7kNvwH__1vP&amp;_nc_oc=Adp9XxmQc8qWLoShR_11mDPOC_p2vdoi093kUQycPtWQBdpIv7AFmZOFg1QWiIKU7sU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=Cn4PepwDyqnKTj0fwmV0Jg&amp;_nc_ss=7e3ba&amp;oh=00_AQKeAK6m4Z5d5UrGwTbdWmMFpqsU4bRfOamnVD-JqxUM9w&amp;oe=6AB70D2F
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwHz6Zza&amp;_nc_oc=Ados52foxDaRgOz2rjFN2uLYLLubmYhy74n1gpJ6c4dFtFrl5bhef_WghqyGcqpn9lE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKJSiBrglOv7CQZfBHnZVk5YhxBN_m0OQ9dOkdu5P2rwg&amp;oe=6AB70DD9
+https://l.instagram.com/?u=https%3A%2F%2Fegud.fa.us2.oraclecloud.com%2FhcmUI%2FCandidateExperience%2Fen%2Fsites%2FCX_1%2Fjob%2F155461%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadAAx_znoxJFNCjR0CjhdXgO3PRPBaEJaVd_STZbU1QbnQoB_umSHM1APJxLw_aem_SqRf-qOgIlH9aM3D8VoJ9A&amp;e=AUC0uS1czvnBwTOCEw9sT6dw3BlITnqwrAUDhJExWaEmfJ5g-KNhIJ7cRuwoK2UF-F6MCFmN5EaaIrf1Qc8_Uk8ukmWUpzln_5nLqL6apQ
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQPF5ckZXcYOq9UD_auW94Y9Pj98s-PCuXLQQ9QpyIItJCIZg5sDVNWJhvnd6Ddcmq_UzcdU1FPaC1uAAjui6UVg4GMvDx5KNmLORaY.mp4?_nc_cat=102&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=OsPIsjjMgEQQ7kNvwFEgEv4&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc3MjExMDY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=6d683f8be63e8f71&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzQwNDY3NjNBRjE1NjcyODFENjc1RDZENDIzMjE3NUIwX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkkuH196uhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=Cn4PepwDyqnKTj0fwmV0Jg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJa5Oy_s8udL-TtAo8QULaq9N5N_6sdoNjSWR7vUxf2Ag&amp;oe=6AB30DA7</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70" ht="45" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>96bf1d1645b8f12e0b12</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:18:26.341605+00:00</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T11:15:03+00:00</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Mercury</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Mercury — Apprenticeship / Externship</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Apprenticeship / Externship</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr"/>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>San Francisco, New York, Remote</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr"/>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/mercury/jobs/6199367004</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
+          <t>(@ 2% &gt;dards.greenhouse.io +
+© San Francisco, CA, New York, NY,
+Portland, OR, or Remote within Canada or
+United States
+It’s 1813, and Hump vy is dazzling
+London with scientifi onstrations and
+lectures. Soon enters the young bookbinder,
+Michael Faraday, dissatisfied with his own
+prospects and enamored by the mysteries of
+electricity. Faraday gets a break and gains an
+apprenticeship with Davy, and shortly
+thereafter (partially) blows himself and ~*~
+up in a nitrogen trichloride explosion. “
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/809519051_1939712363654373_728738205524773074_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MTA0MjAyNjUzMDk2MjMxNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=NCSy1flv6UAQ7kNvwGmnY5C&amp;_nc_oc=Adr-9NxF4CcGoPNLiQl6HcIUrp9n0a0QJzjYgxBkb3MhzoBkXsNtgrjUxBVS1kn5pkA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=Cn4PepwDyqnKTj0fwmV0Jg&amp;_nc_ss=7e3ba&amp;oh=00_AQL6hIHfmrk2jA68NkI2whNZ2YWtWgYpcILZniNujJmGTg&amp;oe=6AB70515
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/809519051_1939712363654373_728738205524773074_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MTA0MjAyNjUzMDk2MjMxNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=NCSy1flv6UAQ7kNvwGmnY5C&amp;_nc_oc=Adr-9NxF4CcGoPNLiQl6HcIUrp9n0a0QJzjYgxBkb3MhzoBkXsNtgrjUxBVS1kn5pkA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=Cn4PepwDyqnKTj0fwmV0Jg&amp;_nc_ss=7e3ba&amp;oh=00_AQLm_za-ACf_8DwayVU1ra_UfQfG8lazXxipAcT8FCKMCw&amp;oe=6AB70515
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwHz6Zza&amp;_nc_oc=Ados52foxDaRgOz2rjFN2uLYLLubmYhy74n1gpJ6c4dFtFrl5bhef_WghqyGcqpn9lE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKJSiBrglOv7CQZfBHnZVk5YhxBN_m0OQ9dOkdu5P2rwg&amp;oe=6AB70DD9
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fmercury%2Fjobs%2F6199367004%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacJCNAHdnzabk_uo0rJT-Fvc3C7UNAX_PDAdIjSSCw18zy31q1rfSNDFYplFA_aem_I9cFUuzbnSkFsuuswjFwQQ&amp;e=AUDccJRZiDJzaPnTfrtB6hEViemrkCr5GJCxlem0vcb3KyhCszhGB-pG5TCmunV1OTpSd3QffGdf3AXKz5D8iqoV1HHDAKPlHrk55X4TaQ
+https://scontent-lax7-1.cdninstagram.com/o1/v/t2/f2/m78/AQN9XkbAgLmeuM8wahq7hTzR7_ry9AUjBFmMo-viiSD7j24b2lYLpHmN55bSC4PXwj4AnV75EADhfeJVhELLfTgXSfJSyH_uY-tIwAk.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ohc=ZZGbzFd_9dwQ7kNvwHHTGSj&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc3Mzc3ODY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=b6776ccc2035727&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0NFNDdDM0ZCN0VFMjY3NjBBODkxRUFBQUY4QjVFOEFEX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk-oWZ9KyhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=Cn4PepwDyqnKTj0fwmV0Jg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKuIGlB2NOCpSGGjMHY40wNKqHzKMICZpuLWIabjj44jg&amp;oe=6AB3273A</t>
+        </is>
+      </c>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q70" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71" ht="45" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>75700025b96d17b2c33d</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:18:27.786560+00:00</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T11:49:54+00:00</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr"/>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr"/>
+      <c r="I71" s="3" t="inlineStr"/>
+      <c r="J71" s="3" t="inlineStr"/>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>https://gunvorgroup.com/careers/graduate-program</t>
+        </is>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
+          <t>Very prominent commodity
+trading firm released their new
+grad program tdy
+Graduate Program
+Applications are now open!
+| GUNVORGROUP.COM
+" w
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/819601500_1818112526013753_6213701210293472223_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MTA1OTU2ODM4NTM5MjA4Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=iF2CZcU9UGcQ7kNvwFODqqP&amp;_nc_oc=AdqUG7AHf414yby484mYqKMA1H2AJUZlDgndc5KCTFubUOPsz-p97MjwTFv-D2nVQGk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=Cn4PepwDyqnKTj0fwmV0Jg&amp;_nc_ss=7e3ba&amp;oh=00_AQLV-OM0d9m0_j4m4CZ1TFBdy0snaO8hYafamAZoRJ8YpQ&amp;oe=6AB71BA7
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/819601500_1818112526013753_6213701210293472223_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MTA1OTU2ODM4NTM5MjA4Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=iF2CZcU9UGcQ7kNvwFODqqP&amp;_nc_oc=AdqUG7AHf414yby484mYqKMA1H2AJUZlDgndc5KCTFubUOPsz-p97MjwTFv-D2nVQGk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=Cn4PepwDyqnKTj0fwmV0Jg&amp;_nc_ss=7e3ba&amp;oh=00_AQLPzrTsk5hBfrxsDCzTQgiWbQkjaN92tQoLqo5fw9uhDw&amp;oe=6AB71BA7
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwHz6Zza&amp;_nc_oc=Ados52foxDaRgOz2rjFN2uLYLLubmYhy74n1gpJ6c4dFtFrl5bhef_WghqyGcqpn9lE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKJSiBrglOv7CQZfBHnZVk5YhxBN_m0OQ9dOkdu5P2rwg&amp;oe=6AB70DD9
+https://l.instagram.com/?u=https%3A%2F%2Fgunvorgroup.com%2Fcareers%2Fgraduate-program%2F%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaf74PEAy-KfkQ5vwBbtJwR4W8UT0rOV_nBHM81a_kxaWScpIPV7Kg1nWuWVWg_aem_PfDhd4PwXkZ8DgGD-2XUpQ&amp;e=AUBL03xfmujSD6d8JdR0ldzzngcDcSl8P9olg9d9lZK2jUFOD3dDgfctpz4bwGHF8qhMalAnvzyAjPhgjXu2vxcbiZUjpIOswxK7tGBYKQ
+https://scontent-lax7-1.cdninstagram.com/o1/v/t2/f2/m78/AQP1bnhlr1d6mlqACH8onib_-A1mbmPzNGVfT2OseZWwHPRyF2o1uxUZTUOIKmk_On1gvq-Dyfp-jyrfQmV2cViGvBeTVvaOK2qeS7Q.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ohc=P94U4H5MNDIQ7kNvwEJFmbf&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc3NDI3MjE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=a81427c1c1130ccc&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzQyNDA0NThCOTM3MDQ1Njg1Q0VDRENERjUwOTYxNEFFX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk-bb7mK2hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=Cn4PepwDyqnKTj0fwmV0Jg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIHQBHpuSr_sbG-aUjwu7F0kEWymEAKU0YycZ99llifbg&amp;oe=6AB315E2</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q71" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R71" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R68"/>
+  <autoFilter ref="A1:R71"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -7013,6 +7271,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId128"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R71"/>
+  <dimension ref="A1:R85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6891,7 +6891,7 @@
     <row r="69" ht="45" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3a9542daa2d64f226608</t>
+          <t>41c2c015a55386c52ba6</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -6904,7 +6904,7 @@
           <t>2026-09-21T07:56:15+00:00</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr"/>
+      <c r="D69" s="3" t="n"/>
       <c r="E69" s="3" t="inlineStr">
         <is>
           <t>AutoZone's Top 100 Internship Program is</t>
@@ -6915,14 +6915,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr"/>
+      <c r="G69" s="3" t="n"/>
       <c r="H69" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr"/>
-      <c r="J69" s="3" t="inlineStr"/>
+      <c r="I69" s="3" t="n"/>
+      <c r="J69" s="3" t="n"/>
       <c r="K69" s="4" t="inlineStr">
         <is>
           <t>https://egud.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/155461</t>
@@ -6972,12 +6972,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R69" s="3" t="inlineStr"/>
+      <c r="R69" s="3" t="n"/>
     </row>
     <row r="70" ht="45" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>96bf1d1645b8f12e0b12</t>
+          <t>fb9b2107b51b649b34d8</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -7005,14 +7005,14 @@
           <t>Apprenticeship / Externship</t>
         </is>
       </c>
-      <c r="G70" s="3" t="inlineStr"/>
-      <c r="H70" s="3" t="inlineStr"/>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
       <c r="I70" s="3" t="inlineStr">
         <is>
           <t>San Francisco, New York, Remote</t>
         </is>
       </c>
-      <c r="J70" s="3" t="inlineStr"/>
+      <c r="J70" s="3" t="n"/>
       <c r="K70" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/mercury/jobs/6199367004</t>
@@ -7065,12 +7065,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R70" s="3" t="inlineStr"/>
+      <c r="R70" s="3" t="n"/>
     </row>
     <row r="71" ht="45" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>75700025b96d17b2c33d</t>
+          <t>6afe655aeedaeeb76ee7</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -7083,7 +7083,7 @@
           <t>2026-09-21T11:49:54+00:00</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr"/>
+      <c r="D71" s="3" t="n"/>
       <c r="E71" s="3" t="inlineStr">
         <is>
           <t>Other Opportunity</t>
@@ -7094,10 +7094,10 @@
           <t>Other Opportunity</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr"/>
-      <c r="H71" s="3" t="inlineStr"/>
-      <c r="I71" s="3" t="inlineStr"/>
-      <c r="J71" s="3" t="inlineStr"/>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+      <c r="I71" s="3" t="n"/>
+      <c r="J71" s="3" t="n"/>
       <c r="K71" s="4" t="inlineStr">
         <is>
           <t>https://gunvorgroup.com/careers/graduate-program</t>
@@ -7144,10 +7144,1351 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R71" s="3" t="inlineStr"/>
+      <c r="R71" s="3" t="n"/>
+    </row>
+    <row r="72" ht="45" customHeight="1">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>983ec485796900be7ac9</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T19:36:14.696629+00:00</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:55:10+00:00</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr"/>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr"/>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>https://wd1.myworkdaysite.com/en-US/recruiting/fmr/FidelityCareers/job/Summer-2027-Undergraduate-Internship---Software_2134524</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
+          <t>Hey sudo, just wanted to let you
+know that Fidelity SWE dropped
+today
+®
+Summer 2027 Undergraduate
+Internship - Software
+Job Description: Note: Fidelity is not
+providing immigration sponsorship
+for this position These internships
+are only located in Boston, MA |
+Durham, NC | Westlake, TX Software
+Engineering Assessment Requirement
+As part of Fidelity's hiring process,
+selected applicants will be required to
+complete a...
+Fidelity SWE Internship
+https://wd1.m
+---Software_213452Z
+e
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/809415457_1702621344741256_3253401823231927351_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MTE1MjgyNjgxMzc4NjMyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=p8-gScJw4cwQ7kNvwHHspeJ&amp;_nc_oc=Adq402Y1cdRX4rQxIZ820dPz8VRyYZKSmlbx9_C4kloPvO0_1kuPnzOBJUQttok5s9k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQLS4RoWzozTgfJ1ePek1Vx1bT4nTAmdP0knRLNexJnZ4w&amp;oe=6AB749AB
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/809415457_1702621344741256_3253401823231927351_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MTE1MjgyNjgxMzc4NjMyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=p8-gScJw4cwQ7kNvwHHspeJ&amp;_nc_oc=Adq402Y1cdRX4rQxIZ820dPz8VRyYZKSmlbx9_C4kloPvO0_1kuPnzOBJUQttok5s9k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQKCyLitnJsJSVMBeShY1HX99XYJMUmSJeHnDytnqNXX5g&amp;oe=6AB749AB
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwE0A6MH&amp;_nc_oc=AdrNJvu6kh947YrzfHb4R4hjRZ-LfcGtmcg1z_jI2NshhsfTiWZ1rTSiZnRYaZT_1DY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKfB2IepL3oNjy3FYapfA0JCkx88Tx0DKiF6TMAl8I_ng&amp;oe=6AB74619
+https://l.instagram.com/?u=https%3A%2F%2Fwd1.myworkdaysite.com%2Fen-US%2Frecruiting%2Ffmr%2FFidelityCareers%2Fjob%2FSummer-2027-Undergraduate-Internship---Software_2134524%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacG3cB9mPyniO8Oa8StgpbU6Ok5PN3R7WcB9V2XUiKBq3u8D-N5_AP4JLA6WA_aem_HLoyN60s3lxR4A4rnnR_UA&amp;e=AUD0thC6pISflks9lxEEvPVG9b_92-O27GZ8FJHnvpsbCsG7m1Fz7pFHFSGU08HcNlD2OtjgAevXneQc4VmlQ_KJcafbKiBwksxLnDDuUw
+https://scontent-lga3-3.cdninstagram.com/o1/v/t2/f2/m78/AQPtnGiTXa4qukdO6_uQH6jUnyBuaHyIOmyNa0DqGdUyA_BGfb2-fQh4YDipeTTCP5DHXsGo8_msYSplpWCgY9g2iaCB1ail8B12_VA.mp4?_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_ohc=yLM5S0zykfkQ7kNvwFBw0Xo&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc3NjEwMzM2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=633fac022b27db65&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzgyNDMwRTEzN0Q2MUYzRDVCNTdDQzY3MkU2QzIwMkI0X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkwY6zoa6hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQItmfYIfzzTrMVMh7bqECVzTH6cNdL92LTb3aPGJDpY9w&amp;oe=6AB37E33</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q72" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73" ht="45" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>c577dffaff4e5f4eb223</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T19:36:15.952762+00:00</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:58:15+00:00</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Fidelity</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Fidelity — Internship</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr"/>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr"/>
+      <c r="J73" s="3" t="inlineStr"/>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.fidelity.com/en/jobs/2134164/summer-2027-undergraduate-internship-systems</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
+          <t>&lt;&lt; @ jobs.fidelity.com CG 7
+Instagram
+ADMINISTRATIVE
+Summer 2027
+Undergraduate
+Internship -
+Systems
+Published: Sep 21 ID: 2134164
+(7) FIDELITY SYSTEMS ANALYST INTERN
+; | |
+Location w
+Westlake, TX Durham, NC
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/815701988_934774906371005_6419842002208600385_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MTE1NDM3NDY5NjU1MjU3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=u_hl4IJ99kEQ7kNvwFNaxkX&amp;_nc_oc=AdogxVbHOMV6iB9UQcNa2c9Q4LKs09g8W36e3nI8vc88TSbxtJHv-nTTMTDt6AYKMEY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQJT_YsjDo8autodebFJb1_dEb7ZXrGooF_qWmf8F535rw&amp;oe=6AB77041
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/815701988_934774906371005_6419842002208600385_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MTE1NDM3NDY5NjU1MjU3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=u_hl4IJ99kEQ7kNvwFNaxkX&amp;_nc_oc=AdogxVbHOMV6iB9UQcNa2c9Q4LKs09g8W36e3nI8vc88TSbxtJHv-nTTMTDt6AYKMEY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQJVx2UI7zyfL5vOovWFmJLhepV-yzBUjdh1iz4y8Eimfw&amp;oe=6AB77041
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwE0A6MH&amp;_nc_oc=AdrNJvu6kh947YrzfHb4R4hjRZ-LfcGtmcg1z_jI2NshhsfTiWZ1rTSiZnRYaZT_1DY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKfB2IepL3oNjy3FYapfA0JCkx88Tx0DKiF6TMAl8I_ng&amp;oe=6AB74619
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.fidelity.com%2Fen%2Fjobs%2F2134164%2Fsummer-2027-undergraduate-internship-systems%2F%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaczPSHB4HL1xdMhFmDqYQix5fj07dWEI2A1_Dspou3FxuPx4Us7dG3JG9m35g_aem_c06vDlNWcGQZUB-YjU_3Jg&amp;e=AUAcMBlvLIjSOhu46YYRfOVIsBL93OBvtKedSZFJwwNpp00VCODjSax2wfd7KG6vOqB5JYpR4N_ywXrsEtFMQ0LlC6_Z4ZU1z6vf-4Ss5Q
+https://scontent-lga3-2.cdninstagram.com/o1/v/t2/f2/m78/AQOXU4U3EfVKZEfsdF3Hzu_50fVZAoAKgfSk3IozpfShBwawSOa0MJtMX380-wOOGygXHKZpjgfzfHG8YiTvWz6Sl_npQqp-e6lLZ-Y.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ohc=4Ndd7dOwL3EQ7kNvwHuVUs-&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc3NjE3MjY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=91a5e15cf401d043&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0YwNEU2MUFGMjA1QzAwNDc0MzgwMzRBNzdGQjg5RTkzX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbknoHIpq6hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLAeeROpvhqipprIOqbH1f31woE66cSclwJWHaNEBY44Q&amp;oe=6AB3770A</t>
+        </is>
+      </c>
+      <c r="O73" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q73" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74" ht="45" customHeight="1">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>7aeb86574fe09c2b119b</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T19:36:17.039050+00:00</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T15:01:06+00:00</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Capitalone</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Capitalone — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Winter 2027</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr"/>
+      <c r="J74" s="3" t="inlineStr"/>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>https://capitalone.wd12.myworkdayjobs.com/en-US/Capital_One/job/Toronto-ON/Intern--Backend-Software-Engineer---Team-Interstellar---Winter-2027_R249022</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
+          <t>Pe 4
+Capital One
+Shape your
+future—and ours
+CAREERS AT CAPITAL ONE
+Intern, Backend Software
+Engineer - Team Interstellar -
+Winter 2027
+Apply
+© Toronto, ON
+feo] Full time
+(©) Posted Today
+) CAPITAL ONE SWE WINTERN CANADA
+161 Bay Street (9302 da,
+Toronto, Toronto, Onta
+https://scontent-lga3-1.cdninstagram.com/v/t51.71878-15/809039500_28208369125501670_7350128245982026836_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MTE1NTgwNTE0NzEyNDcyNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=un5W9cQCWl0Q7kNvwGpt_FT&amp;_nc_oc=AdqNRqJekIji-wGwZUASTRfvC5KI983mMIt_1cPPvRvDUWt3N8odyq2Cqg9BhlAv8o0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQLYw83VWeoybXYZYOZwN3_eahqu538rUhZACDjEF1Tfbg&amp;oe=6AB76D96
+https://scontent-lga3-1.cdninstagram.com/v/t51.71878-15/809039500_28208369125501670_7350128245982026836_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MTE1NTgwNTE0NzEyNDcyNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=un5W9cQCWl0Q7kNvwGpt_FT&amp;_nc_oc=AdqNRqJekIji-wGwZUASTRfvC5KI983mMIt_1cPPvRvDUWt3N8odyq2Cqg9BhlAv8o0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQJ2LP4PPqdgFoGfWOlHzBzep8pe2gSfpec7aUaIK781wA&amp;oe=6AB76D96
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwE0A6MH&amp;_nc_oc=AdrNJvu6kh947YrzfHb4R4hjRZ-LfcGtmcg1z_jI2NshhsfTiWZ1rTSiZnRYaZT_1DY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKfB2IepL3oNjy3FYapfA0JCkx88Tx0DKiF6TMAl8I_ng&amp;oe=6AB74619
+https://l.instagram.com/?u=https%3A%2F%2Fcapitalone.wd12.myworkdayjobs.com%2Fen-US%2FCapital_One%2Fjob%2FToronto-ON%2FIntern--Backend-Software-Engineer---Team-Interstellar---Winter-2027_R249022%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeNVe6odMe7pySO3qWFrXL06zhKl5jDFis0O5WOzKB_HwHBJDphbOki8w7GAA_aem_2WE4joJwQKKX0oYImTtTzQ%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUDlNO_fOEZDdT_sGl6_lH0E9l5f1KgDogfovF5jSNh3bJ58iFTp4oEGStJVxutH2yJxdCBGQHg_lKUIVSBBwFF3bjc-Zu4mZrq2jfgH0Q
+https://scontent-lga3-1.cdninstagram.com/o1/v/t2/f2/m78/AQP3i_JRVm_OgOT9mXqGKBDuiCD-kIAl9gZ5zPh9JOl2LHq9XUct63RJQ-ujNG4Ogw1RSQwCfXsRDZmNDJzBY2z5hrlzR5zdca2pUrM.mp4?_nc_cat=110&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_ohc=mff2vxSvDT0Q7kNvwHF-5jV&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc3NjI4NTE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=d34be27fe9d3a322&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0ZCNEMxNDY5OUIxNjVCQTlGRkM2QjQ1NzdENzQ0MEJGX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkq_L4rq6hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJtMyIKMN1ZmbiFQSJO5rHskJDldS0ESekvz3qyiZrsXQ&amp;oe=6AB35663</t>
+        </is>
+      </c>
+      <c r="O74" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q74" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75" ht="45" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>2bd93cf526e78c9b0324</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T19:36:18.185161+00:00</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T15:02:07+00:00</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Capitalone</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Capitalone — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>Winter 2027</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr"/>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>https://capitalone.wd12.myworkdayjobs.com/en-US/Capital_One/job/Toronto-ON/Intern--Mobile-Software-Engineer---Team-Gringotts-North---Winter-2027_R249015</t>
+        </is>
+      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
+          <t>Capital
+Shape your f
+future—and ours Se ,
+Intern, Mobile Software
+Engineer - Team Gringotts
+North - Winter 2027
+(2) CAPITAL ONE MOBILE SWE INTERN CA
+© Toronto, ON
+feo] Full time
+(©) Posted Today
+[=] R249015
+161 Bay Street (93021), Canada,
+Toronto, Toronto, Ontario,
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/797418567_2668048423631778_8386186600672875637_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTE1NjMzNTg2OTE5OTM2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=31aO1uMN0YEQ7kNvwEbW8it&amp;_nc_oc=Ado-Rjj-5ueddROOmkR1LM1VIzP55r6mfq2lnTH3WFJI_s_lvjN_Xfsejep-DCEPQ9E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQJhVvdG7KcIre-ShQMbyiBwXTTWkwZFrwEvvlHko41WEg&amp;oe=6AB748AC
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/797418567_2668048423631778_8386186600672875637_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTE1NjMzNTg2OTE5OTM2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=31aO1uMN0YEQ7kNvwEbW8it&amp;_nc_oc=Ado-Rjj-5ueddROOmkR1LM1VIzP55r6mfq2lnTH3WFJI_s_lvjN_Xfsejep-DCEPQ9E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQJleOlq6Wh1zZQCn0xa43L7oQE7Yql-_49CG6ogEMS5aA&amp;oe=6AB748AC
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwE0A6MH&amp;_nc_oc=AdrNJvu6kh947YrzfHb4R4hjRZ-LfcGtmcg1z_jI2NshhsfTiWZ1rTSiZnRYaZT_1DY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKfB2IepL3oNjy3FYapfA0JCkx88Tx0DKiF6TMAl8I_ng&amp;oe=6AB74619
+https://l.instagram.com/?u=https%3A%2F%2Fcapitalone.wd12.myworkdayjobs.com%2Fen-US%2FCapital_One%2Fjob%2FToronto-ON%2FIntern--Mobile-Software-Engineer---Team-Gringotts-North---Winter-2027_R249015%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAael_PrcVLneROVBXPexr6OSEka8LAtWfv0iA6IsDqrudZ5KY2FwUyJVswtgoQ_aem_UDnHf2yKR_98Q1L0Q_SoxA%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUCIgGd2SEuTHmTuum2o4CSKUUB_DmqkPitVhIM-lSizHHCHDHPQJDWzdwNquxlYct4f_2m8-vb_cs7_9JFnjfDZfcn3WzXCzOfHiLHp1A
+https://scontent-lga3-1.cdninstagram.com/o1/v/t2/f2/m78/AQOeFmb66qencrthY0aCk3UK6SUahRxBYaFn5i8iVbuEfhyAhH7Z1UPJNIgfaNSrXzt8wYxNbC-HaILk0j6xdbTeFTuigl_oaXckfrU.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_ohc=9iYoCEBp_P0Q7kNvwHD75Sj&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc3NjMwODU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=46e295d54d09110b&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzVCNEM3Qjk1MzVCQ0JFOTdCNzA3Q0E0NTRFMUM0RUE0X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk5YbYsK6hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLVmWQIfC3lEIuSpQPles2ou0WcesWvJRm0Y9U6qrlbBA&amp;oe=6AB36D14</t>
+        </is>
+      </c>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q75" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76" ht="45" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>c790bd579ec2b1298bc7</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T19:36:19.594132+00:00</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T15:03:19+00:00</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Capitalone</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Capitalone — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr"/>
+      <c r="J76" s="3" t="inlineStr"/>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>https://capitalone.wd12.myworkdayjobs.com/en-US/Capital_One/job/McLean-VA/Technology-Development-Program-Associate---February-2027_R244320-1</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
+          <t>a 4
+CapitalOjne
+Shape your &amp;
+future—and ours s ev ‘\ &gt;
+SCS ee
+CAREERS AT CAPITAL ONE : Ay i La
+a) _
+Technology Development
+Program Associate - February
+2027
+(2? CAPITAL ONE NEW GRAD SWE!
+© McLean, VA
+Plano, TX
+Ams Cap One New Grad SWE USA
+fa] Full time
+(©) Posted Today
+[=] R244320
+Technology Development Program Associate -
+February 2027
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/797398267_1596932232211864_5299757366007707309_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MTE1NjkxODQ0MTI2MjgwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=A8WjujD-E_0Q7kNvwGi1-LH&amp;_nc_oc=Adp7f-v97ZX2ijTKvCf7vrF31vz2iYE0ldQj1pFe0CNRKmPnrJtFre7FhUj_3OhVu8I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQIsoT5pI2IhVLzbIIdBldhxE6eiPKJ43XoWAcklEG6tgg&amp;oe=6AB76C88
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/797398267_1596932232211864_5299757366007707309_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MTE1NjkxODQ0MTI2MjgwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=A8WjujD-E_0Q7kNvwGi1-LH&amp;_nc_oc=Adp7f-v97ZX2ijTKvCf7vrF31vz2iYE0ldQj1pFe0CNRKmPnrJtFre7FhUj_3OhVu8I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQKpel1E5mea44nzNe3xzQo5HdtClepwLFPtQXimQnR1tA&amp;oe=6AB76C88
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwE0A6MH&amp;_nc_oc=AdrNJvu6kh947YrzfHb4R4hjRZ-LfcGtmcg1z_jI2NshhsfTiWZ1rTSiZnRYaZT_1DY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKfB2IepL3oNjy3FYapfA0JCkx88Tx0DKiF6TMAl8I_ng&amp;oe=6AB74619
+https://l.instagram.com/?u=https%3A%2F%2Fcapitalone.wd12.myworkdayjobs.com%2Fen-US%2FCapital_One%2Fjob%2FMcLean-VA%2FTechnology-Development-Program-Associate---February-2027_R244320-1%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAad7thZ6Jp85FzQmBwfpJBGYS1SHPrheer9PGIYxc5wxei8xrK8UdIfbkc329Q_aem_FABB57lzG-21tJWFAypgPQ%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUBCRUwzg8NmBM4F3VgTyPcPRUHyhxJJo3SoWRC5eAV8wGFDPUqGoTcQ7czxRzmsA0Rxahvzh7akbxXRx62RFUuZsY9z0XYyHE9HUhKoVA
+https://scontent-lga3-1.cdninstagram.com/o1/v/t2/f2/m78/AQP7LEgawMdT5PX0_8N6AzyyNYjhazWhrof4mvIbvSM9GovuYQjUJBeETDpiKwgeVFawg6wgYmEnIcBbCvgIBbveN4tFAP3ke0KZRrY.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_ohc=k-KEiIeBfnsQ7kNvwG7-_wT&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc3NjMyNDE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=c7c9054f2f2bf852&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzc0NEI5Mzk1MDU3RUVBRjk5ODlGRUYzMTVBRTkyMjhBX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk4enssa6hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJ4NePAxqmpxwNkbr8bVMu-v6BY5wXfGbNKBZRnRAfdyA&amp;oe=6AB37756</t>
+        </is>
+      </c>
+      <c r="O76" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q76" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77" ht="45" customHeight="1">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>dad305ab369e7fd7e8fd</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T19:36:20.775155+00:00</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T15:06:20+00:00</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr"/>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>SS eccanca Apply now</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr"/>
+      <c r="H77" s="3" t="inlineStr"/>
+      <c r="I77" s="3" t="inlineStr"/>
+      <c r="J77" s="3" t="inlineStr"/>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>https://www.perplexity.ai/hub/research/fellowship</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
+          <t>PERPLEXITY
+SS eccanca Apply now
+Perplexity
+Research
+Fellowship
+Our flagship program for enabling the
+best early-career research talent across
+technical disciplines to shape the future
+of Al.
+@ PERPLEXITY.AI
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/797398258_1786978195771074_5757863652618429656_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MTE1ODY4MTU0MjQ2NzAwMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=lG2zSO5QDvEQ7kNvwHNfrUv&amp;_nc_oc=AdooFRJwWEr_D3m39WzYMQac8LQgZEQ7ks-1FjAtZdMRSqOXsRsq94EcYdIO_3l1EmE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQIjQBsWPPM5YbkGac63vl6QfKuK0VuknAqLWV9U-FdPJw&amp;oe=6AB7500A
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/797398258_1786978195771074_5757863652618429656_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MTE1ODY4MTU0MjQ2NzAwMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=lG2zSO5QDvEQ7kNvwHNfrUv&amp;_nc_oc=AdooFRJwWEr_D3m39WzYMQac8LQgZEQ7ks-1FjAtZdMRSqOXsRsq94EcYdIO_3l1EmE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQLokziRVVqTIYqnhai2F-PVknny-Qixla9GvWYwqP4JMQ&amp;oe=6AB7500A
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwE0A6MH&amp;_nc_oc=AdrNJvu6kh947YrzfHb4R4hjRZ-LfcGtmcg1z_jI2NshhsfTiWZ1rTSiZnRYaZT_1DY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKfB2IepL3oNjy3FYapfA0JCkx88Tx0DKiF6TMAl8I_ng&amp;oe=6AB74619
+https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/619850867_17965871424008049_846696741870159830_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GHMs8iRx705o3dM-ANbHpmMzEsALbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=vH6EN2FMsrwQ7kNvwEK_vXH&amp;_nc_oc=AdqtVhxTj97dRCL9S7GHwDHEcoC-K4P0RmI7dEtgvb8OOc2jdMoG49_wHX88dznDBNY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQKEA_mSa9jDQLTYmeed-MhQLqcYxTtErpJxLRkiVznTxg&amp;oe=6AB773FB
+https://l.instagram.com/?u=https%3A%2F%2Fwww.perplexity.ai%2Fhub%2Fresearch%2Ffellowship%3Futm_source%3Dzero2sudo%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacJ0DzB322zB0y2vOz2La6xkKarhrzQvwnLofRwI1Gn7-hiLRclqYT1zhtIKQ_aem_S_rqrPan1Vu0SJrXWbhhfw&amp;e=AUAoodpoHQHty-QMl0_Ll9hTyKt8Tn3wVbQMVgm5M72H44zWGnITYO8oOV8eE_6oMXYQEHDqAo9sD2Rf0mBwZNlds_zAQ6f78x42bZF7pg
+https://scontent-lga3-2.cdninstagram.com/o1/v/t2/f2/m78/AQOFNp5NWmrX5EinRdVSS9NDc4onhyBm-GRge-27thQRhko8kXBwWgwu16udqAGaCpo3tYy82yZq4ZstbEBdX1_etdZXUp2A52iM4Rs.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ohc=f1FSlEwShWwQ7kNvwEFmx4d&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc3NjQxNTk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=9fa698b26abdfa41&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzUxNDg0MEJFRjhBODY4QjAwNjg1OTMxMjk3QUYyNUE0X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkp6bYuK6hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKQSxZaGgDcefqmQnHYR6rqaDm9dmcywpTfIiGwrwzAaw&amp;oe=6AB34E3A</t>
+        </is>
+      </c>
+      <c r="O77" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P77" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q77" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78" ht="45" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>45c2e426db3af34068b2</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T19:36:25.220722+00:00</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T15:55:35+00:00</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr"/>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>Thank you for applying to the Code for Good Hackathon - Software Engineer Program - 2027 Summer Inte</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr"/>
+      <c r="J78" s="3" t="inlineStr"/>
+      <c r="K78" s="3" t="inlineStr"/>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
+          <t>Candidates being considered for
+the Brooklyn Code for Good
+event on October 16-17th can
+expect to receive updates over
+the next one to two weeks.
+Candidates under consideration
+for the Columbus Code for Good
+event on November 6-7th will
+receive updates in October
+sep campus sourcing @
+Good moming,
+Thank you for applying to the Code for Good Hackathon - Software Engineer Program - 2027 Summer Internship (United States) and for your interest in
+JPMorganChase.
+Ne wanted to share a brief update that applications are still being reviewed. As selections are finalized, candidates will be contacted regarding next steps. Please
+keep in mind that Code for Good is a highly competitive program, and participation opportunities are limited, Candidates who are not selected for this event are
+encouraged to apply for future opportunities as they become available.
+Candidates being considered for the Brooklyn Code for Good event on October 16-17" can expect to receive updates over the next one to two weeks.
+Candidates under consideration for the Columbus Code for Good event on November 6-7" will receive updates in October. We appreciate your patience as
+our team continues to review a large number of applications.
+If you have any quick questions about Code for Good, | will be hosting optional office hours on the follo’
++ Monday, September 21%": 4-5pm - Register here
++ Thursday, Soptembor 24": 2-3pm - Ro
++ Tuesday, September 29": 2-3pm - Reg
+Attendance is completely optional, and you are welcome to join whichever session works best for your schedule. You can also review the posting for more
+information about the event and intomship opportunity.
+https://scontent-lga3-1.cdninstagram.com/v/t51.82787-15/816230119_18087771560678962_4075032292524779375_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MTE4MzIwMjAwNjk3NzczNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=Nc1RqteP3IQQ7kNvwGBjiuf&amp;_nc_oc=AdoG_9nuuskfeQLDcdgEIplLkRZCYIMT-RdgnSGvaJ4wCLhnOpxDSw5vu4Ug2fJTX-w&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQLyPoviJlIDFRqEanx801HsLkQi93_qx5huXTjT2jnK8Q&amp;oe=6AB73F40
+https://scontent-lga3-1.cdninstagram.com/v/t51.82787-15/816230119_18087771560678962_4075032292524779375_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MTE4MzIwMjAwNjk3NzczNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=Nc1RqteP3IQQ7kNvwGBjiuf&amp;_nc_oc=AdoG_9nuuskfeQLDcdgEIplLkRZCYIMT-RdgnSGvaJ4wCLhnOpxDSw5vu4Ug2fJTX-w&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQL51xCoaHhkHRF39EuUqaCmcBsBZupasaRpPWBTKeO2Og&amp;oe=6AB73F40
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwE0A6MH&amp;_nc_oc=AdrNJvu6kh947YrzfHb4R4hjRZ-LfcGtmcg1z_jI2NshhsfTiWZ1rTSiZnRYaZT_1DY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKfB2IepL3oNjy3FYapfA0JCkx88Tx0DKiF6TMAl8I_ng&amp;oe=6AB74619</t>
+        </is>
+      </c>
+      <c r="O78" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P78" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q78" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79" ht="45" customHeight="1">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>82f3f0df61965bf77b9b</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T19:36:26.825167+00:00</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T16:40:46+00:00</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr"/>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr"/>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr"/>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>https://icbpjb.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/sites/LazardStudentCareers/job/6606</t>
+        </is>
+      </c>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
+          <t>x @ icbpjb.fa.ocs.oraclecloud.com C+:
+LAZARD &amp;
+of vv t View More Jobs
+2027 Al Engineer Summer
+Internship
+New York, United States
+JOB DESCRIPTION
+Lazard is one of the world’s preeminent financial
+advisory and asset management firms. Our people and
+culture make the difference. While global in presence
+and reach, ours is a close, collaborative community of
+(2) ICBPUB.FA.OCS.ORACLECLOUD.CC
+succeed together. Our e rial culture, flat
+structure and embrace o | differences, allow
+creative ideas, original con nd unique
+perspectives to drive our business forward — and for
+careers to take flight.
+https://scontent-lga3-1.cdninstagram.com/v/t51.71878-15/817742241_1111979484565697_6535147584735226689_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MTIwNTk3MDUwODIxODE5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=uclQZBeoBBkQ7kNvwGsh86M&amp;_nc_oc=Adro-xPdPEte4f-MCZgnqWjg9HvY9b6cllPh_aGgqY6v9p6rd22VQh6T01S26RSH-OU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQKEPUT56G0lKIhsk2E_1w3Ztg3NQyLmEvlFpae--WcfGg&amp;oe=6AB7531B
+https://scontent-lga3-1.cdninstagram.com/v/t51.71878-15/817742241_1111979484565697_6535147584735226689_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MTIwNTk3MDUwODIxODE5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=uclQZBeoBBkQ7kNvwGsh86M&amp;_nc_oc=Adro-xPdPEte4f-MCZgnqWjg9HvY9b6cllPh_aGgqY6v9p6rd22VQh6T01S26RSH-OU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQJG0-PaaY7CVo0Ja1s_cq5DV3Yqcl37mlXHp1qVgiVhNA&amp;oe=6AB7531B
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwE0A6MH&amp;_nc_oc=AdrNJvu6kh947YrzfHb4R4hjRZ-LfcGtmcg1z_jI2NshhsfTiWZ1rTSiZnRYaZT_1DY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKfB2IepL3oNjy3FYapfA0JCkx88Tx0DKiF6TMAl8I_ng&amp;oe=6AB74619
+https://l.instagram.com/?u=https%3A%2F%2Ficbpjb.fa.ocs.oraclecloud.com%2FhcmUI%2FCandidateExperience%2Fen%2Fsites%2FLazardStudentCareers%2Fjob%2F6606%3Futm_medium%3Dzero2sudo%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadFPbsBW0YCjeZPMSBXHb6nHhMsKW0CbRDKJqe6Kq95EuBdVkRqyPbIKfKLrA_aem_sAHlRQjE582yPf5Clth5Mg&amp;e=AUCxr3MZ9OWx9AOtnmYYO5itUCneoBpjibFkXDmynfutPWAM1GrhL75mkBnZOExUxOAwgx0ESHe3NIqSDMBwux3i8cF3rgxGv9bx2gEFaA
+https://scontent-lga3-1.cdninstagram.com/o1/v/t2/f2/m78/AQOsoayXOxKdpAQbT0pHHygwq7Ud1Ug7_QHkVRpJnsWCKBuuJVmMh5FRPqpgY8mQw7-cCKvyZem0-P2ipYX6mGYXoM5bkgBjbfLzjyI.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_ohc=MSE92-JFi7oQ7kNvwHERJuv&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc3Nzc4MTI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=6520b2a93ec53ec8&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzdFNDk4MkI3OTQyRkI0MEEzMzFGQzMzRTYyNjM3MjlEX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkpOi0nq-hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLLaDnQWhqaY5OjhP_aBkqGTNI8iChsNuYDkgPTfm4wxg&amp;oe=6AB34A32</t>
+        </is>
+      </c>
+      <c r="O79" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q79" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80" ht="45" customHeight="1">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>0335faf860ca686097d8</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T19:36:28.510456+00:00</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T16:42:58+00:00</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr"/>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>Data Engineer Intern and help build</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>Data Engineering</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr"/>
+      <c r="J80" s="3" t="inlineStr"/>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>https://icbpjb.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/sites/LazardStudentCareers/job/6605</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
+          <t>2027 Data Engineer Summer
+Internship
+Join Lazard’s Al &amp; Data Group asa
+Data Engineer Intern and help build
+reliable, cloud-based data pipelines
+and high-quality data products that
+support analytics, reporting, and Al
+initiatives across the firm. You will
+work with modern data platforms to
+onboard and model datasets, while
+collaborat...
+Data Engineer Intern
+/6605?utm_mediu
+.
+“~hshare
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/809202037_1852881359492112_2752243091759497243_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5MTIwNzA3Mzk1NDAwMzc2Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=E23TqH94YScQ7kNvwGKJ_q2&amp;_nc_oc=AdrYE7_jlBpOiPe6l_rO1zfqDdqTlO4HGLb9-EH4epcDkBUFDdFvksbj6hiPYD9MzX8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQKrBqumOY0DikyN9e5SVk94JTvOBhvE0lWakfprOZ-liQ&amp;oe=6AB7557F
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/809202037_1852881359492112_2752243091759497243_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5MTIwNzA3Mzk1NDAwMzc2Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=E23TqH94YScQ7kNvwGKJ_q2&amp;_nc_oc=AdrYE7_jlBpOiPe6l_rO1zfqDdqTlO4HGLb9-EH4epcDkBUFDdFvksbj6hiPYD9MzX8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQKJkYu17tYToyuxchPp5fIVVQePZxaypfvb3wO14xoWHQ&amp;oe=6AB7557F
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwE0A6MH&amp;_nc_oc=AdrNJvu6kh947YrzfHb4R4hjRZ-LfcGtmcg1z_jI2NshhsfTiWZ1rTSiZnRYaZT_1DY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKfB2IepL3oNjy3FYapfA0JCkx88Tx0DKiF6TMAl8I_ng&amp;oe=6AB74619
+https://l.instagram.com/?u=https%3A%2F%2Ficbpjb.fa.ocs.oraclecloud.com%2FhcmUI%2FCandidateExperience%2Fen%2Fsites%2FLazardStudentCareers%2Fjob%2F6605%3Futm_medium%3Dzero2sudo%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadOyhocnmDMG3Ogynd1PMplEEZu5XGf1y_OBCVWAjgCtbTqP-G98rIwMDhwQg_aem_6mn_BZ3eWPWiwqiyD91yug&amp;e=AUCCkyaQslf5kcl2E5GDke1qCwDBM17hBtvgrW_V-FR7I5ZL-GTS9CG_9c-0vS9FvmI0dAHZnfcOaeVm8w2P8XYKB7JeTqwAbgo9-pbk-Q
+https://scontent-lga3-3.cdninstagram.com/o1/v/t2/f2/m78/AQO84T5mtAHNEDtPGYAKrKiuPfgANOTGhzJxU0tRgvziwfIuQAQTkl4-_pMCuoVEKTakkNeNG56geb48pT-sZC0AJCBjJZW1kMZD-8c.mp4?_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_ohc=ge3V8JyYqEQQ7kNvwGFX8tQ&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc3NzgxODE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=90b0ba0b2d00f31a&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzI0NDVENTkwNzU5NEMzMzNBRjI1NzEwMkU1REY0M0ExX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkndyUoa-hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJ-Sm6cWrlLFRDN4KuzYWybuM73TtTnIlKvV-WIzo79Yg&amp;oe=6AB35931</t>
+        </is>
+      </c>
+      <c r="O80" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P80" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q80" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81" ht="45" customHeight="1">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>4b908a57794c5a3d3040</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T19:36:34.165412+00:00</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T18:23:49+00:00</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Figma</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>Figma — Internship</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr"/>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>San Francisco, New York</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr"/>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/figma/jobs/6200626004?gh_jid=6200626004</t>
+        </is>
+      </c>
+      <c r="L81" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
+          <t>&lt; Back to jobs
+New
+PhD Intern, Data
+Science (2027)
+© San Francisco, CA * New York, NY
+Figma is growing our team of passionate
+creatives and builders on a mission to make
+design accessible to all. Figma’s platform
+(DP JOB- BOARDS. GREENHOUSE.I0
+with Al. From idea to t., Figma
+empowers teams tos ne workflows,
+move faster, and work together in real time
+from anywhere in the world. If you're ex
+to shape the future of design and Arg
+collaboration, join us!
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/820155649_934627876385396_5816979534645335942_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5MTI1NzgyOTg4MDY0OTYxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=LfsSQVxbgLcQ7kNvwEcaioO&amp;_nc_oc=AdrNSZ89Vb3irP2_fpW1klsXASb79R_77yok3s1m_AjaXajhunD_mIDq5aRxpwRpJgQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQLoNq7pDNTfQUD5928NnmqaBG0O6FvLG1cTxxojfcCPVA&amp;oe=6AB7746B
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/820155649_934627876385396_5816979534645335942_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5MTI1NzgyOTg4MDY0OTYxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=LfsSQVxbgLcQ7kNvwEcaioO&amp;_nc_oc=AdrNSZ89Vb3irP2_fpW1klsXASb79R_77yok3s1m_AjaXajhunD_mIDq5aRxpwRpJgQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQKzBHUGTPATC3o6txFFzIoNJ4EYUtBex-igJTa4AvDzCw&amp;oe=6AB7746B
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwE0A6MH&amp;_nc_oc=AdrNJvu6kh947YrzfHb4R4hjRZ-LfcGtmcg1z_jI2NshhsfTiWZ1rTSiZnRYaZT_1DY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKfB2IepL3oNjy3FYapfA0JCkx88Tx0DKiF6TMAl8I_ng&amp;oe=6AB74619
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Ffigma%2Fjobs%2F6200626004%3Fgh_jid%3D6200626004%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacQKYO-w_b9hZfhTMk3_K8AV4TQ1Y7PhnefZr1gwIoErBNNR7kqdurKHZINew_aem_gWNzMpUW8XhlPwb9ip152A&amp;e=AUAiay4HEH-5FTVFYDvoIXamq8fIydpFxEtEY1sxXaL6buKvYR7lGPaBCp9quCxfc7b-LVFcFfPIRZD0vA_ewVrjcQ9KOL88EFEAUciAJg
+https://scontent-lga3-2.cdninstagram.com/o1/v/t2/f2/m78/AQOgbWZxjfXVWZMAw8MBuYN5pPzwJiScJz69CMiIiWn49TE61PWlzyWfElkMiu44a2A-uvyiZF56_Oz3g-3PW0duBYmb2UW2dOjU4Gg.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ohc=rpqewcU8Eh0Q7kNvwFGWjxj&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc3ODgzMjQ2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=333669bf96a98e7d&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzQ4NDU5QUREQjQ4MkM2QjZGQzkzMDQwMzgxOUFGQjkyX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbktOvd7K-hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKx9lRiawgiFC5QaM3NZYcI72NcZG7tSevaGrS7tni-ZQ&amp;oe=6AB3651D</t>
+        </is>
+      </c>
+      <c r="O81" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P81" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q81" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82" ht="45" customHeight="1">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>fca36e20864312b3fe74</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T19:36:35.490224+00:00</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T18:27:16+00:00</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Upbound</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>Upbound — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr"/>
+      <c r="J82" s="3" t="inlineStr"/>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>https://upbound.wd501.myworkdayjobs.com/Acima/job/Draper-UT/Software-Engineer-Intern_R-100759-1</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
+          <t>4 @ upbound.wd501.myworkdayjo... C:
+Instagram o
+We've been recognized for fixe)
+our people-first culture. [eeress
+topworkplaces.com
+Software Engineer Intern
+© Draper, UT
+fa] Full time
+(©) Posted Today
+(2) UPBOUND.WD501.MYWORKDAYJOBS.
+[=| R-100759
+Job Description:
+2027 Summer Internship Proposal: Acima
+Software Engineering
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/797398264_1639183977620288_3231300044519989860_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5MTI1OTU2Mzk0MDEyOTEwNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=M3MTPOrS898Q7kNvwGvCEaM&amp;_nc_oc=AdqXuztkVTDXGdwSM-e2CtYhvfBehKFqAjRreWeYqu6RESbd11NS_itGDnC4N_pAQqk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQI_3oqgfALTeyGI2DLg4XXq-Ttf3xyza7CxGJ_wO1alHw&amp;oe=6AB740FF
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/797398264_1639183977620288_3231300044519989860_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5MTI1OTU2Mzk0MDEyOTEwNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=M3MTPOrS898Q7kNvwGvCEaM&amp;_nc_oc=AdqXuztkVTDXGdwSM-e2CtYhvfBehKFqAjRreWeYqu6RESbd11NS_itGDnC4N_pAQqk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQK4h8f3Wnb_96x10Jy2Bow3z462DBqTwsR3lruQHopUrg&amp;oe=6AB740FF
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwE0A6MH&amp;_nc_oc=AdrNJvu6kh947YrzfHb4R4hjRZ-LfcGtmcg1z_jI2NshhsfTiWZ1rTSiZnRYaZT_1DY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKfB2IepL3oNjy3FYapfA0JCkx88Tx0DKiF6TMAl8I_ng&amp;oe=6AB74619
+https://l.instagram.com/?u=https%3A%2F%2Fupbound.wd501.myworkdayjobs.com%2FAcima%2Fjob%2FDraper-UT%2FSoftware-Engineer-Intern_R-100759-1%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeu1OysAq0Qs3dMQ3B-4OQQOU3Xz5d1g77DO_WGD3byMyL44sTsQs5_QzeOUA_aem_B4pGO1O3nao3J04iJGJawQ%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUCy-rB6ZEielYwE5zzUHUAMDl6GGCWXzlOd9B_leymXlPfTSDVOCex98zah9T442rmVRrj3Snz4zi-DUiyLxOkx7ToeMAQcr8nzEQud1g
+https://scontent-lga3-3.cdninstagram.com/o1/v/t2/f2/m78/AQPiiRGb6Yeo6YGT0v3C4ZPeT9dD1R8Tb4hivw7-7BrClubtuPjfvC5f_w_eDN-NfCMuWbg4as5vO-wz2NArGaHqsOKsiHtIOzUD3-E.mp4?_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_ohc=3NqeLCexrZEQ7kNvwGP84qr&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc3ODg5NTQ2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=52fd4da6410cfd7d&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzhFNEE0MDAwN0Q1RjJGQTBCRTlFMDdCRkVDQTJBQkFEX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk2tO28a-hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKttaHNwDRyJCNqofUJsY0X0Yasb9wkpE4BY-bBZcCMqw&amp;oe=6AB37409</t>
+        </is>
+      </c>
+      <c r="O82" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P82" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q82" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83" ht="45" customHeight="1">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>866943b1a91056fd320d</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T19:36:40.206039+00:00</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T18:54:14+00:00</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr"/>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr"/>
+      <c r="H83" s="3" t="inlineStr"/>
+      <c r="I83" s="3" t="inlineStr"/>
+      <c r="J83" s="3" t="inlineStr"/>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>https://www.directconsideration.com/p/direct-consideration-007</t>
+        </is>
+      </c>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
+          <t>@ directconsideration.com GC:
+Instagram
+Something's shifting in how
+companies are deciding who even
+gets looked at this cycle.
+Networking used to be above &amp;
+beyond for your application, but
+now it's becoming the bare
+minimum. For a growing number of
+companies, meet-and-greets and
+what's getting yof~_resume
+considered.
+Hey how are you doing! Big fan of
+your account you're super
+helpful. Was wondering how | can
+apply to ramp. Is there some
+exclusive link for people who
+attended ramp events or have |
+just not found it yet?
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/795182445_1096929296380410_8142141806982377272_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5MTI3MzEzNTk0NDU1Nzc5MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=g5Qc7DNZdtQQ7kNvwFaWvtP&amp;_nc_oc=AdqdD87RdGmxzIF2MD8dSn5ZS2LJsiSkcKPNr77FEC5naUpU6a0gQT56BPqraCVZHRg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQJO3lqZac_GKMg8hOLupf1O-RfVHt_Mmjh8NtMCGt97Ig&amp;oe=6AB73E47
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/795182445_1096929296380410_8142141806982377272_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5MTI3MzEzNTk0NDU1Nzc5MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=g5Qc7DNZdtQQ7kNvwFaWvtP&amp;_nc_oc=AdqdD87RdGmxzIF2MD8dSn5ZS2LJsiSkcKPNr77FEC5naUpU6a0gQT56BPqraCVZHRg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQJXszXX3Y5EoNOcNVtOLfKdGKJRpbnfSU5ln7IiVrfMBg&amp;oe=6AB73E47
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwE0A6MH&amp;_nc_oc=AdrNJvu6kh947YrzfHb4R4hjRZ-LfcGtmcg1z_jI2NshhsfTiWZ1rTSiZnRYaZT_1DY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKfB2IepL3oNjy3FYapfA0JCkx88Tx0DKiF6TMAl8I_ng&amp;oe=6AB74619
+https://l.instagram.com/?u=https%3A%2F%2Fwww.directconsideration.com%2Fp%2Fdirect-consideration-007%3Futm_source%3Dig%26utm_medium%3Dsocial%26utm_content%3Dlink_in_bio%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacLzSlTLEcP9q-bNObucWxaIfmrQF9dtFZgZzYNqGxoQoN3bE0cNVlEVG0-Jg_aem_HJO0KHATf3P8B8Dfo9odZA&amp;e=AUDAYBSEnwtW9DA3kNflXie0bV2nGua3eWrKFA03gyDNKGh-TdcK_RhH8xgelbVPg83mRkNVuaVN_PoXdb-JrkYo6WAHJHJYhkQVz41jGg
+https://scontent-lga3-1.cdninstagram.com/o1/v/t2/f2/m78/AQOQlAqx9J9KtlhDUQqSya9NKiHbjASITSJorbAH0nznTo8Gf4ifpqrcdMTIxrBbzn2MVvCiDQODo3zq9Vjm8nAhaf7gGZBXGqRnRZs.mp4?_nc_cat=110&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_ohc=4AoVTSbRPE8Q7kNvwFrlfC1&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc3OTE0NTY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=1dcbcc8c4799a2cf&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzU4NDBCQTVEMzNFNTdGM0FDODRENTY2NkRBRUZFQzg3X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk0N-IhLChQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIraqNxZQPRxWQpoRlJUFBFPhTyJcwcelZQBnSpPkCpOw&amp;oe=6AB35083</t>
+        </is>
+      </c>
+      <c r="O83" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P83" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q83" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84" ht="45" customHeight="1">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>d612bd08db3d1c460aff</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T19:36:41.381934+00:00</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T19:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr"/>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>2027 Summer Intern - Quantitative</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr"/>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>2027, 2026</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr"/>
+      <c r="J84" s="3" t="inlineStr"/>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>https://firstcitizens.jibeapply.com/jobs/35602?icims=1</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
+          <t>@ firstcitizens.jibeapply.com &amp;
+Instagram
+B First Citizens Bank
+€ Back
+2027 Summer Intern - Quantitative
+Analysis (North Carolina)
+Req ID: 35602
+Address: 100 East Tryon Road
+Location(s): Raleigh, North Carolina
+Category: Compliance
+Work Hours: Monday - Friday
+Posted Date: 09/21/2026
+a
+https://scontent-lga3-1.cdninstagram.com/v/t51.71878-15/795913487_2131143867769752_4436356593542603195_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MTI3OTY1NTcwNDg3ODAzMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=yveZzKucyXUQ7kNvwGsS3I5&amp;_nc_oc=AdruoMYij4BlmfE1Z9KOHvJ26xywZt46E7oyPhF_43wCc0J0Z612rvuBoO8sbEPa--w&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQJiNB0NgqkjI0YaAYNj66QJK1lFa2D4zuzhL8NvZ0V9vA&amp;oe=6AB76B70
+https://scontent-lga3-1.cdninstagram.com/v/t51.71878-15/795913487_2131143867769752_4436356593542603195_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MTI3OTY1NTcwNDg3ODAzMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=yveZzKucyXUQ7kNvwGsS3I5&amp;_nc_oc=AdruoMYij4BlmfE1Z9KOHvJ26xywZt46E7oyPhF_43wCc0J0Z612rvuBoO8sbEPa--w&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQK6Gln1OicQjwjlcblgToJY6rbxPRooPU0L5KWValCutA&amp;oe=6AB76B70
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwE0A6MH&amp;_nc_oc=AdrNJvu6kh947YrzfHb4R4hjRZ-LfcGtmcg1z_jI2NshhsfTiWZ1rTSiZnRYaZT_1DY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKfB2IepL3oNjy3FYapfA0JCkx88Tx0DKiF6TMAl8I_ng&amp;oe=6AB74619
+https://l.instagram.com/?u=https%3A%2F%2Ffirstcitizens.jibeapply.com%2Fjobs%2F35602%3Ficims%3D1%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAae0vDWo41NJK6bFC1bPNEs13-DgmgZmeEPTQ-sklYXhB1liIUfPrz768zYarg_aem_Y0WHsw7MULpb9mh6vD3z1g&amp;e=AUDCNbzL1xKJT7IQR__DXTNVdUMGrGYPrtMk4giUZ2DOwmmAktgVjECt0OyUJzQzJP0wIHQNoxgCz5sEfJ4eehWWOThDG3YUBWbiH9xk6w
+https://scontent-lga3-1.cdninstagram.com/o1/v/t2/f2/m78/AQMbwVTgowFGfKpX_bgZJj0xuoo0nCsTt8toZKWhbLcmQBkqNaS6BeKKJ7RRzugnuhYqDVgxxqfdCRXEQrfI9M6l2iggW8gy8sMSJqE.mp4?_nc_cat=110&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_ohc=2NgHCYJctycQ7kNvwE1uNvH&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc3OTI0NTI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=a6174011449fa65d&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0FENDBBMDQ0MjI2NDEzRjZDMUZCN0Q2QTREQzJBMzhBX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk1M2-i7ChQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIm4QIflrM0ygzdZAta_jQHhuL-K4mnXINohwQOQsC6XA&amp;oe=6AB376BF</t>
+        </is>
+      </c>
+      <c r="O84" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P84" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q84" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R84" s="3" t="inlineStr"/>
+    </row>
+    <row r="85" ht="45" customHeight="1">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>c2c6b1f2698ec2738948</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T19:36:42.502626+00:00</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T19:08:20+00:00</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Upbound</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>Upbound — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr"/>
+      <c r="J85" s="3" t="inlineStr"/>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>https://upbound.wd501.myworkdayjobs.com/Upbound/job/Plano-TX/Software-Engineer-Intern_R-100762</t>
+        </is>
+      </c>
+      <c r="L85" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
+          <t>4 8 Hp ROUT WER HID WoHiGiVEa= C i:
+upbound
+upbound
+[za =
+Software Engineer Intern
+© Plano, TX
+fea] Full time
+(©) Posted Today
+fF] End Date: October 9, 2026 (17 days left to
+Job Description:
+Upbound Group SummefZ027 Internship —
+Software Engineer
+https://scontent-lga3-1.cdninstagram.com/v/t51.71878-15/797035961_1759699175281140_2815342702789291414_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MTI4MDI0MDcwMTIxMzU1Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=G3CJYhL2jlkQ7kNvwEL23Ee&amp;_nc_oc=AdpQiA7m0inVrihowmvD_RY1HO2J_GUDpNroRn_QqrBLj5_e3LsDD-9FJJ3qKoYNZWU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQJ3ubIDR19s7YFK1Tzcetr-o-01OZgepP1ppB4Gp5DxJA&amp;oe=6AB76C1F
+https://scontent-lga3-1.cdninstagram.com/v/t51.71878-15/797035961_1759699175281140_2815342702789291414_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MTI4MDI0MDcwMTIxMzU1Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=G3CJYhL2jlkQ7kNvwEL23Ee&amp;_nc_oc=AdpQiA7m0inVrihowmvD_RY1HO2J_GUDpNroRn_QqrBLj5_e3LsDD-9FJJ3qKoYNZWU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;oh=00_AQIbNKuflBNQ3iTokWHg69WhtRwnj6ct_5jgbHBb7BP8gg&amp;oe=6AB76C1F
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwE0A6MH&amp;_nc_oc=AdrNJvu6kh947YrzfHb4R4hjRZ-LfcGtmcg1z_jI2NshhsfTiWZ1rTSiZnRYaZT_1DY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKfB2IepL3oNjy3FYapfA0JCkx88Tx0DKiF6TMAl8I_ng&amp;oe=6AB74619
+https://l.instagram.com/?u=https%3A%2F%2Fupbound.wd501.myworkdayjobs.com%2FUpbound%2Fjob%2FPlano-TX%2FSoftware-Engineer-Intern_R-100762%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadAjpmjDey73eql6cVK2DMNXlKljhqV92ok9P1dRn_ylEz3DfdGWgjJBCGHAQ_aem_V1vOIzJxjS5SDYl35WMCfA%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUBjUS0UPHNqCBDIu6Iok8dOxPqWVaZ1MfGxoiW3YlIBUSSp78h7yStbfQGN2rdOto-OfAVHp8nwCizHPGzTOnnqsZZAtYEijOKo3zZ1ew
+https://scontent-lga3-3.cdninstagram.com/o1/v/t2/f2/m78/AQOURw_KAhqS_aVFnHba0dAQKVYX0fPUVUxdRe3QtcLIZhEVOo32moJRktAfEzLYDPoUlBbroRlSTZ0RgxUIq0slaIrqeV3GQCdQpg0.mp4?_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_ohc=K_dqVcna8wIQ7kNvwEZKspi&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc3OTI4NjA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=a6faa5e668bed91e&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzdDNEEwOTQzQjJBODBFMUIxMjcyQjE3ODI3NUY1NTlBX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkrNrDjrChQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=acmwX1mBAbJ8DcuQtUcqTA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQI7OdojIMn5z9GpKs8qbKGN66PReJczCPjdyWfaXyLu3Q&amp;oe=6AB37DC9</t>
+        </is>
+      </c>
+      <c r="O85" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P85" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q85" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R85" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R71"/>
+  <autoFilter ref="A1:R85"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -7277,6 +8618,33 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L81" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L83" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L84" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId155"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R85"/>
+  <dimension ref="A1:R95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7149,7 +7149,7 @@
     <row r="72" ht="45" customHeight="1">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>983ec485796900be7ac9</t>
+          <t>5d8fe074ef4791982b59</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -7162,7 +7162,7 @@
           <t>2026-09-21T14:55:10+00:00</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr"/>
+      <c r="D72" s="3" t="n"/>
       <c r="E72" s="3" t="inlineStr">
         <is>
           <t>Software Engineering</t>
@@ -7188,7 +7188,7 @@
           <t>Boston</t>
         </is>
       </c>
-      <c r="J72" s="3" t="inlineStr"/>
+      <c r="J72" s="3" t="n"/>
       <c r="K72" s="4" t="inlineStr">
         <is>
           <t>https://wd1.myworkdaysite.com/en-US/recruiting/fmr/FidelityCareers/job/Summer-2027-Undergraduate-Internship---Software_2134524</t>
@@ -7247,12 +7247,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R72" s="3" t="inlineStr"/>
+      <c r="R72" s="3" t="n"/>
     </row>
     <row r="73" ht="45" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>c577dffaff4e5f4eb223</t>
+          <t>00103a346c8fd302188a</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -7280,14 +7280,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr"/>
+      <c r="G73" s="3" t="n"/>
       <c r="H73" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I73" s="3" t="inlineStr"/>
-      <c r="J73" s="3" t="inlineStr"/>
+      <c r="I73" s="3" t="n"/>
+      <c r="J73" s="3" t="n"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
           <t>https://jobs.fidelity.com/en/jobs/2134164/summer-2027-undergraduate-internship-systems</t>
@@ -7339,12 +7339,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R73" s="3" t="inlineStr"/>
+      <c r="R73" s="3" t="n"/>
     </row>
     <row r="74" ht="45" customHeight="1">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>7aeb86574fe09c2b119b</t>
+          <t>92dcb53669d8cf32d4a4</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -7382,8 +7382,8 @@
           <t>Winter 2027</t>
         </is>
       </c>
-      <c r="I74" s="3" t="inlineStr"/>
-      <c r="J74" s="3" t="inlineStr"/>
+      <c r="I74" s="3" t="n"/>
+      <c r="J74" s="3" t="n"/>
       <c r="K74" s="4" t="inlineStr">
         <is>
           <t>https://capitalone.wd12.myworkdayjobs.com/en-US/Capital_One/job/Toronto-ON/Intern--Backend-Software-Engineer---Team-Interstellar---Winter-2027_R249022</t>
@@ -7438,12 +7438,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R74" s="3" t="inlineStr"/>
+      <c r="R74" s="3" t="n"/>
     </row>
     <row r="75" ht="45" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2bd93cf526e78c9b0324</t>
+          <t>394409df0be7257ceb2a</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -7481,8 +7481,8 @@
           <t>Winter 2027</t>
         </is>
       </c>
-      <c r="I75" s="3" t="inlineStr"/>
-      <c r="J75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="n"/>
+      <c r="J75" s="3" t="n"/>
       <c r="K75" s="4" t="inlineStr">
         <is>
           <t>https://capitalone.wd12.myworkdayjobs.com/en-US/Capital_One/job/Toronto-ON/Intern--Mobile-Software-Engineer---Team-Gringotts-North---Winter-2027_R249015</t>
@@ -7535,12 +7535,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R75" s="3" t="inlineStr"/>
+      <c r="R75" s="3" t="n"/>
     </row>
     <row r="76" ht="45" customHeight="1">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>c790bd579ec2b1298bc7</t>
+          <t>7e750868d7699801f72f</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -7578,8 +7578,8 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="I76" s="3" t="inlineStr"/>
-      <c r="J76" s="3" t="inlineStr"/>
+      <c r="I76" s="3" t="n"/>
+      <c r="J76" s="3" t="n"/>
       <c r="K76" s="4" t="inlineStr">
         <is>
           <t>https://capitalone.wd12.myworkdayjobs.com/en-US/Capital_One/job/McLean-VA/Technology-Development-Program-Associate---February-2027_R244320-1</t>
@@ -7638,12 +7638,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R76" s="3" t="inlineStr"/>
+      <c r="R76" s="3" t="n"/>
     </row>
     <row r="77" ht="45" customHeight="1">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>dad305ab369e7fd7e8fd</t>
+          <t>3df951f57a795cd83697</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -7656,7 +7656,7 @@
           <t>2026-09-21T15:06:20+00:00</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr"/>
+      <c r="D77" s="3" t="n"/>
       <c r="E77" s="3" t="inlineStr">
         <is>
           <t>SS eccanca Apply now</t>
@@ -7667,10 +7667,10 @@
           <t>Fellowship</t>
         </is>
       </c>
-      <c r="G77" s="3" t="inlineStr"/>
-      <c r="H77" s="3" t="inlineStr"/>
-      <c r="I77" s="3" t="inlineStr"/>
-      <c r="J77" s="3" t="inlineStr"/>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+      <c r="I77" s="3" t="n"/>
+      <c r="J77" s="3" t="n"/>
       <c r="K77" s="4" t="inlineStr">
         <is>
           <t>https://www.perplexity.ai/hub/research/fellowship</t>
@@ -7721,12 +7721,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R77" s="3" t="inlineStr"/>
+      <c r="R77" s="3" t="n"/>
     </row>
     <row r="78" ht="45" customHeight="1">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>45c2e426db3af34068b2</t>
+          <t>a5620a59cb37efb5f794</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -7739,7 +7739,7 @@
           <t>2026-09-21T15:55:35+00:00</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr"/>
+      <c r="D78" s="3" t="n"/>
       <c r="E78" s="3" t="inlineStr">
         <is>
           <t>Thank you for applying to the Code for Good Hackathon - Software Engineer Program - 2027 Summer Inte</t>
@@ -7760,9 +7760,9 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="I78" s="3" t="inlineStr"/>
-      <c r="J78" s="3" t="inlineStr"/>
-      <c r="K78" s="3" t="inlineStr"/>
+      <c r="I78" s="3" t="n"/>
+      <c r="J78" s="3" t="n"/>
+      <c r="K78" s="3" t="n"/>
       <c r="L78" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -7820,12 +7820,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R78" s="3" t="inlineStr"/>
+      <c r="R78" s="3" t="n"/>
     </row>
     <row r="79" ht="45" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>82f3f0df61965bf77b9b</t>
+          <t>1b5c4d3be031da719ebe</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -7838,7 +7838,7 @@
           <t>2026-09-21T16:40:46+00:00</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr"/>
+      <c r="D79" s="3" t="n"/>
       <c r="E79" s="3" t="inlineStr">
         <is>
           <t>Internship</t>
@@ -7849,7 +7849,7 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G79" s="3" t="inlineStr"/>
+      <c r="G79" s="3" t="n"/>
       <c r="H79" s="3" t="inlineStr">
         <is>
           <t>2027</t>
@@ -7860,7 +7860,7 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="J79" s="3" t="inlineStr"/>
+      <c r="J79" s="3" t="n"/>
       <c r="K79" s="4" t="inlineStr">
         <is>
           <t>https://icbpjb.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/sites/LazardStudentCareers/job/6606</t>
@@ -7917,12 +7917,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R79" s="3" t="inlineStr"/>
+      <c r="R79" s="3" t="n"/>
     </row>
     <row r="80" ht="45" customHeight="1">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>0335faf860ca686097d8</t>
+          <t>00d13a3ba4190698aff2</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -7935,7 +7935,7 @@
           <t>2026-09-21T16:42:58+00:00</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr"/>
+      <c r="D80" s="3" t="n"/>
       <c r="E80" s="3" t="inlineStr">
         <is>
           <t>Data Engineer Intern and help build</t>
@@ -7956,8 +7956,8 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="I80" s="3" t="inlineStr"/>
-      <c r="J80" s="3" t="inlineStr"/>
+      <c r="I80" s="3" t="n"/>
+      <c r="J80" s="3" t="n"/>
       <c r="K80" s="4" t="inlineStr">
         <is>
           <t>https://icbpjb.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/sites/LazardStudentCareers/job/6605</t>
@@ -8012,12 +8012,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R80" s="3" t="inlineStr"/>
+      <c r="R80" s="3" t="n"/>
     </row>
     <row r="81" ht="45" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>4b908a57794c5a3d3040</t>
+          <t>9577413b5002eeec8547</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -8045,7 +8045,7 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G81" s="3" t="inlineStr"/>
+      <c r="G81" s="3" t="n"/>
       <c r="H81" s="3" t="inlineStr">
         <is>
           <t>2027</t>
@@ -8056,7 +8056,7 @@
           <t>San Francisco, New York</t>
         </is>
       </c>
-      <c r="J81" s="3" t="inlineStr"/>
+      <c r="J81" s="3" t="n"/>
       <c r="K81" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/figma/jobs/6200626004?gh_jid=6200626004</t>
@@ -8111,12 +8111,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R81" s="3" t="inlineStr"/>
+      <c r="R81" s="3" t="n"/>
     </row>
     <row r="82" ht="45" customHeight="1">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>fca36e20864312b3fe74</t>
+          <t>d7e450b3d652da76f582</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -8154,8 +8154,8 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="I82" s="3" t="inlineStr"/>
-      <c r="J82" s="3" t="inlineStr"/>
+      <c r="I82" s="3" t="n"/>
+      <c r="J82" s="3" t="n"/>
       <c r="K82" s="4" t="inlineStr">
         <is>
           <t>https://upbound.wd501.myworkdayjobs.com/Acima/job/Draper-UT/Software-Engineer-Intern_R-100759-1</t>
@@ -8209,12 +8209,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R82" s="3" t="inlineStr"/>
+      <c r="R82" s="3" t="n"/>
     </row>
     <row r="83" ht="45" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>866943b1a91056fd320d</t>
+          <t>653b118e4dc225eb4ac7</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -8227,7 +8227,7 @@
           <t>2026-09-21T18:54:14+00:00</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr"/>
+      <c r="D83" s="3" t="n"/>
       <c r="E83" s="3" t="inlineStr">
         <is>
           <t>Other Opportunity</t>
@@ -8238,10 +8238,10 @@
           <t>Other Opportunity</t>
         </is>
       </c>
-      <c r="G83" s="3" t="inlineStr"/>
-      <c r="H83" s="3" t="inlineStr"/>
-      <c r="I83" s="3" t="inlineStr"/>
-      <c r="J83" s="3" t="inlineStr"/>
+      <c r="G83" s="3" t="n"/>
+      <c r="H83" s="3" t="n"/>
+      <c r="I83" s="3" t="n"/>
+      <c r="J83" s="3" t="n"/>
       <c r="K83" s="4" t="inlineStr">
         <is>
           <t>https://www.directconsideration.com/p/direct-consideration-007</t>
@@ -8300,12 +8300,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R83" s="3" t="inlineStr"/>
+      <c r="R83" s="3" t="n"/>
     </row>
     <row r="84" ht="45" customHeight="1">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>d612bd08db3d1c460aff</t>
+          <t>f5fdcb41a0300ff0a032</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -8318,7 +8318,7 @@
           <t>2026-09-21T19:07:10+00:00</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr"/>
+      <c r="D84" s="3" t="n"/>
       <c r="E84" s="3" t="inlineStr">
         <is>
           <t>2027 Summer Intern - Quantitative</t>
@@ -8329,14 +8329,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G84" s="3" t="inlineStr"/>
+      <c r="G84" s="3" t="n"/>
       <c r="H84" s="3" t="inlineStr">
         <is>
           <t>2027, 2026</t>
         </is>
       </c>
-      <c r="I84" s="3" t="inlineStr"/>
-      <c r="J84" s="3" t="inlineStr"/>
+      <c r="I84" s="3" t="n"/>
+      <c r="J84" s="3" t="n"/>
       <c r="K84" s="4" t="inlineStr">
         <is>
           <t>https://firstcitizens.jibeapply.com/jobs/35602?icims=1</t>
@@ -8389,12 +8389,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R84" s="3" t="inlineStr"/>
+      <c r="R84" s="3" t="n"/>
     </row>
     <row r="85" ht="45" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>c2c6b1f2698ec2738948</t>
+          <t>bab96fe3dc36e8493189</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -8432,8 +8432,8 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="I85" s="3" t="inlineStr"/>
-      <c r="J85" s="3" t="inlineStr"/>
+      <c r="I85" s="3" t="n"/>
+      <c r="J85" s="3" t="n"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
           <t>https://upbound.wd501.myworkdayjobs.com/Upbound/job/Plano-TX/Software-Engineer-Intern_R-100762</t>
@@ -8485,10 +8485,940 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R85" s="3" t="inlineStr"/>
+      <c r="R85" s="3" t="n"/>
+    </row>
+    <row r="86" ht="45" customHeight="1">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>c286a1ff663e9adc9c7f</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:22:35.213981+00:00</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T20:10:52+00:00</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Genevatrading</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>Genevatrading — Internship</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr"/>
+      <c r="H86" s="3" t="inlineStr"/>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr"/>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/genevatrading/jobs/5242063007?gh_src=7bx7tr8c7us&amp;t=3253f722teu</t>
+        </is>
+      </c>
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
+          <t>ADING-
+C++ Developer (Intern)
+Chicago Office
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/814575434_1274388944825470_7288911666501287285_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MTMxMTcwNzU1MzMwNDQyNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Q8xd0S5Cmy8Q7kNvwFnPZ-q&amp;_nc_oc=AdpJ2C2_SD36tGKFUePzcPld-h1ujL-iRYWCdFghkZjMxrwODV19Lj0-dYN5gFz5KAo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;oh=00_AQKaDHBg0wQ1BpUll_8oS6fQ13QkZlEC3wop-cBh5Zt7WQ&amp;oe=6AB78C21
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/814575434_1274388944825470_7288911666501287285_n.jpg?stp=dst-jpg_e15_p320x320_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MTMxMTcwNzU1MzMwNDQyNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Q8xd0S5Cmy8Q7kNvwFnPZ-q&amp;_nc_oc=AdpJ2C2_SD36tGKFUePzcPld-h1ujL-iRYWCdFghkZjMxrwODV19Lj0-dYN5gFz5KAo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;oh=00_AQIaaAU21tPCJseqDwQZF8sM84iIYGIYpY0S-HExoBrQvQ&amp;oe=6AB78C21
+https://scontent-xxc1-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwFHhipe&amp;_nc_oc=AdrGD-HVTWaEVSMYt8qlE6H1GC_EDOv7RpmTuZ1UgSz3bdjJtskA7mY-eXGls3o01lk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQJpz9HTjGukImMahmzPq83_-qS-XVpNCz23mBbr82zg7g&amp;oe=6AB77E59
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fgenevatrading%2Fjobs%2F5242063007%3Fgh_src%3D7bx7tr8c7us%26t%3D3253f722teu%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAac8fBHodp5HHw6Zof2ds4UrPjOUuKWFcHFAj_apy2Gp8ropn4_jdB8gYDivqA_aem_WVrHuVSEtHGdsWbgM-bieg&amp;e=AUDQVl6ylt94zC4j1HEk595p296zlMtG3XiYzQC6SwmLhPlrTsEPUGUNLhWqbyvJIXOqXWgCp64RXug_EezQu1zGg1xgoJWzZFKrpJFWlw
+https://scontent-xxc1-1.cdninstagram.com/o1/v/t2/f2/m78/AQN_8_DXk8GbA5g-_-Yoof9CwQreFvYxdvM29jGpzLi2AAnLZQzL-CzUrVGYvaFEVCN1cJVGBNdeeOOhGXeqCx_s-Yc46_K76qgXidQ.mp4?_nc_cat=110&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ohc=vtfADMgkWYIQ7kNvwHYIU0c&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc3OTg4MDk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=71dc9c0193239465&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzgwNDU1QkFERUE3RDc3RUNGQkUyRThGNjgyNUI0MEIzX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk0Y7turChQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJ2fi00TYg0plWRL99MR_Hr0ydDrMkKm1TkZz6o5qxQ5A&amp;oe=6AB38BB7</t>
+        </is>
+      </c>
+      <c r="O86" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P86" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q86" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87" ht="45" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>e8e1bfd1ad020db4c422</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:22:36.770031+00:00</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T20:29:56+00:00</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr"/>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>Scientific Join Talent Network English v</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr"/>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr"/>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>https://bostonscientific.eightfold.ai/careers/job/563602813600504?domain=bostonscientific.com</t>
+        </is>
+      </c>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
+          <t>@ bostonscientific.eightfold.ai C+:
+Instagram
+Boston, . .
+Scientific Join Talent Network English v
+&lt; View All Jobs
+Data Science
+Engineering Internship
+Q Arden Hills US-MN, United States | N/A
+Apply Now Add to cart
+9 PA
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/817742250_2567809583663441_4801417896346276913_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MTMyMTMxMDAwOTAwMjE3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=dWcx58m2hC4Q7kNvwHdAqJt&amp;_nc_oc=Adq46UPNBfeb8D8laRAAnAyPrGLxRsDL-gbjhDRzRO68tkUYPeNaRixf7J5VCjZxtwU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;oh=00_AQL5OL6zwIbgqODJOYsS6b-JxDz3q9n2fAAVf0QQS8T7aQ&amp;oe=6AB78A01
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/817742250_2567809583663441_4801417896346276913_n.jpg?stp=dst-jpg_e15_p320x320_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MTMyMTMxMDAwOTAwMjE3OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=dWcx58m2hC4Q7kNvwHdAqJt&amp;_nc_oc=Adq46UPNBfeb8D8laRAAnAyPrGLxRsDL-gbjhDRzRO68tkUYPeNaRixf7J5VCjZxtwU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;oh=00_AQIKgEFoA97DQ24tvDoj7Hq5oRJMLQrdpZ5eaFwkyc1_WA&amp;oe=6AB78A01
+https://scontent-xxc1-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwFHhipe&amp;_nc_oc=AdrGD-HVTWaEVSMYt8qlE6H1GC_EDOv7RpmTuZ1UgSz3bdjJtskA7mY-eXGls3o01lk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQJpz9HTjGukImMahmzPq83_-qS-XVpNCz23mBbr82zg7g&amp;oe=6AB77E59
+https://l.instagram.com/?u=https%3A%2F%2Fbostonscientific.eightfold.ai%2Fcareers%2Fjob%2F563602813600504%3Fdomain%3Dbostonscientific.com%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadK8WehzPg5DFt2mRHoYHfruy2-hvXvWJfqBJfjA048PNU9KbBJY_zhSuBklg_aem_z8Mg4adJn2YEVc1Q7kUfDw&amp;e=AUCY5eJcgB-E0oOEWEtlLmA1UkmhNbLBBgChf_vOGqZ9rd0MKUTGLkzLZqRHZqQZnpf8K6_Oo2cFWmaf97EdFyh66XfcCVtEqCEoNlNXJw
+https://scontent-xxc1-1.cdninstagram.com/o1/v/t2/f2/m78/AQNk-R2po75CC3GkFj5-WoEpyKFfB04DS2wJKSSEgEVMlwtYCjleGaj78fJx5tiAd3HjzFJKJSJPhIzQcZoWDdgNyZ92P8ow3Djp4l4.mp4?_nc_cat=104&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ohc=SHwrPT0RcywQ7kNvwHx2fhd&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc4MDAzNDI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=4ed5988c3130e5f2&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzE5NDI3RUM1Njg3NkQ4RkJEQzI1QjNCNjE4M0ExNzlBX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbktoyjxrChQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJqSH4bQQGwz5e1BvQD0n6oyjoGwzgHk57AAHMbR0SBXg&amp;oe=6AB3969D</t>
+        </is>
+      </c>
+      <c r="O87" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P87" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q87" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R87" s="3" t="inlineStr"/>
+    </row>
+    <row r="88" ht="45" customHeight="1">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>d1345eb46d9d3f00a185</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:22:49.566132+00:00</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T21:04:53+00:00</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr"/>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>Join us for an informative session</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr"/>
+      <c r="I88" s="3" t="inlineStr"/>
+      <c r="J88" s="3" t="inlineStr"/>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>https://capitalone.eightfold.ai/events/candidate?plannedEventId=EPYJ0oNW</t>
+        </is>
+      </c>
+      <c r="L88" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
+          <t>Product Open House-Innovate &amp;
+Influence | Eightfold
+Join us for an informative session
+to learn about the Small Business
+Bank and Customers, Systems &amp;
+Intelligence teams! You'll have the
+opportunity to hear directly from
+Product leaders about the exciting
+work happening in this space and the
+vision for the Product Management
+team. Please note: Yo...
+(2? CAPITALONE.EIGHTFOLD.AI
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/797058628_1438439848178435_3244161249697307418_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MTMzODg5NjY4MzcxOTM2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=jOH63HSpW7wQ7kNvwEEvt4q&amp;_nc_oc=Adp6U-RifaVCgLllgbrn1x9zEa1GOdLr8wWnU325OyCb5Mkpoo-WlDDeCGKwQyMpkV4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;oh=00_AQJCnujzNFTYS7TpydXrySxrlIYBr_AeFRIO2c6p6vzirg&amp;oe=6AB780EA
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/797058628_1438439848178435_3244161249697307418_n.jpg?stp=dst-jpg_e15_p320x320_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MTMzODg5NjY4MzcxOTM2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=jOH63HSpW7wQ7kNvwEEvt4q&amp;_nc_oc=Adp6U-RifaVCgLllgbrn1x9zEa1GOdLr8wWnU325OyCb5Mkpoo-WlDDeCGKwQyMpkV4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;oh=00_AQIu2VJm9E-zfZ4vTwl4Kb_p4X5be9BAl-Sr4bOuih4PlQ&amp;oe=6AB780EA
+https://scontent-xxc1-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwFHhipe&amp;_nc_oc=AdrGD-HVTWaEVSMYt8qlE6H1GC_EDOv7RpmTuZ1UgSz3bdjJtskA7mY-eXGls3o01lk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQJpz9HTjGukImMahmzPq83_-qS-XVpNCz23mBbr82zg7g&amp;oe=6AB77E59
+https://l.instagram.com/?u=https%3A%2F%2Fcapitalone.eightfold.ai%2Fevents%2Fcandidate%3FplannedEventId%3DEPYJ0oNW%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeSEm33vTk16taYDq6lCHo2Sbhnv-3m41uTXDV8v0x-hfHPpeM-oZxL1NrrUg_aem_E7UZmikBrHawo8S3HWGctg&amp;e=AUBpOD8iYIrSpmymeF8TdDEOavsSx0Wv-Rj3qnmbWESOJKzF_OmHiLKckVbRpjM6_Fng-9TDfMGxM-5CMs20luBo3Yy6kG6x6sSYnJ_q6A
+https://scontent-xxc1-1.cdninstagram.com/o1/v/t2/f2/m78/AQOpP-DcCAB8Q5ysjuu8d39NCH0tJ3Y0grRYaGVfQuJndLc8ZcH7tZpfHph4iZfl-5VXiyvyezgVLnR3ejDW-ntEk3swhrmkxhgQJac.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ohc=tCC7VDcyb8EQ7kNvwEhp1Al&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc4MDMyMzc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=886c677dd2543d06&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzI2NDZENjRFNTdEOTNEMTJEQTNFN0IyQjk5MzQ4RjhDX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk_f3r27ChQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJ6S4Sm32M3iqvuXEMThsxVz6WuO0pOFJgUUHYNlw3jhA&amp;oe=6AB3A918</t>
+        </is>
+      </c>
+      <c r="O88" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P88" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q88" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89" ht="45" customHeight="1">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>fa7f931b516640b13199</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:22:52.176798+00:00</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T21:43:26+00:00</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr"/>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr"/>
+      <c r="H89" s="3" t="inlineStr"/>
+      <c r="I89" s="3" t="inlineStr"/>
+      <c r="J89" s="3" t="inlineStr"/>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasa.gov/careers/pathways</t>
+        </is>
+      </c>
+      <c r="L89" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
+          <t>@ nasa.gov
+Instagram
+Careers
+NASA Ai
+Pathways »
+We strategically hire our Pathways sis A
+based on long-term potentiat an d tla
+with NASA’s future ae
+Specializing in multi- semester experiences, 7”
+“eS
+the Pathways Internship Program prepares #4,
+you fo ireet
+&gt;»
+pipeli A
+upon
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/820024582_1427214422682532_7746524887128194269_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MTM1ODMwMDMyMjU1MTI4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=1FNCfaBcuoMQ7kNvwGtkIxA&amp;_nc_oc=AdooDeQ9mSMz4pkf3o6BsDkDHVtiORPrDs_QML9NaDUjAzJVLY1mH4mDrZo7E0phLmM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;oh=00_AQIn3V8_Gvd5Js9Ap3bPZmE2wAzRNVAh95VjeU0EJKGhJQ&amp;oe=6AB7A201
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/820024582_1427214422682532_7746524887128194269_n.jpg?stp=dst-jpg_e15_p320x320_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MTM1ODMwMDMyMjU1MTI4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=1FNCfaBcuoMQ7kNvwGtkIxA&amp;_nc_oc=AdooDeQ9mSMz4pkf3o6BsDkDHVtiORPrDs_QML9NaDUjAzJVLY1mH4mDrZo7E0phLmM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;oh=00_AQJclg3QGzIkfBQW1WbMbjV7BhGvkdQMgnNXXxwYnetbKQ&amp;oe=6AB7A201
+https://scontent-xxc1-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwFHhipe&amp;_nc_oc=AdrGD-HVTWaEVSMYt8qlE6H1GC_EDOv7RpmTuZ1UgSz3bdjJtskA7mY-eXGls3o01lk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQJpz9HTjGukImMahmzPq83_-qS-XVpNCz23mBbr82zg7g&amp;oe=6AB77E59
+https://l.instagram.com/?u=https%3A%2F%2Fwww.nasa.gov%2Fcareers%2Fpathways%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafuTS94obqcVJU94ysF6qne5c4YHm39iRCkgx0rKJjgORcSIOlw8OtkvpIbyQ_aem_hqmbyoE8WqgPiwdFl1Sskg%23Meet-Our-Interns&amp;e=AUDzEdbmR62vDHfD8Aeucc9aJc3pS3ibNejwPXKf9CVBkDYWTaV12IzZ29_yivIXWQLGVIe-bFwk87VziCYjKbeoS2O0yfxpl9mE_Q9grw
+https://scontent-xxc1-1.cdninstagram.com/o1/v/t2/f2/m78/AQPv_EXWFW3MQvre_k-WU2JTlEuD94QRt7u-PHUhmL1TWBur3YEKTjTZETyP8K9MSDYK8iYLM6kzGFZDM5Cex_u_NSxxs7P8oa2Ny1A.mp4?_nc_cat=104&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ohc=-CRHyjrY5jUQ7kNvwETpsl8&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc4MDY2MTg2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=53e69f7c2c1558ea&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0U2NEYwNkUyRUNBMkE2ODdFNTExMkRCOEYwNjM3NkIwX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk2q2E9bChQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJR2ry1Ky8ggNXsoSkGM765Zy2AEV8xiDKvXHRlSKbASQ&amp;oe=6AB3AB45</t>
+        </is>
+      </c>
+      <c r="O89" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P89" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q89" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90" ht="45" customHeight="1">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>46db7c825ed051a37069</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:22:54.948055+00:00</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T21:47:17+00:00</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr"/>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr"/>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr"/>
+      <c r="J90" s="3" t="inlineStr"/>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>http://prizepicks.com/position?gh_jid=7999266003</t>
+        </is>
+      </c>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
+          <t>&gt;a @ prizepicks.com C 7
+Instagram
+ PRIZEPICKS Get the app
+New
+Software
+Engineering
+Internship -
+summer 2027
+© Atlanta, Georgia, United States
+At PrizePicks, we stest-growing
+sports company in merica, as
+recognized by Inc. 5000. As the leading
+platform for Daily Fantasy Sports, we
+cover a diverse range of sports leagues,
+including the NFL, NBA, and Esports titles
+like League of Legends and Counter-Strike.
+Our team of over 550 employees thrives in
+an inclusive culture that values individuals
+from diverse backgrounds, regardless of
+their level of sports fandom. Ready to
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/815267795_1531727138724131_4665063462638759497_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MTM2MDIzOTc5MzkxNDk2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=lxYHfeRqVGgQ7kNvwFYJh1F&amp;_nc_oc=AdqRev7lE2aP0ln1y5VXSJjYgdgR4pSq_y6567__8bdYqN4nTFkFybcFEfiZCHnRH6M&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;oh=00_AQK8g6QIZgXFsZjC_bmEOrdEjixDZYG7xVWZcAC50KgiNg&amp;oe=6AB79A3A
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/815267795_1531727138724131_4665063462638759497_n.jpg?stp=dst-jpg_e15_p320x320_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MTM2MDIzOTc5MzkxNDk2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=lxYHfeRqVGgQ7kNvwFYJh1F&amp;_nc_oc=AdqRev7lE2aP0ln1y5VXSJjYgdgR4pSq_y6567__8bdYqN4nTFkFybcFEfiZCHnRH6M&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;oh=00_AQIj79LtM-nWoQK_bNCeaW4xpVf76kFKU_Neekp5r6lkSg&amp;oe=6AB79A3A
+https://scontent-xxc1-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwFHhipe&amp;_nc_oc=AdrGD-HVTWaEVSMYt8qlE6H1GC_EDOv7RpmTuZ1UgSz3bdjJtskA7mY-eXGls3o01lk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQJpz9HTjGukImMahmzPq83_-qS-XVpNCz23mBbr82zg7g&amp;oe=6AB77E59
+https://l.instagram.com/?u=http%3A%2F%2Fprizepicks.com%2Fposition%3Fgh_jid%3D7999266003%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeQcfiC2txb9-gnzvnB57FtYDkB3k1OViZlLUpjFWwr1xsS1mVmvfBV2lh6vQ_aem_phIAqzKOtkSv8X743DarEA&amp;e=AUAMEr8UFpaMG19S5z9LxWImuSNUS7awNUb6KGC8diWrfUC9btH6pAG4apdaO9BOosH9NBv4pNIZXGMG4ThN3bOkC_jDGZj205VWNiBLdQ
+https://scontent-xxc1-1.cdninstagram.com/o1/v/t2/f2/m78/AQNwescb6og5fTIqUFxOPNZBnpoHtJFRFaB-RwrYSduDdP8i6s76SsWePDqox1915OtELbRrLhgHEJh5fx0EjTT6liCSJB786Reh9uU.mp4?_nc_cat=107&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ohc=Kxm-jdn8gp4Q7kNvwEpLGMx&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc4MDcwMDI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=41f0dcdfdd8ffc9c&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzU1NEY1QjQ2Qzc2N0I5MEY3NDI1OTdCMjRCRDYyRkJBX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk2sjy97ChQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQL1qYV75bgHeSsgWrQnUCXvErqrAkWLj79jGH6zLzWAEw&amp;oe=6AB388C4</t>
+        </is>
+      </c>
+      <c r="O90" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P90" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q90" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91" ht="45" customHeight="1">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>ad427bec23de6bdc3029</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:23:01.326705+00:00</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T22:14:47+00:00</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Nvidia</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>Nvidia — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr"/>
+      <c r="J91" s="3" t="inlineStr"/>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>https://nvidia.wd5.myworkdayjobs.com/en-US/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Compiler-Engineer--Agentic-Compilation-Systems---New-College-Grad-2027_JR2026218</t>
+        </is>
+      </c>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
+          <t>x @ nvidia.wd5.myworkdayjobs.co... C:
+@QINvIDIA.
+uonme Be AE A
+Compiler Engineer, Agentic
+Compilation Systems - New
+College Grad 2027
+© US, CA, Santa Clara
+feo] Full time
+© Posted Today
+(2 NVIDIA NEW GRAD SWE 2027
+graphics, PC gaming lerated
+computing for more ars. It's a unique
+legacy of innovation t ed by great
+technology—and amazing people. Today, we're
+tapping into the unlimited potential of Al to
+define the next era of computing. An era in
+which our GPU acts as the brains of
+computers, robots, and self-driving cars that
+ean undarectand tha warld Daina what'e navar
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/819897636_1409276504717464_5748898734955374665_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MTM3NDA4MTczNTMyMjI0Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=P5CQU_UQbakQ7kNvwF_waRW&amp;_nc_oc=Adov20ovlBFGacs7c7vN7ORfMGM9ZhZ6awO5sn23HidglqBc7DGaAf_BDJ81gEO96eU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;oh=00_AQI-SrQxdzkxBW31sAUowZ6HtnSJGQd6jWYVUjKY_jljuA&amp;oe=6AB783BF
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/819897636_1409276504717464_5748898734955374665_n.jpg?stp=dst-jpg_e15_p320x320_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MTM3NDA4MTczNTMyMjI0Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=P5CQU_UQbakQ7kNvwF_waRW&amp;_nc_oc=Adov20ovlBFGacs7c7vN7ORfMGM9ZhZ6awO5sn23HidglqBc7DGaAf_BDJ81gEO96eU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;oh=00_AQKyp9gvod05xNXNFng82SyAByMnYcNYUloQwd716CTKOA&amp;oe=6AB783BF
+https://scontent-xxc1-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwFHhipe&amp;_nc_oc=AdrGD-HVTWaEVSMYt8qlE6H1GC_EDOv7RpmTuZ1UgSz3bdjJtskA7mY-eXGls3o01lk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQJpz9HTjGukImMahmzPq83_-qS-XVpNCz23mBbr82zg7g&amp;oe=6AB77E59
+https://l.instagram.com/?u=https%3A%2F%2Fnvidia.wd5.myworkdayjobs.com%2Fen-US%2FNVIDIAExternalCareerSite%2Fjob%2FUS-CA-Santa-Clara%2FCompiler-Engineer--Agentic-Compilation-Systems---New-College-Grad-2027_JR2026218%3Futm_id%3D97760_v0_s00_e0_tv4%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadlZeQQdX8RG_gltci0N4cdcD4JzMSR0-AGAqlu358ilfaBZvf5auUO9wciBA_aem_9eXZ6Npllldda7zzbDfT-g&amp;e=AUD8ft2cyaJlZ1OYybgEk12fSn7Qd_NF4ZC4PL9L2k3l9PfqDXrmPGgNdFZAbiLpvorZLRFDOKFg9gwfSsGTrUiiV2o5JqKh3dSDN5fM9A
+https://scontent-xxc1-1.cdninstagram.com/o1/v/t2/f2/m78/AQPLQLXdxbQBzonjVfzjVCcq33pr3SySq9Hpe1mRLo37j6phJmwvzZGwliXRJW2JjIW73FDJu-J_3aNLbnx8SD4J5sFrq9zQ7iqA8KM.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ohc=y3RjulWsshgQ7kNvwGEAwzg&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc4MTAzNTA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDgyNiwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=d5b6cefbf2732860&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzkzNDlEQUUwOUVCMzI5MjBEMDEyNDZFMzg2NTEyRjkzX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkjrzrkLGhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZZSpAQA&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJNepFkTtTzoohqGTItfTuEUWUchhmiEqtldKmliGEYPA&amp;oe=6AB38794</t>
+        </is>
+      </c>
+      <c r="O91" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P91" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q91" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92" ht="45" customHeight="1">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>0e98c318f4a7e1a7972b</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:23:11.507015+00:00</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T22:36:27+00:00</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>Adobe — Product Management, Design</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>Product Management, Design</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr"/>
+      <c r="J92" s="3" t="inlineStr"/>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>https://form.typeform.com/to/supY07n5</t>
+        </is>
+      </c>
+      <c r="L92" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
+          <t>BLUOAL SHULER! LUMIUrEET
+From Designer to Design Leader
+Lessons on building your craft, finding your voice,
+and growing your impact
+Stephanie Mencarelli
+Vice President of Design
+Tuesday, Sept. 29, 2026
+3 PM PST - 6 PM EST
+Adobe Student Career Talks:
+Stephanie Mencarelli
+RSVP for a career chat and Q&amp;A with
+Stephanie, Adobe's VP of Design, on
+breaking into product design, building
+your craft, and growing your impact
+early in your career.
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/819741842_1306724858136052_4685864180935271903_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MTM4NDk3OTgwMzc5NzA1MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=v2AUV9JcNfUQ7kNvwEmF_gT&amp;_nc_oc=AdpSV1eu4PP-6wLkSd6c6YKkQtrHm7Reh24n9BHRhcW6OIYk_quZPR_MsWLdIqCAdoY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;oh=00_AQK9eV7hchy0f5Qge-ZHNZl277HC8J76Mx1IRKyI45RqyQ&amp;oe=6AB7A987
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/819741842_1306724858136052_4685864180935271903_n.jpg?stp=dst-jpg_e15_p320x320_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MTM4NDk3OTgwMzc5NzA1MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=v2AUV9JcNfUQ7kNvwEmF_gT&amp;_nc_oc=AdpSV1eu4PP-6wLkSd6c6YKkQtrHm7Reh24n9BHRhcW6OIYk_quZPR_MsWLdIqCAdoY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;oh=00_AQLT_rmRToHNmdfJmbi1uuM2fDNONO7RzfiHlH5x0o50Hg&amp;oe=6AB7A987
+https://scontent-xxc1-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwFHhipe&amp;_nc_oc=AdrGD-HVTWaEVSMYt8qlE6H1GC_EDOv7RpmTuZ1UgSz3bdjJtskA7mY-eXGls3o01lk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQJpz9HTjGukImMahmzPq83_-qS-XVpNCz23mBbr82zg7g&amp;oe=6AB77E59
+https://l.instagram.com/?u=https%3A%2F%2Fform.typeform.com%2Fto%2FsupY07n5%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacsqIlQv3YkUDfz1KnfHZuQVez3POVDyKq5OCCdfZGlS3j4Ins62CcuwzOXbg_aem_ReS0eeJ--My4Wne8SkS78w&amp;e=AUD26Y05H-wdjajrUjWeQOiCb8SGR1_44N19Pw9hSqJD2V_H5glTbeZA4FRSL-JA3b81WF5MfgySPfZh6qKvlXeSF6Ki_iZn4dS9rvdEQw
+https://scontent-xxc1-1.cdninstagram.com/o1/v/t2/f2/m78/AQOoQYAhTyyXFd60k7t8HkL87FkxbQjWBHCjPqQOdvP7e5PVVc4GjsGmpgOLzKoKbhSBWYVJNKXD0SpX6OxnVrycaZb9cNST76tYRkM.mp4?_nc_cat=104&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ohc=71TSGEZs1lEQ7kNvwHebtT1&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc4MTIxNjg2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=f33f781b26b60d6d&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzgxNEJDQTdFNUUzMkUwQkIyQTYzQzg1Njc5NkQ3Q0FBX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk-J-xnrGhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJnssSEu7KOaYql1nTCiBzX70T8IlqhzepX8_hBsWWWag&amp;oe=6AB38589</t>
+        </is>
+      </c>
+      <c r="O92" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P92" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q92" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93" ht="45" customHeight="1">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>bb22c3de34087c521f91</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:23:13.366788+00:00</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:10:22+00:00</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>Headlandstechnologiesllc</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>Headlandstechnologiesllc — Internship</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr"/>
+      <c r="H93" s="3" t="inlineStr"/>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>New York, Chicago, Remote</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr"/>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/headlandstechnologiesllc/jobs/4412947009</t>
+        </is>
+      </c>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
+          <t>Headland
+&lt; Back to jobs
+New:
+Deep Learning
+Research Internship
+©) Chicago; New York
+(Z) JOB-BOARDS.GREENHOUSE.IO
+Deep Learning -\ —
+Job Description: RSI i MERE wai
+e Hours: 20 per week
+¢ Compensations: $100/hour
+e Benefits: N/A
+e Duration: 4 months, with renewal
+option
+e Location: Remote
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/820017007_1101814572352243_3289145108050287269_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5MTQwMjA1MzQ3MjcxNDE5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=j-LAqk73MPgQ7kNvwENkZ_f&amp;_nc_oc=AdqVecjrwgCj-wlhqvg7u47GQn4aiAGn1isShrnngl9L7Iutyshh6iCcZHcFbzcSGwA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;oh=00_AQK87fbQSi6LewZyjk6Qev9ZW5uJrIrAdcjoSAIFoJF5gw&amp;oe=6AB784C0
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/820017007_1101814572352243_3289145108050287269_n.jpg?stp=dst-jpg_e15_p320x320_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5MTQwMjA1MzQ3MjcxNDE5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=j-LAqk73MPgQ7kNvwENkZ_f&amp;_nc_oc=AdqVecjrwgCj-wlhqvg7u47GQn4aiAGn1isShrnngl9L7Iutyshh6iCcZHcFbzcSGwA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;oh=00_AQJY_TwjtH0NqlLh2X-sEEGHmWkvZ0Gjxyvnbi-RxH3sqA&amp;oe=6AB784C0
+https://scontent-xxc1-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwFHhipe&amp;_nc_oc=AdrGD-HVTWaEVSMYt8qlE6H1GC_EDOv7RpmTuZ1UgSz3bdjJtskA7mY-eXGls3o01lk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQJpz9HTjGukImMahmzPq83_-qS-XVpNCz23mBbr82zg7g&amp;oe=6AB77E59
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fheadlandstechnologiesllc%2Fjobs%2F4412947009%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAad6cJvEkybVh5eQvLVduq9JrMTOw8bkjgUNRatgIqFW5dLLue5-GQMFDmESrg_aem_fi1kDFO3eDD-XPWFw10Ldw&amp;e=AUCUG9rAg3AW2g4B4aK-lZXZafgWvqmP6YgJdgiG79x-c4i_3n9uMhITXel5VhdPkkABM7Z8WPPfxod1HscgQUl3hZ8L2nBeUBVBtYn8vQ
+https://scontent-xxc1-1.cdninstagram.com/o1/v/t2/f2/m78/AQPih7yCxHIpI9_EqhWnNJ5kke5yZwKCQfGWeRhHDCm6MU5U99lS9f0R8AVHFH9EzZ33b9KxJRO81-B-LPVOlswa85zlbyIO0_dyaCw.mp4?_nc_cat=104&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ohc=iurIKKDFaggQ7kNvwHVuBlT&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc4MTQ5Mzc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=ee645ef5b07e6a3b&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzlDNDA2RTRGNTUxMDU5QkQyQUYyQjE0QTc5MTAyQjg5X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk0fyBs7GhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLvos-8kcm7Xy7vTFR3BHMeNFUj6w4beTfOewz7UxOegA&amp;oe=6AB3A589</t>
+        </is>
+      </c>
+      <c r="O93" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P93" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q93" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94" ht="45" customHeight="1">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>5da4125222dc684116d6</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:23:15.820738+00:00</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:11:10+00:00</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Assuredguaranty</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>Assuredguaranty — Business / Operations</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>Business / Operations</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr"/>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/assuredguaranty/jobs/8827458002</t>
+        </is>
+      </c>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
+          <t>New
+Product Software
+Developer — Back-End -
+Summer 2027
+© New York, NY, United States
+‘(D JOB-BOARDS.GREENHOUSE.IO
+Position Summary dry
+Assured Guaranty is seeking to hire a Product
+Software Developer to join our Secondary
+Market team. As a member of our group, you
+will work closely with business analysts,
+product owners, and other engineers to build
+back-ends for advanced products powered by
+data, Al or advanced analytics that will scale
+our Secondary Market business operations.
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/805485919_1717351839366664_6173610087944355422_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MTQwMjQ2ODM1NjUxNzIzNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Ms51nZvFXMEQ7kNvwGyt2L4&amp;_nc_oc=AdoxIQ_WN4VwYEVw4QfV0UJ3b1lHZw1EvGAhHC6Qb1d3ULqC6Td6sGUzKV0DdGEaC6Y&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;oh=00_AQJU4Qlm4-hvOJhd7xkR6aGs90X4A2QnVxU4gaPID20lGw&amp;oe=6AB778D0
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/805485919_1717351839366664_6173610087944355422_n.jpg?stp=dst-jpg_e15_p320x320_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MTQwMjQ2ODM1NjUxNzIzNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Ms51nZvFXMEQ7kNvwGyt2L4&amp;_nc_oc=AdoxIQ_WN4VwYEVw4QfV0UJ3b1lHZw1EvGAhHC6Qb1d3ULqC6Td6sGUzKV0DdGEaC6Y&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;oh=00_AQIZdOs215jooZSV3ZpGviIlKhaKeAjM6LPEvWErLO9KiA&amp;oe=6AB778D0
+https://scontent-xxc1-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwFHhipe&amp;_nc_oc=AdrGD-HVTWaEVSMYt8qlE6H1GC_EDOv7RpmTuZ1UgSz3bdjJtskA7mY-eXGls3o01lk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQJpz9HTjGukImMahmzPq83_-qS-XVpNCz23mBbr82zg7g&amp;oe=6AB77E59
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fassuredguaranty%2Fjobs%2F8827458002%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaesQCCiJ4nP4yTqVDgUrMQ_9clRHhzqwOWdhTs8i5tryXVxhbrY6X3N_GtMRA_aem_TAZ6SqUTUv0zakiBAi3W5w&amp;e=AUCZ-I6c_TVCmcbQV4e0-PlnYo_XLf58mPfQP-mgLw1rbXzr0SgdisZQTj44_QrKK6NAKyQxi_HLxqmz8bHWvsfEmcdZakzE7nCxIUTJvQ
+https://scontent-xxc1-1.cdninstagram.com/o1/v/t2/f2/m78/AQNw339EajF-nANYw-E47h1wbIcxD2Bd64H_OMZfvpdVlsqSJGKyoPLWsxVnkVMUpaj70PYqdlaxgFJ11Lh6pJOJXItbk4L2C3SKNd8.mp4?_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ohc=uF68WuKYRJ4Q7kNvwE4hfR7&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc4MTUxNjI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=32d657fbb8d93b2f&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzYxNEY2RDRCOEYyN0REQzM4NDZCRUYyOEIzNzUwRUE2X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkusbYtLGhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKz0DOW4rpS92H4oA9k8AsdoD9kwmeUrx5RSbrNqmrSDQ&amp;oe=6AB3B4F1</t>
+        </is>
+      </c>
+      <c r="O94" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P94" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q94" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R94" s="3" t="inlineStr"/>
+    </row>
+    <row r="95" ht="45" customHeight="1">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>d4cb03d405f3af42b507</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:23:17.547397+00:00</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr"/>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>Data Science Intern</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr"/>
+      <c r="I95" s="3" t="inlineStr"/>
+      <c r="J95" s="3" t="inlineStr"/>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>https://epicgames.com/careers/jobs/6202675004?gh_jid=6202675004</t>
+        </is>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
+          <t>EY -
+Data Science Intern
+(R27453)
+Department
+Data &amp; Analytics
+Location
+Cary, United States
+Product
+Epic Online Services
+Companv
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/797784046_1629981315583364_2540099663089796223_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5MTQwMjk2MDk4NTg3NTgyNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=qZh8WpXq-fYQ7kNvwFJdOFR&amp;_nc_oc=AdqrJG_a7y6WEXO97tqsk6mzQRRVGKTz3hCjiR_tZr2HgO_EZY7BUVDopFLcN3gNuEo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;oh=00_AQJxaK7zMAlLaJfB_xh7sAb043nEr0bD2scCcRe368ok7Q&amp;oe=6AB78ADF
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/797784046_1629981315583364_2540099663089796223_n.jpg?stp=dst-jpg_e15_p320x320_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5MTQwMjk2MDk4NTg3NTgyNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=qZh8WpXq-fYQ7kNvwFJdOFR&amp;_nc_oc=AdqrJG_a7y6WEXO97tqsk6mzQRRVGKTz3hCjiR_tZr2HgO_EZY7BUVDopFLcN3gNuEo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;oh=00_AQLfh8flMJk5SzUZyEKSLMUDaPp9egeA1rcuPEeVnbw8Fw&amp;oe=6AB78ADF
+https://scontent-xxc1-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwFHhipe&amp;_nc_oc=AdrGD-HVTWaEVSMYt8qlE6H1GC_EDOv7RpmTuZ1UgSz3bdjJtskA7mY-eXGls3o01lk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQJpz9HTjGukImMahmzPq83_-qS-XVpNCz23mBbr82zg7g&amp;oe=6AB77E59
+https://l.instagram.com/?u=https%3A%2F%2Fepicgames.com%2Fcareers%2Fjobs%2F6202675004%3Fgh_jid%3D6202675004%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaf5QI4-HAgCi9KqButeTJ53-ho1kAopS15KpPCBysC5B0QRVJUhPdTueJ9Fbw_aem_zEH9l_WeUxI9wEuzc0aY5Q&amp;e=AUB0INAg6HFMnn01_rAJBodM6uMBq4rwzLj00F-pD9lQo6SOtI1rL3PX5GEcB4A0vO4BpkD7q_2fQ4RV7UoBi6taQFDgSLMzq1jeAl3QFQ
+https://scontent-xxc1-1.cdninstagram.com/o1/v/t2/f2/m78/AQPexTfIvMX9V-7EGUt52Lko_j_ffGyKz-AXsooU8P_jpgRGEkgWYbL6L0C5bqrAljvc3WJrdPyJcC1lyV0pBNAnXdISP424LISves4.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ohc=c6Vbbi-dHJsQ7kNvwGK5dV8&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc4MTUzODc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=9d9dc81cd317d5ac&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0E3NDRFRTBBNTkxMkQxMjkwMUY4MDVBNjI1QUYxQTg3X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbko5CvtrGhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=tG26L-MlyQTaTwmsqhbDEQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIMk0ph_0lVst1hnxlw4GP7_l09MLeSE_AH4ilog5NbDA&amp;oe=6AB39D36</t>
+        </is>
+      </c>
+      <c r="O95" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P95" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q95" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R95" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R85"/>
+  <autoFilter ref="A1:R95"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -8645,6 +9575,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L84" r:id="rId153"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K87" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L87" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K88" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L90" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId175"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R95"/>
+  <dimension ref="A1:R97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8490,7 +8490,7 @@
     <row r="86" ht="45" customHeight="1">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>c286a1ff663e9adc9c7f</t>
+          <t>a16243e04ea0f7cc979e</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -8518,14 +8518,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G86" s="3" t="inlineStr"/>
-      <c r="H86" s="3" t="inlineStr"/>
+      <c r="G86" s="3" t="n"/>
+      <c r="H86" s="3" t="n"/>
       <c r="I86" s="3" t="inlineStr">
         <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="J86" s="3" t="inlineStr"/>
+      <c r="J86" s="3" t="n"/>
       <c r="K86" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/genevatrading/jobs/5242063007?gh_src=7bx7tr8c7us&amp;t=3253f722teu</t>
@@ -8568,12 +8568,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R86" s="3" t="inlineStr"/>
+      <c r="R86" s="3" t="n"/>
     </row>
     <row r="87" ht="45" customHeight="1">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>e8e1bfd1ad020db4c422</t>
+          <t>2e1086eaac973cd289de</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -8586,7 +8586,7 @@
           <t>2026-09-21T20:29:56+00:00</t>
         </is>
       </c>
-      <c r="D87" s="3" t="inlineStr"/>
+      <c r="D87" s="3" t="n"/>
       <c r="E87" s="3" t="inlineStr">
         <is>
           <t>Scientific Join Talent Network English v</t>
@@ -8602,13 +8602,13 @@
           <t>Data Science</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr"/>
+      <c r="H87" s="3" t="n"/>
       <c r="I87" s="3" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="J87" s="3" t="inlineStr"/>
+      <c r="J87" s="3" t="n"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
           <t>https://bostonscientific.eightfold.ai/careers/job/563602813600504?domain=bostonscientific.com</t>
@@ -8658,12 +8658,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R87" s="3" t="inlineStr"/>
+      <c r="R87" s="3" t="n"/>
     </row>
     <row r="88" ht="45" customHeight="1">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>d1345eb46d9d3f00a185</t>
+          <t>2618faf7cb4f5993418c</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -8676,7 +8676,7 @@
           <t>2026-09-21T21:04:53+00:00</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr"/>
+      <c r="D88" s="3" t="n"/>
       <c r="E88" s="3" t="inlineStr">
         <is>
           <t>Join us for an informative session</t>
@@ -8692,9 +8692,9 @@
           <t>Product Management</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr"/>
-      <c r="I88" s="3" t="inlineStr"/>
-      <c r="J88" s="3" t="inlineStr"/>
+      <c r="H88" s="3" t="n"/>
+      <c r="I88" s="3" t="n"/>
+      <c r="J88" s="3" t="n"/>
       <c r="K88" s="4" t="inlineStr">
         <is>
           <t>https://capitalone.eightfold.ai/events/candidate?plannedEventId=EPYJ0oNW</t>
@@ -8746,12 +8746,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R88" s="3" t="inlineStr"/>
+      <c r="R88" s="3" t="n"/>
     </row>
     <row r="89" ht="45" customHeight="1">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>fa7f931b516640b13199</t>
+          <t>bdf8b469edcec677a0c6</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -8764,7 +8764,7 @@
           <t>2026-09-21T21:43:26+00:00</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr"/>
+      <c r="D89" s="3" t="n"/>
       <c r="E89" s="3" t="inlineStr">
         <is>
           <t>Internship</t>
@@ -8775,10 +8775,10 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G89" s="3" t="inlineStr"/>
-      <c r="H89" s="3" t="inlineStr"/>
-      <c r="I89" s="3" t="inlineStr"/>
-      <c r="J89" s="3" t="inlineStr"/>
+      <c r="G89" s="3" t="n"/>
+      <c r="H89" s="3" t="n"/>
+      <c r="I89" s="3" t="n"/>
+      <c r="J89" s="3" t="n"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
           <t>https://www.nasa.gov/careers/pathways</t>
@@ -8833,12 +8833,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R89" s="3" t="inlineStr"/>
+      <c r="R89" s="3" t="n"/>
     </row>
     <row r="90" ht="45" customHeight="1">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>46db7c825ed051a37069</t>
+          <t>3f5444a794b2b7a53df0</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -8851,7 +8851,7 @@
           <t>2026-09-21T21:47:17+00:00</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr"/>
+      <c r="D90" s="3" t="n"/>
       <c r="E90" s="3" t="inlineStr">
         <is>
           <t>Internship</t>
@@ -8862,14 +8862,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G90" s="3" t="inlineStr"/>
+      <c r="G90" s="3" t="n"/>
       <c r="H90" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I90" s="3" t="inlineStr"/>
-      <c r="J90" s="3" t="inlineStr"/>
+      <c r="I90" s="3" t="n"/>
+      <c r="J90" s="3" t="n"/>
       <c r="K90" s="4" t="inlineStr">
         <is>
           <t>http://prizepicks.com/position?gh_jid=7999266003</t>
@@ -8929,12 +8929,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R90" s="3" t="inlineStr"/>
+      <c r="R90" s="3" t="n"/>
     </row>
     <row r="91" ht="45" customHeight="1">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>ad427bec23de6bdc3029</t>
+          <t>995d56e92f62655f288e</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -8972,8 +8972,8 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="I91" s="3" t="inlineStr"/>
-      <c r="J91" s="3" t="inlineStr"/>
+      <c r="I91" s="3" t="n"/>
+      <c r="J91" s="3" t="n"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
           <t>https://nvidia.wd5.myworkdayjobs.com/en-US/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Compiler-Engineer--Agentic-Compilation-Systems---New-College-Grad-2027_JR2026218</t>
@@ -9032,12 +9032,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R91" s="3" t="inlineStr"/>
+      <c r="R91" s="3" t="n"/>
     </row>
     <row r="92" ht="45" customHeight="1">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>0e98c318f4a7e1a7972b</t>
+          <t>37515b8309e6727dbba0</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -9075,8 +9075,8 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="I92" s="3" t="inlineStr"/>
-      <c r="J92" s="3" t="inlineStr"/>
+      <c r="I92" s="3" t="n"/>
+      <c r="J92" s="3" t="n"/>
       <c r="K92" s="4" t="inlineStr">
         <is>
           <t>https://form.typeform.com/to/supY07n5</t>
@@ -9131,12 +9131,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R92" s="3" t="inlineStr"/>
+      <c r="R92" s="3" t="n"/>
     </row>
     <row r="93" ht="45" customHeight="1">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>bb22c3de34087c521f91</t>
+          <t>9b78c1313d7641eb7f8d</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -9164,14 +9164,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G93" s="3" t="inlineStr"/>
-      <c r="H93" s="3" t="inlineStr"/>
+      <c r="G93" s="3" t="n"/>
+      <c r="H93" s="3" t="n"/>
       <c r="I93" s="3" t="inlineStr">
         <is>
           <t>New York, Chicago, Remote</t>
         </is>
       </c>
-      <c r="J93" s="3" t="inlineStr"/>
+      <c r="J93" s="3" t="n"/>
       <c r="K93" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/headlandstechnologiesllc/jobs/4412947009</t>
@@ -9226,12 +9226,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R93" s="3" t="inlineStr"/>
+      <c r="R93" s="3" t="n"/>
     </row>
     <row r="94" ht="45" customHeight="1">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>5da4125222dc684116d6</t>
+          <t>21504f821f1eee5cdcd5</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -9274,7 +9274,7 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="J94" s="3" t="inlineStr"/>
+      <c r="J94" s="3" t="n"/>
       <c r="K94" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/assuredguaranty/jobs/8827458002</t>
@@ -9329,12 +9329,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R94" s="3" t="inlineStr"/>
+      <c r="R94" s="3" t="n"/>
     </row>
     <row r="95" ht="45" customHeight="1">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>d4cb03d405f3af42b507</t>
+          <t>1027cb3d64fcacbe2519</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -9347,7 +9347,7 @@
           <t>2026-09-21T23:12:09+00:00</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr"/>
+      <c r="D95" s="3" t="n"/>
       <c r="E95" s="3" t="inlineStr">
         <is>
           <t>Data Science Intern</t>
@@ -9363,9 +9363,9 @@
           <t>Data Science</t>
         </is>
       </c>
-      <c r="H95" s="3" t="inlineStr"/>
-      <c r="I95" s="3" t="inlineStr"/>
-      <c r="J95" s="3" t="inlineStr"/>
+      <c r="H95" s="3" t="n"/>
+      <c r="I95" s="3" t="n"/>
+      <c r="J95" s="3" t="n"/>
       <c r="K95" s="4" t="inlineStr">
         <is>
           <t>https://epicgames.com/careers/jobs/6202675004?gh_jid=6202675004</t>
@@ -9415,10 +9415,211 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R95" s="3" t="inlineStr"/>
+      <c r="R95" s="3" t="n"/>
+    </row>
+    <row r="96" ht="45" customHeight="1">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>876735cc0f6788bc05a8</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T05:07:44.835748+00:00</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T20:31:14+00:00</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Genevatrading</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>Genevatrading — Internship</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr"/>
+      <c r="H96" s="3" t="inlineStr"/>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr"/>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/genevatrading/jobs/5240107007</t>
+        </is>
+      </c>
+      <c r="L96" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
+          <t>@ job-boards.greenhouse.io G
+GENEVA-TRADING-CAREERS:
+&lt; Back to jobs
+New
+Al Engineer Internship
+- Summer 202/
+© Chicago Office
+Founded in 1999, Trading isa
+premier global prin trading firm
+with strategically located offices in
+Chicago, Dublin, and London. Our
+relentless focus on trading excellence
+combined with technological
+innovation has equipped us witha
+best-in-class proprietary trading
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/820047577_1099887412396204_1018735392579206909_n.jpg?stp=dst-jpg_e15_p480x480_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MTMyMTk2MjM5MTA2MDM0NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=NSP_ZIi3yakQ7kNvwFpxRN-&amp;_nc_oc=AdotQezOw5ZJCXWm3hwN5sCy3alm4GQK_yMH8E9UK8SMdfMdLb7o1KKrWOqVL-WisWA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=md5Q3Dr-jMEUJnELosuyRQ&amp;_nc_ss=7e3ba&amp;oh=00_AQI2tphHvZfZynP0cdQj3Gkm1CTbaKizJ3VEKtTIcvU-RA&amp;oe=6AB7FA2D
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/820047577_1099887412396204_1018735392579206909_n.jpg?stp=dst-jpg_e15_p160x160_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MTMyMTk2MjM5MTA2MDM0NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=NSP_ZIi3yakQ7kNvwFpxRN-&amp;_nc_oc=AdotQezOw5ZJCXWm3hwN5sCy3alm4GQK_yMH8E9UK8SMdfMdLb7o1KKrWOqVL-WisWA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=md5Q3Dr-jMEUJnELosuyRQ&amp;_nc_ss=7e3ba&amp;oh=00_AQKe8gC_O5CXc-_YbQz7cvUillMLSPpSbRskNSDKXmQivQ&amp;oe=6AB7FA2D
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwF-VKwY&amp;_nc_oc=AdpDJmrBQvx3kPysJ4B_CVYLzhS48ZL4hwxJhbIqpV_kHOa6nOQJ4QhuJ88S_Iaxmgw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKZB5jN9oD-nNu-Dvp2KCgEQWiyxWWW4_tr-fpoaVyOAQ&amp;oe=6AB7EED9
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fgenevatrading%2Fjobs%2F5240107007%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadvImimjevixXyaQfBL8KxxFFai2BkOM91zh7UPBRuQcHR4cAo2GfWyYcv59A_aem_xXsIpf0e6EycjGLc9dtaew&amp;e=AUAlfPugS0bc6pqUdGjRYSxBO8d1-souA_-ZopuWeAY-5KY_zsGZ-16jKOK9FW49wAcHPCJuxSPXR-fbU8kZmQgVFIEG27bSGyjdItdkfw
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQOX_-hqzvhiWqcw5y0XUYvmBnypdogpPw3wlTJn0u0S91wOb5PP_dEHJAlnO8iJzPWrUmLAU41RzUWHGRgzk9CGeUgrzFc9f3vqopU.mp4?_nc_cat=110&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=pNP-YNV3bqsQ7kNvwH4mCTk&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc4MDA1NTI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=55bd3c22d204d7ea&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzI1NDg5QTk3QUNCNEVGQ0JBQjI3RjQyQjQ1NDU4Qjk1X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkmK_rx7ChQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=md5Q3Dr-jMEUJnELosuyRQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLFeHgB64_so8rZuwBclW5TLrETKTkr-Bmy7SbZ4OGvMw&amp;oe=6AB4003F</t>
+        </is>
+      </c>
+      <c r="O96" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P96" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q96" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97" ht="45" customHeight="1">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>7ba23b888fa571365000</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T05:08:23.182193+00:00</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:25:38+00:00</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>Google — Product Management</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>Spring 2027</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr"/>
+      <c r="K97" s="4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/about/careers/applications/jobs/results/107272685397910214-associate-product-manager-university-graduate-2027-start</t>
+        </is>
+      </c>
+      <c r="L97" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N97" s="3">
+        <f> Google Careers OSH: ©
+€ Back to jobs search
+Associate Product
+Manager, University
+Graduate, 2027 Start
+=e) Google © Mountain View, CA, USA; +3 more
+il, Early
+: =
+Google APM opens tomorrow and we'll be
+posting it first bc of our community A,
+SEWEM LAM Google posting is LIVE:
+VAWWA em delineate) associate product manager
+application *b university graduate 2027 start
+October 6, 20 |
+you in advanc
+our team revig
+applicants wil
+Spring 2027
+een
+https://scontent-lax7-1.cdninstagram.com/v/t51.71878-15/809209234_28166127426401533_5923146350242077187_n.jpg?stp=dst-jpg_e15_p480x480_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MTQwOTc0MTM5NzA1MTU1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Ff_f_cODUw4Q7kNvwE-PjnT&amp;_nc_oc=AdqgVMFyYtVxAXPZmOSLcRFBLOfm0gHU7Q7P69Pb0Tcp0sfOPcQ81-Ef8MhAjTnEwsE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_gid=md5Q3Dr-jMEUJnELosuyRQ&amp;_nc_ss=7e3ba&amp;oh=00_AQJyWVNXfx-3vDAVf0M5jztU7xVJ89D04yrCYh0S_Zj9sg&amp;oe=6AB7D136
+https://scontent-lax7-1.cdninstagram.com/v/t51.71878-15/809209234_28166127426401533_5923146350242077187_n.jpg?stp=dst-jpg_e15_p160x160_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MTQwOTc0MTM5NzA1MTU1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Ff_f_cODUw4Q7kNvwE-PjnT&amp;_nc_oc=AdqgVMFyYtVxAXPZmOSLcRFBLOfm0gHU7Q7P69Pb0Tcp0sfOPcQ81-Ef8MhAjTnEwsE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_gid=md5Q3Dr-jMEUJnELosuyRQ&amp;_nc_ss=7e3ba&amp;oh=00_AQLnAF0GeFFf1LgLWHJnu5vN0MnBmjx5rfg7ihyi4k2cqw&amp;oe=6AB7D136
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwF-VKwY&amp;_nc_oc=AdpDJmrBQvx3kPysJ4B_CVYLzhS48ZL4hwxJhbIqpV_kHOa6nOQJ4QhuJ88S_Iaxmgw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKZB5jN9oD-nNu-Dvp2KCgEQWiyxWWW4_tr-fpoaVyOAQ&amp;oe=6AB7EED9
+https://l.instagram.com/?u=https%3A%2F%2Fwww.google.com%2Fabout%2Fcareers%2Fapplications%2Fjobs%2Fresults%2F107272685397910214-associate-product-manager-university-graduate-2027-start%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeb70M3og2lAENFjaN2gFN7NbJTiaOQhwsaGuvQgWJaC3zTdEbHyf3xQce-1g_aem_tUDx6YIFsbeCuL1vJBI95Q&amp;e=AUD5FXqj1uvxwGehF2IjW_fkge8LzN1AbWQE6YmLD1WrqM7OvRdaEj3sKWUyTwXZ1Kez4bDhtfTkyJLeus-TizKvGPUJ762Aqtavs10KXg
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQMJW_ngz-gzGap_vDA33_Kp9r6DhN0IRpL2wJO7eFKXKdcbFtXFITx1L5a0CmzXauor7qCuvQPkPuW6ks5Fe4HidSRBHa-PvyJ-l-c.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=sQPXBpZbcygQ7kNvwEBIMql&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc4MTYyMDk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=13a81b3f00beba2c&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzYzNENDQUZEMzI4MDE2NEU5QzY1RTQyOTAyMjhFMzg2X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkiYa_vLGhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=md5Q3Dr-jMEUJnELosuyRQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJx68l6BAXUWyLqvVQRKSRFcjfKw3dLCD0k8BLOCOWx3Q&amp;oe=6AB3F02A</f>
+        <v/>
+      </c>
+      <c r="O97" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P97" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q97" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R97" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R95"/>
+  <autoFilter ref="A1:R97"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -9595,6 +9796,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId173"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K96" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId179"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -9420,7 +9420,7 @@
     <row r="96" ht="45" customHeight="1">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>876735cc0f6788bc05a8</t>
+          <t>ee4036ed3b40ef6edd84</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -9448,14 +9448,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G96" s="3" t="inlineStr"/>
-      <c r="H96" s="3" t="inlineStr"/>
+      <c r="G96" s="3" t="n"/>
+      <c r="H96" s="3" t="n"/>
       <c r="I96" s="3" t="inlineStr">
         <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="J96" s="3" t="inlineStr"/>
+      <c r="J96" s="3" t="n"/>
       <c r="K96" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/genevatrading/jobs/5240107007</t>
@@ -9510,12 +9510,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R96" s="3" t="inlineStr"/>
+      <c r="R96" s="3" t="n"/>
     </row>
     <row r="97" ht="45" customHeight="1">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>7ba23b888fa571365000</t>
+          <t>2e97106f27de282461f6</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -9558,7 +9558,7 @@
           <t>Mountain View</t>
         </is>
       </c>
-      <c r="J97" s="3" t="inlineStr"/>
+      <c r="J97" s="3" t="n"/>
       <c r="K97" s="4" t="inlineStr">
         <is>
           <t>https://www.google.com/about/careers/applications/jobs/results/107272685397910214-associate-product-manager-university-graduate-2027-start</t>
@@ -9616,7 +9616,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R97" s="3" t="inlineStr"/>
+      <c r="R97" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:R97"/>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$106</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R97"/>
+  <dimension ref="A1:R106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9618,8 +9618,862 @@
       </c>
       <c r="R97" s="3" t="n"/>
     </row>
+    <row r="98" ht="45" customHeight="1">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>6ec85af72f29bd8bdf0a</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:01:48.349307+00:00</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T13:19:44+00:00</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>Google — Product Management</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr"/>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/about/careers/applications/jobs/results/134770032394543814-associate-product-manager-intern-summer-2027</t>
+        </is>
+      </c>
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N98" s="3">
+        <f> Google Careers ¢ OE
+€ Back to jobs search
+Associate Product
+Manager Intern, Summer
+2027
+EE] Google © Mountain View, CA, USA; +3 more
+a], Intern &amp; Apprentice
+Apply ee 6
+@ GOOGLE APM INTERN!
+(i) Parucipation int
+requires that you
+intended for studen Oo are entering
+their penultimate year of a degree
+program in Product Management,
+Computer Science, or a related field.
+This role will begin accepting applications
+on September 22, 2026. Please complete
+your application by October 6, 2026.
+https://scontent-lga3-1.cdninstagram.com/v/t51.71878-15/820251134_1086906984191583_6413718859244956689_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MTgyOTU2MzgzMDE3Mzk2OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Qrk39xfOTfoQ7kNvwHmug69&amp;_nc_oc=AdprXi8DA6SmJQ4onO1_2f7_W91KYjPFKFbIarIfyKZ2eERvH-At74bRw-oHr-KUmok&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;oh=00_AQIhO6OM8MDGU3d9POgY3I-vBKDNn6PyABW-J6-BfPtwJw&amp;oe=6AB86AA7
+https://scontent-lga3-1.cdninstagram.com/v/t51.71878-15/820251134_1086906984191583_6413718859244956689_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MTgyOTU2MzgzMDE3Mzk2OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Qrk39xfOTfoQ7kNvwHmug69&amp;_nc_oc=AdprXi8DA6SmJQ4onO1_2f7_W91KYjPFKFbIarIfyKZ2eERvH-At74bRw-oHr-KUmok&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;oh=00_AQK_cjM736KPi0nCM7znCOFTrW0cXtf0yQcTxUrWSXT0aQ&amp;oe=6AB86AA7
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwHdeK1O&amp;_nc_oc=AdoIap9mqg9pBelrbpNeZf8Emz6jeKl_s-674X9zvLnGAek_8WcT4ccphsW7qyKM4-s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQK9pvoOYaR_cI-BbMhVADumBeItIOP30FhnckCCuzeoyQ&amp;oe=6AB85F59
+https://l.instagram.com/?u=https%3A%2F%2Fwww.google.com%2Fabout%2Fcareers%2Fapplications%2Fjobs%2Fresults%2F134770032394543814-associate-product-manager-intern-summer-2027%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaevRSIGu5Iq9sl8CREpnDNy-eb3SPgLE7k0UvnNJ6G7Wl64307yPxMbt6c_sg_aem_Od0-pd6xjpUpkbZ9NvdEzw&amp;e=AUDO1hjtP8D_BRgcLuq8f4qV37uQxU4rjQATz4XoE8m41WmNBKX7O1dHhJkHKQVAK6k7ibPdx_qpkktow7xCVKThv2TMtf_KTPrtE1K6RQ
+https://scontent-lga3-2.cdninstagram.com/o1/v/t2/f2/m78/AQMjrnTmKhtSHIAaUpnQJSwFbwzPeg7fLqgr_4kTQtj2eIZSqDKrCOVW7kTbu8PuwQz8DG7l_x2ietc-4FRfbldCGNUlcubn9FnNu1Q.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ohc=fpMqK4rnjo4Q7kNvwG3aeO8&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc4OTA2MzA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=9b759702743e0fe5&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzhDNEQyRTkzRENDNjgzMDBBNzQzODFBQjFFQzlENjlEX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk5rj85rWhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIZ9XbzoQKbcj9r4hS2BdTWgc2CCQ6GGDDOX2OUrqjyjA&amp;oe=6AB465FA</f>
+        <v/>
+      </c>
+      <c r="O98" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P98" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q98" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99" ht="45" customHeight="1">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>44659063612094ca5af2</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:01:50.337225+00:00</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T13:21:11+00:00</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>Google — Mentorship / Cohort</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>Mentorship / Cohort</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr"/>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr"/>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/about/careers/applications/jobs/results/107272685397910214-associate-product-manager-university-graduate-2027-start</t>
+        </is>
+      </c>
+      <c r="L99" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
+          <t>@ google.com
+— ece fi o =N
+— Oo! leC... 33 OW Sign in }
+€ Back to jobs search
+Associate Product
+Manager, University
+Graduate, 2027 Start
+EE] Google © Mountain View, CA, USA; +3 more
+th Early
+This role will ting applications
+on September 22, , targeting cohort
+starts between April and August
+2027. You must complete your
+application *before* end of day on
+October 6, 2025 to be considered. Thank
+you in advance for your patience while
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/819855000_2840296039686936_1323997049263278028_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MTgzMDI5ODAxMDUzNzExNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=n63_9WM3rEYQ7kNvwFVEJyG&amp;_nc_oc=Adq9ne5lXzQ7SvJAcTKwmFdzB972FZnZvp6k1qTq4bsssMXe6Y-fVH3yAGqkF3eFeV4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;oh=00_AQIfkgdqgNDAupQNfJuuRnHvowcRBMzbHNlHebkTNkpLGg&amp;oe=6AB84F2E
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/819855000_2840296039686936_1323997049263278028_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MTgzMDI5ODAxMDUzNzExNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=n63_9WM3rEYQ7kNvwFVEJyG&amp;_nc_oc=Adq9ne5lXzQ7SvJAcTKwmFdzB972FZnZvp6k1qTq4bsssMXe6Y-fVH3yAGqkF3eFeV4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;oh=00_AQLjY5eOevPRtobGzgvKim_KCCTkSgar6zh3oEhElcfWOg&amp;oe=6AB84F2E
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwHdeK1O&amp;_nc_oc=AdoIap9mqg9pBelrbpNeZf8Emz6jeKl_s-674X9zvLnGAek_8WcT4ccphsW7qyKM4-s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQK9pvoOYaR_cI-BbMhVADumBeItIOP30FhnckCCuzeoyQ&amp;oe=6AB85F59
+https://l.instagram.com/?u=https%3A%2F%2Fwww.google.com%2Fabout%2Fcareers%2Fapplications%2Fjobs%2Fresults%2F107272685397910214-associate-product-manager-university-graduate-2027-start%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafKHK09djwVidfQmQnj-qlQIGd-2c_bVo67LAdad2Xq9y07RMr3KqParQdazw_aem_iy_meU6hntqt9xfDiXYwoA&amp;e=AUCL6vUD1k87-cdX5hiWw6Y8sNR4IXAlw56BqfHJG367XHxpteKbx3UDLtYDQTPpiUYqb2sz7gIDv0wIwxjWFsDEC_tLN1tUDxhxBrTv0g
+https://scontent-lga3-2.cdninstagram.com/o1/v/t2/f2/m78/AQOxJgSHvs5si6YexzDCZMiSZ2_jtODb65SM0jt8Kn7KWJ0-rqk1wQ1qvbsMNEY6KD7gklOh-asZZeiJwaABR5tjItv9-aoe8pNGtMU.mp4?_nc_cat=107&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ohc=jukPlT5wle8Q7kNvwFjIK3H&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc4OTA4OTE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=f941444a2ba2df91&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0IxN0Q0MUY4OEI4MDQyRTk4RERDNjQ4OEQ1Mjg5RDRDX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkk6316LWhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIK6iGi7k1HQJp335qC7plPm-D66YTHRvLsL5Z7iYR36w&amp;oe=6AB47728</t>
+        </is>
+      </c>
+      <c r="O99" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P99" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q99" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100" ht="45" customHeight="1">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>4add870a7174ccaa9c79</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:01:52.071629+00:00</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T13:24:00+00:00</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>Apple — Machine Learning / AI</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>Machine Learning / AI</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr"/>
+      <c r="I100" s="3" t="inlineStr"/>
+      <c r="J100" s="3" t="inlineStr"/>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.apple.com/en-us/details/200683768/internship-machine-learning-research</t>
+        </is>
+      </c>
+      <c r="L100" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
+          <t>4
+Join Apple.
+Internship - Machine Learning
+Research - Jobs - Careers at
+Apple
+Apply for a Internship - Machine
+Learning Research job at Apple. Read
+about the role and find out if it’s right
+for you.
+htt
+fe)
+-m
+, w
+Gaia
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/816987602_1793228321829398_1758082361199685357_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5MTgzMTcxMjA0NDYyNjQxNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=qF0H-eGCJmgQ7kNvwE12mPH&amp;_nc_oc=AdoQN2OYzn4SH3gmH4-UYKI10FNlkuaNrXPDtrHycvLdN9W_YFh3NNzICSww0dE1N9s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;oh=00_AQIk8Z6PKI4j_oFll_p78MYmtGABtnBn76bWzpqYWHNVHQ&amp;oe=6AB882E8
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/816987602_1793228321829398_1758082361199685357_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5MTgzMTcxMjA0NDYyNjQxNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=qF0H-eGCJmgQ7kNvwE12mPH&amp;_nc_oc=AdoQN2OYzn4SH3gmH4-UYKI10FNlkuaNrXPDtrHycvLdN9W_YFh3NNzICSww0dE1N9s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;oh=00_AQLXApUM5L_UGUGQXrIYJ0QTT3-ta5-RF-RwddFgdEVLew&amp;oe=6AB882E8
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwHdeK1O&amp;_nc_oc=AdoIap9mqg9pBelrbpNeZf8Emz6jeKl_s-674X9zvLnGAek_8WcT4ccphsW7qyKM4-s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQK9pvoOYaR_cI-BbMhVADumBeItIOP30FhnckCCuzeoyQ&amp;oe=6AB85F59
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.apple.com%2Fen-us%2Fdetails%2F200683768%2Finternship-machine-learning-research&amp;e=AUA2epxEZJo_905wWoJsWr6hw2CnMevowl6DYxqZqGl3jpZurHKIWt0LAhTbJ8QtccJUyEpN3SZRh8zv35eBGcZmETikDHqqVDvoEdKbjA
+https://scontent-lga3-1.cdninstagram.com/o1/v/t2/f2/m78/AQNRD7a_9x_pA_rOARem-llkS0RKCfl4juw7UnldaQHrqRwJuOhBUxt0tXtv-QHP_i3Pb9aYI7fYuGs9v8t6LaJ5MlNOl1GMhu8cmJ0.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_ohc=BRGBpFpkQ5AQ7kNvwHaZq_T&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc4OTEwOTg2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=33576f58087a4ecd&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0EwNEQ0OTU2M0REMjI0MDIzMTdFNTI0ODlFOEE3RUJBX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk2uG66rWhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIjgP6itksFeQpcJQzJZw2AoTFLEGKvPihwshYFWCY_LA&amp;oe=6AB480BA</t>
+        </is>
+      </c>
+      <c r="O100" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P100" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q100" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R100" s="3" t="inlineStr"/>
+    </row>
+    <row r="101" ht="45" customHeight="1">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>48b8a5939da8f8f1e7c9</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:01:56.466643+00:00</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T13:48:57+00:00</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>Cisco — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr"/>
+      <c r="I101" s="3" t="inlineStr"/>
+      <c r="J101" s="3" t="inlineStr"/>
+      <c r="K101" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.cisco.com/global/en/job/CISCISGLOBAL2026306EXTERNALENGLOBAL/Software-Engineer-Data-AI-I-Intern-United-States</t>
+        </is>
+      </c>
+      <c r="L101" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
+          <t>x @ careers.cisco.com C:
+Q 90)
+Careers
+@) Global v
+Software Engineer Data &amp; Al |
+(Intern) - United States
+9 Available in 4 locations
+Internships, Apprenticeships, and Co-
+Ops
+F4 2026306
+© Hybrid
+@ CAREERS.CISCO.COM
+wy,
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/794484760_1733282517935545_4045514408347968030_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTg0NDI3NjQ2OTAxODkxMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=-y99AYrbcMIQ7kNvwFRvgZY&amp;_nc_oc=Adr4usJhld6FGXbK9ztCMeXEjtVMfzyEFRKs0IklsUi186YnW93xjjQk0gcmx3ryCYE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;oh=00_AQJxHv5haVBPBCir3AVUPJbiBHiLCKWRGayCT19SubpQEA&amp;oe=6AB8846E
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/794484760_1733282517935545_4045514408347968030_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTg0NDI3NjQ2OTAxODkxMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=-y99AYrbcMIQ7kNvwFRvgZY&amp;_nc_oc=Adr4usJhld6FGXbK9ztCMeXEjtVMfzyEFRKs0IklsUi186YnW93xjjQk0gcmx3ryCYE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;oh=00_AQL2o7FQOuUBTd3Z2uhXS26ghyOTHsmXtgLKyy-iC6OSvA&amp;oe=6AB8846E
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwHdeK1O&amp;_nc_oc=AdoIap9mqg9pBelrbpNeZf8Emz6jeKl_s-674X9zvLnGAek_8WcT4ccphsW7qyKM4-s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQK9pvoOYaR_cI-BbMhVADumBeItIOP30FhnckCCuzeoyQ&amp;oe=6AB85F59
+https://l.instagram.com/?u=https%3A%2F%2Fcareers.cisco.com%2Fglobal%2Fen%2Fjob%2FCISCISGLOBAL2026306EXTERNALENGLOBAL%2FSoftware-Engineer-Data-AI-I-Intern-United-States%3Futm_source%3Dlinkedin%26utm_medium%3Dphenom-feeds%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAae6It_UKWuQ5SJKl2Rwk1q_yTt4qYdiobNgXhGY5QMaKkzwtsEbVOf-bystvQ_aem_DCfcLQjvK-bMfDKdc78JgA&amp;e=AUAN5LJPQO2kHEm2JvBpNCoiio4N3f4DOYGTW3d_d3HOQd5z1IcJTmDOZT4dpK2PnJXvW-aSb0MzXbw0GuUzLa3gkWXq1rawM5oTD6NL2w
+https://scontent-lga3-2.cdninstagram.com/o1/v/t2/f2/m78/AQPGHz4oZ1EuJFhf-jKEB2SxMhNRKlp1icU99S2heClNwZ6MaYPdnCqnM5cHCf9bLelm2op3AEcQ_afLpkvDPXoJnVc7d37mp1aRz_w.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ohc=nP6PaeJr_ngQ7kNvwF45-fK&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc4OTQwNDc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=ef6544f163ab82a4&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzBENDAyRTRBQzE3MkNCODk0NjgxRTNGMDNFMzMwNjkxX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkh5O3gLahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIMUh8O4vQW6TFKFG9fZ76gFySgP_Imguz3XZDA8S-Pig&amp;oe=6AB48F6A</t>
+        </is>
+      </c>
+      <c r="O101" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P101" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q101" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R101" s="3" t="inlineStr"/>
+    </row>
+    <row r="102" ht="45" customHeight="1">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>96e163fb53a75358c4de</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:01:58.365963+00:00</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T13:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr"/>
+      <c r="J102" s="3" t="inlineStr"/>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/cowboyspace/56d1d7e4-fa7e-4c25-aa8b-6828447fc64a?embed=true</t>
+        </is>
+      </c>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
+          <t>x @ jobs.ashbyhg.com CG:
+Instagram a
+&lt; AllJobs
+Intern, Software Engineering,
+2027
+Location
+San Carlos, California
+Address
+San Carlos, California
+Employment Type
+Full time
+Location Type
+On-site
+Department
+Software Engineering
+About Cowboy Spac
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/818535105_2174933256430466_3343516370505550816_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTg0NDgwNDc0MTQ0NzI5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=u1IN0RwF76UQ7kNvwEcHLlZ&amp;_nc_oc=AdrOPMhNN1K46_RxrFI8UuXXCXBvDxebWsx_qeM85lnIjArI1IA_fbvTK9qIsafq9Lo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;oh=00_AQJwdhwzS8TNin15VOkpvLuk-hp6G9E3yFdy-B2JjDtq6Q&amp;oe=6AB8818E
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/818535105_2174933256430466_3343516370505550816_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTg0NDgwNDc0MTQ0NzI5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=u1IN0RwF76UQ7kNvwEcHLlZ&amp;_nc_oc=AdrOPMhNN1K46_RxrFI8UuXXCXBvDxebWsx_qeM85lnIjArI1IA_fbvTK9qIsafq9Lo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;oh=00_AQLPPLVE18yC0UHl-zc25IG4jTXComEvL1TIl7ICPgyCgA&amp;oe=6AB8818E
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwHdeK1O&amp;_nc_oc=AdoIap9mqg9pBelrbpNeZf8Emz6jeKl_s-674X9zvLnGAek_8WcT4ccphsW7qyKM4-s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQK9pvoOYaR_cI-BbMhVADumBeItIOP30FhnckCCuzeoyQ&amp;oe=6AB85F59
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.ashbyhq.com%2Fcowboyspace%2F56d1d7e4-fa7e-4c25-aa8b-6828447fc64a%3Fembed%3Dtrue%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaf2z3wYpE59goJpw6ps-4_ogSzQC79Sf9q1Cher64JWqaHrztl4WK_GNrd04A_aem_yNJ4oXMD1mWPSJ5-IcfsKA&amp;e=AUBFKGcauR-Ro5kJY6yjgtY3vb4_RMnwnje4BpWO6zP-6wIaYcQQw5C72LwwUyAnIF6eqbPHfffWzEIkSSbrKUSaiQAfCUvELskOMMRj4w
+https://scontent-lga3-1.cdninstagram.com/o1/v/t2/f2/m78/AQPwAgvrdV2GcqocWVqa-WhTqF4WcgVuEHmJUjqC2BbCvXxYDRyM5b3E-mFt4p4st2Omg0kMpLLZTgC2bNIoG4r9DaX-yM-xdNwuevA.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_ohc=dN1SkQ4KQNsQ7kNvwE3hht_&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc4OTQyMDY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=37a03b6c1ba58cca&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzU0NDU0MTE4RkNFOTI5OTg2NDhCQjVEMUU1NjI4NzhGX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbknuTOgbahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLVhmyi4OlSCKdzIPzSgoPxngDOugoS0zz44onOrezhWg&amp;oe=6AB46450</t>
+        </is>
+      </c>
+      <c r="O102" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P102" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q102" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R102" s="3" t="inlineStr"/>
+    </row>
+    <row r="103" ht="45" customHeight="1">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>d0008724d544e3e121ba</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:02:00.626354+00:00</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T13:53:11+00:00</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr"/>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>Tesla X Virginia Tech| Apply Now</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr"/>
+      <c r="H103" s="3" t="inlineStr"/>
+      <c r="I103" s="3" t="inlineStr"/>
+      <c r="J103" s="3" t="inlineStr"/>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tesla.com/event/virginia-tech-resume</t>
+        </is>
+      </c>
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
+          <t>Tesla X Virginia Tech| Apply Now
+| Tesla Events
+Join Tesla virtually at Virginia
+Tech! Apply now to connect with
+recruiters for career and internship
+opportunities. Submit your resume
+today!
+ht
+Ivi
+not sure how’ of ur
+followers go to-vx (ol but ya!
+Send this to your Virgina Tech friends before it
+fills up! Tons of people have gotten direct
+consideration from it at other universities :)
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/820542746_1636052604763174_4050211739412077637_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5MTg0NjQwMzI2NjM2MjMzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=JDaFftgzM_wQ7kNvwF3nWkr&amp;_nc_oc=AdqrPTW46yS4MXCdDH-r2vNYuITOr_EyNAYiZ2dIeLoX_j55vIWwmpVIivWdB32KnsA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;oh=00_AQLknJYETjV2q8y4UjRWivAIoWUqO3L2Ui0jGibjpvrmew&amp;oe=6AB86B8C
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/820542746_1636052604763174_4050211739412077637_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5MTg0NjQwMzI2NjM2MjMzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=JDaFftgzM_wQ7kNvwF3nWkr&amp;_nc_oc=AdqrPTW46yS4MXCdDH-r2vNYuITOr_EyNAYiZ2dIeLoX_j55vIWwmpVIivWdB32KnsA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;oh=00_AQJs_n_YSLg9sMP9g4om0M2bX6ch5TYMH3wTGm-3a9-o2A&amp;oe=6AB86B8C
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwHdeK1O&amp;_nc_oc=AdoIap9mqg9pBelrbpNeZf8Emz6jeKl_s-674X9zvLnGAek_8WcT4ccphsW7qyKM4-s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQK9pvoOYaR_cI-BbMhVADumBeItIOP30FhnckCCuzeoyQ&amp;oe=6AB85F59
+https://l.instagram.com/?u=https%3A%2F%2Fwww.tesla.com%2Fevent%2Fvirginia-tech-resume%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafdGXMoeCjf2f8IXHi1xVuEyYmiG-qf6oOSq0qEPDvf7jtbelluc4OnsvmoEg_aem_1A3KzIlCTzT7R8y-_HX2tw&amp;e=AUCNklsaBhR-e6KEZC6OVx7l7fopGEMb5xz5KO_GZaJOqsO8kSQsMDe30JvQD-ykGCBEwwiP6PhFL6JAe2uAm9sqjNobdbKIcBmduWEoEg
+https://scontent-lga3-1.cdninstagram.com/o1/v/t2/f2/m78/AQO6ylW1anOkK5zI9P6pKbElP1uMw-fM9CTfsRNjI-nnTQQsuXyHLFGsNwM8xbUe6cA2H9Oje_lIXMc2Dv5hz_AL3OdtxZkCz92leOM.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_ohc=NTYkzuNkFvIQ7kNvwG7J-g4&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc4OTQ2NzQ2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=5e2300665b418aa5&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzdGNDM5M0U5QUUxNDc1NzQ1NDM1Q0ZEODVGOThFQzg5X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkko2NhbahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKiHHoJS8GMUxlH-2AZtrdy4Vq7BJbKAby4S_EeIrIMIg&amp;oe=6AB45C20</t>
+        </is>
+      </c>
+      <c r="O103" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P103" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q103" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104" ht="45" customHeight="1">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>62d4895b07db67889a81</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:02:08.464831+00:00</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T14:28:34+00:00</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>Genevatrading</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>Genevatrading — Internship</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr"/>
+      <c r="H104" s="3" t="inlineStr"/>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="inlineStr"/>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/genevatrading/jobs/5242196007?gh_src=vukgv78h7us&amp;t=3253f722teu</t>
+        </is>
+      </c>
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
+          <t>ADING-
+Python Developer Intern
+Chicago Office
+https://job-boards.greenhouse.io
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/819966541_2065447744078783_6836614745414293080_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTg2NDIxNDM4NjI3OTM0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=ymzWZohWS6oQ7kNvwF_DSlb&amp;_nc_oc=Adovpp05vwiC2nQlGH4gpYhstcfJB9Es9cUwMnG1oTGNXRuDjHR5Ki4iaAM35nx0_og&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;oh=00_AQLTQN17rxctf4Wj7Bwbiv1iH5YDx3bzSJHypVPPe3okUQ&amp;oe=6AB86AEA
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/819966541_2065447744078783_6836614745414293080_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTg2NDIxNDM4NjI3OTM0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=ymzWZohWS6oQ7kNvwF_DSlb&amp;_nc_oc=Adovpp05vwiC2nQlGH4gpYhstcfJB9Es9cUwMnG1oTGNXRuDjHR5Ki4iaAM35nx0_og&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;oh=00_AQLMLV9bz2NUgXeyhtxCNHmgtBqtCcPsWrOk82n_79GoRw&amp;oe=6AB86AEA
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwHdeK1O&amp;_nc_oc=AdoIap9mqg9pBelrbpNeZf8Emz6jeKl_s-674X9zvLnGAek_8WcT4ccphsW7qyKM4-s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQK9pvoOYaR_cI-BbMhVADumBeItIOP30FhnckCCuzeoyQ&amp;oe=6AB85F59
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fgenevatrading%2Fjobs%2F5242196007%3Fgh_src%3Dvukgv78h7us%26t%3D3253f722teu%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeNx1l1KMlUIijg8NvKKH1PX4ja6KB0zF1l3cT1cAXxJ4P2JNL3xgrDis3puw_aem_tTJvYpTXUV1YP6VtbyQLYA&amp;e=AUCkfQPwvtjp_UwoFWBXd2-lzQbvOgh-FPtIRROXBxror7qcU9xqb4gdy-CVPYbni6qDZ89zehOi-Tc8lSBjD0DIxXQRgz37yAfivq4rrA
+https://scontent-lga3-3.cdninstagram.com/o1/v/t2/f2/m78/AQNs4ZHLiVN8rW4bd8mb1i6mmgmIOcEsqOb7q3yWksHHFYcU3AxBBOM9Ee_7zz-2vPWd_le8Mix2_512ky6yhZUzbZmeZu6I76qkPg4.mp4?_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_ohc=4b9Pbb0ZUZ4Q7kNvwFmTRgS&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc4OTkwODE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=4f8f6656eaad4cb1&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzMxQTA2QTcyOUE5ODQ5MzA4Mjk2MjgxRTJFNzczODJEX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkgfn3pbahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLWICEuGu_yyahrfL2bEvFb8-tLRyK2u5WAMZ85jNc4dg&amp;oe=6AB47FC3</t>
+        </is>
+      </c>
+      <c r="O104" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P104" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q104" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R104" s="3" t="inlineStr"/>
+    </row>
+    <row r="105" ht="45" customHeight="1">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>9403959d8cb009bbbd6c</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:02:10.793115+00:00</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T14:47:12+00:00</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>Meta — Other Opportunity</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr"/>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr"/>
+      <c r="J105" s="3" t="inlineStr"/>
+      <c r="K105" s="3" t="inlineStr"/>
+      <c r="L105" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
+          <t>@ metacareers.com
+Instagram
+IN THEIR OWN WORDS
+"The RPM community connects you with
+extremely inspirational people, creating
+friends and mentors for life."
+— Akanksha, Member of Product Staff
+PSA PMs - Meta rotational product
+manager opens up tomorrow. I'll post
+the link right when it opens :)
+If you see a future in leadership as a product
+manager, take the next step in your career path.
+Status
+Applications open September 23, 2026. Check back
+to apply.
+OO Meta
+Job Search
+Technology Teams
+https://scontent-lga3-2.cdninstagram.com/v/t51.82787-15/809209120_18087901721678962_4771953670990349392_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5MTg3MzU2OTc2Njc1MDY0OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=sCIC8ecQ_O0Q7kNvwHG1DuR&amp;_nc_oc=AdpP3uxME0iGhp6Ss1xTk0Nwire9CSpCc8JrKwpI9P-NGLbikroVbuQZSgtg2SZ4sJc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=7&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;oh=00_AQKbXdR7x5IhrMWBHh0iIZ-lefo8Rquib3LW7juaaa2lcg&amp;oe=6AB86A38
+https://scontent-lga3-2.cdninstagram.com/v/t51.82787-15/809209120_18087901721678962_4771953670990349392_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5MTg3MzU2OTc2Njc1MDY0OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=sCIC8ecQ_O0Q7kNvwHG1DuR&amp;_nc_oc=AdpP3uxME0iGhp6Ss1xTk0Nwire9CSpCc8JrKwpI9P-NGLbikroVbuQZSgtg2SZ4sJc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;oh=00_AQLMu75_-pbiTGBE1T_U7O3zdktvXiBUrtkQLLAMeb2jGw&amp;oe=6AB86A38
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwHdeK1O&amp;_nc_oc=AdoIap9mqg9pBelrbpNeZf8Emz6jeKl_s-674X9zvLnGAek_8WcT4ccphsW7qyKM4-s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQK9pvoOYaR_cI-BbMhVADumBeItIOP30FhnckCCuzeoyQ&amp;oe=6AB85F59</t>
+        </is>
+      </c>
+      <c r="O105" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P105" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q105" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106" ht="45" customHeight="1">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>877f5038848d6a2f3780</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:02:14.089824+00:00</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T14:49:29+00:00</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>Gehealthcare</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>Gehealthcare — Internship</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr"/>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr"/>
+      <c r="J106" s="3" t="inlineStr"/>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.gehealthcare.com/global/en/job/R4046487/Summer-2027-Data-Analytics-Intern</t>
+        </is>
+      </c>
+      <c r="L106" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
+          <t>@ careers.gehealthcare.com
+Instagram
+z ~ r WNIT Na f &gt; -
+SL rT] = £VUZ4I Bseite Ue J Ke
+tit ~I 2U42 7c ALY LIL
+ntern
+r i+ rs 4
+UE healtncare eaitncare Advanced
+Visualization Solutions | Services @
+OD tern R4046487 | 'elocation
+ssistance Ye a ake City, UTa’ Nnitec
+states of America, 84116
+~ Ww . tf
+° .* c &lt;a
+Job Description Summary a Oo
+@ oe
+. /
+looking for a Data Analytics Intern whoo
+curious, detail-oriented, and eager to learn.
+Thie te a hande An Annartiinity ta wsiarls vwasith
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/821223525_28826833296902335_4945366150243038066_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5MTg3NDc3NzcyNDA1MjA5OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=P86qhoyhna8Q7kNvwGSCnAy&amp;_nc_oc=Adqt6YgCa98FI-iXfl2eGxCufgI-AmpWrABx9vCSD6YdrU6ppObeVRZKseaPBW3d8b8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;oh=00_AQIlMY7UX7o-Ajjo8ERLrNi9SbBmbCSIj7EbTLjBV2A12g&amp;oe=6AB86165
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/821223525_28826833296902335_4945366150243038066_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5MTg3NDc3NzcyNDA1MjA5OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=P86qhoyhna8Q7kNvwGSCnAy&amp;_nc_oc=Adqt6YgCa98FI-iXfl2eGxCufgI-AmpWrABx9vCSD6YdrU6ppObeVRZKseaPBW3d8b8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;oh=00_AQKIDOXKkAjTmNXpjvr-0iEG04cCjir2CYfh-ZrXK8gRbQ&amp;oe=6AB86165
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwHdeK1O&amp;_nc_oc=AdoIap9mqg9pBelrbpNeZf8Emz6jeKl_s-674X9zvLnGAek_8WcT4ccphsW7qyKM4-s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQK9pvoOYaR_cI-BbMhVADumBeItIOP30FhnckCCuzeoyQ&amp;oe=6AB85F59
+https://l.instagram.com/?u=https%3A%2F%2Fcareers.gehealthcare.com%2Fglobal%2Fen%2Fjob%2FR4046487%2FSummer-2027-Data-Analytics-Intern%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaccrTSIvn1WqtA1kKW2DVo75rZ7nWqZ7KTEFCrWmuVvKR-P2n9r1BLSn8L-3A_aem_P9My4bpBiXEQ7Rjy5b6dnQ&amp;e=AUA1NayY8EDPEexzMn9oT1SVAGO1Ifr6HP52g0tJF63_AANIBRlqgJSTQznSViR-hu7dm7DC1WnuEkKS-VOAmn7m12H0svThFrIGv6pcjQ
+https://scontent-lga3-2.cdninstagram.com/o1/v/t2/f2/m78/AQN_EZDPxs8RhoY0X-rJR1RINsNR-BtovzSVazCs3W80hcqWZJkd0mr7MKPNVp7GQeRCjwLUmhRPv-H4E2fMaH_zybua5GEW9JucY9o.mp4?_nc_cat=107&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ohc=vdgmFf1LEPsQ7kNvwF3mcQl&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc5MDIwMDk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=781d7f93b4a1022&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzBCNDVFNkJEOEYyODU1MTA3OUY0MTcxMDA4RjQzRTgyX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk8abgu7ahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=SkQZLu2t1XpR34bRlb4Z4w&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIwAjppWcDdwXzTxvBHjc4cjFTH0tKU1ka-LyC7NrFbPQ&amp;oe=6AB47D64</t>
+        </is>
+      </c>
+      <c r="O106" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P106" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q106" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R106" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R97"/>
+  <autoFilter ref="A1:R106"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -9800,6 +10654,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId177"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="rId196"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R106"/>
+  <dimension ref="A1:R111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9621,7 +9621,7 @@
     <row r="98" ht="45" customHeight="1">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>6ec85af72f29bd8bdf0a</t>
+          <t>3fc5fdb1a8f74f816808</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -9664,7 +9664,7 @@
           <t>Mountain View</t>
         </is>
       </c>
-      <c r="J98" s="3" t="inlineStr"/>
+      <c r="J98" s="3" t="n"/>
       <c r="K98" s="4" t="inlineStr">
         <is>
           <t>https://www.google.com/about/careers/applications/jobs/results/134770032394543814-associate-product-manager-intern-summer-2027</t>
@@ -9721,12 +9721,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R98" s="3" t="inlineStr"/>
+      <c r="R98" s="3" t="n"/>
     </row>
     <row r="99" ht="45" customHeight="1">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>44659063612094ca5af2</t>
+          <t>50c45099fe5ebe59870d</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -9754,7 +9754,7 @@
           <t>Mentorship / Cohort</t>
         </is>
       </c>
-      <c r="G99" s="3" t="inlineStr"/>
+      <c r="G99" s="3" t="n"/>
       <c r="H99" s="3" t="inlineStr">
         <is>
           <t>2027</t>
@@ -9765,7 +9765,7 @@
           <t>Mountain View</t>
         </is>
       </c>
-      <c r="J99" s="3" t="inlineStr"/>
+      <c r="J99" s="3" t="n"/>
       <c r="K99" s="4" t="inlineStr">
         <is>
           <t>https://www.google.com/about/careers/applications/jobs/results/107272685397910214-associate-product-manager-university-graduate-2027-start</t>
@@ -9821,12 +9821,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R99" s="3" t="inlineStr"/>
+      <c r="R99" s="3" t="n"/>
     </row>
     <row r="100" ht="45" customHeight="1">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>4add870a7174ccaa9c79</t>
+          <t>8d9f9c021cd4664843fb</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -9859,9 +9859,9 @@
           <t>Machine Learning / AI</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr"/>
-      <c r="I100" s="3" t="inlineStr"/>
-      <c r="J100" s="3" t="inlineStr"/>
+      <c r="H100" s="3" t="n"/>
+      <c r="I100" s="3" t="n"/>
+      <c r="J100" s="3" t="n"/>
       <c r="K100" s="4" t="inlineStr">
         <is>
           <t>https://jobs.apple.com/en-us/details/200683768/internship-machine-learning-research</t>
@@ -9915,12 +9915,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R100" s="3" t="inlineStr"/>
+      <c r="R100" s="3" t="n"/>
     </row>
     <row r="101" ht="45" customHeight="1">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>48b8a5939da8f8f1e7c9</t>
+          <t>5ee59e7f43f82368770d</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -9953,9 +9953,9 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr"/>
-      <c r="I101" s="3" t="inlineStr"/>
-      <c r="J101" s="3" t="inlineStr"/>
+      <c r="H101" s="3" t="n"/>
+      <c r="I101" s="3" t="n"/>
+      <c r="J101" s="3" t="n"/>
       <c r="K101" s="4" t="inlineStr">
         <is>
           <t>https://careers.cisco.com/global/en/job/CISCISGLOBAL2026306EXTERNALENGLOBAL/Software-Engineer-Data-AI-I-Intern-United-States</t>
@@ -10008,12 +10008,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R101" s="3" t="inlineStr"/>
+      <c r="R101" s="3" t="n"/>
     </row>
     <row r="102" ht="45" customHeight="1">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>96e163fb53a75358c4de</t>
+          <t>6d2e52ce4983d928545c</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -10051,8 +10051,8 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="I102" s="3" t="inlineStr"/>
-      <c r="J102" s="3" t="inlineStr"/>
+      <c r="I102" s="3" t="n"/>
+      <c r="J102" s="3" t="n"/>
       <c r="K102" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/cowboyspace/56d1d7e4-fa7e-4c25-aa8b-6828447fc64a?embed=true</t>
@@ -10108,12 +10108,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R102" s="3" t="inlineStr"/>
+      <c r="R102" s="3" t="n"/>
     </row>
     <row r="103" ht="45" customHeight="1">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>d0008724d544e3e121ba</t>
+          <t>88941bab48196552e5c0</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -10126,7 +10126,7 @@
           <t>2026-09-22T13:53:11+00:00</t>
         </is>
       </c>
-      <c r="D103" s="3" t="inlineStr"/>
+      <c r="D103" s="3" t="n"/>
       <c r="E103" s="3" t="inlineStr">
         <is>
           <t>Tesla X Virginia Tech| Apply Now</t>
@@ -10137,10 +10137,10 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G103" s="3" t="inlineStr"/>
-      <c r="H103" s="3" t="inlineStr"/>
-      <c r="I103" s="3" t="inlineStr"/>
-      <c r="J103" s="3" t="inlineStr"/>
+      <c r="G103" s="3" t="n"/>
+      <c r="H103" s="3" t="n"/>
+      <c r="I103" s="3" t="n"/>
+      <c r="J103" s="3" t="n"/>
       <c r="K103" s="4" t="inlineStr">
         <is>
           <t>https://www.tesla.com/event/virginia-tech-resume</t>
@@ -10194,12 +10194,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R103" s="3" t="inlineStr"/>
+      <c r="R103" s="3" t="n"/>
     </row>
     <row r="104" ht="45" customHeight="1">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>62d4895b07db67889a81</t>
+          <t>0b7c0564c5035e511c13</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -10227,14 +10227,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G104" s="3" t="inlineStr"/>
-      <c r="H104" s="3" t="inlineStr"/>
+      <c r="G104" s="3" t="n"/>
+      <c r="H104" s="3" t="n"/>
       <c r="I104" s="3" t="inlineStr">
         <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="J104" s="3" t="inlineStr"/>
+      <c r="J104" s="3" t="n"/>
       <c r="K104" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/genevatrading/jobs/5242196007?gh_src=vukgv78h7us&amp;t=3253f722teu</t>
@@ -10278,12 +10278,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R104" s="3" t="inlineStr"/>
+      <c r="R104" s="3" t="n"/>
     </row>
     <row r="105" ht="45" customHeight="1">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>9403959d8cb009bbbd6c</t>
+          <t>b1c3b547907dcfbbdcd0</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -10311,15 +10311,15 @@
           <t>Other Opportunity</t>
         </is>
       </c>
-      <c r="G105" s="3" t="inlineStr"/>
+      <c r="G105" s="3" t="n"/>
       <c r="H105" s="3" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="I105" s="3" t="inlineStr"/>
-      <c r="J105" s="3" t="inlineStr"/>
-      <c r="K105" s="3" t="inlineStr"/>
+      <c r="I105" s="3" t="n"/>
+      <c r="J105" s="3" t="n"/>
+      <c r="K105" s="3" t="n"/>
       <c r="L105" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -10370,12 +10370,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R105" s="3" t="inlineStr"/>
+      <c r="R105" s="3" t="n"/>
     </row>
     <row r="106" ht="45" customHeight="1">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>877f5038848d6a2f3780</t>
+          <t>e12b0ed6a1298ca6623e</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -10403,14 +10403,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G106" s="3" t="inlineStr"/>
+      <c r="G106" s="3" t="n"/>
       <c r="H106" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="I106" s="3" t="inlineStr"/>
-      <c r="J106" s="3" t="inlineStr"/>
+      <c r="I106" s="3" t="n"/>
+      <c r="J106" s="3" t="n"/>
       <c r="K106" s="4" t="inlineStr">
         <is>
           <t>https://careers.gehealthcare.com/global/en/job/R4046487/Summer-2027-Data-Analytics-Intern</t>
@@ -10470,10 +10470,503 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R106" s="3" t="inlineStr"/>
+      <c r="R106" s="3" t="n"/>
+    </row>
+    <row r="107" ht="45" customHeight="1">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>74d89fdbfe4901adf9a3</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:59:37.767902+00:00</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr"/>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>syst Rippling Fulstack a intern</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr"/>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>Seattle, San Francisco, New York</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="inlineStr"/>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>https://ats.rippling.com/rippling/jobs/f64b6158-9534-4bab-9457-45556166b262</t>
+        </is>
+      </c>
+      <c r="L107" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
+          <t>Full Stack Software
+Engineer Intern - Summer
+2027
+Engineering
+San Francisco, CA
+New York, NY
+Seattle, WA
+Share on:
+M MX
+@ ATS.RIPPLING.COM
+About Rippling
+Rippling gives businesses one place to run HR, IT,
+syst Rippling Fulstack a intern
+computers. For the first time ever, you can manage
+and automate every part of the employee lifecycle
+in a single system.
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/818743085_4669936659961078_9210351453057306976_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MTg5MDI1MjY2NzY5NDM5MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=_G4fRjuaVZsQ7kNvwEIcVP0&amp;_nc_oc=AdobNYrzCIRTPC-7-EW1DI1rXrF8EEBgM-EbDBPYpAjU_MUlhIHgkdavt8aRw_X6ME4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=NhHZMbOOP1wxYHBqrmseIg&amp;_nc_ss=7e3ba&amp;oh=00_AQJ6cljZ93Kf7Nc9CmxUKVPxS0atTDYK63y9cTLu_iBItQ&amp;oe=6AB8897D
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/818743085_4669936659961078_9210351453057306976_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MTg5MDI1MjY2NzY5NDM5MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=_G4fRjuaVZsQ7kNvwEIcVP0&amp;_nc_oc=AdobNYrzCIRTPC-7-EW1DI1rXrF8EEBgM-EbDBPYpAjU_MUlhIHgkdavt8aRw_X6ME4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=NhHZMbOOP1wxYHBqrmseIg&amp;_nc_ss=7e3ba&amp;oh=00_AQITImMArmBNoK1Jk8cizuBHitRhtCRaBuCZQxDkUvV4Ow&amp;oe=6AB8897D
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwGkZ7xu&amp;_nc_oc=AdoRUbV0-oacb_ovWLiavVtHGVQBCD-_s4Oj1SptFb3J-Myfkoirb7EQHPlS-vTw3Lg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKydMHQBFTkBxCFT1N8CtDyuHkKzdUf_Z_Q0EnoaXqZqA&amp;oe=6AB89799
+https://l.instagram.com/?u=https%3A%2F%2Fats.rippling.com%2Frippling%2Fjobs%2Ff64b6158-9534-4bab-9457-45556166b262%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAad28m6OhB1L2WnksCQtpNRMUivoQcpKvY2XUw4umM4js496E8eLeHBR_uo6Cw_aem_RCNYXpf8a3Z6VEieiLJTUg&amp;e=AUBObUW7oF4FbzBs9NJxNC8wuaIjMAUgbgBL_bmrE5YgubB0oPDu1kMbkz5UYuwBVoBtsY0T7NBaY8MIKj-7Dv4ICKKsrXNQVvRHa-xUGg
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQOnRiNRvd9_6lNpX7mtxwYN-_k8YhkZ7788Jw_zZMIG9jOWvimXOiBjc-TIkkM0W3QIHKc2MAyPevgr5qUjuR-WrF6f18iBLDfKDuc.mp4?_nc_cat=104&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=cf7HtNOjzy8Q7kNvwEe4jJm&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc5MDU1MjU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=eb89fd861896d40a&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzkwNDIyQTE5MEY2Mzg3RDk0NUZFMzE5OUE2OEZGREFDX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkjbb51bahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=NhHZMbOOP1wxYHBqrmseIg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJutz9UZxhJFywL76frM7vzxSXleOqzovtQmt8bBld59g&amp;oe=6AB4B571</t>
+        </is>
+      </c>
+      <c r="O107" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P107" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q107" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108" ht="45" customHeight="1">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>e56181e2f123236c7dec</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:59:39.276285+00:00</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:22:20+00:00</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr"/>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>@ RIPPLING MLE SWE INTERN</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering, Machine Learning / AI</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="inlineStr"/>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t>https://ats.rippling.com/rippling/jobs/f9de04c3-e2c5-41f9-8e46-a0684707f89d?_gl=1%2Aw2k05b%2A_gcl_au%2AMTg3NzcwNTIyNy4xNzkwMDkwMzM2</t>
+        </is>
+      </c>
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
+          <t>ats.rippling.com &amp;
+Machine Learning
+Software Engineer Intern -
+Summer 2027
+| Engineering
+\) San Francisco, CA
+Share on:
+XM M XK
+About Rippling
+@ RIPPLING MLE SWE INTERN
+all of the workforce s that are
+normally scattered a company, like
+payroll, expenses, benefits, and
+computers. For the first time ever, you
+can manage and automate every part of
+the employee lifecycle in a single system.
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/820374106_1049426904596138_779138823588338757_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTg5MTI3Nzc2MzIwNTA3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=I-k8TqjmSbcQ7kNvwHtlPIW&amp;_nc_oc=AdrMw5eEqo7EEtmoFT7fpOWSgv7V-KxvyVzBWqm5lI30FoBo-83J2-U9Jb2scF8LQ3w&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=NhHZMbOOP1wxYHBqrmseIg&amp;_nc_ss=7e3ba&amp;oh=00_AQIAIWfch2wrySwPcs8mmWnfOPR2nwd9qoKxPqpQgDvmNQ&amp;oe=6AB89399
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/820374106_1049426904596138_779138823588338757_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MTg5MTI3Nzc2MzIwNTA3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=I-k8TqjmSbcQ7kNvwHtlPIW&amp;_nc_oc=AdrMw5eEqo7EEtmoFT7fpOWSgv7V-KxvyVzBWqm5lI30FoBo-83J2-U9Jb2scF8LQ3w&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=NhHZMbOOP1wxYHBqrmseIg&amp;_nc_ss=7e3ba&amp;oh=00_AQKHpVg976CBTfKLc9_YRq1REgdCjXcj_7B6ISI5Z_-h-Q&amp;oe=6AB89399
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwGkZ7xu&amp;_nc_oc=AdoRUbV0-oacb_ovWLiavVtHGVQBCD-_s4Oj1SptFb3J-Myfkoirb7EQHPlS-vTw3Lg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKydMHQBFTkBxCFT1N8CtDyuHkKzdUf_Z_Q0EnoaXqZqA&amp;oe=6AB89799
+https://l.instagram.com/?u=https%3A%2F%2Fats.rippling.com%2Frippling%2Fjobs%2Ff9de04c3-e2c5-41f9-8e46-a0684707f89d%3F_gl%3D1%252Aw2k05b%252A_gcl_au%252AMTg3NzcwNTIyNy4xNzkwMDkwMzM2%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeCIhow2tRHYJvwwOt_XCsMzTiKDle3vlbKqGjRqquUXzJPmOwhmFgMSG0jmA_aem_wK9vtUGs5o-TNfsFnTubIQ&amp;e=AUC4D3t26WzH6pKd3wyQxLo4BHkUht3ugtXbVzwk9MmlLuix351By-NoCMHX_ZGftvF6iET5jZCSmqgWOfVBH_DkyE-Mzpost6SPyhRohg
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQMUL_e5k_wqP3ryEehDkePBdNzo4xdIUVtA5KZEbzj6OyLZNE5r6ITediFWccNOjvGX12M0QaYrmhiKIOUob79mQ98gBEHd4zSmjRg.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=c0Nyq6B2st8Q7kNvwEngCVT&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc5MDU3MTE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=5d9f0601d1f0b4a5&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0NCNDcxMThDRjg4QjE3ODIwNzA1RDk5MkM3RDA5QkE5X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkl-eq17ahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=NhHZMbOOP1wxYHBqrmseIg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIw_8C5bXMJPMiPP2PbBrp-KWYxyqIGgC-yOeRACoSM6Q&amp;oe=6AB49B7A</t>
+        </is>
+      </c>
+      <c r="O108" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P108" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q108" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109" ht="45" customHeight="1">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>600d322e069382bb2d08</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:59:40.885695+00:00</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:23:47+00:00</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr"/>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern -</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>Seattle, San Francisco, New York</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="inlineStr"/>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>https://ats.rippling.com/rippling/jobs/a07e4e46-3721-4934-b57b-0d58412e22ba</t>
+        </is>
+      </c>
+      <c r="L109" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern -
+Backend Focused -
+Summer 2027
+sta, Engineering
+©) San Francisco, CA
+©) Seattle, WA
+(©) New York, NY
+Share on:
+ink £ Xe
+@ ATS.RIPPLING.COM
+About Rippling
+Rippling gives businesse ace to run HR, IT,
+and Finance. It brings together all of the workforce
+systems that are normally scattered across a
+company, like payroll, expenses, benefits, and
+computers. For the first time ever, you can manage
+and automate every part of the employee lifecycle
+in a single system.
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/820542753_1834426071248979_3345889056115348215_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MTg5MjAwOTU1MTgzMzc1MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=7zk3xomYYxwQ7kNvwHrFw4R&amp;_nc_oc=AdqeoqOXV15vw47N674NDQ-TFz1UA-KBCKVzqSbzZmhMijkwiX_aM_yXddHjFEF3iSs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=NhHZMbOOP1wxYHBqrmseIg&amp;_nc_ss=7e3ba&amp;oh=00_AQLZ4qqCF1vMnqcE-dSYfOW3kpt-F8oAzAe6jyCF4cNe5A&amp;oe=6AB8B164
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/820542753_1834426071248979_3345889056115348215_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MTg5MjAwOTU1MTgzMzc1MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=7zk3xomYYxwQ7kNvwHrFw4R&amp;_nc_oc=AdqeoqOXV15vw47N674NDQ-TFz1UA-KBCKVzqSbzZmhMijkwiX_aM_yXddHjFEF3iSs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=NhHZMbOOP1wxYHBqrmseIg&amp;_nc_ss=7e3ba&amp;oh=00_AQJrBOVcchhnuVUA0TmDT_wryufb9sOt9SYJ2dmoyWB5uQ&amp;oe=6AB8B164
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwGkZ7xu&amp;_nc_oc=AdoRUbV0-oacb_ovWLiavVtHGVQBCD-_s4Oj1SptFb3J-Myfkoirb7EQHPlS-vTw3Lg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKydMHQBFTkBxCFT1N8CtDyuHkKzdUf_Z_Q0EnoaXqZqA&amp;oe=6AB89799
+https://l.instagram.com/?u=https%3A%2F%2Fats.rippling.com%2Frippling%2Fjobs%2Fa07e4e46-3721-4934-b57b-0d58412e22ba%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaficSyeKEKoL9frAD6t5jWHjNUusEGuOC2hzdOybi2QQb38Vn-Wy_J3h3FTWw_aem_ovXb8eneJQwtfrLwG1vxCw&amp;e=AUB9WFtF70DqOerAhH6RT0Gt4YL4YTHEgnt5E9IEq9-bEw5zSLvnPHr2E13rD8dvZ__leVcuavlM2E9-Yx9gUNWAGACoZRCN_nyRYNkiIA
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQO8M-QzBtFGHqlzjkDI5nDpuCdmgujpimjwl1Kgml6XNTUEVTlaMPGL90xTm9a5_JM0vIHFX285oLaYUTcpGuBi0VOINFXHcBa55CA.mp4?_nc_cat=104&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=kt9nN3jGFPkQ7kNvwG4rhXP&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc5MDU4Nzk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=fb5e3fa1d0819fbb&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzlDNDZFOTg4MkUwRjA3MUU3NTgyMEI1NDI0NjczNzk5X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk_4LL2LahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=NhHZMbOOP1wxYHBqrmseIg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQL1SatrYfEtoR8hJ108cTMubqOwWLzrb3j1pSRi5ka0pA&amp;oe=6AB4A4D9</t>
+        </is>
+      </c>
+      <c r="O109" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P109" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q109" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R109" s="3" t="inlineStr"/>
+    </row>
+    <row r="110" ht="45" customHeight="1">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>e4e7b342549f08ab6859</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:59:42.638987+00:00</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:29:13+00:00</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Rivian</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>Rivian — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>Spring 2027</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="inlineStr"/>
+      <c r="J110" s="3" t="inlineStr"/>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.rivian.com/careers-home/jobs?keywords=intern&amp;sortBy=relevance&amp;page=1</t>
+        </is>
+      </c>
+      <c r="L110" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
+          <t>@ careers.rivian.com C:
+Instagram
+Software Engineering Intern - =
+Product Development Portal
+(Spring Co-Op)
+Location
+Palo Alto, California
+US
+Category
+Internships &amp; Early Career
+Apply Now
+a: Y, TALIA Ar NHINJTAALIAITS. Ye
+(Sa j \i | 8 DB, | i | | | \ \} | \] yi a Q + {
+Os f VUINU UT TIVIFAIN TIN : uw F \
+Software Engi Intern -
+Enterprise App ns
+(Spring 2027 Co-Op
+Location
+Normal, Illinois
+US
+Category
+Internships &amp; Early Career
+Ea
+Apply Now
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/800282735_1117752914104611_1867163155253733931_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MTg5NDc1MDkzMjYzMDg4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=hew0jmQvHBAQ7kNvwEJhIdc&amp;_nc_oc=AdqjZhh4XSJUGU8_KNI9aB8zqSg9IOQcunuyNrIZehK1aLVwGqhNYcM8bCuas8SZsKQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=NhHZMbOOP1wxYHBqrmseIg&amp;_nc_ss=7e3ba&amp;oh=00_AQKfSNftmv3f6A5DWNTfngW79JQL98BkOuO9Ikjw-7q7fA&amp;oe=6AB8BC75
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/800282735_1117752914104611_1867163155253733931_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MTg5NDc1MDkzMjYzMDg4OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=hew0jmQvHBAQ7kNvwEJhIdc&amp;_nc_oc=AdqjZhh4XSJUGU8_KNI9aB8zqSg9IOQcunuyNrIZehK1aLVwGqhNYcM8bCuas8SZsKQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=NhHZMbOOP1wxYHBqrmseIg&amp;_nc_ss=7e3ba&amp;oh=00_AQJMstyWW89mPy9H96je-1sEvIb0ya0o2YOL77CKyb1EVg&amp;oe=6AB8BC75
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwGkZ7xu&amp;_nc_oc=AdoRUbV0-oacb_ovWLiavVtHGVQBCD-_s4Oj1SptFb3J-Myfkoirb7EQHPlS-vTw3Lg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKydMHQBFTkBxCFT1N8CtDyuHkKzdUf_Z_Q0EnoaXqZqA&amp;oe=6AB89799
+https://l.instagram.com/?u=https%3A%2F%2Fcareers.rivian.com%2Fcareers-home%2Fjobs%3Fkeywords%3Dintern%26sortBy%3Drelevance%26page%3D1%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacZ_Bg3TvgdaLhZYHznn5-tm5j3N4PkuPAjDVvHFb8qNHI0-WbvZ2qCd4e8eQ_aem_QQfZuhQ2aJKVQOi2QKx3TA&amp;e=AUAqPD72_cIiDJAH4xBIUlroleNh_6XWE8r_6VA7rglMkW4klF5_TVOZHoM9rt-rZHv1LwDE9eADntcMJNcOVWmzWDe2KbchQ8PDvKA-mA
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQM5TLP74B1d7F7TOhetxJnq4RIFv77Yd-I2mR3ldzreTNNIFdXxuizTr3m8UqJQYQIvStoQn2um8x1r09M7DUkFB6B9FRHkqKeEhlM.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=u7wtrVPFLMkQ7kNvwFDlI4x&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc5MDY3MTY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=ff25f36441d62db6&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzFFNEY0QURDQUUzMjlBNUFDOEY5RjU1OUU4MzRDMkIzX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk7J_p3rahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=NhHZMbOOP1wxYHBqrmseIg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLMOMxZVL6eZ6whV0c6jtdAFzbpt5mF52xEOVl5IV4CCg&amp;oe=6AB4C77A</t>
+        </is>
+      </c>
+      <c r="O110" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P110" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q110" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111" ht="45" customHeight="1">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>16f14cd91755c215231d</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:59:45.930748+00:00</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:56:26+00:00</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr"/>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>Program Internship Jobs and</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr"/>
+      <c r="H111" s="3" t="inlineStr"/>
+      <c r="I111" s="3" t="inlineStr"/>
+      <c r="J111" s="3" t="inlineStr"/>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>https://www.att.jobs/en/job/dallas/at-and-t-technology-development-program-internship/117/100954809776</t>
+        </is>
+      </c>
+      <c r="L111" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
+          <t>AT&amp;T Technology Development
+Program Internship Jobs and
+Careers in Dallas at AT&amp;T
+Build a more connected world ina
+telecommunications career at AT&amp;T.
+Learn more and apply for our AT&amp;T
+Technology Development Program
+Internship in Dallas here.
+Hey sudo AT&amp;T just dropped
+their Technology Development
+Internship, Rising Seniors
+https://
+/dallas/
+“develo @
+thank you!!
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/818584104_28306411085648115_2096723024411024773_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MTkwODQzNTc5Njg2Mjk0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=7K5rfdn4OgMQ7kNvwFChKL0&amp;_nc_oc=AdoHmziGNtpSnE9An7jYlP6RlgYOg-pESgbxNyEeAqVThQY_9QXI4VvVX2B6Ez98RRs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=NhHZMbOOP1wxYHBqrmseIg&amp;_nc_ss=7e3ba&amp;oh=00_AQLomWNN9-AluoX22EtAv2AczL2mEO0YXwTrV1E4VdhCZA&amp;oe=6AB89508
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/818584104_28306411085648115_2096723024411024773_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MTkwODQzNTc5Njg2Mjk0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=7K5rfdn4OgMQ7kNvwFChKL0&amp;_nc_oc=AdoHmziGNtpSnE9An7jYlP6RlgYOg-pESgbxNyEeAqVThQY_9QXI4VvVX2B6Ez98RRs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=NhHZMbOOP1wxYHBqrmseIg&amp;_nc_ss=7e3ba&amp;oh=00_AQI0y4ZIsjQwRMWSr5C85rauqonFh72LPKaTMf8hbENP8A&amp;oe=6AB89508
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=2mRME1i9JoMQ7kNvwGkZ7xu&amp;_nc_oc=AdoRUbV0-oacb_ovWLiavVtHGVQBCD-_s4Oj1SptFb3J-Myfkoirb7EQHPlS-vTw3Lg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKydMHQBFTkBxCFT1N8CtDyuHkKzdUf_Z_Q0EnoaXqZqA&amp;oe=6AB89799
+https://l.instagram.com/?u=https%3A%2F%2Fwww.att.jobs%2Fen%2Fjob%2Fdallas%2Fat-and-t-technology-development-program-internship%2F117%2F100954809776%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaftU1xHSA4H_Uzkmyx56SMlLmoV2bLXXSMsAW6EXF6ZSkU03qwkNznECNl50g_aem_d7rKqCEdTgvME-hyizYJGQ&amp;e=AUCJEAPFH2chBjJbe2bXjXKGjRMrLcDevGFuG8j0qPJlLIurmV95-1D04pl8igU3hlQi38Cra6hWUUCgm2C0fv-ifLOiWC5KVwLu4i4vEA
+https://scontent-lax3-2.cdninstagram.com/o1/v/t2/f2/m78/AQN1d3WRaTEoA66AURS9Z2WEusGG1jKLXC5Cg3psHo_xLj0glhdB1VrRdkYCVrqRYAJvw2ozlNySXLlxYZprddQtL3EliGY4ej5I3AI.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ohc=kYrcGwPKb3wQ7kNvwE97er8&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc5MDk3NjE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=4bf851342a3bab3c&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzY1RTAxREFEMjFCQzQwM0FCODFERUZFQTJDRTg5NEE1X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk-ZfB9bahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=NhHZMbOOP1wxYHBqrmseIg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIB4zhvr9Ewsbpzx_Quq5cw56IbCqx8kvmxHztna0yPPQ&amp;oe=6AB492E5</t>
+        </is>
+      </c>
+      <c r="O111" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P111" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q111" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R111" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R106"/>
+  <autoFilter ref="A1:R111"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -10671,6 +11164,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId195"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId206"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$115</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R111"/>
+  <dimension ref="A1:R115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10475,7 +10475,7 @@
     <row r="107" ht="45" customHeight="1">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>74d89fdbfe4901adf9a3</t>
+          <t>439223ee895153925685</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -10488,7 +10488,7 @@
           <t>2026-09-22T15:20:18+00:00</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr"/>
+      <c r="D107" s="3" t="n"/>
       <c r="E107" s="3" t="inlineStr">
         <is>
           <t>syst Rippling Fulstack a intern</t>
@@ -10499,7 +10499,7 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G107" s="3" t="inlineStr"/>
+      <c r="G107" s="3" t="n"/>
       <c r="H107" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
@@ -10510,7 +10510,7 @@
           <t>Seattle, San Francisco, New York</t>
         </is>
       </c>
-      <c r="J107" s="3" t="inlineStr"/>
+      <c r="J107" s="3" t="n"/>
       <c r="K107" s="4" t="inlineStr">
         <is>
           <t>https://ats.rippling.com/rippling/jobs/f64b6158-9534-4bab-9457-45556166b262</t>
@@ -10566,12 +10566,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R107" s="3" t="inlineStr"/>
+      <c r="R107" s="3" t="n"/>
     </row>
     <row r="108" ht="45" customHeight="1">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>e56181e2f123236c7dec</t>
+          <t>547fb6d79f668b7145d0</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -10584,10 +10584,10 @@
           <t>2026-09-22T15:22:20+00:00</t>
         </is>
       </c>
-      <c r="D108" s="3" t="inlineStr"/>
+      <c r="D108" s="3" t="n"/>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>@ RIPPLING MLE SWE INTERN</t>
+          <t>Software Engineering, Machine Learning / AI</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
@@ -10610,7 +10610,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="J108" s="3" t="inlineStr"/>
+      <c r="J108" s="3" t="n"/>
       <c r="K108" s="4" t="inlineStr">
         <is>
           <t>https://ats.rippling.com/rippling/jobs/f9de04c3-e2c5-41f9-8e46-a0684707f89d?_gl=1%2Aw2k05b%2A_gcl_au%2AMTg3NzcwNTIyNy4xNzkwMDkwMzM2</t>
@@ -10666,12 +10666,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R108" s="3" t="inlineStr"/>
+      <c r="R108" s="3" t="n"/>
     </row>
     <row r="109" ht="45" customHeight="1">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>600d322e069382bb2d08</t>
+          <t>81c99f9d29fb64f8aeaa</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -10684,7 +10684,7 @@
           <t>2026-09-22T15:23:47+00:00</t>
         </is>
       </c>
-      <c r="D109" s="3" t="inlineStr"/>
+      <c r="D109" s="3" t="n"/>
       <c r="E109" s="3" t="inlineStr">
         <is>
           <t>Software Engineer Intern -</t>
@@ -10710,7 +10710,7 @@
           <t>Seattle, San Francisco, New York</t>
         </is>
       </c>
-      <c r="J109" s="3" t="inlineStr"/>
+      <c r="J109" s="3" t="n"/>
       <c r="K109" s="4" t="inlineStr">
         <is>
           <t>https://ats.rippling.com/rippling/jobs/a07e4e46-3721-4934-b57b-0d58412e22ba</t>
@@ -10768,12 +10768,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R109" s="3" t="inlineStr"/>
+      <c r="R109" s="3" t="n"/>
     </row>
     <row r="110" ht="45" customHeight="1">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>e4e7b342549f08ab6859</t>
+          <t>d57d0c1f3c0c0fcdccd0</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -10811,8 +10811,8 @@
           <t>Spring 2027</t>
         </is>
       </c>
-      <c r="I110" s="3" t="inlineStr"/>
-      <c r="J110" s="3" t="inlineStr"/>
+      <c r="I110" s="3" t="n"/>
+      <c r="J110" s="3" t="n"/>
       <c r="K110" s="4" t="inlineStr">
         <is>
           <t>https://careers.rivian.com/careers-home/jobs?keywords=intern&amp;sortBy=relevance&amp;page=1</t>
@@ -10876,12 +10876,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R110" s="3" t="inlineStr"/>
+      <c r="R110" s="3" t="n"/>
     </row>
     <row r="111" ht="45" customHeight="1">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>16f14cd91755c215231d</t>
+          <t>e095ec879229132d02d8</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -10894,7 +10894,7 @@
           <t>2026-09-22T15:56:26+00:00</t>
         </is>
       </c>
-      <c r="D111" s="3" t="inlineStr"/>
+      <c r="D111" s="3" t="n"/>
       <c r="E111" s="3" t="inlineStr">
         <is>
           <t>Program Internship Jobs and</t>
@@ -10905,10 +10905,10 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G111" s="3" t="inlineStr"/>
-      <c r="H111" s="3" t="inlineStr"/>
-      <c r="I111" s="3" t="inlineStr"/>
-      <c r="J111" s="3" t="inlineStr"/>
+      <c r="G111" s="3" t="n"/>
+      <c r="H111" s="3" t="n"/>
+      <c r="I111" s="3" t="n"/>
+      <c r="J111" s="3" t="n"/>
       <c r="K111" s="4" t="inlineStr">
         <is>
           <t>https://www.att.jobs/en/job/dallas/at-and-t-technology-development-program-internship/117/100954809776</t>
@@ -10963,10 +10963,377 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R111" s="3" t="inlineStr"/>
+      <c r="R111" s="3" t="n"/>
+    </row>
+    <row r="112" ht="45" customHeight="1">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>b1ea7841f3bd5c329cb7</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T22:17:32.564176+00:00</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T19:51:07+00:00</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr"/>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>oS oy) Apply Now &gt;</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr"/>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="inlineStr"/>
+      <c r="J112" s="3" t="inlineStr"/>
+      <c r="K112" s="4" t="inlineStr">
+        <is>
+          <t>https://mycareer.verizon.com/jobs/r-1101167/verizon-network-and-technology-ai-science-summer-2027-internship?source=zero2sudo</t>
+        </is>
+      </c>
+      <c r="L112" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
+          <t>x @ mycareer.verizon.com G
+Instagram *
+verizon eo =
+Intern
+Verizon Network and
+Technology: Al
+Science Summer
+2027 Internship
+Basking Ridge, New Jersey
+Job ID: R-1101167
+Apply prior to the end date:
+September 26, 2026
+When you we
+You want more out of a career. A place to
+oS oy) Apply Now &gt;
+https://scontent-arn2-1.cdninstagram.com/v/t51.71878-15/820852783_1094819902958333_1575900696699432286_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MjAyNjcyODc3NTEyMDI4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Lqi1IU9kmJsQ7kNvwGwWSfT&amp;_nc_oc=Adp29al9YDhLaSkHGjRMcIr1MkK-8paJRiD4_a3bdRZYki3QUp53ueWZq2NclwD-0eA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-arn2-1.cdninstagram.com&amp;_nc_gid=pUZT6Zxvz4PGT-H60bGh7g&amp;_nc_ss=7a3ba&amp;oh=00_AQIm62SU1oWPtLubdFVhFHq1Wn65HDkcrsvKoLtktWaYRA&amp;oe=6AB8E125
+https://scontent-arn2-1.cdninstagram.com/v/t51.71878-15/820852783_1094819902958333_1575900696699432286_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MjAyNjcyODc3NTEyMDI4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Lqi1IU9kmJsQ7kNvwGwWSfT&amp;_nc_oc=Adp29al9YDhLaSkHGjRMcIr1MkK-8paJRiD4_a3bdRZYki3QUp53ueWZq2NclwD-0eA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-arn2-1.cdninstagram.com&amp;_nc_gid=pUZT6Zxvz4PGT-H60bGh7g&amp;_nc_ss=7a3ba&amp;oh=00_AQL36sbJr1qi3_cbdplf_P43JiX-RGwcY0HfE96qBRSF-A&amp;oe=6AB8E125
+https://scontent-arn2-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLmRqYW5nby4xMDgwLmMyIn0&amp;_nc_ht=scontent-arn2-1.cdninstagram.com&amp;_nc_cat=103&amp;_nc_oc=Q6cZ2gFtyOKsqHJVFYHyYA-S1aBVIIKf9pAKNu8Ri8qmi2-QYJyjey_KaawjXxvVhMlWXsI&amp;_nc_ohc=F7Gp-eT3E5gQ7kNvwHIRh7k&amp;_nc_gid=pUZT6Zxvz4PGT-H60bGh7g&amp;edm=ANmP7GQBAAAA&amp;ccb=7-5&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;oh=00_AQJ_YjyAl2ZuenJ-S1cbssSn6j-l4r1KbGeqTpAGlzBYcw&amp;oe=6AB8CFD9&amp;_nc_sid=982cc7
+https://l.instagram.com/?u=https%3A%2F%2Fmycareer.verizon.com%2Fjobs%2Fr-1101167%2Fverizon-network-and-technology-ai-science-summer-2027-internship%2F%3Fsource%3Dzero2sudo%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacY_4VNqGkkcrMHWPdr08TjXJNXXCtUK7H1Bw226UA0vGKKaMkaZKZyx4JXnA_aem__9ZIFJia5qxzjb7M3VGtwQ&amp;e=AUDLz9Br1wdxXquBxxqkKFDb_5TZOGrr9G7N1Eli5iNseJOA-0ynxSdlS6o7A9a0NRd6EDVTzMJYYhlMX_zyIFq4XX6Ixy7Ag4nCIhSEIQ
+https://scontent-arn2-1.cdninstagram.com/o1/v/t2/f2/m78/AQMK8Tt9RotztDwgjsQjYk_ujqvMZbEWMidD91wv-l_K3lvWpWh6zncxtJbCG1HGjAj8L1Ihyl0i5ijPvnzUjkwK1klg-5V3OxhN3Xo.mp4?_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-arn2-1.cdninstagram.com&amp;_nc_ohc=aQ9fSHPltEYQ7kNvwEdpI8N&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc5MzQyNDE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=9493fa1ba6034b52&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzlGNEI4MjM3QUU4QzA5MjdGQjFDQjU5MDdGQThBRjlFX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkmZHzq7ihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=pUZT6Zxvz4PGT-H60bGh7g&amp;_nc_ss=7a3ba&amp;_nc_zt=28&amp;oh=00_AQLGiKDbj5F2yzsTgzpkRN75Oxa0uFOvS3X5hIGHLJdXig&amp;oe=6AB4D9A3</t>
+        </is>
+      </c>
+      <c r="O112" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P112" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q112" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R112" s="3" t="inlineStr"/>
+    </row>
+    <row r="113" ht="45" customHeight="1">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>48bd76785961866cb64c</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T22:17:33.847443+00:00</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T19:52:44+00:00</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>NFA</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>NFA — Internship</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr"/>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr"/>
+      <c r="J113" s="3" t="inlineStr"/>
+      <c r="K113" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.nfa.org/job/Chicago-Summer-2027-Information-Security-Intern-IL-60606/1432516700</t>
+        </is>
+      </c>
+      <c r="L113" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027 Information
+Security Intern
+Cybersecurity for Finance / Trading!
+https://scontent-arn2-1.cdninstagram.com/v/t51.71878-15/816615043_4570928839831252_6758590330469209055_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MjAyNzM2MDA1MjU1NzE2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=NbYnPBB_1q4Q7kNvwGLg9e7&amp;_nc_oc=AdpqRecTTKWRldZQUyweAvckpbW4QinCqJxLNsAhpI0GvorI2g6LsabtCWzfKQ8RfoY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-arn2-1.cdninstagram.com&amp;_nc_gid=pUZT6Zxvz4PGT-H60bGh7g&amp;_nc_ss=7a3ba&amp;oh=00_AQL_RJG7P60uVanDEYtPe4kxpi34Zig9blHq6j3X7KZCGQ&amp;oe=6AB8D7EE
+https://scontent-arn2-1.cdninstagram.com/v/t51.71878-15/816615043_4570928839831252_6758590330469209055_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MjAyNzM2MDA1MjU1NzE2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=NbYnPBB_1q4Q7kNvwGLg9e7&amp;_nc_oc=AdpqRecTTKWRldZQUyweAvckpbW4QinCqJxLNsAhpI0GvorI2g6LsabtCWzfKQ8RfoY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-arn2-1.cdninstagram.com&amp;_nc_gid=pUZT6Zxvz4PGT-H60bGh7g&amp;_nc_ss=7a3ba&amp;oh=00_AQKkxIXc2Wdxb1WDsl5pI4x_SORvbyIrm_Y6mRbH15TwIw&amp;oe=6AB8D7EE
+https://scontent-arn2-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLmRqYW5nby4xMDgwLmMyIn0&amp;_nc_ht=scontent-arn2-1.cdninstagram.com&amp;_nc_cat=103&amp;_nc_oc=Q6cZ2gFtyOKsqHJVFYHyYA-S1aBVIIKf9pAKNu8Ri8qmi2-QYJyjey_KaawjXxvVhMlWXsI&amp;_nc_ohc=F7Gp-eT3E5gQ7kNvwHIRh7k&amp;_nc_gid=pUZT6Zxvz4PGT-H60bGh7g&amp;edm=ANmP7GQBAAAA&amp;ccb=7-5&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;oh=00_AQJ_YjyAl2ZuenJ-S1cbssSn6j-l4r1KbGeqTpAGlzBYcw&amp;oe=6AB8CFD9&amp;_nc_sid=982cc7
+https://l.instagram.com/?u=https%3A%2F%2Fcareers.nfa.org%2Fjob%2FChicago-Summer-2027-Information-Security-Intern-IL-60606%2F1432516700%2F%3Futm_source%3Dzero2sudo%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeAmHCUF4EPaZ0Asa_un1VY9FI6p5W38RjdHGV_Y4RY7G9jEULPyfKQxC5BlA_aem__KC9vvWDvc1AYUowzacY9g&amp;e=AUBoj9XtbiUYd3cBC_aL55l6hV889puOQrNa8xcV2rwfg_hvu_4vw2ROuOyT7dXQHhkDxbq1u3vcyTSxi3XZlaAfa4JGsmdVZCBLsc58dQ
+https://scontent-arn2-1.cdninstagram.com/o1/v/t2/f2/m78/AQMCZ7i5_srf69tSEhmPeO2kmAVu1yD1YcCt_0Jrod8QirZRipQioMb7u_GTteC13EUuLmNBDLF6ueEBiP1j3vrNGpwZAlsTrPjgka4.mp4?_nc_cat=110&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-arn2-1.cdninstagram.com&amp;_nc_ohc=gFJzmCURTzsQ7kNvwFj9Q9w&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc5MzQ2MjI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=d01609af6ab64a55&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzVGNEQxRTc5RjE0OTk0MzA1NTg1MkM3NzlDQjAzOThDX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk_r3errihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=pUZT6Zxvz4PGT-H60bGh7g&amp;_nc_ss=7a3ba&amp;_nc_zt=28&amp;oh=00_AQIIGMXhBm96ZJ6LNGAWmMy4BQkAca4iIl_lkxp8HdBY4A&amp;oe=6AB4F7FF</t>
+        </is>
+      </c>
+      <c r="O113" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P113" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q113" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114" ht="45" customHeight="1">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>df0e03af589553edf441</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T22:17:38.976830+00:00</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T19:56:52+00:00</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr"/>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr"/>
+      <c r="J114" s="3" t="inlineStr"/>
+      <c r="K114" s="4" t="inlineStr">
+        <is>
+          <t>https://ats.rippling.com/rippling/jobs/f255bf03-9173-4c0a-8a18-7cc43c27ded8?jr_id=6ab29b0778c69ff506c3f2d0</t>
+        </is>
+      </c>
+      <c r="L114" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
+          <t>Yooo | know you posted the rest
+of the ripling ones but the ds
+intern also opened
+Data Science Intern 'r 2027 |
+Current Openings
+About the role Here at Ripprmg, we
+believe in our early talent's potential,
+experience and aspirations. Our mission i...
+G5.
+https://scontent-arn2-1.cdninstagram.com/v/t51.71878-15/805485707_1398070225184686_141309978699025803_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5MjAyOTUxMjg1NDU2NzY3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=M-VlBruBcswQ7kNvwGnKIfX&amp;_nc_oc=AdpM8rcoXizmLVz6Q-GbBOc9LkBGunrXfVZtbL-l3YZmGmAbxj1cM5fG3EjrErpZhrc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-arn2-1.cdninstagram.com&amp;_nc_gid=pUZT6Zxvz4PGT-H60bGh7g&amp;_nc_ss=7a3ba&amp;oh=00_AQL8XWuQoCs9LEwcPbTddflN1am4HxtEAYIJ-ULFFu6lgA&amp;oe=6AB8E709
+https://scontent-arn2-1.cdninstagram.com/v/t51.71878-15/805485707_1398070225184686_141309978699025803_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5MjAyOTUxMjg1NDU2NzY3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=M-VlBruBcswQ7kNvwGnKIfX&amp;_nc_oc=AdpM8rcoXizmLVz6Q-GbBOc9LkBGunrXfVZtbL-l3YZmGmAbxj1cM5fG3EjrErpZhrc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-arn2-1.cdninstagram.com&amp;_nc_gid=pUZT6Zxvz4PGT-H60bGh7g&amp;_nc_ss=7a3ba&amp;oh=00_AQKo_nGtfMzpf_aw6a1FpisydPuwXeqD4dSp1_5CfG-6rA&amp;oe=6AB8E709
+https://scontent-arn2-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLmRqYW5nby4xMDgwLmMyIn0&amp;_nc_ht=scontent-arn2-1.cdninstagram.com&amp;_nc_cat=103&amp;_nc_oc=Q6cZ2gFtyOKsqHJVFYHyYA-S1aBVIIKf9pAKNu8Ri8qmi2-QYJyjey_KaawjXxvVhMlWXsI&amp;_nc_ohc=F7Gp-eT3E5gQ7kNvwHIRh7k&amp;_nc_gid=pUZT6Zxvz4PGT-H60bGh7g&amp;edm=ANmP7GQBAAAA&amp;ccb=7-5&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;oh=00_AQJ_YjyAl2ZuenJ-S1cbssSn6j-l4r1KbGeqTpAGlzBYcw&amp;oe=6AB8CFD9&amp;_nc_sid=982cc7
+https://l.instagram.com/?u=https%3A%2F%2Fats.rippling.com%2Frippling%2Fjobs%2Ff255bf03-9173-4c0a-8a18-7cc43c27ded8%3Fjr_id%3D6ab29b0778c69ff506c3f2d0%26fbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaemVJncEFREhV5fwvYoPBcPw6chICVnMPtJS-UZpc8WsfefMSmXm7UO5EIGWw_aem_uLPgGanx3JCosDPKGthojg&amp;e=AUCSvZ6iePk0TdKA6f0jmroaYUjc7t3mfUxetKIsjbP2dgclmu92pbHtel7sj9EGbY0ym45cOM3wCmcsDHjBMSI6DZKyunV1MrcGBJ8B1Q
+https://scontent-arn2-1.cdninstagram.com/o1/v/t2/f2/m78/AQOCZRRli5RkgKX0ydCdNiOn1HOPUAsyfGF0il8rZxRtttY_lQyMJ5qEXkshCCWWq5EwwjdnM4ucyANYe39H3qVT2_WusnQ6qaOQpxE.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-arn2-1.cdninstagram.com&amp;_nc_ohc=ZJ7MSTTq8NUQ7kNvwFoJqWG&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc5MzUwNjA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=c75507bb2b529b01&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzAwNDA1OTJBQjVBQjJEQkJBRTU5RUMzRjdGQjg4QjgyX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk5JiAsrihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=pUZT6Zxvz4PGT-H60bGh7g&amp;_nc_ss=7a3ba&amp;_nc_zt=28&amp;oh=00_AQI2Wi3TRVKFQ0Eo97-eG3mxBm0OqJvrm0S902aUurUt8g&amp;oe=6AB4E1F5</t>
+        </is>
+      </c>
+      <c r="O114" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P114" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q114" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R114" s="3" t="inlineStr"/>
+    </row>
+    <row r="115" ht="45" customHeight="1">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>861996c259e259e638f1</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T22:17:41.579266+00:00</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22T20:30:26+00:00</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Optiverprivate</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>Optiverprivate — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="J115" s="3" t="inlineStr"/>
+      <c r="K115" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/optiverprivate/jobs/8784302002</t>
+        </is>
+      </c>
+      <c r="L115" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
+          <t>@ job-boards.greenhouse.io C;:
+Optiver A
+&lt; Back to jobs
+New
+Software Engineer
+Co-Op (January -
+April 2027)
+© Chicago, Illinois, United States
+Applications will be open for this role
+(7) JOB-BOARDS.GREENHOUSE.IO
+As a Software Engined}Intern in our Coop
+(January - April 20 Il work side-by-
+side with your mento eammates to
+build real-world applications that powe
+global trading firm. Your projects will be
+scoped based on your team’s real needs —
+https://scontent-arn2-1.cdninstagram.com/v/t51.71878-15/820852799_1751662929457684_8841211562157258109_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5MjA0NjQxNjYyMTEzODgxMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=8GGJ0X-CAPsQ7kNvwGnWvS9&amp;_nc_oc=AdpkUBDufDeMvkKSPvKIATjdnA9ds5hSCJLQR31QvAoPz2JhudlC4074BToifIvI8Uo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-arn2-1.cdninstagram.com&amp;_nc_gid=pUZT6Zxvz4PGT-H60bGh7g&amp;_nc_ss=7a3ba&amp;oh=00_AQKKHOTUnQiLtE80OBlTwB6yNl9x77A43T4KRD-VGouVzw&amp;oe=6AB8DD1F
+https://scontent-arn2-1.cdninstagram.com/v/t51.71878-15/820852799_1751662929457684_8841211562157258109_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5MjA0NjQxNjYyMTEzODgxMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=8GGJ0X-CAPsQ7kNvwGnWvS9&amp;_nc_oc=AdpkUBDufDeMvkKSPvKIATjdnA9ds5hSCJLQR31QvAoPz2JhudlC4074BToifIvI8Uo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-arn2-1.cdninstagram.com&amp;_nc_gid=pUZT6Zxvz4PGT-H60bGh7g&amp;_nc_ss=7a3ba&amp;oh=00_AQL9PdyuDiiUOzf2eVUw6UO1KunGd_HsScyV10OwXTNbqw&amp;oe=6AB8DD1F
+https://scontent-arn2-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLmRqYW5nby4xMDgwLmMyIn0&amp;_nc_ht=scontent-arn2-1.cdninstagram.com&amp;_nc_cat=103&amp;_nc_oc=Q6cZ2gFtyOKsqHJVFYHyYA-S1aBVIIKf9pAKNu8Ri8qmi2-QYJyjey_KaawjXxvVhMlWXsI&amp;_nc_ohc=F7Gp-eT3E5gQ7kNvwHIRh7k&amp;_nc_gid=pUZT6Zxvz4PGT-H60bGh7g&amp;edm=ANmP7GQBAAAA&amp;ccb=7-5&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;oh=00_AQJ_YjyAl2ZuenJ-S1cbssSn6j-l4r1KbGeqTpAGlzBYcw&amp;oe=6AB8CFD9&amp;_nc_sid=982cc7
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Foptiverprivate%2Fjobs%2F8784302002%3Ffbclid%3DPAcGRvZgJleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadFWRtlsqQdi_tjIRlYzs2AdURufVTVPzNDqQuw6zsQ1fEDGODBJAYnMgq7NA_aem_6VdZKratDoa6jxYC9Fu5vg&amp;e=AUCAiDXS43lkQlZwtV3_AdsOEaFRBJ6GlQ65F0Bo-AM9yy0zj8zfk1iagaOErbnTo3HRXN-JkaNBGInqNYhuXSwn8Mk_p3qSpsJk2nJsEA
+https://scontent-arn2-1.cdninstagram.com/o1/v/t2/f2/m78/AQNBk-lPKjkjPkyFXfCWIY8nb6oC2KignxfJy_zv2yiA5n7VLoBeYPdCokswunGfK83nfQfN8yXIUpzId8pZbHcgOcIirOQ9expAJlA.mp4?_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-arn2-1.cdninstagram.com&amp;_nc_ohc=VCdP1Pw5n4IQ7kNvwHXSOwc&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODc5Mzc3MTI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=917b57e8f48762d3&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzczNDIxQzQyMzFFRDJFOUY3NTdEMUI2ODY2RERCMEI1X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkoKvhxbihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=pUZT6Zxvz4PGT-H60bGh7g&amp;_nc_ss=7a3ba&amp;_nc_zt=28&amp;oh=00_AQKb_DVwD0SViAt-nvDX4X7eh1DoE8OUgg9m9Jlpm7noAA&amp;oe=6AB4EDCA</t>
+        </is>
+      </c>
+      <c r="O115" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P115" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q115" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R115" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R111"/>
+  <autoFilter ref="A1:R115"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -11174,6 +11541,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId205"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L114" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L115" r:id="rId214"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$149</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R115"/>
+  <dimension ref="A1:R149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10968,7 +10968,7 @@
     <row r="112" ht="45" customHeight="1">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>b1ea7841f3bd5c329cb7</t>
+          <t>69bcebe18c8299d97835</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -10981,7 +10981,7 @@
           <t>2026-09-22T19:51:07+00:00</t>
         </is>
       </c>
-      <c r="D112" s="3" t="inlineStr"/>
+      <c r="D112" s="3" t="n"/>
       <c r="E112" s="3" t="inlineStr">
         <is>
           <t>oS oy) Apply Now &gt;</t>
@@ -10992,14 +10992,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G112" s="3" t="inlineStr"/>
+      <c r="G112" s="3" t="n"/>
       <c r="H112" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I112" s="3" t="inlineStr"/>
-      <c r="J112" s="3" t="inlineStr"/>
+      <c r="I112" s="3" t="n"/>
+      <c r="J112" s="3" t="n"/>
       <c r="K112" s="4" t="inlineStr">
         <is>
           <t>https://mycareer.verizon.com/jobs/r-1101167/verizon-network-and-technology-ai-science-summer-2027-internship?source=zero2sudo</t>
@@ -11054,12 +11054,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R112" s="3" t="inlineStr"/>
+      <c r="R112" s="3" t="n"/>
     </row>
     <row r="113" ht="45" customHeight="1">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>48bd76785961866cb64c</t>
+          <t>7346c26ba3acfefe6ad1</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -11087,14 +11087,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G113" s="3" t="inlineStr"/>
+      <c r="G113" s="3" t="n"/>
       <c r="H113" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I113" s="3" t="inlineStr"/>
-      <c r="J113" s="3" t="inlineStr"/>
+      <c r="I113" s="3" t="n"/>
+      <c r="J113" s="3" t="n"/>
       <c r="K113" s="4" t="inlineStr">
         <is>
           <t>https://careers.nfa.org/job/Chicago-Summer-2027-Information-Security-Intern-IL-60606/1432516700</t>
@@ -11137,12 +11137,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R113" s="3" t="inlineStr"/>
+      <c r="R113" s="3" t="n"/>
     </row>
     <row r="114" ht="45" customHeight="1">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>df0e03af589553edf441</t>
+          <t>7528bfe73ad9a50fe971</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -11155,7 +11155,7 @@
           <t>2026-09-22T19:56:52+00:00</t>
         </is>
       </c>
-      <c r="D114" s="3" t="inlineStr"/>
+      <c r="D114" s="3" t="n"/>
       <c r="E114" s="3" t="inlineStr">
         <is>
           <t>Data Science</t>
@@ -11176,8 +11176,8 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="I114" s="3" t="inlineStr"/>
-      <c r="J114" s="3" t="inlineStr"/>
+      <c r="I114" s="3" t="n"/>
+      <c r="J114" s="3" t="n"/>
       <c r="K114" s="4" t="inlineStr">
         <is>
           <t>https://ats.rippling.com/rippling/jobs/f255bf03-9173-4c0a-8a18-7cc43c27ded8?jr_id=6ab29b0778c69ff506c3f2d0</t>
@@ -11226,12 +11226,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R114" s="3" t="inlineStr"/>
+      <c r="R114" s="3" t="n"/>
     </row>
     <row r="115" ht="45" customHeight="1">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>861996c259e259e638f1</t>
+          <t>0fc1ce74931c84aacbd7</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -11274,7 +11274,7 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="J115" s="3" t="inlineStr"/>
+      <c r="J115" s="3" t="n"/>
       <c r="K115" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/optiverprivate/jobs/8784302002</t>
@@ -11330,10 +11330,3327 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R115" s="3" t="inlineStr"/>
+      <c r="R115" s="3" t="n"/>
+    </row>
+    <row r="116" ht="45" customHeight="1">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>ccae5bed0ba1324ea1d6</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:08:09.843267+00:00</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T14:07:46+00:00</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>Smartrecruiters</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>Smartrecruiters — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I116" s="3" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="J116" s="3" t="inlineStr"/>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Wise/744000151030889-graduate-software-engineer</t>
+        </is>
+      </c>
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
+          <t>@ jobs.smartrecruiters.com C:
+27WISC
+Graduate Software Engineer
+Domain Tower 2, 10025 Alterra Parkway, Floor 23, Austin
+GH Employees work in a hybrid mode
+Full-time
+Compensation: up to USD 115,000 - yearly
+Company Description
+Wise is a global technology company, building the best
+way to move and manage the world’s money.
+Min fees. Max ease. Full speed.
+Whether people and businesses are sending money to
+another country, spending abroad, or making and
+receiving international payments, Wise is on a mission to
+make their lives easier and save them money.
+@ WISE NEW GRAD SWE
+More about our mission a
+Job Description
+Program start: September 7, 2027
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/819207921_1628606648850176_7755686052161200950_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MjU3ODUwNTE3ODY4NDY2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=xw-6tZoFf_8Q7kNvwHxg2A4&amp;_nc_oc=Adpg9byq7rAUcwYYBBxz9ziO2Hl586CaHTh_6_7OqNRpsQSkgT2Hp74Ap_uQGX32O24&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQKs8yfBmkk97Pf_Lyw-EqiYME6IFujkvw_FroB6o5SSkw&amp;oe=6ABAC161
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/819207921_1628606648850176_7755686052161200950_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MjU3ODUwNTE3ODY4NDY2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=xw-6tZoFf_8Q7kNvwHxg2A4&amp;_nc_oc=Adpg9byq7rAUcwYYBBxz9ziO2Hl586CaHTh_6_7OqNRpsQSkgT2Hp74Ap_uQGX32O24&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQLcpxZntKecm9ccmtwAxMKCMCJoxjuEtn7thXO2sz4Pxg&amp;oe=6ABAC161
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.smartrecruiters.com%2FWise%2F744000151030889-graduate-software-engineer%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeRM9MNtMx1bx3qMPaJYhen6ThHFyzJwa332UVXLxn7SBEMSB9b3O8OvpLutQ_aem_ucDR8nx2UjsjRYRPsN_FrA&amp;e=AUB6B-7USVoaFeGz4ev9MGX2YHgaXYn5O2k4elm00FeRGwSu3OiQXcbFklyPcnu3ejfBFiDckpl2MSDb90avlUJ33OBS6kiP9qjigoxJQQ
+https://scontent-nrt1-1.cdninstagram.com/o1/v/t2/f2/m78/AQOe69IpZ3VFZeWf-5cpCTUlGPkvyyG5sX4RuxvhoHZoIdeIxvPsenhcp-xZzo-E-8i2yQCu0FUsENOGU-5UqeN2Kk2cTV45es0wZrk.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_ohc=mEUzEUnT4rYQ7kNvwED881M&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwNDE4NjA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=42cf225d349765da&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzg2NENCQzQwOThGM0I4MDkxM0FGODE3OTdGNjZBOTlCX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbklM7czb6hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQL0O9m9J49trm4JZlPDFnM4YOJKPWdxhFNWsJbPuh-r4Q&amp;oe=6AB6C602</t>
+        </is>
+      </c>
+      <c r="O116" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P116" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q116" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R116" s="3" t="inlineStr"/>
+    </row>
+    <row r="117" ht="45" customHeight="1">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>fdb0fdf5b544a4410d39</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:08:12.504181+00:00</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T14:08:46+00:00</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>Amazon — Internship</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr"/>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr"/>
+      <c r="J117" s="3" t="inlineStr"/>
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.jobs/en/jobs/10557133/security-engineer-internship-2027-us</t>
+        </is>
+      </c>
+      <c r="L117" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
+          <t>x amazon.jobs C;:
+Instagram AS
+=  amazonjobs Q
+Security Engineer
+Internship -— 2027 (US)
+Job ID: 10557133 | Amazon.com Services LLC - A57
+Description
+Shape what comes next | Discover careers in
+Tech
+x. © AMAZON.JOBS
+systems, cloud servic stomer-facing
+Precuer that operate l scale?" This is an
+customers around the globe, y your work reaches
+) ae a oe an Y are | be ee eer ar Part
+https://scontent-nrt1-2.cdninstagram.com/v/t51.71878-15/821281881_2195167421096352_7527412408137440417_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MjU3OTAwOTM1OTQzMTkyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=MdKCtIuDCHgQ7kNvwE8jMTL&amp;_nc_oc=AdrNmiupSV4CapDt4_rBqHa9V0bmtAAqgGO18twFZslvjMn5N6W3b1xrie6-Znntr6Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQJRuSoYdeQigPLC2fj1w88cBEduLmChlXXwiE7N0N21uQ&amp;oe=6ABAB2DB
+https://scontent-nrt1-2.cdninstagram.com/v/t51.71878-15/821281881_2195167421096352_7527412408137440417_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MjU3OTAwOTM1OTQzMTkyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=MdKCtIuDCHgQ7kNvwE8jMTL&amp;_nc_oc=AdrNmiupSV4CapDt4_rBqHa9V0bmtAAqgGO18twFZslvjMn5N6W3b1xrie6-Znntr6Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQK92ZPUxZu7bSliUcO6UvXPHdJf1GLjCJJRCz-frKhtOA&amp;oe=6ABAB2DB
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fwww.amazon.jobs%2Fen%2Fjobs%2F10557133%2Fsecurity-engineer-internship-2027-us%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafDEV2e_qejB5TBe682OiEPgGpfv4nDRb7WpoLQPMMMjwcKtd3zzEzuCMjnUA_aem_qAq4N4hwFO8xunGQeqTBeA&amp;e=AUCugLXjm38n5SHsqbRArI0FGJEZGb0CF4gwd0RtIj9HZlm3_4tmFRIGyyGRgK7SS3K5Z4dCF5iet7pOQr2BpmXNQTS1dHsUNquv86HmzQ
+https://scontent-nrt1-1.cdninstagram.com/o1/v/t2/f2/m78/AQMsFFWDqGNPHhB7pT9E9_fulcB00cIQGlkR1eBHNhBurlpLWFuHgBMktqdqMw5IyBCEL2ySPrCGjqt7rNMuHZ8gQggxndzWEql_JnM.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_ohc=TQoMVIA5hcIQ7kNvwHmAVgK&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwNDIxNzU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=ac571b83336cc053&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0M1QjdEMEZFMEZGQjQzRkFBNUJDNzIzNDMwRjIwOTQ2X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkp4KJ0L6hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJbBU9u65j5KmrqLdHGjPRf-rsAjn6BT6jV5Pj-kb-ktg&amp;oe=6AB6BC78</t>
+        </is>
+      </c>
+      <c r="O117" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P117" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q117" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R117" s="3" t="inlineStr"/>
+    </row>
+    <row r="118" ht="45" customHeight="1">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>f7d7a94fe7b423cc5dd4</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:08:15.419193+00:00</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T14:09:30+00:00</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr"/>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>PWC Security Consultant Intern [visetn ere</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr"/>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I118" s="3" t="inlineStr"/>
+      <c r="J118" s="3" t="inlineStr"/>
+      <c r="K118" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs-us.pwc.com/us/en/job/PUVPUIUS757226WDEXTERNALENUS/Cybersecurity-Consulting-Intern-Summer-2027</t>
+        </is>
+      </c>
+      <c r="L118" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
+          <t>Cybersecurity Consulting Intern
+- Summer 2027 in IL-Rosemont
+| Information Technology and
+Security at PwC US
+Apply for Cybersecurity Consulting
+Intern - Summer 2027 job in
+IL-Rosemont. Information Technology
+and Security at PwC US
+PWC Security Consultant Intern [visetn ere
+i need to post this in 3 hours
+after west coast wakes up haha
+https://scontent-nrt1-2.cdninstagram.com/v/t51.71878-15/820085292_1749411056182430_6890420790116103000_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5MjU3OTM3NjkxNDg2NDk0NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=nkJrYHb2X3UQ7kNvwGkt64P&amp;_nc_oc=Adq4uvqjhEDJ6Ova5ktafsnE8ajQsa24KWsYmu6A6r13X4U5tXF1LtTTDfPjeaU8Ono&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQKGQ3Olje67QprXt5iO4ILl5EZ6BrCfHyxS--bG0ANBYg&amp;oe=6ABAE0D5
+https://scontent-nrt1-2.cdninstagram.com/v/t51.71878-15/820085292_1749411056182430_6890420790116103000_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5MjU3OTM3NjkxNDg2NDk0NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=nkJrYHb2X3UQ7kNvwGkt64P&amp;_nc_oc=Adq4uvqjhEDJ6Ova5ktafsnE8ajQsa24KWsYmu6A6r13X4U5tXF1LtTTDfPjeaU8Ono&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQKXyXkNK-vQivb2ZeagR4ocsOm6uIfLEv7leW2BeUfLAw&amp;oe=6ABAE0D5
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fjobs-us.pwc.com%2Fus%2Fen%2Fjob%2FPUVPUIUS757226WDEXTERNALENUS%2FCybersecurity-Consulting-Intern-Summer-2027%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAac-ZtSA9JMSchQz289-YONT9iwgJVzPqBxQJYxSHxpL5RU3uK4lA7pm4hGQXQ_aem_pidJmVjq2f87-u-q7WCv8w%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUCP9LbBrKNZhCJkbXl5h3PncjcKTj4LUaOJAgS5MPpDoK-7B_qpmD45SnXFz39yBM6f4MI1Ug5Qb3FmZ6KhJZrn64X0xzu7ZfoKRLizBA
+https://scontent-nrt6-1.cdninstagram.com/o1/v/t2/f2/m78/AQOR2YfAOfST-RNeUFUjNOcXfRg8IsytDM4y5OOtesQK7waScIS_9PhhjgPzhG3_jJQdMla3iMRX-z-Fpr43Ky069ZtJW7A9Ayp9XXI.mp4?_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ohc=-LXDpn43X5AQ7kNvwElja-i&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwNDIyOTg2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=6dc5a3e79fde8798&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0VFNDBENzExOTk1NTc0RkFFQzU5Q0M5NzRCQTA1Rjg4X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk-qj-0L6hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJuSAhWTkRDAZbrGxaK9Z8xLoGFIUcOVUyvQXBy4YgJHA&amp;oe=6AB6DB7B</t>
+        </is>
+      </c>
+      <c r="O118" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P118" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q118" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R118" s="3" t="inlineStr"/>
+    </row>
+    <row r="119" ht="45" customHeight="1">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>62d595039756949496b0</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:08:19.788201+00:00</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T14:12:14+00:00</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>Palantir — Internship</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr"/>
+      <c r="H119" s="3" t="inlineStr"/>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J119" s="3" t="inlineStr"/>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/palantir/ef725594-42dd-4f0d-ba8e-df8179dbc6cb</t>
+        </is>
+      </c>
+      <c r="L119" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
+          <t>@ jobs.lever.co
+instagran
+QO Palantir
+Information Security
+Engineer, Internship
+New York, NY
+Information Security / Internship / Hybrid
+APPLY
+Palantir builds the w ading software for
+data-drivg h _ ht b moas. By
+this might repost
+bringing t : g ea Tapes b who
+need it, our platforms empower our partners
+to develop lifesaving drugs, forecast supply
+chain disruptions, locate missing children, and
+more.
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/817742303_1587462092311573_3789092284175650030_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5MjU4MDc1MzE5MTkzMTgyNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=heHZSj1GSbQQ7kNvwHZHEzg&amp;_nc_oc=AdrNuv1yoRcUy1IwkqT0XaxDSNkPdIZ7n3Nfn-wCevZCrYvgK4HxKw3nO17EtewF6y4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQKJP2gGremefPWHfpuHLAjJfKEvvv9rjKSLkHUBvCdmkw&amp;oe=6ABAC690
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/817742303_1587462092311573_3789092284175650030_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5MjU4MDc1MzE5MTkzMTgyNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=heHZSj1GSbQQ7kNvwHZHEzg&amp;_nc_oc=AdrNuv1yoRcUy1IwkqT0XaxDSNkPdIZ7n3Nfn-wCevZCrYvgK4HxKw3nO17EtewF6y4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQITsZTXMLv_mtJcAiZpueOq2H1R7-21N28xRqIam2Jwmg&amp;oe=6ABAC690
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.lever.co%2Fpalantir%2Fef725594-42dd-4f0d-ba8e-df8179dbc6cb%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeFqnke-YSXT5TKnxVQZz4oFyO-z20Xxbw7piaFxk0WLJtbuIk7sN-jo1MTGQ_aem_XzYcDZRILrzdx1n20Athbg%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUAa_bLAUrjxu7LOdR2JLtxfKl7bBAGdZVO2D3ts7AaH1cBM6NdLjKTQeb3UwaRPlAKJDCx7PHKcy0Gj6I55Qhnl5isfgbOvoVkbc9rcSQ
+https://scontent-nrt1-1.cdninstagram.com/o1/v/t2/f2/m78/AQNmrF24E5EW_fBNXVu907I_Gr2Q5VKNhLBuDGbPePK0NT9R9rffmlC9MAUeJ-AuMb5Mrmmiv2O7DiJBXjftHLOOMefF2as_kBYYcqA.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_ohc=tXYNEqHPK3QQ7kNvwHVTzbB&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwNDI3NjM2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=9798a09e49898f5&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0EwNDk0NDZDNjQ3QjE3QzMwOTM2NTg0MDk0NzJBQUE5X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk0-O51L6hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKUL-SgttvrDhkzp7_YxltonFFBrbjgHeE6rEhtEhM8Pg&amp;oe=6AB6E63E</t>
+        </is>
+      </c>
+      <c r="O119" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P119" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q119" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120" ht="45" customHeight="1">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>1874b557cf3c23544c78</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:08:27.039251+00:00</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T15:03:07+00:00</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>Vercel</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>Vercel — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr"/>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="J120" s="3" t="inlineStr"/>
+      <c r="K120" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/vercel/jobs/6181759004</t>
+        </is>
+      </c>
+      <c r="L120" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
+          <t>@ job-boards.greenhouse.io C+:
+&lt; Back to jobs
+© Hybrid - San Francisco
+Apply
+About Vercel:
+Vercel is the agentic infrastructure company,
+freeing people and agents to ship what's
+VYyervii UVvVIVUpPY =
+Now we're scaling our products for both
+VR, Vevey, Uti
+experience.
+Vercel SWE Intern (not sure if repost)
+PayPal, Ramp, Supreme, and millions of
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/823221859_1933875410905357_1780070169932524485_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5MjYwNjM2NjI4MDY5OTI5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=UpfMStw3VCEQ7kNvwFtjhvD&amp;_nc_oc=AdpMFHBkcWNzCE5DlxfhcgRBIRvb3wWKpc7DTAT5Q6KZfxqqkLxUhR2C5Uz_MP4wulI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQKPvGK-JnQhCRVleitVkGuOUY7wJR5uuBs_mM_Xq2RUEA&amp;oe=6ABAC905
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/823221859_1933875410905357_1780070169932524485_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5MjYwNjM2NjI4MDY5OTI5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=UpfMStw3VCEQ7kNvwFtjhvD&amp;_nc_oc=AdpMFHBkcWNzCE5DlxfhcgRBIRvb3wWKpc7DTAT5Q6KZfxqqkLxUhR2C5Uz_MP4wulI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQLdkhDkhkviE4CDCarvUjqqBFBorhwXuUliPKv5d0V-xA&amp;oe=6ABAC905
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fvercel%2Fjobs%2F6181759004%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAac8rHhnWPvxKQmQM1-RuhuTAdVgFa1TbYq6WkA0RDmql2gT0-5VM0HLKRsmWQ_aem_28c8Xa5jCusE6rx0OdM78A&amp;e=AUDYEVotajE7Yx80tn5FYIK9C3KQDXQm2D54CfzB6AQgRphp2GM1d2Rpmh_MxXPCxQ3ohNi5ruCm7CAOdKA59t2duHJ5liBbsdyZm62Gcg
+https://scontent-nrt1-2.cdninstagram.com/o1/v/t2/f2/m78/AQNG3vUWTlXj0LSWvcIPjBbSQv_-gyTmucyieZ1zJ7k1SuOIYMvm12lfv0334f1DgA-ajY7z0r_95ueE2RAe0PwjpsmBM0IqMi5YatY.mp4?_nc_cat=107&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_ohc=6ofh3RSUJUUQ7kNvwEyAu1r&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwNTEyNDE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=74ab26ce9d2b2053&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0JBNDFDOTNBNTFFMzMyQjUzNDhCQUNDQUIzMDJENEEyX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk4YPPk7-hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLpAZytphLKWHlyi7Ek7iQ64VVPHrrVyojougUjIxS8Ug&amp;oe=6AB6D3DC</t>
+        </is>
+      </c>
+      <c r="O120" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P120" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q120" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R120" s="3" t="inlineStr"/>
+    </row>
+    <row r="121" ht="45" customHeight="1">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>a2882449e6d8026ef0cc</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:08:29.923201+00:00</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T15:21:58+00:00</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>Embed</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>Embed — Other Opportunity</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr"/>
+      <c r="H121" s="3" t="inlineStr"/>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>San Francisco, Remote</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="inlineStr"/>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/embed/job_app?for=coinbase&amp;token=8168315&amp;jr_id=6aa08bd3dbc0e60e37e0e53a</t>
+        </is>
+      </c>
+      <c r="L121" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
+          <t>@ job-boards.greenhouse.io Ge
+&lt; Back to jobs
+C4
+oftware Engineer
+© Hybrid - San Francisco, CA
+Apply
+Ready to do the most impactful work of your
+career? At Coinbase, we are
+uncompromising on our mission to increase
+economic freedom. The bar is high, the
+limits. If you're read pid the future of
+finance alongside pe o refuse to settle
+for "good enough," you belong here.
+Coinbase is a remote-first, but not remote-
+only company. Expect to get together
+quarterly for intense in-person working
+sessions called “surges.” learn more about
+working at Coinbase.
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/821638303_1070179645999181_3947301146208603726_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MjYxNTg1MjkxNDM3Nzg1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Y_ZPPD1JbjYQ7kNvwEMTMkA&amp;_nc_oc=Adruc3st8Rtsr5IsJhmx-OTo7Uz9cw98RpTKqbekMIrglLIx33LTMqFQPLZgen_zILE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQLiWdrYdAS0to1ZanJ_zD9pxHzuuAgMwZN99KffY_dBgQ&amp;oe=6ABAC045
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/821638303_1070179645999181_3947301146208603726_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MjYxNTg1MjkxNDM3Nzg1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Y_ZPPD1JbjYQ7kNvwEMTMkA&amp;_nc_oc=Adruc3st8Rtsr5IsJhmx-OTo7Uz9cw98RpTKqbekMIrglLIx33LTMqFQPLZgen_zILE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQJtLb2PWr4FI3x6vwNl2UogOmp4EoJtkHuJICYfHisIvQ&amp;oe=6ABAC045
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fembed%2Fjob_app%3Ffor%3Dcoinbase%26token%3D8168315%26jr_id%3D6aa08bd3dbc0e60e37e0e53a%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafYDrmUAyrha9aL4XyDm1rvj9X-Sd39Ih6cCPkx0j6XtU9ez-O3fGQQFWD8Ig_aem_qNtp5mQUSGQmvDebJRV0Mg&amp;e=AUD3W1ORJ7P-Eco5rW7G8orGpZ5l_e9E9MO40Btb8hHkoS2U5u3gHZfsqUueCiVMx8UDAvFFmtMex28TpwGb85fXiHwK1IZwPvkc2aQYMg
+https://scontent-nrt6-1.cdninstagram.com/o1/v/t2/f2/m78/AQMYFGl4gfBF-R_HnWs70zCe5VmIbG5jt8Ux00hDNn0d0fJd74ymU17_1vRT_-4seUwsMkyV646ZRTuqsEZaNQxFiNwGD3xMbS7ISUQ.mp4?_nc_cat=110&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ohc=MMaviV2sK6QQ7kNvwGXmNMA&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwNTM3MTk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=b8fa0d3180d70b8d&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzE5OUE2MUE2RkE1QzQ5QTFBNUFEM0Y3MTVGRThCQjJBX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk_52Kpr-hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQK7HoJzR02rkCHig3NZfRHanpX1JYPSmVKuVdepbQkPig&amp;oe=6AB6D2DF</t>
+        </is>
+      </c>
+      <c r="O121" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P121" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q121" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R121" s="3" t="inlineStr"/>
+    </row>
+    <row r="122" ht="45" customHeight="1">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>6ce57f7721c8335d8792</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:08:32.087965+00:00</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr"/>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr"/>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="J122" s="3" t="inlineStr"/>
+      <c r="K122" s="4" t="inlineStr">
+        <is>
+          <t>https://bostonscientific.eightfold.ai/careers/job/563602813638090</t>
+        </is>
+      </c>
+      <c r="L122" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
+          <t>8:48 AM
+‘ern V7
+Data Science Engirz&lt;«
+Boston Scientific
+Currently pursuing aba iv
+graduate degree in data Surcrice,
+computer science, mathematics, physics...
+Got an email to re-apply
+v
+Reposted
+~
+Thank you for looking out!!
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/819031198_1755626305651348_2922437903406397967_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MjYzNzM3ODQ0NDQzNDg0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=lTvulFsZjb8Q7kNvwEvBTQk&amp;_nc_oc=AdrET_BxmbvJ94spm7LK4YjNgFnpgCDfNn-eD4EFAWeCIpbVZCwzu4aDK-GLjAuvFVE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQL5wiWFA4WDpoSa17-Mt-y2A_aW17KhIMPvotDcHTrtrQ&amp;oe=6ABAC680
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/819031198_1755626305651348_2922437903406397967_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MjYzNzM3ODQ0NDQzNDg0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=lTvulFsZjb8Q7kNvwEvBTQk&amp;_nc_oc=AdrET_BxmbvJ94spm7LK4YjNgFnpgCDfNn-eD4EFAWeCIpbVZCwzu4aDK-GLjAuvFVE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQIvZ1iSn1KHM-fOS1dGrdTKe6mbNReYd_KTeNrOLIVQ6A&amp;oe=6ABAC680
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fbostonscientific.eightfold.ai%2Fcareers%2Fjob%2F563602813638090%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafmwGr5GK-6H5RPKBDrOW-4ENjHRl6HaDc6hEgS_i7o-Lozhy58l5fl1YOP0w_aem_RQHUTRzeZ_9Ldaiq1vrAzg&amp;e=AUD1TJVeY0xQtN0FriwXM1U8RyygXAQM47BGIkttd9LPisR7AwRudukIO657INYb_751PzKYKsIufzSeVDXuHofv9P36tUkKX0p-rqiAkw
+https://scontent-nrt6-1.cdninstagram.com/o1/v/t2/f2/m78/AQMZcJXjQnWPlqNBBFEYtmSfLEKqwqDcMSUsDeotPr5U5FxukumoNG_FpnX6nyXis2OUFQmxU2COZdrRp868zeKX4H1HZmGEAjh0Rco.mp4?_nc_cat=110&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ohc=SEEF-CTwU3kQ7kNvwGkX43o&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwNTkyNjY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=6ff9b5fcb2739b9f&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzk3NEY1NkFBQUFBNkU1NjQ1OUFFQzNCOTQ1NTA2REI1X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkgqK0z7-hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKE1zhgtSULE4JE_TVm_0ohzisLOeV6HpUVAY6hqsIQrA&amp;oe=6AB6C72F</t>
+        </is>
+      </c>
+      <c r="O122" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P122" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q122" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R122" s="3" t="inlineStr"/>
+    </row>
+    <row r="123" ht="45" customHeight="1">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>716750d5475a612b5ecc</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:08:36.469847+00:00</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:44:57+00:00</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr"/>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>REGISTER NOW</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr"/>
+      <c r="H123" s="3" t="inlineStr"/>
+      <c r="I123" s="3" t="inlineStr"/>
+      <c r="J123" s="3" t="inlineStr"/>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>https://predictionscup.com</t>
+        </is>
+      </c>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
+          <t>x @ predictionscup.com (&amp;
+Instagram
+SSS SUSQUEHANNA |MENU =|
+PREDICTIONS
+PREDICTIONS
+CUP
+Think You
+Can Price
+What
+Happens
+(2) SIG MARKET PREDICTIONS CUP
+Predictions Cup is 2-f|
+— ter, virtual market
+simulated trading com,
+with a $30,000 first-pic e, Participants start
+with the same balance of 100,000 SUSQies and trade
+across a broad set of market
+university students,
+REGISTER NOW
+probability, and trading judg
+portfolios. Participants can buy and sell positions as
+markets move, update their views as new information
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/820204780_917792167792795_2056366259371822873_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MjY1NzYyNTY5MTc2MzA0OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=YGL-EhWF0gkQ7kNvwEeNq96&amp;_nc_oc=AdpDIcVHYvs4lORUwoUEIvVhKQaduzwXT58z9o0VcDNkUmDIDj5QjzN5ZNay9Sl2npU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQKWOELl5YSQUzVntG_8eZwi0EnZXTbVZNQjlUAFuQrZwg&amp;oe=6ABADD1E
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/820204780_917792167792795_2056366259371822873_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MjY1NzYyNTY5MTc2MzA0OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=YGL-EhWF0gkQ7kNvwEeNq96&amp;_nc_oc=AdpDIcVHYvs4lORUwoUEIvVhKQaduzwXT58z9o0VcDNkUmDIDj5QjzN5ZNay9Sl2npU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQI_eBVO11sk6ynz3EotTGQ_jloxt5MbYmVe-xfJ7e4EBg&amp;oe=6ABADD1E
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fpredictionscup.com%2F%3Futm_source%3Dzero2sudo%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAae4mc1U8yjjREChZXbpCR8sGbc5zbWgp4hbeu99PqlspPNwlUvCaNuBKSS-1A_aem_8MVLOuhc8DNGcmHJrc0IPA&amp;e=AUDVydhgEJ6nzNKyzgWHWtRVeQwpo1Lznf82SMXXKBjuXgUjVtpPGFBqi92f__C0cBwwjHrbRuIeAuAs2KMAG0BIDOVzXJggyU0QKu94kA
+https://scontent-nrt1-2.cdninstagram.com/o1/v/t2/f2/m78/AQNkdO5QEearaqQL7eaUgT4V_PtMkwhuhfy3tPs3jFhmmE-2Gfs-o2Sqk3Sd8BqnWS1zM4t_Balf3QbPRHWmiw2Eg1vaNtiWhdMx5lM.mp4?_nc_cat=104&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_ohc=VvXmJsCcFeAQ7kNvwH9pkn0&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwNjI2NTk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=7259d3a399430563&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0FFNDQ3NjAyQzFBQUQ1N0VFQzlCNTQ3NzQ4NzAyN0IxX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbky4rY6L-hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIcdGYhXjQaSeZNdrRmMxX51BtfKlBNrhX5wyrI066oYw&amp;oe=6AB6C121</t>
+        </is>
+      </c>
+      <c r="O123" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P123" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q123" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R123" s="3" t="inlineStr"/>
+    </row>
+    <row r="124" ht="45" customHeight="1">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>56686b0d705d76a732a2</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:08:43.665276+00:00</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:53:07+00:00</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>Google — Product Management</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr"/>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>Menlo Park</t>
+        </is>
+      </c>
+      <c r="J124" s="3" t="inlineStr"/>
+      <c r="K124" s="4" t="inlineStr">
+        <is>
+          <t>https://share.google/tFtOqKK3aiGWfjkSI</t>
+        </is>
+      </c>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
+          <t>x vy, Meta Careers &lt; n :
+metacareers.com
+_ fe)
+= OY Meta QO
+&lt; Back to Jobs QO
+Rotational Product
+Manager
+Menlo Park, CA +1 location
+Product Strategy +1more
+@ META ROTATIONAL PM
+Meta's Rotational
+opportunity is a gro
+Meta PM not for new grads this year?
+Type something...
+o®
+experiences to the Product Manager 42
+function so we can continue building givwal
+products for billions of users.
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/821405247_1417258576999503_6524453985344803462_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MjY2MTc0MDQ3MDg5OTc2OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=a83Rz66x5u4Q7kNvwGEtsIm&amp;_nc_oc=AdpubzF2Vosha64nOedXB56Xj29o32JKt1N_YamjgFTBNeBjgx5qIAl6jfvmalXU9_c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQJhpL-Ecqg3YHG-40iOB-JaZYAUq8gPTL9ZBF5_9J05zg&amp;oe=6ABAB511
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/821405247_1417258576999503_6524453985344803462_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MjY2MTc0MDQ3MDg5OTc2OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=a83Rz66x5u4Q7kNvwGEtsIm&amp;_nc_oc=AdpubzF2Vosha64nOedXB56Xj29o32JKt1N_YamjgFTBNeBjgx5qIAl6jfvmalXU9_c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQLRC2_doffb6vZpE9meaC0KlXnxttISVKEJigGLgD_81w&amp;oe=6ABAB511
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fshare.google%2FtFtOqKK3aiGWfjkSI%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeFehOw86XAPBg6AtrMgT1dS3H-kfSObjrYjZjHOqmYn2sriEmw9GySQTSPqA_aem_cvCPbwNwze3EOI7wubyV7A&amp;e=AUAMYXbC36S7s477Wvj7cSaFCZX2vbAsGIgd1f_XdIFHqOkIA9-8zqWdbeuE3UhYppdFp281qwwV4XeATWaAnO660timq-Kjlb6wvXOjlQ
+https://scontent-nrt6-1.cdninstagram.com/o1/v/t2/f2/m78/AQNFBZlnsQv1ZyPkkZax3tMYju1Wju4mt98N1H5srG0Fd7S9l7HNDL6SrQVb9HWGRRNg8ImWQSuns1PjzEN_wiegnGvHU08tPRSw_Ww.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ohc=YXq_h2ODaSYQ7kNvwH2PBzA&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwNjM0NjA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=9c99ff88c9cefad5&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzlBNEEyOEI1NkEyREM5NTNGQkY3NTBFMjY2RTkzMkFDX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk9PzT7r-hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJiGCSOD9YvafcTJ-cpLrtfog--aTDp0wkbFFDtT-Fwaw&amp;oe=6AB6EC50</t>
+        </is>
+      </c>
+      <c r="O124" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P124" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q124" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R124" s="3" t="inlineStr"/>
+    </row>
+    <row r="125" ht="45" customHeight="1">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>c329e2adffa9a60b8d73</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:08:45.627248+00:00</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T17:03:42+00:00</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>Capital One — Product Management</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>New York, Chicago</t>
+        </is>
+      </c>
+      <c r="J125" s="3" t="inlineStr"/>
+      <c r="K125" s="4" t="inlineStr">
+        <is>
+          <t>https://www.capitalonecareers.com/job/mclean/product-development-program-associate-2027/31238/97421687328</t>
+        </is>
+      </c>
+      <c r="L125" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
+          <t>@ capitalonecareers.com C:
+Q Search Jobs —
+(2? CAPITAL ONE PM NEW GRAD
+Product Developm ogram
+Associate - 2027
+McLean, Virginia | Richmond, Virginia | Plano, Texas |
+New York, New York | Chicago, Illinois
+Apply
+O Category
+G28) Product
+= Experience
+Associate
+https://scontent-nrt1-2.cdninstagram.com/v/t51.71878-15/814998915_906846012302985_6259328842773928620_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MjY2NzA2MzQxMjIwNjA5MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Ht7V8GN9L1oQ7kNvwFDVSYx&amp;_nc_oc=Ado-JDWp_J3F7bdl1jAhjjQa-cHhqMTO1VWkK7kJiXkddK9DcGx1FtyKmpxPIovaAjs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQLjSh-go_IfdR5mVNQmxAvar7LXfxxq4G_Xyky8bDMRkw&amp;oe=6ABAC828
+https://scontent-nrt1-2.cdninstagram.com/v/t51.71878-15/814998915_906846012302985_6259328842773928620_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MjY2NzA2MzQxMjIwNjA5MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Ht7V8GN9L1oQ7kNvwFDVSYx&amp;_nc_oc=Ado-JDWp_J3F7bdl1jAhjjQa-cHhqMTO1VWkK7kJiXkddK9DcGx1FtyKmpxPIovaAjs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQI9Pz0w9h8i3D4ZGQOXqi_xxQy3vNebHQqhPF1daO0dlw&amp;oe=6ABAC828
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fwww.capitalonecareers.com%2Fjob%2Fmclean%2Fproduct-development-program-associate-2027%2F31238%2F97421687328%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeTK7HVRRYvA74OqLPA6M8ihIbaHZEusZEwTqbdFep511ICxWAW-aAiJv4p5w_aem_NDO2cwVh6RszX0uPFdn-Qw&amp;e=AUAfyUumolxDfbYxN2zcHeqVXdkc6LI7cTXlpLregKwkXxB49ETBLQHoflZHExUF_QxMXBGbBmftxqEuSJ1AjbG7Wb5IK7c_ikTplHORDQ
+https://scontent-nrt6-1.cdninstagram.com/o1/v/t2/f2/m78/AQPd8s5ne_0_KgwuEOTonZKcpx1IRQwlTkU7-7JnUS88UEuypvYeNW3cT8wayY0JItOVVBrcEZONbWGvAuD62FZknWBpWdfmUi-0bOI.mp4?_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ohc=Bz7KT4_1cVUQ7kNvwE0drwr&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwNjQ5NjA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=7688e1750df5f191&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0QwNEUzQ0VFQzYwNDExQzJGMjdBMDBFQjVCMjQ1MTgzX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbksL7q-b-hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJpnKLI2UkodPxUuv-g3hMuUBVlfRlDYzYjrqSKPYWpiw&amp;oe=6AB6DED2</t>
+        </is>
+      </c>
+      <c r="O125" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P125" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q125" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R125" s="3" t="inlineStr"/>
+    </row>
+    <row r="126" ht="45" customHeight="1">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>fda6403a51dfbc11ca94</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:08:56.569214+00:00</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T17:33:07+00:00</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr"/>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>Join Zipline as Droid Autonomy Intern</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr"/>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I126" s="3" t="inlineStr"/>
+      <c r="J126" s="3" t="inlineStr"/>
+      <c r="K126" s="4" t="inlineStr">
+        <is>
+          <t>https://www.zipline.com/open-roles/8002829003?gh_jid=8002829003</t>
+        </is>
+      </c>
+      <c r="L126" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
+          <t>Droid Autonomy Intern (Summer
+2027)
+Join Zipline as Droid Autonomy Intern
+(Summer 2027). Help us build the
+world's most advanced autonomous
+delivery platform.
+http
+-rol
+800
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/821553076_959368619867178_5086494034186267989_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MjY4MTg1OTE3MTk5NTg1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=NKBUaEPWWaIQ7kNvwEzSqU8&amp;_nc_oc=AdqOfgHrune24Ixd1wJWdVZmPC_IFhliFzqR419lSTEMhBB7grL9ybAOuZrtiRj_P6U&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQLsLuK9tuqaT-OE1o2SioKfeI25srmRdlTcbPCMRRJwtQ&amp;oe=6ABAD65C
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/821553076_959368619867178_5086494034186267989_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MjY4MTg1OTE3MTk5NTg1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=NKBUaEPWWaIQ7kNvwEzSqU8&amp;_nc_oc=AdqOfgHrune24Ixd1wJWdVZmPC_IFhliFzqR419lSTEMhBB7grL9ybAOuZrtiRj_P6U&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQKvMZvuswaCrdhgWwDmB8WE8ko_3pS_lVXS1dD3sNXKdA&amp;oe=6ABAD65C
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fwww.zipline.com%2Fopen-roles%2F8002829003%3Fgh_jid%3D8002829003%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaf11IiH4sKcveTP3oIkSC4LTcbVTZ2FvjwhAtEBJcteJE2lA8IpkXotxqsXqw_aem_TuKT6hYgI2amPt3oUVbrvA&amp;e=AUA8ViNza1vJ-awCdTQboTpTGcyMyEEoKv9vCgtmIEdUK54hRVDI5vPXZVUiBEZpQQdktRfKY3t_sCtVgxlz8YaNpIMZovlML6J2g_ofuA
+https://scontent-nrt1-2.cdninstagram.com/o1/v/t2/f2/m78/AQPc-PaG-xvMA8xx4bZHoMM9UaCm1bYnxpiqtSI5zEcMQKVIJSyPOj3EIdZORIwC05_i2De7JoUVofZkYxAx-VNbtxQa39AsyLLRBVw.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_ohc=lWrsCG4jlnwQ7kNvwG0EmU9&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwNjg1NzI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=2c83e1b7398de105&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0E5NDQxQ0QwRjAwRjdGMkVDNjMzMUMyRERFRjdGRjlGX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkrJTflMChQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJXT_hOlVMouuXfZFGQIae6s2tNmo7CycwgcZIKXVJx1w&amp;oe=6AB6BD16</t>
+        </is>
+      </c>
+      <c r="O126" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P126" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q126" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R126" s="3" t="inlineStr"/>
+    </row>
+    <row r="127" ht="45" customHeight="1">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>60b0fb268cc84bf3b94b</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:09:03.366699+00:00</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T17:58:14+00:00</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq — Internship</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr"/>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="J127" s="3" t="inlineStr"/>
+      <c r="K127" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/bedrock-robotics/07b55743-d5c4-4347-bfac-000821317b13</t>
+        </is>
+      </c>
+      <c r="L127" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
+          <t>&lt; All Jobs
+2027 Internship Evaluation
+Engineer, Metric Prototyping
+Location
+San Francisco, CA
+Employment Type
+Intern
+@ JOBS.ASHBYHQ.COM
+Department
+Engineering
+Overview Application
+Join the team bringing advanced
+autonomy to the built world
+At Bedrock, we're moving Al out of the lab
+and into the real world. Our team includes
+veterans who helped launch Waymo,
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/817789222_2893412307726716_2195227400717898704_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MjY5NDUwNjI3MzE5NTYwNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=0wupLyDNzawQ7kNvwFP6N3D&amp;_nc_oc=AdrRsueU_1NuJQTIWVan7vregz7d-4T-DjbArh8NA0d2wfsbyMC1HzLHzSZ110NQGZA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQL4BxKFvmQXr3Z_jbwmdNNB8RPEprRbrrFQiXfSRD9oPA&amp;oe=6ABAC427
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/817789222_2893412307726716_2195227400717898704_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MjY5NDUwNjI3MzE5NTYwNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=0wupLyDNzawQ7kNvwFP6N3D&amp;_nc_oc=AdrRsueU_1NuJQTIWVan7vregz7d-4T-DjbArh8NA0d2wfsbyMC1HzLHzSZ110NQGZA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQKKs4x6T4-5I2ko7d01ge0R-R-Y2Iiraz9aKrQ-C-MNuA&amp;oe=6ABAC427
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.ashbyhq.com%2Fbedrock-robotics%2F07b55743-d5c4-4347-bfac-000821317b13%3Futm_source%3Dzero2sudo%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacj-31zaHEfDP1JWbrlKHektRntrw7pOirwIjcr1ELRhDz-dAsLjbjDvfL5RQ_aem_ZFjXxnMLA8qB8EfkqKNX8g&amp;e=AUDFOtDWKC6BgZnNVu0WJr7Pe4zL0bT1tsoMui9w8SLGdyOKXjyiLEyKG6kxucQ_g-CzNN8otLBitd7F7prQevsBCl5ggK9rlxOxTvQlMA
+https://scontent-nrt6-1.cdninstagram.com/o1/v/t2/f2/m78/AQNZF5cjquNQ8PBdqTbx7syiFAc7HRlCCNyV92g1aX1fkH0e9xOlFUIMDSZH7JTc-KSWOgeEiqpUrahGCoJk54gPk56hfIxgahHq9gY.mp4?_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ohc=u2mqKQgCVIIQ7kNvwG7u2GG&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwNzE1OTM2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=4755ed178ac512b6&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzI2NDFGNEIzMUI5Mzc5QkIzREFCQzEwNzQwMkRFNzlEX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk4Zqgq8ChQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJctPbmk3WEru1BDs-dm_sVeACx6OeZvpIAJzoxHAQvBA&amp;oe=6AB6E727</t>
+        </is>
+      </c>
+      <c r="O127" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P127" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q127" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R127" s="3" t="inlineStr"/>
+    </row>
+    <row r="128" ht="45" customHeight="1">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>3a8697ed539ff2b9f3f4</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:09:06.015195+00:00</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T18:08:09+00:00</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>Scaleai</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>Scaleai — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr"/>
+      <c r="I128" s="3" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="J128" s="3" t="inlineStr"/>
+      <c r="K128" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
+        </is>
+      </c>
+      <c r="L128" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
+          <t>@ job-boards.greenhouse.io CG:
+&lt; Back to jobs
+Software Engineer,
+Public Sector - New
+Grad
+© San Francisco, CA
+At Scale, our missi lop reliable Al
+systems for the wo portant
+decisions. For 10 yea as provided
+the high-quality data and full-stack
+tech
+— ScaleAl New Grad SWE
+applications that deliver feu impact. We
+work closely with industry leaders like Meta,
+Ernst &amp; Young, Mayo Clinic, Time Inc., the
+Government of Qatar, and U.S. government
+agencies including the Army and Air Force
+_.
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/820335942_1655854349465103_4786851433148981971_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MjY5OTQ5ODc0NTg4NzM3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=grmTnJWVLGEQ7kNvwGkO6a-&amp;_nc_oc=Adp2Eqet9nCDgQICLWBbWyyt61DbDmeCBfsyyc5KmC4T8X5yhtZPsIq9Q9RGyZ8TZnQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQLYqUV3jjbvey10hO47rc0Ur2lCKFQnHhBCHprnswuJdw&amp;oe=6ABAC1B1
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/820335942_1655854349465103_4786851433148981971_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MjY5OTQ5ODc0NTg4NzM3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=grmTnJWVLGEQ7kNvwGkO6a-&amp;_nc_oc=Adp2Eqet9nCDgQICLWBbWyyt61DbDmeCBfsyyc5KmC4T8X5yhtZPsIq9Q9RGyZ8TZnQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQIXxnC5EgIM4B7nGs9DwRAhix5Diw-0WJ-1cs1asaUoGg&amp;oe=6ABAC1B1
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fscaleai%2Fjobs%2F4736426005%3Futm_source%3Dzero2sudo%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadDVWz8bBtAYGyN752NPCyBaRXO31AJSDs3KPMK0V45ztpBLddAK5kjUL70yA_aem_jVWUD31C29_8MkiFcXCGwg&amp;e=AUD9pKviDooFiEtD6I2dgsSYSpHKzukh1_ZJamLQcimHSSABVjzgsfBboyIuYMwUfZ3DlAwk1mOpT9QxGk-CWE9RO9hTiXM3gzx_JWBnMQ
+https://scontent-nrt1-1.cdninstagram.com/o1/v/t2/f2/m78/AQPvllxd43d-VMNBT__UA7-W7Vpym8EAPdqBK22J16Soe6Zq_VD_v7eTCs2j9MzpCAtgm1cBYFQqDBvXmguMEtKDpCROpo9fUPKU3x4.mp4?_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_ohc=z93GhWfl2xsQ7kNvwEyFO-1&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwNzI2NDA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=134160d118f80f52&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0ZCNDU1QzQxNTYyOUZGRTNCQ0ZCMTZBN0QxM0Q0REI2X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbksNqGs8ChQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQImBnylv_JxRscbtTSp-2A5S9ErvymkU34VJrKNo4ASBA&amp;oe=6AB6D10D</t>
+        </is>
+      </c>
+      <c r="O128" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P128" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q128" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R128" s="3" t="inlineStr"/>
+    </row>
+    <row r="129" ht="45" customHeight="1">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>c53b5151ad08be983421</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:09:08.707975+00:00</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T18:11:47+00:00</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr"/>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>opportunity for Summer Analyst. This is</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>Quant</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="J129" s="3" t="inlineStr"/>
+      <c r="K129" s="4" t="inlineStr">
+        <is>
+          <t>https://recruiting.ultipro.com/LOS1000LADOD/JobBoard/5365ad6e-23ff-4703-bb77-1e9451fb855e/OpportunityDetail?opportunityId=fb796a9d-16f1-4514-8f6b-e5c5dbbb6019</t>
+        </is>
+      </c>
+      <c r="L129" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
+          <t>@ recruiting.ultipro.com Ez
+Summer Analyst
+Job Category: BASEBALL RESEARCH AND DEVELOP
+Requisition Number: SUMME002310
+Apply now
+Posted: September 22, 2026
+Part-Time
+On-site
+CALIFORNIA
+Los Angeles, CA 90012, USA
+Job Details
+Description
+The Los Angeles Dodgers currently have a job
+opportunity for Summer Analyst. This is
+(2) LA DODGERS QUANT INTERN
+brief description of t d application
+process.
+Title: Summer Analyst
+Department: Quantitative Analysis
+Status: Part-Time
+https://scontent-nrt1-2.cdninstagram.com/v/t51.71878-15/818971938_1658958225577630_3941194897046769181_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5MjcwMTMyMDcwMDA0NDA2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=cT2Bu0OxGSwQ7kNvwEAPh0E&amp;_nc_oc=AdrJpdKDlYF0Iqclea5IzMS0YJg3-8LhZcXjc4DBqpbK5x65EodnG4bLfBamWykrtdc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQImj6md6cX49rqjyp22KVXtqGBMuFZvymk5mmKT3ahwXA&amp;oe=6ABAB13D
+https://scontent-nrt1-2.cdninstagram.com/v/t51.71878-15/818971938_1658958225577630_3941194897046769181_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5MjcwMTMyMDcwMDA0NDA2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=cT2Bu0OxGSwQ7kNvwEAPh0E&amp;_nc_oc=AdrJpdKDlYF0Iqclea5IzMS0YJg3-8LhZcXjc4DBqpbK5x65EodnG4bLfBamWykrtdc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQJOT3hYikyjEb_ytfRYK1RjvB5EgUGZiTZRFPFXh17xQQ&amp;oe=6ABAB13D
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Frecruiting.ultipro.com%2FLOS1000LADOD%2FJobBoard%2F5365ad6e-23ff-4703-bb77-1e9451fb855e%2FOpportunityDetail%3FopportunityId%3Dfb796a9d-16f1-4514-8f6b-e5c5dbbb6019%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAae2RCSYumpOp2NOwfxDOyh17JET3LL4plaOVSAZg88xxL2Z_aAJ27xJcBS_LQ_aem_LZrCQMtzw_JYRNCzkEhQHQ&amp;e=AUBPE2ufQCh6zckK_2zsJj5REvooS5Wv_07a6Wie2hPnwiwLkEovidUpqzoPWuNnQDDES_xq2MYb0GFxDpwjQXhKAuPQXKswppN2XDtWwQ
+https://scontent-nrt6-1.cdninstagram.com/o1/v/t2/f2/m78/AQPS0TqW4Vjb00DHObLFdlfrkGkUbmIM40SxVoy6DDiJkyvB0KzCIbu-EgJpKnEi5IBm35W6_YGmM4ZA-uI1f9zTT2F9JWf7XD5Rrzo.mp4?_nc_cat=110&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ohc=Qu4-K787GqkQ7kNvwFEk7Kr&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwNzMzNTc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=62c79e82de302b57&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzNFNDZBMjhEMUFDREEzMUQwMEJGRjVDNUE2RjVFQzkwX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk5b6yuMChQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJIM9fcMI8vNOPjNUtj3evPBaLT7ik9Boc9YQpKTJcoKQ&amp;oe=6AB6D767</t>
+        </is>
+      </c>
+      <c r="O129" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P129" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q129" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R129" s="3" t="inlineStr"/>
+    </row>
+    <row r="130" ht="45" customHeight="1">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>d75bced132e4a967d1dd</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:09:11.881177+00:00</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T19:18:26+00:00</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr"/>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>Graduate-Level Hiring Information Session</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>Job / Hiring</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr"/>
+      <c r="J130" s="3" t="inlineStr"/>
+      <c r="K130" s="4" t="inlineStr">
+        <is>
+          <t>https://app.eightfold.ai/events/candidate/landing?plannedEventId=agEXbYjN4</t>
+        </is>
+      </c>
+      <c r="L130" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
+          <t>@ app.eightfold.ai C7
+Qualcomm
+Events &gt;... &gt;
+Fall 2026 Campus Visits: Building
+On-Device Al at Qualcomm Tech Talk &amp;
+Graduate-Level Hiring Information Session
+* Tech Talk or Info Session
+a Sep 9 2026 - Oct 31 2026, 12:00 AM - 11:59 PM PDT
+@ Happening
+© Across Different Universities, Across Different Universities
+Register
+Description
+Interested In Building Generative Al And Agentic Al Systems That
+Run Directly On Real Devices And Exploring Full-Time Machine
+Learning Roles After Graduation?
+Join engineers and researchers from Qualcomm for an
+Qualcomm teams work ction of Al research,
+ML systems, and speciali are, translating
+advanced ideas into a nro sed hv millions of
+Powered by » eightfold.ai #WhatsNextForYou
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/817719240_1120118220704122_9016360406136546866_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5MjczNDg3MzkwNzM0NjIzMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Anmtr1KtwtMQ7kNvwHBNlin&amp;_nc_oc=AdqI34S5ZaHsTD-Jhj6pDtzCbEMM88ShmOvlp86b6bkqNOAxRapfecVjSdzvQoMSFxI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQJAHLjGfSXl3-q5ktcy76-GuvtGyJt5SG4GpF9EpP9_WA&amp;oe=6ABAC88E
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/817719240_1120118220704122_9016360406136546866_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5MjczNDg3MzkwNzM0NjIzMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Anmtr1KtwtMQ7kNvwHBNlin&amp;_nc_oc=AdqI34S5ZaHsTD-Jhj6pDtzCbEMM88ShmOvlp86b6bkqNOAxRapfecVjSdzvQoMSFxI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQKjYAgwPA19otqhBpN35ScvJDlO6V2KS18JS9_5_6uL_Q&amp;oe=6ABAC88E
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fapp.eightfold.ai%2Fevents%2Fcandidate%2Flanding%3FplannedEventId%3DagEXbYjN4%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacO_f3v1TCnOfcq2aECVC7NcMyb9ihBWr-3l-MeQ4s6ILLByAESZiAgpBp2GA_aem_l21d1q6uMP0708JoSdJW5w&amp;e=AUA-rhX_Jhy9ne0QWyWYH_s52FwEISqnm8ZlWVXq2SqVe6KcrK2hrST6RCSdHfaB6aOaOx1jJWKYmcjdJZP-IK75TwoGWkqoB1CcWQ4owQ
+https://scontent-nrt6-1.cdninstagram.com/o1/v/t2/f2/m78/AQM1jrK4Plb3t1ZcI9_i4HT6YSudBCF8z3ThhwEenJLFPAgxn4GGjQ9ofSB6V8bgv3aqRR1c_KaSA9pS0biknmGG48nRfn_ZKKOhYr4.mp4?_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ohc=NHW-A43ipWEQ7kNvwGDdNSe&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwNzk2MTg2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=6d55fef226db8c95&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzA0NDczMEY2NDJERTc4MTNENTc5RDc4QUQyNEY3RDgwX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkgrmF58ChQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIsIg2JGfPPcmr6Rd-bD8wTm4KGmXpLIXzWhY249P36bA&amp;oe=6AB6BD17</t>
+        </is>
+      </c>
+      <c r="O130" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P130" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q130" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R130" s="3" t="inlineStr"/>
+    </row>
+    <row r="131" ht="45" customHeight="1">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>9289b2e4630a9fd9a05a</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:09:15.866476+00:00</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T19:40:35+00:00</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>Figma</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>Figma — Data Engineering</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>Data Engineering</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>San Francisco, New York</t>
+        </is>
+      </c>
+      <c r="J131" s="3" t="inlineStr"/>
+      <c r="K131" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/figma/jobs/6178851004?gh_jid=6178851004&amp;gh_src=28109e334us</t>
+        </is>
+      </c>
+      <c r="L131" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
+          <t>@ job-boards.greenhouse.io CG:
+&lt; Back to jobs
+New
+Data Engineer Intern
+(2027)
+© San Francisco, CA « New York, NY
+Figma is growing our team of passionate
+creatives and builders on a mission to make
+(2) FIGMA DAIA ENGINEER INTERN:
+eanutatinig dadianey e, or a
+with Al. From idea to t, Figma
+empowers teams to streamline workflows,
+move faster, and work together in real time
+from anywhere in the world. If you're excited
+to shape the future of design and &gt; |
+collaboration, join us! =p
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/822118231_1668857271240617_1488009819447499041_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5Mjc0NjAxNTg5ODg1MDY2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=AKIw3zsIsIEQ7kNvwFXZ-Qt&amp;_nc_oc=Adr_1jckuoWi9k4MWbqELvECSPobunpHkqBSBR4MyE2TJgi4urhY3i9NVocg6u_A1vM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQJwz0j5tDNujMVr7KggZgG9w0Q0jdGEYSUOedMX5Xlx1g&amp;oe=6ABAC9E0
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/822118231_1668857271240617_1488009819447499041_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5Mjc0NjAxNTg5ODg1MDY2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=AKIw3zsIsIEQ7kNvwFXZ-Qt&amp;_nc_oc=Adr_1jckuoWi9k4MWbqELvECSPobunpHkqBSBR4MyE2TJgi4urhY3i9NVocg6u_A1vM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQJDp_P3wkSXuVolcPkrBhBrrT31Ibblo0gDIRgCtr4YfQ&amp;oe=6ABAC9E0
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Ffigma%2Fjobs%2F6178851004%3Fgh_jid%3D6178851004%26gh_src%3D28109e334us%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAach7P49p5VZZqsKVHW8Mqr9nwEPq9CyIkKfM6G4U1ZrXCuqYOZUgrd73kGHpQ_aem_QAY2zU6ksYqhaCsG1ic1xg&amp;e=AUDj6nJnuS79sBUQSaOv-hPtiB4lRsdLoc4RFHdG_y3kqLNCZURAD-fF5ssCy8pjXkfgQ0usVe4tt6YhQlx_wWG4pmHMHqmlOYVm0JTN2g
+https://scontent-nrt1-2.cdninstagram.com/o1/v/t2/f2/m78/AQP7LKFoA335ZGMOUm4kPQHu05lLKOmDGLbKldiqLhmELG_8R-AUiauFcBU4FnW7VGIUyr7vpNgAs4-6xyZe-Balz1OCNAA512ZwKeI.mp4?_nc_cat=104&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_ohc=4rF7G3WoTRcQ7kNvwEiV-Nr&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwODE1MjA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=17a01ec37c3e0bfd&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzRCNEI0QUVBOUI5MzdEQUJBNjFFQkQ1NUIwMjU4NTg2X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk4Kqb9cChQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIFEgPCozeBA_IsAUwK5-r16FCsHnTG9xzFyrwm1uHBug&amp;oe=6AB6EEAD</t>
+        </is>
+      </c>
+      <c r="O131" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P131" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q131" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R131" s="3" t="inlineStr"/>
+    </row>
+    <row r="132" ht="45" customHeight="1">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>046cae51d7151f663250</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:09:18.746835+00:00</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T19:42:06+00:00</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr"/>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>Registration Deadline: Oct 2, 2026 12:00 PM</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>Workshop / Info Session</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I132" s="3" t="inlineStr"/>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>Oct 2, 2026</t>
+        </is>
+      </c>
+      <c r="K132" s="4" t="inlineStr">
+        <is>
+          <t>https://connect.uwo.ca/events/events.htm?eventId=12914</t>
+        </is>
+      </c>
+      <c r="L132" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
+          <t>@ connect.uwo.ca SG
+Western) =
+| INFORMATION SESSION: TESLA ENERGY
+Oct 2, 2026 06:00 PM to 07:30 PM
+Weldon Library - Community Room
+Registration Deadline: Oct 2, 2026 12:00 PM
+Information Session: Tesla Energy
+Date: October 2, 2026
+™@ TESLA UWO EVENT!
+Location: Weldon Li Community Room
+You must register to attend this event.
+Registration closes on October 2, 2026 at
+UWO the goat of underdog
+noon.
+universities in Canada
+Tesla Energy focuses on accelerating the
+alobal shift to sustainable enerav through
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/818062418_1735760900825206_4247078274002964848_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5Mjc0Njc3MzY0MTc2Njc5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=i3exJWWBQTkQ7kNvwHuretc&amp;_nc_oc=AdrajoWGvxvH856sBIe3yDTiwQ6OOMaAhl4GM_tGAFtoGsEndH-yx8tPGdadG_1_ae4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQK4vevhsDTja-3zXfSnzLzg18qKoPL9mLV2ij6Pg_cD4g&amp;oe=6ABAC640
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/818062418_1735760900825206_4247078274002964848_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5Mjc0Njc3MzY0MTc2Njc5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=i3exJWWBQTkQ7kNvwHuretc&amp;_nc_oc=AdrajoWGvxvH856sBIe3yDTiwQ6OOMaAhl4GM_tGAFtoGsEndH-yx8tPGdadG_1_ae4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQKmDLrjAbNkB__Vq2Q54FJAW7-gTiXaLvrwh7ZQyVF4Tw&amp;oe=6ABAC640
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://scontent-nrt1-2.cdninstagram.com/v/t51.2885-19/458741572_517626100851764_3474477448346804853_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=102&amp;ig_cache_key=GETXVxs0JN43x9YBAHUi0ajU0jcwbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=aWW0VgfwjDQQ7kNvwHUo2xC&amp;_nc_oc=Ado4pgY5dExr57qB8x6BPuaOjDtM96Sh2JUBClAPO9OOU9ULUNhZTJSWwh3DAxca73c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQK6YGqplyektOJ5E6myXHem9Zbahtee1e4DG0skCPTtTw&amp;oe=6ABAB0ED
+https://l.instagram.com/?u=https%3A%2F%2Fconnect.uwo.ca%2Fevents%2Fevents.htm%3FeventId%3D12914%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaftzsObdQQFt0zrGWxtsmoHVHSuxVXFL77M3ALA9GbWORlHg739bJxKMHpYBg_aem_UpRavKl3k867J3DueJLJIQ%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUCR7QxVsGn7stpITzPTrZwSJQ3-0v36DD6OHMlBM8kkLRqWO_nreIKRH_XwK6hq9P8wTS1PqXer4FhkCJ7sgt5ZXS7i4xfOON2jJXG_sw
+https://scontent-nrt6-1.cdninstagram.com/o1/v/t2/f2/m78/AQNnjMpdZD9_NOGaylEe-vLbqTq7luN83KYQb4_gAxnZQSj0luOSHcONqX57N4Ua3rXT9N24DwplV8NwQ4AQ_Q_ozWVegJt18JUkrQo.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ohc=hFBgsUGczXcQ7kNvwECsB9E&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwODE3OTA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=8c1baf76800f6e7e&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0I1NEI4ODQ1NzkzMDY5RjZGQTU5NEI5NDFCNDFFM0I1X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk3umc98ChQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKlKNiPddTw4NBlRdfejdOe5T88o-Wy37HOJVf_ZN1Tzg&amp;oe=6AB6D18D</t>
+        </is>
+      </c>
+      <c r="O132" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P132" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q132" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R132" s="3" t="inlineStr"/>
+    </row>
+    <row r="133" ht="45" customHeight="1">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>35a323c15ead7138213a</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:09:20.596949+00:00</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T19:49:37+00:00</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr"/>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="J133" s="3" t="inlineStr"/>
+      <c r="K133" s="4" t="inlineStr">
+        <is>
+          <t>https://apply.careers.microsoft.com/careers/job/1970393557004819?domain=microsoft.com&amp;hl=en</t>
+        </is>
+      </c>
+      <c r="L133" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
+          <t>@ apply.careers.microsoft.com Cc.
+Instagran -
+pp B® Microsoft Sign in
+Careers ~
+€ View All Jobs
+Software Engineer:
+Intern Opportunity for
+University Students
+@ United States, California, Mountain View
+Apply now Add to cart
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/822118628_1745430506710863_4787510909713737042_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5Mjc1MDU2MTgxMTM0NjE2Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=go_zCMCbEFMQ7kNvwG9C5Ps&amp;_nc_oc=Adp1DJ3Y_a2PXMHbjWhE4Q_MSxbjSoe74DWZfzA8_J3b_Xm3gG0cp4PSgM8TR6iZ-XY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQLSZuoRE85WEh3hBvl2yiTRY5kGOS3imUX4QPrPGOUiAQ&amp;oe=6ABAD4F2
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/822118628_1745430506710863_4787510909713737042_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5Mjc1MDU2MTgxMTM0NjE2Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=go_zCMCbEFMQ7kNvwG9C5Ps&amp;_nc_oc=Adp1DJ3Y_a2PXMHbjWhE4Q_MSxbjSoe74DWZfzA8_J3b_Xm3gG0cp4PSgM8TR6iZ-XY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQKuL3xqcstwQx4HzVzZAqD0bxQ2-TYXKDb1WYCkATUdGg&amp;oe=6ABAD4F2
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fapply.careers.microsoft.com%2Fcareers%2Fjob%2F1970393557004819%3Fdomain%3Dmicrosoft.com%26hl%3Den%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadK8mtFdgYICX1oOBaJ9AU06Hx7jzzNRP3NAT3L1dCxdLt95FW2YlzH2mBs6Q_aem_SxilNHXaE18aeSjt65p4Fg&amp;e=AUDiUMs7RZiA5CQPw3_En_MPvpXrFkEFcAno0NDRwwuK1fGSGW1PArnAkPFEltxd8uKodh6kyxke_ROleKEBZ4nUCRhYQkFTrgMqN5K5Wg
+https://scontent-nrt1-1.cdninstagram.com/o1/v/t2/f2/m78/AQPPaV0XnPhIEX5YL_wZQ2K7FTTQz74NOeCeZqq2hjFc5oUV2OT78KXfF53VJea5dju_B13HBXk_dWDR3ffwcyPWWMCQoKK5W2kck4U.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_ohc=1L5pIG4NV-YQ7kNvwHgX66C&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwODI0MDU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=aa4773cbf0b41f09&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0Q5NDdCNzgyQTNDRDc2MUVFQzdDRTUzMDIyRDhGMjlEX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk_arn-8ChQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKOuUVsSwDnfjM84WgUV2ZGZ_pI1a-PEZite9vytWVPwA&amp;oe=6AB6DFA2</t>
+        </is>
+      </c>
+      <c r="O133" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P133" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q133" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R133" s="3" t="inlineStr"/>
+    </row>
+    <row r="134" ht="45" customHeight="1">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>5ad854bbad4ccc3da64b</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:09:25.940576+00:00</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:02:46+00:00</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>Nvidia</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>Nvidia — Design</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr"/>
+      <c r="J134" s="3" t="inlineStr"/>
+      <c r="K134" s="4" t="inlineStr">
+        <is>
+          <t>https://nvidia.wd5.myworkdayjobs.com/en-US/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Product-Design-Intern--AI-Infrastructure---Summer-2027_JR2025784</t>
+        </is>
+      </c>
+      <c r="L134" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
+          <t>1 NVIDIA.
+Product Design Intern, Al
+Infrastructure - Summer 2027
+Our work at NVIDIA is dedicated
+towards a computing model focused
+on visual and Al computing. For two
+decades, NVIDIA has pioneered visual
+computing, the art and science of
+computer graphics, with our invention
+of the GPU. The GPU has also shown
+to be spectacularly effective at
+solving some of the m...
+ate eae was
+hell yea!!
+https://scontent-nrt1-2.cdninstagram.com/v/t51.71878-15/819130439_1080516497713033_1303309999128987258_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5Mjc1NzE3NzAwMTYxOTE0MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=L63p8CTQuQkQ7kNvwEt_bpe&amp;_nc_oc=AdqaXOeL40nwEapUb_DCwDsHgVYKrJh9jma1qQTKMWl0_xdBh8wVfW4CUtONj-u7l3A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQJ3RTK1we36WvqKBcwwzCGjwEU3b2Rg6chGMr8Sw08nSg&amp;oe=6ABABFD0
+https://scontent-nrt1-2.cdninstagram.com/v/t51.71878-15/819130439_1080516497713033_1303309999128987258_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5Mjc1NzE3NzAwMTYxOTE0MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=L63p8CTQuQkQ7kNvwEt_bpe&amp;_nc_oc=AdqaXOeL40nwEapUb_DCwDsHgVYKrJh9jma1qQTKMWl0_xdBh8wVfW4CUtONj-u7l3A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQIU_uQNg3J7bXRfRDh9_aLOxgAUd0puUFoCIZXfRUAG-w&amp;oe=6ABABFD0
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fnvidia.wd5.myworkdayjobs.com%2Fen-US%2FNVIDIAExternalCareerSite%2Fjob%2FUS-CA-Santa-Clara%2FProduct-Design-Intern--AI-Infrastructure---Summer-2027_JR2025784%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAac3m0oYsKQD5_3x2sG-g0l-cneKB8iJfOGTkNjqJnzNl8AxF1rYG7Vm8e4k9g_aem_fiLyGrDI01ys_kGp6yLCWA%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUA2AS_bM1-9Q5ynOqJenExPjRHXmIxYHCo4ZtBP5AvaOsXjd9YR4K2TJEOuICXA_BR30nuLYVusZzXsTIQbLOA4b1VsKB7gejqC18PHlw
+https://scontent-nrt6-1.cdninstagram.com/o1/v/t2/f2/m78/AQPtdgGV82KcUoi5SiLNrdEvuLFT9t-c3n7NHmt7rUaxc-hB7-wJoq8iWXJc5WyoCjpPUrhwNODvTs09UZXXop1sHjfnYJXXu6dp9Js.mp4?_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ohc=dRpsqCavzmoQ7kNvwGA-djR&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwODM0Mzc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=acf830503cc82476&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0VGNDk0NDY4NURBMUUxNzdFQ0U4RkM3MzI1ODcwMjlGX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkxcO_g8GhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLO3uFwc74RSFdgupjuA3fdQwY2e4YAVeoSn4gLzEuJcA&amp;oe=6AB6CF6E</t>
+        </is>
+      </c>
+      <c r="O134" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P134" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q134" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R134" s="3" t="inlineStr"/>
+    </row>
+    <row r="135" ht="45" customHeight="1">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>af56e3ac1f7c9bf49843</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:09:27.911413+00:00</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:22:21+00:00</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr"/>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>Applications Open Technology ; _</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr"/>
+      <c r="H135" s="3" t="inlineStr"/>
+      <c r="I135" s="3" t="inlineStr"/>
+      <c r="J135" s="3" t="inlineStr"/>
+      <c r="K135" s="3" t="inlineStr"/>
+      <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
+          <t>“Drenep
+pplication Process
+INTERNSHIF
+Applications Open Technology ; _
+10/26/26-11/9/26 = Ranceamant =&gt; Team Interview SS Offer Decision
+Apply via Disneyinterns.com_
+Disney intern timeline
+From virtual event*®
+od
+https://scontent-nrt6-1.cdninstagram.com/v/t51.82787-15/823235083_18088085051678962_2178909995822802102_n.heic?stp=dst-jpg_e35_sh2.08_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5Mjc2NzAyMDg4NTYxMjc4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=f_M4UwPlHsUQ7kNvwFX3eC4&amp;_nc_oc=AdrxW4BNBmuLdjgMCxL6BN93t1zVa0-PaUVpJ0aJ6CXIEejPXBCmQ2BaqFgUg_x_qm0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;se=8&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQJtnhDGMJW5fmq_YQoB_aF8oexEVPeMIGr2PuE0HNRklQ&amp;oe=6ABAC238
+https://scontent-nrt6-1.cdninstagram.com/v/t51.82787-15/823235083_18088085051678962_2178909995822802102_n.heic?stp=dst-jpg_e35_s640x640_sh2.08_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5Mjc2NzAyMDg4NTYxMjc4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjEwODAuc2RyLnJlZ3VsYXJfcGhvdG8uQzMifQ%3D%3D&amp;_nc_ohc=f_M4UwPlHsUQ7kNvwFX3eC4&amp;_nc_oc=AdrxW4BNBmuLdjgMCxL6BN93t1zVa0-PaUVpJ0aJ6CXIEejPXBCmQ2BaqFgUg_x_qm0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQI6TrwCikhIeb0YMcGCBQqcxEFLedN_K6wPXRRSS9WDzg&amp;oe=6ABAC238
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19</t>
+        </is>
+      </c>
+      <c r="O135" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P135" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q135" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R135" s="3" t="inlineStr"/>
+    </row>
+    <row r="136" ht="45" customHeight="1">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>3c56e34b3f28ed5c759a</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:09:41.478861+00:00</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:37:55+00:00</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>Roblox</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>Roblox — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr"/>
+      <c r="I136" s="3" t="inlineStr"/>
+      <c r="J136" s="3" t="inlineStr"/>
+      <c r="K136" s="4" t="inlineStr">
+        <is>
+          <t>https://oncampus2026berkeleybuilderpan.splashthat.com</t>
+        </is>
+      </c>
+      <c r="L136" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
+          <t>x @ oncampus2026berkeleybuilde... CG: :
+Instagram
+RQ@BLOX
+Berkeley Day in
+the Life Panel
+Get a behind-the-scenes look into how our Builders
+applied, interviewed, and joined Robliox! You'll hear
+firsthand about their journeys to Roblox, previous
+experience, and what makes working at Roblox so
+special. Don't miss this opportunity to get an insider's
+view into what it’s like to work at Roblox as a
+software engineer!
+Roblox @ Berkeley, today 6 630pm!
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/794413618_1960896704582894_3487751389732270746_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5Mjc3NDg3MDkwNzkwMTE1MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=NvHbYcKIFzAQ7kNvwFCOYYX&amp;_nc_oc=Adqbr-rPvGxCahPVnekfoLeuJqJulDO6Kwp4ojBNgs2FFGdkMlnFvKXtJSXG9exmfHU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQKOTZHoaGWQ26G9LBdh9V_0j-VBRkbCCnX9x3qg_QzWwg&amp;oe=6ABACBB1
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/794413618_1960896704582894_3487751389732270746_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5Mjc3NDg3MDkwNzkwMTE1MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=NvHbYcKIFzAQ7kNvwFCOYYX&amp;_nc_oc=Adqbr-rPvGxCahPVnekfoLeuJqJulDO6Kwp4ojBNgs2FFGdkMlnFvKXtJSXG9exmfHU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQLgcuQdX4gjfhy4NFsJq7V-GqrAnxd1XqVtbcc8xqrVkw&amp;oe=6ABACBB1
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Foncampus2026berkeleybuilderpan.splashthat.com%2F%3Futm_id%3D97760_v0_s00_e0_tv4%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafz7c4kjuNNUXZNDB27xsVLSZHFPJl0i0aufy3rKzohMXW7dxFgzXazSmDuIQ_aem_3v-LLRi2V75fvWEWxUOmEw&amp;e=AUBzkdXl52i8N8QmBgmVt7Qwj3xy51Uf3woSavbfH21tKqId7XQ5tlyvwYjgZVSY36ZlyHf0NHcceF9lWCpGYGbfgGWZOT18vVrKBFHwNQ
+https://scontent-nrt1-1.cdninstagram.com/o1/v/t2/f2/m78/AQP3P1YMUSwdbLMUtVerCMSXVabTnwbMGXqRUQ1qwoIY6TSoLXWbQ1uvqgQ2-GpR_UjXKz2o1fBSTZer2oR_xB6SCZMTE5K6uvGRN1g.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_ohc=CQmZCRfa1SwQ7kNvwH45OuB&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwODU4OTc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=15f8dcef5a3af43e&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzU1NERGNkMxREFEQzc4RDZBQUQ4RDc5RjM1NjFGQjk0X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkwcjplcGhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIL_IFW2T40wM7xqgFxrMqxpND_NigtBqLDsWTTWssuew&amp;oe=6AB6CDFA</t>
+        </is>
+      </c>
+      <c r="O136" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P136" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q136" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R136" s="3" t="inlineStr"/>
+    </row>
+    <row r="137" ht="45" customHeight="1">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>bd55e3972784867d890e</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:09:44.052372+00:00</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:55:15+00:00</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>Ziprecruiter</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>Ziprecruiter — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr"/>
+      <c r="I137" s="3" t="inlineStr"/>
+      <c r="J137" s="3" t="inlineStr"/>
+      <c r="K137" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/ziprecruiter/jobs/8180455</t>
+        </is>
+      </c>
+      <c r="L137" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
+          <t>@ job-boards.greenhouse.io C:
+&lt; Back to jobs
+New”
+Software Engineer -
+Intern
+© Santa Monica, CA
+We offer a hybrid work environment. Most
+US-based positions can also be performed
+remotely (any exceptions will be noted in the
+Minimum Qualifications below.)
+Our Mission:
+(2) JOB-BOARDS.GREENHOUSE. 10
+Who We Ar
+ZipRecruiter is the fastest-growing onli
+employment marketplace for both desk a
+and mobile traffic. Powered by Al-driven
+https://scontent-nrt1-2.cdninstagram.com/v/t51.71878-15/822604572_3991697064472751_8435564644543348975_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5Mjc4MzU5ODQwNzI3NjIyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=VxTJ_4bTy9YQ7kNvwFAK8KZ&amp;_nc_oc=Adosia1ZFn_ZcF_5WhMbzIK9J0jugtcCcavd7jx23pPzG-6NrU3LFqaC9Mf6PjBlPe4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQKIyWNvaHUb_871hVRw2A-00adCVMve_DaB8A1FsHsLLQ&amp;oe=6ABAE04E
+https://scontent-nrt1-2.cdninstagram.com/v/t51.71878-15/822604572_3991697064472751_8435564644543348975_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5Mjc4MzU5ODQwNzI3NjIyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=VxTJ_4bTy9YQ7kNvwFAK8KZ&amp;_nc_oc=Adosia1ZFn_ZcF_5WhMbzIK9J0jugtcCcavd7jx23pPzG-6NrU3LFqaC9Mf6PjBlPe4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQJ0ADojnufglNROjy8S2wBV59trAVwNXPzslns-WGA4uA&amp;oe=6ABAE04E
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fziprecruiter%2Fjobs%2F8180455%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaflB6ie344qcR79dTz9QmbuzQ4zWagEitTPa-Fm0DudrX0mje3AtpdJr61fYg_aem_6aR6ZRs3anvG6Au8tHRr2Q&amp;e=AUB0v4ejAp8MdRJP_WPEzh8Ni40K2Zq-9U12GwlCi2oqK_UmZyaTFlgPb90BxKDTI9-vqKNxkzpSm-wpvkZD-qTK0rcsqD9VVQ_QuL-Vjw
+https://scontent-nrt1-2.cdninstagram.com/o1/v/t2/f2/m78/AQMoNqTJ2S3p_uT1LF20G9Ai8Ue8XsJvddkP0K1uf15LXzYFZEEYdxtX8pMBTbMbu3FjbmBG5cTKpVq_iPWVETNJIRCOKOtkhk1piaE.mp4?_nc_cat=102&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_ohc=jHIxEEyIbAIQ7kNvwHzReeQ&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwODcxMzk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=696393fab9fedb66&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0FFNDM1MkM4MDkyMjhFMjFBRkIxRDA1N0UxQjlGRDhCX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk64OKn8GhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJe-wc5iKFDY9Y7rg-q0d06hJENDXnmsk-kuUHCKtTyIA&amp;oe=6AB6DA3F</t>
+        </is>
+      </c>
+      <c r="O137" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P137" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q137" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R137" s="3" t="inlineStr"/>
+    </row>
+    <row r="138" ht="45" customHeight="1">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>c467252f03d2556818a7</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:09:46.070745+00:00</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T21:13:20+00:00</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr"/>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr"/>
+      <c r="I138" s="3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J138" s="3" t="inlineStr"/>
+      <c r="K138" s="4" t="inlineStr">
+        <is>
+          <t>https://seatgeek.com/jobs/8227553</t>
+        </is>
+      </c>
+      <c r="L138" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
+          <t>OED -
+€ View all jobs
+Software Engineer
+- Internship
+New York, New York
+Software Engineer -
+Internship
+© New York, New York
+are powerful experiences that
+unite humans. With our
+technological savvy and fan-
+first attitude we're simplifying
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/819828488_1043004125226446_2781640311788603909_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5Mjc5MjcwNjA3MDAwOTE5Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=3l0t29LxpKkQ7kNvwHnyUEn&amp;_nc_oc=AdphgwJECZfY5WGIpVb6HPxFxn-8VRuFQ570zZTL7pPg8_0JW_v6p6D_qHx70J0Skiw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQKgYFNLlD2Qs-Rs0XkvDn13Fe4bI62r_vwB1sF0AYelUw&amp;oe=6ABAB228
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/819828488_1043004125226446_2781640311788603909_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5Mjc5MjcwNjA3MDAwOTE5Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=3l0t29LxpKkQ7kNvwHnyUEn&amp;_nc_oc=AdphgwJECZfY5WGIpVb6HPxFxn-8VRuFQ570zZTL7pPg8_0JW_v6p6D_qHx70J0Skiw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQJADYgbj2NyV9pKL1eXcs-Vv7-orYRDH_XkQDA4SQVVzg&amp;oe=6ABAB228
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fseatgeek.com%2Fjobs%2F8227553%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafJOUa3lK_X9F-Kt8RjIGYhdznJRBZwNXrx7CSh5W9qOuT8_zqdXQCHmA_7lg_aem_NPWAKKtDVb0oPoWW0V7Xjw&amp;e=AUBHXwWwvQWe9gxVKwdzlHAAoBEYnfxyaEp3B_fYYjilo2Fb5_9qcY9crMtGaXBpb4HXRmN1-JaaXcA2_EOFp2ZDhgmWaXwsuC2hwzCLvQ
+https://scontent-nrt1-1.cdninstagram.com/o1/v/t2/f2/m78/AQMNU9mc2n7w1s7meR0235Cn4JK4Zv0bA_FpzKk-jgtZvBj5-TyUwvg9D2JO7diPvFb-eZ64azeX5sG6vlBNJ16FZNNoojSs4ZMO_8I.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_ohc=4Z3TppIgJxgQ7kNvwEaQcFS&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwODg2ODc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=96a514bf2f81a061&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0IxNDBGRUU4MDFCQTRBMUQ0QTQ0NzYxQjk2MzZBRDhDX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk16jOqsGhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJxpfnvPxL2GJjedt52EeWLu7Zs40n7bIaF1OxuzrXqbA&amp;oe=6AB6C3B8</t>
+        </is>
+      </c>
+      <c r="O138" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P138" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q138" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R138" s="3" t="inlineStr"/>
+    </row>
+    <row r="139" ht="45" customHeight="1">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>b264d6481d33cdaa1219</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:09:48.258542+00:00</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T21:14:32+00:00</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr"/>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>New Grad</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr"/>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J139" s="3" t="inlineStr"/>
+      <c r="K139" s="4" t="inlineStr">
+        <is>
+          <t>https://seatgeek.com/jobs/8227548</t>
+        </is>
+      </c>
+      <c r="L139" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
+          <t>@ seatgeek.com C:
+Instagram
+€ View all jobs
+Software Engineer
+- New Grad
+New York, New York
+Software Engineer -
+New Grad
+© New York, New York
+SeatGeek bell e events
+are powerful ex ences that
+unite humans. With our
+technological savvy and fan-
+first attitude we’re simplifying
+https://scontent-nrt1-2.cdninstagram.com/v/t51.71878-15/819616190_1420119280224017_187649275019862841_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5Mjc5MzMxMjEwNDk1Nzg3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=dYTDz8LfxggQ7kNvwHLdQnr&amp;_nc_oc=Adq8JT-irEwmxbOefOnSIHmiln8z2dP9qzxxbbzEXHyvm-OicDULpTiKzpxHdT3hE3g&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQJT_fQYpQP7xvZFsNPG0QeCvwp_wMOodcNxFQ3BuGc0LA&amp;oe=6ABACCF0
+https://scontent-nrt1-2.cdninstagram.com/v/t51.71878-15/819616190_1420119280224017_187649275019862841_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5Mjc5MzMxMjEwNDk1Nzg3NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=dYTDz8LfxggQ7kNvwHLdQnr&amp;_nc_oc=Adq8JT-irEwmxbOefOnSIHmiln8z2dP9qzxxbbzEXHyvm-OicDULpTiKzpxHdT3hE3g&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQJatcTqtaJhQhPu5uDbe0KLBSCpaPOVBBRcNnjeoj4CNA&amp;oe=6ABACCF0
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fseatgeek.com%2Fjobs%2F8227548%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaft7Upad4Ws8JmSepYR70-J0dFb7d-pvNCEJz6aoCBlYU3E9ZcU14y2v_Xsfg_aem_GS6SVn3_IZmeTtU3oR3urA&amp;e=AUBo2WW5v5R0s8NYbiwjWMiMtp1bzbD24pTz7s4s7mkWxHqltuZqhP7fH05HLVda8wtDl8Cu0YYRd-GfgyhhrhXk83FIY4cZ9H17XVVCJg
+https://scontent-nrt1-2.cdninstagram.com/o1/v/t2/f2/m78/AQPqt_S-r0BbzKyf2qI-dmkxPHLASVbHRsfEqhUp3KRKz5inadmI2HEBTyezTclkDC2bVMl3fI1LyYShAAUhizi_4khHkKkKJq8j73c.mp4?_nc_cat=104&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_ohc=NLPXA84om2cQ7kNvwF9ikKa&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwODg4MDQ2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=80346d09d123275c&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzQxNDE4RkQ1RkZCODA0NjVBNDBCODk3RUFGNUFDODk2X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk9PK9q8GhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJ3NGMqAUIuzL0USbqhWFj6hQobEsHrSITO0JhN8mcW6Q&amp;oe=6AB6D70D</t>
+        </is>
+      </c>
+      <c r="O139" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P139" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q139" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R139" s="3" t="inlineStr"/>
+    </row>
+    <row r="140" ht="45" customHeight="1">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>6cd16254f396a9fad374</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:09:54.017021+00:00</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T21:43:41+00:00</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft — Product Management</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="J140" s="3" t="inlineStr"/>
+      <c r="K140" s="4" t="inlineStr">
+        <is>
+          <t>https://apply.careers.microsoft.com/careers/job/1970393557004836?domain=microsoft.com</t>
+        </is>
+      </c>
+      <c r="L140" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
+          <t>@ apply.careers.microsoft.com C;:
+Pp B® Microsoft Sign in
+Careers ~
+€ View All Jobs
+Product Manager:
+Internship Opportunities
+Q United States, California, Mountain View
+Apply now | Add to cart
+9 PA
+Microsoft PM Intern (reopen?!
+Job description ty benefits
+Job number Date posted
+200057344 Sep 23, 2026
+Work site Travel
+3 days / week Less than 25%
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/800317196_3375649172822614_2932953651851603986_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MjgwNzk3MDQ3NjAwODM1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=3YGBif1wGVcQ7kNvwE-Kqyq&amp;_nc_oc=Adq9gllM-vh4iuSg9nJiexf71_laL0A39E_KWALx9lEEfRik-4Fz-Ql7Hjrgl5lp314&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQJiWIRGTZ9XE4otlz_A8uientkXyP02ECmX0L0VMm3_XQ&amp;oe=6ABADBDD
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/800317196_3375649172822614_2932953651851603986_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MjgwNzk3MDQ3NjAwODM1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=3YGBif1wGVcQ7kNvwE-Kqyq&amp;_nc_oc=Adq9gllM-vh4iuSg9nJiexf71_laL0A39E_KWALx9lEEfRik-4Fz-Ql7Hjrgl5lp314&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQKz5FvsUtM9Zmjlr64ECtiuzJFYfhTdVZd9P1cc59IyNQ&amp;oe=6ABADBDD
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fapply.careers.microsoft.com%2Fcareers%2Fjob%2F1970393557004836%3Fdomain%3Dmicrosoft.com%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeKAgn_2OILMGJ9Zg1Shlqa5VUCZpUAQ40lHnR1VD8pEGd0BW1jYTpmbeeNAQ_aem_o3WpR9qqnLa2A3nrXlExLA&amp;e=AUCk599sBoyueqz8JMfAgwz-kH11WeLhE_qIaOvsPpLXiSVlr51A8s7TP5XxrGAljyAhCow5tnYu8YUGABG1cBwzNklPSWlDPkxIPPupzg
+https://scontent-nrt1-2.cdninstagram.com/o1/v/t2/f2/m78/AQNQ1jMiW-nv10XflQlzofqz8d7hoIoQJQ5TH3vEyswfju43EzN6ReR4hKupBdNmrChQLYHq_dXViCStNqScTcNp3EjyaaGMc7ARLuM.mp4?_nc_cat=107&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_ohc=TRPMYM7eHNUQ7kNvwGCciXh&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwOTEwNDU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=ba3821b92b34ef0b&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzIwNDI0MkFEODQ3QzY4Q0M3QTQzMTNDNUZERjg4RjgxX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkvYqXvMGhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIdULzsxB17RzifdmYnm-_wDAHfHrpEmEWUoErDyjR96w&amp;oe=6AB6C760</t>
+        </is>
+      </c>
+      <c r="O140" s="3" t="inlineStr">
+        <is>
+          <t>Reopened</t>
+        </is>
+      </c>
+      <c r="P140" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q140" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R140" s="3" t="inlineStr"/>
+    </row>
+    <row r="141" ht="45" customHeight="1">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>a1384d44d1b4350117b1</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:09:56.814694+00:00</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T22:02:23+00:00</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>Smartrecruiters</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>Smartrecruiters — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr"/>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>Bellevue</t>
+        </is>
+      </c>
+      <c r="J141" s="3" t="inlineStr"/>
+      <c r="K141" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/LinkedIn3/744000151447279-software-engineer</t>
+        </is>
+      </c>
+      <c r="L141" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
+          <t>@ jobs.smartrecruiters.com
+Software Engineer
+Bellevue, WA
+GH Employees work in a hybrid mode
+Full-time
+Workplace Type: Hybrid
+Career Track &amp; Grade: IC2/7
+Department: Engineering
+LinkedIn Early Career SWE for 1 YOE
+Company Description
+powerful connections, disco
+build necessary skills, an
+day. We're also committed
+opportunities for our own em
+iting opportunities,
+le insights every
+transformational
+S by investing in their
+growth. We aspire to create a culture that's built on trust,
+care, inclusion, and fun — where everyone can succeed.
+Join us to transform the way the world works.
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/821717599_1704787464985001_1344866028737673198_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MjgxNzM5MDY3MTk3MjEwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=nPhLemToufkQ7kNvwGwsivn&amp;_nc_oc=AdppUBYQsDBgROX86OUSDfp3zSwOge5GL2z5r4LsU7nr4MnCPsHAoOM_MtMZ_AKBG5M&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQL8QwuV1zaui0rHh2MeQmH79Y8j6f3XO--WXownf6pL5A&amp;oe=6ABAC832
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/821717599_1704787464985001_1344866028737673198_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MjgxNzM5MDY3MTk3MjEwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=nPhLemToufkQ7kNvwGwsivn&amp;_nc_oc=AdppUBYQsDBgROX86OUSDfp3zSwOge5GL2z5r4LsU7nr4MnCPsHAoOM_MtMZ_AKBG5M&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQLiuVCKxi-fdHZqNR9Nd0DeTLL8yGjIo68w3DlK_pGQxg&amp;oe=6ABAC832
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.smartrecruiters.com%2FLinkedIn3%2F744000151447279-software-engineer%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafSOagrefixnQNSmBlOjbTJJRySibFKMsmt-Dov_P-sfnvw5IO7E75hP495lA_aem_gc3RmgZLty2Rombc_afTKg&amp;e=AUDcAvNO-1jtDElsvc28cnrignNkVq3NV0zl-tLE2oflBN-SvuwQYHiMjHIfoCBK5dWv4BBm_7TapKSK055WaLQAxMypgQ9MYazbsLh8Tg
+https://scontent-nrt6-1.cdninstagram.com/o1/v/t2/f2/m78/AQM4Wx5N7WjzwSvkUJhRjLz-dPUXSiZ67U74v4seuZ36UQca5lQP_-gb9umQzgSXzdqQ39Y6hPXBPzmTUm3XBWVvar6xvTzu8ZzKbuo.mp4?_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ohc=xOmPFAgR5LMQ7kNvwGDc8fi&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwOTMxNjA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=c76dd88871ce593e&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzJFNDUxRjk0RjYxRENEQ0IxMjE1Q0E5QTEwNjhFMzg1X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkmI34y8GhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLh86xWbrks0ib4Oy4IypIu2d_SZMeIYkvJXvrG5UUztg&amp;oe=6AB6BD2E</t>
+        </is>
+      </c>
+      <c r="O141" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P141" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q141" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R141" s="3" t="inlineStr"/>
+    </row>
+    <row r="142" ht="45" customHeight="1">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>914f86da78d0de45f3e4</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:10:03.958060+00:00</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T22:22:30+00:00</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr"/>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I142" s="3" t="inlineStr"/>
+      <c r="J142" s="3" t="inlineStr"/>
+      <c r="K142" s="4" t="inlineStr">
+        <is>
+          <t>https://luma.com/ramp-waterloo-coffee</t>
+        </is>
+      </c>
+      <c r="L142" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
+          <t>x @ luma.com C;: °
+e .
+Instagram . 0
+luma’ Discover Events Sign In
+ramp AZ. EMERGING TALENT PRESENTS
+CHATS IRL
+@ WATERLOO
+WITH RAMP SOFTWARE —s
+a ¥ Se
+=
+FRI, OCT 2, 2026 | UWATERLOO CAMPUS AREA
+1-3 PM ET WATERLOO, CANADA
+Ramp @ Waterloo: IRL
+Coffee Chats
+Ramp Emerging Talent &gt;
+&gt;
+© Register to See Adc
+Waterloo, Canada
+Registration
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/799634253_1534586321687259_4868190611886848599_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MjgyNzUxOTQxMjg1OTUxMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=IM20rdWwX0QQ7kNvwHSz231&amp;_nc_oc=AdobHVdjok1XDAUUy2WzFI8bY7UexTneXs0DjISl3KLIzf2E9sFKheWkjAlI-1ZoNn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQJuGAvtB7N1CsWmrLRNN306Y7dlxQe-tGAFt4ZFwLWOvw&amp;oe=6ABAC775
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/799634253_1534586321687259_4868190611886848599_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MjgyNzUxOTQxMjg1OTUxMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=IM20rdWwX0QQ7kNvwHSz231&amp;_nc_oc=AdobHVdjok1XDAUUy2WzFI8bY7UexTneXs0DjISl3KLIzf2E9sFKheWkjAlI-1ZoNn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQLz6d6OhWgtSzqTKpXhDLuIr5zdYGBTx-_DlCcV1RuVuQ&amp;oe=6ABAC775
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fluma.com%2Framp-waterloo-coffee%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacsDUAZYcNgydE_xlH4NIKtmNOtQN4aPuloBTpksXgZgB4-nD79y1TjP1vUUg_aem_C5bCNwZHb9xfSRes4DNL2w%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUAPHoansv35ZNnqgzFbJp1uHiHwEqLuxE4BMYXtoL20zdVfXXf6KQI6kJQ5XXkXoxHSGPd-MD4h8aJqt0WpUsyMXNMtSioqzOEuyw5uLQ
+https://scontent-nrt1-1.cdninstagram.com/o1/v/t2/f2/m78/AQMIDUYniVEmnyVmpJPDRQxs-WtPC9PM_LLBE-4lcaasHUt6DJ_3jFECwusSlMMgI5PBgjv1NwLiuQl1Id9GzeMTuR3cx8Lv3cmFJEI.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_ohc=nGKeU4FWccwQ7kNvwEvlksc&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwOTQ2NDI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=bc563385e733c233&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzBGNDRBQUJCQzM4REIxMjYyMTMxRURFNzM3NzU4NTgwX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbksrn91sGhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKr_nQPylH80e7C5FfVoR_Slk3kIi4R9vWBfewFpgQ7qA&amp;oe=6AB6CB1A</t>
+        </is>
+      </c>
+      <c r="O142" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P142" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q142" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R142" s="3" t="inlineStr"/>
+    </row>
+    <row r="143" ht="45" customHeight="1">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>95240c4e8ffdb47a93a1</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:10:06.976059+00:00</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T22:32:36+00:00</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>Databricks — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>Bellevue, Mountain View</t>
+        </is>
+      </c>
+      <c r="J143" s="3" t="inlineStr"/>
+      <c r="K143" s="4" t="inlineStr">
+        <is>
+          <t>https://www.databricks.com/company/careers/university-recruiting---engineering/software-engineering-intern-2027-start---winter-8732364002</t>
+        </is>
+      </c>
+      <c r="L143" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
+          <t>databricks
+Careers at Databricks
+Software Engineering Intern
+(2027 Start) - Winter - Databricks
+Software Engineering Intern (2027
+Start) - Winter, Bellevue, Washington;
+Mountain View, California; San
+Francisco, California. Join us!
+Together we can use data to solve the
+challenges of tomorrow
+https://www.databricks.com
+/
+-r
+/
+-2027-start---winter
+a 222304002
+Edited
+Databricks winter repost???
+~
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/819404770_1634359388075288_1497712077110959838_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MjgzMjU5NzQ2NTA3NTYxNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=l1qus7EZgukQ7kNvwFZDsvi&amp;_nc_oc=AdqcLSlTqVf9eQnGFIX_lK2atW0Wz2xptiauX0yEUNU4vrZxlimcrGmKkN4eH6G7r_E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQJ_YIvhOOTkpvtDTVOxSOhlSvdLCvkXMxMQw8HnFpaIpQ&amp;oe=6ABAD22A
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/819404770_1634359388075288_1497712077110959838_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MjgzMjU5NzQ2NTA3NTYxNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=l1qus7EZgukQ7kNvwFZDsvi&amp;_nc_oc=AdqcLSlTqVf9eQnGFIX_lK2atW0Wz2xptiauX0yEUNU4vrZxlimcrGmKkN4eH6G7r_E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQLbg6do4AxSB797phzyUWd4IiBVg2pmaQ8OZd3ivuhAwA&amp;oe=6ABAD22A
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fwww.databricks.com%2Fcompany%2Fcareers%2Funiversity-recruiting---engineering%2Fsoftware-engineering-intern-2027-start---winter-8732364002%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAad09FX5oqnFJuS4LxcFKyzpQlVBdjayawxuZXMDv1Z-sa5P_CJJ5fN6Mtj4zA_aem_DD-5rKKwaFxmVhd6vAEpnA&amp;e=AUAtFXSXJPOt-ILMn4ZvxudweIu2mZSD8FbUgjOhHuRf5ySb9fzrnrZnSfFHC1H1iuua9IFCOQEY3g3FOKrJ6NZkjM6V9btF7VrWa4wdeg
+https://scontent-nrt6-1.cdninstagram.com/o1/v/t2/f2/m78/AQP-ohygIb9djC9TWkd0z6HdiG2wBvfa3iX7EK_fLCnAcM33-1aQzN4um7RmeVtyXntxhYbCyCDvDpapBJs7MymUWd4rZLmMENic6Kw.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ohc=MvCuyPdPIw4Q7kNvwHTRKSr&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgwOTU3Mzc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=ad3f65493d28b04a&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0E1NEYyRjg1RkI2NzEzQUFFQjU4RkFEMEY4MTMwQjk5X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbksdyR38GhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJDp8QNaaiyNUF5g_F2AyRH93qa6ZHJMCQ8jRHoRi4aaw&amp;oe=6AB6BCA5</t>
+        </is>
+      </c>
+      <c r="O143" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P143" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q143" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R143" s="3" t="inlineStr"/>
+    </row>
+    <row r="144" ht="45" customHeight="1">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>82fd7d03371c972a3ddc</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:10:09.496997+00:00</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:13:48+00:00</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>Atlassian</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>Atlassian — Data Science</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I144" s="3" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="J144" s="3" t="inlineStr"/>
+      <c r="K144" s="4" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/details/26271</t>
+        </is>
+      </c>
+      <c r="L144" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
+          <t>@ atlassian.com CG:
+A ATLASSIAN
+Careers Vv
+Data Scientist Intern,
+2027 Summer U.S.
+Interns | Seattle, United States |
+@ ATLASSIAN.COM
+Working at AtlassianA ians have the
+flexibility to work where they can collaborate
+most effectively with their team, whether at
+home, one of our global offices, or both. We
+hire in any country where we have a legal
+entity. Learn how we work at
+go.atlassian.com/distributed.
+Your Future Org
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/822536098_1048181831551034_853270316805834288_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5Mjg4MzUzMzkxNTc1NzkxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=olrIZQb4BLUQ7kNvwEVwvWF&amp;_nc_oc=AdoXzq7Mf_SSAIADo6E_M5ISIzEYIzraYqmUFk-o3WY1rwwRRSnctUx1xvdgAWGqNSg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQJHMtTvZQ49GwxsCHFTp6oPLMk9I_El7_5wUt7ASvp3eQ&amp;oe=6ABAD318
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/822536098_1048181831551034_853270316805834288_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5Mjg4MzUzMzkxNTc1NzkxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=olrIZQb4BLUQ7kNvwEVwvWF&amp;_nc_oc=AdoXzq7Mf_SSAIADo6E_M5ISIzEYIzraYqmUFk-o3WY1rwwRRSnctUx1xvdgAWGqNSg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQICU4UCvHZ384sGxNvvqcZsafIQhzNbuMj0SIcCBWgY0g&amp;oe=6ABAD318
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fwww.atlassian.com%2Fcompany%2Fcareers%2Fdetails%2F26271%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadWu_GaDDxIypk7fU4pmEshctRTySBg9E4ggYfJwFe7Tf85dL5MLCASfUJQ6Q_aem_kujFq2-mZgY1YdQ154T4FQ&amp;e=AUAXN36XOsgugtyG1WUJkW3D9Su6PsxayYAIgVoE-MYmEaYhjSlA0RjDLNZeMGycja7ATGukFYnjlPSL-Cj2vBEh73SkJnyScfsKK8UHzg
+https://scontent-nrt1-2.cdninstagram.com/o1/v/t2/f2/m78/AQPEX0Z552X6s3sfSkmNwglBljI-sAFuYiORIEa_2fe9Ha5w-7QqOmuQJi0XJqvnF3z2p2UVb1h5bCQxQFKh397LS6yHzj_TQ3yTmk8.mp4?_nc_cat=107&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_ohc=05x0COSp4LQQ7kNvwEZdQrC&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgxMDI0MzA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=8169e1a9bd574178&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzQ0NDdCRjVDMUFENEM5QjdGREM2QzZGRUM3NzAwQTg3X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk_tSAkcKhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIhLWMPhmCXL4y9DsY9MK7r12jpcbHIxS_WIeszuOhIng&amp;oe=6AB6BD14</t>
+        </is>
+      </c>
+      <c r="O144" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P144" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q144" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R144" s="3" t="inlineStr"/>
+    </row>
+    <row r="145" ht="45" customHeight="1">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>1a691906372350b2c9fa</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:10:11.288425+00:00</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:31:41+00:00</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="inlineStr"/>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J145" s="3" t="inlineStr"/>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/ramp/acf6b28d-767f-483f-8ff2-114620cd7e04</t>
+        </is>
+      </c>
+      <c r="L145" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
+          <t>« ramp Za
+Software Engineering Intern,
+Backend
+Location
+New York, NY (HQ)
+Employment Type
+Intern
+@ RAMP SWE INTERN!
+Department
+Engineering
+Compensation
+$12.5K per month * Offers Equity
+RAMP POSTED 1 MINUTE AGO &amp;
+Overview Application
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/822772940_1416357080684318_471185523953789759_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5Mjg5MjUzNjMyNjcwMjU0OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=IBntqWySQLUQ7kNvwFKj-oJ&amp;_nc_oc=AdpS1UGRmG8mjFINSh9pJQqhLW9UYKJx8FNy5IDEN7GHXnqSihDEzKhipmsl_YLSsAA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQKuhuyUG-52Td3Lv2cDUZ6U5HsOR9i7FsGN83rINCYcHQ&amp;oe=6ABAD779
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/822772940_1416357080684318_471185523953789759_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5Mjg5MjUzNjMyNjcwMjU0OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=IBntqWySQLUQ7kNvwFKj-oJ&amp;_nc_oc=AdpS1UGRmG8mjFINSh9pJQqhLW9UYKJx8FNy5IDEN7GHXnqSihDEzKhipmsl_YLSsAA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQJ1hkDYgzV5SQ68dfDDFkEpKIfJ4yTKNvrbp5iw7e-tGA&amp;oe=6ABAD779
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.ashbyhq.com%2Framp%2Facf6b28d-767f-483f-8ff2-114620cd7e04%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAae4NJMBc6F1rwBqmh98wP3ZAF-bVtXK_zsSWPSMJ18mRkHa-Cy_FSO8uZUv9g_aem__M8V0VmfhetMPwzmwWQOgQ&amp;e=AUBBQXJ_Gxs7nT771RffYr12GFngS6SQ_OZyeELSDYdaKNALjb9AKcc3KXHp6a7nPYSQDL7VSmLSUQp4LYh1RmmO06y9oMZvFJiiqcTCTA
+https://scontent-nrt6-1.cdninstagram.com/o1/v/t2/f2/m78/AQNG7VcFSyXt8_xaITBo03E0yGeaFTAckiYKsXLI9QleHUWes14fhycWsnJdqhC5SmWd-vPJel52vLWsJivuh_iDuYCpidyFH-2LpQ4.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ohc=injQRR7qpIwQ7kNvwH12Q5R&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgxMDM2NDU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=e3480e72e9aadac8&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0I0NEVBMkJEMDNEQUNBRjEyQTA4QkE3QkVFNjhEREE5X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbktbCHmsKhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;_nc_enc=QfuHeqm18_EyNJVGzeRiGqpYyGeiDkT9lvPUO9mEClf0DuCOLzG3m4Ok1-Hblrahn5drwqpDBp98yyRJPEb-21ijmfHXEiPrE1TsDj5qC4ZopfKWw-mrS-bb0i4&amp;oh=00_AQKA9sFSccV9iRTHxK37b_zvcDV8wN8xwX5kQfq-qcksxA&amp;oe=6AB6CC8D</t>
+        </is>
+      </c>
+      <c r="O145" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P145" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q145" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R145" s="3" t="inlineStr"/>
+    </row>
+    <row r="146" ht="45" customHeight="1">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>770fb578a354b9f72a25</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:10:12.894315+00:00</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:44:22+00:00</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr"/>
+      <c r="I146" s="3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J146" s="3" t="inlineStr"/>
+      <c r="K146" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/ramp/a13ae586-f4cb-4385-8822-c42b9b54ed74</t>
+        </is>
+      </c>
+      <c r="L146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
+          <t>« ramp a
+Software Engineer Internship,
+Frontend
+Location
+New York, NY (HQ)
+Employment Type
+Intern
+Location Type
+Hybrid
+@ JOBS.ASHBYHQ.COM
+Compensation
+$12.5K per month
+See More
+Overview Application
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/819902515_28881788688112046_5040053246284816448_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5Mjg5ODkxNDY4ODU1MDkzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=6C-M3Y4BNrEQ7kNvwHoZieN&amp;_nc_oc=AdqDRMtYgOpkhZ_m4qyl46CEhPsO2qPR2y83Kzcu8g1DXWe0B3BjZmnX_6ZKgnABJmM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQJHXX3AyU4aCP3owNEW5k9u9b_U9MvZoeFUSiYM1OYXxg&amp;oe=6ABACBAD
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/819902515_28881788688112046_5040053246284816448_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5Mjg5ODkxNDY4ODU1MDkzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=6C-M3Y4BNrEQ7kNvwHoZieN&amp;_nc_oc=AdqDRMtYgOpkhZ_m4qyl46CEhPsO2qPR2y83Kzcu8g1DXWe0B3BjZmnX_6ZKgnABJmM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQLhsAJI7wDt3YHs4W-H_gnVgiGD1R_uQHaL16n4g5su2g&amp;oe=6ABACBAD
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.ashbyhq.com%2Framp%2Fa13ae586-f4cb-4385-8822-c42b9b54ed74%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadAtnkddktbcvCe-LcGnmww1gzEcyWq7jjMk8WOk4nN9Xs04eZyEiwvMpPotw_aem_PuA5n9WOh3Xqd5fdqFENdw&amp;e=AUDw-grtby3ptsSnff6n3JKwl_cIHno9Q3RnJvsAryOulwqLCHoQ7ZO_AI8StVqUC-qLE7MdtiqW9Bq-D0RgUmGOa0PlUNerwOkWVfl6yQ
+https://scontent-nrt6-1.cdninstagram.com/o1/v/t2/f2/m78/AQMpJ8O2Jke-f-fL7nJNkoc4NMYFwl-awzwz-02vJ1cGAo-nU0eD7KpK4dLb54qvr4un8O5gr8-__0pYqP-9bo7rOcQzji7OHVVWEoo.mp4?_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ohc=qQFH0S5b4doQ7kNvwHs4MR0&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgxMDQ2Mzg2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=4c41badb5e986934&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0QxNEMxNkFGREU3NjA2QjA1Q0JBMTYxM0E4MEIzNjhEX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbknrC6ocKhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJ3x4PWtU6ywji0qTZyEfF0wJ9rBB-Qr0160sjG0Pasqw&amp;oe=6AB6C596</t>
+        </is>
+      </c>
+      <c r="O146" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P146" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q146" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R146" s="3" t="inlineStr"/>
+    </row>
+    <row r="147" ht="45" customHeight="1">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>0e714ed621f1777e06fc</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:10:14.494354+00:00</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:56:58+00:00</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr"/>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J147" s="3" t="inlineStr"/>
+      <c r="K147" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/ramp/fcf118cc-521a-4a62-9d13-945e5b6e3cb8</t>
+        </is>
+      </c>
+      <c r="L147" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
+          <t>« ramp az
+Software Engineering Intern,
+Android
+Location
+New York, NY (HQ)
+Employment Type
+Intern
+Location Type
+On-site
+@ JOBS.ASHBYHQ.COM
+Compensation
+$12.5K per month
+See More
+Overview Application
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/799487531_1074717458810342_857296097650056856_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MjkwNTI1NzczNTY2NTY1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=msG05X9Mip8Q7kNvwHYEp0y&amp;_nc_oc=AdroVtDoRhFYk47CMeH-OujGYIpuSRELk2UNBvbqzyVBh8E7NplvTffnv5KXKZY4QpQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQI0IwZup88u9RjEC7uTmrwk7dbltKK61KCCvHql7Je9yQ&amp;oe=6ABAC3DD
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/799487531_1074717458810342_857296097650056856_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MjkwNTI1NzczNTY2NTY1NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=msG05X9Mip8Q7kNvwHYEp0y&amp;_nc_oc=AdroVtDoRhFYk47CMeH-OujGYIpuSRELk2UNBvbqzyVBh8E7NplvTffnv5KXKZY4QpQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQKtB6f505DTsEDKCsOTCALvNgR-LfLXXjAloka-2TMOyA&amp;oe=6ABAC3DD
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.ashbyhq.com%2Framp%2Ffcf118cc-521a-4a62-9d13-945e5b6e3cb8%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAae8s3L_CTuL4qVLA9Dpbomd5l_H83RN05Gu6FZ0NgOic2Y_mNjGeCatHXhWyg_aem_RxtvyaLRSZ-f16JhpiF2Eg&amp;e=AUCBl9X7NxSv0h1RMrxktvMuVBa36O3zhQ0BABHYeikZBrVmJ4WLvTEa8j4clP_Xv6kYvIprmRhhGtV4UrI4EoIZG_pmzP1Y6Aq3KYKdqQ
+https://scontent-nrt1-1.cdninstagram.com/o1/v/t2/f2/m78/AQMENVgyLmXa_uzQISC1eg7dOhtOg93JmCMqaEsXphcax6sbpVKpNtwqa_7nXCgKPJwLD7wKFJqdck9x3vmDzTn6o4w2TkSJZSSghHs.mp4?_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_ohc=SLEmGAfpM4UQ7kNvwExFvmb&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgxMDY0MDI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=8f6ebf345a310563&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0M3NEZEMkI1NzVFQTAwQjg2NkY1N0M2NUYwNDRGQ0ExX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkotTMrsKhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQL9P3RYQMwQK9pGoAZ37zIdM_LHc963kCikOP4Tf7sPAQ&amp;oe=6AB6C465</t>
+        </is>
+      </c>
+      <c r="O147" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P147" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q147" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R147" s="3" t="inlineStr"/>
+    </row>
+    <row r="148" ht="45" customHeight="1">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>6878c79d4a64626bc1de</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:10:16.160698+00:00</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T01:40:11+00:00</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr"/>
+      <c r="I148" s="3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J148" s="3" t="inlineStr"/>
+      <c r="K148" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/ramp/b66be397-240b-41a6-9b05-493299b270a9</t>
+        </is>
+      </c>
+      <c r="L148" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
+          <t>« ramp az
+Software Engineering Intern, iOS
+Location
+New York, NY (HQ)
+Employment Type
+Intern
+Location Type
+Hybrid
+© JOBS.ASHBYHO.COM
+Compensation
+$12.5K per month
+See More
+Overview Application
+Al acet Nawrn
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/810931219_1063728330034582_4865012730141111763_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MjkyNzAwNjUzNDUwOTYwOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=CfvrnLvJ5uMQ7kNvwEP0ck_&amp;_nc_oc=AdrpboZlmhoT7NUmftwPD4vDs4z58WuBijM_0wLtHhhsOwcXLG4UKi1ZgSS42D-7s8s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQJK2MQwc76mN5yQUsQRBlxuTy_B0sS7rDZk12ClsrsxAQ&amp;oe=6ABAC6FC
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/810931219_1063728330034582_4865012730141111763_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MjkyNzAwNjUzNDUwOTYwOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=CfvrnLvJ5uMQ7kNvwEP0ck_&amp;_nc_oc=AdrpboZlmhoT7NUmftwPD4vDs4z58WuBijM_0wLtHhhsOwcXLG4UKi1ZgSS42D-7s8s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQJOskHm6W1QUww3ok_SIqgrt5EyIRjborv8bd5vcgmkYw&amp;oe=6ABAC6FC
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.ashbyhq.com%2Framp%2Fb66be397-240b-41a6-9b05-493299b270a9%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAac6jiisBCdNdRTrDiO5IJDJOlTOYwj-5UVCgfk8lsIO2a-LYxwzJvwgUX_uYw_aem_IZnq1odPchaBSmT6wAqm6w&amp;e=AUDSoVcU8eVSKvdgRyc8n5-ahYH2SgS8dYB2gkqMnUNVFmkD33v5a4pII5SGGlSb8sdbfPlxMZo1M084reNFdBTsBJtD5ReDWE7jOWraPA
+https://scontent-nrt1-2.cdninstagram.com/o1/v/t2/f2/m78/AQO0rvjdUF0TdGoYaxUSbp2KHBhr3X5VrbOqQCdcY0jW26rDq3K5ZiDzj_R_5UA0c6GaCS1tIWEfm5ss820VuEy_znCbYSpbRohVnoM.mp4?_nc_cat=107&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_ohc=i0GYfQ4WnfMQ7kNvwEiBmjd&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgxMTExMDA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=3f0876d5bdb54408&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0Q2NEI2RkNCQzA2NUQ0NENEMzBGRDVCMkMyOTUyREJFX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkzILN0cKhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJ6_mOntfXrBmO-y-Ul_JwBkLZtuGYNuvyuntHRvP0UcQ&amp;oe=6AB6BBAC</t>
+        </is>
+      </c>
+      <c r="O148" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P148" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q148" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R148" s="3" t="inlineStr"/>
+    </row>
+    <row r="149" ht="45" customHeight="1">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>8bd6d354ea30fa8f1c38</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:10:20.237633+00:00</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T03:24:05+00:00</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>Astranis</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>Astranis — Internship</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr"/>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="J149" s="3" t="inlineStr"/>
+      <c r="K149" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4716088006</t>
+        </is>
+      </c>
+      <c r="L149" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
+          <t>@ job-boards.greenhouse.io
+Instagram
+Software Defined Radio
+Hardware Intern
+(Summer 2027)
+© San Francisco
+JOB-BOARDS.GREENHOUSE. IO
+Astranis builds advan 'es for high
+orbits, expanding huma ach into the
+solar system. Today, Astranis satellites provide
+dedicated, secure networks to highly-
+sophisticated customers across the globe—
+large enterprises, sovereign governments, and
+the US military. With five satellites on orbit and
+many more set to launch soon, the company is
+servicing a backlog of more than $1 billion of
+commercial contracts.
+Astranis is the preferred satellite
+https://scontent-nrt1-2.cdninstagram.com/v/t51.71878-15/820852827_2287738405359565_5371385572926766878_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5Mjk3OTMwMjc4NjM2MzM3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=WNY62bqugfMQ7kNvwHcgAgN&amp;_nc_oc=AdrWNcErJd44jdzNh8HYD_8PaFqxM4Urj7bxIxIiK8q3yLAfVfY9hi3qW-H3p0djAyQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQLtlQZeB-RvtXH58UBJplnbyQWAJnieMZfvap99JvPh-g&amp;oe=6ABAC8DE
+https://scontent-nrt1-2.cdninstagram.com/v/t51.71878-15/820852827_2287738405359565_5371385572926766878_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5Mjk3OTMwMjc4NjM2MzM3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=WNY62bqugfMQ7kNvwHcgAgN&amp;_nc_oc=AdrWNcErJd44jdzNh8HYD_8PaFqxM4Urj7bxIxIiK8q3yLAfVfY9hi3qW-H3p0djAyQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;oh=00_AQL3k0OPbxYDq2HwS0pgzPIeXOSGNlWK3b-zLChjGp5-yA&amp;oe=6ABAC8DE
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwF12Jtc&amp;_nc_oc=Adq_IpdtqUh1EKELpNjmrbwicBx80IPnZcD9W5oV5azrCsn0pVgf3Mdo94JE_V_K4K0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKRYzcFQkKYmrbWtdAoiOSJL7yHwjupI9cYgxVdAVzpMg&amp;oe=6ABACA19
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fastranis%2Fjobs%2F4716088006%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaclzFADQo5o0LLTNHp_T_RpDBEr4lJ5cQLYHmCMBzzPlbxFFoLLLd5xZGA-wQ_aem__e31zIoh1LTW3TmTd87RYg&amp;e=AUCdotIe7qoNN7NCGUQvDajqmqbrXIK9Ww-IUDSZe8sURjE9qGRE8Uk5bj67TKwy37r1M7euHXTLG2_8jugfdMr1JaTed0lRKrCyJBWkmQ
+https://scontent-nrt6-1.cdninstagram.com/o1/v/t2/f2/m78/AQPNjI7uFDq5r4DVkpXrv688j7Jwhn_J2pmEP750_P49RJ37u61jDMzN9iI4Zjjxl-TNuDjimHQ2XAGiD1sxi3OM9AQEWAVV4Dkz-kw.mp4?_nc_cat=110&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ohc=5_61WFtdR0sQ7kNvwGTr83J&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgxMjA5OTE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=8491d94aec06ce75&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0YxOTk1Q0RBNEE5ODQzOEFBOTBFMThDNkY5QjhFREE0X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkh-ilm8OhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=32jZJwPNQeK6pWUQqu_SlA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKkcV-j8FT5KAaGqKJrGwg1YabOVepin82z3gQctErnWA&amp;oe=6AB6C263</t>
+        </is>
+      </c>
+      <c r="O149" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P149" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q149" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R149" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R115"/>
+  <autoFilter ref="A1:R149"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -11549,6 +14866,73 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L114" r:id="rId212"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId213"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L115" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K123" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K125" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K126" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K129" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L129" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L130" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K138" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L141" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K142" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K143" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L143" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L144" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K145" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L145" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K146" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L146" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K147" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L147" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K148" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L148" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K149" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" r:id="rId281"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$159</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R149"/>
+  <dimension ref="A1:R159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11335,7 +11335,7 @@
     <row r="116" ht="45" customHeight="1">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>ccae5bed0ba1324ea1d6</t>
+          <t>c6fb4480b707a0eacb09</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -11378,7 +11378,7 @@
           <t>Austin</t>
         </is>
       </c>
-      <c r="J116" s="3" t="inlineStr"/>
+      <c r="J116" s="3" t="n"/>
       <c r="K116" s="4" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Wise/744000151030889-graduate-software-engineer</t>
@@ -11437,12 +11437,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R116" s="3" t="inlineStr"/>
+      <c r="R116" s="3" t="n"/>
     </row>
     <row r="117" ht="45" customHeight="1">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>fdb0fdf5b544a4410d39</t>
+          <t>5cc7cc2f37746ed9e9a7</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -11470,14 +11470,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G117" s="3" t="inlineStr"/>
+      <c r="G117" s="3" t="n"/>
       <c r="H117" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="I117" s="3" t="inlineStr"/>
-      <c r="J117" s="3" t="inlineStr"/>
+      <c r="I117" s="3" t="n"/>
+      <c r="J117" s="3" t="n"/>
       <c r="K117" s="4" t="inlineStr">
         <is>
           <t>https://www.amazon.jobs/en/jobs/10557133/security-engineer-internship-2027-us</t>
@@ -11531,12 +11531,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R117" s="3" t="inlineStr"/>
+      <c r="R117" s="3" t="n"/>
     </row>
     <row r="118" ht="45" customHeight="1">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>f7d7a94fe7b423cc5dd4</t>
+          <t>2b1614a160202c4cec0b</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -11549,7 +11549,7 @@
           <t>2026-09-23T14:09:30+00:00</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr"/>
+      <c r="D118" s="3" t="n"/>
       <c r="E118" s="3" t="inlineStr">
         <is>
           <t>PWC Security Consultant Intern [visetn ere</t>
@@ -11560,14 +11560,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G118" s="3" t="inlineStr"/>
+      <c r="G118" s="3" t="n"/>
       <c r="H118" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I118" s="3" t="inlineStr"/>
-      <c r="J118" s="3" t="inlineStr"/>
+      <c r="I118" s="3" t="n"/>
+      <c r="J118" s="3" t="n"/>
       <c r="K118" s="4" t="inlineStr">
         <is>
           <t>https://jobs-us.pwc.com/us/en/job/PUVPUIUS757226WDEXTERNALENUS/Cybersecurity-Consulting-Intern-Summer-2027</t>
@@ -11618,12 +11618,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R118" s="3" t="inlineStr"/>
+      <c r="R118" s="3" t="n"/>
     </row>
     <row r="119" ht="45" customHeight="1">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>62d595039756949496b0</t>
+          <t>342e36e2d6bfaee2f3f3</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -11651,14 +11651,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G119" s="3" t="inlineStr"/>
-      <c r="H119" s="3" t="inlineStr"/>
+      <c r="G119" s="3" t="n"/>
+      <c r="H119" s="3" t="n"/>
       <c r="I119" s="3" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="J119" s="3" t="inlineStr"/>
+      <c r="J119" s="3" t="n"/>
       <c r="K119" s="4" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/palantir/ef725594-42dd-4f0d-ba8e-df8179dbc6cb</t>
@@ -11714,12 +11714,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R119" s="3" t="inlineStr"/>
+      <c r="R119" s="3" t="n"/>
     </row>
     <row r="120" ht="45" customHeight="1">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>1874b557cf3c23544c78</t>
+          <t>af15daa7b3d427062979</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -11752,13 +11752,13 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H120" s="3" t="inlineStr"/>
+      <c r="H120" s="3" t="n"/>
       <c r="I120" s="3" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="J120" s="3" t="inlineStr"/>
+      <c r="J120" s="3" t="n"/>
       <c r="K120" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/vercel/jobs/6181759004</t>
@@ -11811,12 +11811,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R120" s="3" t="inlineStr"/>
+      <c r="R120" s="3" t="n"/>
     </row>
     <row r="121" ht="45" customHeight="1">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>a2882449e6d8026ef0cc</t>
+          <t>5d95813f1ea6d9a266f6</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -11844,14 +11844,14 @@
           <t>Other Opportunity</t>
         </is>
       </c>
-      <c r="G121" s="3" t="inlineStr"/>
-      <c r="H121" s="3" t="inlineStr"/>
+      <c r="G121" s="3" t="n"/>
+      <c r="H121" s="3" t="n"/>
       <c r="I121" s="3" t="inlineStr">
         <is>
           <t>San Francisco, Remote</t>
         </is>
       </c>
-      <c r="J121" s="3" t="inlineStr"/>
+      <c r="J121" s="3" t="n"/>
       <c r="K121" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/embed/job_app?for=coinbase&amp;token=8168315&amp;jr_id=6aa08bd3dbc0e60e37e0e53a</t>
@@ -11909,12 +11909,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R121" s="3" t="inlineStr"/>
+      <c r="R121" s="3" t="n"/>
     </row>
     <row r="122" ht="45" customHeight="1">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>6ce57f7721c8335d8792</t>
+          <t>b873aaf6bcea48d4f0cb</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -11927,7 +11927,7 @@
           <t>2026-09-23T16:04:44+00:00</t>
         </is>
       </c>
-      <c r="D122" s="3" t="inlineStr"/>
+      <c r="D122" s="3" t="n"/>
       <c r="E122" s="3" t="inlineStr">
         <is>
           <t>Data Science</t>
@@ -11943,13 +11943,13 @@
           <t>Data Science</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr"/>
+      <c r="H122" s="3" t="n"/>
       <c r="I122" s="3" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="J122" s="3" t="inlineStr"/>
+      <c r="J122" s="3" t="n"/>
       <c r="K122" s="4" t="inlineStr">
         <is>
           <t>https://bostonscientific.eightfold.ai/careers/job/563602813638090</t>
@@ -12001,12 +12001,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R122" s="3" t="inlineStr"/>
+      <c r="R122" s="3" t="n"/>
     </row>
     <row r="123" ht="45" customHeight="1">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>716750d5475a612b5ecc</t>
+          <t>c79a48b46f3c9a150f03</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -12019,7 +12019,7 @@
           <t>2026-09-23T16:44:57+00:00</t>
         </is>
       </c>
-      <c r="D123" s="3" t="inlineStr"/>
+      <c r="D123" s="3" t="n"/>
       <c r="E123" s="3" t="inlineStr">
         <is>
           <t>REGISTER NOW</t>
@@ -12030,10 +12030,10 @@
           <t>Other Opportunity</t>
         </is>
       </c>
-      <c r="G123" s="3" t="inlineStr"/>
-      <c r="H123" s="3" t="inlineStr"/>
-      <c r="I123" s="3" t="inlineStr"/>
-      <c r="J123" s="3" t="inlineStr"/>
+      <c r="G123" s="3" t="n"/>
+      <c r="H123" s="3" t="n"/>
+      <c r="I123" s="3" t="n"/>
+      <c r="J123" s="3" t="n"/>
       <c r="K123" s="4" t="inlineStr">
         <is>
           <t>https://predictionscup.com</t>
@@ -12095,12 +12095,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R123" s="3" t="inlineStr"/>
+      <c r="R123" s="3" t="n"/>
     </row>
     <row r="124" ht="45" customHeight="1">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>56686b0d705d76a732a2</t>
+          <t>51f8f8922f9887774883</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -12133,13 +12133,13 @@
           <t>Product Management</t>
         </is>
       </c>
-      <c r="H124" s="3" t="inlineStr"/>
+      <c r="H124" s="3" t="n"/>
       <c r="I124" s="3" t="inlineStr">
         <is>
           <t>Menlo Park</t>
         </is>
       </c>
-      <c r="J124" s="3" t="inlineStr"/>
+      <c r="J124" s="3" t="n"/>
       <c r="K124" s="4" t="inlineStr">
         <is>
           <t>https://share.google/tFtOqKK3aiGWfjkSI</t>
@@ -12197,12 +12197,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R124" s="3" t="inlineStr"/>
+      <c r="R124" s="3" t="n"/>
     </row>
     <row r="125" ht="45" customHeight="1">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>c329e2adffa9a60b8d73</t>
+          <t>7576d6ad24ea637676c5</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -12245,7 +12245,7 @@
           <t>New York, Chicago</t>
         </is>
       </c>
-      <c r="J125" s="3" t="inlineStr"/>
+      <c r="J125" s="3" t="n"/>
       <c r="K125" s="4" t="inlineStr">
         <is>
           <t>https://www.capitalonecareers.com/job/mclean/product-development-program-associate-2027/31238/97421687328</t>
@@ -12297,12 +12297,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R125" s="3" t="inlineStr"/>
+      <c r="R125" s="3" t="n"/>
     </row>
     <row r="126" ht="45" customHeight="1">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>fda6403a51dfbc11ca94</t>
+          <t>f1e740741a3a85e03a0c</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -12315,7 +12315,7 @@
           <t>2026-09-23T17:33:07+00:00</t>
         </is>
       </c>
-      <c r="D126" s="3" t="inlineStr"/>
+      <c r="D126" s="3" t="n"/>
       <c r="E126" s="3" t="inlineStr">
         <is>
           <t>Join Zipline as Droid Autonomy Intern</t>
@@ -12326,14 +12326,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G126" s="3" t="inlineStr"/>
+      <c r="G126" s="3" t="n"/>
       <c r="H126" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I126" s="3" t="inlineStr"/>
-      <c r="J126" s="3" t="inlineStr"/>
+      <c r="I126" s="3" t="n"/>
+      <c r="J126" s="3" t="n"/>
       <c r="K126" s="4" t="inlineStr">
         <is>
           <t>https://www.zipline.com/open-roles/8002829003?gh_jid=8002829003</t>
@@ -12382,12 +12382,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R126" s="3" t="inlineStr"/>
+      <c r="R126" s="3" t="n"/>
     </row>
     <row r="127" ht="45" customHeight="1">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>60b0fb268cc84bf3b94b</t>
+          <t>f81b500a0b2c2613af81</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -12415,7 +12415,7 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G127" s="3" t="inlineStr"/>
+      <c r="G127" s="3" t="n"/>
       <c r="H127" s="3" t="inlineStr">
         <is>
           <t>2027</t>
@@ -12426,7 +12426,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="J127" s="3" t="inlineStr"/>
+      <c r="J127" s="3" t="n"/>
       <c r="K127" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/bedrock-robotics/07b55743-d5c4-4347-bfac-000821317b13</t>
@@ -12482,12 +12482,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R127" s="3" t="inlineStr"/>
+      <c r="R127" s="3" t="n"/>
     </row>
     <row r="128" ht="45" customHeight="1">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>3a8697ed539ff2b9f3f4</t>
+          <t>ec03b5aaa7a9a17afa30</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -12520,13 +12520,13 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H128" s="3" t="inlineStr"/>
+      <c r="H128" s="3" t="n"/>
       <c r="I128" s="3" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="J128" s="3" t="inlineStr"/>
+      <c r="J128" s="3" t="n"/>
       <c r="K128" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
@@ -12584,12 +12584,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R128" s="3" t="inlineStr"/>
+      <c r="R128" s="3" t="n"/>
     </row>
     <row r="129" ht="45" customHeight="1">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>c53b5151ad08be983421</t>
+          <t>47229138beb6697d47ce</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -12602,7 +12602,7 @@
           <t>2026-09-23T18:11:47+00:00</t>
         </is>
       </c>
-      <c r="D129" s="3" t="inlineStr"/>
+      <c r="D129" s="3" t="n"/>
       <c r="E129" s="3" t="inlineStr">
         <is>
           <t>opportunity for Summer Analyst. This is</t>
@@ -12628,7 +12628,7 @@
           <t>Los Angeles</t>
         </is>
       </c>
-      <c r="J129" s="3" t="inlineStr"/>
+      <c r="J129" s="3" t="n"/>
       <c r="K129" s="4" t="inlineStr">
         <is>
           <t>https://recruiting.ultipro.com/LOS1000LADOD/JobBoard/5365ad6e-23ff-4703-bb77-1e9451fb855e/OpportunityDetail?opportunityId=fb796a9d-16f1-4514-8f6b-e5c5dbbb6019</t>
@@ -12688,12 +12688,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R129" s="3" t="inlineStr"/>
+      <c r="R129" s="3" t="n"/>
     </row>
     <row r="130" ht="45" customHeight="1">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>d75bced132e4a967d1dd</t>
+          <t>d03c3d204190100d987d</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -12706,7 +12706,7 @@
           <t>2026-09-23T19:18:26+00:00</t>
         </is>
       </c>
-      <c r="D130" s="3" t="inlineStr"/>
+      <c r="D130" s="3" t="n"/>
       <c r="E130" s="3" t="inlineStr">
         <is>
           <t>Graduate-Level Hiring Information Session</t>
@@ -12727,8 +12727,8 @@
           <t>Fall 2026</t>
         </is>
       </c>
-      <c r="I130" s="3" t="inlineStr"/>
-      <c r="J130" s="3" t="inlineStr"/>
+      <c r="I130" s="3" t="n"/>
+      <c r="J130" s="3" t="n"/>
       <c r="K130" s="4" t="inlineStr">
         <is>
           <t>https://app.eightfold.ai/events/candidate/landing?plannedEventId=agEXbYjN4</t>
@@ -12788,12 +12788,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R130" s="3" t="inlineStr"/>
+      <c r="R130" s="3" t="n"/>
     </row>
     <row r="131" ht="45" customHeight="1">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>9289b2e4630a9fd9a05a</t>
+          <t>391f08cab1f339ac5d60</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -12836,7 +12836,7 @@
           <t>San Francisco, New York</t>
         </is>
       </c>
-      <c r="J131" s="3" t="inlineStr"/>
+      <c r="J131" s="3" t="n"/>
       <c r="K131" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/figma/jobs/6178851004?gh_jid=6178851004&amp;gh_src=28109e334us</t>
@@ -12892,12 +12892,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R131" s="3" t="inlineStr"/>
+      <c r="R131" s="3" t="n"/>
     </row>
     <row r="132" ht="45" customHeight="1">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>046cae51d7151f663250</t>
+          <t>dbc3f10d11839929efed</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -12910,7 +12910,7 @@
           <t>2026-09-23T19:42:06+00:00</t>
         </is>
       </c>
-      <c r="D132" s="3" t="inlineStr"/>
+      <c r="D132" s="3" t="n"/>
       <c r="E132" s="3" t="inlineStr">
         <is>
           <t>Registration Deadline: Oct 2, 2026 12:00 PM</t>
@@ -12931,7 +12931,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="I132" s="3" t="inlineStr"/>
+      <c r="I132" s="3" t="n"/>
       <c r="J132" s="3" t="inlineStr">
         <is>
           <t>Oct 2, 2026</t>
@@ -12994,12 +12994,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R132" s="3" t="inlineStr"/>
+      <c r="R132" s="3" t="n"/>
     </row>
     <row r="133" ht="45" customHeight="1">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>35a323c15ead7138213a</t>
+          <t>c94b7b1763396ee07770</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -13032,13 +13032,13 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H133" s="3" t="inlineStr"/>
+      <c r="H133" s="3" t="n"/>
       <c r="I133" s="3" t="inlineStr">
         <is>
           <t>Mountain View</t>
         </is>
       </c>
-      <c r="J133" s="3" t="inlineStr"/>
+      <c r="J133" s="3" t="n"/>
       <c r="K133" s="4" t="inlineStr">
         <is>
           <t>https://apply.careers.microsoft.com/careers/job/1970393557004819?domain=microsoft.com&amp;hl=en</t>
@@ -13088,12 +13088,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R133" s="3" t="inlineStr"/>
+      <c r="R133" s="3" t="n"/>
     </row>
     <row r="134" ht="45" customHeight="1">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>5ad854bbad4ccc3da64b</t>
+          <t>8ca3457cf46c04a66feb</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -13131,8 +13131,8 @@
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I134" s="3" t="inlineStr"/>
-      <c r="J134" s="3" t="inlineStr"/>
+      <c r="I134" s="3" t="n"/>
+      <c r="J134" s="3" t="n"/>
       <c r="K134" s="4" t="inlineStr">
         <is>
           <t>https://nvidia.wd5.myworkdayjobs.com/en-US/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Product-Design-Intern--AI-Infrastructure---Summer-2027_JR2025784</t>
@@ -13186,12 +13186,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R134" s="3" t="inlineStr"/>
+      <c r="R134" s="3" t="n"/>
     </row>
     <row r="135" ht="45" customHeight="1">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>af56e3ac1f7c9bf49843</t>
+          <t>423c4f248458dd75f6a1</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -13204,7 +13204,7 @@
           <t>2026-09-23T20:22:21+00:00</t>
         </is>
       </c>
-      <c r="D135" s="3" t="inlineStr"/>
+      <c r="D135" s="3" t="n"/>
       <c r="E135" s="3" t="inlineStr">
         <is>
           <t>Applications Open Technology ; _</t>
@@ -13215,11 +13215,11 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G135" s="3" t="inlineStr"/>
-      <c r="H135" s="3" t="inlineStr"/>
-      <c r="I135" s="3" t="inlineStr"/>
-      <c r="J135" s="3" t="inlineStr"/>
-      <c r="K135" s="3" t="inlineStr"/>
+      <c r="G135" s="3" t="n"/>
+      <c r="H135" s="3" t="n"/>
+      <c r="I135" s="3" t="n"/>
+      <c r="J135" s="3" t="n"/>
+      <c r="K135" s="3" t="n"/>
       <c r="L135" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/stories/zero2sudo/</t>
@@ -13261,12 +13261,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R135" s="3" t="inlineStr"/>
+      <c r="R135" s="3" t="n"/>
     </row>
     <row r="136" ht="45" customHeight="1">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>3c56e34b3f28ed5c759a</t>
+          <t>6a307f121e427e87f81f</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -13299,9 +13299,9 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H136" s="3" t="inlineStr"/>
-      <c r="I136" s="3" t="inlineStr"/>
-      <c r="J136" s="3" t="inlineStr"/>
+      <c r="H136" s="3" t="n"/>
+      <c r="I136" s="3" t="n"/>
+      <c r="J136" s="3" t="n"/>
       <c r="K136" s="4" t="inlineStr">
         <is>
           <t>https://oncampus2026berkeleybuilderpan.splashthat.com</t>
@@ -13354,12 +13354,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R136" s="3" t="inlineStr"/>
+      <c r="R136" s="3" t="n"/>
     </row>
     <row r="137" ht="45" customHeight="1">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>bd55e3972784867d890e</t>
+          <t>a6b88546fd75425cac8a</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -13392,9 +13392,9 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H137" s="3" t="inlineStr"/>
-      <c r="I137" s="3" t="inlineStr"/>
-      <c r="J137" s="3" t="inlineStr"/>
+      <c r="H137" s="3" t="n"/>
+      <c r="I137" s="3" t="n"/>
+      <c r="J137" s="3" t="n"/>
       <c r="K137" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/ziprecruiter/jobs/8180455</t>
@@ -13450,12 +13450,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R137" s="3" t="inlineStr"/>
+      <c r="R137" s="3" t="n"/>
     </row>
     <row r="138" ht="45" customHeight="1">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>c467252f03d2556818a7</t>
+          <t>be349433e6d0fa78959a</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -13468,7 +13468,7 @@
           <t>2026-09-23T21:13:20+00:00</t>
         </is>
       </c>
-      <c r="D138" s="3" t="inlineStr"/>
+      <c r="D138" s="3" t="n"/>
       <c r="E138" s="3" t="inlineStr">
         <is>
           <t>Software Engineering</t>
@@ -13484,13 +13484,13 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H138" s="3" t="inlineStr"/>
+      <c r="H138" s="3" t="n"/>
       <c r="I138" s="3" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="J138" s="3" t="inlineStr"/>
+      <c r="J138" s="3" t="n"/>
       <c r="K138" s="4" t="inlineStr">
         <is>
           <t>https://seatgeek.com/jobs/8227553</t>
@@ -13542,12 +13542,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R138" s="3" t="inlineStr"/>
+      <c r="R138" s="3" t="n"/>
     </row>
     <row r="139" ht="45" customHeight="1">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>b264d6481d33cdaa1219</t>
+          <t>49707b2299a100c1db5d</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -13560,7 +13560,7 @@
           <t>2026-09-23T21:14:32+00:00</t>
         </is>
       </c>
-      <c r="D139" s="3" t="inlineStr"/>
+      <c r="D139" s="3" t="n"/>
       <c r="E139" s="3" t="inlineStr">
         <is>
           <t>New Grad</t>
@@ -13576,13 +13576,13 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H139" s="3" t="inlineStr"/>
+      <c r="H139" s="3" t="n"/>
       <c r="I139" s="3" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="J139" s="3" t="inlineStr"/>
+      <c r="J139" s="3" t="n"/>
       <c r="K139" s="4" t="inlineStr">
         <is>
           <t>https://seatgeek.com/jobs/8227548</t>
@@ -13636,12 +13636,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R139" s="3" t="inlineStr"/>
+      <c r="R139" s="3" t="n"/>
     </row>
     <row r="140" ht="45" customHeight="1">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>6cd16254f396a9fad374</t>
+          <t>3903e266b68c83dae090</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -13684,7 +13684,7 @@
           <t>Mountain View</t>
         </is>
       </c>
-      <c r="J140" s="3" t="inlineStr"/>
+      <c r="J140" s="3" t="n"/>
       <c r="K140" s="4" t="inlineStr">
         <is>
           <t>https://apply.careers.microsoft.com/careers/job/1970393557004836?domain=microsoft.com</t>
@@ -13739,12 +13739,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R140" s="3" t="inlineStr"/>
+      <c r="R140" s="3" t="n"/>
     </row>
     <row r="141" ht="45" customHeight="1">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>a1384d44d1b4350117b1</t>
+          <t>96a8f509f22c0ccae8e6</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -13777,13 +13777,13 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H141" s="3" t="inlineStr"/>
+      <c r="H141" s="3" t="n"/>
       <c r="I141" s="3" t="inlineStr">
         <is>
           <t>Bellevue</t>
         </is>
       </c>
-      <c r="J141" s="3" t="inlineStr"/>
+      <c r="J141" s="3" t="n"/>
       <c r="K141" s="4" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/LinkedIn3/744000151447279-software-engineer</t>
@@ -13844,12 +13844,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R141" s="3" t="inlineStr"/>
+      <c r="R141" s="3" t="n"/>
     </row>
     <row r="142" ht="45" customHeight="1">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>914f86da78d0de45f3e4</t>
+          <t>fecec3cda16c47d622f4</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -13862,7 +13862,7 @@
           <t>2026-09-23T22:22:30+00:00</t>
         </is>
       </c>
-      <c r="D142" s="3" t="inlineStr"/>
+      <c r="D142" s="3" t="n"/>
       <c r="E142" s="3" t="inlineStr">
         <is>
           <t>Product Management</t>
@@ -13883,8 +13883,8 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="I142" s="3" t="inlineStr"/>
-      <c r="J142" s="3" t="inlineStr"/>
+      <c r="I142" s="3" t="n"/>
+      <c r="J142" s="3" t="n"/>
       <c r="K142" s="4" t="inlineStr">
         <is>
           <t>https://luma.com/ramp-waterloo-coffee</t>
@@ -13943,12 +13943,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R142" s="3" t="inlineStr"/>
+      <c r="R142" s="3" t="n"/>
     </row>
     <row r="143" ht="45" customHeight="1">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>95240c4e8ffdb47a93a1</t>
+          <t>03d5f3f7b2423885d0c9</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -13991,7 +13991,7 @@
           <t>Bellevue, Mountain View</t>
         </is>
       </c>
-      <c r="J143" s="3" t="inlineStr"/>
+      <c r="J143" s="3" t="n"/>
       <c r="K143" s="4" t="inlineStr">
         <is>
           <t>https://www.databricks.com/company/careers/university-recruiting---engineering/software-engineering-intern-2027-start---winter-8732364002</t>
@@ -14050,12 +14050,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R143" s="3" t="inlineStr"/>
+      <c r="R143" s="3" t="n"/>
     </row>
     <row r="144" ht="45" customHeight="1">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>82fd7d03371c972a3ddc</t>
+          <t>1fe3a05767b0b70d6552</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -14098,7 +14098,7 @@
           <t>Seattle</t>
         </is>
       </c>
-      <c r="J144" s="3" t="inlineStr"/>
+      <c r="J144" s="3" t="n"/>
       <c r="K144" s="4" t="inlineStr">
         <is>
           <t>https://www.atlassian.com/company/careers/details/26271</t>
@@ -14153,12 +14153,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R144" s="3" t="inlineStr"/>
+      <c r="R144" s="3" t="n"/>
     </row>
     <row r="145" ht="45" customHeight="1">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>1a691906372350b2c9fa</t>
+          <t>334329f64238cf7a5345</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -14191,13 +14191,13 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H145" s="3" t="inlineStr"/>
+      <c r="H145" s="3" t="n"/>
       <c r="I145" s="3" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="J145" s="3" t="inlineStr"/>
+      <c r="J145" s="3" t="n"/>
       <c r="K145" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/ramp/acf6b28d-767f-483f-8ff2-114620cd7e04</t>
@@ -14251,12 +14251,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R145" s="3" t="inlineStr"/>
+      <c r="R145" s="3" t="n"/>
     </row>
     <row r="146" ht="45" customHeight="1">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>770fb578a354b9f72a25</t>
+          <t>2ca5da204f5c4a9aacab</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -14289,13 +14289,13 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H146" s="3" t="inlineStr"/>
+      <c r="H146" s="3" t="n"/>
       <c r="I146" s="3" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="J146" s="3" t="inlineStr"/>
+      <c r="J146" s="3" t="n"/>
       <c r="K146" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/ramp/a13ae586-f4cb-4385-8822-c42b9b54ed74</t>
@@ -14349,12 +14349,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R146" s="3" t="inlineStr"/>
+      <c r="R146" s="3" t="n"/>
     </row>
     <row r="147" ht="45" customHeight="1">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>0e714ed621f1777e06fc</t>
+          <t>0fe27c247dbc169c7a21</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -14387,13 +14387,13 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H147" s="3" t="inlineStr"/>
+      <c r="H147" s="3" t="n"/>
       <c r="I147" s="3" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="J147" s="3" t="inlineStr"/>
+      <c r="J147" s="3" t="n"/>
       <c r="K147" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/ramp/fcf118cc-521a-4a62-9d13-945e5b6e3cb8</t>
@@ -14447,12 +14447,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R147" s="3" t="inlineStr"/>
+      <c r="R147" s="3" t="n"/>
     </row>
     <row r="148" ht="45" customHeight="1">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>6878c79d4a64626bc1de</t>
+          <t>2ab263ea09598e8f9e90</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -14485,13 +14485,13 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H148" s="3" t="inlineStr"/>
+      <c r="H148" s="3" t="n"/>
       <c r="I148" s="3" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="J148" s="3" t="inlineStr"/>
+      <c r="J148" s="3" t="n"/>
       <c r="K148" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/ramp/b66be397-240b-41a6-9b05-493299b270a9</t>
@@ -14545,12 +14545,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R148" s="3" t="inlineStr"/>
+      <c r="R148" s="3" t="n"/>
     </row>
     <row r="149" ht="45" customHeight="1">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>8bd6d354ea30fa8f1c38</t>
+          <t>18c6cd3fe64b3ea0ff9f</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -14578,7 +14578,7 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G149" s="3" t="inlineStr"/>
+      <c r="G149" s="3" t="n"/>
       <c r="H149" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
@@ -14589,7 +14589,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="J149" s="3" t="inlineStr"/>
+      <c r="J149" s="3" t="n"/>
       <c r="K149" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/astranis/jobs/4716088006</t>
@@ -14647,10 +14647,979 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R149" s="3" t="inlineStr"/>
+      <c r="R149" s="3" t="n"/>
+    </row>
+    <row r="150" ht="45" customHeight="1">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>7098899272a9e8af44f6</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T15:14:30.847870+00:00</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T13:58:48+00:00</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="inlineStr"/>
+      <c r="J150" s="3" t="inlineStr"/>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/cerebras/99c289fa-8fc6-49f7-b7e8-78ac4e9d99ac/application?source=zero2sudo</t>
+        </is>
+      </c>
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
+          <t>@ jobs.ashbyhq.com C+:
+Gerebras
+Software Engineer - New Grad 2026
+Location
+Toronto, CAN
+Employment Type
+Full time
+@ JOBS.ASHBYHQ.COM
+Department
+University Departm
+Cerebras New Grad SWE
+Y Autofill from resume
+Upload your resume here to autofill key
+application fields.
+Cookie Preferences
+Upload file
+https://scontent-atl3-2.cdninstagram.com/v/t51.71878-15/823965176_1657182112468357_2905658400007234779_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5MzI5ODc2NjUzOTY3ODEwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=M__uB0EE9nMQ7kNvwHu7sYx&amp;_nc_oc=Adr-UCUDey0XB66yoSsJToCABtS8EZpWEO0oFHCADp_6Vk_oqpV06rKANQxfu7y7SCQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;oh=00_AQKKyEVgRFm0BqTxDdw4iJ-ZxW54HnpiRcg3TOB2OhuJow&amp;oe=6ABB0803
+https://scontent-atl3-2.cdninstagram.com/v/t51.71878-15/823965176_1657182112468357_2905658400007234779_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5MzI5ODc2NjUzOTY3ODEwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=M__uB0EE9nMQ7kNvwHu7sYx&amp;_nc_oc=Adr-UCUDey0XB66yoSsJToCABtS8EZpWEO0oFHCADp_6Vk_oqpV06rKANQxfu7y7SCQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;oh=00_AQI6nMYXbs8UmunvFNS66iru0_PWVNgNyZiD1p6bhNeixA&amp;oe=6ABB0803
+https://scontent-atl3-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwG2Zbdj&amp;_nc_oc=AdpPL-ekOE7yCZKpp7q9-AFthrMciBbwOBRKY8lwkPP-PDux-Lp4Gvyf95O2Aym5Jqs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIiusJf0YzNCNyJKOXQmkXsu08sjXnXqPt63pERummjEA&amp;oe=6ABB0259
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.ashbyhq.com%2Fcerebras%2F99c289fa-8fc6-49f7-b7e8-78ac4e9d99ac%2Fapplication%3Futm_source%3D6yz8EKyljj%26source%3Dzero2sudo%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafPnQGl-WxdESAmObrDVOj4pMdZ0OjORsi8ZsYXac64Vls-FTUbnFJtrXbkIA_aem_SJY5gshkJbGvjG1W_ELt8A&amp;e=AUDwL1UzF6_gsYzkEXaL4YE7LUAyALzNWL0xK4qpLdTHyPeiDMgrlhnajhIHLECgEbfosZa1-u13xVNaYGbHCj-7Y5upYfV5_shkbR31wA
+https://scontent-atl3-1.cdninstagram.com/o1/v/t2/f2/m78/AQPeEh8Ec7o1gbiPh0E0d82PXbPBlIeKkWTdkCDt_3iLp4zHF5MbZJEVrciXP3Kxd32dykYCz4EM4ugFL0LqlOizEnt39Y4yuFzP6gE.mp4?_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ohc=AOx8og-XE4AQ7kNvwEJ56fA&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgxNzk5Nzc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=f957d03a005a7ee9&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzZFNDIzNjFGMUY0QjM3N0Y0RjI5QkQ3M0U4NENDN0IxX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkwZ_j0sahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJU9UNcdWUNpMt0-UhR0cFNwkQ5Pok4oAToTJeHzs2rkQ&amp;oe=6AB71145</t>
+        </is>
+      </c>
+      <c r="O150" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P150" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q150" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R150" s="3" t="inlineStr"/>
+    </row>
+    <row r="151" ht="45" customHeight="1">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>e7773f47f444ea257bad</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T15:14:32.055762+00:00</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T13:59:40+00:00</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq — Internship</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr"/>
+      <c r="H151" s="3" t="inlineStr"/>
+      <c r="I151" s="3" t="inlineStr"/>
+      <c r="J151" s="3" t="inlineStr"/>
+      <c r="K151" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/cerebras/c4faac59-3dbb-4ab7-9f74-d1fcbcddc7c6/application?source=zero2sudo</t>
+        </is>
+      </c>
+      <c r="L151" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
+          <t>@ jobs.ashbyhg.com
+€ Gerebras
+| DevOps Engineer Intern - PEY
+Location
+Toronto, CAN
+Employment Type
+Intern
+@ DEVOPS ENGINEER INTERN
+Department
+University Departments
+Overview Application
+https://scontent-atl3-2.cdninstagram.com/v/t51.71878-15/822639545_2598233393953873_5788982346146820681_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MzI5OTIwMDQ4OTgzMTk4Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=jmaoMZuSQyMQ7kNvwHC8aw_&amp;_nc_oc=AdryAP5lRxjGFvNwCK8eDkZHxDDmqRmXhQnM7YrO1Cz5GhwMwoFS5VNwfQhOwhSh6Ek&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;oh=00_AQL05XgDJnA5RnBgO1Mk2szmMoiku7mD8dU4aykG7URQVA&amp;oe=6ABB1BD3
+https://scontent-atl3-2.cdninstagram.com/v/t51.71878-15/822639545_2598233393953873_5788982346146820681_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MzI5OTIwMDQ4OTgzMTk4Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=jmaoMZuSQyMQ7kNvwHC8aw_&amp;_nc_oc=AdryAP5lRxjGFvNwCK8eDkZHxDDmqRmXhQnM7YrO1Cz5GhwMwoFS5VNwfQhOwhSh6Ek&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;oh=00_AQJb-vIfWWE7ENDEWlmIvQRxGR2FXYRoDoPNfgzhm6Y-nQ&amp;oe=6ABB1BD3
+https://scontent-atl3-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwG2Zbdj&amp;_nc_oc=AdpPL-ekOE7yCZKpp7q9-AFthrMciBbwOBRKY8lwkPP-PDux-Lp4Gvyf95O2Aym5Jqs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIiusJf0YzNCNyJKOXQmkXsu08sjXnXqPt63pERummjEA&amp;oe=6ABB0259
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.ashbyhq.com%2Fcerebras%2Fc4faac59-3dbb-4ab7-9f74-d1fcbcddc7c6%2Fapplication%3Futm_source%3D6yz8EKyljj%26source%3Dzero2sudo%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAad5Ghh5zZmP0jyUse1wKElMWnMbQMyLOJIi30TLfEmXX77Ri3qT9GbESN__Vg_aem_WtsJlnCThfxQ_MDqmdRAdA&amp;e=AUB_WLSM8rFuwLoDpDgBSQ_1juVq3WZTEIKyWjtVeNOOaHa97tQ1YaNBb0y1_R4AVNuugzE4_gSoBu9WN-37swEwtC2zE-CwacxWW2AIgQ
+https://scontent-atl3-2.cdninstagram.com/o1/v/t2/f2/m78/AQPHjZXu9uSjFDowBMSHfgLCoMcaaJLIvZlh_pMCw2xSIjhgEqrhDVED6s0TLO1BIUyetH5p-E6AcOZgAIFTcnDLvnuGXduHZaxtRhY.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_ohc=AGypzRwezrkQ7kNvwF2yPdK&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgxODAxMzM2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=4dc1a0a068818c16&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0Y3NEYxRkY4OEU1N0M3NDZBMEQ4RjFFOUFENzM0MUIxX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkvYL408ahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIvaXflF-Sbx08y3dyg66CLV1p5c5ZoV7AOE5Jqr4mQyA&amp;oe=6AB70C8C</t>
+        </is>
+      </c>
+      <c r="O151" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P151" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q151" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R151" s="3" t="inlineStr"/>
+    </row>
+    <row r="152" ht="45" customHeight="1">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>f449cd91b7e57d900840</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T15:14:34.416221+00:00</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T14:00:22+00:00</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr"/>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>Our Summer 2027 Early Talent internships are a</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr"/>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="J152" s="3" t="inlineStr"/>
+      <c r="K152" s="4" t="inlineStr">
+        <is>
+          <t>https://campus-libertymutual.icims.com/jobs/77035/2027-techstart-summer-internship-program/job?mode=view</t>
+        </is>
+      </c>
+      <c r="L152" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
+          <t>@ campus-libertymutual.icims.c... CG:
+Inst
+Liberty Mutual.
+INSURANCE
+&lt; Welcome page Returning Candidate? Log back in!
+2027 TechStart Summer
+Internship Program
+US-NH-Portsmouth | US-MA-
+Boston | US-IN-Indianapolis | US-
+TX-Plano
+ID 2026-77035 Position Type Intern/Coop
+(2) CAMPUS-LIBERTYMUTUAL.ICIMS.
+Flexible Time Off Annual 15
+Description
+We encourage interested candidates to apply
+promptly, as the role may be unposted once
+we've received a sufficient number of
+candidates. We conduct interviews and extend
+offers on a rolling basis.
+Our Summer 2027 Early Talent internships are a
+https://scontent-atl3-1.cdninstagram.com/v/t51.71878-15/817651275_1061149630092699_8682374756109858094_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MzI5OTU1Njk4MDM1MzUyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=vlEHL_QdYeMQ7kNvwFuRAuk&amp;_nc_oc=AdoEXf2V3DhkaS-xzTDCCFsop3zUcYxKQZ2MRR9SYSdqrTF_RgA8HxT7xRlXDrD2aZM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;oh=00_AQK8o_QBQIe0Ue6ZaxhereOdghJn_H1ODBwHBbaJqRaftQ&amp;oe=6ABB07C3
+https://scontent-atl3-1.cdninstagram.com/v/t51.71878-15/817651275_1061149630092699_8682374756109858094_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MzI5OTU1Njk4MDM1MzUyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=vlEHL_QdYeMQ7kNvwFuRAuk&amp;_nc_oc=AdoEXf2V3DhkaS-xzTDCCFsop3zUcYxKQZ2MRR9SYSdqrTF_RgA8HxT7xRlXDrD2aZM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;oh=00_AQK_TG8WBWD2tv8UuWZCTkDxaZ1U240ujav1UAUk9ML0Rw&amp;oe=6ABB07C3
+https://scontent-atl3-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwG2Zbdj&amp;_nc_oc=AdpPL-ekOE7yCZKpp7q9-AFthrMciBbwOBRKY8lwkPP-PDux-Lp4Gvyf95O2Aym5Jqs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIiusJf0YzNCNyJKOXQmkXsu08sjXnXqPt63pERummjEA&amp;oe=6ABB0259
+https://l.instagram.com/?u=https%3A%2F%2Fcampus-libertymutual.icims.com%2Fjobs%2F77035%2F2027-techstart-summer-internship-program%2Fjob%3Fmode%3Dview%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadSpFTj_qDsUXfbqldJT_zeX1d5ieDnEdp-6uG7mE1t8EG_e8yHb1maOkqbUA_aem_GAzSKN0aX6t_lFvoMXzXVw&amp;e=AUDPQX6zZQR7EcHIwcNy-DYMSOb1NHCK348C2JnkQE9U7lfZr3BM2QD4Z71lvUnwtGjYaK9D-Hu7kEQpslCCY-Ifl9SZ3arytg1JzPozGQ
+https://scontent-atl3-2.cdninstagram.com/o1/v/t2/f2/m78/AQMQSdzjQIU_4tMnOUUO3Q5Cjd0aFJiN4ZS5Eqpm7hUFelseRhen723Djc7ryLE5uciwswQYZxa4KtAbct56vd-QgXIv6kBGos6mmAE.mp4?_nc_cat=102&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_ohc=chM7CfZhRbIQ7kNvwHen3Vy&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgxODAyNTM2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=f357d0a0f8b50d2e&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzE0MTg0M0ZGQjU4NzQwOEE5NzY3QTAxQkVEQzFERkY1X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk9brq1MahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJexxDOWy1i5MMJzDNEtD1KiRiynat1Dko4e8Dihowx1A&amp;oe=6AB712C3</t>
+        </is>
+      </c>
+      <c r="O152" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P152" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q152" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R152" s="3" t="inlineStr"/>
+    </row>
+    <row r="153" ht="45" customHeight="1">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>5a57751d996f75a193b4</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T15:14:36.595484+00:00</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T14:01:00+00:00</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr"/>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>@ LIBMU NEW GRAD SWE</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>2027, 2026</t>
+        </is>
+      </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="J153" s="3" t="inlineStr"/>
+      <c r="K153" s="4" t="inlineStr">
+        <is>
+          <t>https://campus-libertymutual.icims.com/jobs/77144/2027-techstart-full-time-program/job?mode=view&amp;mobile=false&amp;width=735&amp;height=500&amp;bga=true&amp;needsRedirect=false&amp;jan1offset=-300&amp;jun1offset=-240</t>
+        </is>
+      </c>
+      <c r="L153" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
+          <t>x @ campus-libertymutual.icims.c... C+:
+&lt; Welcome page
+Returning Candidate? Log back in!
+2027 TechStart Full-Time
+Program
+US-NH-Portsmouth | US-MA-
+Boston | US-TX-Plano | US-
+IN-Indianapolis
+ID 2026-77144 Position Type Full-Time
+@ LIBMU NEW GRAD SWE
+Flexible Time Off Annual l-days 15
+Description
+Description
+At Liberty Mutual, we're on a mission to
+change the way people experience
+insurance in a world rewired by Al. From
+test-driving the latest technologies to
+building intuitive applications our
+customers rely on, technology is the
+https://scontent-atl3-2.cdninstagram.com/v/t51.71878-15/823786723_1093934440038884_7782146159043644960_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MzI5OTg3NDI3MTM4ODIzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=OgG3idqOElAQ7kNvwH2SIeF&amp;_nc_oc=Adoy6qbSbwtBNKOk8CwI0UVqqrsM7sZKUQWvUtvND4ipYsG8OxBQlc_9WpOM-tV7g6A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;oh=00_AQLljYDaSshGOVX8eqRqE3XDbr0hN_qTmWoVdMCaDWZCnA&amp;oe=6ABB0E08
+https://scontent-atl3-2.cdninstagram.com/v/t51.71878-15/823786723_1093934440038884_7782146159043644960_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MzI5OTg3NDI3MTM4ODIzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=OgG3idqOElAQ7kNvwH2SIeF&amp;_nc_oc=Adoy6qbSbwtBNKOk8CwI0UVqqrsM7sZKUQWvUtvND4ipYsG8OxBQlc_9WpOM-tV7g6A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;oh=00_AQJjraK7n_CQ-EZC6vYWWkR99dSIsolM_N8WHDZBRCvKjQ&amp;oe=6ABB0E08
+https://scontent-atl3-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwG2Zbdj&amp;_nc_oc=AdpPL-ekOE7yCZKpp7q9-AFthrMciBbwOBRKY8lwkPP-PDux-Lp4Gvyf95O2Aym5Jqs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIiusJf0YzNCNyJKOXQmkXsu08sjXnXqPt63pERummjEA&amp;oe=6ABB0259
+https://l.instagram.com/?u=https%3A%2F%2Fcampus-libertymutual.icims.com%2Fjobs%2F77144%2F2027-techstart-full-time-program%2Fjob%3Fmode%3Dview%26mobile%3Dfalse%26width%3D735%26height%3D500%26bga%3Dtrue%26needsRedirect%3Dfalse%26jan1offset%3D-300%26jun1offset%3D-240%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAad3LV9AtSBtyN6-9T8-vXnuB7Ef3rWkHT_nfHcn6YiQTNEo6wMF7OcDLe1nlw_aem_9vQBzx8Dzuz40-f9IikyBA&amp;e=AUBJlUri-yJC8JGS6-hFm7oSuQPh2hlBlzXrNALy9eO4X_iSjsQKTbT7krYw58Fmt9v-DJAnQA2veqgEWRM9v-UOGlHlMQEwQbPmvA2vFQ
+https://scontent-atl3-2.cdninstagram.com/o1/v/t2/f2/m78/AQMpv8ux289pJTDIOfykX2cDCF9SVYgJ6FOfJ5giyf6MPDxQYnzgucHFMf0cg1Gri16jTZ73euuHet71_xOSuU2CHd5wW8aFxIjJWBk.mp4?_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_ohc=wLu4A4FUWEIQ7kNvwFNIJum&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgxODA1MzU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=7179fbe96310187f&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0NCNEU0RjA0RTFDNEVFQzRCMUQwRDA4OTI4M0Y1QkE1X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk37L31sahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQI6_-AhIimPqDfi66kRmHTxo1BdjgZnHX2LravLoRy5hg&amp;oe=6AB70E46</t>
+        </is>
+      </c>
+      <c r="O153" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P153" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q153" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R153" s="3" t="inlineStr"/>
+    </row>
+    <row r="154" ht="45" customHeight="1">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>838767d8463b0c180ad1</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T15:14:40.583361+00:00</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T14:16:18+00:00</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr"/>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>Summer Internship Program Whippany</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr"/>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I154" s="3" t="inlineStr"/>
+      <c r="J154" s="3" t="inlineStr"/>
+      <c r="K154" s="4" t="inlineStr">
+        <is>
+          <t>https://search.jobs.barclays/search-jobs?acm=8736272&amp;alrpm=ALL&amp;ascf=%5B%7B%22key%22%3A%22custom_fields.MultiValueField3%22%2C%22value%22%3A%22Internships+Technology%22%7D%5D</t>
+        </is>
+      </c>
+      <c r="L154" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
+          <t>2027 Technology Developer Summer
+Internship Program Wilmington
+Wilmington, United States
+© 03 Sep
+2027 Technology Developer Summer
+Internship Program Whippany
+Whippany, United States
+2027 Technology C Security
+Summer Internship Program Whippany
+Whippany, United States
+© 03 Sep
+https://scontent-atl3-2.cdninstagram.com/v/t51.71878-15/821699106_3312770548893158_8179528120559988069_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MzMwNzU3OTE4MjYxOTM4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=fOc1r3Scvt4Q7kNvwEqd4JJ&amp;_nc_oc=AdocWhMBAGGAniM8WL6dDVNLmwFUmB9CgV1IizceW4L2vxtC6mf7bHfG-hj-DE6BPy8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;oh=00_AQK89MCf7ab71jRgQXXWFRLVxexjc1OE45HFyFhBYmwvqA&amp;oe=6ABAFEC6
+https://scontent-atl3-2.cdninstagram.com/v/t51.71878-15/821699106_3312770548893158_8179528120559988069_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MzMwNzU3OTE4MjYxOTM4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=fOc1r3Scvt4Q7kNvwEqd4JJ&amp;_nc_oc=AdocWhMBAGGAniM8WL6dDVNLmwFUmB9CgV1IizceW4L2vxtC6mf7bHfG-hj-DE6BPy8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;oh=00_AQKxFFkwOU9rFTX3EYWAfZQYd3S8GvO0g4LhQNMaxTqhAQ&amp;oe=6ABAFEC6
+https://scontent-atl3-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwG2Zbdj&amp;_nc_oc=AdpPL-ekOE7yCZKpp7q9-AFthrMciBbwOBRKY8lwkPP-PDux-Lp4Gvyf95O2Aym5Jqs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIiusJf0YzNCNyJKOXQmkXsu08sjXnXqPt63pERummjEA&amp;oe=6ABB0259
+https://l.instagram.com/?u=https%3A%2F%2Fsearch.jobs.barclays%2Fsearch-jobs%3Facm%3D8736272%26alrpm%3DALL%26ascf%3D%255B%257B%2522key%2522%253A%2522custom_fields.MultiValueField3%2522%252C%2522value%2522%253A%2522Internships%2BTechnology%2522%257D%255D%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafhlV2yZnfL-H_SZQGVY3UI2PGVSxk4rNepFx1SQd-05eZ7j1uJ1Oodou58dw_aem_b0zIuZT-TLZMg9qFlIdu4Q&amp;e=AUAF_UHewVaZjilR6h_u412mouv2_fg35qdmURXo0R_DKAhjPHJZCoFYESJjtXKpJixNOgBzwArdf4zhnBgeLVtupB0DKfTm4HHl_PiPBA
+https://scontent-atl3-2.cdninstagram.com/o1/v/t2/f2/m78/AQMSS33vxO8pCHZxnG212CfXya6JRv5D_ofYlEvaNe86QwFP6dbrnW-XkzPAce08htnib3LnywA8_6LmL5L2JYWRUFVFK2t_wMuWtOs.mp4?_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_ohc=lYsLFZG1WFAQ7kNvwHwr6Zi&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgxODMwNjc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=fe337dc934150427&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzMyNDdDOTIyQjY3OTI0QkQ0REQ4QjcwOTdBMkY3QUFCX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk44zm6cahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJ0NK5a4dFD5QDWqwK0kwaylk-njsEIUu4LKUTNFLZcUg&amp;oe=6AB71446</t>
+        </is>
+      </c>
+      <c r="O154" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P154" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q154" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R154" s="3" t="inlineStr"/>
+    </row>
+    <row r="155" ht="45" customHeight="1">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>f6bf7bc78c816475e005</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T15:14:43.083649+00:00</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T14:18:47+00:00</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>Meta — Quant</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>Quant</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr"/>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>Bellevue</t>
+        </is>
+      </c>
+      <c r="J155" s="3" t="inlineStr"/>
+      <c r="K155" s="4" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/profile/job_details/1609178343953401</t>
+        </is>
+      </c>
+      <c r="L155" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
+          <t>@ metacareers.com C:
+Instagram
+— MMeta
+Do
+&lt; Back to Jobs
+Production Engineering
+Intern
+Bellevue, WA +1 location
+Production Engineering +1more
+Apply now
+Production Engineers (PEs) at Meta are
+(Z) META PROD ENGINEER INTERN!
+of every major engi ffort that keeps
+our platforms runnin thly and scaling
+efficiently.
+&amp; Meta drop - quant trading firms
+frequently poach interns and new
+M grads from this role at Meta!
+writing high-quality code, solving cor s*¢
+problems in live production, and tackh.
+challenges that impact over 2 billion people
+https://scontent-atl3-1.cdninstagram.com/v/t51.71878-15/817383517_4640595566168685_4462576466083505619_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MzMwODgzMTI0MTExMzQ1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=gvBDG7lSLBgQ7kNvwFWw6Jf&amp;_nc_oc=AdrWRLW9PEAUSYLYO09vtsra2nqGe28Te7IuGfyvFLqi2-2TK4vPgUtOYaV0LbBTaj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;oh=00_AQIDSXDnF926sLZeN45k_9rBts9fv6YOi92n6ia5RvDVPQ&amp;oe=6ABB080C
+https://scontent-atl3-1.cdninstagram.com/v/t51.71878-15/817383517_4640595566168685_4462576466083505619_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MzMwODgzMTI0MTExMzQ1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=gvBDG7lSLBgQ7kNvwFWw6Jf&amp;_nc_oc=AdrWRLW9PEAUSYLYO09vtsra2nqGe28Te7IuGfyvFLqi2-2TK4vPgUtOYaV0LbBTaj0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;oh=00_AQLI0WX5zLreFxVKdJZDWtkCbbI4_aPZ-9EcPwBgyDrU0w&amp;oe=6ABB080C
+https://scontent-atl3-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwG2Zbdj&amp;_nc_oc=AdpPL-ekOE7yCZKpp7q9-AFthrMciBbwOBRKY8lwkPP-PDux-Lp4Gvyf95O2Aym5Jqs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIiusJf0YzNCNyJKOXQmkXsu08sjXnXqPt63pERummjEA&amp;oe=6ABB0259
+https://l.instagram.com/?u=https%3A%2F%2Fwww.metacareers.com%2Fprofile%2Fjob_details%2F1609178343953401%2F%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafDkmKlmGRD9NAVKTBJmTOcfw6nRcFSc4U3ys9kq1VGFrdNf2hQ5cmdYj1dYQ_aem_NY_JSsZ0xkYumA1SppXH-A&amp;e=AUD4z2s0FdhEu00qw1LiCueIevcjwsx4LyhxxYwrA4IbbW5GhtwLnzwTtDVBjTQcg_FB-PhqI7ijwHXtDb0d8tc2CZV1ZhcU8ffQZWahDw
+https://scontent-atl3-2.cdninstagram.com/o1/v/t2/f2/m78/AQOUB8m-oDV88m9076aSstCIe_NGqqZBJM7f1-Hfm4FsvDZKBZ1xp-r4DDBRqf9q8PYttoJZDIIWwoq_n65XNyCktvNUwzkUuRog5D4.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_ohc=attGICsVWfMQ7kNvwGbOPAm&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgxODM1ODY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=9fc67d9f9fab29db&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzQwNDNCNDVBMTBFRUUwN0QyNkEwRUVEOTYxQUUwQkI1X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkoofV7cahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLOiODJ1BbqSXS_ORZCS_JUN8AN8f1hMq_r400D87Hmnw&amp;oe=6AB736A8</t>
+        </is>
+      </c>
+      <c r="O155" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P155" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q155" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R155" s="3" t="inlineStr"/>
+    </row>
+    <row r="156" ht="45" customHeight="1">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>b7d8d5f1836d97b9794c</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T15:14:47.312790+00:00</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T15:08:18+00:00</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>Wurljobs</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>Wurljobs — Data Science</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr"/>
+      <c r="I156" s="3" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="J156" s="3" t="inlineStr"/>
+      <c r="K156" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/wurljobs/jobs/4716249006</t>
+        </is>
+      </c>
+      <c r="L156" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
+          <t>New
+Data Science Intern
+© Remote - United States
+About Wurl, LLC.
+At Wurl, our mission is to create innovative
+technologies and services that help
+accelerate the shift to streaming. At our core
+we are innovators focused on driving the
+streaming industry forward with
+technologies that help connect viewers to
+thea rinht eantant and ade Oiirtachnalaayv
+(D JOB-BOARDS.GREENHOUSE.I0
+viewers, and ultimatef increase their —
+revenue.
+In 2022, Wurl was ac y AppLovin
+(Nasdaq: APP), a leading marketing
+platform, giving our employees the be
+both worlds: the dynamic envionment =
+150+ person startup as well as the stab
+https://scontent-atl3-1.cdninstagram.com/v/t51.71878-15/823914167_1414956247461116_333002267403923827_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MzMzMzc1NTIyMTU4NTA2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=bcvnRS-Z0t0Q7kNvwGn3-sM&amp;_nc_oc=AdqXCPGt89ZBkrLAYLv_KnGWBsW6d-bFKNr1-3VdqkzsPBM3_vC_c-JhEojN3RJrIHM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;oh=00_AQIJTXVPVMh_NbaDi2H0IKBXZfSh-mXnXwTSpKgv1BvSnw&amp;oe=6ABB17CD
+https://scontent-atl3-1.cdninstagram.com/v/t51.71878-15/823914167_1414956247461116_333002267403923827_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MzMzMzc1NTIyMTU4NTA2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=bcvnRS-Z0t0Q7kNvwGn3-sM&amp;_nc_oc=AdqXCPGt89ZBkrLAYLv_KnGWBsW6d-bFKNr1-3VdqkzsPBM3_vC_c-JhEojN3RJrIHM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;oh=00_AQKuLGEpmG0cleA2UEqenp1C0JG5xHkLdojHx-vZ_NcDrw&amp;oe=6ABB17CD
+https://scontent-atl3-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwG2Zbdj&amp;_nc_oc=AdpPL-ekOE7yCZKpp7q9-AFthrMciBbwOBRKY8lwkPP-PDux-Lp4Gvyf95O2Aym5Jqs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIiusJf0YzNCNyJKOXQmkXsu08sjXnXqPt63pERummjEA&amp;oe=6ABB0259
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fwurljobs%2Fjobs%2F4716249006%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAae1qpbcXYfwOE0LHesmC5ZJnBzYJhGtexM09HVWqR-Lbdumqgov5gnnzPh-hg_aem_xpwaPoivcBSkazEfSMiRaw&amp;e=AUBZ75W1cdpuS1n21rPx8HvaWaUTeBy7yq5yBNssqbKy9Xv3kKMnkjJaaixZbiY1wZZZT9RXN-hjUV1_ZIOGGSDZtVZsNuRjUc30MjMLuQ
+https://scontent-atl3-1.cdninstagram.com/o1/v/t2/f2/m78/AQNc3w6OBy93nd6GOby7V0jsut3TTm7VxHbTxKDNQmKPXD4OVAHH8jEcG1qP7ddUtZ0RdZ7_oqT1FWWgpHETwFFpxSXt5dXHFTJnMxI.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ohc=syiADvSe6l8Q7kNvwGO8qr_&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgxODg5ODk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=39465cbaae83696a&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0FBNDUwNzlFRDI2RkNFMTY3NjZFQzJCRjlCNTY0MjhGX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkleH1lcehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJaMZctx1rn6GdXo-1zoIKZwTNo9Ax8wMkx5hXu-ARzWQ&amp;oe=6AB72D05</t>
+        </is>
+      </c>
+      <c r="O156" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P156" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q156" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R156" s="3" t="inlineStr"/>
+    </row>
+    <row r="157" ht="45" customHeight="1">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>9f2a89e41d378d20d516</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T15:14:48.810149+00:00</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T15:08:53+00:00</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr"/>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>APPLY NOW</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I157" s="3" t="inlineStr"/>
+      <c r="J157" s="3" t="inlineStr"/>
+      <c r="K157" s="4" t="inlineStr">
+        <is>
+          <t>https://hdnn.fa.us6.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX/job/114233</t>
+        </is>
+      </c>
+      <c r="L157" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
+          <t>of vw t View More Jobs
+Software Developer Intern
+Job Identification 114233
+Job Category Information Technology
+Posting Date 09/24/2026, 05:06 AM
+Apply Before 12/30/2026, 04:00 PM
+Degree Level Some College
+(Z) HDNN.FA.US6.ORACLECLOUD.CO!
+Locations i?) tate Street,
+Bettendorf, IA, 52722, US
+APPLY NOW
+https://scontent-atl3-1.cdninstagram.com/v/t51.71878-15/823091580_1339220021561296_4928032290660834278_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MzMzNDAzNzYwNzc5NjE0Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=egWoa6kZSksQ7kNvwEDnteS&amp;_nc_oc=Adofa7Q9vuDSScX4cZ6d4FH2T-CKwEbpm6ovU7ZnmKZ41tahnKIbrYDFhN2G2Oym0mI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;oh=00_AQIMirLd11l-ZLQQ6wgtm_DD3CKKS3cmE6SvqqQ4bA7WFg&amp;oe=6ABB1703
+https://scontent-atl3-1.cdninstagram.com/v/t51.71878-15/823091580_1339220021561296_4928032290660834278_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MzMzNDAzNzYwNzc5NjE0Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=egWoa6kZSksQ7kNvwEDnteS&amp;_nc_oc=Adofa7Q9vuDSScX4cZ6d4FH2T-CKwEbpm6ovU7ZnmKZ41tahnKIbrYDFhN2G2Oym0mI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;oh=00_AQIc31COgz6VIP7jIy5n1_z8Zm-aie8Dpy_JbdMkE4Z2Vw&amp;oe=6ABB1703
+https://scontent-atl3-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwG2Zbdj&amp;_nc_oc=AdpPL-ekOE7yCZKpp7q9-AFthrMciBbwOBRKY8lwkPP-PDux-Lp4Gvyf95O2Aym5Jqs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIiusJf0YzNCNyJKOXQmkXsu08sjXnXqPt63pERummjEA&amp;oe=6ABB0259
+https://l.instagram.com/?u=https%3A%2F%2Fhdnn.fa.us6.oraclecloud.com%2FhcmUI%2FCandidateExperience%2Fen%2Fsites%2FCX%2Fjob%2F114233%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadTOKgsr8F2GJ1EFVIK5X4_NlsjxOnNE0PsiUWqu3YKFKpztpXaUUfuMrWHbg_aem_6yLGqObWjp7BVfHOg0knXg&amp;e=AUBsMBJ6XSHPqETzPfRywKS5-H5lXlWpwjC1M9L2nrI0gErVlolxWoSfrtnjS83amYAXN-xejw4A2vB5USwVMCUB0at4fHZuBICU2xLnOQ
+https://scontent-atl3-1.cdninstagram.com/o1/v/t2/f2/m78/AQNrmVpjLn625kLJ4rztSOuqKB2M5k1_Kv-oNth9pfEDnFoEwCOFe9Wm1Q7Xfb7szV2ME9hO79aw2i45i8fVcqLiwn1c9kgSBCgMsAY.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ohc=vswuEQnqV3QQ7kNvwHnKhR_&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgxODkxMzA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=6ef747527c3a30c&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzg1NDJENjlFMjM3RTJBODhDNjgxNzA5OTQ5NTUwMEFGX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkip38lsehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJikyxSOXLtGJnIkANlLcQEd333r_L9YO60tGWwHG7XtA&amp;oe=6AB72FA6</t>
+        </is>
+      </c>
+      <c r="O157" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P157" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q157" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R157" s="3" t="inlineStr"/>
+    </row>
+    <row r="158" ht="45" customHeight="1">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>6d71fb6352cb778fd028</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T15:14:50.014302+00:00</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T15:09:31+00:00</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>Kitware</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>Kitware — Internship</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr"/>
+      <c r="H158" s="3" t="inlineStr"/>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J158" s="3" t="inlineStr"/>
+      <c r="K158" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/kitware/e76197d1-4dc3-4f7c-a30a-597713283bb3/apply</t>
+        </is>
+      </c>
+      <c r="L158" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
+          <t>¢ kitware
+Computer Vision
+Co-Op
+Clifton Park, New York
+Technical - Computer Vision / Intern /
+On-Site
+@ JOBS.LEVER.CO
+SUBMIT YOUR ay i
+Resume/CV *
+Q) ATTACH RESUME/CV
+Full name *
+https://scontent-atl3-2.cdninstagram.com/v/t51.71878-15/824993255_1326503919430933_855979864078288521_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5MzMzNDM2MjE4ODY0MTU4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=rvzPI0Q9G44Q7kNvwHJMnnN&amp;_nc_oc=AdpP2rHhiVQTkruVvw7bgYPHn2HpQxNv7mxutbqhUH5CjvvUKLQuns1w9yfJ0RV1hak&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;oh=00_AQKHHd9R2oBDq2y3HPAWUoeSk41-HSstatpbnws9wi3TZA&amp;oe=6ABB2927
+https://scontent-atl3-2.cdninstagram.com/v/t51.71878-15/824993255_1326503919430933_855979864078288521_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5MzMzNDM2MjE4ODY0MTU4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=rvzPI0Q9G44Q7kNvwHJMnnN&amp;_nc_oc=AdpP2rHhiVQTkruVvw7bgYPHn2HpQxNv7mxutbqhUH5CjvvUKLQuns1w9yfJ0RV1hak&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;oh=00_AQJqgAtSzg8p8eSRyRdROBKZiAQmRjvM9FqFmgYgBJD_eA&amp;oe=6ABB2927
+https://scontent-atl3-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwG2Zbdj&amp;_nc_oc=AdpPL-ekOE7yCZKpp7q9-AFthrMciBbwOBRKY8lwkPP-PDux-Lp4Gvyf95O2Aym5Jqs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIiusJf0YzNCNyJKOXQmkXsu08sjXnXqPt63pERummjEA&amp;oe=6ABB0259
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.lever.co%2Fkitware%2Fe76197d1-4dc3-4f7c-a30a-597713283bb3%2Fapply%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacrm84gvazHpXZtxni8SXiDIbEIj9wBpOULYCncbUVAysSM_8ujQAiJIsUCiw_aem_OLhBoXs0nzbei_3_Qp3DiA%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUBvKzr2744n62aWxJ8o8-YWs7bT54MT9tK8dVIPOs_1_C_buQDsQnZwhZXXYduDckMgBy3h1nqZhMWmUGsVhvHZg7FXixTHNgLTxFD4kQ
+https://scontent-atl3-2.cdninstagram.com/o1/v/t2/f2/m78/AQNTYeE9tTQtES9ozBu12eEtF592dNo6JlX3c7CMjMYuHqWUet_co9MwAamY5ggAQKVC7cyWxq2qte3PuR-DR2h3jc3qdU82uIr5Dlg.mp4?_nc_cat=104&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_ohc=6QrpoaGAJ0MQ7kNvwFhQPAX&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgxODkzMTY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=67b608015fff5d35&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0Y5NEZFNkE4N0UyNEY0NDc0MzRBMTc0QzQzNEYyMDgwX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbklM6tmMehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIki6EzYvwCATUnDXNpsAuvvl7VCYA0uXIwgPkNUzpezg&amp;oe=6AB70D0D</t>
+        </is>
+      </c>
+      <c r="O158" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P158" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q158" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R158" s="3" t="inlineStr"/>
+    </row>
+    <row r="159" ht="45" customHeight="1">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>97858e37b1a984b189ab</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T15:14:52.488439+00:00</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T15:09:59+00:00</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr"/>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>Category Internships / Co-op - IT Internship</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>Data Engineering</t>
+        </is>
+      </c>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I159" s="3" t="inlineStr"/>
+      <c r="J159" s="3" t="inlineStr"/>
+      <c r="K159" s="4" t="inlineStr">
+        <is>
+          <t>https://us-erac.icims.com/jobs/567651/job?mobile=true&amp;needsRedirect=false</t>
+        </is>
+      </c>
+      <c r="L159" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
+          <t>Enterprise
+&lt; Welcome page
+Returning Prospect or Candidate?
+Click for Password or Log back in!
+Intern - Data Engineer (EFM IT)
+9
+St. Louis - Brentwood, Richmond Heights, Clayton,
+Maplewood &amp; central areas
+Category Internships / Co-op - IT Internship
+JobID 2026-567651
+Overview
+@ US-ERAC.ICIMS.COM
+an affiliate of Enterprise Mof ity is excited to announce
+the opening of a Data En rn.
+The Information Technology (IT) department of
+Enterprise Fleet Management builds and implements
+powerful solutions that help to drive and support the
+operations of our business spread across the US and
+Canada. Here, you will be part of a team that creates
+and delivers leading-edge technologies and expansive
+systems that impact eve :
+Refer
+https://scontent-atl3-1.cdninstagram.com/v/t51.71878-15/820568611_1301290595372147_6651792172090452022_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MzMzNDU5NzI4NzE2MTczMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=qSiJO8bWt1IQ7kNvwGX-o45&amp;_nc_oc=AdrfRp36TrHl94yLQKX6cdqugZvEfYS5e8XHcKcQcD8WHuKT-OdOHfI-fC0pXknjXkA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;oh=00_AQJNb-jkWOKw9hpZdAaEWQxlBR6qOs7KGtt2nwMZnW7Wxg&amp;oe=6ABAF5A7
+https://scontent-atl3-1.cdninstagram.com/v/t51.71878-15/820568611_1301290595372147_6651792172090452022_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MzMzNDU5NzI4NzE2MTczMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=qSiJO8bWt1IQ7kNvwGX-o45&amp;_nc_oc=AdrfRp36TrHl94yLQKX6cdqugZvEfYS5e8XHcKcQcD8WHuKT-OdOHfI-fC0pXknjXkA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;oh=00_AQIIt_Kvj700o7zcVDmEUphOOYgbyT6ltaO-FDT0q9FZ4A&amp;oe=6ABAF5A7
+https://scontent-atl3-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwG2Zbdj&amp;_nc_oc=AdpPL-ekOE7yCZKpp7q9-AFthrMciBbwOBRKY8lwkPP-PDux-Lp4Gvyf95O2Aym5Jqs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIiusJf0YzNCNyJKOXQmkXsu08sjXnXqPt63pERummjEA&amp;oe=6ABB0259
+https://l.instagram.com/?u=https%3A%2F%2Fus-erac.icims.com%2Fjobs%2F567651%2Fjob%3Fmobile%3Dtrue%26needsRedirect%3Dfalse%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacjGiDLl54zmzst9C5awgOY_R96NHqAB6z5SKUKwRIiVVBe7uQAYYqq6a_nrg_aem_w62JCQiRz-5ES8HthShJ0w&amp;e=AUDj6osGzXDxFc7m_Cpuh26GPBI-bL46_4jf1U8nELCQFno4ITguVEcF8GgRLgQmzWg1DmjpfGMRQrDu9SwlZxfGDk73bK6pNQDCCmF87g
+https://scontent-atl3-1.cdninstagram.com/o1/v/t2/f2/m78/AQPNyEk43eiF4HVCFwwRPBZYLQD6mk3nbGm3DWCBbCRH-21IJvyK3-8qVfBbLGrJJft_krDndFyPwKGu5yJNxknAyqlIHwterTgrfRg.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ohc=oW4CBqMBao8Q7kNvwG8RQX_&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgxODk0MzY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=16ba234d3c205e83&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0ZENDZDM0JCODA0OTFBMjAwREU4NzBBNjNCMjUxRTg2X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkzIagmcehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=Vqx34iFYueZxodicu17pUQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQImthKMIveEA5zMI2tcD1NjcUotwI4HqgdDQGmtF1Jleg&amp;oe=6AB722BC</t>
+        </is>
+      </c>
+      <c r="O159" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P159" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q159" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R159" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R149"/>
+  <autoFilter ref="A1:R159"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -14933,6 +15902,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L148" r:id="rId279"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K149" r:id="rId280"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K150" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L150" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K151" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L151" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K152" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L152" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K153" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L153" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K154" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L154" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K155" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L155" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K156" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K157" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L157" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K158" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K159" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L159" r:id="rId301"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R159"/>
+  <dimension ref="A1:R175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14652,7 +14652,7 @@
     <row r="150" ht="45" customHeight="1">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>7098899272a9e8af44f6</t>
+          <t>7e33cf52c00aa3178f39</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -14690,8 +14690,8 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="I150" s="3" t="inlineStr"/>
-      <c r="J150" s="3" t="inlineStr"/>
+      <c r="I150" s="3" t="n"/>
+      <c r="J150" s="3" t="n"/>
       <c r="K150" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/cerebras/99c289fa-8fc6-49f7-b7e8-78ac4e9d99ac/application?source=zero2sudo</t>
@@ -14747,12 +14747,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R150" s="3" t="inlineStr"/>
+      <c r="R150" s="3" t="n"/>
     </row>
     <row r="151" ht="45" customHeight="1">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>e7773f47f444ea257bad</t>
+          <t>f659ba580cd9c7d028a5</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -14780,10 +14780,10 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G151" s="3" t="inlineStr"/>
-      <c r="H151" s="3" t="inlineStr"/>
-      <c r="I151" s="3" t="inlineStr"/>
-      <c r="J151" s="3" t="inlineStr"/>
+      <c r="G151" s="3" t="n"/>
+      <c r="H151" s="3" t="n"/>
+      <c r="I151" s="3" t="n"/>
+      <c r="J151" s="3" t="n"/>
       <c r="K151" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/cerebras/c4faac59-3dbb-4ab7-9f74-d1fcbcddc7c6/application?source=zero2sudo</t>
@@ -14834,12 +14834,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R151" s="3" t="inlineStr"/>
+      <c r="R151" s="3" t="n"/>
     </row>
     <row r="152" ht="45" customHeight="1">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>f449cd91b7e57d900840</t>
+          <t>bcca646c805d6c0793ea</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -14852,7 +14852,7 @@
           <t>2026-09-24T14:00:22+00:00</t>
         </is>
       </c>
-      <c r="D152" s="3" t="inlineStr"/>
+      <c r="D152" s="3" t="n"/>
       <c r="E152" s="3" t="inlineStr">
         <is>
           <t>Our Summer 2027 Early Talent internships are a</t>
@@ -14863,7 +14863,7 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G152" s="3" t="inlineStr"/>
+      <c r="G152" s="3" t="n"/>
       <c r="H152" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
@@ -14874,7 +14874,7 @@
           <t>Boston</t>
         </is>
       </c>
-      <c r="J152" s="3" t="inlineStr"/>
+      <c r="J152" s="3" t="n"/>
       <c r="K152" s="4" t="inlineStr">
         <is>
           <t>https://campus-libertymutual.icims.com/jobs/77035/2027-techstart-summer-internship-program/job?mode=view</t>
@@ -14934,12 +14934,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R152" s="3" t="inlineStr"/>
+      <c r="R152" s="3" t="n"/>
     </row>
     <row r="153" ht="45" customHeight="1">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>5a57751d996f75a193b4</t>
+          <t>18b35f3954bd8c253cd5</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -14952,10 +14952,10 @@
           <t>2026-09-24T14:01:00+00:00</t>
         </is>
       </c>
-      <c r="D153" s="3" t="inlineStr"/>
+      <c r="D153" s="3" t="n"/>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>@ LIBMU NEW GRAD SWE</t>
+          <t>Software Engineering</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -14978,7 +14978,7 @@
           <t>Boston</t>
         </is>
       </c>
-      <c r="J153" s="3" t="inlineStr"/>
+      <c r="J153" s="3" t="n"/>
       <c r="K153" s="4" t="inlineStr">
         <is>
           <t>https://campus-libertymutual.icims.com/jobs/77144/2027-techstart-full-time-program/job?mode=view&amp;mobile=false&amp;width=735&amp;height=500&amp;bga=true&amp;needsRedirect=false&amp;jan1offset=-300&amp;jun1offset=-240</t>
@@ -15037,12 +15037,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R153" s="3" t="inlineStr"/>
+      <c r="R153" s="3" t="n"/>
     </row>
     <row r="154" ht="45" customHeight="1">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>838767d8463b0c180ad1</t>
+          <t>317caf8b282e13ff2921</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -15055,7 +15055,7 @@
           <t>2026-09-24T14:16:18+00:00</t>
         </is>
       </c>
-      <c r="D154" s="3" t="inlineStr"/>
+      <c r="D154" s="3" t="n"/>
       <c r="E154" s="3" t="inlineStr">
         <is>
           <t>Summer Internship Program Whippany</t>
@@ -15066,14 +15066,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G154" s="3" t="inlineStr"/>
+      <c r="G154" s="3" t="n"/>
       <c r="H154" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="I154" s="3" t="inlineStr"/>
-      <c r="J154" s="3" t="inlineStr"/>
+      <c r="I154" s="3" t="n"/>
+      <c r="J154" s="3" t="n"/>
       <c r="K154" s="4" t="inlineStr">
         <is>
           <t>https://search.jobs.barclays/search-jobs?acm=8736272&amp;alrpm=ALL&amp;ascf=%5B%7B%22key%22%3A%22custom_fields.MultiValueField3%22%2C%22value%22%3A%22Internships+Technology%22%7D%5D</t>
@@ -15124,12 +15124,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R154" s="3" t="inlineStr"/>
+      <c r="R154" s="3" t="n"/>
     </row>
     <row r="155" ht="45" customHeight="1">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>f6bf7bc78c816475e005</t>
+          <t>a220481ffd3d67b79af6</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -15162,13 +15162,13 @@
           <t>Quant</t>
         </is>
       </c>
-      <c r="H155" s="3" t="inlineStr"/>
+      <c r="H155" s="3" t="n"/>
       <c r="I155" s="3" t="inlineStr">
         <is>
           <t>Bellevue</t>
         </is>
       </c>
-      <c r="J155" s="3" t="inlineStr"/>
+      <c r="J155" s="3" t="n"/>
       <c r="K155" s="4" t="inlineStr">
         <is>
           <t>https://www.metacareers.com/profile/job_details/1609178343953401</t>
@@ -15229,12 +15229,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R155" s="3" t="inlineStr"/>
+      <c r="R155" s="3" t="n"/>
     </row>
     <row r="156" ht="45" customHeight="1">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>b7d8d5f1836d97b9794c</t>
+          <t>49b90935a43955e315f8</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -15267,13 +15267,13 @@
           <t>Data Science</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr"/>
+      <c r="H156" s="3" t="n"/>
       <c r="I156" s="3" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="J156" s="3" t="inlineStr"/>
+      <c r="J156" s="3" t="n"/>
       <c r="K156" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/wurljobs/jobs/4716249006</t>
@@ -15332,12 +15332,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R156" s="3" t="inlineStr"/>
+      <c r="R156" s="3" t="n"/>
     </row>
     <row r="157" ht="45" customHeight="1">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>9f2a89e41d378d20d516</t>
+          <t>8709d1c17ff0616955e4</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -15350,7 +15350,7 @@
           <t>2026-09-24T15:08:53+00:00</t>
         </is>
       </c>
-      <c r="D157" s="3" t="inlineStr"/>
+      <c r="D157" s="3" t="n"/>
       <c r="E157" s="3" t="inlineStr">
         <is>
           <t>APPLY NOW</t>
@@ -15371,8 +15371,8 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="I157" s="3" t="inlineStr"/>
-      <c r="J157" s="3" t="inlineStr"/>
+      <c r="I157" s="3" t="n"/>
+      <c r="J157" s="3" t="n"/>
       <c r="K157" s="4" t="inlineStr">
         <is>
           <t>https://hdnn.fa.us6.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX/job/114233</t>
@@ -15423,12 +15423,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R157" s="3" t="inlineStr"/>
+      <c r="R157" s="3" t="n"/>
     </row>
     <row r="158" ht="45" customHeight="1">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>6d71fb6352cb778fd028</t>
+          <t>562bf11f7680082d2b11</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -15456,14 +15456,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G158" s="3" t="inlineStr"/>
-      <c r="H158" s="3" t="inlineStr"/>
+      <c r="G158" s="3" t="n"/>
+      <c r="H158" s="3" t="n"/>
       <c r="I158" s="3" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="J158" s="3" t="inlineStr"/>
+      <c r="J158" s="3" t="n"/>
       <c r="K158" s="4" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/kitware/e76197d1-4dc3-4f7c-a30a-597713283bb3/apply</t>
@@ -15514,12 +15514,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R158" s="3" t="inlineStr"/>
+      <c r="R158" s="3" t="n"/>
     </row>
     <row r="159" ht="45" customHeight="1">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>97858e37b1a984b189ab</t>
+          <t>0730588641b02a9973a4</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -15532,7 +15532,7 @@
           <t>2026-09-24T15:09:59+00:00</t>
         </is>
       </c>
-      <c r="D159" s="3" t="inlineStr"/>
+      <c r="D159" s="3" t="n"/>
       <c r="E159" s="3" t="inlineStr">
         <is>
           <t>Category Internships / Co-op - IT Internship</t>
@@ -15553,8 +15553,8 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="I159" s="3" t="inlineStr"/>
-      <c r="J159" s="3" t="inlineStr"/>
+      <c r="I159" s="3" t="n"/>
+      <c r="J159" s="3" t="n"/>
       <c r="K159" s="4" t="inlineStr">
         <is>
           <t>https://us-erac.icims.com/jobs/567651/job?mobile=true&amp;needsRedirect=false</t>
@@ -15616,10 +15616,1527 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R159" s="3" t="inlineStr"/>
+      <c r="R159" s="3" t="n"/>
+    </row>
+    <row r="160" ht="45" customHeight="1">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>51d7d7d9b65fda4897f7</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:16:19.682515+00:00</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T15:47:56+00:00</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr"/>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>join! RSVP to confirm your attendance.</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr"/>
+      <c r="H160" s="3" t="inlineStr"/>
+      <c r="I160" s="3" t="inlineStr"/>
+      <c r="J160" s="3" t="inlineStr"/>
+      <c r="K160" s="4" t="inlineStr">
+        <is>
+          <t>https://events.riviancareers.com/plugin-earlycareer2027</t>
+        </is>
+      </c>
+      <c r="L160" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
+          <t>Plug-in with Rivian: New Grads
+and Early Career
+Join Rivian's Emerging Talent team
+for our annual ‘Plug-in’ virtual event
+series! We'll be chatting more about
+all our new grad &amp; early career
+opportunities.|f you've graduated in
+the past few years, or are graduating
+next spring, we'd love to have you
+join! RSVP to confirm your attendance.
+(2) EVENTS.RIVIANCAREERS.COM
+Rivian info session for interns
+and new grads
+https://scontent-ord5-2.cdninstagram.com/v/t51.71878-15/823965176_1676431430669395_7072460048041307037_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MzM1MzcwNDMwNDM4MDEwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=78rSvY_e9RcQ7kNvwGcQgkf&amp;_nc_oc=AdoRXR4tkjPZb6_LeRbJbAXP0YVBk28UP6rHIqw5iOKoGUYUgsJKwnMAAi8WOnc36CE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;oh=00_AQJOnCWIwLe3OaS8SuCXWrxZgeX_ZCW4M9tCxBXKwh4tEw&amp;oe=6ABB2F7E
+https://scontent-ord5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHlkAqF&amp;_nc_oc=AdqulOi4hZS51D5YYQLnIJClsZ5LI9n2Rf7zAHk3ulFFWRnu8u28hUM0Rspap24BbuQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIOf9rA0pPDj69YInvfSjaqFoQMJlh9G8fSA9QAvIu1yg&amp;oe=6ABB3A99
+https://l.instagram.com/?u=https%3A%2F%2Fevents.riviancareers.com%2Fplugin-earlycareer2027%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAad2Z9WR1EysXz1FT_k7ju1NjFeJTRY03buKu2Kzwu2tskXHL7GYK3GhFH9B7A_aem_tP-eTBOodsHXZfeNaeONnw&amp;e=AUAVZ9hqaXkPjg1X0Z1CNxzNxLYnJTbELqSIiPc5NKi67AHVur2VzxTEUjYDwjp0KhbPtHsXNwU0iVi3UVs075phoinQtfzRco4-AgH2ZQ
+https://scontent-ord5-1.cdninstagram.com/o1/v/t2/f2/m78/AQO5mwXEatBKzpG-Dn73Ah9eTqyn_ptVJkT3mJIDxstLd9W9fTq0jV16h3QCl9Se0jBxKGBe3IIhCb1-lvFSLE5PqncgQaolS50TGGk.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-1.cdninstagram.com&amp;_nc_ohc=DGVV-EY1MGsQ7kNvwGa9Wxe&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgxOTM5NjY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=31a684fe4d6afc28&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzUyNDQyQzdCMkIyN0Q1QTI1RENEQTg1QTc0ODIzOEJDX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkjpmAu8ehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKSoHMTlToRswuHJbcX0yQT_SD3xadHxPKwYGFCMxJ9LQ&amp;oe=6AB76276</t>
+        </is>
+      </c>
+      <c r="O160" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P160" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q160" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R160" s="3" t="inlineStr"/>
+    </row>
+    <row r="161" ht="45" customHeight="1">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>fa552c8503e2cb450935</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:16:20.983646+00:00</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T15:50:24+00:00</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>Amazon — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I161" s="3" t="inlineStr"/>
+      <c r="J161" s="3" t="inlineStr"/>
+      <c r="K161" s="4" t="inlineStr">
+        <is>
+          <t>https://amazon.jobs/en/jobs/3177934/software-development-engineer-2026-us</t>
+        </is>
+      </c>
+      <c r="L161" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
+          <t>x a poem aoe
+— amazonjobs
+Software Development
+Engineer - 2026 (US)
+Job ID: 3177934 | Amazon.com Services LLC
+Apply now
+Description
+Do you want to solve real customer problems
+=~ 2 AMAZON.JOBS *
+code directly impact of customers
+worldwide?
+re Amazon SWE New Grad 2026
+our customers. Customer obsession is part of
+our company DNA, which has made us one of
+the world's most beloved brands.
+https://scontent-ord5-2.cdninstagram.com/v/t51.71878-15/824450918_4507269179591623_1268371666803025550_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MzM1NDkzNzQxMzQyNDgyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=PZec_6AbV6sQ7kNvwHxnW6h&amp;_nc_oc=AdpTU2-05iF2pVPjMNgEcPTOdrTnrMqukQTvLV8RdxapXRZNNgYdBU-80_QJawEXwWY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;oh=00_AQK4EYZhasca5OlcBqIicLgerARcasxCacnQvAINzJcPSw&amp;oe=6ABB31F2
+https://scontent-ord5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHlkAqF&amp;_nc_oc=AdqulOi4hZS51D5YYQLnIJClsZ5LI9n2Rf7zAHk3ulFFWRnu8u28hUM0Rspap24BbuQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIOf9rA0pPDj69YInvfSjaqFoQMJlh9G8fSA9QAvIu1yg&amp;oe=6ABB3A99
+https://l.instagram.com/?u=https%3A%2F%2Famazon.jobs%2Fen%2Fjobs%2F3177934%2Fsoftware-development-engineer-2026-us%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadW0PhVZl4VKf7vahTaPMcdr-7JvkjhUorDp1w1WDdBhHRBpyIk8Np4sd6zjQ_aem_FGNTRQhHf1-N1y-vn46yGw&amp;e=AUAOlFXJK0PRvpDv8W6dcWWuyCRiYdbGd6e1p8nzqole8kc1XCjIZxlpOEvvfAHq-BqXAl1EILSCX67Hxj9txGai4ByyCtcHOaCcnlMmzg
+https://scontent-ord5-1.cdninstagram.com/o1/v/t2/f2/m78/AQO_eVNenShIhVUgTBdPYt9cCXlybJIpM3RblIMaIpKmZfjNZMSXII1LsmZ-5WwAPkfXBkWZT1_c6dlGX25ek6DkgiBxSc2oZweNYLc.mp4?_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-1.cdninstagram.com&amp;_nc_ohc=LOEv3WbbkOcQ7kNvwEIS9lD&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgxOTQxNzY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDgyNiwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=2ba52697b1fbf1be&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0IxNEJGQ0ZDMTRDMkYxOTBGRDJBNDBFQzFDRjE0RDkxX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk8LvIvMehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZZSpAQA&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJUFczD2f-nvo9d4ua4QKwLJiRpjx8fk0_Nr6ULreMzsw&amp;oe=6AB76493</t>
+        </is>
+      </c>
+      <c r="O161" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P161" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q161" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R161" s="3" t="inlineStr"/>
+    </row>
+    <row r="162" ht="45" customHeight="1">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>1f415241cb06464d53d5</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:16:23.522000+00:00</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T15:52:13+00:00</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>Klaviyocampus</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>Klaviyocampus — Internship</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr"/>
+      <c r="H162" s="3" t="inlineStr"/>
+      <c r="I162" s="3" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="J162" s="3" t="inlineStr"/>
+      <c r="K162" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/klaviyocampus/jobs/8003260003</t>
+        </is>
+      </c>
+      <c r="L162" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
+          <t>@ job-boards.greenhouse.io G
+klaviyo"
+New
+Al Engineer Intern
+© Boston, MA
+(7) JOB-BOARDS.GREENHOUSE.I0
+At Klaviyo, we value ue
+backgrounds, experie nd perspectives
+each Klaviyo (we call ourselves Klaviyos)
+brings to our workplace each and every day.
+We believe everyone deserves a fair shot at
+success and appreciate the experiences each
+person brings beyond the traditional job
+requirements. If you’re a close but not €
+match with the description, we hope yo rap |
+still consider applying.
+https://scontent-ord5-2.cdninstagram.com/v/t51.71878-15/816615027_935948415794676_3065367897612022613_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MzM1NTg1Mjc5NDcxMzI0Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=1cL77kvF6qsQ7kNvwEMoS8t&amp;_nc_oc=AdqmQi3yd4EHLme0qyxQdtmpczqMgSoN8x3Y3iqM55BT9ZQvl1GsIVlGWVQElvmJg14&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;oh=00_AQKeTeMex4smxIfwNPp_Sh1Ir9eR4K4k8oAxnu-MJTDS6A&amp;oe=6ABB2F56
+https://scontent-ord5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHlkAqF&amp;_nc_oc=AdqulOi4hZS51D5YYQLnIJClsZ5LI9n2Rf7zAHk3ulFFWRnu8u28hUM0Rspap24BbuQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIOf9rA0pPDj69YInvfSjaqFoQMJlh9G8fSA9QAvIu1yg&amp;oe=6ABB3A99
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fklaviyocampus%2Fjobs%2F8003260003%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeIhttzz5o50loYlHfNmR_C5uytDphGcvwxBpDLkckaTLWZON2eMF-k960GOQ_aem_cIGMFxaaCav30BSo0ja2fg&amp;e=AUCcHmxEdh6yz359DHke4VHm-czKhlS1wPmpoJwTvvxT9HNFLqi4iVkLp9zyg0qkxUFjmfJc4dlhxvKMB20C4uO_zCa98U4UBfhyr5GeiA
+https://scontent-ord5-2.cdninstagram.com/o1/v/t2/f2/m78/AQOnifC_eaW9vKLfF9BHC0_gCg4cR4399kv2ZJfayl33HNbDrW4Mq3DSlvzNMy_rp6vTTMciKlK_6gDYL4UYutv-1z9yupkHRh29Gdc.mp4?_nc_cat=104&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ohc=kIZPTDsVd3MQ7kNvwEnTlaR&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgxOTQ1OTA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=dec38fc480bc5da3&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzQ4NDc5NzAzNDRBNzA1NDI0REQ5RTdFMkY0NDdDNjg1X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk_qTTv8ehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLyIixht_AswKDIopVNBp8pSnSAUn4aSngBBA11xR2ZFw&amp;oe=6AB742A5</t>
+        </is>
+      </c>
+      <c r="O162" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P162" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q162" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R162" s="3" t="inlineStr"/>
+    </row>
+    <row r="163" ht="45" customHeight="1">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>29671a80dcb3a72986d6</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:16:24.879288+00:00</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>Meta — Internship</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="inlineStr"/>
+      <c r="H163" s="3" t="inlineStr"/>
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t>Menlo Park</t>
+        </is>
+      </c>
+      <c r="J163" s="3" t="inlineStr"/>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/profile/job_details/1412139847020398</t>
+        </is>
+      </c>
+      <c r="L163" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
+          <t>i) metacareers.com
+OO Meta
+&lt; Back to Jobs
+Network Production
+Engineer Intern
+Menlo Park, CA
+Network Engineering +1more
+Apply now
+Meta is looking for talented, highly
+motivated university students for our
+Network Engineering team. As a member of
+scale global netwo
+This will be your net it is constantly
+growing. Your primary function will be to
+ensure that the network and its related
+This role is highly coveted by High
+billio Frequency Trading firms!
+https://scontent-ord5-2.cdninstagram.com/v/t51.71878-15/817177234_4433732183549408_3259886971473021286_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MzM2NjM0NzQ4ODU0MzM2OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=7ydMqp3T2y8Q7kNvwHug3BK&amp;_nc_oc=AdokooHnA6kKWzsOq9JMjRCWP_aQHpDH9PWObxRNajCMbcdfD6zIg0Iidb8RpDreGSg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;oh=00_AQJMz3107wG40f8sDqP9hAHsj_Eky7XDuvHepqwrwyW7sg&amp;oe=6ABB4B26
+https://scontent-ord5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHlkAqF&amp;_nc_oc=AdqulOi4hZS51D5YYQLnIJClsZ5LI9n2Rf7zAHk3ulFFWRnu8u28hUM0Rspap24BbuQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIOf9rA0pPDj69YInvfSjaqFoQMJlh9G8fSA9QAvIu1yg&amp;oe=6ABB3A99
+https://l.instagram.com/?u=https%3A%2F%2Fwww.metacareers.com%2Fprofile%2Fjob_details%2F1412139847020398%2F%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadVsSqT-lVMR2elKde5WSyymav8qHUXUBn9LClTbkTumXtgoT63r67D6nypUA_aem_9LBpTldAd5a5mhHqpa5I4Q&amp;e=AUAWGXFxueiNqltHiBgqhgHhfIA49UwChvSLK_oiBcPt-gIEwj5YXTeDq3kaIZEixM-xp6K2v0alZLhRJtRJfZqB24Y0XAxI30r82PKQuw
+https://scontent-ord5-2.cdninstagram.com/o1/v/t2/f2/m78/AQMfzri8AHy5R0uFxlK5xAZbJs07Jvjf3eHlsPPWkQUYt2jfSWG8Ru-p0kU7nLt5gJidJUvnxGmnp4gZYbgarz6WdZSox7cJ5i2J3YQ.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ohc=1SEh9hdszXIQ7kNvwHdtSIu&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgxOTc4MTg2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=26e3034a195493c9&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzFBNEE3MkI5NkY2QzBCNzVENDVGREFCMEU5MDZFOUJEX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk-t_Z18ehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKd_kCXfRVzGwGYjGrk94g2M5-_iadtAtKkiKJk1ldtdA&amp;oe=6AB74D8C</t>
+        </is>
+      </c>
+      <c r="O163" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P163" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q163" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R163" s="3" t="inlineStr"/>
+    </row>
+    <row r="164" ht="45" customHeight="1">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>c5d0b12b0e45fe127452</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:16:26.408467+00:00</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:25:18+00:00</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>Boxinc</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>Boxinc — Internship</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr"/>
+      <c r="H164" s="3" t="inlineStr"/>
+      <c r="I164" s="3" t="inlineStr"/>
+      <c r="J164" s="3" t="inlineStr"/>
+      <c r="K164" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/boxinc/jobs/8226667</t>
+        </is>
+      </c>
+      <c r="L164" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
+          <t>@ job-boards.greenhouse.io C;:
+Cloud &amp; Al Finance
+Intern
+© Redwood City, CA, United States
+Apply
+WHAT IS BOX?
+Box (NYSE:BOX) is the leader in Intelligent
+Content Management. Our platform enables
+(2) JOB-BOARDS.GREENHOUSE. 10
+4 CANIM LIGIIOIVEITIE WU STICS INIT VVD VVELTE
+enterprise Al. We hel nies thrive in the
+new Al-first era of busi “Founded in 2005,
+Box simplifies work for leading global
+organizations, including JLL, Morgan Stanley,
+and Nationwide. Box is headquartered in
+Redwood City, CA, with offices across the ae
+United States, Europe, and Asia. =
+https://scontent-ord5-2.cdninstagram.com/v/t51.71878-15/824450907_1023141117446177_1255192680213439093_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MzM3MjUxMTE3ODYzODU4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=06wN38ou8GIQ7kNvwH_-SQO&amp;_nc_oc=AdokwufsBQf-xHgG3UnvToPgfNsOYf-aiZnqDjn0K736QVNb0ynXkSA7BS8GjFpb4VA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;oh=00_AQIrvmrteXcU9hUeixboG2NuJVB5x2eoJOmw-pb_l07wDw&amp;oe=6ABB5BC6
+https://scontent-ord5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHlkAqF&amp;_nc_oc=AdqulOi4hZS51D5YYQLnIJClsZ5LI9n2Rf7zAHk3ulFFWRnu8u28hUM0Rspap24BbuQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIOf9rA0pPDj69YInvfSjaqFoQMJlh9G8fSA9QAvIu1yg&amp;oe=6ABB3A99
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fboxinc%2Fjobs%2F8226667%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeA5qMPEw_MA9BBvQdDCu_ATuya-P3KPo3b-fgl8xNkPgpI06OzRp4DEfKQlw_aem_m4L_yMtuj1AyGse57FL5sQ&amp;e=AUBvpj2dApUmIy8Pr2dRL6d_6QgswjDlwVj587gvq7qDJHGIJ7fZorpSe8WRRh6aaZSmf8CJa8HlVH1P6R-Oq5L7EEFBcxoZq61NcuQEWg
+https://scontent-ord5-2.cdninstagram.com/o1/v/t2/f2/m78/AQOld-BgOxsy2eadeIogh6owWaDUXmmpF1br3TwjbqPxcJSIeY8DxHVVU8RJSZsV3PRX9cHQaybzCXNYQqdPYdEH6mePWwKxI4lFtVk.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ohc=poktb5TUgqAQ7kNvwGAMERC&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgyMDAwMTc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=e6ea0ccbc9eea668&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzQ4NDJDQjkwMjhCNzI4RkU5MkE1QkZBMzMwMzI0N0IwX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkyfCK6MehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKQIPwKMtQuyZ1ZkJoHp0tppaXDd4Dj-b_2jy3x4m0QrA&amp;oe=6AB76955</t>
+        </is>
+      </c>
+      <c r="O164" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P164" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q164" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R164" s="3" t="inlineStr"/>
+    </row>
+    <row r="165" ht="45" customHeight="1">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>859986cdba3feebf4b1e</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:16:27.478415+00:00</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:35:21+00:00</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>Adobe — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I165" s="3" t="inlineStr">
+        <is>
+          <t>Seattle, San Francisco, Austin</t>
+        </is>
+      </c>
+      <c r="J165" s="3" t="inlineStr"/>
+      <c r="K165" s="4" t="inlineStr">
+        <is>
+          <t>https://adobe.wd5.myworkdayjobs.com/en-US/external_experienced/job/San-Jose/XMLNAME-2027-University-Graduate---Software-Engineer_R172083</t>
+        </is>
+      </c>
+      <c r="L165" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
+          <t>x @ adobe.wd5.myworkdayjobs.c... C:
+@ English | 2 Signin
+A Search for Jobs
+Adobe Careers 7%
+2027 University Graduate -
+Software Engineer
+Apply
+© San Jose
+San Francisco
+Austin
+Seattle
+Lehi
+@ ADOBE NEW GRAD SWE!!!
+©) Posted Today
+f=] End Date: Dece 6 (30+ days
+left to apply)
+[=] R172083
+The Opportunity
+https://scontent-ord5-1.cdninstagram.com/v/t51.71878-15/823587589_2928761280829382_7786261632067860542_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5MzM3NzU2NTk1MTI1NTI1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=u0v4oZgLbxgQ7kNvwGF32G-&amp;_nc_oc=AdoCREzc1LLRC79ItGYLTfTpudLY9F9Esy4r2hYo3hZlI5NhAMULyRyANs-ouxs1n0U&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-1.cdninstagram.com&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;oh=00_AQK1AYqzjdm_VOMITzhzxu6dPNnrN9bueT2OI9g_UbjjjQ&amp;oe=6ABB3A9F
+https://scontent-ord5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHlkAqF&amp;_nc_oc=AdqulOi4hZS51D5YYQLnIJClsZ5LI9n2Rf7zAHk3ulFFWRnu8u28hUM0Rspap24BbuQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIOf9rA0pPDj69YInvfSjaqFoQMJlh9G8fSA9QAvIu1yg&amp;oe=6ABB3A99
+https://l.instagram.com/?u=https%3A%2F%2Fadobe.wd5.myworkdayjobs.com%2Fen-US%2Fexternal_experienced%2Fjob%2FSan-Jose%2FXMLNAME-2027-University-Graduate---Software-Engineer_R172083%3Futm_id%3D97760_v0_s00_e0_tv4%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeon6aOEQLlNo-mlQsipiMxKtqL8x971yJWNO4A9gmmgtu4yJeJiX3gp7lcrQ_aem_urFQmu7QafMcRECdd2dTsw&amp;e=AUBm8bGmch7KCFuDjd9NVjIt-Qee4PMDBZtgxll0JR-piLMeT5WVcno1T2eQPupjYeaxpq1Kuhc22sU-aM7KpczHQyTgt-BLZ8nMldnOkA
+https://scontent-ord5-2.cdninstagram.com/o1/v/t2/f2/m78/AQNO31aKpgDg4sVXkAAS5qbWD7_CW8h7Wt-DNQFt3y0DnxX_asFT4Y3Qta3cJZPh_9r9FptmGW3-gbf5bNo5KwjzXGAlEFdoSy_c0_s.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ohc=PqaZnpcB1YsQ7kNvwF2RsZv&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgyMDE5Njc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDgyNiwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=69c9c7221bd31448&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzgzNDU3Njg1ODk0QTBDREIwRjhBOENBMTc2MTRERjgzX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk18XO9sehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZZSpAQA&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKfzznW3_jnqj48AzPYEr0Y4kNbXhrJCrx2J7ZnR_pkVA&amp;oe=6AB766B0</t>
+        </is>
+      </c>
+      <c r="O165" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P165" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q165" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R165" s="3" t="inlineStr"/>
+    </row>
+    <row r="166" ht="45" customHeight="1">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>e1283f0dbe8bb2b77461</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:16:28.893663+00:00</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:55:18+00:00</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>Adobe — Product Management</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I166" s="3" t="inlineStr"/>
+      <c r="J166" s="3" t="inlineStr"/>
+      <c r="K166" s="4" t="inlineStr">
+        <is>
+          <t>https://adobe.wd5.myworkdayjobs.com/external_experienced/job/San-Jose/XMLNAME-2027-University-Graduate---Product-Manager_R171844</t>
+        </is>
+      </c>
+      <c r="L166" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
+          <t>€ English | 2 Signin
+A Search for Jobs
+Adobe Careers
+Adobe
+2027 University Graduate -
+Product Manager
+© San Jose
+fea] Full time
+(©) Posted Today
+© ADOBE NEW GRAD PM
+Hue Yppurcuiicy
+We're looking for a nager to join
+Adobe's Experience a ement team and
+help shape the future of Intelligent digital
+experiences. In this role, you will spearhead the
+evolution of Adobe's self-service experience by
+developing agentic Al solutions that move
+beyond static automation. You'll make digital
+experiences more seamless, intuitive, and
+https://scontent-ord5-1.cdninstagram.com/v/t51.71878-15/818233210_2200203130555721_2370047600075644387_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MzM4NzYwNTg2NTYyMzAzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=n_4ErJ9qbCcQ7kNvwEkIiQO&amp;_nc_oc=AdoOGiW4e_Vemu4jCrWZfDv0sFa9O4Rw1nhQSr9RfQ6_zOa1tRyGKF6i0qXKTb0OyjM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-1.cdninstagram.com&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;oh=00_AQKt08W94rH3FT7W7_r2fzgkBaeNOMcKU5oRnYo44gNGhw&amp;oe=6ABB4B79
+https://scontent-ord5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHlkAqF&amp;_nc_oc=AdqulOi4hZS51D5YYQLnIJClsZ5LI9n2Rf7zAHk3ulFFWRnu8u28hUM0Rspap24BbuQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIOf9rA0pPDj69YInvfSjaqFoQMJlh9G8fSA9QAvIu1yg&amp;oe=6ABB3A99
+https://l.instagram.com/?u=https%3A%2F%2Fadobe.wd5.myworkdayjobs.com%2Fexternal_experienced%2Fjob%2FSan-Jose%2FXMLNAME-2027-University-Graduate---Product-Manager_R171844%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAac9WmDkl51F4zvBVr-xgG7cFkS3YzpUGkA_21it_xxcGPzq_y0piwHHsVkUhw_aem_dBgH1fbPHgC-J0RgwzPhmw%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUAAH3O_kxwyHVksx62c2c5BiTFpeAexYlRgCXinE4U_INL7dBgB4INxU-79v1KKdOV-xh2d8nx8MJ_vsgFFB_aumpYknc-Dp79UQFrO2w
+https://scontent-ord5-2.cdninstagram.com/o1/v/t2/f2/m78/AQNsOdikrq-BPMUExDmv0NDSpis4zMHyLMFR6i8ZkeuTrdsBrx5BheNEPGkD1KMHdPiQfh7QtiLu5KhBOmiB4DLI1Gek0z2LDac1qGY.mp4?_nc_cat=102&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ohc=nDY_D-p4voUQ7kNvwENog_6&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgyMDQzOTc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=d5caff731d7b94c4&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0IyNEM5NkZGNzk4MUUwOEVGMDg1QjVFOUY4QzU1RTlBX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkxfzbiMihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJCnUp73HeNL-ftwhuRN4_hlN1XWPBVjgKiQYFfUVlS2g&amp;oe=6AB765E3</t>
+        </is>
+      </c>
+      <c r="O166" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P166" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q166" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R166" s="3" t="inlineStr"/>
+    </row>
+    <row r="167" ht="45" customHeight="1">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>db8279f0092dc22703c5</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:16:30.588350+00:00</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T17:09:09+00:00</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="inlineStr"/>
+      <c r="I167" s="3" t="inlineStr"/>
+      <c r="J167" s="3" t="inlineStr"/>
+      <c r="K167" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/perplexity/8a99d9be-6955-4f28-8150-80c8ce72c523</t>
+        </is>
+      </c>
+      <c r="L167" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
+          <t>Vs perplexity
+Member of Technical Staff (New
+Grad)
+Welcome! This is the general
+application portal for university
+students and recent graduates who
+wish to be considered for full-time
+Member of Technical Staff positions at
+Perplexity. Our elite new grad cohorts
+enjoy unparalleled mentorship,
+top-of-market compensation, and the
+chance to tackle some....
+@ JOBS.ASHBYHQ.COM ¢
+thank you!!
+Perplexity New Grad SWE!
+https://scontent-ord5-1.cdninstagram.com/v/t51.71878-15/820155593_1558367695977118_1843419551492690157_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MzM5NDU3OTM5ODgwODc0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=03SLOdRoKoEQ7kNvwFglZtk&amp;_nc_oc=AdqqTt-2-HalFkKzwFiBeF9zN0DoYZrx97hOx8eEgvHPP9F7b7npvb5GKCoFdzJw5uQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-1.cdninstagram.com&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;oh=00_AQJms2jnJ8hsF3w4r91XIca56rjwkiIbzRpnN-Uz65kckw&amp;oe=6ABB532E
+https://scontent-ord5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHlkAqF&amp;_nc_oc=AdqulOi4hZS51D5YYQLnIJClsZ5LI9n2Rf7zAHk3ulFFWRnu8u28hUM0Rspap24BbuQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIOf9rA0pPDj69YInvfSjaqFoQMJlh9G8fSA9QAvIu1yg&amp;oe=6ABB3A99
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.ashbyhq.com%2Fperplexity%2F8a99d9be-6955-4f28-8150-80c8ce72c523%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadhcN2e_vu5b3dVSTYN7glw_jUuT-WEHCtsE1Bap4bPT8u4ubFxdruQckRwCQ_aem_NKgNizSwQFqu4jkdvJhynw&amp;e=AUAmpCLojrhbynlD-n4FL1-cWiIvleY31JpVSNKqCzneHT5b3XkxWBCInedLn8GRWcZ2lS2r5bxuccqCkvwUKkGpEFXOJDg-Trj40638hQ
+https://scontent-ord5-2.cdninstagram.com/o1/v/t2/f2/m78/AQOi3tTtABGDGPYBcd7iDaWl_-oF2UK789wLL0ad6P-6nAiEUAwqmjmBe_-nBd4JEX4gpShNmLFYUfiZJ63AA_PT40gmiDP9yWxkVKw.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ohc=sCsp4jzxda4Q7kNvwE_b6aj&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgyMDcwOTE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=2f56d507f20492d6&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzhENDVEODlGQkU4MTkzMjRENjE2RjVDQzE3NTg1Qzg5X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk-5XlnMihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKdAZIdp3XS0cgtAp-IRt89t2_yt-5GWCtuBkdiJwBw4A&amp;oe=6AB73A35</t>
+        </is>
+      </c>
+      <c r="O167" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P167" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q167" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R167" s="3" t="inlineStr"/>
+    </row>
+    <row r="168" ht="45" customHeight="1">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>f4dfbbd8ab9825421b9d</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:16:31.648160+00:00</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T17:13:24+00:00</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq — Research</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I168" s="3" t="inlineStr">
+        <is>
+          <t>Bay Area, NYC</t>
+        </is>
+      </c>
+      <c r="J168" s="3" t="inlineStr"/>
+      <c r="K168" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/genesis-molecular-ai/42fc0631-3f81-481a-b496-daa875c9e92e?src=zero2sudo</t>
+        </is>
+      </c>
+      <c r="L168" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
+          <t>@ jobs.ashbyhg.com G4
+es genesis AR Al
+ML Research Intern - BS/MS
+(Summer 2027)
+Location
+NYC or SF Bay Area
+Employment Type
+Intern
+@ JOBS.ASHBYHQ.COM
+_ men
+Overview Application
+About the Team
+Join a world-class team at the forefront
+of Al and biochemistry.
+At Genesis Molecular Al, we're a tight-
+https://scontent-ord5-2.cdninstagram.com/v/t51.71878-15/817651170_1833392411155503_8063795715036369796_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5MzM5NjcyNDEwNjYzOTAxNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=idlyFvS7VKUQ7kNvwGzOYI_&amp;_nc_oc=AdoqAFshfEo3s783Z34F2iwZIhz_b4eXx4jKHn5I5g-ved5WSD0Y5WLkDoXODNvxIqw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;oh=00_AQI5ph9mX-a1ebKGl7BmXUU6b9FhgkQ0eoqP4POStC93Tw&amp;oe=6ABB61F4
+https://scontent-ord5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHlkAqF&amp;_nc_oc=AdqulOi4hZS51D5YYQLnIJClsZ5LI9n2Rf7zAHk3ulFFWRnu8u28hUM0Rspap24BbuQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIOf9rA0pPDj69YInvfSjaqFoQMJlh9G8fSA9QAvIu1yg&amp;oe=6ABB3A99
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.ashbyhq.com%2Fgenesis-molecular-ai%2F42fc0631-3f81-481a-b496-daa875c9e92e%3Fsrc%3Dzero2sudo%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAae9u4dSO9cV4VjKP1kh2SgRr9lx-YjkCS9aUjxOTyrvmrWQwFcJDvEgX3Bwtw_aem_Bc2PQ6Ho9JbRvBtwxfIxVA&amp;e=AUBOl6MDapxx4G0W04ZgiUiLpsrA588LjF9271VaUuQymLjbrKgWzhQ_jd-gMZWZqja8yxNfCmroi85cWF4d6olSzCeA1PTplp-HYDxLWg
+https://scontent-ord5-2.cdninstagram.com/o1/v/t2/f2/m78/AQMpnVC7qSx1oce_PnaFv64ZcJpXFhHfVHPaurVz3kpA4Yv4niXT9o4o-y9PS82uh-QVPh-aOgtNbIhu2txuS8yE_OOMGcJPCbFNWwk.mp4?_nc_cat=104&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ohc=A_guKSsUXwIQ7kNvwHbL9ny&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgyMDc1MTQ2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=2c461a35e335d481&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzEyNDIxQUY3QkU0RTMwMUU0RUM0MzJBQTcxRTUwQjgzX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk2sn4n8ihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKVBAAPDQ-RpHajDL-jJVrcWfTpaaDBB0EFZbWId0Pz4A&amp;oe=6AB756F1</t>
+        </is>
+      </c>
+      <c r="O168" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P168" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q168" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R168" s="3" t="inlineStr"/>
+    </row>
+    <row r="169" ht="45" customHeight="1">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>59af26457e8355c55890</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:16:32.597882+00:00</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T17:15:21+00:00</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr"/>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>Home &gt; JobSearchResults &gt; _ Intern - Data</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="inlineStr"/>
+      <c r="H169" s="3" t="inlineStr"/>
+      <c r="I169" s="3" t="inlineStr"/>
+      <c r="J169" s="3" t="inlineStr"/>
+      <c r="K169" s="4" t="inlineStr">
+        <is>
+          <t>https://www.enterprisemobility.com/en/careers/job.html/567651/st-louis/intern-data-engineer-efm-it?mcid=jobboard%3A45130921&amp;gad_source=7</t>
+        </is>
+      </c>
+      <c r="L169" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
+          <t>@ enterprisemobility.com GC:
+© Enterprise Mobility © Saved Jobs —
+Home &gt; JobSearchResults &gt; _ Intern - Data
+Engineer (EFM IT)
+Intern - Data
+Engineer (EFM
+IT)
+| @ ENTERPRISEMOBILITY.COM |
+Brand
+-&lt;Snterprise
+https://scontent-ord5-2.cdninstagram.com/v/t51.71878-15/824693717_3083104255363601_3134666209160728736_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MzM5NzcwMzIzMjg1MDMxMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=1aJYBzBCV9cQ7kNvwHpS0HU&amp;_nc_oc=AdqIMTSXZoznWEeFMX8SncdSdenElXGTvtJMUfLLzyUOkxBAWKRyBDYLIC0hD5YaoqY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;oh=00_AQJlJUiaM0wSpFq4G0eh9QIh4-GRwGBAfZknWPgXb38fEw&amp;oe=6ABB43AE
+https://scontent-ord5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHlkAqF&amp;_nc_oc=AdqulOi4hZS51D5YYQLnIJClsZ5LI9n2Rf7zAHk3ulFFWRnu8u28hUM0Rspap24BbuQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIOf9rA0pPDj69YInvfSjaqFoQMJlh9G8fSA9QAvIu1yg&amp;oe=6ABB3A99
+https://l.instagram.com/?u=https%3A%2F%2Fwww.enterprisemobility.com%2Fen%2Fcareers%2Fjob.html%2F567651%2Fst-louis%2Fintern-data-engineer-efm-it%3Futm_source%3Dlinkedin.com%26utm_medium%3Dlisting%26utm_campaign%3Dxml_feed_us%26mcid%3Djobboard%253A45130921%26gad_source%3D7%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAae2ahKZiGTGzT_lMLlDNFWs2h8mqarP-_zmvlhKD7_8-7m8dNaQn0Fh6m9CCA_aem_qabW9b3sEXDUB6pr8AdCEg&amp;e=AUCHK8IQIcbc_YGMlb4jwbkz4EZ-njqNti6vk9xvfBjg0rW2F1Avpoq76c2HvK6A8ePCm73-3uNj0yop--LhqTAM349cv1OmOsUSguKXOA
+https://scontent-ord5-2.cdninstagram.com/o1/v/t2/f2/m78/AQOJuli4Wzht-TMRxm2eNDbS7krGlL5dRqP327w40NqQylOFh630wGgIrYH8tQDdH0UgeQeSaL2Ew7TvFfSKO751DSkb_3cMwG9bSxQ.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ohc=_lAfIinZ86QQ7kNvwFhY2zU&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgyMDc3NDU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=5e868d61e135c671&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzA0NDkwRTAxNDZFMThGRkNCRjY1QTExRjAwREUxQzk4X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk-e_UocihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKPMuFKxO3NGsaNRSrItUteBbDVbto1AJD7SqR5VhRriw&amp;oe=6AB762C0</t>
+        </is>
+      </c>
+      <c r="O169" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P169" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q169" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R169" s="3" t="inlineStr"/>
+    </row>
+    <row r="170" ht="45" customHeight="1">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>cf41d7f9b071100f87e6</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:16:33.564676+00:00</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T17:42:23+00:00</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>Revantage</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>Revantage — Quant</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>Quant</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr"/>
+      <c r="I170" s="3" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="J170" s="3" t="inlineStr"/>
+      <c r="K170" s="4" t="inlineStr">
+        <is>
+          <t>https://revantage.wd1.myworkdayjobs.com/Revantage/job/Remote---Illinois/Quantitative-Developer-Intern_JR104315</t>
+        </is>
+      </c>
+      <c r="L170" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr">
+        <is>
+          <t>Revantage
+Quantitative Developer Intern
+€} Remote
+© Remote - Illinois
+Remote - USA
+fen] Full time
+(©) Posted Today
+Who We Are
+Revantage, a Blackst state portfolio
+company, is a global pr of corporate
+services.
+With a corporate purpose of ‘In Pursuit of
+https://scontent-ord5-2.cdninstagram.com/v/t51.71878-15/815396810_3544422059072137_5140162354846146934_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5MzQxMTMwODQxNDYyMTI3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=RmvWIp0XvxIQ7kNvwFIGS9W&amp;_nc_oc=AdojFM-PunB1Pea-MLOvnmRLvJmEtuzFni1wSs7OcscjTt3W9qYPb7qeg_7QG_5TQnU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;oh=00_AQLsOAg9xgVH3Lmxah2AEs3Sl720foCh19xtAHHfrnEsfg&amp;oe=6ABB4FF7
+https://scontent-ord5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHlkAqF&amp;_nc_oc=AdqulOi4hZS51D5YYQLnIJClsZ5LI9n2Rf7zAHk3ulFFWRnu8u28hUM0Rspap24BbuQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIOf9rA0pPDj69YInvfSjaqFoQMJlh9G8fSA9QAvIu1yg&amp;oe=6ABB3A99
+https://l.instagram.com/?u=https%3A%2F%2Frevantage.wd1.myworkdayjobs.com%2FRevantage%2Fjob%2FRemote---Illinois%2FQuantitative-Developer-Intern_JR104315%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaesoidQvBXC0l_j3bMbQgCCGT_QAHQcFFqwcvJjP3TCeIE_hSc1DvyPSR3IUg_aem_dSC4ME5TKj0_2GNXNQ6L7w%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUCUq_Z9dPP__lD3JvoxkUfS66s-Ovvbqchir6tpojlGzeEVIhLsTvE62mqQVKn6L4bzLiFO3ZVvkgumADiNIaJtNAsZ3aB3-RhXCoaHhQ
+https://scontent-ord5-2.cdninstagram.com/o1/v/t2/f2/m78/AQNAZqYSYybF85nxA4HVIZT-HyrKjUdrn4ZPiHF1IQ3oK1d1LUFye4r108u4-ZeZdxMDBRX-sPLsrCEosQacWdi7z3HWyFsV6QXDlHE.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ohc=qlnrWCOaJBwQ7kNvwGYIBoZ&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgyMTIxMTA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=199f7de506f1b2bc&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0ZFNDVBRkFGQUVFQjhGRDc4RUFGMTUwNjZBM0Y0NEIxX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk7tSXwsihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLIEj_pvOh8HXVVK5hwkAc6PBVeaT1gUzUuFwrDFrsjfg&amp;oe=6AB753A0</t>
+        </is>
+      </c>
+      <c r="O170" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P170" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q170" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R170" s="3" t="inlineStr"/>
+    </row>
+    <row r="171" ht="45" customHeight="1">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>daab6d4ed0b7616eb274</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:16:38.127282+00:00</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:47:11+00:00</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>Apple — Internship</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="inlineStr"/>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I171" s="3" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="J171" s="3" t="inlineStr"/>
+      <c r="K171" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.apple.com/en-us/details/200674758/2026-Fall-UT-Austin-Intern-Event</t>
+        </is>
+      </c>
+      <c r="L171" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
+          <t>4
+Join Apple.
+2026 Fall UT Austin Intern Event
+- Jobs - Careers at Apple
+Apply for a 2026 Fall UT Austin Intern
+Event job at Apple. Read about the
+role and find out if it’s right for you.
+w
+PSA UT students - send this to your friends! Also, I'll
+be hosting a UT meetup before EOY since a few of my
+friends started ng jobs at Amazon :)
+https://scontent-ord5-1.cdninstagram.com/v/t51.71878-15/821529950_1642589934153285_4011455457998716315_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MzQ0MzkyMDY2NDA1MTM0Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=k3LlhmOIYPoQ7kNvwFJ8-32&amp;_nc_oc=AdrFmX5zAAPf24s0qpW8DE50V3_WdvLnEghjA5w9vJ2lwUneJ4zoXcnUe-ma7RbvKxY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-1.cdninstagram.com&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;oh=00_AQI1-i8OlVQBMzJht1bNg6IR1p7dqS41dlLw-N4bJThuMA&amp;oe=6ABB47B8
+https://scontent-ord5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHlkAqF&amp;_nc_oc=AdqulOi4hZS51D5YYQLnIJClsZ5LI9n2Rf7zAHk3ulFFWRnu8u28hUM0Rspap24BbuQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIOf9rA0pPDj69YInvfSjaqFoQMJlh9G8fSA9QAvIu1yg&amp;oe=6ABB3A99
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.apple.com%2Fen-us%2Fdetails%2F200674758%2F2026-Fall-UT-Austin-Intern-Event&amp;e=AUCxT5aw-rEXMqWH9-Bn0umYI8BNP_xtmKWx1PVbBDv1zySD4Jcpr0IgXAZ0l8yCW_JzQRrMSITyuni5TQra2b5yUZJf0XEtM7yNTvAqdQ
+https://scontent-ord5-2.cdninstagram.com/o1/v/t2/f2/m78/AQM_gVrcASmyYL0RSA_epk5PB70A5YNm3NOPo78kYbsRSI4IFLYdWonPT7PneknfZxXfmMRt1zskna5GTM5uEn7lGYrrv6Q9apnnMec.mp4?_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ohc=N2SjwzmH7EAQ7kNvwGDr-X-&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgyMTgwOTI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=e92f0f2f1741804a&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0UyNDU3RjIyRjZEMjZFNDE5MTY4NjkyNTE0M0Q5QThEX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkvMXg7sihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJgJpQXFv-lNORzJYASG_ybOGBKlZ3wHImj_mQKI6N2Tw&amp;oe=6AB76AFE</t>
+        </is>
+      </c>
+      <c r="O171" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P171" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q171" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R171" s="3" t="inlineStr"/>
+    </row>
+    <row r="172" ht="45" customHeight="1">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>49d612c5c6e9d1c3a93e</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:16:39.440882+00:00</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:48:21+00:00</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr"/>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr"/>
+      <c r="H172" s="3" t="inlineStr"/>
+      <c r="I172" s="3" t="inlineStr"/>
+      <c r="J172" s="3" t="inlineStr"/>
+      <c r="K172" s="4" t="inlineStr">
+        <is>
+          <t>https://luma.com/ptsnzkkl</t>
+        </is>
+      </c>
+      <c r="L172" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
+          <t>luma Spacex x V1
+Y e 4,
+SpaceX x V1 | “yt 2
+mie
+— —.,
+SpaceX x V1- Luma
+SpaceX is coming to the University
+of Michigan. Join V1 @ Michigan for
+a conversation with the team behind
+SpaceX on what they’re building, the
+technical...
+https://I
+SpaceX @ UMich .
+v
+Michigan students, send this SpaceX
+event to your friends!
+https://scontent-ord5-2.cdninstagram.com/v/t51.71878-15/821553089_1404482541143223_3251141281677036414_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MzQ0NDUwODY0NTU5MzAzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Qq_xkb2LjOoQ7kNvwGBaNRw&amp;_nc_oc=Ado24puImQ-dMLQyQCsr5_QBH_t6Zxk5-fX15uTAQY5z74_0vVLElvSSdd_5MeWwFlM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;oh=00_AQL2ce16lCx7oEPxU4wjaKzRJz2mh_t5XagnFWIFChPhOQ&amp;oe=6ABB5FFC
+https://scontent-ord5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHlkAqF&amp;_nc_oc=AdqulOi4hZS51D5YYQLnIJClsZ5LI9n2Rf7zAHk3ulFFWRnu8u28hUM0Rspap24BbuQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIOf9rA0pPDj69YInvfSjaqFoQMJlh9G8fSA9QAvIu1yg&amp;oe=6ABB3A99
+https://l.instagram.com/?u=https%3A%2F%2Fluma.com%2Fptsnzkkl%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacKH7ikTyK4sFNWKlzbF8eUgQXW2zwNR1O2EUU_daUKyLK8X3Yv4C3BD9hsRQ_aem_o4JsVzz2JTB-_cqyRPID3g%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUDr50bOm797_i3cgaSjivI-aIIXVtsrx7RF-bRK72Imre7w0-Dwfkxw1invMf0dL7Ev2bWKRC3BQ00AJUkfSopN4Zf4yqhOw1dQw5BuCQ
+https://scontent-ord5-2.cdninstagram.com/o1/v/t2/f2/m78/AQO_MFBfkVELc5RFK7czcKVOYQM7BmIQ9nzdRTGjNUDul-eR6Vezy-gdwaVfBFwHT4_58OdWclSwndC2H65ZSp_Em1maHn45F8Sbf1g.mp4?_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ohc=lsKbtbaRdL0Q7kNvwHt9p-1&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgyMTgzODM2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=4a8493b275e380af&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0RDNDQxNzFFQTE3MzI4OEYwNDhERTUzOTE2RTgwNEFCX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk94f28MihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQK8OxieN_3Lu4REIceDUO_Kxjb8sE-dxWw5lWCKLOOnug&amp;oe=6AB745AE</t>
+        </is>
+      </c>
+      <c r="O172" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P172" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q172" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R172" s="3" t="inlineStr"/>
+    </row>
+    <row r="173" ht="45" customHeight="1">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>aa7558ca0df39b94ea44</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:16:41.119515+00:00</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:49:17+00:00</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr"/>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>RecSys 2026 — Intern | Life at</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="inlineStr"/>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I173" s="3" t="inlineStr"/>
+      <c r="J173" s="3" t="inlineStr"/>
+      <c r="K173" s="4" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com/jobs/recsys-2026-intern</t>
+        </is>
+      </c>
+      <c r="L173" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
+          <t>hey sudo wanted to let you know
+that Spotify Internships dropped
+here's the link. | just wanted to
+ask though, there’s seems to be
+no requirements so i’m not really
+sure if they’re looking for new
+grad or undergrad students hope
+it’s u der grad lol
+7
+Eo
+Join Pr os
+a a
+RecSys 2026 — Intern | Life at
+Spotify
+OC K
+Spotify internships!!!
+https://scontent-ord5-2.cdninstagram.com/v/t51.71878-15/820292146_1564520991576830_8526884510725672990_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MzQ0NDk3NjM1MjQyNzA5MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=xXEIJloa7AYQ7kNvwHm__qv&amp;_nc_oc=Ado9NRLJ4FNU3ZgX3Yj8GtDYAPBCSASrmND2Vfv0TKC_HZ7BF1Kii9fNQz6Ezob38wM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;oh=00_AQLpv_s1ikIu_ADEVqreVl9DcWA5I_Jxe9Uqk6usRfNVYA&amp;oe=6ABB32F3
+https://scontent-ord5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHlkAqF&amp;_nc_oc=AdqulOi4hZS51D5YYQLnIJClsZ5LI9n2Rf7zAHk3ulFFWRnu8u28hUM0Rspap24BbuQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIOf9rA0pPDj69YInvfSjaqFoQMJlh9G8fSA9QAvIu1yg&amp;oe=6ABB3A99
+https://l.instagram.com/?u=https%3A%2F%2Fwww.lifeatspotify.com%2Fjobs%2Frecsys-2026-intern%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAactB6KYLKxMjaBOfilTQ_pjjhg_4Q2VVrKsprEEkTh5Kd13wTsXygPwzvQi-A_aem_ebkUGICzQbS2tYjEineB7g&amp;e=AUDG64pCh6dbtuMmm-upySjk0MRf_fLYayABnSJe1iPoM4pKwatvmxU1qTBBj2hZqki1-yC_f9InIz27s78_80PpKu8xnBzrsb2xV0Av6w
+https://scontent-ord5-2.cdninstagram.com/o1/v/t2/f2/m78/AQM6tqAy9wOmCyeF22vEB9D46PXDMXI4wLMZOtwb09pXr3jjIN2Ev1yyM9CElbfCk0vwjADeY4Oqx9SvKXZDqHNaSdbTJZ3Nj6TUohM.mp4?_nc_cat=107&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ohc=ZosU1v2gCpsQ7kNvwEYaPig&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgyMTg1MzM2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=a085474a1a5ceb39&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzQ3NDYzOEM1N0E5REQzQzI0NDE5MUU5REZCQzUzQ0FBX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkvY6F8sihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLgufIhM-B8GKiDpAySOy-bzcnqlGPzxsSox0p35IdwaQ&amp;oe=6AB763C0</t>
+        </is>
+      </c>
+      <c r="O173" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P173" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q173" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R173" s="3" t="inlineStr"/>
+    </row>
+    <row r="174" ht="45" customHeight="1">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>ac45cdc9a3be1671d228</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:16:42.821878+00:00</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:52:50+00:00</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr"/>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>As an intern, you'll work with our technologists and</t>
+        </is>
+      </c>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="inlineStr"/>
+      <c r="H174" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I174" s="3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J174" s="3" t="inlineStr"/>
+      <c r="K174" s="4" t="inlineStr">
+        <is>
+          <t>https://ecnf.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX/job/301908</t>
+        </is>
+      </c>
+      <c r="L174" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
+          <t>Tradeweb 2 =
+a WwW t View More Jobs
+Summer 2027 Product &amp; Sales
+Internship
+New York, NY, United States
+(2) 2027 PRODUCT AND SALES INTER!
+Who are we?
+At Tradeweb, we're constantly moving forward. We
+were the first to electronify the bond market, and
+we've been innovating ever since. Come join our
+team and find out what it means to lead the way
+into the future of electronic trading. Collaborate with
+our creative thinkers who have the vision and the
+drive and learn how you too can make an impact of
+your own.
+What's in it for you?
+As an intern, you'll work with our technologists and
+business experts to gain practical, hands-on
+experience that you can actually use. Our program
+https://scontent-ord5-2.cdninstagram.com/v/t51.71878-15/823849694_1372168018239031_8953684536632102977_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5MzQ0Njc2MTc4MzcxOTQxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=ptVWnGk4_wIQ7kNvwGPXNuB&amp;_nc_oc=AdrN71bpt2SBvUodVxosq9P0luTLRz1vELPmLZ5eS8LzvuVJ-aLIydRO9Wo16qXAIv0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;oh=00_AQKhugkbYUyxhjHqU2KwFhv6n8kovNfBiMzoaAJ-3CR2qw&amp;oe=6ABB5B2E
+https://scontent-ord5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHlkAqF&amp;_nc_oc=AdqulOi4hZS51D5YYQLnIJClsZ5LI9n2Rf7zAHk3ulFFWRnu8u28hUM0Rspap24BbuQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIOf9rA0pPDj69YInvfSjaqFoQMJlh9G8fSA9QAvIu1yg&amp;oe=6ABB3A99
+https://l.instagram.com/?u=https%3A%2F%2Fecnf.fa.us2.oraclecloud.com%2FhcmUI%2FCandidateExperience%2Fen%2Fsites%2FCX%2Fjob%2F301908%2F%3Futm_medium%3Djobshare%26utm_source%3Dzero2sudo%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAad1pRJmvOe365POtwvDJXYyqSLt9VjYZX4MZmpec-z5eaigk7UP7F3Oq-hcmg_aem_EF8QnuFkm36boIeOvMkftA&amp;e=AUDToLxSHqO9IXJhtALaO9AKYQbT2k5EzkveeKXUJzTNSIymKy0sidV63MamgmXrHQMFXr8NwZKc-ll4wpOXfOZdDJpdlwCOKvfigTceTQ
+https://scontent-ord5-1.cdninstagram.com/o1/v/t2/f2/m78/AQOvL95rOSFAmi16E3XsgsD1bj_GaIZdU1_uHv2Fcv_-RxyXFuKrGQZSylY1oO5vNLQLp2FWHR6e97koLPFXLsFcodBq9mF6N73rVx8.mp4?_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-1.cdninstagram.com&amp;_nc_ohc=STs0VuaTJW4Q7kNvwGuyBmA&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgyMTg4MDk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=1abf7bf961aa7d01&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzVENENCQjBGODJCOThBMEYyQkM5OTY0RDI4NDdDQUE2X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk8amM9MihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIvKefewZ7H7cqVJN5vYyI5f-JO_7eN57x4VPZ9E1D4ow&amp;oe=6AB769D3</t>
+        </is>
+      </c>
+      <c r="O174" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P174" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q174" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R174" s="3" t="inlineStr"/>
+    </row>
+    <row r="175" ht="45" customHeight="1">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>e62d49de52202b14784c</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:16:44.787053+00:00</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:54:15+00:00</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>Amazon — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H175" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I175" s="3" t="inlineStr"/>
+      <c r="J175" s="3" t="inlineStr"/>
+      <c r="K175" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.jobs/en/jobs/10558915/software-development-engineer-i-annapurna-labs-early-career-2027</t>
+        </is>
+      </c>
+      <c r="L175" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
+          <t>— amazonjobs
+— I
+Software Development
+Engineer I, Annapurna
+Labs, Early Career - 2027
+Job ID: 10558915 | Annapurna Labs (U.S.) Inc. - D63
+Apply now
+Description
+At Amazon, our tech isn't just a tool, it's your
+S ~ fe = Pee ae ae Pe BIFLAI CRPR Ar £1
+t) | iy7 | AA “JOVAI AIT rOnAK QuvUl
+. 7
+‘Zz , , IVA TY 4 Hay Vibe B/LE fo kee J vay | |
+° 4 ZN Xe If 2 1 i = | | V ! | | | i U | \ { Y es V V lJ i } i = LJ 4 ) V V L : e S
+environment where y y building.
+Whether you're creati native solutions,
+optimizing ieGHTIFE lea aes or ePueinng
+amazon swe ng according to follower
+bo nenorts at Szenadeusoalum) |
+https://scontent-ord5-1.cdninstagram.com/v/t51.71878-15/821501080_1650145866539875_3582608712316627656_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5MzQ0NzQ3NTcyOTg5OTM3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=IxnX7rPpcGkQ7kNvwEA7tOP&amp;_nc_oc=Adrca_prBcF_xVSfF_sT6pP5FOu-7_-sC_bTmy78tAFLSZOn296fb0ilrlaqJJ9nX5A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-1.cdninstagram.com&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;oh=00_AQLPNbKPTteliri177o7XZJ-SZJ6GfNxhKxEY8-4ffKXaA&amp;oe=6ABB3FB3
+https://scontent-ord5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHlkAqF&amp;_nc_oc=AdqulOi4hZS51D5YYQLnIJClsZ5LI9n2Rf7zAHk3ulFFWRnu8u28hUM0Rspap24BbuQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIOf9rA0pPDj69YInvfSjaqFoQMJlh9G8fSA9QAvIu1yg&amp;oe=6ABB3A99
+https://scontent-ord5-1.cdninstagram.com/v/t51.82787-19/797775631_18103318937000254_3335198124454043468_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=111&amp;ig_cache_key=GA8XjS8_2X5m31BAAEzfoQcGAUkubmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;_nc_aid=2427&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=7t0xZn7RXnIQ7kNvwGyyQS4&amp;_nc_oc=Ado7OBrFS0OeXscC4GtJfezbwFaRg0p9nNgvOGfsEc_OZ3ddFV6eOWJaH8Ki-l75z0U&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-ord5-1.cdninstagram.com&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;oh=00_AQKCkU3CqCbBayzfI57cbShMY0OU9Ql2pRy3omkqYhJcyA&amp;oe=6ABB61EB
+https://l.instagram.com/?u=https%3A%2F%2Fwww.amazon.jobs%2Fen%2Fjobs%2F10558915%2Fsoftware-development-engineer-i-annapurna-labs-early-career-2027%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadTAjPBpvRdzkIfi1edEqGTMXBn6H_eQUYQpMIg6iF6QJrmRa0unkWRn8ZEjA_aem_2CL7GwPYwHEo30fZskMr_A&amp;e=AUBTsViwdfMmRQKaE3bGTakBGVZWLkiqq1SolirbXgUkz2Kmc1HBisxUZa-X9e8FKVzRwgwdOyaZdgJNMylcHUlgcOOIH9S2FOSzMSv-GA
+https://scontent-ord5-2.cdninstagram.com/o1/v/t2/f2/m78/AQM1_enD1cnonqZqfAo9BX4mJMfAuce0b76uWPl4nWthqAYs101pxZndgTJLoAAoI2AVkQBB5TljZHdnAun94H5GfWUFoUVd5_IA8Z0.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ohc=yZQBDkSpCWsQ7kNvwGpzLj2&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgyMTg5ODk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDgyNiwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=e3862fe1806dd563&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0FCNDA0MkVCRTQwOTVGRjNCNzRBRDk3RDM4QUNFOUFFX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkxf639cihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZZSpAQA&amp;_nc_gid=2X_1Bdq2VpbVzU3ILG_KcA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJBqL-gpNzeXGnQ22Rj3Pbi8LAZgor7BSAP5Nlp13OzaQ&amp;oe=6AB75BB8</t>
+        </is>
+      </c>
+      <c r="O175" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P175" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q175" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R175" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R159"/>
+  <autoFilter ref="A1:R175"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -15922,6 +17439,38 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" r:id="rId299"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K159" r:id="rId300"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L159" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K160" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L160" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K161" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K162" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L162" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K163" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L163" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K164" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L164" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K165" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L165" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K166" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L166" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K167" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L167" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K168" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L168" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K169" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L169" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K170" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L170" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K171" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L171" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K172" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L172" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K173" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L173" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K174" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L174" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K175" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L175" r:id="rId333"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$177</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R175"/>
+  <dimension ref="A1:R177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15621,7 +15621,7 @@
     <row r="160" ht="45" customHeight="1">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>51d7d7d9b65fda4897f7</t>
+          <t>5e630896300c6b5bb0c7</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -15634,7 +15634,7 @@
           <t>2026-09-24T15:47:56+00:00</t>
         </is>
       </c>
-      <c r="D160" s="3" t="inlineStr"/>
+      <c r="D160" s="3" t="n"/>
       <c r="E160" s="3" t="inlineStr">
         <is>
           <t>join! RSVP to confirm your attendance.</t>
@@ -15645,10 +15645,10 @@
           <t>New Grad / Early Career</t>
         </is>
       </c>
-      <c r="G160" s="3" t="inlineStr"/>
-      <c r="H160" s="3" t="inlineStr"/>
-      <c r="I160" s="3" t="inlineStr"/>
-      <c r="J160" s="3" t="inlineStr"/>
+      <c r="G160" s="3" t="n"/>
+      <c r="H160" s="3" t="n"/>
+      <c r="I160" s="3" t="n"/>
+      <c r="J160" s="3" t="n"/>
       <c r="K160" s="4" t="inlineStr">
         <is>
           <t>https://events.riviancareers.com/plugin-earlycareer2027</t>
@@ -15700,12 +15700,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R160" s="3" t="inlineStr"/>
+      <c r="R160" s="3" t="n"/>
     </row>
     <row r="161" ht="45" customHeight="1">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>fa552c8503e2cb450935</t>
+          <t>aa477f60e27375fce5d7</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -15743,8 +15743,8 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="I161" s="3" t="inlineStr"/>
-      <c r="J161" s="3" t="inlineStr"/>
+      <c r="I161" s="3" t="n"/>
+      <c r="J161" s="3" t="n"/>
       <c r="K161" s="4" t="inlineStr">
         <is>
           <t>https://amazon.jobs/en/jobs/3177934/software-development-engineer-2026-us</t>
@@ -15798,12 +15798,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R161" s="3" t="inlineStr"/>
+      <c r="R161" s="3" t="n"/>
     </row>
     <row r="162" ht="45" customHeight="1">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>1f415241cb06464d53d5</t>
+          <t>a536426acd2de94919de</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -15831,14 +15831,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G162" s="3" t="inlineStr"/>
-      <c r="H162" s="3" t="inlineStr"/>
+      <c r="G162" s="3" t="n"/>
+      <c r="H162" s="3" t="n"/>
       <c r="I162" s="3" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="J162" s="3" t="inlineStr"/>
+      <c r="J162" s="3" t="n"/>
       <c r="K162" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/klaviyocampus/jobs/8003260003</t>
@@ -15893,12 +15893,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R162" s="3" t="inlineStr"/>
+      <c r="R162" s="3" t="n"/>
     </row>
     <row r="163" ht="45" customHeight="1">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>29671a80dcb3a72986d6</t>
+          <t>e7357d50754f99bfdecd</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -15926,14 +15926,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G163" s="3" t="inlineStr"/>
-      <c r="H163" s="3" t="inlineStr"/>
+      <c r="G163" s="3" t="n"/>
+      <c r="H163" s="3" t="n"/>
       <c r="I163" s="3" t="inlineStr">
         <is>
           <t>Menlo Park</t>
         </is>
       </c>
-      <c r="J163" s="3" t="inlineStr"/>
+      <c r="J163" s="3" t="n"/>
       <c r="K163" s="4" t="inlineStr">
         <is>
           <t>https://www.metacareers.com/profile/job_details/1412139847020398</t>
@@ -15989,12 +15989,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R163" s="3" t="inlineStr"/>
+      <c r="R163" s="3" t="n"/>
     </row>
     <row r="164" ht="45" customHeight="1">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>c5d0b12b0e45fe127452</t>
+          <t>29bd66672b379387e6c1</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -16022,10 +16022,10 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G164" s="3" t="inlineStr"/>
-      <c r="H164" s="3" t="inlineStr"/>
-      <c r="I164" s="3" t="inlineStr"/>
-      <c r="J164" s="3" t="inlineStr"/>
+      <c r="G164" s="3" t="n"/>
+      <c r="H164" s="3" t="n"/>
+      <c r="I164" s="3" t="n"/>
+      <c r="J164" s="3" t="n"/>
       <c r="K164" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/boxinc/jobs/8226667</t>
@@ -16081,12 +16081,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R164" s="3" t="inlineStr"/>
+      <c r="R164" s="3" t="n"/>
     </row>
     <row r="165" ht="45" customHeight="1">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>859986cdba3feebf4b1e</t>
+          <t>790d610bd0cd2794be3a</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -16129,7 +16129,7 @@
           <t>Seattle, San Francisco, Austin</t>
         </is>
       </c>
-      <c r="J165" s="3" t="inlineStr"/>
+      <c r="J165" s="3" t="n"/>
       <c r="K165" s="4" t="inlineStr">
         <is>
           <t>https://adobe.wd5.myworkdayjobs.com/en-US/external_experienced/job/San-Jose/XMLNAME-2027-University-Graduate---Software-Engineer_R172083</t>
@@ -16186,12 +16186,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R165" s="3" t="inlineStr"/>
+      <c r="R165" s="3" t="n"/>
     </row>
     <row r="166" ht="45" customHeight="1">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>e1283f0dbe8bb2b77461</t>
+          <t>8af693b8ef87e6be5ee3</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -16229,8 +16229,8 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="I166" s="3" t="inlineStr"/>
-      <c r="J166" s="3" t="inlineStr"/>
+      <c r="I166" s="3" t="n"/>
+      <c r="J166" s="3" t="n"/>
       <c r="K166" s="4" t="inlineStr">
         <is>
           <t>https://adobe.wd5.myworkdayjobs.com/external_experienced/job/San-Jose/XMLNAME-2027-University-Graduate---Product-Manager_R171844</t>
@@ -16288,12 +16288,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R166" s="3" t="inlineStr"/>
+      <c r="R166" s="3" t="n"/>
     </row>
     <row r="167" ht="45" customHeight="1">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>db8279f0092dc22703c5</t>
+          <t>35428bddc6dfcae4f2db</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -16326,9 +16326,9 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H167" s="3" t="inlineStr"/>
-      <c r="I167" s="3" t="inlineStr"/>
-      <c r="J167" s="3" t="inlineStr"/>
+      <c r="H167" s="3" t="n"/>
+      <c r="I167" s="3" t="n"/>
+      <c r="J167" s="3" t="n"/>
       <c r="K167" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/perplexity/8a99d9be-6955-4f28-8150-80c8ce72c523</t>
@@ -16382,12 +16382,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R167" s="3" t="inlineStr"/>
+      <c r="R167" s="3" t="n"/>
     </row>
     <row r="168" ht="45" customHeight="1">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>f4dfbbd8ab9825421b9d</t>
+          <t>261fba51e29fbb223eb8</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -16430,7 +16430,7 @@
           <t>Bay Area, NYC</t>
         </is>
       </c>
-      <c r="J168" s="3" t="inlineStr"/>
+      <c r="J168" s="3" t="n"/>
       <c r="K168" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/genesis-molecular-ai/42fc0631-3f81-481a-b496-daa875c9e92e?src=zero2sudo</t>
@@ -16484,12 +16484,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R168" s="3" t="inlineStr"/>
+      <c r="R168" s="3" t="n"/>
     </row>
     <row r="169" ht="45" customHeight="1">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>59af26457e8355c55890</t>
+          <t>0c6437187383061186a0</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -16502,7 +16502,7 @@
           <t>2026-09-24T17:15:21+00:00</t>
         </is>
       </c>
-      <c r="D169" s="3" t="inlineStr"/>
+      <c r="D169" s="3" t="n"/>
       <c r="E169" s="3" t="inlineStr">
         <is>
           <t>Home &gt; JobSearchResults &gt; _ Intern - Data</t>
@@ -16513,10 +16513,10 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G169" s="3" t="inlineStr"/>
-      <c r="H169" s="3" t="inlineStr"/>
-      <c r="I169" s="3" t="inlineStr"/>
-      <c r="J169" s="3" t="inlineStr"/>
+      <c r="G169" s="3" t="n"/>
+      <c r="H169" s="3" t="n"/>
+      <c r="I169" s="3" t="n"/>
+      <c r="J169" s="3" t="n"/>
       <c r="K169" s="4" t="inlineStr">
         <is>
           <t>https://www.enterprisemobility.com/en/careers/job.html/567651/st-louis/intern-data-engineer-efm-it?mcid=jobboard%3A45130921&amp;gad_source=7</t>
@@ -16565,12 +16565,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R169" s="3" t="inlineStr"/>
+      <c r="R169" s="3" t="n"/>
     </row>
     <row r="170" ht="45" customHeight="1">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>cf41d7f9b071100f87e6</t>
+          <t>e7ea9e4175d9b1a5e131</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -16603,13 +16603,13 @@
           <t>Quant</t>
         </is>
       </c>
-      <c r="H170" s="3" t="inlineStr"/>
+      <c r="H170" s="3" t="n"/>
       <c r="I170" s="3" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="J170" s="3" t="inlineStr"/>
+      <c r="J170" s="3" t="n"/>
       <c r="K170" s="4" t="inlineStr">
         <is>
           <t>https://revantage.wd1.myworkdayjobs.com/Revantage/job/Remote---Illinois/Quantitative-Developer-Intern_JR104315</t>
@@ -16660,12 +16660,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R170" s="3" t="inlineStr"/>
+      <c r="R170" s="3" t="n"/>
     </row>
     <row r="171" ht="45" customHeight="1">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>daab6d4ed0b7616eb274</t>
+          <t>04eff52294e1e05f86f2</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -16693,7 +16693,7 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G171" s="3" t="inlineStr"/>
+      <c r="G171" s="3" t="n"/>
       <c r="H171" s="3" t="inlineStr">
         <is>
           <t>2026</t>
@@ -16704,7 +16704,7 @@
           <t>Austin</t>
         </is>
       </c>
-      <c r="J171" s="3" t="inlineStr"/>
+      <c r="J171" s="3" t="n"/>
       <c r="K171" s="4" t="inlineStr">
         <is>
           <t>https://jobs.apple.com/en-us/details/200674758/2026-Fall-UT-Austin-Intern-Event</t>
@@ -16754,12 +16754,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R171" s="3" t="inlineStr"/>
+      <c r="R171" s="3" t="n"/>
     </row>
     <row r="172" ht="45" customHeight="1">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>49d612c5c6e9d1c3a93e</t>
+          <t>3249cd0daef8faaa0307</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -16772,7 +16772,7 @@
           <t>2026-09-24T18:48:21+00:00</t>
         </is>
       </c>
-      <c r="D172" s="3" t="inlineStr"/>
+      <c r="D172" s="3" t="n"/>
       <c r="E172" s="3" t="inlineStr">
         <is>
           <t>Other Opportunity</t>
@@ -16783,10 +16783,10 @@
           <t>Other Opportunity</t>
         </is>
       </c>
-      <c r="G172" s="3" t="inlineStr"/>
-      <c r="H172" s="3" t="inlineStr"/>
-      <c r="I172" s="3" t="inlineStr"/>
-      <c r="J172" s="3" t="inlineStr"/>
+      <c r="G172" s="3" t="n"/>
+      <c r="H172" s="3" t="n"/>
+      <c r="I172" s="3" t="n"/>
+      <c r="J172" s="3" t="n"/>
       <c r="K172" s="4" t="inlineStr">
         <is>
           <t>https://luma.com/ptsnzkkl</t>
@@ -16841,12 +16841,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R172" s="3" t="inlineStr"/>
+      <c r="R172" s="3" t="n"/>
     </row>
     <row r="173" ht="45" customHeight="1">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>aa7558ca0df39b94ea44</t>
+          <t>6500e0d192592887086b</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -16859,7 +16859,7 @@
           <t>2026-09-24T18:49:17+00:00</t>
         </is>
       </c>
-      <c r="D173" s="3" t="inlineStr"/>
+      <c r="D173" s="3" t="n"/>
       <c r="E173" s="3" t="inlineStr">
         <is>
           <t>RecSys 2026 — Intern | Life at</t>
@@ -16870,14 +16870,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G173" s="3" t="inlineStr"/>
+      <c r="G173" s="3" t="n"/>
       <c r="H173" s="3" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="I173" s="3" t="inlineStr"/>
-      <c r="J173" s="3" t="inlineStr"/>
+      <c r="I173" s="3" t="n"/>
+      <c r="J173" s="3" t="n"/>
       <c r="K173" s="4" t="inlineStr">
         <is>
           <t>https://www.lifeatspotify.com/jobs/recsys-2026-intern</t>
@@ -16932,12 +16932,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R173" s="3" t="inlineStr"/>
+      <c r="R173" s="3" t="n"/>
     </row>
     <row r="174" ht="45" customHeight="1">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>ac45cdc9a3be1671d228</t>
+          <t>ec5a338f5ff898e94780</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -16950,10 +16950,10 @@
           <t>2026-09-24T18:52:50+00:00</t>
         </is>
       </c>
-      <c r="D174" s="3" t="inlineStr"/>
+      <c r="D174" s="3" t="n"/>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>As an intern, you'll work with our technologists and</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -16961,7 +16961,7 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G174" s="3" t="inlineStr"/>
+      <c r="G174" s="3" t="n"/>
       <c r="H174" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
@@ -16972,7 +16972,7 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="J174" s="3" t="inlineStr"/>
+      <c r="J174" s="3" t="n"/>
       <c r="K174" s="4" t="inlineStr">
         <is>
           <t>https://ecnf.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX/job/301908</t>
@@ -17030,12 +17030,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R174" s="3" t="inlineStr"/>
+      <c r="R174" s="3" t="n"/>
     </row>
     <row r="175" ht="45" customHeight="1">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>e62d49de52202b14784c</t>
+          <t>f230624684d30d919fcf</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -17073,8 +17073,8 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="I175" s="3" t="inlineStr"/>
-      <c r="J175" s="3" t="inlineStr"/>
+      <c r="I175" s="3" t="n"/>
+      <c r="J175" s="3" t="n"/>
       <c r="K175" s="4" t="inlineStr">
         <is>
           <t>https://www.amazon.jobs/en/jobs/10558915/software-development-engineer-i-annapurna-labs-early-career-2027</t>
@@ -17133,10 +17133,216 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R175" s="3" t="inlineStr"/>
+      <c r="R175" s="3" t="n"/>
+    </row>
+    <row r="176" ht="45" customHeight="1">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>079f963bee22206d00b2</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T22:32:39.512038+00:00</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T22:26:53+00:00</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>Amazon — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H176" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I176" s="3" t="inlineStr"/>
+      <c r="J176" s="3" t="inlineStr"/>
+      <c r="K176" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.jobs/en/jobs/10559746/software-development-engineer-intern-summer-2027-usa-amazon-dedicated-cloud-adc</t>
+        </is>
+      </c>
+      <c r="L176" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
+          <t>— amazonjobs
+— ——7
+Software Development
+Engineer Intern -
+Summer 2027 (USA) ,
+Amazon Dedicated Cloud
+(ADC)
+Job ID: 10559746 | Amazon.com Services LLC
+Amazon SWE Intern 2027
+Description
+Appli:
+accep
+Shape what comes n er careers in
+Tech
+At Amazon, our tech isn't just a tool, it's your
+playground. Our engineers work on scalable
+systems, cloud services, and customer-facing
+products that operate at global scale. This is an
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/819286880_2053043681982473_3180953103862228712_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MzU1NDQ5NTY3NzI1MzIzNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=qrswl5tbRQQQ7kNvwF9nf36&amp;_nc_oc=Adp7yp18LDcnpb7ykf3RgTJbbOJFwJD1wX292YQoirX3VpAcPdiSvPmYvCnY64eRsD8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=SOesJhqVBmx7iTDoBcaAyg&amp;_nc_ss=7e3ba&amp;oh=00_AQKHSMgyUR12wo0Ec6gJfNlWz2W9VPWnCD95pxMXRnSzcA&amp;oe=6ABB8247
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/819286880_2053043681982473_3180953103862228712_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MzU1NDQ5NTY3NzI1MzIzNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=qrswl5tbRQQQ7kNvwF9nf36&amp;_nc_oc=Adp7yp18LDcnpb7ykf3RgTJbbOJFwJD1wX292YQoirX3VpAcPdiSvPmYvCnY64eRsD8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=SOesJhqVBmx7iTDoBcaAyg&amp;_nc_ss=7e3ba&amp;oh=00_AQLYBHxoSljOTAcxcPPocOoqqcutMzHxlJEUv0nGEmNoqw&amp;oe=6ABB8247
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwEdDP0S&amp;_nc_oc=AdqYz2sDp9rPCzqccaTXWuWkQwrF4bE5McRbAEbCa0j2qyZeMszAjVV5DEiRb8q-gAc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQILkUxnhURfUKLd-NWFFhQoU-tmq8FzYL7HyIcRIyfXyA&amp;oe=6ABB72D9
+https://l.instagram.com/?u=https%3A%2F%2Fwww.amazon.jobs%2Fen%2Fjobs%2F10559746%2Fsoftware-development-engineer-intern-summer-2027-usa-amazon-dedicated-cloud-adc%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaen_-1mqOY4RMpj-k4GGatmyO2mh5TVvsrif2o5GbptUtovHji0q23drCUAHA_aem_MF3w7qn__L02vtLwVl0h1g&amp;e=AUBEPZx0pZVgvq_ukGXDfy4V78YR7dxlwq2GvNiEWY7_eaPOfsZBp1pPlns_ndoNDNCEgL3ZIOsH2_HqYT8nnDRmzXF32PWD8Y6pmTjVHQ
+https://scontent-sjc6-1.cdninstagram.com/o1/v/t2/f2/m78/AQPkJc2q6cN8DE54LvVf0XCNHtDGlX0__H4YNdBmI2CIvf3WI5EWDWAeDtN7GyzavtV8C6nt4Xih4AtpCmQIKdpFzYaJLk3qmKITAK8.mp4?_nc_cat=107&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ohc=IkJAZpSJqlsQ7kNvwFOpOss&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgyMzg5MzY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=f2d7d47528f15552&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzI5NDk1MjNDRTU3MkVBQUVCQUE4NTc1NDE4QjI3Q0EzX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkiPeGisqhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=SOesJhqVBmx7iTDoBcaAyg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLogHl5PPwykkbECsMRRqU9hNDsd-ccM6X9x4xxMdqRIw&amp;oe=6AB78074</t>
+        </is>
+      </c>
+      <c r="O176" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P176" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q176" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R176" s="3" t="inlineStr"/>
+    </row>
+    <row r="177" ht="45" customHeight="1">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>73b1fd99847db3f2b05d</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T22:32:41.326307+00:00</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T22:30:28+00:00</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>Amazon — Software Engineering, Machine Learning / AI</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G177" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering, Machine Learning / AI</t>
+        </is>
+      </c>
+      <c r="H177" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I177" s="3" t="inlineStr"/>
+      <c r="J177" s="3" t="inlineStr"/>
+      <c r="K177" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.jobs/en/jobs/10559762/software-development-engineer-intern-amazon-leo-summer-2027-usa</t>
+        </is>
+      </c>
+      <c r="L177" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="inlineStr">
+        <is>
+          <t>— amazonjobs
+— 7
+Software Development
+Engineer Intern, Amazon
+Leo - Summer 2027
+(USA)
+Job ID: 10559762 | Amazon.com Services LLC
+Apply now
+Description
+Shape what comes next | Discover careers in
+Tech
+(2) AMAZON LEO 2027 SWE INTERN
+customer-facing
+systems, cloud services
+products that opera l scale. This is an
+environment where y y building.
+Whether you're creating cloud-native solutions,
+optimizing machine learning models, or building
+products that drive experiences for millions of
+a ee ee eee ee
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/825016832_1627987385395137_4428288922100101405_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MzU1NjMwMDYyMTM2NjkzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=HYoKPnWqRekQ7kNvwFbO9h1&amp;_nc_oc=Adp3giWpKvtD6_d9eMHn7flYMsBFHqjPY1Z7gwidTVtOlcg7kM_7H7S283uOQjLGNIk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=SOesJhqVBmx7iTDoBcaAyg&amp;_nc_ss=7e3ba&amp;oh=00_AQLxi3RUJ80PCgb4gXAozI2Vyz_QJfMNcbZrfmoqBxF1nw&amp;oe=6ABB6997
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/825016832_1627987385395137_4428288922100101405_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MzU1NjMwMDYyMTM2NjkzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=HYoKPnWqRekQ7kNvwFbO9h1&amp;_nc_oc=Adp3giWpKvtD6_d9eMHn7flYMsBFHqjPY1Z7gwidTVtOlcg7kM_7H7S283uOQjLGNIk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=SOesJhqVBmx7iTDoBcaAyg&amp;_nc_ss=7e3ba&amp;oh=00_AQJmP3Hp-Q9dblGsk049tZbvxaqpoCfk7idhvO-C2VTjrg&amp;oe=6ABB6997
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwEdDP0S&amp;_nc_oc=AdqYz2sDp9rPCzqccaTXWuWkQwrF4bE5McRbAEbCa0j2qyZeMszAjVV5DEiRb8q-gAc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQILkUxnhURfUKLd-NWFFhQoU-tmq8FzYL7HyIcRIyfXyA&amp;oe=6ABB72D9
+https://l.instagram.com/?u=https%3A%2F%2Fwww.amazon.jobs%2Fen%2Fjobs%2F10559762%2Fsoftware-development-engineer-intern-amazon-leo-summer-2027-usa%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafiO2CMcFm8usOMMJiP-_PwH9zodoOMS8H9Sj535x1eteVjugjvdJaBu-MUHw_aem_G1BupsyrD1owWbx-YFXENQ&amp;e=AUAEj5Hd5-HXZK9JXeZ3U1laIPSltDDGFYNAT7XFmA7zsVKZuPWPyg-gltGPJT8yRGcqOm9jC7DsUiPYnMMuiYw0gGgebOKWXbW9dm2AvQ
+https://scontent-sjc3-1.cdninstagram.com/o1/v/t2/f2/m78/AQNmREXTqOTgJSUFowfKluvYdxZ-53D8ldeHxyXycYp2ZlMWwz76p5Hgs4Ac8TmyIn-wq7Bkd5xgodYz8c3zl7-izUPkLuwFt3Mqzpc.mp4?_nc_cat=110&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_ohc=Ttpa8bTtpSMQ7kNvwEVGQl5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgyMzkyMjE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=e00fc5a0020b7c84&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzEyNDQwNTZCMjU0NjM3NDdENDk4MDQwNzZDMjdBRkI2X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkjd2WjMqhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=SOesJhqVBmx7iTDoBcaAyg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIxzCGPzt1uwancgX3lKionWcI9E_EDzBvx14_VHuS0sg&amp;oe=6AB7934B</t>
+        </is>
+      </c>
+      <c r="O177" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P177" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q177" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R177" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R175"/>
+  <autoFilter ref="A1:R177"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -17471,6 +17677,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L174" r:id="rId331"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K175" r:id="rId332"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L175" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K176" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L176" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K177" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" r:id="rId337"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$180</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R177"/>
+  <dimension ref="A1:R180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17138,7 +17138,7 @@
     <row r="176" ht="45" customHeight="1">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>079f963bee22206d00b2</t>
+          <t>b322cfdb679f4c1281ef</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -17176,8 +17176,8 @@
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I176" s="3" t="inlineStr"/>
-      <c r="J176" s="3" t="inlineStr"/>
+      <c r="I176" s="3" t="n"/>
+      <c r="J176" s="3" t="n"/>
       <c r="K176" s="4" t="inlineStr">
         <is>
           <t>https://www.amazon.jobs/en/jobs/10559746/software-development-engineer-intern-summer-2027-usa-amazon-dedicated-cloud-adc</t>
@@ -17235,12 +17235,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R176" s="3" t="inlineStr"/>
+      <c r="R176" s="3" t="n"/>
     </row>
     <row r="177" ht="45" customHeight="1">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>73b1fd99847db3f2b05d</t>
+          <t>1343541a412bf908a8be</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -17278,8 +17278,8 @@
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I177" s="3" t="inlineStr"/>
-      <c r="J177" s="3" t="inlineStr"/>
+      <c r="I177" s="3" t="n"/>
+      <c r="J177" s="3" t="n"/>
       <c r="K177" s="4" t="inlineStr">
         <is>
           <t>https://www.amazon.jobs/en/jobs/10559762/software-development-engineer-intern-amazon-leo-summer-2027-usa</t>
@@ -17339,10 +17339,301 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R177" s="3" t="inlineStr"/>
+      <c r="R177" s="3" t="n"/>
+    </row>
+    <row r="178" ht="45" customHeight="1">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>86b3676ac0b8b8702ae1</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T01:37:35.148140+00:00</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T22:49:31+00:00</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>AMD — Internship</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="inlineStr"/>
+      <c r="H178" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I178" s="3" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="J178" s="3" t="inlineStr"/>
+      <c r="K178" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.amd.com/careers-home/jobs/92880?lang=en-us&amp;iis=Job+Board&amp;iisn=zero2sudo</t>
+        </is>
+      </c>
+      <c r="L178" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
+          <t>x @ careers.amd.com C:
+Instagram
+AMD ¢1 | Careers —
+€ Back
+2027 Undergrad Program Management
+Intern/Co-op
+Locations: Austin, Texas
+Categories: Student / Intern / Temp
+Req ID: 92880
+Hiring Target Min: USD $59,072.00/Yr.
+Hiring Target Max: USD $88,608.00/Yr.
+https://scontent-atl3-2.cdninstagram.com/v/t51.71878-15/819002825_1506945411257933_1840454424843831975_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MzU2NTg4NTQ4NjgxMzgxNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=YiD4vSOBmtsQ7kNvwFJ4ABa&amp;_nc_oc=AdqUdJDlTJ9TBaSdlBAtiO8DMfrMswE-BeofmeLpgorgOrNEFzWtWVbtE1kRzMpEZ9c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=YmeEk6d89TUVk09YjtsUeg&amp;_nc_ss=7e3ba&amp;oh=00_AQLeYAW4pSc7b2AMx3QorHpp3P8YBxERmVwRxo7pQWBgLQ&amp;oe=6ABBA007
+https://scontent-atl3-2.cdninstagram.com/v/t51.71878-15/819002825_1506945411257933_1840454424843831975_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MzU2NTg4NTQ4NjgxMzgxNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=YiD4vSOBmtsQ7kNvwFJ4ABa&amp;_nc_oc=AdqUdJDlTJ9TBaSdlBAtiO8DMfrMswE-BeofmeLpgorgOrNEFzWtWVbtE1kRzMpEZ9c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=YmeEk6d89TUVk09YjtsUeg&amp;_nc_ss=7e3ba&amp;oh=00_AQIWXr3E2uhFJNPfO8SbpDQze1Am9SoGF1unzPWSZXYzMg&amp;oe=6ABBA007
+https://scontent-atl3-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHvkmAd&amp;_nc_oc=AdriCIokFaRj7V5yZ_bglFa8ayVBw2MbKEzbbSZuIxlXEq6ygicYgSOaFddhh0hwCJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQI-XhE2q_sVW-ToSKarkhW0NvAZdMrbDALBaz8flCzYjg&amp;oe=6ABBAB19
+https://l.instagram.com/?u=https%3A%2F%2Fcareers.amd.com%2Fcareers-home%2Fjobs%2F92880%3Flang%3Den-us%26iis%3DJob%2BBoard%26iisn%3Dzero2sudo%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadoiYhz2Xky8whjOXPO2SCg0xLH8WH1IbIUUl0K2n17XTkEgod_Vmud8PKK1A_aem_ddPZGrD8umk_kfEJUcM_Pg&amp;e=AUBsmg6tzej2Gulr0glgdEkgHorC1bRFQy8_trluVp8x4W5sL3ZSfkOjtUk-20knyu4pf19bhylMrDDMm_PDJ6J1vj0TOx-5HEo8fz42nQ
+https://scontent-atl3-1.cdninstagram.com/o1/v/t2/f2/m78/AQOtqt3VxTutxQlwyxK2eD7FTOl9LMstqbINM9GlHa_oFvKOq91Qr9Pd9qE4x5vqDQPnVH-MOfUyZWltAmByMm0otJwxyO3vUzKsGeY.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ohc=QdOcJHiAUDwQ7kNvwHlI5AC&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgyNDA5NDk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=4d5c298a190c4f53&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzZGNEExMDEzNzc2QUJEQjlEMkUwRDk2RjM2NTc3RDlDX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkzdaGmcqhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=YmeEk6d89TUVk09YjtsUeg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKa0LQOcAcsrDlrhPFPLJxC7dNKcMBC_ema1t4jeLxCFA&amp;oe=6AB7B342</t>
+        </is>
+      </c>
+      <c r="O178" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P178" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q178" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R178" s="3" t="inlineStr"/>
+    </row>
+    <row r="179" ht="45" customHeight="1">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>1a5eb89da90c25a42ef6</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T01:37:43.826160+00:00</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:26:23+00:00</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>Ziprecruiter</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>Ziprecruiter — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G179" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H179" s="3" t="inlineStr"/>
+      <c r="I179" s="3" t="inlineStr"/>
+      <c r="J179" s="3" t="inlineStr"/>
+      <c r="K179" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/ziprecruiter/jobs/8127108</t>
+        </is>
+      </c>
+      <c r="L179" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N179" s="3" t="inlineStr">
+        <is>
+          <t>@ job-boards.greenhouse.io C:
+&lt; Back to jobs
+Software Engineer -
+New Grad
+© Santa Monica, CA
+We offer a hybrid work environment. Most
+US-based positions can also be performed
+remotely (any exceptions will be noted in the
+Minimum Qualifications below.)
+(2) ZIP RECRUITER NEW GRAD SWE
+To actively connec their next great
+opportunity.
+Who We Are:
+ZipRecruiter is the fastest-growing onli
+employment marketplace for both desk —
+and mobile traffic. Powered by Al-driven
+https://scontent-atl3-1.cdninstagram.com/v/t51.71878-15/824596092_1613595780486530_6605253838494115175_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MzU4NDQ0MjMxMjQ2OTIzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=utHJS-VLKjcQ7kNvwGEbQHJ&amp;_nc_oc=AdoQ6y_2FaYlLcyQ4kK8U9FxIPAUx-o8CI6SVeZSrwUVt7asvqwJo0J_HZVGU8rgnVw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_gid=YmeEk6d89TUVk09YjtsUeg&amp;_nc_ss=7e3ba&amp;oh=00_AQJumxHfWgF2G7YF2TbAjuBlKGKuSIt5z2PAVSrWpXhEvA&amp;oe=6ABBBB6A
+https://scontent-atl3-1.cdninstagram.com/v/t51.71878-15/824596092_1613595780486530_6605253838494115175_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MzU4NDQ0MjMxMjQ2OTIzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=utHJS-VLKjcQ7kNvwGEbQHJ&amp;_nc_oc=AdoQ6y_2FaYlLcyQ4kK8U9FxIPAUx-o8CI6SVeZSrwUVt7asvqwJo0J_HZVGU8rgnVw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_gid=YmeEk6d89TUVk09YjtsUeg&amp;_nc_ss=7e3ba&amp;oh=00_AQJLuBVoJlApSnF1Q1B8fvNRMgPsEG4wChnnonq5EgMJPw&amp;oe=6ABBBB6A
+https://scontent-atl3-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHvkmAd&amp;_nc_oc=AdriCIokFaRj7V5yZ_bglFa8ayVBw2MbKEzbbSZuIxlXEq6ygicYgSOaFddhh0hwCJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQI-XhE2q_sVW-ToSKarkhW0NvAZdMrbDALBaz8flCzYjg&amp;oe=6ABBAB19
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fziprecruiter%2Fjobs%2F8127108%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafTmh4_6HH7AcjmKCDE6KnKrIOZoEg9Vxk_9PStTr--8JYsRLHKRahk4A-0rg_aem_WBN3WDCKpmxyicuTdbFHkw&amp;e=AUC0G0ViRwvsIhq7shKQXEa2oe0GBJ_xxOuVaPTCzJLiGNUtLkbR3D87LaSlWhWeOZnFa1l_dCgmq9rN-tE9KmPArsO0E2J_whSjqvIT7g
+https://scontent-atl3-1.cdninstagram.com/o1/v/t2/f2/m78/AQOHun8MAeFsm_w8J4eHGjzweahnKQS_F4yOthXFQAsVWQSamw02BQRj2Exl19fTLAarB5V59DRG5Wj2WxBiVdj23fX7a3vfFY0m7M8.mp4?_nc_cat=107&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ohc=34To4MeDZOAQ7kNvwGqLOY1&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgyNDMxNjk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=b4e21795176a9dde&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0EzNEQ5QjBCNEJEQzYwQUI4QUUyQTkzNjZEQzQyQkE4X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk2erLqcqhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=YmeEk6d89TUVk09YjtsUeg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKs5wa3l0H3dBQ70VBsI4WepRIu1eCdzKGbStyoVRhxLQ&amp;oe=6AB7C130</t>
+        </is>
+      </c>
+      <c r="O179" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P179" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q179" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R179" s="3" t="inlineStr"/>
+    </row>
+    <row r="180" ht="45" customHeight="1">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>62b03babf0905ea52cc4</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T01:37:45.213426+00:00</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:36:24+00:00</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G180" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H180" s="3" t="inlineStr">
+        <is>
+          <t>Winter 2027</t>
+        </is>
+      </c>
+      <c r="I180" s="3" t="inlineStr">
+        <is>
+          <t>San Francisco, New York</t>
+        </is>
+      </c>
+      <c r="J180" s="3" t="inlineStr"/>
+      <c r="K180" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7?source=zero2sudo</t>
+        </is>
+      </c>
+      <c r="L180" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N180" s="3" t="inlineStr">
+        <is>
+          <t>@ jobs.ashbyhg.com CG:
+: [N) Notion
+Software Engineer Intern, Mobile
+(Winter 2027)
+Location
+San Francisco, California; New York, New
+York
+Employment Type
+Intern
+. 2 JOBS.ASHBYHO.COM
+Department
+Early Career
+https://scontent-atl3-1.cdninstagram.com/v/t51.71878-15/817679086_1643182407467634_4831393841502179161_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MzU4OTQ4NzU3MzYwMTI4Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=bLxMaHDHw9UQ7kNvwH4kqye&amp;_nc_oc=AdqTpF40o8QjubJOlOXkiys4vt5a2orJF3-xzGGe6MfKC8vyHDdrtEbPu-_oSHnwM8s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_gid=YmeEk6d89TUVk09YjtsUeg&amp;_nc_ss=7e3ba&amp;oh=00_AQKJIe9C8hzkd8Ym0Gipr_aUFY9CA0On8QDIHreUuyMeVw&amp;oe=6ABB9C07
+https://scontent-atl3-1.cdninstagram.com/v/t51.71878-15/817679086_1643182407467634_4831393841502179161_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5MzU4OTQ4NzU3MzYwMTI4Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=bLxMaHDHw9UQ7kNvwH4kqye&amp;_nc_oc=AdqTpF40o8QjubJOlOXkiys4vt5a2orJF3-xzGGe6MfKC8vyHDdrtEbPu-_oSHnwM8s&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_gid=YmeEk6d89TUVk09YjtsUeg&amp;_nc_ss=7e3ba&amp;oh=00_AQIwD6YJFUkXAg9zQaDYPJMN-2mbKUGeeUFnyWcZssTJtA&amp;oe=6ABB9C07
+https://scontent-atl3-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHvkmAd&amp;_nc_oc=AdriCIokFaRj7V5yZ_bglFa8ayVBw2MbKEzbbSZuIxlXEq6ygicYgSOaFddhh0hwCJw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQI-XhE2q_sVW-ToSKarkhW0NvAZdMrbDALBaz8flCzYjg&amp;oe=6ABBAB19
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.ashbyhq.com%2Fnotion%2F2b587e66-deac-421a-a824-9415ba78b5a7%3Fsource%3Dzero2sudo%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafnukkFMrb857qYG2fZUprBVoMJTlsdsOvAO7gwIrScGwzkJzFOZugR-YkKKg_aem_Dtb5PDFKXCsjnNWVT8g7NA&amp;e=AUD1_456yrW6Yhwl0lwvJKUpAeeweAGpg_nINiFzr0BkWR9gP3ZwjY6dBdCE-O6D2kGeUAyTD_EA9RIqkfxNPRMm7FvPwB9fIFzbaIjHCQ
+https://scontent-atl3-2.cdninstagram.com/o1/v/t2/f2/m78/AQOiPItmFvaWB2QrLePL0fXG4WJEzneln0Pd7QiHfTmgFLUUo538MKKHS58l14fCsy39AiMKcQ7gDUTFJPsdBr9Vj-jT60xzsQP_qLU.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_ohc=YFq1LKpG7sIQ7kNvwElPP2_&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgyNDM5NzY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=ca0644e15d8c7b3e&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0VDNEYzRjU5MDM5MDZFMDQzOEI2REVGQkY1RkVGMDg5X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkuLnNr8qhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=YmeEk6d89TUVk09YjtsUeg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQK0jKYmYpo_hazvvw8CTG6KC5gt95-lAtC3CRosO5RFug&amp;oe=6AB7BDE4</t>
+        </is>
+      </c>
+      <c r="O180" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P180" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q180" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R180" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R177"/>
+  <autoFilter ref="A1:R180"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -17681,6 +17972,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L176" r:id="rId335"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K177" r:id="rId336"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K178" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K179" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K180" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId343"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$185</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R180"/>
+  <dimension ref="A1:R185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17344,7 +17344,7 @@
     <row r="178" ht="45" customHeight="1">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>86b3676ac0b8b8702ae1</t>
+          <t>761757f28b56129ee7e1</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -17372,7 +17372,7 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G178" s="3" t="inlineStr"/>
+      <c r="G178" s="3" t="n"/>
       <c r="H178" s="3" t="inlineStr">
         <is>
           <t>2027</t>
@@ -17383,7 +17383,7 @@
           <t>Austin</t>
         </is>
       </c>
-      <c r="J178" s="3" t="inlineStr"/>
+      <c r="J178" s="3" t="n"/>
       <c r="K178" s="4" t="inlineStr">
         <is>
           <t>https://careers.amd.com/careers-home/jobs/92880?lang=en-us&amp;iis=Job+Board&amp;iisn=zero2sudo</t>
@@ -17434,12 +17434,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R178" s="3" t="inlineStr"/>
+      <c r="R178" s="3" t="n"/>
     </row>
     <row r="179" ht="45" customHeight="1">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>1a5eb89da90c25a42ef6</t>
+          <t>f441b35881a41f626463</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -17472,9 +17472,9 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H179" s="3" t="inlineStr"/>
-      <c r="I179" s="3" t="inlineStr"/>
-      <c r="J179" s="3" t="inlineStr"/>
+      <c r="H179" s="3" t="n"/>
+      <c r="I179" s="3" t="n"/>
+      <c r="J179" s="3" t="n"/>
       <c r="K179" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/ziprecruiter/jobs/8127108</t>
@@ -17530,12 +17530,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R179" s="3" t="inlineStr"/>
+      <c r="R179" s="3" t="n"/>
     </row>
     <row r="180" ht="45" customHeight="1">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>62b03babf0905ea52cc4</t>
+          <t>8ba6544eab1ef0c5bb78</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -17578,7 +17578,7 @@
           <t>San Francisco, New York</t>
         </is>
       </c>
-      <c r="J180" s="3" t="inlineStr"/>
+      <c r="J180" s="3" t="n"/>
       <c r="K180" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7?source=zero2sudo</t>
@@ -17630,10 +17630,527 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R180" s="3" t="inlineStr"/>
+      <c r="R180" s="3" t="n"/>
+    </row>
+    <row r="181" ht="45" customHeight="1">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>92f5320de73489c9d4b0</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T07:57:40.800686+00:00</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G181" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H181" s="3" t="inlineStr">
+        <is>
+          <t>Spring 2027</t>
+        </is>
+      </c>
+      <c r="I181" s="3" t="inlineStr">
+        <is>
+          <t>Bellevue, Menlo Park</t>
+        </is>
+      </c>
+      <c r="J181" s="3" t="inlineStr"/>
+      <c r="K181" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/snowflake/4be290ae-dd9d-488c-9d90-56fcd69101ca/application?jr_id=6ab5cf5f634ec6aa7c0d1431</t>
+        </is>
+      </c>
+      <c r="L181" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N181" s="3" t="inlineStr">
+        <is>
+          <t>@ jobs.ashbyhg.com &amp;
+wb
+26 snowflake
+SOFTWARE ENGINEER
+INTERN (Al / ML) -
+SPRING 2027
+LOCATION
+US-CA-Menlo Park; US-WA-Bellevue
+EMPLOYMENT TYPE
+Full time
+@ JOBS.ASHBYHQ.COM
+COMPENSATION
+$42 - $60 per hour
+Overview Application
+https://scontent-nrt1-2.cdninstagram.com/v/t51.71878-15/820553363_2052491898729953_6177754525704524759_n.jpg?stp=dst-jpg_e15_p480x480_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5MzY2NzY0MzUzODk2MzQwNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMyIn0%3D&amp;_nc_ohc=qh4KwQ4DcJoQ7kNvwHI9VCl&amp;_nc_oc=Ado4OA6_jRWrLYmL7Sw8SG09xjOMLuUa9DnK6Cv800KwUFGcOrTFEsP5jS-0g_JOBu4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=cWy4JLJFbR1_uL__ejxAZw&amp;_nc_ss=7e3ba&amp;oh=00_AQI-atGyMiHKiNuvzhikyh1-DO2dUmpEc4DsecgDinsSow&amp;oe=6ABBEBD4
+https://scontent-nrt1-2.cdninstagram.com/v/t51.71878-15/820553363_2052491898729953_6177754525704524759_n.jpg?stp=dst-jpg_e15_p150x150_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5MzY2NzY0MzUzODk2MzQwNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMyIn0%3D&amp;_nc_ohc=qh4KwQ4DcJoQ7kNvwHI9VCl&amp;_nc_oc=Ado4OA6_jRWrLYmL7Sw8SG09xjOMLuUa9DnK6Cv800KwUFGcOrTFEsP5jS-0g_JOBu4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=cWy4JLJFbR1_uL__ejxAZw&amp;_nc_ss=7e3ba&amp;oh=00_AQIGiB8EytzCxZ1qchVlNdAsErMQNuCGZ99X4vMl7ZLpsg&amp;oe=6ABBEBD4
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMyIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwFGExly&amp;_nc_oc=Adq68KULLxb7pBh685S_BG6MCdy3Cg-xT5088690c0pZE-or68SimJlbB3Uf777P2T8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIKQD_Rx2KbZfuC1S9exdFYsnTwWE8zSSjdKJaxcWGuIA&amp;oe=6ABBE359
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.ashbyhq.com%2Fsnowflake%2F4be290ae-dd9d-488c-9d90-56fcd69101ca%2Fapplication%3Fjr_id%3D6ab5cf5f634ec6aa7c0d1431%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAae7-7DdYwOL7GnHpMS6wuUr7l50c5cTGWhB0ZgQS9_jGW0KSIxuH8eufiD3uQ_aem_a1ndjuRH-6fttMvbb29z2Q&amp;e=AUCE02lEykgBQqn9_5_VuIQ2fU1OcMAYjoLIRPfN2PMR0ySfgehOF-YNMBQWPx_bSSbylJAMTi-y1ptAVXzqeNBwT5TmSBdpQttW5HapIA
+https://scontent-nrt1-1.cdninstagram.com/o1/v/t2/f2/m78/AQOSo-I5SJgVtjzQMTdNMhS6mGEw4a2POE2KAELnR5Erf-1JNJznVWTRkrbLxeAYm3qXXsUCJxJZCIWZVoDjGJibqp4wsnVIJDBvh80.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_ohc=p87USo3Ep14Q7kNvwEQZOFl&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzIuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgyNTc4MjE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=3319250f00a28985&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0YxNDM5NDg1OEI5RUUyOUQ2QTI1Njk2OTQyMjNFOUJBX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk9YjhlsuhQBUCKAJDMiwXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=cWy4JLJFbR1_uL__ejxAZw&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIwh3k_JlguoCc70OkIVR_MDXHX2iIgfq6aZltG02CxIw&amp;oe=6AB8000A</t>
+        </is>
+      </c>
+      <c r="O181" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P181" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q181" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R181" s="3" t="inlineStr"/>
+    </row>
+    <row r="182" ht="45" customHeight="1">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>7575b9ddb065854bcffa</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T07:57:42.179803+00:00</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:15:48+00:00</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H182" s="3" t="inlineStr">
+        <is>
+          <t>Spring 2027</t>
+        </is>
+      </c>
+      <c r="I182" s="3" t="inlineStr">
+        <is>
+          <t>Bellevue, Menlo Park</t>
+        </is>
+      </c>
+      <c r="J182" s="3" t="inlineStr"/>
+      <c r="K182" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/snowflake/5315b6f6-2c14-4cb9-a884-c2bae69f2c69</t>
+        </is>
+      </c>
+      <c r="L182" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N182" s="3" t="inlineStr">
+        <is>
+          <t>@ jobs.ashbyhq.com G
+&gt;
+L
+iS snowflake
+SOFTWARE ENGINEER
+INTERN (CORE,
+INFRASTRUCTURE &amp;
+SECURITY) — SPRING
+2027
+LOCATION
+US-CA-Menlo Park; US-WA-Bellevue
+@ JOBS.ASHBYHQ.COM
+LOCATION TYPE
+On-site
+DEPARTMENT
+Engineering
+COMPENSATION
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/822919712_1769190164023386_40267410398846725_n.jpg?stp=dst-jpg_e15_p480x480_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MzY2OTcxNjc5MTY2NDk2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMyIn0%3D&amp;_nc_ohc=3U565C-o8CgQ7kNvwHi0FE-&amp;_nc_oc=AdrR_CExn417s6Pxz04o45MoYTMfeql8Q_lvUk72OQ7HUs4fEVFLz4ABCDTm8AQXkZc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=cWy4JLJFbR1_uL__ejxAZw&amp;_nc_ss=7e3ba&amp;oh=00_AQJYUEARn6gk93D7qdunuYMbez4Cl09lrecN91ETx2oVrw&amp;oe=6ABBE588
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/822919712_1769190164023386_40267410398846725_n.jpg?stp=dst-jpg_e15_p150x150_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5MzY2OTcxNjc5MTY2NDk2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMyIn0%3D&amp;_nc_ohc=3U565C-o8CgQ7kNvwHi0FE-&amp;_nc_oc=AdrR_CExn417s6Pxz04o45MoYTMfeql8Q_lvUk72OQ7HUs4fEVFLz4ABCDTm8AQXkZc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=cWy4JLJFbR1_uL__ejxAZw&amp;_nc_ss=7e3ba&amp;oh=00_AQIL15q5BIxhz23BaxVgE7pS7WY5ulmJXuaM4OiNs9OzRw&amp;oe=6ABBE588
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMyIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwFGExly&amp;_nc_oc=Adq68KULLxb7pBh685S_BG6MCdy3Cg-xT5088690c0pZE-or68SimJlbB3Uf777P2T8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIKQD_Rx2KbZfuC1S9exdFYsnTwWE8zSSjdKJaxcWGuIA&amp;oe=6ABBE359
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.ashbyhq.com%2Fsnowflake%2F5315b6f6-2c14-4cb9-a884-c2bae69f2c69%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadD5mmbfLAsT8y-KihjmvejzEOacfN4p6GlqS1r330iVwD4vH2b-sdUPL6vPA_aem_dwFE-Th0zv86MPm3pfzZAg&amp;e=AUAqWaduVRlSVV7IFSJCMl3S3sjMS6iTwcXoiKmvExWqKi3Wxg1pqnyOunFmCDMj9LTkVoFg84rH2xey5cMOhXD-s8REQT4SVLA9pDwsDg
+https://scontent-nrt1-2.cdninstagram.com/o1/v/t2/f2/m78/AQNnLKMvpptX-wx9V6x_EfarZFxPp3v5gIdXDu0MKn4UDqAuIzI0qpwY4lbqUerssufbw4SnoibZFbZGHRk2LzUdagMrh0OnYEqCkCk.mp4?_nc_cat=107&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_ohc=5k-IP1AlAYYQ7kNvwH5kgg1&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzIuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgyNTgzNDk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=36bf9f8c6c096bbd&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzEwNDM0NkZDQUE1OTc1Nzk3RTg5QzNBNTVBNDVERUIxX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkhc7YmsuhQBUCKAJDMiwXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=cWy4JLJFbR1_uL__ejxAZw&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJR90lg29VpNR_A1OvziDAH5Q3GP6RpL16GN9pnMW8_-w&amp;oe=6AB81DDC</t>
+        </is>
+      </c>
+      <c r="O182" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P182" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q182" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R182" s="3" t="inlineStr"/>
+    </row>
+    <row r="183" ht="45" customHeight="1">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>de59c7c5d66d47f54502</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T07:57:43.539372+00:00</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:16:31+00:00</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G183" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H183" s="3" t="inlineStr">
+        <is>
+          <t>Spring 2027</t>
+        </is>
+      </c>
+      <c r="I183" s="3" t="inlineStr">
+        <is>
+          <t>Bellevue, Menlo Park</t>
+        </is>
+      </c>
+      <c r="J183" s="3" t="inlineStr"/>
+      <c r="K183" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/snowflake/7bd393df-67d7-4009-ba4f-1cd79a82b0be</t>
+        </is>
+      </c>
+      <c r="L183" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N183" s="3" t="inlineStr">
+        <is>
+          <t>@ jobs.ashbyhq.com C:
+&gt;
+L :
+XS snowflake
+SOFTWARE ENGINEER
+INTERN (DATABASE
+ENGINEERING) -
+SPRING 2027
+LOCATION
+US-CA-Menlo Park; US-WA-Bellevue
+@ JOBS.ASHBYHQ.COM
+DEPARTMENT
+Engineering
+COMPENSATION
+$42 - $60 per hour
+Overview Application
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/823153284_1595120888752141_2524554844785480635_n.jpg?stp=dst-jpg_e15_p480x480_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MzY3MDA4MjI5OTcwNTEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMyIn0%3D&amp;_nc_ohc=x-yHaxFhiHsQ7kNvwH8HEDO&amp;_nc_oc=Adoei64ThQg7WREw9WuxSarFrirpi9drg6c8dBCCJqOHg-Y4mW4eR4-OuedzyEJrXrE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=cWy4JLJFbR1_uL__ejxAZw&amp;_nc_ss=7e3ba&amp;oh=00_AQIVnda-iBzrWbDFmNZ6unCoDsTy-P_X-g6GCKuiQoDiEw&amp;oe=6ABBEBEE
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/823153284_1595120888752141_2524554844785480635_n.jpg?stp=dst-jpg_e15_p150x150_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5MzY3MDA4MjI5OTcwNTEwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMyIn0%3D&amp;_nc_ohc=x-yHaxFhiHsQ7kNvwH8HEDO&amp;_nc_oc=Adoei64ThQg7WREw9WuxSarFrirpi9drg6c8dBCCJqOHg-Y4mW4eR4-OuedzyEJrXrE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=cWy4JLJFbR1_uL__ejxAZw&amp;_nc_ss=7e3ba&amp;oh=00_AQI4-LgAvblb7YN4Kq32rFYlxONf9nuGpRFKGYtBAI28cg&amp;oe=6ABBEBEE
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMyIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwFGExly&amp;_nc_oc=Adq68KULLxb7pBh685S_BG6MCdy3Cg-xT5088690c0pZE-or68SimJlbB3Uf777P2T8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIKQD_Rx2KbZfuC1S9exdFYsnTwWE8zSSjdKJaxcWGuIA&amp;oe=6ABBE359
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.ashbyhq.com%2Fsnowflake%2F7bd393df-67d7-4009-ba4f-1cd79a82b0be%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadK7tFOdogt2LQrL5ZJFo8Mc53oJUuGU9EhKU-5t4ZtYb8GSQeIw8lbk7IxeQ_aem_NeVQv2nIYlR8jwL6EYOFHw&amp;e=AUBPhofjOGOkTwlVWeGMuL1HLVQ1arYty4nz4PQ1LsKNefQ1R-iZB998Rt8MKO2XDy1u2JFsRzRi2RhnVnpJVsO3oC7vqJoqJwQAohHMTA
+https://scontent-nrt1-1.cdninstagram.com/o1/v/t2/f2/m78/AQPdptvlltCreBHeFsWsM4O_SDLtLzF3Agdfonv8jVaYDspunISwSK_8qWhu3ABOpX7_0zZ4wT4E69YDsiuWRnM2QuIW-3mzDqntE00.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_ohc=efe2qF-VStwQ7kNvwFqWWRj&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzIuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgyNTg0Nzg2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=3064085ac9171486&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0U5NDNGREJCMjAwRTRCNkI0NzEzMTRFODkzQzk2REFCX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkjtHTm8uhQBUCKAJDMiwXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=cWy4JLJFbR1_uL__ejxAZw&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLqp4FwKGVGu-NxgUF2RVxa7QhJVtvD3mSI1dCWNTpE-A&amp;oe=6AB804A4</t>
+        </is>
+      </c>
+      <c r="O183" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P183" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q183" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R183" s="3" t="inlineStr"/>
+    </row>
+    <row r="184" ht="45" customHeight="1">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>538755ae0d7310221aff</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T07:57:46.423998+00:00</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:40:10+00:00</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>Astranis</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>Astranis — Internship</t>
+        </is>
+      </c>
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G184" s="3" t="inlineStr"/>
+      <c r="H184" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I184" s="3" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="J184" s="3" t="inlineStr"/>
+      <c r="K184" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/astranis/jobs/4708369006?gh_src=602966e76us</t>
+        </is>
+      </c>
+      <c r="L184" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
+          <t>@ job-boards.greenhouse.io
+Instagram
+{New ]
+Technical Project
+Management Intern
+(Summer 2027)
+© San Francisco
+Astranis builds advar~ ‘ites for high
+orbits, expanding hur, 2ach into the
+solar system. Today Asi. satellites provide
+dedicated, secure networks to highly-
+sophisticated customers across the globe —
+large enterprises, sovereign governments, and
+the US military.
+With five satellites on orbit and many more set
+to launch soon, the company is servicing
+backlog of more than $1 billion of comme
+contracts. Astranis is the preferred satelli
+rcammunicatinne nartnar far hinsare with
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/820279973_1410378760502251_2034870063073206526_n.jpg?stp=dst-jpg_e15_p480x480_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MzY4MTk3OTM4MzgzNTg4Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMyIn0%3D&amp;_nc_ohc=iYwqEv42diMQ7kNvwF_I-0W&amp;_nc_oc=Adqh7PrAzm4v3SPLK5FAoXljdrxmgd3QCDh6N2EILhAVwEuaiMhcJl0GPQAkf1941T0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=cWy4JLJFbR1_uL__ejxAZw&amp;_nc_ss=7e3ba&amp;oh=00_AQIZ0A7c3DtSJ9BbCmlw9GfiT0MHBKJqkH9sbNyIjYoz-A&amp;oe=6ABC0264
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/820279973_1410378760502251_2034870063073206526_n.jpg?stp=dst-jpg_e15_p150x150_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5MzY4MTk3OTM4MzgzNTg4Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMyIn0%3D&amp;_nc_ohc=iYwqEv42diMQ7kNvwF_I-0W&amp;_nc_oc=Adqh7PrAzm4v3SPLK5FAoXljdrxmgd3QCDh6N2EILhAVwEuaiMhcJl0GPQAkf1941T0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=cWy4JLJFbR1_uL__ejxAZw&amp;_nc_ss=7e3ba&amp;oh=00_AQIsqq1DZvnrrSnpT37gN6XehW6vrXhOsZMdn4-FK5R1lQ&amp;oe=6ABC0264
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMyIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwFGExly&amp;_nc_oc=Adq68KULLxb7pBh685S_BG6MCdy3Cg-xT5088690c0pZE-or68SimJlbB3Uf777P2T8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIKQD_Rx2KbZfuC1S9exdFYsnTwWE8zSSjdKJaxcWGuIA&amp;oe=6ABBE359
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fastranis%2Fjobs%2F4708369006%3Fgh_src%3D602966e76us%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaf5583nu6Li55nuMazFvsV7XlT9bzi9-cpxPW1lBSeHXSwxZhLSGsQNDG63hA_aem_kvOo4MaVfSgLBEFSFZW3rQ&amp;e=AUCHA5O7x7xPw7QeDRz-09q3yNnphX_-WxIYblj0ReLTYb_bioAAySKJtF3gFfQyTVEzxsxl64lQE3BDwB1Wj2GmwXZqoUwZhD4pyCYdPw
+https://scontent-nrt6-1.cdninstagram.com/o1/v/t2/f2/m78/AQNzEM_q-bWMSvsQ8kbkGOFtvk9hmyu6Jf5qxku6zHWhFPzvNbp6cljtzXfm5T22l9VB9OAF_pW89bl08-WrgB76u7-HAhiQ2xm_M_o.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ohc=-E8nsLq_GzQQ7kNvwGAzzbk&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzIuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgyNjA4NTc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=788c527fec46dcec&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0UzNDI4QTNFRDMxRkQ5QUUyRTUyOEFCNTdGMjQ1OTgxX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbksbawrcuhQBUCKAJDMiwXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=cWy4JLJFbR1_uL__ejxAZw&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJ349-QanJ_c6RG40mLRA38beYpX0b8Bx_TgtpyVPERJw&amp;oe=6AB8062C</t>
+        </is>
+      </c>
+      <c r="O184" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P184" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q184" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R184" s="3" t="inlineStr"/>
+    </row>
+    <row r="185" ht="45" customHeight="1">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>91f5f5694f23895f1295</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T07:57:48.972669+00:00</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:50:07+00:00</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>Smartrecruiters</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>Smartrecruiters — Internship</t>
+        </is>
+      </c>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="inlineStr"/>
+      <c r="H185" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I185" s="3" t="inlineStr"/>
+      <c r="J185" s="3" t="inlineStr"/>
+      <c r="K185" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/WabashValleyPowerAlliance/744000149889459-power-supply-energy-services-internship-summer-2027</t>
+        </is>
+      </c>
+      <c r="L185" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
+          <t>@ jobs.smartrecruiters.com C:
+Wabash Valley
+POWER ALLIANCE
+Power Supply &amp; Energy Services
+Internship - Summer 2027
+6702 Intech Blvd, Indianapolis, IN 46278, USA
+Intern
+I'm interested
+Company Description
+Headquartered in Indianapolis, Indiana, Wabash Valley
+Power is a not-for-profit electric cooperative and
+wholesale provider of reliable, affordable electricity to
+2 POWER TRADING INTERN
+As a not-for-profit co-op, a bit differently—
+and that's the point. Beca 't influenced by
+shareholders, we make our with our members
+in mind. That means we value things like teamwork, and
+putting families first. It also means a business model
+that's designed for stability and growth. It's a Deliberately
+Different approach to the energy industry, and that's
+great news for the people who count on us.
+Job Description
+~~ tat ~
+https://scontent-nrt1-2.cdninstagram.com/v/t51.71878-15/815920234_1096147379779207_1806892819269649646_n.jpg?stp=dst-jpg_e15_p480x480_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MzY4Njk5MDE4NDY3OTc5MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMyIn0%3D&amp;_nc_ohc=FSK-4MIJ4roQ7kNvwGfRrju&amp;_nc_oc=Adrd2ySKbKQs0B67754Dn8YrSktlr6173kBHLVmgI0mq-nSB1WzyPQRP83OeTDso3fg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=cWy4JLJFbR1_uL__ejxAZw&amp;_nc_ss=7e3ba&amp;oh=00_AQJcl2QTYsz4JP92fARId4dsAZ2YwpP1vx6mAmIjgNSFvw&amp;oe=6ABBE044
+https://scontent-nrt1-2.cdninstagram.com/v/t51.71878-15/815920234_1096147379779207_1806892819269649646_n.jpg?stp=dst-jpg_e15_p150x150_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5MzY4Njk5MDE4NDY3OTc5MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMyIn0%3D&amp;_nc_ohc=FSK-4MIJ4roQ7kNvwGfRrju&amp;_nc_oc=Adrd2ySKbKQs0B67754Dn8YrSktlr6173kBHLVmgI0mq-nSB1WzyPQRP83OeTDso3fg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-2.cdninstagram.com&amp;_nc_gid=cWy4JLJFbR1_uL__ejxAZw&amp;_nc_ss=7e3ba&amp;oh=00_AQL7u3Q3sy2im2OOL-w0yI8VnVqTZIjZ3ynekGtgyZBU0Q&amp;oe=6ABBE044
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMyIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwFGExly&amp;_nc_oc=Adq68KULLxb7pBh685S_BG6MCdy3Cg-xT5088690c0pZE-or68SimJlbB3Uf777P2T8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIKQD_Rx2KbZfuC1S9exdFYsnTwWE8zSSjdKJaxcWGuIA&amp;oe=6ABBE359
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.smartrecruiters.com%2FWabashValleyPowerAlliance%2F744000149889459-power-supply-energy-services-internship-summer-2027%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafQNoArQwOD-4dfFnzh7VcaBay8QZTYdYrLlA0m18gcfH_qG0mp3Hs3Dg5B5g_aem_k1Pc7Z_V3GvjCoW1DSJg6A&amp;e=AUDPn-_tJ9HCwZAoKYGjoy2Xl1ObJwP90UlL9tqFjGR4KXE9mATQQComN-sciyW1dcm59B5p8TBpLwVhEnwkTfJeyrGTG7XxeX9daUOz0A
+https://scontent-nrt1-1.cdninstagram.com/o1/v/t2/f2/m78/AQNbjS7aL1eOvhWqWCYnejbxoVpzNcNNcXnkU7htxPAUBFbTlgtvUCr8txKHjFgZ-hT8LZx6KbxJAeEeX33uzs-_FY5EpffJs_nl22I.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_ohc=kmbNMtMCh6kQ7kNvwEjlTaK&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzIuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgyNjE3OTY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=1acbae2f703a424a&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzRGNDdDNjY4MTI4RDQ1NDREQzI5MTFGQjZCNjYzQjhCX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbktPavtMuhQBUCKAJDMiwXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=cWy4JLJFbR1_uL__ejxAZw&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJGSBgrgF_EAyaa6lv1g8XwAkTBC4XjQsfWVkuJ4Y1YQA&amp;oe=6AB81064</t>
+        </is>
+      </c>
+      <c r="O185" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P185" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q185" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R185" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R180"/>
+  <autoFilter ref="A1:R185"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -17978,6 +18495,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="rId341"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K180" r:id="rId342"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K181" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K182" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K183" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K184" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K185" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L185" r:id="rId353"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -17635,7 +17635,7 @@
     <row r="181" ht="45" customHeight="1">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>92f5320de73489c9d4b0</t>
+          <t>c898beea86d97501ceee</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -17678,7 +17678,7 @@
           <t>Bellevue, Menlo Park</t>
         </is>
       </c>
-      <c r="J181" s="3" t="inlineStr"/>
+      <c r="J181" s="3" t="n"/>
       <c r="K181" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/snowflake/4be290ae-dd9d-488c-9d90-56fcd69101ca/application?jr_id=6ab5cf5f634ec6aa7c0d1431</t>
@@ -17732,12 +17732,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R181" s="3" t="inlineStr"/>
+      <c r="R181" s="3" t="n"/>
     </row>
     <row r="182" ht="45" customHeight="1">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>7575b9ddb065854bcffa</t>
+          <t>13954ba494f265048eb6</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -17780,7 +17780,7 @@
           <t>Bellevue, Menlo Park</t>
         </is>
       </c>
-      <c r="J182" s="3" t="inlineStr"/>
+      <c r="J182" s="3" t="n"/>
       <c r="K182" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/snowflake/5315b6f6-2c14-4cb9-a884-c2bae69f2c69</t>
@@ -17837,12 +17837,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R182" s="3" t="inlineStr"/>
+      <c r="R182" s="3" t="n"/>
     </row>
     <row r="183" ht="45" customHeight="1">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>de59c7c5d66d47f54502</t>
+          <t>0eeb5b829665df8c6782</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -17885,7 +17885,7 @@
           <t>Bellevue, Menlo Park</t>
         </is>
       </c>
-      <c r="J183" s="3" t="inlineStr"/>
+      <c r="J183" s="3" t="n"/>
       <c r="K183" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/snowflake/7bd393df-67d7-4009-ba4f-1cd79a82b0be</t>
@@ -17941,12 +17941,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R183" s="3" t="inlineStr"/>
+      <c r="R183" s="3" t="n"/>
     </row>
     <row r="184" ht="45" customHeight="1">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>538755ae0d7310221aff</t>
+          <t>e3b8146aee49d1bce47c</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -17974,7 +17974,7 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G184" s="3" t="inlineStr"/>
+      <c r="G184" s="3" t="n"/>
       <c r="H184" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
@@ -17985,7 +17985,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="J184" s="3" t="inlineStr"/>
+      <c r="J184" s="3" t="n"/>
       <c r="K184" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/astranis/jobs/4708369006?gh_src=602966e76us</t>
@@ -18044,12 +18044,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R184" s="3" t="inlineStr"/>
+      <c r="R184" s="3" t="n"/>
     </row>
     <row r="185" ht="45" customHeight="1">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>91f5f5694f23895f1295</t>
+          <t>f5a58ebe99f5b8eb8bd1</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -18077,14 +18077,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G185" s="3" t="inlineStr"/>
+      <c r="G185" s="3" t="n"/>
       <c r="H185" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I185" s="3" t="inlineStr"/>
-      <c r="J185" s="3" t="inlineStr"/>
+      <c r="I185" s="3" t="n"/>
+      <c r="J185" s="3" t="n"/>
       <c r="K185" s="4" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/WabashValleyPowerAlliance/744000149889459-power-supply-energy-services-internship-summer-2027</t>
@@ -18147,7 +18147,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R185" s="3" t="inlineStr"/>
+      <c r="R185" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:R185"/>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$196</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R185"/>
+  <dimension ref="A1:R196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18149,8 +18149,1060 @@
       </c>
       <c r="R185" s="3" t="n"/>
     </row>
+    <row r="186" ht="45" customHeight="1">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>5e979738777941fe558d</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T22:27:29.875622+00:00</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T14:13:00+00:00</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>Statefarm</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>Statefarm — Internship</t>
+        </is>
+      </c>
+      <c r="F186" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="inlineStr"/>
+      <c r="H186" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I186" s="3" t="inlineStr"/>
+      <c r="J186" s="3" t="inlineStr"/>
+      <c r="K186" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.statefarm.com/main/jobs/45928?lang=en-us&amp;iis=zero2sudo&amp;iisn=zero2sudo</t>
+        </is>
+      </c>
+      <c r="L186" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
+          <t>@ jobs.statefarm.com C:
+Instagram :
+@ Back
+Summer 2027 Intern - Security Analyst
+- Ent Sec
+Location Bloomington, Illinois
+Job Category Intern
+Position Type Intern - Summer
+Req ID 45928
+.
+® JOBS.STATEFARM.COM
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/821699002_2336120166792144_9134940999147889753_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5NDAzMDY5MTQzNjE2OTQwNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=7YjKe_AS03kQ7kNvwGZQqoo&amp;_nc_oc=AdpKQdQTl4bulYCGvru5j7mz8WYBbJ3JLbi7EiQVbKHtpToVxZe8Q_g-lwi8-pfnVdI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;oh=00_AQIc65dwhfpkykAEHr0kNnsgNefgdMR_kK8C2L1HP-xPDw&amp;oe=6ABCD40B
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/821699002_2336120166792144_9134940999147889753_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5NDAzMDY5MTQzNjE2OTQwNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=7YjKe_AS03kQ7kNvwGZQqoo&amp;_nc_oc=AdpKQdQTl4bulYCGvru5j7mz8WYBbJ3JLbi7EiQVbKHtpToVxZe8Q_g-lwi8-pfnVdI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;oh=00_AQI7NJXJHzNs-eJWSMSqSw0Jux_tQb5WxKDCUz7EpWvdyQ&amp;oe=6ABCD40B
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHdpRXJ&amp;_nc_oc=AdrYY50kV6jR2Z3-4tvDVcgaZVfceHPnQ1Lat0VqYlkKxM_0jTpDPO80Sr2NioQ0rWI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKizT2WSacqva9y6qDwEG6OYGkLs0RdCboMZeal0hlvdA&amp;oe=6ABCC459
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.statefarm.com%2Fmain%2Fjobs%2F45928%3Flang%3Den-us%26iis%3Dzero2sudo%26iisn%3Dzero2sudo%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAac8BmYFNHdeMWCpixlR0lBJ6uRRWzva0RcSJt6p06Z0bk8l0tBFlFi7X2txAg_aem_xcWbbm0qOO1BmDQRT4Ouug&amp;e=AUDXVmOsNwrqntr0KDkukbHJoqj8q3TfleCV9PWtCoq2-rpc8_6E9ODvJC-GUrFilxXuEU1UctnpWWcs_01jCEzvyH6oUq_LWypNWhd7HA
+https://scontent-lax3-2.cdninstagram.com/o1/v/t2/f2/m78/AQNMfYHzx90_2kq6qvZ4Mluv0Af9oHk3h1FhVLetcAfaGghtSzthEmVic8IO6XlTPah3kZmJIsKu6yvIl3zjl27J9GrU3IIMzJ0gK0E.mp4?_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ohc=xjoO9COzeaAQ7kNvwEP_kWZ&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgzNDQzMzg2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=195103644c1e185c&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzE2NDEwMzFGRjVGRTk0MzIyNjEyRUMwMzUwMjQ1MzlDX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkko6um9ChQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLYjShIjLvPnFosTR08rbwKC-FCBTUnZm9E2xPI59is-g&amp;oe=6AB8DC0F</t>
+        </is>
+      </c>
+      <c r="O186" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P186" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q186" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R186" s="3" t="inlineStr"/>
+    </row>
+    <row r="187" ht="45" customHeight="1">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>11be6d9cd2b017665f26</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T22:27:34.534328+00:00</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T14:42:43+00:00</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>Google — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F187" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H187" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I187" s="3" t="inlineStr">
+        <is>
+          <t>Kirkland, Austin, Los Angeles, Sunnyvale</t>
+        </is>
+      </c>
+      <c r="J187" s="3" t="inlineStr"/>
+      <c r="K187" s="4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/about/careers/applications/jobs/results/84680705375642310-software-engineer-infrastructure-phd-early-career-2027-start</t>
+        </is>
+      </c>
+      <c r="L187" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N187" s="3">
+        <f> GoogleCareers i 33 ©
+€ Back to jobs search
+Software Engineer,
+Infrastructure, PhD, Early
+Career, 2027 Start
+EE] Google © Sunnyvale, CA, USA; +11 more
+7 =
+(2 GOOGLE INFRA PHD NEW GRAD
+a
+Qualified applic with arrest or
+conviction r considered for
+employment i e with the Los
+Angeles Count ce Ordinance
+for Employers and the California Fair
+Chance Act.Note: By applying to this
+® position you will have an opportunity to
+share your preferred working location
+from the following: Sunnyvale, CA, USA;
+Atlanta, GA, USA; Austin, TX, USA;
+Kirkland, WA, USA; Los Angeles, CA, USA;
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/825554805_1109277158177057_648391953722959520_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5NDA0NTY1NDAxOTcxOTczOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=FAzW_9z3M9QQ7kNvwHJ8hUk&amp;_nc_oc=AdqzzP2QebSnDdHuAGVVrtFoG2DXCQ5kGBZ_VDJHvD9ocMylmhFGF3GybNfgVrnwtB4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;oh=00_AQLt8cJNG3kNUYncOYXhDUNOe5qyIkEEX80w68zkZE9-aQ&amp;oe=6ABCDC27
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/825554805_1109277158177057_648391953722959520_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5NDA0NTY1NDAxOTcxOTczOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=FAzW_9z3M9QQ7kNvwHJ8hUk&amp;_nc_oc=AdqzzP2QebSnDdHuAGVVrtFoG2DXCQ5kGBZ_VDJHvD9ocMylmhFGF3GybNfgVrnwtB4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;oh=00_AQJWpKqZm7noouXHqwHZ7GNT2KaWm0RW_yln4sg3iuhhsg&amp;oe=6ABCDC27
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHdpRXJ&amp;_nc_oc=AdrYY50kV6jR2Z3-4tvDVcgaZVfceHPnQ1Lat0VqYlkKxM_0jTpDPO80Sr2NioQ0rWI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKizT2WSacqva9y6qDwEG6OYGkLs0RdCboMZeal0hlvdA&amp;oe=6ABCC459
+https://l.instagram.com/?u=https%3A%2F%2Fwww.google.com%2Fabout%2Fcareers%2Fapplications%2Fjobs%2Fresults%2F84680705375642310-software-engineer-infrastructure-phd-early-career-2027-start%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafEHe99vARFf6jrVNiNSnKEVl_bRZ7abphVEZUoBUihrChtp3mK8uEG8_mQeA_aem_V9x41ligotQun48Ar6VRrw&amp;e=AUCaEx2SPRC1Bn0zQw0hV6MHWdKovZfo33wusfb4T9-9Hg79dNyX79odcjq7uiEtEIzmyEVy5VjdPomc4hteE5Qukj0I3KB8pEVGQsjJFw
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQMugUamUjas4WSXCIXPVVROWZBRhbylkYjQ4b9J0M1FZGOZArKgDt8mILK6iKpq9ETdvqrm48ZMbn70BpoYAnUvWniO65QBLDTuLsI.mp4?_nc_cat=102&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=nGCak3JEDYQQ7kNvwGYwmpl&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgzNDc5NDc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=5494d1a1482259c4&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzJDNDYwNTk2QUMzMkU3QkE0QjdDREI3MjM3NjY2NTk5X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk8_WfttChQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQI_ziZ1QxZRD5orevLekRzQWvf8XpVw8RA31GxuMOKJQg&amp;oe=6AB8D1E7</f>
+        <v/>
+      </c>
+      <c r="O187" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P187" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q187" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R187" s="3" t="inlineStr"/>
+    </row>
+    <row r="188" ht="45" customHeight="1">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>9e9382601db71bacdbb8</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T22:27:36.539937+00:00</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T14:44:42+00:00</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>Google — Software Engineering, Machine Learning / AI</t>
+        </is>
+      </c>
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering, Machine Learning / AI</t>
+        </is>
+      </c>
+      <c r="H188" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I188" s="3" t="inlineStr">
+        <is>
+          <t>Sunnyvale</t>
+        </is>
+      </c>
+      <c r="J188" s="3" t="inlineStr"/>
+      <c r="K188" s="4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/about/careers/applications/jobs/results/123087196289671878-software-engineer-aimachine-learning-phd-early-career-2027-start</t>
+        </is>
+      </c>
+      <c r="L188" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
+          <t>Google Careers ees (s)
+€ Back to jobs search
+Software Engineer,
+Al/Machine Learning, PhD,
+Early Career, 2027 Start
+ER] Google © Sunnyvale, CA, USA; +9 more
+ils Mid
+Apply eg
+@ GOOGLE.COM “
+eligible US base ees. Benefits for
+this role inclu
+¢ Health, ision, life,
+disability insurance
+e Retirement Benefits: 401 (k)
+with company match
+e Paid Time Off: 20 days of
+vacation ber vear. accruina at a
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/824709794_1409524794484731_462393393310606738_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5NDA0NjY0NTIzNTkyNDI5OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=b3xS2uoqHnwQ7kNvwHHSDY_&amp;_nc_oc=Adou1TeTaU0UQZAC5FPsGxKLaXoOwSVLUPCRA4MKbgZTrkwut_YaLrDtaXnWBsX362U&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;oh=00_AQJEFZH_0FZraw0urD3hd15zhVVVD01kzPieNZ0BoPYfng&amp;oe=6ABCAD2E
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/824709794_1409524794484731_462393393310606738_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5NDA0NjY0NTIzNTkyNDI5OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=b3xS2uoqHnwQ7kNvwHHSDY_&amp;_nc_oc=Adou1TeTaU0UQZAC5FPsGxKLaXoOwSVLUPCRA4MKbgZTrkwut_YaLrDtaXnWBsX362U&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;oh=00_AQJdtgciiIfz_mq_tzy6zuzWg4hYJ39B_saG4-dqEexYYg&amp;oe=6ABCAD2E
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHdpRXJ&amp;_nc_oc=AdrYY50kV6jR2Z3-4tvDVcgaZVfceHPnQ1Lat0VqYlkKxM_0jTpDPO80Sr2NioQ0rWI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKizT2WSacqva9y6qDwEG6OYGkLs0RdCboMZeal0hlvdA&amp;oe=6ABCC459
+https://l.instagram.com/?u=https%3A%2F%2Fwww.google.com%2Fabout%2Fcareers%2Fapplications%2Fjobs%2Fresults%2F123087196289671878-software-engineer-aimachine-learning-phd-early-career-2027-start%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafqikkrWRt1mPBG_QJKNUhaV9J-V8k-MewxenwMZ1-dMFsFrc_1X5YOkBI-Og_aem_ku1SBnG-07Lniywsdyuigg&amp;e=AUArfqTcykHketf-zmzjj6PzffA9h5xNSlEqJapkC4o3iAR-4ULM-8u57ZGNJGDMklLJT-HMefNPju2A9n9w2OVKg4NttAbE6_ltYTOoOw
+https://scontent-lax3-2.cdninstagram.com/o1/v/t2/f2/m78/AQPXJrZsjhXz_7_-EJnLHxl1LA-z6C__8h0k33eih1hJSofaQ6k1Vpf84QglEn79kI4I2lksb7scb28p-kZlbdmaKEJuK7h8uxVQUKE.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ohc=U09h0vwuP8YQ7kNvwFRovFs&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgzNDgyMjY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=a9a4bc8e14eaeb35&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzVBODVGNEY4RjlCMzQwMURBOUNCNDY4Mzk4MjU3MEU4X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkwv-puNChQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKBFdd-bQk1UpZTXjOh3v5fbzyg6maPtEW7n3nbu4tksg&amp;oe=6AB8D335</t>
+        </is>
+      </c>
+      <c r="O188" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P188" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q188" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R188" s="3" t="inlineStr"/>
+    </row>
+    <row r="189" ht="45" customHeight="1">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>7864806dcc1654def276</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T22:27:39.114875+00:00</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T16:52:57+00:00</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr"/>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>Data and Computer Eng/Sci Intern -</t>
+        </is>
+      </c>
+      <c r="F189" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G189" s="3" t="inlineStr"/>
+      <c r="H189" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I189" s="3" t="inlineStr"/>
+      <c r="J189" s="3" t="inlineStr"/>
+      <c r="K189" s="4" t="inlineStr">
+        <is>
+          <t>https://careers-barrios.icims.com/jobs/2897/job?mobile=true&amp;needsRedirect=false</t>
+        </is>
+      </c>
+      <c r="L189" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="inlineStr">
+        <is>
+          <t>io.
+&lt; Welcome page Returning Candidate? Log back in!
+Data and Computer Eng/Sci Intern -
+Summer 2027
+US-TX-Houston
+JobID 2026-2897 Category Information Technology
+Overview
+We are looking for talented and passionate
+college students for the summer to join our
+(2) CAREERS-BARRIOS.ICIMS.COM
+Spportiinity for’ a colle rit (Sophomore
+by credit or higher) to nternship
+supporting missions to th orbit, the
+Moon, and to Mars and beyond.
+This position will be in our Digital Solutions
+department, supporting one of the various
+Barrios disciplines, conducting digital
+infrastructure support and or supporting
+application and data develonment across
+https://scontent-lax7-1.cdninstagram.com/v/t51.71878-15/823893366_1624805859357983_4644189717653602765_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5NDExMTE5MTkzMjI3ODUwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=anp2FWQ0Z88Q7kNvwGALq5S&amp;_nc_oc=AdqvX82q5zh0ZEd4qAIGasix9ZlzcvSL48we7goLjpE3jTuKfa5Y5w4nStj8BBrR6EE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;oh=00_AQIWFYZxIUQjE2no8e14bb3j9Sl8hIWGNqD336p3T1t9EQ&amp;oe=6ABCC2AA
+https://scontent-lax7-1.cdninstagram.com/v/t51.71878-15/823893366_1624805859357983_4644189717653602765_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5NDExMTE5MTkzMjI3ODUwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=anp2FWQ0Z88Q7kNvwGALq5S&amp;_nc_oc=AdqvX82q5zh0ZEd4qAIGasix9ZlzcvSL48we7goLjpE3jTuKfa5Y5w4nStj8BBrR6EE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;oh=00_AQI3yprSPRbh3owbFP6MMI4yJ3vM7djSpJLsKAaC8BQupg&amp;oe=6ABCC2AA
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHdpRXJ&amp;_nc_oc=AdrYY50kV6jR2Z3-4tvDVcgaZVfceHPnQ1Lat0VqYlkKxM_0jTpDPO80Sr2NioQ0rWI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKizT2WSacqva9y6qDwEG6OYGkLs0RdCboMZeal0hlvdA&amp;oe=6ABCC459
+https://l.instagram.com/?u=https%3A%2F%2Fcareers-barrios.icims.com%2Fjobs%2F2897%2Fjob%3Fmobile%3Dtrue%26needsRedirect%3Dfalse%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafK3WhSa5GEc0HeFAwds1wBa7GQx5lu2qxg1f0maCmIVttGkWBe0c8k5beyzw_aem_eIBPGI4nfCLBzcUPaMeL7A&amp;e=AUDvIt-BnGKjAUMye4XtXpINuEzIoUgiPuQphjWmzFe_zGPzawQdiDSNkrqiM_4WcW2JqWTVSmUJOQLqDfL6my2v0DoD09k3DCEmPTVypw
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQMmtFCWLJScHM7EUd95mp9F__f9rj8xvwSRsMlpGqdt5Km9Seywd9awZCJMNU0EnpSdFIY-CfvL3VJGtOuCKx0GIxQL-3WkmHp3nYQ.mp4?_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=m53h3yTZXQ0Q7kNvwEjaIST&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgzNjY2OTc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=cda555010281e2a&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0Y5NjBGOTg1OTM0NjRDN0ZBM0Q5MjZBREJEODUyODA5X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkoaj5wdGhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJrxTejwzmAEMwBu7BIeFnzjes18lHXdS7JRtf_kA2mjg&amp;oe=6AB8DC45</t>
+        </is>
+      </c>
+      <c r="O189" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P189" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q189" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R189" s="3" t="inlineStr"/>
+    </row>
+    <row r="190" ht="45" customHeight="1">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>3daff133088708de0c07</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T22:27:41.222259+00:00</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T16:56:26+00:00</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>Bluestaq</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>Bluestaq — Software Engineering, Product Management</t>
+        </is>
+      </c>
+      <c r="F190" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G190" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering, Product Management</t>
+        </is>
+      </c>
+      <c r="H190" s="3" t="inlineStr"/>
+      <c r="I190" s="3" t="inlineStr"/>
+      <c r="J190" s="3" t="inlineStr"/>
+      <c r="K190" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/bluestaq/jobs/4420189009</t>
+        </is>
+      </c>
+      <c r="L190" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
+          <t>New
+Software Engineering
+Residency Program
+© Colorado Springs
+Software Engineering Residency Program
+Program Duration: January 11 through March
+4 30 minute lunchis crazy iJ
+4:30 PM with a 30-minute lunch.
+(7) JOB-BOARDS.GREENHOUSE. IO
+the program: reside ccessfully
+complete the reside e eligible to join
+Bluestaq full-time as a ciate Software
+Engineer. Full-time offers are contingent on
+performance and business need.
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/825320585_1418104266935775_411845346570642531_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5NDExMjk0OTM3OTU5ODg3Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=4yJh2RgyVPYQ7kNvwF-s54p&amp;_nc_oc=AdrAvSaCwS4G-AfkmGAOU6AZC3yQSMCQ4TPw0Alq6ubfssL_P1AK1pUZTY_BYKl9q7o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;oh=00_AQJ4Yp6oKvxxR6wozW9q4WIxxNB0D-pf76UZP6_jso8BEw&amp;oe=6ABCB0BB
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/825320585_1418104266935775_411845346570642531_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5NDExMjk0OTM3OTU5ODg3Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=4yJh2RgyVPYQ7kNvwF-s54p&amp;_nc_oc=AdrAvSaCwS4G-AfkmGAOU6AZC3yQSMCQ4TPw0Alq6ubfssL_P1AK1pUZTY_BYKl9q7o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;oh=00_AQL4EQy4aMUIm-nBE-19EVvgZDScPKVt7bOiBoVEqhNwnA&amp;oe=6ABCB0BB
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHdpRXJ&amp;_nc_oc=AdrYY50kV6jR2Z3-4tvDVcgaZVfceHPnQ1Lat0VqYlkKxM_0jTpDPO80Sr2NioQ0rWI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKizT2WSacqva9y6qDwEG6OYGkLs0RdCboMZeal0hlvdA&amp;oe=6ABCC459
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fbluestaq%2Fjobs%2F4420189009%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafiSXaBr8daLFSgA0X8yCyPa5ciIIXndLJRVdkLxzyWopHdVQNqncbfA6DARA_aem_535WNoDZNYqA4MP8FIolqg&amp;e=AUCe-ayLvIHPSxMWMfcRN0an1GmT5FUTzCPyr7M53BbJXnVAjfR9D89t2wikUxfS-Z6TxyBUer769CDeEbqNozft35y30RNkWREbZsgIsw
+https://scontent-lax3-2.cdninstagram.com/o1/v/t2/f2/m78/AQMISfla4rXALYwe2GX1qaZVu8_BbtkMOapNt_MHPEybmW_nqDmZc2WRVDlGbcHeWwbGV8k-LjuBzK5FdBLlQ7qmW-TGKqmysYr5adA.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ohc=KcSieTfVxNMQ7kNvwFr9XcZ&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgzNjc0NTM2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=6028b3979dbc364a&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzgxNDE0REZFMEZFODIyQzFDNTE1MjA4MjA2RThBQzk5X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbktaXKx9GhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQI9_vuj-dYf2G48UA_Y1_zA9eh2roti9YlB7oEq4py5DQ&amp;oe=6AB8EB4C</t>
+        </is>
+      </c>
+      <c r="O190" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P190" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q190" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R190" s="3" t="inlineStr"/>
+    </row>
+    <row r="191" ht="45" customHeight="1">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>30dbda23908a17d4190d</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T22:27:42.884766+00:00</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T16:57:02+00:00</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr"/>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>2027 IT Summer Intern - Software</t>
+        </is>
+      </c>
+      <c r="F191" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G191" s="3" t="inlineStr"/>
+      <c r="H191" s="3" t="inlineStr">
+        <is>
+          <t>2027, 2026</t>
+        </is>
+      </c>
+      <c r="I191" s="3" t="inlineStr"/>
+      <c r="J191" s="3" t="inlineStr"/>
+      <c r="K191" s="4" t="inlineStr">
+        <is>
+          <t>https://firstcitizens.jibeapply.com/jobs/35709?icims=1</t>
+        </is>
+      </c>
+      <c r="L191" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N191" s="3" t="inlineStr">
+        <is>
+          <t>a . aise
+First Citizens Bank
+= Back
+2027 IT Summer Intern - Software
+Developer (Raleigh, NC)
+Req ID: 35709
+Address: 100 East Tryon Road
+Location(s): Raleigh, North Carolina
+Category: Technology
+Work Hours: Monday - Friday
+Posted Date: 09/25/2026
+(2) FIRSTCITIZENS. JIBEAPPLY.COM
+Login or r
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/825322298_2052261525411663_4115126091602688107_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5NDExMzI1MTUyOTgzNjAxNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=YXDWavh73IAQ7kNvwFFTqK1&amp;_nc_oc=AdqlRZHQ0lUmWChWFTXivZyVttEE1qLYu4GlXff3jBT7Lyin3lDSmEzvYsjrJh5P-R4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;oh=00_AQLgdb6mF_DXL8G2492ssmbj3wC7RSfxlQ7rXeM2r_6-Kg&amp;oe=6ABCB365
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/825322298_2052261525411663_4115126091602688107_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5NDExMzI1MTUyOTgzNjAxNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=YXDWavh73IAQ7kNvwFFTqK1&amp;_nc_oc=AdqlRZHQ0lUmWChWFTXivZyVttEE1qLYu4GlXff3jBT7Lyin3lDSmEzvYsjrJh5P-R4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;oh=00_AQLg5vu1wGIl-tU_6TMaNHl_RCqXRzWGllcvFGim3xzMFw&amp;oe=6ABCB365
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHdpRXJ&amp;_nc_oc=AdrYY50kV6jR2Z3-4tvDVcgaZVfceHPnQ1Lat0VqYlkKxM_0jTpDPO80Sr2NioQ0rWI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKizT2WSacqva9y6qDwEG6OYGkLs0RdCboMZeal0hlvdA&amp;oe=6ABCC459
+https://l.instagram.com/?u=https%3A%2F%2Ffirstcitizens.jibeapply.com%2Fjobs%2F35709%3Ficims%3D1%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadkBZ2FLsF5ktIaT09Km3cXkVxir5ZETk7lBeIyc2-86irmsIk5us8E1Nlg4g_aem_mEEcECmE9JyhCQy014uRMg&amp;e=AUAoYkqx7tlXNaT65G-G-FiUHemY3TyL1-dGxWZtEp9Y3XUtir1s7C8VxteJxa8dDTI2NUx6gO5BPRujTbFK4riVvvqLbNp2PtiJEMGapA
+https://scontent-lax7-1.cdninstagram.com/o1/v/t2/f2/m78/AQNSvGd7g7Fak0vjWhqKBp1iNo8Zaez55ioJ1egzWY4atF5bOI63nyH7CK3ZzroLmfGdRHG6BzB21ncklSrgiRc3bJZQiF6RieFbOtI.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ohc=pETVe9WFfdMQ7kNvwFPlrPf&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgzNjc2MDY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=e45230be9dee8d5c&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzVCNEExN0RCOTM4NUFEMzlGNTJBNkZEODRFRjUxRkE1X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbklprcyNGhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIcFKE8goLfkhv1Tkb4sWMXHhMF2ag8IoKNAM8cqS0IvQ&amp;oe=6AB8C072</t>
+        </is>
+      </c>
+      <c r="O191" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P191" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q191" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R191" s="3" t="inlineStr"/>
+    </row>
+    <row r="192" ht="45" customHeight="1">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>de4a07577993016e2c0b</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T22:27:45.117674+00:00</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T16:57:36+00:00</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>Lutron</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>Lutron — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H192" s="3" t="inlineStr">
+        <is>
+          <t>Spring 2027</t>
+        </is>
+      </c>
+      <c r="I192" s="3" t="inlineStr"/>
+      <c r="J192" s="3" t="inlineStr"/>
+      <c r="K192" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.lutron.com/jobs/5616?icims=1</t>
+        </is>
+      </c>
+      <c r="L192" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N192" s="3">
+        <f> &gt; &lt;LUTRON
+= Back
+Spring 2027 - Software Engineering
+Co-Op - Philadelphia, PA
+Locations: Philadelphia, Pennsylvania
+Categories: Engineering
+Req ID: 5616
+@ CAREERS.LUTRON.COM
+Overview
+Lutron is seeking a Software ring Co-Op to join our
+collaborative team and contribute to high-impact projects.
+In this role, you will help design and deliver software driven
+solutions that power smart lighting and shading systems.
+At Lutron, your interest in application software development
+will grow through hands-on experience, practical skill-
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/825322423_1583282133005771_8638692649231956596_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5NDExMzUzMjA2MDY5MTAzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Ws3K4e5_TvYQ7kNvwEmFLaC&amp;_nc_oc=Adq99Xksy4ScIC_hvDyF0dcGAA7s_W6vJbkDIbsdpiPyLF6HgDQIecoeUvXu4YvyRqo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;oh=00_AQJb8PLRvZW80LnWeDkUa6OpCPOfiW79fxBabyly2g5ATw&amp;oe=6ABCB767
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/825322423_1583282133005771_8638692649231956596_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5NDExMzUzMjA2MDY5MTAzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Ws3K4e5_TvYQ7kNvwEmFLaC&amp;_nc_oc=Adq99Xksy4ScIC_hvDyF0dcGAA7s_W6vJbkDIbsdpiPyLF6HgDQIecoeUvXu4YvyRqo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;oh=00_AQKDpNw8j-jIlAoJ5G0x7EvFmMYhc9tU5lOOM1F8cB45xA&amp;oe=6ABCB767
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHdpRXJ&amp;_nc_oc=AdrYY50kV6jR2Z3-4tvDVcgaZVfceHPnQ1Lat0VqYlkKxM_0jTpDPO80Sr2NioQ0rWI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKizT2WSacqva9y6qDwEG6OYGkLs0RdCboMZeal0hlvdA&amp;oe=6ABCC459
+https://l.instagram.com/?u=https%3A%2F%2Fcareers.lutron.com%2Fjobs%2F5616%3Ficims%3D1%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeY7rOnZeF0RXy2F0wGnqLKQlK2Ia4TLyHldSDxQ8-YmXhaVQKGatxT5CePmw_aem_tPhwTO6-WE7nnNjXjkgNIA&amp;e=AUA_7YqKM1Y104GcxMOHGDT59oibvIDagaEl6wMfDlFn60QpDAiEtkBlC0WSPzIKdxlN-EDiUn2GO1yUTVAnvbFHZyGoZaifs5BwPRtMkA
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQNRUGXdvgxQQ7hnTGrgH7imPgGWvnYerTwZEDKnOnHDFq1JgeqAa8LqU0BxFZ4rdLTJPsyko6Rkd9REo1DVyp1wuAr-gjoyEGEDtg4.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=AqS9DszdaCIQ7kNvwH5cRV_&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgzNjc4MzE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=82c60c74b12bc1ea&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0JDNDM1MDgzQTVDMzY0NUFBQTA4OTNBRTA1NTVCOThGX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk_-OyytGhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQIBoCylcYmOM9w3L28N6BXEYXbChMF0RSf07Vy_Xd0JPw&amp;oe=6AB8C986</f>
+        <v/>
+      </c>
+      <c r="O192" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P192" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q192" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R192" s="3" t="inlineStr"/>
+    </row>
+    <row r="193" ht="45" customHeight="1">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>ac6c4ee5f267195b1c01</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T22:27:46.625826+00:00</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T17:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr"/>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>Lyft Content Systems Intern (Summer</t>
+        </is>
+      </c>
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="inlineStr"/>
+      <c r="H193" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I193" s="3" t="inlineStr"/>
+      <c r="J193" s="3" t="inlineStr"/>
+      <c r="K193" s="4" t="inlineStr">
+        <is>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8817900002?gh_jid=8817900002</t>
+        </is>
+      </c>
+      <c r="L193" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M193" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N193" s="3" t="inlineStr">
+        <is>
+          <t>Content Systems Intern
+(Summer 2027)
+Lyft Content Systems Intern (Summer
+2027) is where you apply online to
+the Content Systems Intern (Summer
+2027) role.
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/825322253_1865965434169059_2433642725996208824_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5NDEyMDYzNjkxMDIwNDY1MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=ztv4-4q9FHMQ7kNvwEPsEi3&amp;_nc_oc=AdptV1IruOEoVLUKe1MbyVzlQ1oy1Vkgj0rYQxlRXiEpby8Vy4Bg9TeGnhSZffbMSM4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;oh=00_AQLQ6637zn2Fi6EiKDVPNV5-otoNoNdlaJTb7eSExQnw5g&amp;oe=6ABCB8EF
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/825322253_1865965434169059_2433642725996208824_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5NDEyMDYzNjkxMDIwNDY1MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=ztv4-4q9FHMQ7kNvwEPsEi3&amp;_nc_oc=AdptV1IruOEoVLUKe1MbyVzlQ1oy1Vkgj0rYQxlRXiEpby8Vy4Bg9TeGnhSZffbMSM4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;oh=00_AQLtbdim_S_4nryIlaYCXSI-y0Wc6jjSTRj6Bn1jqdmSPA&amp;oe=6ABCB8EF
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHdpRXJ&amp;_nc_oc=AdrYY50kV6jR2Z3-4tvDVcgaZVfceHPnQ1Lat0VqYlkKxM_0jTpDPO80Sr2NioQ0rWI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKizT2WSacqva9y6qDwEG6OYGkLs0RdCboMZeal0hlvdA&amp;oe=6ABCC459
+https://l.instagram.com/?u=https%3A%2F%2Fapp.careerpuck.com%2Fjob-board%2Flyft%2Fjob%2F8817900002%3Fgh_jid%3D8817900002%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeQKNSur2hke-8W1rvwaNmW7_cArh6Wq4_pyGuSYQYLvo_MycuCBTS5Sx4htg_aem_5jbM7j5bGJ7N6a2sYK8xew&amp;e=AUCU5Shcsd7FxpBsr2MMzcKoI1xpnWhaTfXZPKq2vhtHz2l9u4h37Kk-YsUUnKg1Q_cn6ag8c5GYUsDmGgANJ8nL9I9FA_tEietU0LznXA
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQOBFeOwJtTf9lA92j8vwlvjTKcZDEk8xGpvTdFY6S6v0dgEkid9ASHVYXov5VZH9SZSAhuCWg_V1wtGnuY_zYHuSMixCR9V10YS8KM.mp4?_nc_cat=104&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=HStUX6zbtYkQ7kNvwEcvkEd&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgzNzAyMDc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=a8c60be201574e80&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0ZENDcwNDYxODc2RDRENkJBNTU1RTk2QjEwOTk1OUJEX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkh9uM3NGhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQL2_qLJ9_Z_TBewhw9j59bydz-kZj594XeutvrWaCxHUA&amp;oe=6AB8E005</t>
+        </is>
+      </c>
+      <c r="O193" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P193" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q193" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R193" s="3" t="inlineStr"/>
+    </row>
+    <row r="194" ht="45" customHeight="1">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>a7fba5b716f2372ebd0f</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T22:27:53.231573+00:00</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:38:57+00:00</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>Smartrecruiters</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>Smartrecruiters — Research</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H194" s="3" t="inlineStr"/>
+      <c r="I194" s="3" t="inlineStr"/>
+      <c r="J194" s="3" t="inlineStr"/>
+      <c r="K194" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Intuitive/744000151714759-ai-research-intern</t>
+        </is>
+      </c>
+      <c r="L194" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
+          <t>Grad ai research intern
+INTUITIVE
+Al Research Intern
+Company Description: It started
+with a simple idea: what if surgery
+could be less invasive and recovery
+less painful? Nearly 30 years later,
+that question still fuels everything
+we do at Intuitive. As a global
+leader in robotic-assisted surgery
+and minimally invasive care, our
+technologies—like th...
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/825277238_1315015633921309_5573978742875770227_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5NDE2NDU1MTYxNjUzMDQxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=401iY3kfuVIQ7kNvwFflBGa&amp;_nc_oc=AdpcRPKD5MGuq9T3JA48Rf7WtI0U8hE9CnSpwtjfRx-b_f3GUY8YBcp4-stkt5MV_EA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;oh=00_AQJQmgqDH3KbOv71ci6cNmofcvs-sxDMnP-NeW6VXsMtYw&amp;oe=6ABCB0C2
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/825277238_1315015633921309_5573978742875770227_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5NDE2NDU1MTYxNjUzMDQxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=401iY3kfuVIQ7kNvwFflBGa&amp;_nc_oc=AdpcRPKD5MGuq9T3JA48Rf7WtI0U8hE9CnSpwtjfRx-b_f3GUY8YBcp4-stkt5MV_EA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;oh=00_AQIu7Ro60w8muRvcK53kjgzRVP6GQJo4-m46QOowRClZiA&amp;oe=6ABCB0C2
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHdpRXJ&amp;_nc_oc=AdrYY50kV6jR2Z3-4tvDVcgaZVfceHPnQ1Lat0VqYlkKxM_0jTpDPO80Sr2NioQ0rWI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKizT2WSacqva9y6qDwEG6OYGkLs0RdCboMZeal0hlvdA&amp;oe=6ABCC459
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.smartrecruiters.com%2FIntuitive%2F744000151714759-ai-research-intern%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacKOu2NzosQUJUsAStusxGRxxF9VuDYTkE2mODD0ufeIB2BB5NO6vbbpyzt-w_aem_rhvf7qL1PBt12xFpjNN5wg&amp;e=AUCyzpS9AOVM9OvuKEIiGRAcjsAIhweAWdjClbx4jFu6zaWIdBXAgKg7Ag79g54avroNXE7fpRSOCkA12Hiu3gcsQRojgO4NgketTP4F7Q
+https://scontent-lax7-1.cdninstagram.com/o1/v/t2/f2/m78/AQMxc5zcjDFs9f1k8cLfkCXMRcASOU0aIKPqdmWmAJ3WASXh26Q-cViWaxWHLOd62Wq5HfCw0ELVAC3ENQG6sp264YAz41Xu7eEOJ28.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_ohc=YLosntDTlD8Q7kNvwFA5Rnb&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgzODA5MzU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=a89f09936fc7e31b&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0Q1NDAxRjNEQjVFM0VBOTMwQjJEM0JDQjVBREZEMUJCX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkr92DrNKhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJeCqICo7z2J8qTdpibh0AeTyolKyu23zCRfXQUmCZJWA&amp;oe=6AB8E746</t>
+        </is>
+      </c>
+      <c r="O194" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P194" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q194" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R194" s="3" t="inlineStr"/>
+    </row>
+    <row r="195" ht="45" customHeight="1">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>f2a0649d87fc6f8b1a95</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T22:27:54.993480+00:00</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T21:02:51+00:00</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr"/>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H195" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I195" s="3" t="inlineStr"/>
+      <c r="J195" s="3" t="inlineStr"/>
+      <c r="K195" s="4" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/easyf100-2026</t>
+        </is>
+      </c>
+      <c r="L195" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M195" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N195" s="3" t="inlineStr">
+        <is>
+          <t>Cloud « Artificial g
+G@aictiigence
+TD SYNNEX
+Summer 2027
+Internship Program |
+Technical, Applied
+Innovation Track: e
+Information
+Technology « Supply
+Chain « Systems and
+(2) F100 Al SWE - EASY INTERVIEWS
+w
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/825323974_1792521751695798_1429046351890741176_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5NDIzNjk3MjU3NTEyNzg4MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=DCSOYkNbvE4Q7kNvwGs_fTo&amp;_nc_oc=Adrn4V58lFbK1AR61086K7tCr_qVTgzqZ1gfdNcbylGk3yvLabeCExDDTdv9fldJeqY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;oh=00_AQKe4oCce7UgThVT9IJN1wpojH2_icd6m7kTiR6rEKtzdw&amp;oe=6ABCCF14
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/825323974_1792521751695798_1429046351890741176_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5NDIzNjk3MjU3NTEyNzg4MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=DCSOYkNbvE4Q7kNvwGs_fTo&amp;_nc_oc=Adrn4V58lFbK1AR61086K7tCr_qVTgzqZ1gfdNcbylGk3yvLabeCExDDTdv9fldJeqY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;oh=00_AQKgKe5WG7RXluPSjxRgjWAaK8EPG8d3umKVKR1TTw4rug&amp;oe=6ABCCF14
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHdpRXJ&amp;_nc_oc=AdrYY50kV6jR2Z3-4tvDVcgaZVfceHPnQ1Lat0VqYlkKxM_0jTpDPO80Sr2NioQ0rWI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKizT2WSacqva9y6qDwEG6OYGkLs0RdCboMZeal0hlvdA&amp;oe=6ABCC459
+https://l.instagram.com/?u=https%3A%2F%2Ftinyurl.com%2Feasyf100-2026%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafsAniZETzwtqIGevdqUaaDWz2vxaozVZJE9o-HGtdNDGO9PTx9kmv2AP0Mwg_aem_-21am9nIxsi3_ltQlBYbvA&amp;e=AUCJHjqQ0Vrc2w8xZB2-fEzSHAg-LZTeTR8_uqH1ax5ZfEOxNQoZ52rp4mM61PEQcErPQI6rWFx5blsgKtoHabjmxV4gpRPoJxWACKELng
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQNQerz5W0Y3Mb2WeTgx6fG0sLvgaY-bXuIltdVsEDQOvIQznMTdSr15BawihXk35eOqxq2R0PnXHSv7vRTr7nozI7m6yzZVcPUFU_o.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=C3yF2wYGBhgQ7kNvwE90y6x&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgzOTI4ODQ2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=88e933cc7fd74800&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0IzQkRCNkE4M0NBQjQ0MEJBOTdCMEU5MjkxRkJEM0EyX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkxJeHhdOhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLd3NHL0YU0uIZKZPXJGztOEjEt8hBV3xJsW1eWbeD7Sg&amp;oe=6AB8B9DE</t>
+        </is>
+      </c>
+      <c r="O195" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P195" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q195" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R195" s="3" t="inlineStr"/>
+    </row>
+    <row r="196" ht="45" customHeight="1">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>2f8a2920647baaf8abb9</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T22:27:58.283611+00:00</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T21:10:18+00:00</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>Withwaymo</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>Withwaymo — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H196" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I196" s="3" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="J196" s="3" t="inlineStr"/>
+      <c r="K196" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.withwaymo.com/jobs/2027-summer-intern-bs-software-engineer-driver-refinement-foundations-mountain-view-california-united-states</t>
+        </is>
+      </c>
+      <c r="L196" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
+          <t>2027 Summer Intern, BS,
+Software Engineer, Driver
+Refinement Foundations -
+Mountain View, California, United
+States
+Waymo is an autonomous driving
+technology company with the mission
+to be the world's most trusted
+driver. Since its start as the Google
+Self-Driving Car Project in 2009,
+Waymo has focused on building the
+Waymo Driver—The World's Most
+Experienced Driver™—to improve
+access to mobility while savi...
+https://careers.withwaymo
+-mountain-view-cali f “nia-united
+-states
+Another waymo drop
+¥
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/825320487_2306390800157566_5583297566393084099_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5NDI0MDcyMzc0MjUwNjI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=3_cEsr0il7IQ7kNvwGQuA7o&amp;_nc_oc=Adqo6y8fCxPcp9sXTuweWJ-chheDlztgNVmnKAhYVC-p5jdBcjm6ImG1B7QeQF_BNyg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;oh=00_AQKKuodvmtGJzqaC4BmBev3CtBPjvMBvsDixSOCxyLFepg&amp;oe=6ABCE32E
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/825320487_2306390800157566_5583297566393084099_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5NDI0MDcyMzc0MjUwNjI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=3_cEsr0il7IQ7kNvwGQuA7o&amp;_nc_oc=Adqo6y8fCxPcp9sXTuweWJ-chheDlztgNVmnKAhYVC-p5jdBcjm6ImG1B7QeQF_BNyg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;oh=00_AQIRxcrspVe8EJfEFJRCxx073Tt9p4YjELezFuh1quDlaQ&amp;oe=6ABCE32E
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHdpRXJ&amp;_nc_oc=AdrYY50kV6jR2Z3-4tvDVcgaZVfceHPnQ1Lat0VqYlkKxM_0jTpDPO80Sr2NioQ0rWI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKizT2WSacqva9y6qDwEG6OYGkLs0RdCboMZeal0hlvdA&amp;oe=6ABCC459
+https://l.instagram.com/?u=https%3A%2F%2Fcareers.withwaymo.com%2Fjobs%2F2027-summer-intern-bs-software-engineer-driver-refinement-foundations-mountain-view-california-united-states%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacDhqrQPsDIf9JPuhs4E-qJ6CjdOLGHd4bLo7luRsEFaWogbQ7-1iFjSTcH8w_aem_B9MSk0dmpr4gzDvGVgTmXg&amp;e=AUBUoDv8dpxQT5fZaDnAIM8KbHrs74MCS3KfeCe3-8Y0GnhtniHakSWQeo6kkbGz6La7zGe9L88Of_gIQm-96V2r0zoR8fVvV10X70bVDQ
+https://scontent-lax3-2.cdninstagram.com/o1/v/t2/f2/m78/AQNom1iPqXEHvv5G59BK5meGH7-T-Z_AujkAoqXzXLeZpr3rws6s0s29Cs1KHqMstQmhYvzS63FyiBnCQtieutVBZO07cGb8noMVL7U.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ohc=dj2JUmocjKcQ7kNvwFu6sIM&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODgzOTM0MDY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=327fcf15bf997cf6&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0EyNDA2RTQ5Rjk2QkQyRjdCQUZEMEZEQjVEMUI5QkJBX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbknoD5iNOhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=4jwg-PdGAz7mwp52DMvCzg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLVmoBqoqjhFbUIUx94vu8ToiJFZy63sg_1-Dui-qQbFA&amp;oe=6AB8B868</t>
+        </is>
+      </c>
+      <c r="O196" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P196" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q196" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R196" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R185"/>
+  <autoFilter ref="A1:R196"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -18505,6 +19557,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId351"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K185" r:id="rId352"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L185" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K186" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L186" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K187" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L187" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K188" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L188" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K189" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L189" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K190" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L190" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K191" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L191" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K192" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L192" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K193" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L193" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K194" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L194" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K195" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L195" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K196" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L196" r:id="rId375"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$203</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R196"/>
+  <dimension ref="A1:R203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18152,7 +18152,7 @@
     <row r="186" ht="45" customHeight="1">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>5e979738777941fe558d</t>
+          <t>9a4d5634f6b84ef96393</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -18180,14 +18180,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G186" s="3" t="inlineStr"/>
+      <c r="G186" s="3" t="n"/>
       <c r="H186" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I186" s="3" t="inlineStr"/>
-      <c r="J186" s="3" t="inlineStr"/>
+      <c r="I186" s="3" t="n"/>
+      <c r="J186" s="3" t="n"/>
       <c r="K186" s="4" t="inlineStr">
         <is>
           <t>https://jobs.statefarm.com/main/jobs/45928?lang=en-us&amp;iis=zero2sudo&amp;iisn=zero2sudo</t>
@@ -18238,12 +18238,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R186" s="3" t="inlineStr"/>
+      <c r="R186" s="3" t="n"/>
     </row>
     <row r="187" ht="45" customHeight="1">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>11be6d9cd2b017665f26</t>
+          <t>55542d41bb9e6a960501</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -18286,7 +18286,7 @@
           <t>Kirkland, Austin, Los Angeles, Sunnyvale</t>
         </is>
       </c>
-      <c r="J187" s="3" t="inlineStr"/>
+      <c r="J187" s="3" t="n"/>
       <c r="K187" s="4" t="inlineStr">
         <is>
           <t>https://www.google.com/about/careers/applications/jobs/results/84680705375642310-software-engineer-infrastructure-phd-early-career-2027-start</t>
@@ -18345,12 +18345,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R187" s="3" t="inlineStr"/>
+      <c r="R187" s="3" t="n"/>
     </row>
     <row r="188" ht="45" customHeight="1">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>9e9382601db71bacdbb8</t>
+          <t>0186a71f69f678bafc19</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -18393,7 +18393,7 @@
           <t>Sunnyvale</t>
         </is>
       </c>
-      <c r="J188" s="3" t="inlineStr"/>
+      <c r="J188" s="3" t="n"/>
       <c r="K188" s="4" t="inlineStr">
         <is>
           <t>https://www.google.com/about/careers/applications/jobs/results/123087196289671878-software-engineer-aimachine-learning-phd-early-career-2027-start</t>
@@ -18450,12 +18450,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R188" s="3" t="inlineStr"/>
+      <c r="R188" s="3" t="n"/>
     </row>
     <row r="189" ht="45" customHeight="1">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>7864806dcc1654def276</t>
+          <t>d3d97416c58d893e9b6f</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -18468,7 +18468,7 @@
           <t>2026-09-25T16:52:57+00:00</t>
         </is>
       </c>
-      <c r="D189" s="3" t="inlineStr"/>
+      <c r="D189" s="3" t="n"/>
       <c r="E189" s="3" t="inlineStr">
         <is>
           <t>Data and Computer Eng/Sci Intern -</t>
@@ -18479,14 +18479,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G189" s="3" t="inlineStr"/>
+      <c r="G189" s="3" t="n"/>
       <c r="H189" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I189" s="3" t="inlineStr"/>
-      <c r="J189" s="3" t="inlineStr"/>
+      <c r="I189" s="3" t="n"/>
+      <c r="J189" s="3" t="n"/>
       <c r="K189" s="4" t="inlineStr">
         <is>
           <t>https://careers-barrios.icims.com/jobs/2897/job?mobile=true&amp;needsRedirect=false</t>
@@ -18545,12 +18545,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R189" s="3" t="inlineStr"/>
+      <c r="R189" s="3" t="n"/>
     </row>
     <row r="190" ht="45" customHeight="1">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>3daff133088708de0c07</t>
+          <t>94ca4a3521cd40db9303</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -18583,9 +18583,9 @@
           <t>Software Engineering, Product Management</t>
         </is>
       </c>
-      <c r="H190" s="3" t="inlineStr"/>
-      <c r="I190" s="3" t="inlineStr"/>
-      <c r="J190" s="3" t="inlineStr"/>
+      <c r="H190" s="3" t="n"/>
+      <c r="I190" s="3" t="n"/>
+      <c r="J190" s="3" t="n"/>
       <c r="K190" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/bluestaq/jobs/4420189009</t>
@@ -18639,12 +18639,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R190" s="3" t="inlineStr"/>
+      <c r="R190" s="3" t="n"/>
     </row>
     <row r="191" ht="45" customHeight="1">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>30dbda23908a17d4190d</t>
+          <t>a1abf1854385de146b19</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -18657,7 +18657,7 @@
           <t>2026-09-25T16:57:02+00:00</t>
         </is>
       </c>
-      <c r="D191" s="3" t="inlineStr"/>
+      <c r="D191" s="3" t="n"/>
       <c r="E191" s="3" t="inlineStr">
         <is>
           <t>2027 IT Summer Intern - Software</t>
@@ -18668,14 +18668,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G191" s="3" t="inlineStr"/>
+      <c r="G191" s="3" t="n"/>
       <c r="H191" s="3" t="inlineStr">
         <is>
           <t>2027, 2026</t>
         </is>
       </c>
-      <c r="I191" s="3" t="inlineStr"/>
-      <c r="J191" s="3" t="inlineStr"/>
+      <c r="I191" s="3" t="n"/>
+      <c r="J191" s="3" t="n"/>
       <c r="K191" s="4" t="inlineStr">
         <is>
           <t>https://firstcitizens.jibeapply.com/jobs/35709?icims=1</t>
@@ -18728,12 +18728,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R191" s="3" t="inlineStr"/>
+      <c r="R191" s="3" t="n"/>
     </row>
     <row r="192" ht="45" customHeight="1">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>de4a07577993016e2c0b</t>
+          <t>e651bbc16d691080737e</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -18771,8 +18771,8 @@
           <t>Spring 2027</t>
         </is>
       </c>
-      <c r="I192" s="3" t="inlineStr"/>
-      <c r="J192" s="3" t="inlineStr"/>
+      <c r="I192" s="3" t="n"/>
+      <c r="J192" s="3" t="n"/>
       <c r="K192" s="4" t="inlineStr">
         <is>
           <t>https://careers.lutron.com/jobs/5616?icims=1</t>
@@ -18826,12 +18826,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R192" s="3" t="inlineStr"/>
+      <c r="R192" s="3" t="n"/>
     </row>
     <row r="193" ht="45" customHeight="1">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>ac6c4ee5f267195b1c01</t>
+          <t>8810155e68e72c8cf5ed</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -18844,7 +18844,7 @@
           <t>2026-09-25T17:11:42+00:00</t>
         </is>
       </c>
-      <c r="D193" s="3" t="inlineStr"/>
+      <c r="D193" s="3" t="n"/>
       <c r="E193" s="3" t="inlineStr">
         <is>
           <t>Lyft Content Systems Intern (Summer</t>
@@ -18855,14 +18855,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G193" s="3" t="inlineStr"/>
+      <c r="G193" s="3" t="n"/>
       <c r="H193" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I193" s="3" t="inlineStr"/>
-      <c r="J193" s="3" t="inlineStr"/>
+      <c r="I193" s="3" t="n"/>
+      <c r="J193" s="3" t="n"/>
       <c r="K193" s="4" t="inlineStr">
         <is>
           <t>https://app.careerpuck.com/job-board/lyft/job/8817900002?gh_jid=8817900002</t>
@@ -18908,12 +18908,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R193" s="3" t="inlineStr"/>
+      <c r="R193" s="3" t="n"/>
     </row>
     <row r="194" ht="45" customHeight="1">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>a7fba5b716f2372ebd0f</t>
+          <t>17e7168c85f2700eaf54</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -18946,9 +18946,9 @@
           <t>Research</t>
         </is>
       </c>
-      <c r="H194" s="3" t="inlineStr"/>
-      <c r="I194" s="3" t="inlineStr"/>
-      <c r="J194" s="3" t="inlineStr"/>
+      <c r="H194" s="3" t="n"/>
+      <c r="I194" s="3" t="n"/>
+      <c r="J194" s="3" t="n"/>
       <c r="K194" s="4" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Intuitive/744000151714759-ai-research-intern</t>
@@ -19000,12 +19000,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R194" s="3" t="inlineStr"/>
+      <c r="R194" s="3" t="n"/>
     </row>
     <row r="195" ht="45" customHeight="1">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>f2a0649d87fc6f8b1a95</t>
+          <t>b46be4d882feb204b41d</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -19018,7 +19018,7 @@
           <t>2026-09-25T21:02:51+00:00</t>
         </is>
       </c>
-      <c r="D195" s="3" t="inlineStr"/>
+      <c r="D195" s="3" t="n"/>
       <c r="E195" s="3" t="inlineStr">
         <is>
           <t>Software Engineering</t>
@@ -19039,8 +19039,8 @@
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I195" s="3" t="inlineStr"/>
-      <c r="J195" s="3" t="inlineStr"/>
+      <c r="I195" s="3" t="n"/>
+      <c r="J195" s="3" t="n"/>
       <c r="K195" s="4" t="inlineStr">
         <is>
           <t>https://tinyurl.com/easyf100-2026</t>
@@ -19092,12 +19092,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R195" s="3" t="inlineStr"/>
+      <c r="R195" s="3" t="n"/>
     </row>
     <row r="196" ht="45" customHeight="1">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>2f8a2920647baaf8abb9</t>
+          <t>e80c96cd3c6e97f20d69</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -19140,7 +19140,7 @@
           <t>Mountain View</t>
         </is>
       </c>
-      <c r="J196" s="3" t="inlineStr"/>
+      <c r="J196" s="3" t="n"/>
       <c r="K196" s="4" t="inlineStr">
         <is>
           <t>https://careers.withwaymo.com/jobs/2027-summer-intern-bs-software-engineer-driver-refinement-foundations-mountain-view-california-united-states</t>
@@ -19199,10 +19199,685 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R196" s="3" t="inlineStr"/>
+      <c r="R196" s="3" t="n"/>
+    </row>
+    <row r="197" ht="45" customHeight="1">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>2bed5bd9cfb514537e15</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T01:39:32.367209+00:00</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:59:04+00:00</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr"/>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>internship period with the goal</t>
+        </is>
+      </c>
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="inlineStr"/>
+      <c r="H197" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I197" s="3" t="inlineStr"/>
+      <c r="J197" s="3" t="inlineStr"/>
+      <c r="K197" s="4" t="inlineStr">
+        <is>
+          <t>https://www.redventures.com/careers/positions/open?gh_jid=8233284</t>
+        </is>
+      </c>
+      <c r="L197" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N197" s="3" t="inlineStr">
+        <is>
+          <t>RIV —
+New
+2027 Launch
+Program: Data
+Science Intern
+© Charlotte, NC
+Apply
+This role is not open to visa
+sponsorship or transfer of visa
+sponsorship including those
+@ REDVENTURES.COM
+Skip the “ent nt-
+work,” and star a real
+impact on Day 1. As part of the
+Red Ventures Launch program
+internship, you'll find
+unparalleled opportunities to
+gain exposure to the role and
+learn what it’s like to work at RV
+over the 1l-week summer
+internship period with the goal
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/825837873_1855797805582783_6920731566284657694_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5NDMyNTY3MzIyMDc2ODc0Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=y_pX4JBtPXkQ7kNvwGMyzYi&amp;_nc_oc=Adq-jpckvZIo3yqF4ZPyPzY_qHOhQXs7qeuVzvFlWlXChIV95l8K45zJ1ZNj95VbK3Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=ZWIEeddlBe0ZlrduoTzsqQ&amp;_nc_ss=7e3ba&amp;oh=00_AQK5NMhRLclSaPom_uQUF_LLvr3USUtrIK981G6IJ7QPdQ&amp;oe=6ABD0EF5
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/825837873_1855797805582783_6920731566284657694_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5NDMyNTY3MzIyMDc2ODc0Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=y_pX4JBtPXkQ7kNvwGMyzYi&amp;_nc_oc=Adq-jpckvZIo3yqF4ZPyPzY_qHOhQXs7qeuVzvFlWlXChIV95l8K45zJ1ZNj95VbK3Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=ZWIEeddlBe0ZlrduoTzsqQ&amp;_nc_ss=7e3ba&amp;oh=00_AQIrvmqwooQwRl-Z47bVBsgFbteudAQ5DG52r8s1mYiD7Q&amp;oe=6ABD0EF5
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwFmCgf4&amp;_nc_oc=AdpMqq-8bPKeJ-s0gBuPOJdm_LeVjmIiooM0fxYbmvqt92kivH1MJfMkVA_ons2_CfY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKBJO__B-c4Dvkn0CAvI75WmI0lS4MJ89eHBP66fNqvNg&amp;oe=6ABCFC99
+https://l.instagram.com/?u=https%3A%2F%2Fwww.redventures.com%2Fcareers%2Fpositions%2Fopen%3Fgh_jid%3D8233284%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacjkwBB8QzYxDKH7D_2bbunHzRmJo9b9d61eejDNBYQlIHDCTywrl9JSPbCQw_aem_IwI3IkEidCpHei_9q4BN_w&amp;e=AUADsZ0OQZAV6ADfKoa91xRTMKWAjYkQUCJU8kepFyBy1MPsJ-0T_S3PMacLvMD410NQeQxD_vx1pIJcLwsiZIP_QhiJV7l6zDqTrlIL6g
+https://scontent-lga3-2.cdninstagram.com/o1/v/t2/f2/m78/AQM90AMMX7KHlh37bAOOeHY8hhk9mCzP-l_ar-47WJiGDehH-mSLcCQ27pCFFJvX4fE2uod_YlqLAWtni_yQCE7mc9aAfeteYLs65Ug.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ohc=9dgYObOeIKUQ7kNvwGvBqDo&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg0MDYxNjI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=21a98b049adadfee&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0VENEM0QzE4NDc5MjJGRDQ1QkEzQkJEMjkzOEI1MUFDX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkkon-59OhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=ZWIEeddlBe0ZlrduoTzsqQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJv8z5WTWD9zM1YS6BcjsXW8U9j72_DFBY03AASykPWrw&amp;oe=6AB8E87D</t>
+        </is>
+      </c>
+      <c r="O197" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P197" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q197" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R197" s="3" t="inlineStr"/>
+    </row>
+    <row r="198" ht="45" customHeight="1">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>0e7d36f1fb1bdfbd0fe7</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T01:39:34.302873+00:00</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T00:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>Intuit — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H198" s="3" t="inlineStr">
+        <is>
+          <t>Winter 2027</t>
+        </is>
+      </c>
+      <c r="I198" s="3" t="inlineStr"/>
+      <c r="J198" s="3" t="inlineStr"/>
+      <c r="K198" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.intuit.com/job/toronto/winter-2027-software-developer-co-op-4-or-8-months/27595/101130613680?cid=unknownReferringDomains_unknownReferringDomains</t>
+        </is>
+      </c>
+      <c r="L198" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M198" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N198" s="3" t="inlineStr">
+        <is>
+          <t>INTUIT Careers [=]
+Job Search v
+Winter 2027: Software Developer Co-op
+(4 or 8 months)
+Category: Software Engineering, Internship
+Location: Toronto, Canada
+Job ID: 24372
+Apply Now
+Company Overview
+Intuit is the global financial technology
+@ JOBS.INTUIT.COM
+Nr wr mew
+VEN Mt
+aredres such as JJ edit Karma,
+QuickBooks, and
+everyone should ha
+e believe that
+portunity to
+prosper. We never stop working to find new,
+innovative ways to make the
+&amp; Give Feedback
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/825277341_1466820965352382_2975505612944074146_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5NDMyNjE0NTgwMTc2NjA5Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=P_yVMQqP4AIQ7kNvwH0mzit&amp;_nc_oc=Adp3lAzuCCzebsJL-0cEinDb0WpO314pFGypHLkx5fB-MD7oH0oo9Zye0OiWveD6ezQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=ZWIEeddlBe0ZlrduoTzsqQ&amp;_nc_ss=7e3ba&amp;oh=00_AQKisAnqMxmYZcXG7Tx55Lp9gK0LLNetnxQjUgNiqJtZDA&amp;oe=6ABCE1BF
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/825277341_1466820965352382_2975505612944074146_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5NDMyNjE0NTgwMTc2NjA5Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=P_yVMQqP4AIQ7kNvwH0mzit&amp;_nc_oc=Adp3lAzuCCzebsJL-0cEinDb0WpO314pFGypHLkx5fB-MD7oH0oo9Zye0OiWveD6ezQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=ZWIEeddlBe0ZlrduoTzsqQ&amp;_nc_ss=7e3ba&amp;oh=00_AQI9WbJUEjLwFu9aj_H-qC9tWu5yfEFaobyt74sQdMGbEg&amp;oe=6ABCE1BF
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwFmCgf4&amp;_nc_oc=AdpMqq-8bPKeJ-s0gBuPOJdm_LeVjmIiooM0fxYbmvqt92kivH1MJfMkVA_ons2_CfY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKBJO__B-c4Dvkn0CAvI75WmI0lS4MJ89eHBP66fNqvNg&amp;oe=6ABCFC99
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.intuit.com%2Fjob%2Ftoronto%2Fwinter-2027-software-developer-co-op-4-or-8-months%2F27595%2F101130613680%3Fcid%3DunknownReferringDomains_unknownReferringDomains%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadjlh0nsHfweiC9UR4XKJv4sPStqckZ07RVKIOr5rspIfzs9odmFvn-xe0hRA_aem_NGIwFato-18ce4U1ewIfEQ&amp;e=AUAs0x4Si85Sg_lSWNwKRd5niKcy3gT0G-0MQFkHd5WgHYntjZbz9dOzSx4GzIalnqVtPRoJSxfcT8-9mXt4r7Nwq0OQa2nt3PRkDl_euA
+https://scontent-lga3-2.cdninstagram.com/o1/v/t2/f2/m78/AQOGclhkNZuAlM-Vg3jTuA2cYvuPWooXENHTxJFje8VyHHjsQxmzhZ_QySBpTUt2qWJBoAiDA93117zLWksc1j6OTkt_VlZNG4OAdbA.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ohc=sh_5C_sKLAcQ7kNvwEyJ3GQ&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg0MDYzMTg2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=74d9e29c2ca80681&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0E3NDBCODlFMzQwRDAzNjM2NDVGQjVEMDMwN0FDRkI2X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkjuyS6dOhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=ZWIEeddlBe0ZlrduoTzsqQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJM4_xVHu6t1XL3ta8YIy8WnkV42Awgx7TrMoyjxbD2Og&amp;oe=6AB904EE</t>
+        </is>
+      </c>
+      <c r="O198" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P198" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q198" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R198" s="3" t="inlineStr"/>
+    </row>
+    <row r="199" ht="45" customHeight="1">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>503c0a3a1486eb47b47f</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T01:39:35.626491+00:00</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T00:00:38+00:00</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>Withwaymo</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>Withwaymo — Internship</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="inlineStr"/>
+      <c r="H199" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I199" s="3" t="inlineStr"/>
+      <c r="J199" s="3" t="inlineStr"/>
+      <c r="K199" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.withwaymo.com/jobs/2027-summer-intern-bs-software-engineer-driver-refinement-foundations-mountain-view-california-united-states?gh_jid=8224900</t>
+        </is>
+      </c>
+      <c r="L199" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N199" s="3" t="inlineStr">
+        <is>
+          <t>WY Careers —_
+AT WAYMO
+%
+2027 Summer
+Intern, BS,
+Software
+Engineer, Driver
+Refinement
+(2) CAREERS.WITHWAYMO.COM
+9 MOUNTAIN VI ORNIA, UNITED STATES
+A) INTERN SG
+© Search jobs Q
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/825322654_1626259012345080_8540829094730974857_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5NDMyNjQ2MTI1NTYzMTc2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=eHmZml4pbDgQ7kNvwFlfS9M&amp;_nc_oc=Adoe1QAVIA_MTDsIzMKLeTSdF2-Y2vjm4fgoXUHF_L839nI8GXLQiVy1p34Gy9LtIlc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=ZWIEeddlBe0ZlrduoTzsqQ&amp;_nc_ss=7e3ba&amp;oh=00_AQLmFi_HO3xisunF4HviBo5L257kGhhqKfrI31HlGd-aPA&amp;oe=6ABCFDC2
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/825322654_1626259012345080_8540829094730974857_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5NDMyNjQ2MTI1NTYzMTc2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=eHmZml4pbDgQ7kNvwFlfS9M&amp;_nc_oc=Adoe1QAVIA_MTDsIzMKLeTSdF2-Y2vjm4fgoXUHF_L839nI8GXLQiVy1p34Gy9LtIlc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=ZWIEeddlBe0ZlrduoTzsqQ&amp;_nc_ss=7e3ba&amp;oh=00_AQL50bpmVkWaeawTRE_7hQnBkXGvSCocmWdSdkeS2CVVCA&amp;oe=6ABCFDC2
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwFmCgf4&amp;_nc_oc=AdpMqq-8bPKeJ-s0gBuPOJdm_LeVjmIiooM0fxYbmvqt92kivH1MJfMkVA_ons2_CfY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKBJO__B-c4Dvkn0CAvI75WmI0lS4MJ89eHBP66fNqvNg&amp;oe=6ABCFC99
+https://l.instagram.com/?u=https%3A%2F%2Fcareers.withwaymo.com%2Fjobs%2F2027-summer-intern-bs-software-engineer-driver-refinement-foundations-mountain-view-california-united-states%3Fgh_jid%3D8224900%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadVop-LXozaR4N8LvADs2VX9yLDWt4dpa7jIKgEK5lS0YuwpOpx0uHUNHrfXw_aem_GjRNMl05SQEHlpYcIxaozQ&amp;e=AUAiLc6nbG-Aoz5Cp9rbP1K4LzuZNvXmC20Jx7ytaqx__9Xn6Ve_7cH0rprJg8a2mA1XyJbNHWP0s7D7nEQCxFsZUl2ZxST66_HXFnK21Q
+https://scontent-lga3-2.cdninstagram.com/o1/v/t2/f2/m78/AQNHAyw1iCtVdQyFH6ANJgBPYfJ5Rg80dN9lc2-lfqL-OTRvcstNRT1E59VE0NetQy8gAqd81FNi2h9mokkWYbOB-DJRtJE7IfF5RSA.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ohc=NXHsXEF5gswQ7kNvwGbdVr3&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg0MDY0MjY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=7b1d58a98710a7ef&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0ZGNEEwN0M3MDE5QTQ4NDlEQzg5NThBM0Q3QjAxNDkzX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk2uv56dOhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=ZWIEeddlBe0ZlrduoTzsqQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLx0TUIQRbcEJ8Za1hZklSqKF2MgIJCx8LAD0UJx6cmqQ&amp;oe=6AB90E36</t>
+        </is>
+      </c>
+      <c r="O199" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P199" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q199" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R199" s="3" t="inlineStr"/>
+    </row>
+    <row r="200" ht="45" customHeight="1">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>f9b7b1b69967915a74b3</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T01:39:36.905279+00:00</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T00:02:11+00:00</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>Withwaymo</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>Withwaymo — Internship</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr"/>
+      <c r="H200" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I200" s="3" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="J200" s="3" t="inlineStr"/>
+      <c r="K200" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.withwaymo.com/jobs/2027-summer-intern-ms-phd-systems-engineer-autonomous-vehicle-networks-diagnostics-mountain-view-california-united-states?gh_jid=8231711</t>
+        </is>
+      </c>
+      <c r="L200" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N200" s="3" t="inlineStr">
+        <is>
+          <t>VV Careers oe
+AT WAYMO
+2027 Summer
+Intern, MS/PhD,
+Systems
+Engineer,
+Autonomous
+Vehicle
+2) CAREERS.WITHWAYMO.COM
+Liagnodlgs
+Q MOUNTAIN VIEW, CA} Searchiobs unl
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/825322294_2089748675325156_7431839644821980695_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5NDMyNzIzODk3OTY1MDM0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=xTTm9oZjPa0Q7kNvwH1aoip&amp;_nc_oc=AdqbJ3KwKgdkxnk84CFfGwybO8CyHKg1uPjAkj1P4aQ2dUYJT_dM-FdkQznlPBLpc6U&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=ZWIEeddlBe0ZlrduoTzsqQ&amp;_nc_ss=7e3ba&amp;oh=00_AQKcC95FSxJMGvlhUHu8O2KY5Fspxj1aVdXfKYLli-9A3w&amp;oe=6ABCEB54
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/825322294_2089748675325156_7431839644821980695_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5NDMyNzIzODk3OTY1MDM0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=xTTm9oZjPa0Q7kNvwH1aoip&amp;_nc_oc=AdqbJ3KwKgdkxnk84CFfGwybO8CyHKg1uPjAkj1P4aQ2dUYJT_dM-FdkQznlPBLpc6U&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=ZWIEeddlBe0ZlrduoTzsqQ&amp;_nc_ss=7e3ba&amp;oh=00_AQL4ZHEslm-QRakxu3d7iFI2r9Y_JiDchuTmJr8Ns8q1ig&amp;oe=6ABCEB54
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwFmCgf4&amp;_nc_oc=AdpMqq-8bPKeJ-s0gBuPOJdm_LeVjmIiooM0fxYbmvqt92kivH1MJfMkVA_ons2_CfY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKBJO__B-c4Dvkn0CAvI75WmI0lS4MJ89eHBP66fNqvNg&amp;oe=6ABCFC99
+https://l.instagram.com/?u=https%3A%2F%2Fcareers.withwaymo.com%2Fjobs%2F2027-summer-intern-ms-phd-systems-engineer-autonomous-vehicle-networks-diagnostics-mountain-view-california-united-states%3Fgh_jid%3D8231711%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeMjIqU8YlBORisqrmW_R3bTzUPNo-rifUesnkuVwMsk4411eSxxRxf0lFLww_aem_2vh-MqydoBYGPZtvaL5F_w&amp;e=AUCw3v0GH938jBXRbY4dJ7vKWzPiJbl9yGyfvDGaV_tRLk_lKKGlFdgntqL7sO4ACWhokGAbvKNfijGTkk426xanO6JlzMR7eqMKRHH9OQ
+https://scontent-lga3-2.cdninstagram.com/o1/v/t2/f2/m78/AQPGfswvy3nx3KAZ4REJwApT_V_F7SYkFmne3yF6F_eBgVkN1N_C8AyFtg8J5lRyZ2xGMTIZU0frfKuTrKZXurJ8t7x_LIp3XHy0nzo.mp4?_nc_cat=107&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ohc=BKMsORUoxFYQ7kNvwFfAxPa&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg0MDY1NzA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=afa627ed964b463c&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzE4NDRBNjZCMzA3MTc1MTc1MURERkRDNzBGOTFBQkFGX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk6pWD69OhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=ZWIEeddlBe0ZlrduoTzsqQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKI0fozMChEVab8EV12MhcQKunEk9Pm5TfDyQdR3b2IqA&amp;oe=6AB91644</t>
+        </is>
+      </c>
+      <c r="O200" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P200" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q200" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R200" s="3" t="inlineStr"/>
+    </row>
+    <row r="201" ht="45" customHeight="1">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>58ecb945fc0ccb157389</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T01:39:38.426855+00:00</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T00:17:09+00:00</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G201" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H201" s="3" t="inlineStr"/>
+      <c r="I201" s="3" t="inlineStr"/>
+      <c r="J201" s="3" t="inlineStr"/>
+      <c r="K201" s="4" t="inlineStr">
+        <is>
+          <t>https://apply.careers.microsoft.com/careers/job/1970393557008714</t>
+        </is>
+      </c>
+      <c r="L201" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N201" s="3" t="inlineStr">
+        <is>
+          <t>@ apply.careers.microsoft.com
+Instagram
+7:
+~P B® Microsoft Sign in
+Careers
+€ View All Jobs
+Software Engineer:
+Intern Opportunities
+for University Students,
+Atla faléeie Microsoft SWE Intern Atlanta
+@ United States, Georgia, Atlanta
+eam | Add to cart
+w
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/825276717_1072551742330338_2536312899328998081_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5NDMzNDc3MjQyNzc2NDM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=27v3eJJCxSEQ7kNvwFhVNMO&amp;_nc_oc=Adoldql_AJW4fvXfJE5kK7FAKeNxiTomii1nczLKqs9tAXID6tOwLOi2IuIFB-5LWls&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=ZWIEeddlBe0ZlrduoTzsqQ&amp;_nc_ss=7e3ba&amp;oh=00_AQJWFyPtGPbyAn_9NPc2EUNxDdDa09m3byUq6qf9WEnpUg&amp;oe=6ABCF296
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/825276717_1072551742330338_2536312899328998081_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5NDMzNDc3MjQyNzc2NDM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=27v3eJJCxSEQ7kNvwFhVNMO&amp;_nc_oc=Adoldql_AJW4fvXfJE5kK7FAKeNxiTomii1nczLKqs9tAXID6tOwLOi2IuIFB-5LWls&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=ZWIEeddlBe0ZlrduoTzsqQ&amp;_nc_ss=7e3ba&amp;oh=00_AQIycueNvj070FNhU5IjQ_EgBNzcXep49B7eGmNNUFPUmA&amp;oe=6ABCF296
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwFmCgf4&amp;_nc_oc=AdpMqq-8bPKeJ-s0gBuPOJdm_LeVjmIiooM0fxYbmvqt92kivH1MJfMkVA_ons2_CfY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKBJO__B-c4Dvkn0CAvI75WmI0lS4MJ89eHBP66fNqvNg&amp;oe=6ABCFC99
+https://l.instagram.com/?u=https%3A%2F%2Fapply.careers.microsoft.com%2Fcareers%2Fjob%2F1970393557008714%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafmpX-4HiZNDZj2pLQJy2VZF5R7aRSPL2u2acZqWPrXbN6zP9LDt2GlvlrDHw_aem_Bf7zyky16G0KGDPcJlP2ew&amp;e=AUC0QMBojgeSFICfPQZi7az-1BR9xHLnOZRdMEueJuUIkYm8uIYd2NLikDIZb8GEhZJ_Z7ZdsAeeWG8deHkzbqUrD0_fcae-E3nXleInEw
+https://scontent-lga3-2.cdninstagram.com/o1/v/t2/f2/m78/AQNv4OfK89ySiTYNaBiKLF-U6NcGSPuqWvMnJNE1E2SK1Ug4AlUXBJDQ5dJnjLTZ6BglzzOI8IA_cp0sARB4BbXlVcLEtPSdgt4mke8.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ohc=gv3LjhYEr2IQ7kNvwFkLYUq&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg0MDc5MzI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=102e8d6c9ca5af6&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzU0NDhCM0NCNUU5MTI4NzI0QUJEMzNFQzdDNTM4REI2X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkzImW9dOhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=ZWIEeddlBe0ZlrduoTzsqQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJGb5rG_xYG8MOB2nFeMzYDCnJDJmtc_sSCSDYOqzo-lg&amp;oe=6AB9104D</t>
+        </is>
+      </c>
+      <c r="O201" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P201" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q201" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R201" s="3" t="inlineStr"/>
+    </row>
+    <row r="202" ht="45" customHeight="1">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>e6502cdabcec85d98734</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T01:39:40.020935+00:00</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T00:18:13+00:00</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr"/>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>Interview Workshop</t>
+        </is>
+      </c>
+      <c r="F202" s="3" t="inlineStr">
+        <is>
+          <t>Workshop / Info Session</t>
+        </is>
+      </c>
+      <c r="G202" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H202" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I202" s="3" t="inlineStr"/>
+      <c r="J202" s="3" t="inlineStr"/>
+      <c r="K202" s="4" t="inlineStr">
+        <is>
+          <t>https://bloomberg.avature.net/events/EventDetailsPage?jobId=22022</t>
+        </is>
+      </c>
+      <c r="L202" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M202" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N202" s="3" t="inlineStr">
+        <is>
+          <t>x @ bloomberg.avature.net Cz
+Instagram -
+Bloomberg =
+Bloomberg X Berkeley
+SWE Technical
+Interview Workshop
+&lt; Back to Events
+PSA UC Berkeley Students - share
+with your friends before this fills
+In-Person
+Event Date
+Sep-30-2026
+Time
+https://scontent-lga3-1.cdninstagram.com/v/t51.71878-15/825269519_1557936165651768_5414963147007151429_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5NDMzNTMxMjk4OTg4NjA5Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=hPNYQF3Q-rEQ7kNvwFDmc7A&amp;_nc_oc=AdotUtQ8mUdFByHET4vVR0cDYCzHJWCaw6hB2GhFOlA3oKlhVOP9MhyQFnNVgfFY1XA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=ZWIEeddlBe0ZlrduoTzsqQ&amp;_nc_ss=7e3ba&amp;oh=00_AQIehrgF_zNaU_Rrh-qOphrgjo2W2L38DOS8dOIDGLW0zw&amp;oe=6ABCE5A2
+https://scontent-lga3-1.cdninstagram.com/v/t51.71878-15/825269519_1557936165651768_5414963147007151429_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5NDMzNTMxMjk4OTg4NjA5Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=hPNYQF3Q-rEQ7kNvwFDmc7A&amp;_nc_oc=AdotUtQ8mUdFByHET4vVR0cDYCzHJWCaw6hB2GhFOlA3oKlhVOP9MhyQFnNVgfFY1XA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=ZWIEeddlBe0ZlrduoTzsqQ&amp;_nc_ss=7e3ba&amp;oh=00_AQJWTpUCxVdzFhVTDcSrlmxclCOkAIdf7v68LC8AyjekhA&amp;oe=6ABCE5A2
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwFmCgf4&amp;_nc_oc=AdpMqq-8bPKeJ-s0gBuPOJdm_LeVjmIiooM0fxYbmvqt92kivH1MJfMkVA_ons2_CfY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKBJO__B-c4Dvkn0CAvI75WmI0lS4MJ89eHBP66fNqvNg&amp;oe=6ABCFC99
+https://l.instagram.com/?u=https%3A%2F%2Fbloomberg.avature.net%2Fevents%2FEventDetailsPage%3FjobId%3D22022%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafUoSJmpzj2AoxFgIgtU8rFosyXNc54VtvjWQkESSqS9xnj5I1XKtV--G2J_Q_aem_zjdKrZ7c1t6Gr2C0qJvarw&amp;e=AUDnqMMHTPXXF-vuYZq7qY-Zy6RKmBcOepPb-X8nKXD9ac_tkQmoIt0ctA8vj91EwHPiFrMF740U_0vbZaunpLPitsENJNqUIBgh0FEFuw
+https://scontent-lga3-1.cdninstagram.com/o1/v/t2/f2/m78/AQOb1EvpyiUJn7Dwi51mKvAvnkNJmp9QIC2WhUT7btFNltiqg26uW4FAnmtPARF4EerWlnaJwEN8-8nhvhPRVuuIs6Yj4yGo3kRz2pI.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_ohc=57eUzpACxCIQ7kNvwHt1vhI&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg0MDgyMTc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=a06d0a6d78b42937&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzY1NDlFMEM0Mjg0NTcyRUUzNDAxMTFBNzk0OURDOTg2X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk0e-l99OhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=ZWIEeddlBe0ZlrduoTzsqQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKYOmILKxeSNMWqjsVe3qMMyZ5AL7llVsX0otgWNqBZjQ&amp;oe=6AB8F55C</t>
+        </is>
+      </c>
+      <c r="O202" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P202" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q202" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R202" s="3" t="inlineStr"/>
+    </row>
+    <row r="203" ht="45" customHeight="1">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>87861f14fb9a6f2f6512</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T01:39:42.405083+00:00</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T00:39:56+00:00</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq — Software Engineering, Machine Learning / AI</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering, Machine Learning / AI</t>
+        </is>
+      </c>
+      <c r="H203" s="3" t="inlineStr"/>
+      <c r="I203" s="3" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="J203" s="3" t="inlineStr"/>
+      <c r="K203" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/quora/cf34f80e-fe5c-454d-bc9a-4c59993ffda0/application?jr_id=6ab7035a39fd8792cb73d1fe</t>
+        </is>
+      </c>
+      <c r="L203" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N203" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer New Grad,
+Machine Learning Platform -
+Quora (Remote)
+[Quora is a privately held,
+"remote-first" company https://
+www.quora.com/q/quora/Remote
+-First-at-Quora. This position can be
+performed remotely from anywhere
+in Canada or the United States.
+Please visit careers.quora.com/
+eligible-countries http://careers.quora
+.com/eligible-countries for details
+rega...
+Quora also posted NG SWE MLE
+a
+Completely remote too
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/825326333_1109202385221922_3297973935529237666_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5NDM0NjI1MzM3MDM3MTI3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=5OlQFfUDD0kQ7kNvwGuDzsI&amp;_nc_oc=Adpu019_DYkRxInbjytVuiwc6Fbz62cNwe25-R-nKbqAe54GlmWmAHbdkiBax0Dxplc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=ZWIEeddlBe0ZlrduoTzsqQ&amp;_nc_ss=7e3ba&amp;oh=00_AQKQammCXQ1dpHWUSeRTPmkqunNUXtDxJjIBl0yEQN_1mg&amp;oe=6ABCFF5B
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/825326333_1109202385221922_3297973935529237666_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5NDM0NjI1MzM3MDM3MTI3OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=5OlQFfUDD0kQ7kNvwGuDzsI&amp;_nc_oc=Adpu019_DYkRxInbjytVuiwc6Fbz62cNwe25-R-nKbqAe54GlmWmAHbdkiBax0Dxplc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=ZWIEeddlBe0ZlrduoTzsqQ&amp;_nc_ss=7e3ba&amp;oh=00_AQJJvECcBlgPHlo8ZZ7hR5BtdNcFLzy4baqL1SM0ObgTcw&amp;oe=6ABCFF5B
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwFmCgf4&amp;_nc_oc=AdpMqq-8bPKeJ-s0gBuPOJdm_LeVjmIiooM0fxYbmvqt92kivH1MJfMkVA_ons2_CfY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQKBJO__B-c4Dvkn0CAvI75WmI0lS4MJ89eHBP66fNqvNg&amp;oe=6ABCFC99
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.ashbyhq.com%2Fquora%2Fcf34f80e-fe5c-454d-bc9a-4c59993ffda0%2Fapplication%3Fjr_id%3D6ab7035a39fd8792cb73d1fe%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaff06N7GSi8klKEms4xwKtZVAKf9gIyko8QySYirwTabSzTRH0u3waTmlun4A_aem_jjj5WVyeCR3UAUdwY9AENA&amp;e=AUAROIJX62CvVfwADV7bkWFhbEwJwQ93pgQ56rCdQ2zJ4-bB4CECr9DgdzP1fqh-AoYCNHVSBz1Q75tReMKiT9Kec3zDh6nGjhDBjUTxbA
+https://scontent-lga3-1.cdninstagram.com/o1/v/t2/f2/m78/AQMxtf9n3f-5xSCRrGotZas6hwDCZbMKMppWJJUYPg3AOX2AOd8MJUQhX-bnVoUGAtmgRYMqtzrP269ca_I4CUKcGCGAXMIkRZE6J-s.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_ohc=om_b4H0Ex44Q7kNvwFEkaJu&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg0MDkzOTY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=e29b013b0fe89407&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzUwNDg2MTBCOEE1QUVGREEwRUYyMjNGNERCMUJGRDkxX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkxKCKgNShQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=ZWIEeddlBe0ZlrduoTzsqQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQL06ov-rWbGlV7CLkuH9uTk85IN4GGk1Iy0qfQZyjknog&amp;oe=6AB8EBBA</t>
+        </is>
+      </c>
+      <c r="O203" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P203" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q203" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R203" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R196"/>
+  <autoFilter ref="A1:R203"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -19579,6 +20254,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L195" r:id="rId373"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K196" r:id="rId374"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L196" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K197" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L197" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K198" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L198" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K199" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L199" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K200" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L200" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K201" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L201" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K202" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L202" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K203" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L203" r:id="rId389"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -19204,7 +19204,7 @@
     <row r="197" ht="45" customHeight="1">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>2bed5bd9cfb514537e15</t>
+          <t>dee5474f68c9ff6b820f</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -19217,7 +19217,7 @@
           <t>2026-09-25T23:59:04+00:00</t>
         </is>
       </c>
-      <c r="D197" s="3" t="inlineStr"/>
+      <c r="D197" s="3" t="n"/>
       <c r="E197" s="3" t="inlineStr">
         <is>
           <t>internship period with the goal</t>
@@ -19228,14 +19228,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G197" s="3" t="inlineStr"/>
+      <c r="G197" s="3" t="n"/>
       <c r="H197" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="I197" s="3" t="inlineStr"/>
-      <c r="J197" s="3" t="inlineStr"/>
+      <c r="I197" s="3" t="n"/>
+      <c r="J197" s="3" t="n"/>
       <c r="K197" s="4" t="inlineStr">
         <is>
           <t>https://www.redventures.com/careers/positions/open?gh_jid=8233284</t>
@@ -19296,12 +19296,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R197" s="3" t="inlineStr"/>
+      <c r="R197" s="3" t="n"/>
     </row>
     <row r="198" ht="45" customHeight="1">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>0e7d36f1fb1bdfbd0fe7</t>
+          <t>4e77ea1bf8ded131ecc8</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -19339,8 +19339,8 @@
           <t>Winter 2027</t>
         </is>
       </c>
-      <c r="I198" s="3" t="inlineStr"/>
-      <c r="J198" s="3" t="inlineStr"/>
+      <c r="I198" s="3" t="n"/>
+      <c r="J198" s="3" t="n"/>
       <c r="K198" s="4" t="inlineStr">
         <is>
           <t>https://jobs.intuit.com/job/toronto/winter-2027-software-developer-co-op-4-or-8-months/27595/101130613680?cid=unknownReferringDomains_unknownReferringDomains</t>
@@ -19401,12 +19401,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R198" s="3" t="inlineStr"/>
+      <c r="R198" s="3" t="n"/>
     </row>
     <row r="199" ht="45" customHeight="1">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>503c0a3a1486eb47b47f</t>
+          <t>c0ab94a72bcb08e74fbb</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -19434,14 +19434,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G199" s="3" t="inlineStr"/>
+      <c r="G199" s="3" t="n"/>
       <c r="H199" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="I199" s="3" t="inlineStr"/>
-      <c r="J199" s="3" t="inlineStr"/>
+      <c r="I199" s="3" t="n"/>
+      <c r="J199" s="3" t="n"/>
       <c r="K199" s="4" t="inlineStr">
         <is>
           <t>https://careers.withwaymo.com/jobs/2027-summer-intern-bs-software-engineer-driver-refinement-foundations-mountain-view-california-united-states?gh_jid=8224900</t>
@@ -19493,12 +19493,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R199" s="3" t="inlineStr"/>
+      <c r="R199" s="3" t="n"/>
     </row>
     <row r="200" ht="45" customHeight="1">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>f9b7b1b69967915a74b3</t>
+          <t>5d30ac8b1714a38df635</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -19526,7 +19526,7 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G200" s="3" t="inlineStr"/>
+      <c r="G200" s="3" t="n"/>
       <c r="H200" s="3" t="inlineStr">
         <is>
           <t>2027</t>
@@ -19537,7 +19537,7 @@
           <t>Mountain View</t>
         </is>
       </c>
-      <c r="J200" s="3" t="inlineStr"/>
+      <c r="J200" s="3" t="n"/>
       <c r="K200" s="4" t="inlineStr">
         <is>
           <t>https://careers.withwaymo.com/jobs/2027-summer-intern-ms-phd-systems-engineer-autonomous-vehicle-networks-diagnostics-mountain-view-california-united-states?gh_jid=8231711</t>
@@ -19588,12 +19588,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R200" s="3" t="inlineStr"/>
+      <c r="R200" s="3" t="n"/>
     </row>
     <row r="201" ht="45" customHeight="1">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>58ecb945fc0ccb157389</t>
+          <t>11fa1a648748bd05a732</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -19626,9 +19626,9 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H201" s="3" t="inlineStr"/>
-      <c r="I201" s="3" t="inlineStr"/>
-      <c r="J201" s="3" t="inlineStr"/>
+      <c r="H201" s="3" t="n"/>
+      <c r="I201" s="3" t="n"/>
+      <c r="J201" s="3" t="n"/>
       <c r="K201" s="4" t="inlineStr">
         <is>
           <t>https://apply.careers.microsoft.com/careers/job/1970393557008714</t>
@@ -19681,12 +19681,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R201" s="3" t="inlineStr"/>
+      <c r="R201" s="3" t="n"/>
     </row>
     <row r="202" ht="45" customHeight="1">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>e6502cdabcec85d98734</t>
+          <t>a1906e3c6092cc30f826</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -19699,7 +19699,7 @@
           <t>2026-09-26T00:18:13+00:00</t>
         </is>
       </c>
-      <c r="D202" s="3" t="inlineStr"/>
+      <c r="D202" s="3" t="n"/>
       <c r="E202" s="3" t="inlineStr">
         <is>
           <t>Interview Workshop</t>
@@ -19720,8 +19720,8 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="I202" s="3" t="inlineStr"/>
-      <c r="J202" s="3" t="inlineStr"/>
+      <c r="I202" s="3" t="n"/>
+      <c r="J202" s="3" t="n"/>
       <c r="K202" s="4" t="inlineStr">
         <is>
           <t>https://bloomberg.avature.net/events/EventDetailsPage?jobId=22022</t>
@@ -19774,12 +19774,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R202" s="3" t="inlineStr"/>
+      <c r="R202" s="3" t="n"/>
     </row>
     <row r="203" ht="45" customHeight="1">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>87861f14fb9a6f2f6512</t>
+          <t>13bb1dda7f89aec3f661</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -19812,13 +19812,13 @@
           <t>Software Engineering, Machine Learning / AI</t>
         </is>
       </c>
-      <c r="H203" s="3" t="inlineStr"/>
+      <c r="H203" s="3" t="n"/>
       <c r="I203" s="3" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="J203" s="3" t="inlineStr"/>
+      <c r="J203" s="3" t="n"/>
       <c r="K203" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/quora/cf34f80e-fe5c-454d-bc9a-4c59993ffda0/application?jr_id=6ab7035a39fd8792cb73d1fe</t>
@@ -19874,7 +19874,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R203" s="3" t="inlineStr"/>
+      <c r="R203" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:R203"/>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$206</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R203"/>
+  <dimension ref="A1:R206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19876,8 +19876,261 @@
       </c>
       <c r="R203" s="3" t="n"/>
     </row>
+    <row r="204" ht="45" customHeight="1">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>30c0238916547f390698</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T17:16:02.692906+00:00</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T15:52:31+00:00</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr"/>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>Great hiring at every step. Make</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>Job / Hiring</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="inlineStr"/>
+      <c r="H204" s="3" t="inlineStr"/>
+      <c r="I204" s="3" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
+        </is>
+      </c>
+      <c r="J204" s="3" t="inlineStr"/>
+      <c r="K204" s="4" t="inlineStr">
+        <is>
+          <t>https://app3.greenhouse.io/e/arnmvw</t>
+        </is>
+      </c>
+      <c r="L204" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N204" s="3" t="inlineStr">
+        <is>
+          <t>Greenhouse
+Great hiring at every step. Make
+smarter and more effective hiring
+decisions with Greenhouse.
+For Bay Area students or
+students interning in the bay.
+Neuralink meetup
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/828495622_1724468365303455_7036887462026342041_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5NDgwNTU1NDg3NDIyODAzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=aE3Lgq3NNvMQ7kNvwF2YNNn&amp;_nc_oc=AdoNMLSejAKfNPT1kd-jLxtuFofN8FOhchJfzjGnW-_ZGkIW6kTVqI3ZbvVm5S8oX8c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=Qc2NZTXl8-9ZHJw4zaUK3A&amp;_nc_ss=7e3ba&amp;oh=00_AQIcBG7NZ4KezN0RqAmNbMKOPriYOzAVIFvoh4tFdGW3Gg&amp;oe=6ABDBC02
+https://scontent-nrt6-1.cdninstagram.com/v/t51.71878-15/828495622_1724468365303455_7036887462026342041_n.jpg?stp=dst-jpg_e15_p240x240_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5NDgwNTU1NDg3NDIyODAzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=aE3Lgq3NNvMQ7kNvwF2YNNn&amp;_nc_oc=AdoNMLSejAKfNPT1kd-jLxtuFofN8FOhchJfzjGnW-_ZGkIW6kTVqI3ZbvVm5S8oX8c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_gid=Qc2NZTXl8-9ZHJw4zaUK3A&amp;_nc_ss=7e3ba&amp;oh=00_AQLKXsu16xbWHOHz3VjPe8osE71Vxcmy50e74vbgOPubrQ&amp;oe=6ABDBC02
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHlVQI4&amp;_nc_oc=AdrI8qE5qAsa-pvZdXswNnOvAzzee0vWIqv9RAc1sSzHIxgF_UBvPG-49tTjbbIfyts&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIYHmIfCnVsrb-5zNjzuz5Umcv4vaupivEWnJJWUhODuA&amp;oe=6ABDDD99
+https://l.instagram.com/?u=https%3A%2F%2Fapp3.greenhouse.io%2Fe%2Farnmvw%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAac-FfHvoujdzZJUJYaDimON9_rUpInCc2GjRalkm0Cx7fmu6qjMmqQJOtDOCw_aem_-a3p0OH3sfgNpNL7qd0wdQ&amp;e=AUBOuUufcjPKtiJElsWcj8Wp_B2s6CWjUwL1kiGp9EijN_K_bt66qOUoLJ-eQb2Q-uzQrrBrtZAv_0g2sX1ol_YvkA_5DbWf05jdtYMfdw
+https://scontent-nrt6-1.cdninstagram.com/o1/v/t2/f2/m78/AQMtk-kNVKGG3V4wWTYwg3eW4A2b65yTY2opPhUp3n53ybBu8E6X11__MM16Y1v7QYiq9iUsKWdhEkAk_H3nZh7frtN2YshN9Ymr8yE.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ohc=yEDZX2E8Mk4Q7kNvwECJxPK&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg1MTQwMzM2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=a6970dc5cd6881e5&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0RENDUzRDdFN0E0MUQ5NjExMkQwRDZGMzcxRkFCQzhDX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk6e_Xi9qhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=Qc2NZTXl8-9ZHJw4zaUK3A&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLxbDVqjve3oa2byrb_iQVUm1n2MAwc910o0IRb7eJ-Gg&amp;oe=6AB9D6AD</t>
+        </is>
+      </c>
+      <c r="O204" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P204" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q204" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R204" s="3" t="inlineStr"/>
+    </row>
+    <row r="205" ht="45" customHeight="1">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>2428ae6469e3c6649fb9</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T17:16:04.619596+00:00</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T15:53:30+00:00</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>Point72</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>Point72 — Hackathon / Competition</t>
+        </is>
+      </c>
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t>Hackathon / Competition</t>
+        </is>
+      </c>
+      <c r="G205" s="3" t="inlineStr"/>
+      <c r="H205" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I205" s="3" t="inlineStr"/>
+      <c r="J205" s="3" t="inlineStr"/>
+      <c r="K205" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.point72.com/CSJobDetail?jobName=2026-point72-academy-national-case-competition-us&amp;jobCode=CPC-0015213&amp;location=New+York&amp;locale=English&amp;retURL=%2FCSCareerSearch</t>
+        </is>
+      </c>
+      <c r="L205" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N205" s="3" t="inlineStr">
+        <is>
+          <t>eens
+ee
+.
+2026 Point72 -
+Academy
+National Case
+Competition -
+@ CAREERS.POINT/2.COM
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/825277031_1593016731751919_7959214073825477533_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5NDgwNjA1MDE2MzM4ODI2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=6l7xNNePODkQ7kNvwERvSpj&amp;_nc_oc=Adrd847rjdFaqXhYNsfTMD4PW7zFOTSFidd9KqbjiX0BHFwT7odjXLyeMp4HEnRQ9lY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=Qc2NZTXl8-9ZHJw4zaUK3A&amp;_nc_ss=7e3ba&amp;oh=00_AQJCtQq5LGB6mIOzQQHzmSmX5xAivYIgg3FBnk_VqCEMWg&amp;oe=6ABDEAC2
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/825277031_1593016731751919_7959214073825477533_n.jpg?stp=dst-jpg_e15_p240x240_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5NDgwNjA1MDE2MzM4ODI2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=6l7xNNePODkQ7kNvwERvSpj&amp;_nc_oc=Adrd847rjdFaqXhYNsfTMD4PW7zFOTSFidd9KqbjiX0BHFwT7odjXLyeMp4HEnRQ9lY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=Qc2NZTXl8-9ZHJw4zaUK3A&amp;_nc_ss=7e3ba&amp;oh=00_AQK99V6WaHKJ8ei3623n3DWjMtTJg9kU4f38TjBxfDnIog&amp;oe=6ABDEAC2
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHlVQI4&amp;_nc_oc=AdrI8qE5qAsa-pvZdXswNnOvAzzee0vWIqv9RAc1sSzHIxgF_UBvPG-49tTjbbIfyts&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIYHmIfCnVsrb-5zNjzuz5Umcv4vaupivEWnJJWUhODuA&amp;oe=6ABDDD99
+https://l.instagram.com/?u=https%3A%2F%2Fcareers.point72.com%2FCSJobDetail%3FjobName%3D2026-point72-academy-national-case-competition-us%26jobCode%3DCPC-0015213%26location%3DNew%2BYork%26locale%3DEnglish%26retURL%3D%252FCSCareerSearch%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeRlKyIaNb5cgfzmUzWf4U2GZHpa37CbmvX4iMgA161R7rwnyjwD7YppDs4Dg_aem_6csytSU0YqfV_s0l95RpUw&amp;e=AUDsBCIAAIKXbE5buxoQDz5Q0V6o23n5N_C9imvLhV65D83dJ6QRQUE18oKYuuwfxDRzoJRyc7J7llBejaNCGyYo876QGEV7vjHnGSAckg
+https://scontent-nrt1-1.cdninstagram.com/o1/v/t2/f2/m78/AQMThh9d4nOupq_DyzU6DdFWKIRG6WchDu8mxV_bbdonTUdpWgqHpbwgTQ_611l-gbWeSzOHSjhowniUQzkQzq2UuFRtdFWLs_dXtvM.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_ohc=j_J2EsQ4i8IQ7kNvwFvJQqc&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg1MTQ1NjE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=a6ffd2c35e739b60&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzY5NEVFMjNDQUI5QzU5QTZCNTAzNUNEMzQ3QUVEMDk1X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk-bTPj9qhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=Qc2NZTXl8-9ZHJw4zaUK3A&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJyUuHrQXGW_buflpyWGljopCce7w9X8s3ZDsgdFCrEDQ&amp;oe=6AB9D3DC</t>
+        </is>
+      </c>
+      <c r="O205" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P205" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q205" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R205" s="3" t="inlineStr"/>
+    </row>
+    <row r="206" ht="45" customHeight="1">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>c71d7cc5af9f71c7ad05</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T17:16:06.809442+00:00</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T15:54:18+00:00</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>Humana — Internship</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="inlineStr"/>
+      <c r="H206" s="3" t="inlineStr"/>
+      <c r="I206" s="3" t="inlineStr"/>
+      <c r="J206" s="3" t="inlineStr"/>
+      <c r="K206" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.humana.com/us/en/event/6a9896e6539e900c3a9d9ff6/Humana-Technology-Internship-Program-Virtual-Information-Session</t>
+        </is>
+      </c>
+      <c r="L206" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N206" s="3" t="inlineStr">
+        <is>
+          <t>@ careers.humana.com C:
+Instagram
+Humana Technology Internship
+Program Virtual Information Session
+Description
+lAin ie Fav Ur amanade Crammmayv INIT
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/825326082_1134575909251030_4742473803823853372_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5NDgwNjQ1MTM0OTUxMTQ0MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=VUd2hlQtew8Q7kNvwEdtG_Q&amp;_nc_oc=Ado5fKrXS6LGr6Er6lOv09hw5et57PRTlyDLHNvT4wwEtIQMkfL0LEH9UEpjkvh3cOY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=Qc2NZTXl8-9ZHJw4zaUK3A&amp;_nc_ss=7e3ba&amp;oh=00_AQLxTBtUITl5eQNCXDbEwxQiPP_Kc3hCvvxOidoJSsPyKQ&amp;oe=6ABDEBE8
+https://scontent-nrt1-1.cdninstagram.com/v/t51.71878-15/825326082_1134575909251030_4742473803823853372_n.jpg?stp=dst-jpg_e15_p240x240_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5NDgwNjQ1MTM0OTUxMTQ0MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=VUd2hlQtew8Q7kNvwEdtG_Q&amp;_nc_oc=Ado5fKrXS6LGr6Er6lOv09hw5et57PRTlyDLHNvT4wwEtIQMkfL0LEH9UEpjkvh3cOY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-nrt1-1.cdninstagram.com&amp;_nc_gid=Qc2NZTXl8-9ZHJw4zaUK3A&amp;_nc_ss=7e3ba&amp;oh=00_AQIi6yiFEUGm2e9DG_KLOL-TS3_JKnzOe2eZopXsfyapaw&amp;oe=6ABDEBE8
+https://scontent-nrt6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHlVQI4&amp;_nc_oc=AdrI8qE5qAsa-pvZdXswNnOvAzzee0vWIqv9RAc1sSzHIxgF_UBvPG-49tTjbbIfyts&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQIYHmIfCnVsrb-5zNjzuz5Umcv4vaupivEWnJJWUhODuA&amp;oe=6ABDDD99
+https://l.instagram.com/?u=https%3A%2F%2Fcareers.humana.com%2Fus%2Fen%2Fevent%2F6a9896e6539e900c3a9d9ff6%2FHumana-Technology-Internship-Program-Virtual-Information-Session%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaf0sC0dUIn_oxfxiceE1419U-YldjmzRNGLZpnglgMpqk7wNIfH0DUpgS64Ng_aem_IKSEUe58MLoqnbVGADYvjg&amp;e=AUCmveNuRK45OxzWY3iINbSfGdIWcu5ijV2cG13CWWyTUwwjT4DSPhVKooLwPz4q6m6HN_ICDmK6zAh-jnPjDnOiWGXf6KvJwCSwO65CkQ
+https://scontent-nrt6-1.cdninstagram.com/o1/v/t2/f2/m78/AQMgmGyugTMzVVT30VMjcxvD5OnXNFBGcy2_DArpaay2ujh4DYdjuABLjffUUSxtajJo3kjwNm_LHDfo0xDUl7ScvFRGzgSoP6sbuz0.mp4?_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-nrt6-1.cdninstagram.com&amp;_nc_ohc=5FybGT-nPX4Q7kNvwGIvzCS&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg1MTQ3NjU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=9fdfbd201c511376&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0Y3NDMwQ0E0ODE5NjE0MUMzNDc5N0REOTI4OUY4OThDX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkpfuRkdqhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=Qc2NZTXl8-9ZHJw4zaUK3A&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQLA8PLObZnR3if7tPIKgVUtM-r50GSwWonL3EL93FhP-Q&amp;oe=6AB9E5EB</t>
+        </is>
+      </c>
+      <c r="O206" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P206" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q206" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R206" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R203"/>
+  <autoFilter ref="A1:R206"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -20268,6 +20521,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L202" r:id="rId387"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K203" r:id="rId388"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L203" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K204" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L204" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K205" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L205" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K206" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L206" r:id="rId395"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -19879,7 +19879,7 @@
     <row r="204" ht="45" customHeight="1">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>30c0238916547f390698</t>
+          <t>2b03677952f98cbb3b70</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -19892,7 +19892,7 @@
           <t>2026-09-26T15:52:31+00:00</t>
         </is>
       </c>
-      <c r="D204" s="3" t="inlineStr"/>
+      <c r="D204" s="3" t="n"/>
       <c r="E204" s="3" t="inlineStr">
         <is>
           <t>Great hiring at every step. Make</t>
@@ -19903,14 +19903,14 @@
           <t>Job / Hiring</t>
         </is>
       </c>
-      <c r="G204" s="3" t="inlineStr"/>
-      <c r="H204" s="3" t="inlineStr"/>
+      <c r="G204" s="3" t="n"/>
+      <c r="H204" s="3" t="n"/>
       <c r="I204" s="3" t="inlineStr">
         <is>
           <t>Bay Area</t>
         </is>
       </c>
-      <c r="J204" s="3" t="inlineStr"/>
+      <c r="J204" s="3" t="n"/>
       <c r="K204" s="4" t="inlineStr">
         <is>
           <t>https://app3.greenhouse.io/e/arnmvw</t>
@@ -19957,12 +19957,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R204" s="3" t="inlineStr"/>
+      <c r="R204" s="3" t="n"/>
     </row>
     <row r="205" ht="45" customHeight="1">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>2428ae6469e3c6649fb9</t>
+          <t>c7f89ed59339893f715b</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -19990,14 +19990,14 @@
           <t>Hackathon / Competition</t>
         </is>
       </c>
-      <c r="G205" s="3" t="inlineStr"/>
+      <c r="G205" s="3" t="n"/>
       <c r="H205" s="3" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="I205" s="3" t="inlineStr"/>
-      <c r="J205" s="3" t="inlineStr"/>
+      <c r="I205" s="3" t="n"/>
+      <c r="J205" s="3" t="n"/>
       <c r="K205" s="4" t="inlineStr">
         <is>
           <t>https://careers.point72.com/CSJobDetail?jobName=2026-point72-academy-national-case-competition-us&amp;jobCode=CPC-0015213&amp;location=New+York&amp;locale=English&amp;retURL=%2FCSCareerSearch</t>
@@ -20045,12 +20045,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R205" s="3" t="inlineStr"/>
+      <c r="R205" s="3" t="n"/>
     </row>
     <row r="206" ht="45" customHeight="1">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>c71d7cc5af9f71c7ad05</t>
+          <t>8d2875d5121486010fb7</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -20078,10 +20078,10 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G206" s="3" t="inlineStr"/>
-      <c r="H206" s="3" t="inlineStr"/>
-      <c r="I206" s="3" t="inlineStr"/>
-      <c r="J206" s="3" t="inlineStr"/>
+      <c r="G206" s="3" t="n"/>
+      <c r="H206" s="3" t="n"/>
+      <c r="I206" s="3" t="n"/>
+      <c r="J206" s="3" t="n"/>
       <c r="K206" s="4" t="inlineStr">
         <is>
           <t>https://careers.humana.com/us/en/event/6a9896e6539e900c3a9d9ff6/Humana-Technology-Internship-Program-Virtual-Information-Session</t>
@@ -20127,7 +20127,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R206" s="3" t="inlineStr"/>
+      <c r="R206" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:R206"/>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$208</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R206"/>
+  <dimension ref="A1:R208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20129,8 +20129,199 @@
       </c>
       <c r="R206" s="3" t="n"/>
     </row>
+    <row r="207" ht="45" customHeight="1">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>6b5a65e9c930d8ba4fd2</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T22:56:52.855733+00:00</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T20:24:59+00:00</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>Doordashusa</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>Doordashusa — Machine Learning / AI</t>
+        </is>
+      </c>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G207" s="3" t="inlineStr">
+        <is>
+          <t>Machine Learning / AI</t>
+        </is>
+      </c>
+      <c r="H207" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I207" s="3" t="inlineStr">
+        <is>
+          <t>Seattle, San Francisco, Sunnyvale</t>
+        </is>
+      </c>
+      <c r="J207" s="3" t="inlineStr"/>
+      <c r="K207" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/doordashusa/jobs/8204111</t>
+        </is>
+      </c>
+      <c r="L207" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N207" s="3" t="inlineStr">
+        <is>
+          <t>@ job-boards.greenhouse.io C;:
+a
+&lt; Back to jobs
+(NeW)
+Machine Learning
+Intern (Masters) -
+Summer 2027
+© San Francisco, CA; Sunnyvale, CA ; New
+York City, NY; Seattle, WA
+(A JOB-BOARDS$. GREENHOUSE. IO
+About the Te
+engineer interns to join our fast-growing
+engineering team to help us develop az &gt;
+global infrastructure system that powe!
+DoorDash’s three-sided marketplace ot
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/825326594_1337081814975073_1058048220809705874_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5NDk0MjY5MjA3MzMxMzE1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=w6AnsfJBQiUQ7kNvwHa1_-S&amp;_nc_oc=AdplDT4lgiy0PsS6m2XLbYIs7fRyuQQzhvlmWI2nPf5Sdl2NUwMas8tSy8xHPx1Wb78&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=9nUMtycNRf2SA36ARufB4w&amp;_nc_ss=7e3ba&amp;oh=00_AQKdhpUWm2dhQeF2zvEvV3bV2EZptDT5j0CvbxExv4d6CA&amp;oe=6ABE07F2
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/825326594_1337081814975073_1058048220809705874_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5NDk0MjY5MjA3MzMxMzE1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=w6AnsfJBQiUQ7kNvwHa1_-S&amp;_nc_oc=AdplDT4lgiy0PsS6m2XLbYIs7fRyuQQzhvlmWI2nPf5Sdl2NUwMas8tSy8xHPx1Wb78&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=9nUMtycNRf2SA36ARufB4w&amp;_nc_ss=7e3ba&amp;oh=00_AQJiAOt8orosnggz8XyNsqhZHmoAAAhMsi26dPwG2QgfWg&amp;oe=6ABE07F2
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHCxoQe&amp;_nc_oc=AdrYIQC6XMB_qXW9-c7-gY-cYkmLfabdIacogzstQ6z2njt1LBJjhlF0444fUjnerC4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQL9V4wecTfTy-1Bl3HIwskXZiszT9PGQEHnSUM6ATdyQg&amp;oe=6ABE15D9
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fdoordashusa%2Fjobs%2F8204111%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacrQzZuMufPvjNuVSE2jHGi2TX79CLPAhZBOvT7OfGaX3GNzuwTfcXUAdXJDA_aem_6ahieogtvfefXIfwnZ7Bww&amp;e=AUDn784z2BhemDp-vJRvKyGPnicIeLsrBRwCatQr3wicqQwC2folXHpfZzvyYhPBQsW4FMGHSo2rN_fiJPe5E4P4aCx1PtPiHotHeO6Y0Q
+https://scontent-lga3-1.cdninstagram.com/o1/v/t2/f2/m78/AQPxKBac_JGxePbgaz1-S2yvkdcPhmw3FvjQ3EjumafwkoMvKofbsAp3Wy_QmLLAPgzY7lQD33E5UtCz9irV8xRI6WEUYSaW3C3Gcoc.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_ohc=EjBSuDh5d0EQ7kNvwFKgKMR&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg1NDc4ODI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=b449287aa003d2d4&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzI5NTIyNzZGMkIyNjQ0NEJBQThENTdCOURDMTQ4OUYxX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk6uXwh9yhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=9nUMtycNRf2SA36ARufB4w&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKG0f4ZBx4eJzxpdjBFUiBt5MOjkBysiXk2IrGaUPfpHw&amp;oe=6ABA1C88</t>
+        </is>
+      </c>
+      <c r="O207" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P207" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q207" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R207" s="3" t="inlineStr"/>
+    </row>
+    <row r="208" ht="45" customHeight="1">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>986a6e9968187895c073</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T22:56:55.560381+00:00</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T21:34:41+00:00</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>Roblox</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>Roblox — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H208" s="3" t="inlineStr"/>
+      <c r="I208" s="3" t="inlineStr"/>
+      <c r="J208" s="3" t="inlineStr"/>
+      <c r="K208" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.roblox.com/jobs/8171283</t>
+        </is>
+      </c>
+      <c r="L208" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N208" s="3" t="inlineStr">
+        <is>
+          <t>Roblox early career swe!
+1yoe
+ROBLOX
+Careers
+Software Engineer, GenAl
+Platform | Roblox
+Software Engineer, GenAl Platform
+w
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/825324218_1113394207931308_7408846961931712720_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5NDk3Nzc3ODEzMDkxNjA2Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=1ARp0-4xWQwQ7kNvwHuSqQL&amp;_nc_oc=Adqz1imOvJzF8IOK0gR0PzEx9kQAByqe2K217uhNcAUQib-DDC8mCI2rF5VsjqSuzJ8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=9nUMtycNRf2SA36ARufB4w&amp;_nc_ss=7e3ba&amp;oh=00_AQKrBBMa7AcikpuXq06Vcpv6DP2kKcDXsmYZlUSPFiMrlw&amp;oe=6ABE2825
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/825324218_1113394207931308_7408846961931712720_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5NDk3Nzc3ODEzMDkxNjA2Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=1ARp0-4xWQwQ7kNvwHuSqQL&amp;_nc_oc=Adqz1imOvJzF8IOK0gR0PzEx9kQAByqe2K217uhNcAUQib-DDC8mCI2rF5VsjqSuzJ8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=9nUMtycNRf2SA36ARufB4w&amp;_nc_ss=7e3ba&amp;oh=00_AQKyGkDOlSYyGBy6dmRN3h-vYUtZlPeRz0pWmZvk53XmuA&amp;oe=6ABE2825
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=N-Z37ibGQsQQ7kNvwHCxoQe&amp;_nc_oc=AdrYIQC6XMB_qXW9-c7-gY-cYkmLfabdIacogzstQ6z2njt1LBJjhlF0444fUjnerC4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQL9V4wecTfTy-1Bl3HIwskXZiszT9PGQEHnSUM6ATdyQg&amp;oe=6ABE15D9
+https://l.instagram.com/?u=https%3A%2F%2Fcareers.roblox.com%2Fjobs%2F8171283%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacuOOZoeHvZMkYzIfulvwfkJxLxLOUe4eH-P6R39eprYs8H2jjDVvR5-1TbNw_aem_Sa87A8_Wepo08qzYj_b4qg&amp;e=AUAuaC4twvK2BRK1R0TdyCxvVRIM7M7lS0DOevkvUlUxGlM-5jF2VJdi3Lu3jSPP_n8D3DQ95_BF8fbZuGVUYshEyVuNHauXcCizl2_2sQ
+https://scontent-lga3-3.cdninstagram.com/o1/v/t2/f2/m78/AQNVNa1ZWjO9faqxtlNBL3xvC39uIkdVZQDNIJd_CtXkYn0nK5EHKMMotrMQvAIvB3nLK4j9lbgPeitAf4dGteQMVvpzG4UeHsnweHU.mp4?_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_ohc=y4tAEt4EW3oQ7kNvwGiLMqi&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg1NTQ0MTM2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=dab6e21626e4076&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0RCM0NEQkRDMEQzMDQyMkRBNEQwN0U2NTNFMTZDNzFEX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkhZ_FuNyhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=9nUMtycNRf2SA36ARufB4w&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQI1s7XYN2JMp3P0oayMAD-Hq2353Vs167MgPFwZ9ac0Cg&amp;oe=6ABA3CED</t>
+        </is>
+      </c>
+      <c r="O208" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P208" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q208" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R208" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R206"/>
+  <autoFilter ref="A1:R208"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -20527,6 +20718,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L205" r:id="rId393"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K206" r:id="rId394"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L206" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K207" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L207" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K208" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L208" r:id="rId399"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -20132,7 +20132,7 @@
     <row r="207" ht="45" customHeight="1">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>6b5a65e9c930d8ba4fd2</t>
+          <t>bbe75c20afe15f38fd6a</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -20175,7 +20175,7 @@
           <t>Seattle, San Francisco, Sunnyvale</t>
         </is>
       </c>
-      <c r="J207" s="3" t="inlineStr"/>
+      <c r="J207" s="3" t="n"/>
       <c r="K207" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/doordashusa/jobs/8204111</t>
@@ -20230,12 +20230,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R207" s="3" t="inlineStr"/>
+      <c r="R207" s="3" t="n"/>
     </row>
     <row r="208" ht="45" customHeight="1">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>986a6e9968187895c073</t>
+          <t>faa9d109afa9082cb43a</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -20268,9 +20268,9 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H208" s="3" t="inlineStr"/>
-      <c r="I208" s="3" t="inlineStr"/>
-      <c r="J208" s="3" t="inlineStr"/>
+      <c r="H208" s="3" t="n"/>
+      <c r="I208" s="3" t="n"/>
+      <c r="J208" s="3" t="n"/>
       <c r="K208" s="4" t="inlineStr">
         <is>
           <t>https://careers.roblox.com/jobs/8171283</t>
@@ -20318,7 +20318,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R208" s="3" t="inlineStr"/>
+      <c r="R208" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:R208"/>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$208</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$209</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R208"/>
+  <dimension ref="A1:R209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20320,8 +20320,106 @@
       </c>
       <c r="R208" s="3" t="n"/>
     </row>
+    <row r="209" ht="45" customHeight="1">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>c4c23888a47b19041b9c</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27T08:18:34.119257+00:00</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27T02:52:40+00:00</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>Meta — Product Management</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="H209" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I209" s="3" t="inlineStr"/>
+      <c r="J209" s="3" t="inlineStr"/>
+      <c r="K209" s="4" t="inlineStr">
+        <is>
+          <t>https://metacareerprogramsaipanelatnyu.splashthat.com</t>
+        </is>
+      </c>
+      <c r="L209" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M209" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N209" s="3" t="inlineStr">
+        <is>
+          <t>x&lt; @ metacareerprogramsaipaneia... Ce
+Meta Career Programs: Al
+Panel at NYU
+SEPTEMBER 30, 2026
+12:30 PM - 2:00 PM
+NYU Wasserman Presentation Room A - 133 East 13th
+Street
+Zt outs&lt;-} You must use your @nyu.edu email to RSVP
+Building the models is only half of
+it
+Meta builds some of the most capable Al
+models in the world. We also use them
+every day to change how engineering,
+design, and research actually get done.
+https://scontent-lga3-1.cdninstagram.com/v/t51.71878-15/825323438_1552725839504301_2498230423904248782_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5NTEzNzgyMDAwMzgxMjgxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=WKZKMCqoqFwQ7kNvwFYGzHp&amp;_nc_oc=Adqac8EVm9SZoxCbMhx2-bbvjWnEPZTstFlN6kJFWZypFrfpn7azyDOl1sdxg1njECM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=ccgceceJ3qGVICVWEh2V7g&amp;_nc_ss=7e3ba&amp;oh=00_AQL1Rm2OFxs7y-zs5KsWLa__AzcisuBkZ5zPt2r_hY6jLA&amp;oe=6ABEB5F7
+https://scontent-lga3-1.cdninstagram.com/v/t51.71878-15/825323438_1552725839504301_2498230423904248782_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5NTEzNzgyMDAwMzgxMjgxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=WKZKMCqoqFwQ7kNvwFYGzHp&amp;_nc_oc=Adqac8EVm9SZoxCbMhx2-bbvjWnEPZTstFlN6kJFWZypFrfpn7azyDOl1sdxg1njECM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=ccgceceJ3qGVICVWEh2V7g&amp;_nc_ss=7e3ba&amp;oh=00_AQK_Qcw8qcFhJV8WxsWmH25GQSiDq36AWBDhcnME-GIE4Q&amp;oe=6ABEB5F7
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwHcFswi&amp;_nc_oc=Ado_-Rekn6Nf_y7G208aJmK-aIQ4B8gNKMaSeNTtAuJS4QMACvIbEeoCA3oJ-QUsupo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQJcqK9dCRXMPI2O0r89m8_Os0BOBlXCW8G-SKrLdM-u4A&amp;oe=6ABEBE99
+https://l.instagram.com/?u=https%3A%2F%2Fmetacareerprogramsaipanelatnyu.splashthat.com%2F%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaclE1RK0CslKuxXvPpfsE6yPpyWTmpr821xOAwY4clWA7FRybUXJfZh_J1rmA_aem_aDa9rsmm3ZOXdQSmAcsx_w%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUDVEVdzdsQ1vPhwfJImmua8k5TfU1scRHbkZyn4D_exrvtHrbEcOv5V_zI36DJj2mHSfXrsnb0V4YbRF37GWXUJS59icf6DfqAFI-MIsg
+https://scontent-lga3-3.cdninstagram.com/o1/v/t2/f2/m78/AQNYUsk4pJoAhu0HJN1x6VUJyNkHUTQHpH-wtTDpOxP-HgO1ZkzXVGOUXMMlNiWgS9p8P0ia2ACuBiAUic4ipPQGUVVCnZdZk0qKnFU.mp4?_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_ohc=G128Cfm2Z-YQ7kNvwGICa7k&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg1ODM3NTk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=b948e2f149b00bcc&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzk0NEY0RUVDREQwMkQyQzZFQkQ5NEJFNUVGQkE2Rjg1X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkt-KXk96hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=ccgceceJ3qGVICVWEh2V7g&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQJu5X8HDYpprOOvqngWRXMzC6ul6G3jB83s8IGMnPCluA&amp;oe=6ABAB81D</t>
+        </is>
+      </c>
+      <c r="O209" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P209" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q209" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R209" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R208"/>
+  <autoFilter ref="A1:R209"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -20722,6 +20820,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L207" r:id="rId397"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K208" r:id="rId398"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L208" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K209" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L209" r:id="rId401"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -20323,7 +20323,7 @@
     <row r="209" ht="45" customHeight="1">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>c4c23888a47b19041b9c</t>
+          <t>66498131f8c1f7ed575d</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -20361,8 +20361,8 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="I209" s="3" t="inlineStr"/>
-      <c r="J209" s="3" t="inlineStr"/>
+      <c r="I209" s="3" t="n"/>
+      <c r="J209" s="3" t="n"/>
       <c r="K209" s="4" t="inlineStr">
         <is>
           <t>https://metacareerprogramsaipanelatnyu.splashthat.com</t>
@@ -20416,7 +20416,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R209" s="3" t="inlineStr"/>
+      <c r="R209" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:R209"/>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$209</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$210</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R209"/>
+  <dimension ref="A1:R210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20418,8 +20418,107 @@
       </c>
       <c r="R209" s="3" t="n"/>
     </row>
+    <row r="210" ht="45" customHeight="1">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>4fd38985cc3433718753</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27T19:01:35.609117+00:00</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27T16:52:38+00:00</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft — Other Opportunity</t>
+        </is>
+      </c>
+      <c r="F210" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="inlineStr"/>
+      <c r="H210" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I210" s="3" t="inlineStr">
+        <is>
+          <t>New York, NYC</t>
+        </is>
+      </c>
+      <c r="J210" s="3" t="inlineStr"/>
+      <c r="K210" s="4" t="inlineStr">
+        <is>
+          <t>https://luma.com/xl0io4zc</t>
+        </is>
+      </c>
+      <c r="L210" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N210" s="3" t="inlineStr">
+        <is>
+          <t>HOLA
+Hispanic &amp; Latinx at Microsoft LEAD
+LEAD
+ASPIRE
+2026
+Microsoft NYC Event for students!
+For team name, put down Gi) flere:
+zero2sudo - &lt;Team Name&gt;
+LEAD ASPIRE 2026
+Hosted by Microsoft LEAD
+- STUDENT EVENT!
+© Microsoft
+New York, NY
+Registration
+Annronwal) Raniiirad
+https://scontent-dfw6-1.cdninstagram.com/v/t51.71878-15/825277046_1636124498103191_3423952454801657203_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5NTU2MDU4Mjc3ODM1MDM2OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=645mfiBtOtQQ7kNvwE5VeAx&amp;_nc_oc=Adrpv0go2pdZHD_7Fhyv8Tee8_xyZe1KHbZFjNlvNs6X7QKe051wI6a8p5ZaqPzwk6I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=YSStu5YTTxFWcXGq6MFv8w&amp;_nc_ss=7e3ba&amp;oh=00_AQLgOAE1rP28HUIg5HsaGymttgSgTfKI1zl7oUQY9YxM6A&amp;oe=6ABF299E
+https://scontent-dfw6-1.cdninstagram.com/v/t51.71878-15/825277046_1636124498103191_3423952454801657203_n.jpg?stp=dst-jpg_e15_p240x240_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5NTU2MDU4Mjc3ODM1MDM2OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=645mfiBtOtQQ7kNvwE5VeAx&amp;_nc_oc=Adrpv0go2pdZHD_7Fhyv8Tee8_xyZe1KHbZFjNlvNs6X7QKe051wI6a8p5ZaqPzwk6I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=YSStu5YTTxFWcXGq6MFv8w&amp;_nc_ss=7e3ba&amp;oh=00_AQKk1HkUN9WJcRlHtBSD6VD7iqVhS-2eJSSE2uN4RIx-1A&amp;oe=6ABF299E
+https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwFC2wAd&amp;_nc_oc=AdpwQ3BGViZ_IVfUhP2Vf92cyNEzLzG6Awplf3b8bvC5wrSP9DwgcmraKc0xPTzagPo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQL2sxOvrscNpHnri2ANJ0u9l5cQKdLZ81BIKdOBiOoSYg&amp;oe=6ABF2F19
+https://l.instagram.com/?u=https%3A%2F%2Fluma.com%2Fxl0io4zc%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaf_AAb9jMrZZwhfJKHYb7z_0YUGKbvC98aJmfF7joSAlmMPl207eIu5Emr04Q_aem_-ZrPx-9NLLMMD9hjbX0PYw%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUCeQaLTZY43vPdyb62Epiq8H0q6MLT4t2b19cieSLPiSB9wWzd5rAxsIIIGbCgI_iUimYqOTbja3SgXn_K8tzfZeTgfw2EIfYTA0a7nYw
+https://scontent-dfw5-1.cdninstagram.com/o1/v/t2/f2/m78/AQP_d2BUOgP2l4GFyP1cTURJahvldLZgVLutuIaftTCrFdhRrZw1nSHs7iXHQrCxPwoD-Tn2bIRsP4QsmUJypDL8OuBnOlAzM_rdURk.mp4?_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_ohc=OLEAQruvTVAQ7kNvwEI3pnK&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg2ODMzOTI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=525315952292df78&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzlDNEYwMEZCQzM1RTBEM0Q0NjFGRDlDMUUyMjAyRkIxX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk8JnB-eOhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=YSStu5YTTxFWcXGq6MFv8w&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQKT5Qu1nxRqvBj_13HLjOhKsqKsb_VPIsIm09rQXuedqA&amp;oe=6ABB2B76</t>
+        </is>
+      </c>
+      <c r="O210" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P210" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q210" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R210" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R209"/>
+  <autoFilter ref="A1:R210"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -20822,6 +20921,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L208" r:id="rId399"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K209" r:id="rId400"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L209" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K210" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L210" r:id="rId403"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$210</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$211</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R210"/>
+  <dimension ref="A1:R211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20421,7 +20421,7 @@
     <row r="210" ht="45" customHeight="1">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>4fd38985cc3433718753</t>
+          <t>9ebf2441f3aa580f5820</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -20449,7 +20449,7 @@
           <t>Other Opportunity</t>
         </is>
       </c>
-      <c r="G210" s="3" t="inlineStr"/>
+      <c r="G210" s="3" t="n"/>
       <c r="H210" s="3" t="inlineStr">
         <is>
           <t>2026</t>
@@ -20460,7 +20460,7 @@
           <t>New York, NYC</t>
         </is>
       </c>
-      <c r="J210" s="3" t="inlineStr"/>
+      <c r="J210" s="3" t="n"/>
       <c r="K210" s="4" t="inlineStr">
         <is>
           <t>https://luma.com/xl0io4zc</t>
@@ -20515,10 +20515,107 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R210" s="3" t="inlineStr"/>
+      <c r="R210" s="3" t="n"/>
+    </row>
+    <row r="211" ht="45" customHeight="1">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>71b3b56c68049a60d722</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27T22:17:18.598823+00:00</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27T20:45:56+00:00</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>NVIDIA — Research</t>
+        </is>
+      </c>
+      <c r="F211" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G211" s="3" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H211" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I211" s="3" t="inlineStr"/>
+      <c r="J211" s="3" t="inlineStr"/>
+      <c r="K211" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.nvidia.com/careers/job/893393154096</t>
+        </is>
+      </c>
+      <c r="L211" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M211" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N211" s="3">
+        <f>&gt; NVIDIA Join Talent Network Sign In
+€ View All Jobs
+Research Scientist,
+Fundamental
+Generative Al - New
+College Grad 2026
+Q US, CA, Santa Clara
+a
+NVIDIA Research Scientist New Grad
+Find out how well you
+match with this job
+@ JOBS.NVIDIA.COM
+Job Description
+Job Requisition Job Category
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/825269533_1614197210431076_6662402852302306453_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5NTY3ODAxMTIzNjE4ODU3Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=BOdJRYDivjgQ7kNvwGLRp3C&amp;_nc_oc=AdqXAEjP7tfsUAVJfY5OAkPg8FmjflK6PSDCLs_CA20zUF6HnC9djtoC_QU3F5Ay1tY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=z2PR52hEL_6u86wzd7K8qQ&amp;_nc_ss=7e3ba&amp;oh=00_AQNQnIpWyrxQbczw2eEid9eoSLXJhsIdqp3fKL3l3mPFyw&amp;oe=6ABF7EDF
+https://scontent-lga3-2.cdninstagram.com/v/t51.71878-15/825269533_1614197210431076_6662402852302306453_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5NTY3ODAxMTIzNjE4ODU3Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=BOdJRYDivjgQ7kNvwGLRp3C&amp;_nc_oc=AdqXAEjP7tfsUAVJfY5OAkPg8FmjflK6PSDCLs_CA20zUF6HnC9djtoC_QU3F5Ay1tY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_gid=z2PR52hEL_6u86wzd7K8qQ&amp;_nc_ss=7e3ba&amp;oh=00_AQPBN0qYz_tqJjO6GjqxzOPLYrjJcZLweF2cmkAkxat7pA&amp;oe=6ABF7EDF
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwFhg2wM&amp;_nc_oc=AdqU1B4u9-hmIeeC88HiIPzXfjj9Zu0U0kghiPCbdky0lhXbMkYnw6BW07_3lEPwg14&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQMHsg9LM-0iMUXyvLxv4rWT4eaQtPWvZkLazJCOvBsWSw&amp;oe=6ABF6759
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.nvidia.com%2Fcareers%2Fjob%2F893393154096%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacQ4lkD72H9XpuqAow5gYqBFCJyB44jdotYOMw9k1krDUWPkaDeHdSKDnrObw_aem_CIb7FQ7_Jf8Pxn_DQm6ERA&amp;e=AUDOubxiLvwapOQ9t3kJR-TGogwoTfpWsWCIMJYNUVJ3i7FJsnR1PQdzc1F7W6ILAr4dv3dOOrb5QTiy_DMTDkyLAivz_bnnm87qoywq5AmKlg_JzgKfzRwtSs5kqERiE3pvWuSTuflsVg
+https://scontent-lga3-3.cdninstagram.com/o1/v/t2/f2/m78/AQNTMDXaVOWRKsmwVfxcme_1YCdIQLAAS5pKzeivLRNQjNh1zkDpvVqxw9gAedqyxxlZW2s4hofKQAoFtAdFbFxSZfC-_UC_mxj39oE.mp4?_nc_cat=104&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_ohc=r7jU6epfIHoQ7kNvwG2TwJ0&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg3MDU0MDM2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=fec39e6ff634b085&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzYxRkZDMzJCMDI1NDQ3QTc5MUVGMjE2RkNGOUY5QjJFX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkw8PAneWhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=z2PR52hEL_6u86wzd7K8qQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQOymwY46qdbT4j1CbipyYyL6ADs4-OS4rMJRuSHxVQz9Q&amp;oe=6ABB825D</f>
+        <v/>
+      </c>
+      <c r="O211" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P211" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q211" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R211" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R210"/>
+  <autoFilter ref="A1:R211"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -20923,6 +21020,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L209" r:id="rId401"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K210" r:id="rId402"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L210" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K211" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L211" r:id="rId405"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$211</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$213</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R211"/>
+  <dimension ref="A1:R213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20520,7 +20520,7 @@
     <row r="211" ht="45" customHeight="1">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>71b3b56c68049a60d722</t>
+          <t>1d715dee935222a07a08</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -20558,8 +20558,8 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="I211" s="3" t="inlineStr"/>
-      <c r="J211" s="3" t="inlineStr"/>
+      <c r="I211" s="3" t="n"/>
+      <c r="J211" s="3" t="n"/>
       <c r="K211" s="4" t="inlineStr">
         <is>
           <t>https://jobs.nvidia.com/careers/job/893393154096</t>
@@ -20612,10 +20612,206 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R211" s="3" t="inlineStr"/>
+      <c r="R211" s="3" t="n"/>
+    </row>
+    <row r="212" ht="45" customHeight="1">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>ee60d1876ee92d704ad6</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T00:55:46.532379+00:00</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T00:10:24+00:00</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>Queracomputinginc</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>Queracomputinginc — Internship</t>
+        </is>
+      </c>
+      <c r="F212" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="inlineStr"/>
+      <c r="H212" s="3" t="inlineStr"/>
+      <c r="I212" s="3" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="J212" s="3" t="inlineStr"/>
+      <c r="K212" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/queracomputinginc/jobs/5435901008</t>
+        </is>
+      </c>
+      <c r="L212" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N212" s="3" t="inlineStr">
+        <is>
+          <t>QuEra &gt;
+&lt; Back to jobs
+New |
+Internship - Quantum
+Applications Research
+© Boston, MA, USA
+(Z) JOB-BOARDS.GREENHOUSE.I0
+About QuEra Com Cc.
+QuEra Computing is building the world’s
+most powerful neutral-atom quantum
+computers. Our systems are designed to
+scale and enable groundbreaking advances
+in science and technology. We collaborate
+closely with leading academic and industry
+partners to push the boundaries of quantum
+computing, error correction, and fault
+tolerance.
+Summary
+https://scontent-lax7-1.cdninstagram.com/v/t51.71878-15/829035644_2597979377315253_4233927019356189512_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5NTc4MDkyMjIyNzA0OTE1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=VUb1pLDKKMcQ7kNvwFk3VYn&amp;_nc_oc=AdqkyVJl3nO6Eob4R7mAhEDC_12P-dT5FHXUAE4XWQSc70QUAC9KVX8Doj2Jofp-Z8Y&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_gid=-5PWsHKGAQhfOYPyJeL6gg&amp;_nc_ss=7e3ba&amp;oh=00_AQNcx5Qt3fvePF44t_u8OOyIQRWxwBJC-njgb9MuFtvvJg&amp;oe=6ABF764B
+https://scontent-lax7-1.cdninstagram.com/v/t51.71878-15/829035644_2597979377315253_4233927019356189512_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5NTc4MDkyMjIyNzA0OTE1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=VUb1pLDKKMcQ7kNvwFk3VYn&amp;_nc_oc=AdqkyVJl3nO6Eob4R7mAhEDC_12P-dT5FHXUAE4XWQSc70QUAC9KVX8Doj2Jofp-Z8Y&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_gid=-5PWsHKGAQhfOYPyJeL6gg&amp;_nc_ss=7e3ba&amp;oh=00_AQOJbv2urdtCecmgRC26w6DmbPz37WR1w7kjI3z6lPL_Mg&amp;oe=6ABF764B
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwFqLdwQ&amp;_nc_oc=AdogxUC3bHOJLrBP1VyxuD-5w-g8yJxOUFjA7UbeNFY6k5i-1oQQzE7BidCoEiZ3Gyk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQNwpeUakHdEZa4OXRCfw6CQM6DIBpK7i7H4CCBrWIFGMg&amp;oe=6ABF9F99
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fqueracomputinginc%2Fjobs%2F5435901008%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAac9o6uspmsyFNg8xysO1Tuo-DD5gs1OQ1vddRzVUk-xRpSTj8FC_e1Nqe7agg_aem_4mXecMy6QtvA3Z8aMI0UDA&amp;e=AUBOJsVXT0JIFm7yt994zmzBzyCX3S3wC-c2ow5iSYJxrAG3zQd3gEplC6Z9QDXGMqxluNEbm_g45nZlHqPVr7JSETdb00frtXjqfvd1yw
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQO5CnvfsPGvUNO8UscAHnMqOb8_cIHII0QddUa3MmnzYrec3O7iz-cW8E6TerhimMa6mj8YnASZ_nXRlxXVf59SHqu_MdA09JQEB1Q.mp4?_nc_cat=102&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=20XkY1nLaOIQ7kNvwH1fsGn&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg3MjQ5NjM2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=5aa35d966a6daba8&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzU1NEQ1RDhENDAxMkJBQzE4QzY5OEUyQjM1NzI4NUE0X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk67Ker-ahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=-5PWsHKGAQhfOYPyJeL6gg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQOIzH0DH78AqaAMD0-pPx-roucn5o-l9gqwQJerjNT5_Q&amp;oe=6ABB97EB</t>
+        </is>
+      </c>
+      <c r="O212" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P212" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q212" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R212" s="3" t="inlineStr"/>
+    </row>
+    <row r="213" ht="45" customHeight="1">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>bcec2bf18fc535c97569</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T00:55:48.210931+00:00</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T00:25:09+00:00</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>Queracomputinginc</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>Queracomputinginc — Internship</t>
+        </is>
+      </c>
+      <c r="F213" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G213" s="3" t="inlineStr"/>
+      <c r="H213" s="3" t="inlineStr"/>
+      <c r="I213" s="3" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="J213" s="3" t="inlineStr"/>
+      <c r="K213" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/queracomputinginc/jobs/5435902008</t>
+        </is>
+      </c>
+      <c r="L213" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M213" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N213" s="3" t="inlineStr">
+        <is>
+          <t>‘QuEra:
+&lt; Back to jobs
+New
+Internship - Scientific
+Software and
+Compilation
+© Boston, MAUSA
+(2) JOB-BOARDS.GREENHOUSE.IO
+About QuEra Co Cc.
+QuEra Computing is the world’s
+most powerful neutral-atom quantum
+computers. Our systems are designed to
+scale and enable groundbreaking advances
+in science and technology. We collaborate
+closely with leading academic and industry
+partners to push the boundaries of quar *
+computing, error correction, and fault
+tolerance.
+https://scontent-lax7-1.cdninstagram.com/v/t51.71878-15/829262990_2046219559414341_6595926140082067067_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5NTc4ODM0NTkxNzk5NTExOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=-CnXWbkrh6IQ7kNvwEWERHE&amp;_nc_oc=AdqJBN1t4CDzts6DU3JUqqstAIlCw93POAcJSILOq5iqJdygQBAJffsfdLu_Jz7wUgQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_gid=-5PWsHKGAQhfOYPyJeL6gg&amp;_nc_ss=7e3ba&amp;oh=00_AQOb-yZSukxunXZPxxW9Ug55xjtp9Lkmsmt-8DlwjRnMtQ&amp;oe=6ABF970B
+https://scontent-lax7-1.cdninstagram.com/v/t51.71878-15/829262990_2046219559414341_6595926140082067067_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5NTc4ODM0NTkxNzk5NTExOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=-CnXWbkrh6IQ7kNvwEWERHE&amp;_nc_oc=AdqJBN1t4CDzts6DU3JUqqstAIlCw93POAcJSILOq5iqJdygQBAJffsfdLu_Jz7wUgQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_gid=-5PWsHKGAQhfOYPyJeL6gg&amp;_nc_ss=7e3ba&amp;oh=00_AQOIw1PjvPal-f-tF4NT-T6-LpSPlLzbafO7gJbV76zK0w&amp;oe=6ABF970B
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwFqLdwQ&amp;_nc_oc=AdogxUC3bHOJLrBP1VyxuD-5w-g8yJxOUFjA7UbeNFY6k5i-1oQQzE7BidCoEiZ3Gyk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQNwpeUakHdEZa4OXRCfw6CQM6DIBpK7i7H4CCBrWIFGMg&amp;oe=6ABF9F99
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fqueracomputinginc%2Fjobs%2F5435902008%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacKcYfKQ_vgdtC6ey5IBgHpg5A6I4stYA5EHigT7E-ooRmz7eUXIKOxv64bHw_aem_ogfzJuHBwdD8sO_fXneUTw&amp;e=AUC7-CXzJpqBEkexWy_ebvm3yu9hf5gHnOR5m0Zy-7w-HEDlUap5tZQevvLAbf257KuDiJxcO4W0xq1XNOnjh_LwhhDcUuk2GtnvA-J-yA
+https://scontent-lax3-2.cdninstagram.com/o1/v/t2/f2/m78/AQOmlwV0DeNQhkFHJCzc11aN2CaRpZDmsJgLu97928-xQ8xD1gQqHaVmyqOqQXq0_pKrIJk7dpWc94tEABbSqk4-LDWvMIT91RraNR4.mp4?_nc_cat=107&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ohc=ODpsOkpVnN8Q7kNvwExKAmB&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg3MjYzNDk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=15c9422209a17f&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0U2NDJDMEE0M0Y4NjdFNzhERTFEQzc3RTlCODc4NUE0X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkpZjIueahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=-5PWsHKGAQhfOYPyJeL6gg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQMdzftI-TGcf-QtvWCZvT0z1fPJDXXjiWMqcwlzoBH4aA&amp;oe=6ABB8CE8</t>
+        </is>
+      </c>
+      <c r="O213" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P213" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q213" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R213" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R211"/>
+  <autoFilter ref="A1:R213"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -21022,6 +21218,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L210" r:id="rId403"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K211" r:id="rId404"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L211" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K212" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L212" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K213" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L213" r:id="rId409"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$214</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R213"/>
+  <dimension ref="A1:R214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20617,7 +20617,7 @@
     <row r="212" ht="45" customHeight="1">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>ee60d1876ee92d704ad6</t>
+          <t>cdcdbadcac30895dc319</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -20645,14 +20645,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G212" s="3" t="inlineStr"/>
-      <c r="H212" s="3" t="inlineStr"/>
+      <c r="G212" s="3" t="n"/>
+      <c r="H212" s="3" t="n"/>
       <c r="I212" s="3" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="J212" s="3" t="inlineStr"/>
+      <c r="J212" s="3" t="n"/>
       <c r="K212" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/queracomputinginc/jobs/5435901008</t>
@@ -20710,12 +20710,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R212" s="3" t="inlineStr"/>
+      <c r="R212" s="3" t="n"/>
     </row>
     <row r="213" ht="45" customHeight="1">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>bcec2bf18fc535c97569</t>
+          <t>208fc581712d77a3d27a</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -20743,14 +20743,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G213" s="3" t="inlineStr"/>
-      <c r="H213" s="3" t="inlineStr"/>
+      <c r="G213" s="3" t="n"/>
+      <c r="H213" s="3" t="n"/>
       <c r="I213" s="3" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="J213" s="3" t="inlineStr"/>
+      <c r="J213" s="3" t="n"/>
       <c r="K213" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/queracomputinginc/jobs/5435902008</t>
@@ -20808,10 +20808,104 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R213" s="3" t="inlineStr"/>
+      <c r="R213" s="3" t="n"/>
+    </row>
+    <row r="214" ht="45" customHeight="1">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>51473f34c12c0656d6a9</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T07:02:18.985042+00:00</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T03:36:16+00:00</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr">
+        <is>
+          <t>Citadel</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>Citadel — Data Science</t>
+        </is>
+      </c>
+      <c r="F214" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G214" s="3" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="H214" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I214" s="3" t="inlineStr"/>
+      <c r="J214" s="3" t="inlineStr"/>
+      <c r="K214" s="4" t="inlineStr">
+        <is>
+          <t>https://www.citadel.com/careers/details/sector-data-scientist-2027-intern-us</t>
+        </is>
+      </c>
+      <c r="L214" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M214" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N214" s="3" t="inlineStr">
+        <is>
+          <t>@ citadel.com
+Instagram
+N ( eEeNnTiSsST — (yD 7
+JWI LILIOL i a
+Job Description
+Citadel 2027 Sector Data Science Intern
+and analyzing large, unstructured data
+sets to generate new insights. Given the
+vast amount of data being produced,
+Citadal ic imnlameantina new recearch
+https://scontent-iad3-1.cdninstagram.com/v/t51.71878-15/828255498_2521217878376390_6913097123587374034_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5NTg4NDUzNTY3Nzc3NDk5Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=zpgXkesxBVMQ7kNvwEWu1tO&amp;_nc_oc=AdpQ8PCvluco3BFWAA7-wji79zzo--72G96gzyaMeUDU0y2JOKbB66ykQZpzM5LN5PY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;_nc_gid=IR7fTDpU5-QBp4aVuowAAA&amp;_nc_ss=7e3ba&amp;oh=00_AQMtp-N7qTfcR6nM0zZZE5AeMwuGvPRBpRgs6YGYSAJW2w&amp;oe=6ABFCC80
+https://scontent-iad3-1.cdninstagram.com/v/t51.71878-15/828255498_2521217878376390_6913097123587374034_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5NTg4NDUzNTY3Nzc3NDk5Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=zpgXkesxBVMQ7kNvwEWu1tO&amp;_nc_oc=AdpQ8PCvluco3BFWAA7-wji79zzo--72G96gzyaMeUDU0y2JOKbB66ykQZpzM5LN5PY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;_nc_gid=IR7fTDpU5-QBp4aVuowAAA&amp;_nc_ss=7e3ba&amp;oh=00_AQOsIQ5cglRnBO8OJ2qJoBzwfal5AGkt5S1bcJ6P2dHAng&amp;oe=6ABFCC80
+https://scontent-iad6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwE5pPvn&amp;_nc_oc=AdrJTJRUGtnd1eL-Dy1bHqDbSZRkMjXqdpcWkgIjc4fEFUixlz1TKtKrnoMdaSiVXn8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQOmtS9Bk1Wup4K5RarMEnVwXz_rxKe5n2TBHuA90GlKsQ&amp;oe=6ABFD7D9
+https://l.instagram.com/?u=https%3A%2F%2Fwww.citadel.com%2Fcareers%2Fdetails%2Fsector-data-scientist-2027-intern-us%2F%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAad3Hil5sL7U62mPvujZZYlh-Lj82gGRCCEKld4N2YbbiEhcc6F-4sVFQkEpTQ_aem_aZsl-ZIGXiH7WeX3DmIrig&amp;e=AUAf29q5N4NvU_pPwXS8xEr-ntkmNvIhJ3abEKBa-Fo5FGVMsNWxGz5L8Id-9T-RVeppJ51qwfkPmbZpCUWhvnvkSnz--rkdO56gq84aAA
+https://scontent-iad3-1.cdninstagram.com/o1/v/t2/f2/m78/AQP-7ctSj0muavSvpWOpsElGuMjcq4zxCpcqJyi4j_SqCyo9i7OANI9XIPcTpRsXDCtdxm6k8DBAufBU9dwXDxJJ-vc-kDgjImywaK8.mp4?_nc_cat=104&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;_nc_ohc=3zSO2OwjceAQ7kNvwHD4vBF&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg3NDE2MjI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=be00d32d1bf54dc4&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0Q2NEVCMUJGNENDQjQxMDZDNjEzODk1MzJDNURFMjkzX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkltStq-ehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=IR7fTDpU5-QBp4aVuowAAA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQO5ydITBpzuWMahL-NvPy2eiLECq6h5qtDeVPg7YDN8Wg&amp;oe=6ABBEF59</t>
+        </is>
+      </c>
+      <c r="O214" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P214" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q214" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R214" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R213"/>
+  <autoFilter ref="A1:R214"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -21222,6 +21316,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L212" r:id="rId407"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K213" r:id="rId408"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L213" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K214" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L214" r:id="rId411"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$218</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R214"/>
+  <dimension ref="A1:R218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20813,7 +20813,7 @@
     <row r="214" ht="45" customHeight="1">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>51473f34c12c0656d6a9</t>
+          <t>a511252824befede6d3b</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -20851,8 +20851,8 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="I214" s="3" t="inlineStr"/>
-      <c r="J214" s="3" t="inlineStr"/>
+      <c r="I214" s="3" t="n"/>
+      <c r="J214" s="3" t="n"/>
       <c r="K214" s="4" t="inlineStr">
         <is>
           <t>https://www.citadel.com/careers/details/sector-data-scientist-2027-intern-us</t>
@@ -20902,10 +20902,414 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R214" s="3" t="inlineStr"/>
+      <c r="R214" s="3" t="n"/>
+    </row>
+    <row r="215" ht="45" customHeight="1">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>f5fd748134b7f364c714</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T15:35:58.252265+00:00</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T13:16:03+00:00</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>Atlassian</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>Atlassian — Research</t>
+        </is>
+      </c>
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H215" s="3" t="inlineStr">
+        <is>
+          <t>2027, 2026</t>
+        </is>
+      </c>
+      <c r="I215" s="3" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="J215" s="3" t="inlineStr"/>
+      <c r="K215" s="4" t="inlineStr">
+        <is>
+          <t>https://campus-americas.icims.com/jobs/26270/research-intern,-2027-summer-u.s./job?mobile=true&amp;width=384&amp;height=693&amp;bga=true&amp;needsRedirect=false&amp;jan1offset=-480&amp;jun1offset=-420</t>
+        </is>
+      </c>
+      <c r="L215" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M215" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N215" s="3" t="inlineStr">
+        <is>
+          <t>Atlassian
+&lt; Back to Atlassian Careers
+Returning Candidate? Log back in!
+Research Intern, 2027 Summer U.S.
+US-WA-Seattle REQ-2026-1978
+Category Interns
+Overview
+Working at Atlassian
+Atlassians have the flexibility to work where they can
+collaborate most effectively with their team, whether
+at home, one of our global offices, or both. We hire in
+any country where we have a legal entity. Learn how
+we work at go.atlassian.com/distributed.
+Your Future Org
+(2 ATLASSIAN RESEARCH INTERN
+connections. This holisti empowers
+students to hit the groun and sets them up
+for a successful and impactful career at Atlassian!
+This role is located in the Seattle hub location. You
+must be willing and able to work out of this hub
+location to qualify.
+This position is not eligible for Fl and J1 students. It
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/825351997_1804103407599750_5408065891533440268_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5NjE3NjM1Mzk4NDkzODU4Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=WVUBMAA2fKoQ7kNvwH0Cyep&amp;_nc_oc=AdoNDgiOe25-Df1Sz9Y5aJtI5XUPD-KR4GTwbU0aAy2LIlBO372ppLq0wthuy3Jk17c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=8VT9HeIXJA_uwrx5yjrUyQ&amp;_nc_ss=7e3ba&amp;oh=00_AQOJYpu1jma_8NaYrx84MUlkzsaGmD8scX0BWwEt8b96bA&amp;oe=6AC05153
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/825351997_1804103407599750_5408065891533440268_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5NjE3NjM1Mzk4NDkzODU4Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=WVUBMAA2fKoQ7kNvwH0Cyep&amp;_nc_oc=AdoNDgiOe25-Df1Sz9Y5aJtI5XUPD-KR4GTwbU0aAy2LIlBO372ppLq0wthuy3Jk17c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=8VT9HeIXJA_uwrx5yjrUyQ&amp;_nc_ss=7e3ba&amp;oh=00_AQMu1ZQ9AsgFNH148QkCphkwrLsitP_uRH-NVApLvfpXTQ&amp;oe=6AC05153
+https://scontent-xxc1-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwFR3J8m&amp;_nc_oc=AdqPcbKYTpAxmV7nwBV79vzPDLsOp0sPk5_5nm8EMGfyQnP2qeuYY_IdtHFdYQDNI9Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQOEHM-yDfqODAD3h8C2eBjcy8UiQVgV1-x1GXgEvvmGPA&amp;oe=6AC04859
+https://l.instagram.com/?u=https%3A%2F%2Fcampus-americas.icims.com%2Fjobs%2F26270%2Fresearch-intern%2C-2027-summer-u.s.%2Fjob%3Fmobile%3Dtrue%26width%3D384%26height%3D693%26bga%3Dtrue%26needsRedirect%3Dfalse%26jan1offset%3D-480%26jun1offset%3D-420%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeRmPMJPXYPf1ABtm4AP9iwHCUJgQsPYyCbeckMcUS5Bn1720z6tnYmrDSRLg_aem_gelzdj29A3COF7xVrXFLCw&amp;e=AUBj-j07M9wEA1nOVWxqQ3hGMuQfd0hVbEym-r7WryCtDgeXluB4M29yJrHMJOOs5-GO0ZnCFM1Oz4UAULKu2Mdhi71DNewpkdd94nTiPg
+https://scontent-xxc1-1.cdninstagram.com/o1/v/t2/f2/m78/AQP3UHGZvf94WsozV_WewTI3YTYMscKIErjemYAu3zIdLOZmn0ohHNO8IhLuLVEXLx6aXMvS299bmFSyZ3RzJl7H5uJC_COA7SbBn5g.mp4?_nc_cat=104&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ohc=-WL-vXNYvlYQ7kNvwHjWBRr&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg3OTUzMTk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=1eb1c5ab346c616&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0REMUY2QTVEQ0RFQzQxMDFBQTg5MDRFNjNBNzEyQTExX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk3423u-qhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=8VT9HeIXJA_uwrx5yjrUyQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQPkIYIJYSE5LFuXq23C5DZ7nMcJjCaSBHbS1sLWrToPcQ&amp;oe=6ABC53DD</t>
+        </is>
+      </c>
+      <c r="O215" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P215" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q215" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R215" s="3" t="inlineStr"/>
+    </row>
+    <row r="216" ht="45" customHeight="1">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>540f744a0eede890c9a3</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T15:35:59.503184+00:00</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T13:17:01+00:00</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr"/>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr"/>
+      <c r="H216" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I216" s="3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J216" s="3" t="inlineStr"/>
+      <c r="K216" s="4" t="inlineStr">
+        <is>
+          <t>https://www.foxcareers.com/Search/JobDetail/R50033968?source=zero2sudo</t>
+        </is>
+      </c>
+      <c r="L216" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M216" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N216" s="3" t="inlineStr">
+        <is>
+          <t>x @ foxcareers.com SG
+Ins vr
+FOX CAREERS =
+SUMMER 2027 FOX
+TECHNOLOGY
+INTERNSHIP
+PROGRAM - NEW
+YORK, NY
+Job Number: R50033968
+Brand Fox Corporation
+Job Type: Internships
+_® FOXCAREERS.COM
+Location New York, N
+Job Posting Date: Sept 8, 2026
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/825277170_1428654315381305_5009238193929980741_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5NjE3Njg0MTA0MzgyNzYyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Qr0BLmXzPxYQ7kNvwF1sUVw&amp;_nc_oc=AdqYJ3qZcAKBKrg9tzgBxnDEjBJV59WXYLC8iiQf5SN2_ldnV6yaWkzSygxT9S0ouG4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=8VT9HeIXJA_uwrx5yjrUyQ&amp;_nc_ss=7e3ba&amp;oh=00_AQMQYVH5MeNuNDkN9PBWljargS3ymLDiCB8vwgNsGX3tIg&amp;oe=6AC0501A
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/825277170_1428654315381305_5009238193929980741_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5NjE3Njg0MTA0MzgyNzYyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Qr0BLmXzPxYQ7kNvwF1sUVw&amp;_nc_oc=AdqYJ3qZcAKBKrg9tzgBxnDEjBJV59WXYLC8iiQf5SN2_ldnV6yaWkzSygxT9S0ouG4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=8VT9HeIXJA_uwrx5yjrUyQ&amp;_nc_ss=7e3ba&amp;oh=00_AQOz4DHOM7-mEqadnQPWatfRhD_vZ3xAvOQLGzgr5oxSyg&amp;oe=6AC0501A
+https://scontent-xxc1-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwFR3J8m&amp;_nc_oc=AdqPcbKYTpAxmV7nwBV79vzPDLsOp0sPk5_5nm8EMGfyQnP2qeuYY_IdtHFdYQDNI9Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQOEHM-yDfqODAD3h8C2eBjcy8UiQVgV1-x1GXgEvvmGPA&amp;oe=6AC04859
+https://l.instagram.com/?u=https%3A%2F%2Fwww.foxcareers.com%2FSearch%2FJobDetail%2FR50033968%3Fsource%3Dzero2sudo%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeeBxvwAcVjFUCsA5hWPTWJeJE5n8NtAIml1ZedRQYkfQo46Wiib2bVUtdiRg_aem_3CMEVLcFE8RYvzWpTUgNZg&amp;e=AUDjEf8ncWIg4IHAWlW3q6SvBCr1DTKDn5_278m7THuQ4LTb-0NBCB7_iP3JqOSZVaB06YkhLJkvXOX5SnZpsPKfQUuY5ErSqVrhSeDzsw
+https://scontent-xxc1-1.cdninstagram.com/o1/v/t2/f2/m78/AQM7SfsavF9F0Yl-JdxZZtLJN440U63-N8o3DxxZMOUIrtbxntFJVl5InWhtXv9P2O1oshAoOUu_DP7n4hZPV7a6HANRoQWdgxI2R80.mp4?_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ohc=ueOKyZVpwoAQ7kNvwHeZTdD&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg3OTU0NDI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=a45a8882022a818d&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0RDNEM0RENGOENCNzE3NkZCMkJEMEM0Rjk0MEYzNEE5X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbksrSsvOqhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=8VT9HeIXJA_uwrx5yjrUyQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQMPmdI2xvDzsvUN9ggnj0ROmxTW3QVZkkul2ex2GKrz_Q&amp;oe=6ABC729D</t>
+        </is>
+      </c>
+      <c r="O216" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P216" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q216" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R216" s="3" t="inlineStr"/>
+    </row>
+    <row r="217" ht="45" customHeight="1">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>eadfcb5afc5520ec913e</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T15:36:00.785638+00:00</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T13:21:15+00:00</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr"/>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="inlineStr"/>
+      <c r="H217" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I217" s="3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J217" s="3" t="inlineStr"/>
+      <c r="K217" s="4" t="inlineStr">
+        <is>
+          <t>https://www.foxcareers.com/Search/JobDetail/R50033981?source=zero2sudo</t>
+        </is>
+      </c>
+      <c r="L217" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M217" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N217" s="3" t="inlineStr">
+        <is>
+          <t>x @ foxcareers.com C:
+In AS
+| FOX CAREERS =
+SUMMER 2027 FOX
+NEWS MEDIA
+INTERNSHIP
+PROGRAM - DATA
+ANALYTICS - NEW
+YORK
+Job Number: R50033981
+Brand Fox News Media
+Job Type: Internships
+@ FOXCAREERS.COM
+Location New York,
+Job Posting Date: Sept 8, 2026
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/825326729_960686479771458_360529895543489077_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5NjE3ODk3MzM2OTY5MTM3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=0QcsmBTKnSAQ7kNvwENcwOA&amp;_nc_oc=AdrUkHfaIOispAZMZJmEGpR7nYoA1V5F6CaRaJN9QmFyW-MNHTb2X3aDLg40w4iwsmY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=8VT9HeIXJA_uwrx5yjrUyQ&amp;_nc_ss=7e3ba&amp;oh=00_AQMY3dBRul465Yt82I3EfWP1NOM9Cm1n40CRwJmv-ZnJ7Q&amp;oe=6AC056FA
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/825326729_960686479771458_360529895543489077_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5NjE3ODk3MzM2OTY5MTM3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=0QcsmBTKnSAQ7kNvwENcwOA&amp;_nc_oc=AdrUkHfaIOispAZMZJmEGpR7nYoA1V5F6CaRaJN9QmFyW-MNHTb2X3aDLg40w4iwsmY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=8VT9HeIXJA_uwrx5yjrUyQ&amp;_nc_ss=7e3ba&amp;oh=00_AQOr4QEIO92tw40diAjf_LAa45la6wi405MdSwc-H9Jtmw&amp;oe=6AC056FA
+https://scontent-xxc1-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwFR3J8m&amp;_nc_oc=AdqPcbKYTpAxmV7nwBV79vzPDLsOp0sPk5_5nm8EMGfyQnP2qeuYY_IdtHFdYQDNI9Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQOEHM-yDfqODAD3h8C2eBjcy8UiQVgV1-x1GXgEvvmGPA&amp;oe=6AC04859
+https://l.instagram.com/?u=https%3A%2F%2Fwww.foxcareers.com%2FSearch%2FJobDetail%2FR50033981%3Fsource%3Dzero2sudo%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacCdMapILScK4j95enNdW8ceFu7SE3dVE4IVyZwmG36v5eaFDzuOy5pKSd2Ug_aem_3Ev21aj8lQit-IolIKcaSQ&amp;e=AUBARL-2ZMbI7ZPqgYnQU6CHi9jffvF2YEt4wzUiueODW-HD7PH9jb4stBEV5oxvWYGwzCQJH6wWSY7XtjM9OfxrTjCQJ58fWaY6yOvlzg
+https://scontent-xxc1-1.cdninstagram.com/o1/v/t2/f2/m78/AQMQ7XEg1ERa6HPI7_YrqIicYngVwtv6k3WMLREM8e-x5i0KA-rMrW1yJmbfZ2fPgFuwxzEnl-FfyjzyI8rsFxjIZDq_LwgEeXYVbFk.mp4?_nc_cat=110&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ohc=gfJCymLxLZwQ7kNvwHmYLc6&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg3OTU4Mjk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=7e426b194c65cef8&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzA3NDQ4NDFFRkUwNDZBM0UzMTFGNzVGNzEwMkE4NEJCX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkzb2dv-qhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=8VT9HeIXJA_uwrx5yjrUyQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQPkKYBbp-0LwyuoCekdB7RY0rzbdW3m7JSC4yFbZZGWeA&amp;oe=6ABC5B6B</t>
+        </is>
+      </c>
+      <c r="O217" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P217" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q217" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R217" s="3" t="inlineStr"/>
+    </row>
+    <row r="218" ht="45" customHeight="1">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>5b22e8d5f944b6bb723d</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T15:36:05.997635+00:00</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T13:37:35+00:00</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>Philips — Product Management</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="H218" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I218" s="3" t="inlineStr"/>
+      <c r="J218" s="3" t="inlineStr"/>
+      <c r="K218" s="4" t="inlineStr">
+        <is>
+          <t>https://philips.wd3.myworkdayjobs.com/jobs-and-careers/job/Bothell-Washington-United-States/Intern---Digital-Healthtech-Product-Management---Bothell--WA---Summer-2027_585564</t>
+        </is>
+      </c>
+      <c r="L218" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M218" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N218" s="3" t="inlineStr">
+        <is>
+          <t>Intern — Digital Healthtech
+Product Management -—
+Bothell, WA — Summer 2027
+f
+|
+Apply
+Bothell, Washington, United States
+Full time
+Posted Today
+[tI © Eh ©
+End Date: October 16, 2026 (17 days left to
+apply)
+[=] 585564
+Job Title ese
+Job Description
+Intern — Digital Health duct
+Management - Bothell, WA — Summer 2027
+Are you interested in an internship opportunity
+with Philips? We welcome individuals who are
+currently pursuing an undergraduate (BS)
+and/or graduate (MS) degree to participate in
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/829226077_4419775355002648_7241793010173907730_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5NjE4NzE5MzY1OTc2NzY4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=sPB4lYQ2KjwQ7kNvwFTl3ja&amp;_nc_oc=AdoDrboyBF0F-_Joj0Sco0dGfwBnVyf49DhbEEC49wDlfKRV-Z-sKsl_RC0HdjBCRHc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=8VT9HeIXJA_uwrx5yjrUyQ&amp;_nc_ss=7e3ba&amp;oh=00_AQN2y-BIYimJrny90YJb0pqhKRUQGQXsppeFSHvZNBXLAw&amp;oe=6AC05807
+https://scontent-xxc1-1.cdninstagram.com/v/t51.71878-15/829226077_4419775355002648_7241793010173907730_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5NjE4NzE5MzY1OTc2NzY4Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=sPB4lYQ2KjwQ7kNvwFTl3ja&amp;_nc_oc=AdoDrboyBF0F-_Joj0Sco0dGfwBnVyf49DhbEEC49wDlfKRV-Z-sKsl_RC0HdjBCRHc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_gid=8VT9HeIXJA_uwrx5yjrUyQ&amp;_nc_ss=7e3ba&amp;oh=00_AQPhePc7ngd4yTCgY68O0nh9HqtppTr11gTMKVfe7Pvvmw&amp;oe=6AC05807
+https://scontent-xxc1-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwFR3J8m&amp;_nc_oc=AdqPcbKYTpAxmV7nwBV79vzPDLsOp0sPk5_5nm8EMGfyQnP2qeuYY_IdtHFdYQDNI9Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQOEHM-yDfqODAD3h8C2eBjcy8UiQVgV1-x1GXgEvvmGPA&amp;oe=6AC04859
+https://l.instagram.com/?u=https%3A%2F%2Fphilips.wd3.myworkdayjobs.com%2Fjobs-and-careers%2Fjob%2FBothell-Washington-United-States%2FIntern---Digital-Healthtech-Product-Management---Bothell--WA---Summer-2027_585564%2F%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadrnLG8jaZ6gv8Us26vkUVyS-7qsxU0L2cRouA12vrYkrLN8HVJn89hmXPdDg_aem_0yO8n10ryj5u9c8OLBneDA%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUDlzGETt1ll4qYhuIOJFrRAPzsfFQ7bH-l2CorIvNalDsJFKD0LRJQ5QKQx8I8TQa80Zs6qhjN17zC4q-tFaV2nH1oPuBvgNmZwJ8GLZQ
+https://scontent-xxc1-1.cdninstagram.com/o1/v/t2/f2/m78/AQMd-LAIR5_AjICDfLhcr_tTJO8u7DyyP6tSIlauPZ1DHWflZMaDWybJ9nwZCB4AcciDNKAWABgNQdm--Fa3kAIr65kfMYMYpo8qtKs.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-xxc1-1.cdninstagram.com&amp;_nc_ohc=opNT2MCWL-wQ7kNvwHQCBV-&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg3OTc1MTg2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=6ff48a331864afb4&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzMyNDI5QTJFMjRDRUI5OEQ1N0JEMzU4N0EzMEQ0NTkxX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkrp7oy-qhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=8VT9HeIXJA_uwrx5yjrUyQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQO5GVL-C5tbmIBrJ0DQSLVoNjADoUxnMxrj_R2sDC_2qA&amp;oe=6ABC5965</t>
+        </is>
+      </c>
+      <c r="O218" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P218" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q218" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R218" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R214"/>
+  <autoFilter ref="A1:R218"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -21318,6 +21722,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L213" r:id="rId409"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K214" r:id="rId410"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L214" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K215" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L215" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K216" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L216" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K217" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L217" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K218" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L218" r:id="rId419"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$218</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$231</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R218"/>
+  <dimension ref="A1:R231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20907,7 +20907,7 @@
     <row r="215" ht="45" customHeight="1">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>f5fd748134b7f364c714</t>
+          <t>17aa7677af15157b2675</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -20950,7 +20950,7 @@
           <t>Seattle</t>
         </is>
       </c>
-      <c r="J215" s="3" t="inlineStr"/>
+      <c r="J215" s="3" t="n"/>
       <c r="K215" s="4" t="inlineStr">
         <is>
           <t>https://campus-americas.icims.com/jobs/26270/research-intern,-2027-summer-u.s./job?mobile=true&amp;width=384&amp;height=693&amp;bga=true&amp;needsRedirect=false&amp;jan1offset=-480&amp;jun1offset=-420</t>
@@ -21012,12 +21012,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R215" s="3" t="inlineStr"/>
+      <c r="R215" s="3" t="n"/>
     </row>
     <row r="216" ht="45" customHeight="1">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>540f744a0eede890c9a3</t>
+          <t>d0ccca28380449b5c5c0</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -21030,7 +21030,7 @@
           <t>2026-09-28T13:17:01+00:00</t>
         </is>
       </c>
-      <c r="D216" s="3" t="inlineStr"/>
+      <c r="D216" s="3" t="n"/>
       <c r="E216" s="3" t="inlineStr">
         <is>
           <t>Internship</t>
@@ -21041,7 +21041,7 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G216" s="3" t="inlineStr"/>
+      <c r="G216" s="3" t="n"/>
       <c r="H216" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
@@ -21052,7 +21052,7 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="J216" s="3" t="inlineStr"/>
+      <c r="J216" s="3" t="n"/>
       <c r="K216" s="4" t="inlineStr">
         <is>
           <t>https://www.foxcareers.com/Search/JobDetail/R50033968?source=zero2sudo</t>
@@ -21106,12 +21106,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R216" s="3" t="inlineStr"/>
+      <c r="R216" s="3" t="n"/>
     </row>
     <row r="217" ht="45" customHeight="1">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>eadfcb5afc5520ec913e</t>
+          <t>1ea072c1a42a1185533a</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -21124,7 +21124,7 @@
           <t>2026-09-28T13:21:15+00:00</t>
         </is>
       </c>
-      <c r="D217" s="3" t="inlineStr"/>
+      <c r="D217" s="3" t="n"/>
       <c r="E217" s="3" t="inlineStr">
         <is>
           <t>Internship</t>
@@ -21135,7 +21135,7 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G217" s="3" t="inlineStr"/>
+      <c r="G217" s="3" t="n"/>
       <c r="H217" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
@@ -21146,7 +21146,7 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="J217" s="3" t="inlineStr"/>
+      <c r="J217" s="3" t="n"/>
       <c r="K217" s="4" t="inlineStr">
         <is>
           <t>https://www.foxcareers.com/Search/JobDetail/R50033981?source=zero2sudo</t>
@@ -21201,12 +21201,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R217" s="3" t="inlineStr"/>
+      <c r="R217" s="3" t="n"/>
     </row>
     <row r="218" ht="45" customHeight="1">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>5b22e8d5f944b6bb723d</t>
+          <t>1095f932e1842e131569</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -21244,8 +21244,8 @@
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I218" s="3" t="inlineStr"/>
-      <c r="J218" s="3" t="inlineStr"/>
+      <c r="I218" s="3" t="n"/>
+      <c r="J218" s="3" t="n"/>
       <c r="K218" s="4" t="inlineStr">
         <is>
           <t>https://philips.wd3.myworkdayjobs.com/jobs-and-careers/job/Bothell-Washington-United-States/Intern---Digital-Healthtech-Product-Management---Bothell--WA---Summer-2027_585564</t>
@@ -21306,10 +21306,1256 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R218" s="3" t="inlineStr"/>
+      <c r="R218" s="3" t="n"/>
+    </row>
+    <row r="219" ht="45" customHeight="1">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>2edcdbaf6cc387f6e8b3</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T22:07:38.505292+00:00</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T17:22:31+00:00</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>NVIDIA — Product Management</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="H219" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I219" s="3" t="inlineStr"/>
+      <c r="J219" s="3" t="inlineStr"/>
+      <c r="K219" s="4" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/nvidia-canada-2026</t>
+        </is>
+      </c>
+      <c r="L219" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N219" s="3" t="inlineStr">
+        <is>
+          <t>Tomorrow is the day! NVIDIA University
+Recruiting Insights (Canada Only) is almost
+here, and we have an incredible session lined
+up that you won't want to miss.
+Here's everything you need to join:
+Date &amp; Time: Sep 29, 2026, 12: fg ,\4 - 01:00
+PM | EDT |
+This event is designed for students currently
+enrolled at a Canadian university. If that doesn't
+apply to you, we encourage you to explore our
+other events that may be a better fit.
+Warm regards,
+University Recruiting Campus Manager
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/829072595_1359992272603082_1869405475139629499_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5NjMwMDQwODQ0NDY4NjAzMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=QjbeyA6svn8Q7kNvwHeMMXY&amp;_nc_oc=AdovjyjACyXTapFQkwzkRvTHFVgc5anoVSyn_akabcVVWPm_g8O59sPVX020qE8hVzw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQOqZMKbYg6noyCEbju6O0LUl9g0j1A_vzO-_Yc3afbMww&amp;oe=6AC0B7AC
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/829072595_1359992272603082_1869405475139629499_n.jpg?stp=dst-jpg_e15_p240x240_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5NjMwMDQwODQ0NDY4NjAzMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=QjbeyA6svn8Q7kNvwHeMMXY&amp;_nc_oc=AdovjyjACyXTapFQkwzkRvTHFVgc5anoVSyn_akabcVVWPm_g8O59sPVX020qE8hVzw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQMAsYKe4KFtXY3ebB_J0ALPGuRwbvVMvxBHdVQ59BG9ng&amp;oe=6AC0B7AC
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwHf6ioD&amp;_nc_oc=AdovB9AKcBUzTua_q6lzURFZRtyhShbn0UZEBvsZT5_scG8HL7MoD4TmphIUTCCWOjQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQMKrRkmuIoydkGGWVFHgekEqaKUCNzkCQHc9GSOTGiPVA&amp;oe=6AC0B8D9
+https://l.instagram.com/?u=https%3A%2F%2Ftinyurl.com%2Fnvidia-canada-2026%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaffQsZZ1ihmtKUwdX7d30DjyNZjRnJrhe-kNlhZsPfRhYvzy-CWxQ-NXRaKAw_aem_EzaS-fk9flt_GJh4rGqgOA&amp;e=AUA0leeiQDcgtwVDTWzCJG43BW_wlGoyKuyR9a4AzC-HqsoUAj6rS7YtlWPwiAQ899HvddEIQ9HpMloy4K9ZASiqd8tdSe85FJCLtL6SOw
+https://scontent-sjc6-1.cdninstagram.com/o1/v/t2/f2/m78/AQNW3FRz9VKBqb1GN1x_1h-SdO_JZoMjIdhAe6ATJRLSimnhHRtkLXBaliNDWLAeX8_u0NZwT_Bthbje4pXHs-80lPj-OKOTz2o6-5I.mp4?_nc_cat=102&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ohc=7aaZECh47NgQ7kNvwGu7UR7&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg4MzAwNzE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=caa0cd4f7343a965&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzQwNEM5RTczNTFGMEM4RDE4NUNFNTgzQTkyNTFDREIxX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkn5mtvuyhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQM4DkQiQEqp2MgTjBfNvmtYD_iF8ph0mZ_Pq1jmACvFqA&amp;oe=6ABCBEE3</t>
+        </is>
+      </c>
+      <c r="O219" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P219" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q219" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R219" s="3" t="inlineStr"/>
+    </row>
+    <row r="220" ht="45" customHeight="1">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>331798a30b4131c3cb8b</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T22:07:42.931643+00:00</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T17:30:31+00:00</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>Meta — Data Science, Data Engineering</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr">
+        <is>
+          <t>Data Science, Data Engineering</t>
+        </is>
+      </c>
+      <c r="H220" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I220" s="3" t="inlineStr">
+        <is>
+          <t>Menlo Park</t>
+        </is>
+      </c>
+      <c r="J220" s="3" t="inlineStr"/>
+      <c r="K220" s="4" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/profile/job_details/1373603594867455</t>
+        </is>
+      </c>
+      <c r="L220" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M220" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N220" s="3" t="inlineStr">
+        <is>
+          <t>@ metacareers.com C+:
+Instagran
+OY Meta
+Do
+&lt; Back to Jobs QO
+Data Engineer Intern,
+Product Analytics
+(Summer 2027)
+Menlo Park, CA +2 locations
+Data Engineering +2more
+Apply now
+Data Engineers at Meta shape the future of
+people-facing and business-facing products
+we build across our entire familv of
+(2) META DATA ENGINEER INTERN!!!
+PreeVeaMss. EWU COLE IVINttto UbiMm Ut tary Liwvul
+mindset will be utge ing and
+building some of t ost extensive
+data sets, helping t eriences for
+billions of people and hundreds of millions of
+businesses worldwide. A
+Ae
+In this role, you will collaborate with sor.ware
+engineering, data science, and product
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/828413509_1302669261871433_4960646730205485217_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5NjMwNDQzNTEzNTI4NDg0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=ISRh1eO7I7wQ7kNvwEa1Wt-&amp;_nc_oc=AdrACgYYEuD1UTqvduT8Xt1SfRDiRCzRUt0xKrW-7jmYESGTXtV-5ceqoMTCTwqTq2g&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQMyrjNJUEeqhX_16sOBjdkqIP2Rlu__uBuGp_43CHt0Pg&amp;oe=6AC0CFD4
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/828413509_1302669261871433_4960646730205485217_n.jpg?stp=dst-jpg_e15_p240x240_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5NjMwNDQzNTEzNTI4NDg0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=ISRh1eO7I7wQ7kNvwEa1Wt-&amp;_nc_oc=AdrACgYYEuD1UTqvduT8Xt1SfRDiRCzRUt0xKrW-7jmYESGTXtV-5ceqoMTCTwqTq2g&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQPbJ1bjSEWSD0r5cYXWY2dByfhEnaCNtqV660RWUvDuFw&amp;oe=6AC0CFD4
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwHf6ioD&amp;_nc_oc=AdovB9AKcBUzTua_q6lzURFZRtyhShbn0UZEBvsZT5_scG8HL7MoD4TmphIUTCCWOjQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQMKrRkmuIoydkGGWVFHgekEqaKUCNzkCQHc9GSOTGiPVA&amp;oe=6AC0B8D9
+https://l.instagram.com/?u=https%3A%2F%2Fwww.metacareers.com%2Fprofile%2Fjob_details%2F1373603594867455%2F%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAace8npHmcNrSybPdpzZGg-RNtk60f8ddcRM8UHxnfwnpQZq4F128e2BOwuuiQ_aem_cgtasVVJGYbipC_T4Xhf4g&amp;e=AUBwvpJZCvMhkdq0eyUHxz_l5ajOwXySao_6V2yfNenwUvnqlCupmE8BzgyqwDXT7Evb0yF4d2nogp4Hh8jeSdK-WCsiia7x8w3W_WBazg
+https://scontent-sjc6-1.cdninstagram.com/o1/v/t2/f2/m78/AQPvthzweoNe9dDSgIdabrIEOSX6GMXECPfJe2Ioc5Ue1N0kW7iKf9GwWJMJeRsYCWS2hpIVMF366h5Qrp34mVSmOJ7JvdDt_D4RSmw.mp4?_nc_cat=104&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ohc=UFvOWztUAsEQ7kNvwGFnaAs&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg4MzA4Njk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=81ab6ed527700396&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzM2NEU2OEMxRURCQkM0QjVBNjI0RTlCODY3MTc4NzhGX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkrZ2mxOyhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQMqtj0sVAHNogEIhd1NlgxE4Vq1ZJHlmFjcTU3dXqVrwg&amp;oe=6ABCBE3D</t>
+        </is>
+      </c>
+      <c r="O220" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P220" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q220" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R220" s="3" t="inlineStr"/>
+    </row>
+    <row r="221" ht="45" customHeight="1">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>7c0a86e1558a98d88207</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T22:07:44.967539+00:00</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T17:41:02+00:00</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>Underarmour</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>Underarmour — Internship</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="inlineStr"/>
+      <c r="H221" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I221" s="3" t="inlineStr"/>
+      <c r="J221" s="3" t="inlineStr"/>
+      <c r="K221" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.underarmour.com/job/Baltimore-2027-Summer-Internship%2C-Business-Analytics-MD-21230/1434332500?feedId=346600&amp;JobPipeline=zero2sudo</t>
+        </is>
+      </c>
+      <c r="L221" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M221" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N221" s="3" t="inlineStr">
+        <is>
+          <t>ial] careers.underarmour.com
+2027 Summer Internship,
+Business Analytics
+Under Armour has one mission: to make you better.
+We have a commitment to innovation that lies at
+the heart of everything we do, not just for our
+athletes but also for our teammates. As a global
+(2) CAREERS.UNDERARMOUR.COM
+and are grounded in o inspire you with
+performance solutions knew you needed
+but can't imagine living
+Position Summary
+The Rookie Program is designed for students who
+are ready to learn, lead, and make an impact.
+Throughout the summer, you'll take ownership of a
+business-critical project, collaborate with teams
+across the organization, and work closely with a
+dedicated leaders and mentors. From candid
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/829602631_2580840955750987_5231463535505560654_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5NjMwOTcyMzU1NjkwNjkyMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=1fhrxUprH1AQ7kNvwF7aKID&amp;_nc_oc=Adpy8xgjD5PUac3fjiXTw6TzQOVRjuUv8tPE1ABqn4MruxI1EwebrkYlYOoyX5ydemM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQOenRcMIqPRgsGPbtvOAxDrBoRaXwM0XEHKpOYDAwiHXw&amp;oe=6AC0AAEC
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/829602631_2580840955750987_5231463535505560654_n.jpg?stp=dst-jpg_e15_p240x240_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5NjMwOTcyMzU1NjkwNjkyMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=1fhrxUprH1AQ7kNvwF7aKID&amp;_nc_oc=Adpy8xgjD5PUac3fjiXTw6TzQOVRjuUv8tPE1ABqn4MruxI1EwebrkYlYOoyX5ydemM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQP_xwVCZVK0mMHwWoRkl9BXP5kK25Dw51dZehFbBOglbA&amp;oe=6AC0AAEC
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwHf6ioD&amp;_nc_oc=AdovB9AKcBUzTua_q6lzURFZRtyhShbn0UZEBvsZT5_scG8HL7MoD4TmphIUTCCWOjQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQMKrRkmuIoydkGGWVFHgekEqaKUCNzkCQHc9GSOTGiPVA&amp;oe=6AC0B8D9
+https://l.instagram.com/?u=https%3A%2F%2Fcareers.underarmour.com%2Fjob%2FBaltimore-2027-Summer-Internship%252C-Business-Analytics-MD-21230%2F1434332500%2F%3FfeedId%3D346600%26utm_source%3Dzero2sudo%26JobPipeline%3Dzero2sudo%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafs_3wl6WCfESompw2a-0rvBhMl5sV44guHNbrw86wYaWo3PuVgDe60rDx5bQ_aem_lX8PTn1ungKhUr0-WEtKaw&amp;e=AUB71DB4bVRt1LRQck3-98cdvFultCgk_l1Dg_0_BmpXIinsluAQFIT2lyHKhVUJTwVYa4R0UTkStjn49jUEM_cDGjkqW2oozfL6C4oi3Q
+https://scontent-sjc3-1.cdninstagram.com/o1/v/t2/f2/m78/AQMKCr_zcq7LgWPQdg3vJpmUjHSKK1PDZ6_dAyt0C1P_5-apX6QTGUkOroeX_ZleKqcB2Y3ZqgkU2ZobEatUGMX-_3dcc9V4o1AAbb4.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_ohc=9DVhhhlDE-8Q7kNvwHl-le5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg4MzE2NTU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=fd7537564f1ff4c6&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzhDNDJGQ0QzMUVDQjNCRkFBMDFFOENGMTgyOTk3NjlDX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkz-iTyuyhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQOcSYJQk11N3trsPwaHeXG8lu92EAk_KhOnAfznyT51CA&amp;oe=6ABCD52C</t>
+        </is>
+      </c>
+      <c r="O221" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P221" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q221" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R221" s="3" t="inlineStr"/>
+    </row>
+    <row r="222" ht="45" customHeight="1">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>25deccc68b15cbf2ecd8</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T22:07:45.976865+00:00</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T17:42:13+00:00</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>Underarmour</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>Underarmour — Internship</t>
+        </is>
+      </c>
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="inlineStr"/>
+      <c r="H222" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I222" s="3" t="inlineStr"/>
+      <c r="J222" s="3" t="inlineStr"/>
+      <c r="K222" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.underarmour.com/job/Baltimore-2027-Summer-Internship%2C-AI-Automation-MD-21230/1434354900</t>
+        </is>
+      </c>
+      <c r="L222" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M222" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N222" s="3" t="inlineStr">
+        <is>
+          <t>2027 Summer Internship, Al
+Automation
+2027 Summer Internship, Al
+Automation
+https://careers.underarmour.com
+2027 Al Automation Intern
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/825324380_1566503114631981_5237115421600210091_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5NjMxMDMyMTUwNTg4NTgwNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=lhMtJL59n5MQ7kNvwGxxAMG&amp;_nc_oc=Adoska9amb57hXcIm2M_36Nnqj41EWHRMQSv8XuXoeR-ifDsYEcwSPoMR64CZZWCFAc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQOqSjWXTBd2E2M5nTARLOYwADj33G9Kz3KJf2fImP5r5w&amp;oe=6AC0D26C
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/825324380_1566503114631981_5237115421600210091_n.jpg?stp=dst-jpg_e15_p240x240_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5NjMxMDMyMTUwNTg4NTgwNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=lhMtJL59n5MQ7kNvwGxxAMG&amp;_nc_oc=Adoska9amb57hXcIm2M_36Nnqj41EWHRMQSv8XuXoeR-ifDsYEcwSPoMR64CZZWCFAc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQM_coDPVFIGbmIEAW_fqqPcscEpZztjDBUXkLRLtPqRKg&amp;oe=6AC0D26C
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwHf6ioD&amp;_nc_oc=AdovB9AKcBUzTua_q6lzURFZRtyhShbn0UZEBvsZT5_scG8HL7MoD4TmphIUTCCWOjQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQMKrRkmuIoydkGGWVFHgekEqaKUCNzkCQHc9GSOTGiPVA&amp;oe=6AC0B8D9
+https://l.instagram.com/?u=https%3A%2F%2Fcareers.underarmour.com%2Fjob%2FBaltimore-2027-Summer-Internship%252C-AI-Automation-MD-21230%2F1434354900%2F%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafLK0B1315wRKH6B4VhtJxnBMUU_Ithoj8Jfw5ZwPSLWiMgpYJvnptUOqO09Q_aem_ELw4aIjlJUxbqADFJvsGvA&amp;e=AUA_ZVCIiuiCRIkQ-p-lBVYN6t6lwqHWJhLpJAoUfebkak2AEMbXz3l6Ngz8m7uFdE1CGQ5_SgFFSyQaIBHud6Vg7d8Vw5geMa7b1JfPFg
+https://scontent-sjc3-1.cdninstagram.com/o1/v/t2/f2/m78/AQMn6qDkkSKCmcNOHB_kWSMLDEA2AkQtVjGppw1FV75i5XdECHgAy9a75bqh82_VjzZJ3pp_3soVikibeKZkyMMkao5pWl_uWj_tqq4.mp4?_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_ohc=n42SHdpBihgQ7kNvwF6ACtA&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg4MzE3OTk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=dbebf87d17e66027&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzFENEZENTgxRjRCM0MxQ0ZFMDYwRUVEQjdGRjg5M0IyX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk35Kdy-yhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQNMVlS-XFit0K4koxUnRH-1QyXsx5xzbg97Vstsu57Omw&amp;oe=6ABCB45E</t>
+        </is>
+      </c>
+      <c r="O222" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P222" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q222" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R222" s="3" t="inlineStr"/>
+    </row>
+    <row r="223" ht="45" customHeight="1">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>ce5df30e971376d453f1</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T22:07:48.044503+00:00</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T17:45:06+00:00</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>Arcteryx.com</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>Arcteryx.com — Internship</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="inlineStr"/>
+      <c r="H223" s="3" t="inlineStr"/>
+      <c r="I223" s="3" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="J223" s="3" t="inlineStr"/>
+      <c r="K223" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/arcteryx.com/826dc4d8-f91e-4893-b8d6-56706194edfb</t>
+        </is>
+      </c>
+      <c r="L223" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M223" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N223" s="3" t="inlineStr">
+        <is>
+          <t>if you get this arcteryx internship and take me to your
+corporate store i will deadass find you referrals for
+your next job i spend too much $ here
+also shoutout ryan at drop day LOL ay SE
+ARC'TERYX - People Data
+Analyst Co-Op Student
+Department: People &amp; Culture
+Reports to: Senior Data Analyst,
+People Analytics Location: North
+Vancouver, BC - This role is primarily
+based out of our North Vancouver
+office, and is open to hybrid remote
+work Work Arrangement: Flexible,
+between in-office and home Pay
+Range:$42,100 - $55,100; pay is....
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/829340299_2108470953208162_1345573709483264027_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5NjMxMTc3MjA1NTE1Mjc1Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=P2HkhmCb-FAQ7kNvwFyw8tf&amp;_nc_oc=Adr0imxHA7dCNLQAkTUAga0KZtfbYRv6rNHfx2NrtEFN1zzSIOjVCSiXezI_RlAtjEA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQM1-ZTFbkXXU3gxP38_wkLpKWSNoNTRx-BWq4rn9kEq8w&amp;oe=6AC0D184
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/829340299_2108470953208162_1345573709483264027_n.jpg?stp=dst-jpg_e15_p240x240_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5NjMxMTc3MjA1NTE1Mjc1Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=P2HkhmCb-FAQ7kNvwFyw8tf&amp;_nc_oc=Adr0imxHA7dCNLQAkTUAga0KZtfbYRv6rNHfx2NrtEFN1zzSIOjVCSiXezI_RlAtjEA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQMBSdpbKoevPstKwNzE4vegR6mJqNwKgv_rAofqOEvyrQ&amp;oe=6AC0D184
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwHf6ioD&amp;_nc_oc=AdovB9AKcBUzTua_q6lzURFZRtyhShbn0UZEBvsZT5_scG8HL7MoD4TmphIUTCCWOjQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQMKrRkmuIoydkGGWVFHgekEqaKUCNzkCQHc9GSOTGiPVA&amp;oe=6AC0B8D9
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.lever.co%2Farcteryx.com%2F826dc4d8-f91e-4893-b8d6-56706194edfb%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafrutsL37ZdKzAPgtlqfyGIwZiBaDroTfVM3hUvJ50athIpZVpllnLGAUYFnQ_aem_ygGFxs_O7OG-iK35NkgkKg%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUANTZ-ggZIu8hGNv5i7_mCAzV8rbhbPgznCm8fHftDZ8ySEYvAgWvi3Ln94ViRUhHI4HEBGpYBJmEDK9xVaQ_8zJYWhXkRyC5GmUTOtpg
+https://scontent-sjc6-1.cdninstagram.com/o1/v/t2/f2/m78/AQNTni0xebheWalb6h4Sr5FZ8iHwB9ax0aw68ASJrp8C7U0U1K7VSsQCdNvWbSLbxpdDV6WrJO8eUWV1qpGiSs-RAG2vSgNfgEMn_0Y.mp4?_nc_cat=107&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ohc=Zt1mwlYeMAUQ7kNvwH6uvvt&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg4MzI1NTg2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=1272152dd43fceb&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzI1NDVGM0U0MDkxNDc1QUJCQTM4NDlDMzQxMDFDMkI3X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkjv7w0OyhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQMzEYnD_5Tmczk2I7nYlfWfEjem5W7Dmy20_RATRUo2JA&amp;oe=6ABCDC7C</t>
+        </is>
+      </c>
+      <c r="O223" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P223" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q223" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R223" s="3" t="inlineStr"/>
+    </row>
+    <row r="224" ht="45" customHeight="1">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>ba8a91cf0ad0d95fbed9</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T22:07:50.000332+00:00</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T17:46:30+00:00</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>Arcteryx.com</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>Arcteryx.com — Internship</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="inlineStr"/>
+      <c r="H224" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I224" s="3" t="inlineStr"/>
+      <c r="J224" s="3" t="inlineStr"/>
+      <c r="K224" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/arcteryx.com/59e99784-0e0c-4e07-a5df-9b2043074002</t>
+        </is>
+      </c>
+      <c r="L224" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M224" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N224" s="3" t="inlineStr">
+        <is>
+          <t>ARC'TERYX - Wholesale
+Analytics Intern
+Department: NAM - Wholesale
+Reports to: National Account Manager
+- USA Location: Portland, Oregon
+Work Arrangement: Flexible, between
+in-office and home Pay Range: $21.49
+- $26.49/hourly; pay is dependent on
+year of study and related experience
+Duration: Eight (8) months, January 4,
+2027 - August...
+Vv
+v , arcteryx
+Arcteryx USA analytics intern is
+crazy, | hope someone here bags
+this ® A,
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/829586376_1384439203773293_9160058668253584190_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5NjMxMjQ3MjUxMjM0NTc2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=JOOaxE6dBEMQ7kNvwHZOWts&amp;_nc_oc=AdqI-_sCTvCnO5a4XKZoJOun1Zy30tl19xLZ8EQHXgfn3WhFGp6NWnMo6QcqiIQC2bM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQNGt6MdoxAM0d5rgeDrEtdRcSWYcqxG6CPf51yH9TTtjA&amp;oe=6AC0C6BD
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/829586376_1384439203773293_9160058668253584190_n.jpg?stp=dst-jpg_e15_p240x240_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5NjMxMjQ3MjUxMjM0NTc2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=JOOaxE6dBEMQ7kNvwHZOWts&amp;_nc_oc=AdqI-_sCTvCnO5a4XKZoJOun1Zy30tl19xLZ8EQHXgfn3WhFGp6NWnMo6QcqiIQC2bM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQMt7YhN2PcxsEmsqWnyKQoJ0fwzEmMJFUdxnVyWlAD9DA&amp;oe=6AC0C6BD
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwHf6ioD&amp;_nc_oc=AdovB9AKcBUzTua_q6lzURFZRtyhShbn0UZEBvsZT5_scG8HL7MoD4TmphIUTCCWOjQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQMKrRkmuIoydkGGWVFHgekEqaKUCNzkCQHc9GSOTGiPVA&amp;oe=6AC0B8D9
+https://scontent-sjc3-1.cdninstagram.com/v/t51.82787-19/741197071_18602434987000481_1837506364311052498_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GA-FLSyhglvp0BZCANKgR4VNIoAZbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;_nc_aid=2427&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=wJ0Hw7uCANYQ7kNvwGbuOPU&amp;_nc_oc=AdqGx6_No189kPrPagYHI5y-5wk30W8Z0bjw4m-suQ5G-qSffWSUnwbQruLbpikolJ4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQO7-8Nv7bokKHUGjxvLYg_BnBTmBdjc2g83hp-JASi4zg&amp;oe=6AC0A1E8
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.lever.co%2Farcteryx.com%2F59e99784-0e0c-4e07-a5df-9b2043074002%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaff_Wdct7jbBVQijXpCSgti52mj2hoXuAc0QmGVZ9KbK2QpCh-S5tpb6FqWOQ_aem_pdduA38fHvGqy8ZNLt-rQw%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUA9uHuCQo2o5eoAbqauS5yBIOtvfY1h7TZfaLxzRUAjuXPL3tjmcpHpPOvxP0le9zOn4fuTTvvm-SirVsOdaYMpGp20ihiR9ZrMqJfGcA
+https://scontent-sjc3-1.cdninstagram.com/o1/v/t2/f2/m78/AQP_ChXZ_PD1IXlQ94HmTHtL7Aau8m7o0n_qozFMz8fElZiWMxJ5U4gssdkGneVVzaytnFB4JBOI698D2Vn6VXdegu6YOKkh4rAMWC4.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_ohc=XbQRq7_wxdsQ7kNvwHPrkSR&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg4MzI4MDE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=6d245a25a685d44e&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzBGNDY4QUYzOEJCRDAzMTY5OTVFRkJDMzRGODNGRjgzX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkmd3Y0uyhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQOg79mOmSff9Yet55G-W-gjGUBryoCLIuoRC5xqPsH2Dg&amp;oe=6ABCCAFC</t>
+        </is>
+      </c>
+      <c r="O224" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P224" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q224" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R224" s="3" t="inlineStr"/>
+    </row>
+    <row r="225" ht="45" customHeight="1">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>63363e5b950091def883</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T22:07:52.892521+00:00</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T19:14:44+00:00</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr"/>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>The Internship Program at BCBSM is</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="inlineStr"/>
+      <c r="H225" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I225" s="3" t="inlineStr"/>
+      <c r="J225" s="3" t="inlineStr"/>
+      <c r="K225" s="4" t="inlineStr">
+        <is>
+          <t>https://ejko.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_3/job/14841?src=SNS-102</t>
+        </is>
+      </c>
+      <c r="L225" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N225" s="3" t="inlineStr">
+        <is>
+          <t>2027 Summer Intern - Data
+Analytics, Program Performance
+The Internship Program at BCBSM is
+designed to enhance the skills and
+abilities of young professionals as well
+as to identify and attract future talent
+for our organization. Interns will gain
+practical hands-on work experience
+as well as a solid understanding of the
+health insurance industry. Our pr...
+https://ejko.fa.us2
+jobshare&amp;src=fe
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/825277116_2310868569758216_2148063437323681448_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5NjM1Njg4NzcxNjEwNTE4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=ewQnK0ZmN7oQ7kNvwHv3K9X&amp;_nc_oc=Adqqj9ukwb8WXCKWberNEpvA2SLmeP6aWFanC5fnZ_wbbFSgUy6Ua-H33fUJtGp1-8w&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQOzaXzio3z11Jrs_Cdp3IhPFlAFwJ1D2eUBPAbY5rwPkQ&amp;oe=6AC0C909
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/825277116_2310868569758216_2148063437323681448_n.jpg?stp=dst-jpg_e15_p240x240_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5NjM1Njg4NzcxNjEwNTE4MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=ewQnK0ZmN7oQ7kNvwHv3K9X&amp;_nc_oc=Adqqj9ukwb8WXCKWberNEpvA2SLmeP6aWFanC5fnZ_wbbFSgUy6Ua-H33fUJtGp1-8w&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQOinN0jBXxnyQU5LwMMjmaaru_1eJwau5rq37gFk_EGSg&amp;oe=6AC0C909
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwHf6ioD&amp;_nc_oc=AdovB9AKcBUzTua_q6lzURFZRtyhShbn0UZEBvsZT5_scG8HL7MoD4TmphIUTCCWOjQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQMKrRkmuIoydkGGWVFHgekEqaKUCNzkCQHc9GSOTGiPVA&amp;oe=6AC0B8D9
+https://l.instagram.com/?u=https%3A%2F%2Fejko.fa.us2.oraclecloud.com%2FhcmUI%2FCandidateExperience%2Fen%2Fsites%2FCX_3%2Fjob%2F14841%3Futm_medium%3Djobshare%26src%3DSNS-102%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeS_Wl007ODgLuL08nstT-1R0ZXnxvLMRBUos275CwLhASZ8Y6NAfGpFUa1Ig_aem_wyDjCkyhKWqR5280hk92fg&amp;e=AUBAfj0JcGAj_hSh0p7dfApfqFrhno7gjx1qhe28R1RYkj8Xr_butz8oCyOfpQeBBlGVEBYTiSLHHPEIaCKmxlFd2DRYskJ_0NmAUYcdMQ
+https://scontent-sjc6-1.cdninstagram.com/o1/v/t2/f2/m78/AQO1HF2HKut5aN418EcGMMOLzUnzY19fH1mKbkduU3KwnT8n1IcRVcG-vY5GXgF1L2RDR4sQ4cRyBKlPdgw4EBZsJ3rqjATQD5cgYzs.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ohc=FgJajTYh5akQ7kNvwGba3NQ&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg4NDMyMDU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=903f641e02f580de&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0ZFNDQzOEYwRTNDMjI0RUI2RDdFRkJFQzM5MzIxNEJFX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk3eCaoO2hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQPCCDx2ddwZ2iSeyKEyLPLkd6DL1QNF2zu6kgYdHKXJMQ&amp;oe=6ABCDA32</t>
+        </is>
+      </c>
+      <c r="O225" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P225" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q225" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R225" s="3" t="inlineStr"/>
+    </row>
+    <row r="226" ht="45" customHeight="1">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t>069a7dd359d2102cf233</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T22:07:54.165035+00:00</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T19:15:44+00:00</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr"/>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>&amp; Shopify Summer 2027 SWE Intern!</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H226" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I226" s="3" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="J226" s="3" t="inlineStr"/>
+      <c r="K226" s="4" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers/us-software-engineering-internships-summer-2027_2c62d9d7-3f52-42b3-a51d-3a7f3ed03679</t>
+        </is>
+      </c>
+      <c r="L226" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N226" s="3" t="inlineStr">
+        <is>
+          <t>@ shopify.com
+Instagram
+(4 shopify careers
+US Software
+Engineering Internships
+Summer 2027
+@ Remote - Americas
+Engineering &amp; Data
+@ 2 SHOPIFY.COM
+ns
+About the role
+&amp; Shopify Summer 2027 SWE Intern!
+internships at Shopify.
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/825277091_1747435539666273_746206249516246350_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5NjM1NzM5MTUwMjM4ODAwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=v_UJfHph2BoQ7kNvwFr4Jwm&amp;_nc_oc=AdoXSJ3683dYIpeoFGCQUCACzWuczOPVRpd-ALshj99RbT5qidn26LR3nAkl8R24Iyo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQPDzFM5VBa-K1wIjbF9xRl0k2c-f32xbWjMBXHyiS6cKg&amp;oe=6AC0A4B2
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/825277091_1747435539666273_746206249516246350_n.jpg?stp=dst-jpg_e15_p240x240_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5NjM1NzM5MTUwMjM4ODAwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=v_UJfHph2BoQ7kNvwFr4Jwm&amp;_nc_oc=AdoXSJ3683dYIpeoFGCQUCACzWuczOPVRpd-ALshj99RbT5qidn26LR3nAkl8R24Iyo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQOHkgBTbsRgVmU7AtW_6xWrh62CRGhLhrnwnqXhLPwIJA&amp;oe=6AC0A4B2
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwHf6ioD&amp;_nc_oc=AdovB9AKcBUzTua_q6lzURFZRtyhShbn0UZEBvsZT5_scG8HL7MoD4TmphIUTCCWOjQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQMKrRkmuIoydkGGWVFHgekEqaKUCNzkCQHc9GSOTGiPVA&amp;oe=6AC0B8D9
+https://l.instagram.com/?u=https%3A%2F%2Fwww.shopify.com%2Fcareers%2Fus-software-engineering-internships-summer-2027_2c62d9d7-3f52-42b3-a51d-3a7f3ed03679%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacYoUnSXzLqGdcafQP8pWPpLN4x8U9XenWFy_UxWSqbetshLWNFZ5c7F4EU2g_aem_cnRQ1jFWlQzo9k_U-ttAew&amp;e=AUDfkhcNNoPyjn8NZodTsDAtnBoMP8tWzTpbyL4928wmQ3W7KfqLz8wZHgV4RMKY7uQ46MJ2e-MtE_rZteMuHxIM-OQx0IJ8r2Db_uzZ7Q
+https://scontent-sjc6-1.cdninstagram.com/o1/v/t2/f2/m78/AQO1AZHuEmHoxLOIwq0LVxUyKY-GnwcOrMLDG1vjxNrhNGWghCRRhbZC-dXo1SqFMj7lKjbYmYD40VeEODakv6nV5UroTmAPgvpBDmA.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ohc=hzEQD-BQAYQQ7kNvwEUNrUs&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg4NDMzMzc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=35050efbb28730b&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzdCNDUzQUVDRkMyMTg5QUNEQzQxOUQzQjY0NjhEREJBX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkgdKYoe2hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQO9sFJbUvQmZ2vFw49pMqh02MTirj6LJJBMVhAnuLsLHQ&amp;oe=6ABCA76A</t>
+        </is>
+      </c>
+      <c r="O226" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P226" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q226" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R226" s="3" t="inlineStr"/>
+    </row>
+    <row r="227" ht="45" customHeight="1">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>e301165daa60840c966a</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T22:07:59.340608+00:00</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T19:54:32+00:00</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>ATT</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>ATT — Data Engineering</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G227" s="3" t="inlineStr">
+        <is>
+          <t>Data Engineering</t>
+        </is>
+      </c>
+      <c r="H227" s="3" t="inlineStr"/>
+      <c r="I227" s="3" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="J227" s="3" t="inlineStr"/>
+      <c r="K227" s="4" t="inlineStr">
+        <is>
+          <t>https://att.wd1.myworkdayjobs.com/ATTCollegeSpecialInvite/job/Alpharetta-Georgia/AT-T-Data-Engineering-Scholars-Program_R-122646</t>
+        </is>
+      </c>
+      <c r="L227" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N227" s="3" t="inlineStr">
+        <is>
+          <t>Sign In
+AT&amp;T Data Engineering
+Scholars Program
+Apply
+€) Office Worker (NOT Remote)
+so many data engineering roles today!
+(©) Posted Today
+(2) AT&amp;T DATA ENGINEERING INTER
+[=| R-122646
+This position requires resence of a
+minimum of 5 days per week and is only
+located in the location(s) posted. No
+relocation is offered.
+At AT&amp;T, you'll be empowered to create real
+change in an ever-expanding, connected world.
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/830056346_1712450860880117_236497094009233565_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5NjM3NjkyOTI1MDk3MTQ0NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=J-7dAIrnN2EQ7kNvwFSnDaU&amp;_nc_oc=AdqYyTcxUmQ812Tv8yClCVDpSuPScpLOORwQcBYW2x2DK3RpnxfebvEjeB_WoWdd2KY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQMoGEzVcTDYR91IJ29s6blXVdd7iLuHOLFipdP9ykJMoQ&amp;oe=6AC0C1D4
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/830056346_1712450860880117_236497094009233565_n.jpg?stp=dst-jpg_e15_p240x240_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5NjM3NjkyOTI1MDk3MTQ0NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=J-7dAIrnN2EQ7kNvwFSnDaU&amp;_nc_oc=AdqYyTcxUmQ812Tv8yClCVDpSuPScpLOORwQcBYW2x2DK3RpnxfebvEjeB_WoWdd2KY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQOazwSqYpjfPa28qwQDPWi2r1pqxpMFiZ7NA2kSQ1FTNA&amp;oe=6AC0C1D4
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwHf6ioD&amp;_nc_oc=AdovB9AKcBUzTua_q6lzURFZRtyhShbn0UZEBvsZT5_scG8HL7MoD4TmphIUTCCWOjQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQMKrRkmuIoydkGGWVFHgekEqaKUCNzkCQHc9GSOTGiPVA&amp;oe=6AC0B8D9
+https://l.instagram.com/?u=https%3A%2F%2Fatt.wd1.myworkdayjobs.com%2FATTCollegeSpecialInvite%2Fjob%2FAlpharetta-Georgia%2FAT-T-Data-Engineering-Scholars-Program_R-122646%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafXGKpvMbL9aP6T1DPV1y_vu9_A1Cwt4uxTPTVSzeXtmBT6awZJdXcZwtEdfQ_aem_Bq6FJQFnbzBpu7KV4gBE-Q%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUDaZOfHEalWasFXK2E0kIBoaO_QHGdX6GiCQ2cMpYkXWT6NRl-rIXD2orCSNputBiGm2UoJGlS6juPVGpn4LuMHukwH-HoplP-M7yoKHg
+https://scontent-sjc6-1.cdninstagram.com/o1/v/t2/f2/m78/AQNs-6uksk_4mKFR7rgkLjcujE_C4hZLrcsczGzMi-lGsfowrde4ThOsN7TcNBjXwrAQ0CypKU8ywLsxd7KLEdnQsZNQPAofYzkLXok.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ohc=XeHDOF8hSC8Q7kNvwE1BAm-&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg4NDY3NDU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=78ad196f9dead15&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzcwNEQ4NzgyMTEwN0UwNjZGNkM0RUIyMkVEQkIxQzk4X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk0eHKuu2hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQOMyhUr1tN-ul3dvYDQU7FVA3iYSxV9PDxLha9UMVpNGQ&amp;oe=6ABCDF21</t>
+        </is>
+      </c>
+      <c r="O227" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P227" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q227" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R227" s="3" t="inlineStr"/>
+    </row>
+    <row r="228" ht="45" customHeight="1">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t>bd9fc39d348046ca6467</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T22:08:01.259271+00:00</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T20:14:23+00:00</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr"/>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>the world, we are looking for a Data Science Intern</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G228" s="3" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="H228" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I228" s="3" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="J228" s="3" t="inlineStr"/>
+      <c r="K228" s="4" t="inlineStr">
+        <is>
+          <t>https://fa-eups-saasfaprod1.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/sites/ULSolutionsCareers/job/10629</t>
+        </is>
+      </c>
+      <c r="L228" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M228" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N228" s="3" t="inlineStr">
+        <is>
+          <t>x @ fa-eups-saasfaprod1.fa.ocs.or... CG:
+Instagram
+@ Solutions £4 =
+oe vw t View More Jobs
+2027 Summer Intern: Data
+Science Intern
+Northbrook, IL, United States and 1 more
+pr” TRENDING
+JOB DESCRIPTION
+From day one, we've blazed a trail protecting the
+@ DATA SCIENCE INTERN
+OT It Could Nappen witno u. It takes passion to
+protect people, proble safeguard
+personal data and con ake the world a
+more sustainable place. Id ideas and
+brilliant minds to build a better world for future
+generations across the globe.
+As our global footprint continues to spread across
+the world, we are looking for a Data Science Intern
+to join our team in Northbrook, IL or Chicago, IL.
+Thic rola ic hwhrid —~ 2 dave awiaale nn_cita at tha
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/827532743_3583560318473758_1417116410609652996_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5NjM4Njk0MTQ5OTIyMjE0MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=IEXcTnKBK3MQ7kNvwENqLmj&amp;_nc_oc=AdoVx9dwQsXjYm9oMKgXhBnBS_m8Bu70QeGWrL4-qCHrOe_qPOChPVLKBxTG9gIXg7w&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQMJyyDfRnUlcgH7jmdl6jX8AgP8cLlo9MLBSoQX6tKUcw&amp;oe=6AC0B26C
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/827532743_3583560318473758_1417116410609652996_n.jpg?stp=dst-jpg_e15_p240x240_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5NjM4Njk0MTQ5OTIyMjE0MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=IEXcTnKBK3MQ7kNvwENqLmj&amp;_nc_oc=AdoVx9dwQsXjYm9oMKgXhBnBS_m8Bu70QeGWrL4-qCHrOe_qPOChPVLKBxTG9gIXg7w&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQNU7d1EVfrBQUmnGZqJ-zz-y6HQAQFh7Sw9TlGKbY7Iqg&amp;oe=6AC0B26C
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwHf6ioD&amp;_nc_oc=AdovB9AKcBUzTua_q6lzURFZRtyhShbn0UZEBvsZT5_scG8HL7MoD4TmphIUTCCWOjQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQMKrRkmuIoydkGGWVFHgekEqaKUCNzkCQHc9GSOTGiPVA&amp;oe=6AC0B8D9
+https://l.instagram.com/?u=https%3A%2F%2Ffa-eups-saasfaprod1.fa.ocs.oraclecloud.com%2FhcmUI%2FCandidateExperience%2Fen%2Fsites%2FULSolutionsCareers%2Fjob%2F10629%3Futm_medium%3Djobboard%26utm_source%3Dzero2sudo%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeWNATUPkgoj01u7nozmYSGr6J-RVV2abrkVT2k5FaqZ5_d6wv-kplqtABuCA_aem_2TerKOQrUVPHQIEdDkw_1Q&amp;e=AUAqRySPjisYmVOE9OgNHjrEZS_cXfFEP22EqhgfMXdRgvP2MQ_2i8Wg2ZHN82TddFTiQQwZfJj_mukoJPsIL4LrNY8PMhXK_AMqBgtIlw
+https://scontent-sjc6-1.cdninstagram.com/o1/v/t2/f2/m78/AQOh0Veq0Kt2viJlaW72vFNAvjdhuQyXnJLW20O8zZI_4mKicM5sijFIUeJifnnG-JCHcVz10OcfvChQdCpVm8WfqCMzeURHZStCjLI.mp4?_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ohc=gmupzgvzvToQ7kNvwEEsQEw&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg4NDg1Mjc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=b578e8a2c370f004&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0EyNEZCMkMzQUU4MzI3M0JDQzJFMDM3NTRGODJFREI5X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk95rux-2hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQNldfctOZSdiW6XGBZ4IZorpVZT32dlgPuuZ3BgVXhFyQ&amp;oe=6ABCD055</t>
+        </is>
+      </c>
+      <c r="O228" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P228" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q228" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R228" s="3" t="inlineStr"/>
+    </row>
+    <row r="229" ht="45" customHeight="1">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>13484030044c879d804f</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T22:08:02.339734+00:00</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T20:23:06+00:00</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr"/>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>@ BEST BUY Al INTERN!</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G229" s="3" t="inlineStr"/>
+      <c r="H229" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I229" s="3" t="inlineStr"/>
+      <c r="J229" s="3" t="inlineStr"/>
+      <c r="K229" s="4" t="inlineStr">
+        <is>
+          <t>https://sjobs.brassring.com/TGnewUI/Search/Home/Home?partnerid=25632&amp;siteid=5798</t>
+        </is>
+      </c>
+      <c r="L229" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M229" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N229" s="3" t="inlineStr">
+        <is>
+          <t>@ sjobs.brassring.com G:
+Instagram
+Most Recent Jobs Posted
+25-Sep-2026
+Al Transformation
+Engineering Intern
+Best Buy
+Full time
+1047474BR
+@ BEST BUY Al INTERN!
+25-Sep-2026
+Al Transfor Product
+Intern
+Best Buy
+Full time
+1047476BR
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/825323976_2101515430463415_6158040530252791243_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5NjM5MTMwNTY4MDkyNDEwOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=h8HXz1dIQIUQ7kNvwH779Kc&amp;_nc_oc=Ado46ty8qADHbe_E6aVls-ehrH8nw7LBqpdCJ2CjpwMD83txAd5NDm6aBmrUveW00KY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQMf89Uxftyr3dumchKqv4HOd6dpykW5AmyaTNzs0Pq7KA&amp;oe=6AC0A19D
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/825323976_2101515430463415_6158040530252791243_n.jpg?stp=dst-jpg_e15_p240x240_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5NjM5MTMwNTY4MDkyNDEwOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=h8HXz1dIQIUQ7kNvwH779Kc&amp;_nc_oc=Ado46ty8qADHbe_E6aVls-ehrH8nw7LBqpdCJ2CjpwMD83txAd5NDm6aBmrUveW00KY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQNh2MIfQw2jO5pZAD6QcbsXzvccjiV9C_KMT1fMKM80QQ&amp;oe=6AC0A19D
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwHf6ioD&amp;_nc_oc=AdovB9AKcBUzTua_q6lzURFZRtyhShbn0UZEBvsZT5_scG8HL7MoD4TmphIUTCCWOjQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQMKrRkmuIoydkGGWVFHgekEqaKUCNzkCQHc9GSOTGiPVA&amp;oe=6AC0B8D9
+https://l.instagram.com/?u=https%3A%2F%2Fsjobs.brassring.com%2FTGnewUI%2FSearch%2FHome%2FHome%3Fpartnerid%3D25632%26siteid%3D5798%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaf1Lez4PRF7mVyEvmRxmtCQY5zbQTNLDTLak8IvHO8xDKFjgd8KHabA9tPbuQ_aem_yZsEjFtu4OxYJYln-Y_QvA%23home&amp;e=AUAMOjnM7_WcixIMtjsF9QoO2VbiD_AeAeHFu5Mn8-s3_Z-tArp-lriGzN5cm7R3Tj46PENMaRc_aiCyt9Kw9KLYjJ62r16QjzZU6PdGkg
+https://scontent-sjc3-1.cdninstagram.com/o1/v/t2/f2/m78/AQNaM4LVU3tl4-lnAdDfZmQLIkProWykINsfflNdPduDFpP0Gl7A_q32qlKJMHPaWMaiHWWi7eV6pSPRbEBjmnu2f70zUZRD9s4m6z8.mp4?_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_ohc=RbuTbbdsFU8Q7kNvwFdgEY1&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg4NDkzMzQ2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=9e19e46916145345&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzE2MDRDQzY0NkJEQTQ1RjNCMDY4MUI0MkJGN0JBQjExX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk1unvze2hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQNJRA3GHgIGKYEvwKx0fO75u-UqQnUmdAWP3uvn_83Rjg&amp;oe=6ABCD906</t>
+        </is>
+      </c>
+      <c r="O229" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P229" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q229" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R229" s="3" t="inlineStr"/>
+    </row>
+    <row r="230" ht="45" customHeight="1">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t>64e79bd8dd7bba842147</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T22:08:03.384770+00:00</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T20:58:55+00:00</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr"/>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>Data Journalism Summer Intern</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G230" s="3" t="inlineStr"/>
+      <c r="H230" s="3" t="inlineStr"/>
+      <c r="I230" s="3" t="inlineStr"/>
+      <c r="J230" s="3" t="inlineStr"/>
+      <c r="K230" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/financialtimes33/jobs/4986356101?gh_src=b3cf5a62teu</t>
+        </is>
+      </c>
+      <c r="L230" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M230" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N230" s="3" t="inlineStr">
+        <is>
+          <t>BUILD Aft
+CA
+Data Journalism Summer Intern
+(PD JOB-BOARDS.EU.GREENHOUSE.IC
+b3cfba62teu
+e
+Super cool role!!! So many data
+roles today
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/828201820_2287196532058482_4633700618535998517_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5NjQwOTM3OTgyNjA4MTkwNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=NDLn7H6SIIUQ7kNvwFo4J46&amp;_nc_oc=AdoiBLeIyPcOGleAiOHknNaYslN8Hphq9H6-WJyOaEIRRNKGXJW-2har4Rvsz4V9gUE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQNWNH1Q4JerZIKfNkdoEEdVpoPwZHJ6yauMS2M3VkKvWw&amp;oe=6AC0A6FD
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/828201820_2287196532058482_4633700618535998517_n.jpg?stp=dst-jpg_e15_p240x240_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5NjQwOTM3OTgyNjA4MTkwNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=NDLn7H6SIIUQ7kNvwFo4J46&amp;_nc_oc=AdoiBLeIyPcOGleAiOHknNaYslN8Hphq9H6-WJyOaEIRRNKGXJW-2har4Rvsz4V9gUE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQMZaNHh-_p8Yl62DIBI_nprMkQhju0MgP-rPVgQn_Qh_g&amp;oe=6AC0A6FD
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwHf6ioD&amp;_nc_oc=AdovB9AKcBUzTua_q6lzURFZRtyhShbn0UZEBvsZT5_scG8HL7MoD4TmphIUTCCWOjQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQMKrRkmuIoydkGGWVFHgekEqaKUCNzkCQHc9GSOTGiPVA&amp;oe=6AC0B8D9
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.eu.greenhouse.io%2Ffinancialtimes33%2Fjobs%2F4986356101%3Fgh_src%3Db3cf5a62teu%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaca9w1Rjz4CxMp0GJxXrdPEZBinyk3VGQenjbA9ngoG70CWDd-Gls0r8WkOIg_aem_W5wK-AXZVVFC1q-meJerag&amp;e=AUDaJ8ml-in6pAZhXq0OjL_QnoWa1y08OrrdtmfTlwYIF35KS7zjzQn-ANl6jXBB6n-pat4D2kK0ijbnbdAD-ZkRDesfv7vpgH2b5jwM9A
+https://scontent-sjc3-1.cdninstagram.com/o1/v/t2/f2/m78/AQNPykL3IRWHQEEV7d8daIO6g5q9NyPaujmo4F-zmcUR0UDYTsRY0xV7DubJjRklXYVeZB6j5iWiyNVD20iOvizcXAHMAO_Lh8d_TUs.mp4?_nc_cat=110&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_ohc=vj4CBkaMyisQ7kNvwEHhIGm&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg4NTI4MjY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=c51f8ce41dc7e34d&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0NDRjFDNEFGRTA1MjQ3RkQ4QzUyREEwMkQzMzFFNDIyX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkmofy5-2hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQNBMqeAcWetSwRFVIwtYej1CKGNn7_wc0T7APD7HSAEzw&amp;oe=6ABCDD6B</t>
+        </is>
+      </c>
+      <c r="O230" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P230" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q230" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R230" s="3" t="inlineStr"/>
+    </row>
+    <row r="231" ht="45" customHeight="1">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>b0b091f8000529ef264b</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T22:08:04.759098+00:00</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T21:38:01+00:00</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>NVIDIA — New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G231" s="3" t="inlineStr"/>
+      <c r="H231" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I231" s="3" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="J231" s="3" t="inlineStr"/>
+      <c r="K231" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.nvidia.com/careers?query=asci&amp;start=0&amp;pid=893392585259&amp;sort_by=relevance&amp;filter_job_category=engineering&amp;filter_job_type=new+college+graduate</t>
+        </is>
+      </c>
+      <c r="L231" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M231" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N231" s="3" t="inlineStr">
+        <is>
+          <t>@ jobs.nvidia.com C*;
+Instagram
+=&gt; ONVODIA. Join Talent Network Sign In
+ASIC Physical Design
+Engineer, Netlisting - New
+College Grad 2026
+p.s. Hardware Engineers - tons of
+NVIDIA new grad, tell your friends!
+Low Power ASIC Engineer -
+New College Grad 2026
+@ NVIDIA NEW GRAD JOBS!!!
+ASIC Design Verification
+Engineer - New College Grad
+2026
+JR2010391
+US, TX, Austin
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/828626994_1420704699395962_7206929320319198008_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5NjQyOTAwMzc0OTc0MjMyOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=tqC9dpG2ta0Q7kNvwGv_Ku1&amp;_nc_oc=AdoSJHIZi8D6f_Slp0UgYvbjSwbB_oKFObM_jqlDxkGAFdQcTiBbcDStjIH2Wlmhgf8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQMO15LpmY0q7zpS15vzEzHb3Y0n_XhiMuCyfX3ywWFVMw&amp;oe=6AC0BEFA
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/828626994_1420704699395962_7206929320319198008_n.jpg?stp=dst-jpg_e15_p240x240_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5NjQyOTAwMzc0OTc0MjMyOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=tqC9dpG2ta0Q7kNvwGv_Ku1&amp;_nc_oc=AdoSJHIZi8D6f_Slp0UgYvbjSwbB_oKFObM_jqlDxkGAFdQcTiBbcDStjIH2Wlmhgf8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;oh=00_AQPHLBZqgCPd59-pPXvAbRtZceB9EkYmFdRY83gB8G5mUg&amp;oe=6AC0BEFA
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwHf6ioD&amp;_nc_oc=AdovB9AKcBUzTua_q6lzURFZRtyhShbn0UZEBvsZT5_scG8HL7MoD4TmphIUTCCWOjQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQMKrRkmuIoydkGGWVFHgekEqaKUCNzkCQHc9GSOTGiPVA&amp;oe=6AC0B8D9
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.nvidia.com%2Fcareers%3Fquery%3Dasci%26start%3D0%26pid%3D893392585259%26sort_by%3Drelevance%26filter_job_category%3Dengineering%26filter_job_type%3Dnew%2Bcollege%2Bgraduate%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafmSIrPrgcSiZswDtl-U7fVN84peEeHRJb1QOByZTFyH7Peik0YGSeJgPDKzA_aem__-QLfq8GVeD_VL4dljNIvg&amp;e=AUD7ZS9gySFmXPF3kEuaIaGzK_5WBP7hY86_TEiiT0LXKdQZIPTBS2YjkeejT18B2k7n-5N1tlPq9y4bP3yIrPdftXGmz5KxEyYEp5ZwIQ
+https://scontent-sjc3-1.cdninstagram.com/o1/v/t2/f2/m78/AQOUXuH4qvCUifuzCnBnrxvKnsn_wjyIZ9xIeOZ4Q65ABFbUNMyda9zPQUkwcT9rflTvjzF6N-Ml15RnTYBNUMKkMF2g_MNCFkFeZfM.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_ohc=DF8oNPNsPfgQ7kNvwHR-xma&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg4NTUzODI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=ffddcb29f6c57647&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0NBQTNDNzFFMDFBMDRGQjNBNzFGMDVFMDBENjc4REU0X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk9tL3-u2hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=yFKi4BvTI5UYnGTeOwt_LQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQOINa9P2M18-U4aAl1JiEM8HlLshUC79Lbx8wfEe97a5g&amp;oe=6ABCD22C</t>
+        </is>
+      </c>
+      <c r="O231" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P231" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q231" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R231" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R218"/>
+  <autoFilter ref="A1:R231"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -21730,6 +22976,32 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L217" r:id="rId417"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K218" r:id="rId418"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L218" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K219" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L219" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K220" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L220" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K221" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L221" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K222" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L222" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K223" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L223" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K224" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L224" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K225" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L225" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K226" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L226" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K227" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L227" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K228" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L228" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K229" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L229" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K230" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L230" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K231" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L231" r:id="rId445"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$231</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$236</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R231"/>
+  <dimension ref="A1:R236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21311,7 +21311,7 @@
     <row r="219" ht="45" customHeight="1">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>2edcdbaf6cc387f6e8b3</t>
+          <t>22ee79947caa3eb099e6</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -21349,8 +21349,8 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="I219" s="3" t="inlineStr"/>
-      <c r="J219" s="3" t="inlineStr"/>
+      <c r="I219" s="3" t="n"/>
+      <c r="J219" s="3" t="n"/>
       <c r="K219" s="4" t="inlineStr">
         <is>
           <t>https://tinyurl.com/nvidia-canada-2026</t>
@@ -21403,12 +21403,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R219" s="3" t="inlineStr"/>
+      <c r="R219" s="3" t="n"/>
     </row>
     <row r="220" ht="45" customHeight="1">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>331798a30b4131c3cb8b</t>
+          <t>260e5c6f16abfc37c7d1</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -21451,7 +21451,7 @@
           <t>Menlo Park</t>
         </is>
       </c>
-      <c r="J220" s="3" t="inlineStr"/>
+      <c r="J220" s="3" t="n"/>
       <c r="K220" s="4" t="inlineStr">
         <is>
           <t>https://www.metacareers.com/profile/job_details/1373603594867455</t>
@@ -21515,12 +21515,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R220" s="3" t="inlineStr"/>
+      <c r="R220" s="3" t="n"/>
     </row>
     <row r="221" ht="45" customHeight="1">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>7c0a86e1558a98d88207</t>
+          <t>bb34358b8f1d56725caf</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -21548,14 +21548,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G221" s="3" t="inlineStr"/>
+      <c r="G221" s="3" t="n"/>
       <c r="H221" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="I221" s="3" t="inlineStr"/>
-      <c r="J221" s="3" t="inlineStr"/>
+      <c r="I221" s="3" t="n"/>
+      <c r="J221" s="3" t="n"/>
       <c r="K221" s="4" t="inlineStr">
         <is>
           <t>https://careers.underarmour.com/job/Baltimore-2027-Summer-Internship%2C-Business-Analytics-MD-21230/1434332500?feedId=346600&amp;JobPipeline=zero2sudo</t>
@@ -21613,12 +21613,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R221" s="3" t="inlineStr"/>
+      <c r="R221" s="3" t="n"/>
     </row>
     <row r="222" ht="45" customHeight="1">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>25deccc68b15cbf2ecd8</t>
+          <t>09d698dc5af0dc03aba1</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -21646,14 +21646,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G222" s="3" t="inlineStr"/>
+      <c r="G222" s="3" t="n"/>
       <c r="H222" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="I222" s="3" t="inlineStr"/>
-      <c r="J222" s="3" t="inlineStr"/>
+      <c r="I222" s="3" t="n"/>
+      <c r="J222" s="3" t="n"/>
       <c r="K222" s="4" t="inlineStr">
         <is>
           <t>https://careers.underarmour.com/job/Baltimore-2027-Summer-Internship%2C-AI-Automation-MD-21230/1434354900</t>
@@ -21699,12 +21699,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R222" s="3" t="inlineStr"/>
+      <c r="R222" s="3" t="n"/>
     </row>
     <row r="223" ht="45" customHeight="1">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>ce5df30e971376d453f1</t>
+          <t>80a50fac2440eae1a5fe</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -21732,14 +21732,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G223" s="3" t="inlineStr"/>
-      <c r="H223" s="3" t="inlineStr"/>
+      <c r="G223" s="3" t="n"/>
+      <c r="H223" s="3" t="n"/>
       <c r="I223" s="3" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="J223" s="3" t="inlineStr"/>
+      <c r="J223" s="3" t="n"/>
       <c r="K223" s="4" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/arcteryx.com/826dc4d8-f91e-4893-b8d6-56706194edfb</t>
@@ -21794,12 +21794,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R223" s="3" t="inlineStr"/>
+      <c r="R223" s="3" t="n"/>
     </row>
     <row r="224" ht="45" customHeight="1">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>ba8a91cf0ad0d95fbed9</t>
+          <t>7680420b0b038b0432c4</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -21827,14 +21827,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G224" s="3" t="inlineStr"/>
+      <c r="G224" s="3" t="n"/>
       <c r="H224" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="I224" s="3" t="inlineStr"/>
-      <c r="J224" s="3" t="inlineStr"/>
+      <c r="I224" s="3" t="n"/>
+      <c r="J224" s="3" t="n"/>
       <c r="K224" s="4" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/arcteryx.com/59e99784-0e0c-4e07-a5df-9b2043074002</t>
@@ -21891,12 +21891,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R224" s="3" t="inlineStr"/>
+      <c r="R224" s="3" t="n"/>
     </row>
     <row r="225" ht="45" customHeight="1">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>63363e5b950091def883</t>
+          <t>833fb1312e1c03572487</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -21909,7 +21909,7 @@
           <t>2026-09-28T19:14:44+00:00</t>
         </is>
       </c>
-      <c r="D225" s="3" t="inlineStr"/>
+      <c r="D225" s="3" t="n"/>
       <c r="E225" s="3" t="inlineStr">
         <is>
           <t>The Internship Program at BCBSM is</t>
@@ -21920,14 +21920,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G225" s="3" t="inlineStr"/>
+      <c r="G225" s="3" t="n"/>
       <c r="H225" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="I225" s="3" t="inlineStr"/>
-      <c r="J225" s="3" t="inlineStr"/>
+      <c r="I225" s="3" t="n"/>
+      <c r="J225" s="3" t="n"/>
       <c r="K225" s="4" t="inlineStr">
         <is>
           <t>https://ejko.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_3/job/14841?src=SNS-102</t>
@@ -21979,12 +21979,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R225" s="3" t="inlineStr"/>
+      <c r="R225" s="3" t="n"/>
     </row>
     <row r="226" ht="45" customHeight="1">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>069a7dd359d2102cf233</t>
+          <t>562568e2d24dd9ae37ac</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -21997,7 +21997,7 @@
           <t>2026-09-28T19:15:44+00:00</t>
         </is>
       </c>
-      <c r="D226" s="3" t="inlineStr"/>
+      <c r="D226" s="3" t="n"/>
       <c r="E226" s="3" t="inlineStr">
         <is>
           <t>&amp; Shopify Summer 2027 SWE Intern!</t>
@@ -22023,7 +22023,7 @@
           <t>Remote</t>
         </is>
       </c>
-      <c r="J226" s="3" t="inlineStr"/>
+      <c r="J226" s="3" t="n"/>
       <c r="K226" s="4" t="inlineStr">
         <is>
           <t>https://www.shopify.com/careers/us-software-engineering-internships-summer-2027_2c62d9d7-3f52-42b3-a51d-3a7f3ed03679</t>
@@ -22076,12 +22076,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R226" s="3" t="inlineStr"/>
+      <c r="R226" s="3" t="n"/>
     </row>
     <row r="227" ht="45" customHeight="1">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>e301165daa60840c966a</t>
+          <t>c39d7f3514832082ce44</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -22114,13 +22114,13 @@
           <t>Data Engineering</t>
         </is>
       </c>
-      <c r="H227" s="3" t="inlineStr"/>
+      <c r="H227" s="3" t="n"/>
       <c r="I227" s="3" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="J227" s="3" t="inlineStr"/>
+      <c r="J227" s="3" t="n"/>
       <c r="K227" s="4" t="inlineStr">
         <is>
           <t>https://att.wd1.myworkdayjobs.com/ATTCollegeSpecialInvite/job/Alpharetta-Georgia/AT-T-Data-Engineering-Scholars-Program_R-122646</t>
@@ -22175,12 +22175,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R227" s="3" t="inlineStr"/>
+      <c r="R227" s="3" t="n"/>
     </row>
     <row r="228" ht="45" customHeight="1">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>bd9fc39d348046ca6467</t>
+          <t>bb3143122cc150dc052a</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -22193,7 +22193,7 @@
           <t>2026-09-28T20:14:23+00:00</t>
         </is>
       </c>
-      <c r="D228" s="3" t="inlineStr"/>
+      <c r="D228" s="3" t="n"/>
       <c r="E228" s="3" t="inlineStr">
         <is>
           <t>the world, we are looking for a Data Science Intern</t>
@@ -22219,7 +22219,7 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="J228" s="3" t="inlineStr"/>
+      <c r="J228" s="3" t="n"/>
       <c r="K228" s="4" t="inlineStr">
         <is>
           <t>https://fa-eups-saasfaprod1.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/sites/ULSolutionsCareers/job/10629</t>
@@ -22280,12 +22280,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R228" s="3" t="inlineStr"/>
+      <c r="R228" s="3" t="n"/>
     </row>
     <row r="229" ht="45" customHeight="1">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>13484030044c879d804f</t>
+          <t>2900bd0651476e4cc263</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -22298,10 +22298,10 @@
           <t>2026-09-28T20:23:06+00:00</t>
         </is>
       </c>
-      <c r="D229" s="3" t="inlineStr"/>
+      <c r="D229" s="3" t="n"/>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>@ BEST BUY Al INTERN!</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
@@ -22309,14 +22309,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G229" s="3" t="inlineStr"/>
+      <c r="G229" s="3" t="n"/>
       <c r="H229" s="3" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="I229" s="3" t="inlineStr"/>
-      <c r="J229" s="3" t="inlineStr"/>
+      <c r="I229" s="3" t="n"/>
+      <c r="J229" s="3" t="n"/>
       <c r="K229" s="4" t="inlineStr">
         <is>
           <t>https://sjobs.brassring.com/TGnewUI/Search/Home/Home?partnerid=25632&amp;siteid=5798</t>
@@ -22372,12 +22372,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R229" s="3" t="inlineStr"/>
+      <c r="R229" s="3" t="n"/>
     </row>
     <row r="230" ht="45" customHeight="1">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>64e79bd8dd7bba842147</t>
+          <t>86bc8fcaa45eefbd149d</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -22390,7 +22390,7 @@
           <t>2026-09-28T20:58:55+00:00</t>
         </is>
       </c>
-      <c r="D230" s="3" t="inlineStr"/>
+      <c r="D230" s="3" t="n"/>
       <c r="E230" s="3" t="inlineStr">
         <is>
           <t>Data Journalism Summer Intern</t>
@@ -22401,10 +22401,10 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G230" s="3" t="inlineStr"/>
-      <c r="H230" s="3" t="inlineStr"/>
-      <c r="I230" s="3" t="inlineStr"/>
-      <c r="J230" s="3" t="inlineStr"/>
+      <c r="G230" s="3" t="n"/>
+      <c r="H230" s="3" t="n"/>
+      <c r="I230" s="3" t="n"/>
+      <c r="J230" s="3" t="n"/>
       <c r="K230" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/financialtimes33/jobs/4986356101?gh_src=b3cf5a62teu</t>
@@ -22452,12 +22452,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R230" s="3" t="inlineStr"/>
+      <c r="R230" s="3" t="n"/>
     </row>
     <row r="231" ht="45" customHeight="1">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>b0b091f8000529ef264b</t>
+          <t>ce3e2aba5d9285a842d6</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -22485,7 +22485,7 @@
           <t>New Grad / Early Career</t>
         </is>
       </c>
-      <c r="G231" s="3" t="inlineStr"/>
+      <c r="G231" s="3" t="n"/>
       <c r="H231" s="3" t="inlineStr">
         <is>
           <t>2026</t>
@@ -22496,7 +22496,7 @@
           <t>Austin</t>
         </is>
       </c>
-      <c r="J231" s="3" t="inlineStr"/>
+      <c r="J231" s="3" t="n"/>
       <c r="K231" s="4" t="inlineStr">
         <is>
           <t>https://jobs.nvidia.com/careers?query=asci&amp;start=0&amp;pid=893392585259&amp;sort_by=relevance&amp;filter_job_category=engineering&amp;filter_job_type=new+college+graduate</t>
@@ -22552,10 +22552,513 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R231" s="3" t="inlineStr"/>
+      <c r="R231" s="3" t="n"/>
+    </row>
+    <row r="232" ht="45" customHeight="1">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>3e1190ef9b399861811a</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T02:03:57.171690+00:00</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T22:21:00+00:00</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>Capital One — Recruiting / Career Event</t>
+        </is>
+      </c>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>Recruiting / Career Event</t>
+        </is>
+      </c>
+      <c r="G232" s="3" t="inlineStr"/>
+      <c r="H232" s="3" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="I232" s="3" t="inlineStr"/>
+      <c r="J232" s="3" t="inlineStr"/>
+      <c r="K232" s="4" t="inlineStr">
+        <is>
+          <t>http://directconsideration.com</t>
+        </is>
+      </c>
+      <c r="L232" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M232" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N232" s="3" t="inlineStr">
+        <is>
+          <t>@ directconsideration.com C:
+Instagram
+Capital One Product Open
+House
+Capital One is hosting an online
+"Product Open House — Innovate &amp;
+Influence" session covering its
+Small Business Bank and
+Customers, Systems &amp; Intelligence
+teams, with product leaders
+Multiple Recruiting Related Events on the
+latest send of Direct Consideration!
+Register for the open house &gt;
+Qualcomm Fall 2026 Campus
+(2) DIRECTCONSIDERATION.COM
+grads. In their T s, you'll
+https://scontent-atl3-2.cdninstagram.com/v/t51.71878-15/828051582_2197342621195119_6562219312709860211_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5NjQ1MDYzMTIyNDIyOTQ3Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=xE_CIQ1-NtsQ7kNvwEBP8Jy&amp;_nc_oc=AdosTcS-8e_9kV8CzICm_ZXO1rRlMPukTtaM4zu1vFJbRCwrVpsq5T-Z9ZQ0fMu_Nec&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=u4ePZ3JAslWjC61iDhnkIA&amp;_nc_ss=7e3ba&amp;oh=00_AQNTR2fsZz8NFm2rt35jwqL2dv0ui6ZiMrwgdaVzhnEWwA&amp;oe=6AC108C5
+https://scontent-atl3-2.cdninstagram.com/v/t51.71878-15/828051582_2197342621195119_6562219312709860211_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5NjQ1MDYzMTIyNDIyOTQ3Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=xE_CIQ1-NtsQ7kNvwEBP8Jy&amp;_nc_oc=AdosTcS-8e_9kV8CzICm_ZXO1rRlMPukTtaM4zu1vFJbRCwrVpsq5T-Z9ZQ0fMu_Nec&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=u4ePZ3JAslWjC61iDhnkIA&amp;_nc_ss=7e3ba&amp;oh=00_AQOyPRKzdWRgO6QYf4jFkHnnzf5Mj7qFfyDY82giAZSoMg&amp;oe=6AC108C5
+https://scontent-atl3-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwGwM5uw&amp;_nc_oc=Ado4y3WYvOqJF1t7TFnIrsu_yWPlP7AG-RZbeMJIB3fNUCXCoY5DB-Sq0PI-I3gDZKw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQPpvnDVsOHAFwtTEJ_7Ap4bgG0CvymsgvTGKFGkoaGTGA&amp;oe=6AC0F119
+https://l.instagram.com/?u=http%3A%2F%2Fdirectconsideration.com%2F%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadRwM5Qbjoz7CWLu-E07BRM56S6mNP9BfaE4Fx48GqSciLegZ8zOeBo3Ruxdw_aem_RYRcEe66Csl_taMBjmWDoA&amp;e=AUDkD_qjqlHRjM6RylVUob0M4dghS2f7e5pyLs0y0wmFeoG7MPWV48qGnox6areI7MWieRRswOFfrdiEGxNVIH9SseoCxGto0lCKV2UOag
+https://scontent-atl3-1.cdninstagram.com/o1/v/t2/f2/m78/AQNiRC8UfGm1Gh7PBCsdq5j0O8u2M7bGEKBHSJOAJwJvQqKZVVc1EXfAvrxzsWKlrXvK9y1MkRm4RN08J-M3S91aJ257NDbbGhZ38IM.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ohc=dheFt3WqGPsQ7kNvwEflwpo&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg4NTg0NjA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=4a9b8f1ff52cab44&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzA1OENDMzhBMUY3NTQ3M0M5MzY5ODZGRTZBM0FBNjI2X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkrIfvke6hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=u4ePZ3JAslWjC61iDhnkIA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQPI5HIpDOqt38vJ2YmgQPwmvkEaO8P_QjmR6Y-siX9iUA&amp;oe=6ABCE5B1</t>
+        </is>
+      </c>
+      <c r="O232" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P232" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q232" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R232" s="3" t="inlineStr"/>
+    </row>
+    <row r="233" ht="45" customHeight="1">
+      <c r="A233" s="3" t="inlineStr">
+        <is>
+          <t>99731edcd8d3bbf26001</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T02:03:58.575087+00:00</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T22:22:54+00:00</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G233" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H233" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I233" s="3" t="inlineStr">
+        <is>
+          <t>Redmond</t>
+        </is>
+      </c>
+      <c r="J233" s="3" t="inlineStr"/>
+      <c r="K233" s="4" t="inlineStr">
+        <is>
+          <t>https://apply.careers.microsoft.com/careers/job/1970393556914839</t>
+        </is>
+      </c>
+      <c r="L233" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M233" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N233" s="3" t="inlineStr">
+        <is>
+          <t>@ apply.careers.microsoft.com C:
+&lt;€ View All Jobs
+Software Engineering -
+Commercial
+Engineering &amp; Al (CEAI)
+g United States, Washington, Redmond
+9 PA
+Find out how well you
+match with this job
+(2) APPLY.CAREERS.MICROSOFT.COM
+Job description C nd benefits
+Job number Date posted
+200041565 Sep 28, 2026
+https://scontent-atl3-2.cdninstagram.com/v/t51.71878-15/825351983_1802165604247449_2661424517128797256_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5NjQ1MTU4ODg0MjU3OTYyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=4I8lxxIQXkQQ7kNvwEXEiRD&amp;_nc_oc=AdqZD0BKojxPJsgV0bWNL2KsLS9T5gL5U2NJydTjH9yYyXDYvYpp3mZvyMM1le-h9aE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=u4ePZ3JAslWjC61iDhnkIA&amp;_nc_ss=7e3ba&amp;oh=00_AQPvkpj5wPlsnwzcXtsPWUven3GtEYvwtDk1iQ5NMLUS-A&amp;oe=6AC0D4EB
+https://scontent-atl3-2.cdninstagram.com/v/t51.71878-15/825351983_1802165604247449_2661424517128797256_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5NjQ1MTU4ODg0MjU3OTYyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=4I8lxxIQXkQQ7kNvwEXEiRD&amp;_nc_oc=AdqZD0BKojxPJsgV0bWNL2KsLS9T5gL5U2NJydTjH9yYyXDYvYpp3mZvyMM1le-h9aE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=u4ePZ3JAslWjC61iDhnkIA&amp;_nc_ss=7e3ba&amp;oh=00_AQP85m_R9GhqmRqnARd1YaBKI1oStA-7imX3W0mHa-aYrA&amp;oe=6AC0D4EB
+https://scontent-atl3-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwGwM5uw&amp;_nc_oc=Ado4y3WYvOqJF1t7TFnIrsu_yWPlP7AG-RZbeMJIB3fNUCXCoY5DB-Sq0PI-I3gDZKw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQPpvnDVsOHAFwtTEJ_7Ap4bgG0CvymsgvTGKFGkoaGTGA&amp;oe=6AC0F119
+https://l.instagram.com/?u=https%3A%2F%2Fapply.careers.microsoft.com%2Fcareers%2Fjob%2F1970393556914839%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacKoapTlqDRa44frprgHk1cWvMbcy_seRhKfb3ugU0X-uZjQDwaS3mUmlKDGA_aem_JGW6YiK1mcqKmYryTf_9vA&amp;e=AUDSvIEhYmfDtBmGRtGBsgdiAHtrUWh3ZaDXzhkbe8JdHnG1E81YTOVu-MdngBKoFUZKYMd8kLWIFN1EMcTx91Q2sOJCSPqCJYonoA8IOA
+https://scontent-atl3-1.cdninstagram.com/o1/v/t2/f2/m78/AQPX_tpqalq-_geB9HPSIrposYD0ZBo_cQ2lKElTxH6plFZvkzO7j2rRD4r6rzyg65wp0uxfqhf9I_yIulCdi_pWXl0DcI4c0kTAv04.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ohc=dXupWnBfP3wQ7kNvwFlBB1c&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg4NTg1OTU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=741fe7d71740442c&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzM5Nzg3QkQxOUUyOTQxQTg4MTZERUY4ODhBM0UwNTM4X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk6-bvku6hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=u4ePZ3JAslWjC61iDhnkIA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQMGbIuAVZ5EKKK6iFCvs7oSA04rb9IDJFeevavKJ0yJUQ&amp;oe=6ABCF72E</t>
+        </is>
+      </c>
+      <c r="O233" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P233" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q233" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R233" s="3" t="inlineStr"/>
+    </row>
+    <row r="234" ht="45" customHeight="1">
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>6e7ba1666f322d51d109</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T02:04:01.614287+00:00</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T22:52:39+00:00</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>Voyagertechnologiesinc</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>Voyagertechnologiesinc — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G234" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H234" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I234" s="3" t="inlineStr"/>
+      <c r="J234" s="3" t="inlineStr"/>
+      <c r="K234" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/voyagertechnologiesinc/jobs/4423330009?source=zero2sudo</t>
+        </is>
+      </c>
+      <c r="L234" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M234" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N234" s="3" t="inlineStr">
+        <is>
+          <t>@ job-boards.greenhouse.io
+&lt; Back to jobs
+New
+2027 Software
+Engineering Intern
+© Long Beach
+Voyager is an innovative defense, national
+security and space technology company
+committed to advancing and delivering
+transformative, mission-critical solutions.
+2 2027 DEEP TECH SWE INTERN!
+assets to lead inther echnological
+and operational su m ground to
+space.
+Forge the Future: Join Voyager
+Technologies
+The future belongs to those who build it. At
+Voyager Technologies, we’re building
+technologies that protect lives, expand
+https://scontent-atl3-1.cdninstagram.com/v/t51.71878-15/829381330_1104598448755078_2151798951623554826_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5NjQ2NjU2ODQ2NDY4MzkzMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=MwfS8rWpTCgQ7kNvwH9U6se&amp;_nc_oc=Adq3hZg5vJeExMVjaflP84rPsTf6-DwvRFMgzIwODPk0Dq6_osXUa2VCr5M8hzaweDg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_gid=u4ePZ3JAslWjC61iDhnkIA&amp;_nc_ss=7e3ba&amp;oh=00_AQO8VrLmFpgApJK68h0Rg6OL0p0DKDnu6z3QTLacm-NybA&amp;oe=6AC0DEC3
+https://scontent-atl3-1.cdninstagram.com/v/t51.71878-15/829381330_1104598448755078_2151798951623554826_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5NjQ2NjU2ODQ2NDY4MzkzMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=MwfS8rWpTCgQ7kNvwH9U6se&amp;_nc_oc=Adq3hZg5vJeExMVjaflP84rPsTf6-DwvRFMgzIwODPk0Dq6_osXUa2VCr5M8hzaweDg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_gid=u4ePZ3JAslWjC61iDhnkIA&amp;_nc_ss=7e3ba&amp;oh=00_AQNWWpVJWHyZoZwjcX8HmBIi-CGm7mfzmFjJE-KBt4_Sdg&amp;oe=6AC0DEC3
+https://scontent-atl3-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwGwM5uw&amp;_nc_oc=Ado4y3WYvOqJF1t7TFnIrsu_yWPlP7AG-RZbeMJIB3fNUCXCoY5DB-Sq0PI-I3gDZKw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQPpvnDVsOHAFwtTEJ_7Ap4bgG0CvymsgvTGKFGkoaGTGA&amp;oe=6AC0F119
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fvoyagertechnologiesinc%2Fjobs%2F4423330009%3Fsource%3Dzero2sudo%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadp8cFS1S0SyLGMaiJez8MNMvKVfacHSaOuUtD1tTgMt2GjcWtcqaSPbeoNlA_aem_jMAz2ND1berILGFyIXwWUg&amp;e=AUCShzQ63AOVFNyh0FR46ZHNG413fVA1NlBayXuTxfSEmCWrM_KgdLoTpjrerfG_93S-cQt1tRLehi31zMTBBKg5w3HSOdtshpeeLBcYNw
+https://scontent-atl3-1.cdninstagram.com/o1/v/t2/f2/m78/AQOletUyFjhlNZQGteMXiQuhhvWBHmFMPwUz_aooyD86bLT2HvKXSnqNlyjK2d6NyuQE0id0RtMDDogYYRU2amcUn9-OGvWmGyi7vgc.mp4?_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ohc=jvTMH3RdIGsQ7kNvwGpsguW&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg4NjAwODM2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=b1132151ba6db1d1&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0M1MEI2NkEzOEQ5NDRCM0ZBNDg0RUI1OEVCRTExOTc4X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbku-_6ne6hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=u4ePZ3JAslWjC61iDhnkIA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQOxhq8YvsrOMXnC5hBt9m2ChH58uWatx-6rWXQdCo3oAg&amp;oe=6ABCFDFD</t>
+        </is>
+      </c>
+      <c r="O234" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P234" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q234" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R234" s="3" t="inlineStr"/>
+    </row>
+    <row r="235" ht="45" customHeight="1">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>092efb6c50b1dc6d35f0</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T02:04:05.695304+00:00</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T23:34:11+00:00</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>Cloudflare — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G235" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H235" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I235" s="3" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="J235" s="3" t="inlineStr"/>
+      <c r="K235" s="4" t="inlineStr">
+        <is>
+          <t>http://job-boards.greenhouse.io/cloudflare/jobs/8199958?gh_jid=8199958&amp;gh_src=58wic34y1us</t>
+        </is>
+      </c>
+      <c r="L235" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M235" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N235" s="3" t="inlineStr">
+        <is>
+          <t>@ job-boards.greenhouse.io C:
+CLOUDFLARE
+&lt; Back to jobs
+Software Engineer
+Intern (2027) - Austin,
+TX
+© In-Office
+About Us
+At Cloudflare, we are on a mission to help build a
+better Internet. Today the company runs one of
+2 JOB-BOARDS. GREENHOUSE. |G
+Ne
+bloggers to SMBs to Eo
+Cloudflare protects a ates any Internet
+application online with g hardware,
+installing software, or changing a line of code.
+10. companies.
+https://scontent-atl3-1.cdninstagram.com/v/t51.71878-15/829226086_983089771480229_3351263398379471969_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5NjQ4NzUwMDQyNDAwOTM5MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=m7dmbP5bvfoQ7kNvwFp2j42&amp;_nc_oc=AdpMhAes9SITjpY-uFSlxahuwZhljb3rQeDUqIqZUAlildvvWU8dOxDMK-P-EWS2CJE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_gid=u4ePZ3JAslWjC61iDhnkIA&amp;_nc_ss=7e3ba&amp;oh=00_AQMNxVfxzl3lpHYeWoxB2FuR_Zp8IuCq3rZLwXiTbzFaAA&amp;oe=6AC0D707
+https://scontent-atl3-1.cdninstagram.com/v/t51.71878-15/829226086_983089771480229_3351263398379471969_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5NjQ4NzUwMDQyNDAwOTM5MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=m7dmbP5bvfoQ7kNvwFp2j42&amp;_nc_oc=AdpMhAes9SITjpY-uFSlxahuwZhljb3rQeDUqIqZUAlildvvWU8dOxDMK-P-EWS2CJE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_gid=u4ePZ3JAslWjC61iDhnkIA&amp;_nc_ss=7e3ba&amp;oh=00_AQOG_BHPjNQy10N7_ERSNDtW-jedNTUaVe-mJAglQgxc5A&amp;oe=6AC0D707
+https://scontent-atl3-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwGwM5uw&amp;_nc_oc=Ado4y3WYvOqJF1t7TFnIrsu_yWPlP7AG-RZbeMJIB3fNUCXCoY5DB-Sq0PI-I3gDZKw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQPpvnDVsOHAFwtTEJ_7Ap4bgG0CvymsgvTGKFGkoaGTGA&amp;oe=6AC0F119
+https://l.instagram.com/?u=http%3A%2F%2Fjob-boards.greenhouse.io%2Fcloudflare%2Fjobs%2F8199958%3Fgh_jid%3D8199958%26gh_src%3D58wic34y1us%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadtxNFiK3_fS_tTaTMibmF_C-6GifRVtCe20BD0fJp5Y0bhHPS_Qf3ELxbhxw_aem_LO_UDVb4fw5sdGd8iHJArQ&amp;e=AUDMi1LDP6GD7EgxT3pbVd4qEBqrgjTjYpcO7pmGI2kvt7ggd4bFSGnY-AHeK--kp6TMZ34A8472PKfHyfFNeYXyo5uICLZJaFWLDRmSNA
+https://scontent-atl3-1.cdninstagram.com/o1/v/t2/f2/m78/AQMfwDJwQ7cqvB3B_Y5tBTe_1pxcCg7WhHnq8gjXQ0d8azdy9_SHNK3yXn6n9tqtIohxyXXMiQOcHzZTxkPlf5sDsS35gTvoU0YHGaQ.mp4?_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ohc=shHRI1yXNPkQ7kNvwHlA6tF&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg4NjMxNDk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=894665d90cff366f&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0YzODBDMTcyQjhEOTQ1MUM4MjBEQTlBQjFGQjNDQjBCX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkhevmtO6hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=u4ePZ3JAslWjC61iDhnkIA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQOSxVep99O06i6Lsfv85MFEToCXBmwjH5b2XBvg_ftp6g&amp;oe=6ABD0859</t>
+        </is>
+      </c>
+      <c r="O235" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P235" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q235" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R235" s="3" t="inlineStr"/>
+    </row>
+    <row r="236" ht="45" customHeight="1">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>f1101579456f687169cc</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T02:04:07.264701+00:00</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T01:30:17+00:00</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>Google — Data Science</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="H236" s="3" t="inlineStr"/>
+      <c r="I236" s="3" t="inlineStr">
+        <is>
+          <t>Chicago, Sunnyvale</t>
+        </is>
+      </c>
+      <c r="J236" s="3" t="inlineStr"/>
+      <c r="K236" s="4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/about/careers/applications/jobs/results/74579965571408582-business-data-scientist-internal-audit</t>
+        </is>
+      </c>
+      <c r="L236" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M236" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N236" s="3">
+        <f> Google C... $3
+€ Back to jobs search
+Business Data Scientist,
+Internal Audit
+EE] Google ©) Sunnyvale,CA,USA th Early
+Apply Ce
+@ Note: By applying to this position you will
+have an opportunity to share your
+preferred working location from the
+following: Sunnyvale, CA, USA; Chicago,
+IL, USA.
+(2) GOOGLE DATA SCIENCE NEW GRAD
+¢ Bachelor's deg istics, Data
+Science, Mathe hysics,
+Google Data Science current grads!
+https://scontent-atl3-2.cdninstagram.com/v/t51.71878-15/829381325_1124308246919062_6824798240231590492_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5NjU0NTkwOTA4NTE1MDMyOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=pObiOk096Q0Q7kNvwHuYHyR&amp;_nc_oc=AdpMF-Ig2nCnhpwE_8OtxSU3t1jO2ifCeAs-4sjaScYgNpNJKg3T8qR9fLxvnISwrxE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=u4ePZ3JAslWjC61iDhnkIA&amp;_nc_ss=7e3ba&amp;oh=00_AQM_8WCophT3SfGdphEM7Wh3jPrLKZdN0afhE-zmJoaxug&amp;oe=6AC1089E
+https://scontent-atl3-2.cdninstagram.com/v/t51.71878-15/829381325_1124308246919062_6824798240231590492_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5NjU0NTkwOTA4NTE1MDMyOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=pObiOk096Q0Q7kNvwHuYHyR&amp;_nc_oc=AdpMF-Ig2nCnhpwE_8OtxSU3t1jO2ifCeAs-4sjaScYgNpNJKg3T8qR9fLxvnISwrxE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_gid=u4ePZ3JAslWjC61iDhnkIA&amp;_nc_ss=7e3ba&amp;oh=00_AQPPZeEhShE1sgYvjiWzy_WoiAWhgaLirH509Acz4P5C8g&amp;oe=6AC1089E
+https://scontent-atl3-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwGwM5uw&amp;_nc_oc=Ado4y3WYvOqJF1t7TFnIrsu_yWPlP7AG-RZbeMJIB3fNUCXCoY5DB-Sq0PI-I3gDZKw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQPpvnDVsOHAFwtTEJ_7Ap4bgG0CvymsgvTGKFGkoaGTGA&amp;oe=6AC0F119
+https://l.instagram.com/?u=https%3A%2F%2Fwww.google.com%2Fabout%2Fcareers%2Fapplications%2Fjobs%2Fresults%2F74579965571408582-business-data-scientist-internal-audit%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaekP9Ym-ksh_6_ifLuoROcz82z0v5YKaeLSPzJRiK00_YqTUCWieLhVc8Zc-Q_aem_1N-ySZEhW_a0Myg2TCsJRw&amp;e=AUDG5ZIP3M0Gz1Q08zQKusHiKh9w8fGd8hHmUzviCZLsd0dQkqo2YOa6qlho0uJCyTqUeAUTA1MFOM38U65cVpETgIpcShKgj4hskOJXog
+https://scontent-atl3-2.cdninstagram.com/o1/v/t2/f2/m78/AQM7XWbKXTtNIQVkvmXF9sMKmPD_ZJS2mgmdGewkO-JmX7S4bSeggrJUjclTAqoe-hvfIWE5QiQBP1VYImx4CMoU0Sd-XIhYYE9gw7Q.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_ohc=Z6occQwdL2sQ7kNvwFrZO9D&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg4NzMyODY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=1ca9ef5f60a40701&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzRFQzNDRkVEMTA0MTRGMzJCMzAzQkUxNzQyMTk1M0JCX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk5p2qgO-hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=u4ePZ3JAslWjC61iDhnkIA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQPDKIiLM2pHRiKh7rzNKPNGIc-MFaAtGZVjOcpD5qy4sA&amp;oe=6ABCEE24</f>
+        <v/>
+      </c>
+      <c r="O236" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P236" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q236" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R236" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R231"/>
+  <autoFilter ref="A1:R236"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -23002,6 +23505,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L230" r:id="rId443"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K231" r:id="rId444"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L231" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K232" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L232" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K233" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L233" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K234" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L234" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K235" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L235" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K236" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L236" r:id="rId455"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$236</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$240</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R236"/>
+  <dimension ref="A1:R240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22557,7 +22557,7 @@
     <row r="232" ht="45" customHeight="1">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>3e1190ef9b399861811a</t>
+          <t>31d6f573477e61d80080</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -22585,14 +22585,14 @@
           <t>Recruiting / Career Event</t>
         </is>
       </c>
-      <c r="G232" s="3" t="inlineStr"/>
+      <c r="G232" s="3" t="n"/>
       <c r="H232" s="3" t="inlineStr">
         <is>
           <t>Fall 2026</t>
         </is>
       </c>
-      <c r="I232" s="3" t="inlineStr"/>
-      <c r="J232" s="3" t="inlineStr"/>
+      <c r="I232" s="3" t="n"/>
+      <c r="J232" s="3" t="n"/>
       <c r="K232" s="4" t="inlineStr">
         <is>
           <t>http://directconsideration.com</t>
@@ -22648,12 +22648,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R232" s="3" t="inlineStr"/>
+      <c r="R232" s="3" t="n"/>
     </row>
     <row r="233" ht="45" customHeight="1">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>99731edcd8d3bbf26001</t>
+          <t>752f9acada528ea325f7</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -22696,7 +22696,7 @@
           <t>Redmond</t>
         </is>
       </c>
-      <c r="J233" s="3" t="inlineStr"/>
+      <c r="J233" s="3" t="n"/>
       <c r="K233" s="4" t="inlineStr">
         <is>
           <t>https://apply.careers.microsoft.com/careers/job/1970393556914839</t>
@@ -22749,12 +22749,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R233" s="3" t="inlineStr"/>
+      <c r="R233" s="3" t="n"/>
     </row>
     <row r="234" ht="45" customHeight="1">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>6e7ba1666f322d51d109</t>
+          <t>6094e4ce81a7c5cc9a34</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -22792,8 +22792,8 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="I234" s="3" t="inlineStr"/>
-      <c r="J234" s="3" t="inlineStr"/>
+      <c r="I234" s="3" t="n"/>
+      <c r="J234" s="3" t="n"/>
       <c r="K234" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/voyagertechnologiesinc/jobs/4423330009?source=zero2sudo</t>
@@ -22852,12 +22852,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R234" s="3" t="inlineStr"/>
+      <c r="R234" s="3" t="n"/>
     </row>
     <row r="235" ht="45" customHeight="1">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>092efb6c50b1dc6d35f0</t>
+          <t>9209cf53903965c67902</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -22900,7 +22900,7 @@
           <t>Austin</t>
         </is>
       </c>
-      <c r="J235" s="3" t="inlineStr"/>
+      <c r="J235" s="3" t="n"/>
       <c r="K235" s="4" t="inlineStr">
         <is>
           <t>http://job-boards.greenhouse.io/cloudflare/jobs/8199958?gh_jid=8199958&amp;gh_src=58wic34y1us</t>
@@ -22957,12 +22957,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R235" s="3" t="inlineStr"/>
+      <c r="R235" s="3" t="n"/>
     </row>
     <row r="236" ht="45" customHeight="1">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>f1101579456f687169cc</t>
+          <t>67100ead4ba7bdddead8</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -22995,13 +22995,13 @@
           <t>Data Science</t>
         </is>
       </c>
-      <c r="H236" s="3" t="inlineStr"/>
+      <c r="H236" s="3" t="n"/>
       <c r="I236" s="3" t="inlineStr">
         <is>
           <t>Chicago, Sunnyvale</t>
         </is>
       </c>
-      <c r="J236" s="3" t="inlineStr"/>
+      <c r="J236" s="3" t="n"/>
       <c r="K236" s="4" t="inlineStr">
         <is>
           <t>https://www.google.com/about/careers/applications/jobs/results/74579965571408582-business-data-scientist-internal-audit</t>
@@ -23055,10 +23055,366 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R236" s="3" t="inlineStr"/>
+      <c r="R236" s="3" t="n"/>
+    </row>
+    <row r="237" ht="45" customHeight="1">
+      <c r="A237" s="3" t="inlineStr">
+        <is>
+          <t>f2e5dd94d3cfaa1ad3cd</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T08:40:14.157419+00:00</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T02:43:05+00:00</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr"/>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>Lyft Applied Scientist Intern (Summer</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G237" s="3" t="inlineStr"/>
+      <c r="H237" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I237" s="3" t="inlineStr"/>
+      <c r="J237" s="3" t="inlineStr"/>
+      <c r="K237" s="4" t="inlineStr">
+        <is>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8843341002?gh_jid=8843341002</t>
+        </is>
+      </c>
+      <c r="L237" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M237" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N237" s="3" t="inlineStr">
+        <is>
+          <t>Applied Scientist Intern (Summer
+2027)
+Lyft Applied Scientist Intern (Summer
+2027) is where you apply online to
+the Applied Scientist Intern (Summer
+2027) role.
+Lyft Applied Scientist Intern!
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/826395556_1479303770678286_5583474569105756041_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5NjU4MjU0OTI5OTk3ODI3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=fIGG3j10bEgQ7kNvwG2Ckj6&amp;_nc_oc=Adq-Yb_KZMqdYHVrKIPzglECyHmDnwdo0ecFJxYSjZikF09Dad7fgXCqoz9SzgKT4O4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=oyiZVGVdbUv3EPZ_Q74RPg&amp;_nc_ss=7e3ba&amp;oh=00_AQOQ6DEo8Vprdm1yZ0GiQSL56CvG3atIDMDC6_7HfJKUZA&amp;oe=6AC150FE
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/826395556_1479303770678286_5583474569105756041_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5NjU4MjU0OTI5OTk3ODI3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=fIGG3j10bEgQ7kNvwG2Ckj6&amp;_nc_oc=Adq-Yb_KZMqdYHVrKIPzglECyHmDnwdo0ecFJxYSjZikF09Dad7fgXCqoz9SzgKT4O4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=oyiZVGVdbUv3EPZ_Q74RPg&amp;_nc_ss=7e3ba&amp;oh=00_AQM8D9mbgrqtRDCzZC7m9XL-sWNJgxZYurLZLGLBRrlpTQ&amp;oe=6AC150FE
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwEWn8JO&amp;_nc_oc=Adpg88I1HR43DnP7EVP4Jlkvp0Qngj5v2rId9ZanckodLXsyNyPXPKB3dlzSUnr69_w&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQOq35kRVkVPmxrA9PukJMVUzTkV8KB3R-VkwZNh4nfayQ&amp;oe=6AC16199
+https://l.instagram.com/?u=https%3A%2F%2Fapp.careerpuck.com%2Fjob-board%2Flyft%2Fjob%2F8843341002%3Fgh_jid%3D8843341002%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadLNfhIXpWw9zIo3-gjTlqSxmEM0aOcnlj66A5TUIfqpxYflJ27PwJZXYDTOw_aem_7uEnr7Aj3u5gIwRxlV3pRg&amp;e=AUCR1fxRbUM_HTAOxURU7nw9CnFfIkzemeH4SzG-PO_P52v_DJbKCtzWraeavAXM6Pn5a1CaE9EJOVgBv8BZCVUFoF10868dL3Ma_Mld3w
+https://scontent-lga3-1.cdninstagram.com/o1/v/t2/f2/m78/AQOuKgj4UTExiKQEw2ps6P0Wy55HUBDbWi8etz9aLeYgiITuOlq8Fp6sNhHC7uzrKywJ6O1MKnNN9c005A0TAfofjYNXjLYSVbSvlYM.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_ohc=6N68HIuwaSEQ7kNvwGTJe8e&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg4ODQyMDA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=7003776650f331fe&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0MzMTE4QzVBREI2QTRCOEVCNDI2NjYzRjIwMkM4QjM1X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkmNHS0e-hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=oyiZVGVdbUv3EPZ_Q74RPg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQOQ7pPyiAX5IXOmxJMOtO5xcsIzARZwnRLgGBco16_wpw&amp;oe=6ABD43A6</t>
+        </is>
+      </c>
+      <c r="O237" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P237" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q237" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R237" s="3" t="inlineStr"/>
+    </row>
+    <row r="238" ht="45" customHeight="1">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>10119cd6d23bda189362</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T08:40:15.856866+00:00</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T02:44:12+00:00</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr"/>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>Lyft Industrialization Engineer Intern</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G238" s="3" t="inlineStr"/>
+      <c r="H238" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I238" s="3" t="inlineStr"/>
+      <c r="J238" s="3" t="inlineStr"/>
+      <c r="K238" s="4" t="inlineStr">
+        <is>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8817930002?gh_jid=8817930002</t>
+        </is>
+      </c>
+      <c r="L238" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M238" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N238" s="3" t="inlineStr">
+        <is>
+          <t>Industrialization Engineer Intern
+(Summer 2027)
+Lyft Industrialization Engineer
+Intern (Summer 2027) is where you
+apply online to the Industrialization
+Engineer Intern (Summer 2027) role.
+Lyft Industrialization Engineer Intern
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/830027568_1347896700552894_3314847562930213110_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5NjU4MzExMTYzODgyNDU3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=h8lQmqdMHPIQ7kNvwEptH9h&amp;_nc_oc=AdrrhgIm0E3CvIAuDIsr3KSDeuW0_lnqNWZWUNzvti_Q31KFBreuKEH5EdiIovsy8fc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=oyiZVGVdbUv3EPZ_Q74RPg&amp;_nc_ss=7e3ba&amp;oh=00_AQN-NlFKz1qASozqpnW8WBOhJp9y7MQpdmMNi6PCVel3-w&amp;oe=6AC1489E
+https://scontent-lga3-3.cdninstagram.com/v/t51.71878-15/830027568_1347896700552894_3314847562930213110_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5NjU4MzExMTYzODgyNDU3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=h8lQmqdMHPIQ7kNvwEptH9h&amp;_nc_oc=AdrrhgIm0E3CvIAuDIsr3KSDeuW0_lnqNWZWUNzvti_Q31KFBreuKEH5EdiIovsy8fc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_gid=oyiZVGVdbUv3EPZ_Q74RPg&amp;_nc_ss=7e3ba&amp;oh=00_AQOeHcQHP9AEYDbPgp6zn04dT7sKb0AP_6U5RHfdvGRacg&amp;oe=6AC1489E
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwEWn8JO&amp;_nc_oc=Adpg88I1HR43DnP7EVP4Jlkvp0Qngj5v2rId9ZanckodLXsyNyPXPKB3dlzSUnr69_w&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQOq35kRVkVPmxrA9PukJMVUzTkV8KB3R-VkwZNh4nfayQ&amp;oe=6AC16199
+https://l.instagram.com/?u=https%3A%2F%2Fapp.careerpuck.com%2Fjob-board%2Flyft%2Fjob%2F8817930002%3Fgh_jid%3D8817930002%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAac9uBdChgZCTR-ejmiKyPaIydeyZ3i4mVYqTTdXnvvK2nghHKFsd25xZxhdjQ_aem_FdG16KyQGNhnCgAV40GUfQ&amp;e=AUCjSBEkfbm-MJhfoVwbYaeDkpeNhBiF0uflVX95lc_I_ludGVaSPiuyFshdGZsNGULZuxugWWFWvxfyBXLpkF3jeQ1WyRUKX5AIue6-6g
+https://scontent-lga3-1.cdninstagram.com/o1/v/t2/f2/m78/AQPNdJEFSk0a4aIzMFtfUU6AZ4E-bpH972wljzcBPi7BNrAnBSAGFFyGU5iMGGi6LjV5aSBMXJQu1M0XaHk28tUZa7yE7wvdhZFasmE.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_ohc=XMh51G8u8C8Q7kNvwENvD2e&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg4ODQ2MDI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=4dfc90ea3b9a792a&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzVCMEI2Q0NEQjEyOTQwMzc5MkQ3MjE2QTUxODY2NkI1X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkuoHS1O-hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=oyiZVGVdbUv3EPZ_Q74RPg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQOdTYXFUFY8z3rgjUS8ZWYj09w53AAW7pHGE79tcMlc1Q&amp;oe=6ABD55FE</t>
+        </is>
+      </c>
+      <c r="O238" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P238" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q238" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R238" s="3" t="inlineStr"/>
+    </row>
+    <row r="239" ht="45" customHeight="1">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>077f15ce0c1a41665f31</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T08:40:17.567793+00:00</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T02:44:54+00:00</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr"/>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>and have the opportunity to thrive.</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G239" s="3" t="inlineStr"/>
+      <c r="H239" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I239" s="3" t="inlineStr"/>
+      <c r="J239" s="3" t="inlineStr"/>
+      <c r="K239" s="4" t="inlineStr">
+        <is>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8802222002</t>
+        </is>
+      </c>
+      <c r="L239" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M239" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N239" s="3" t="inlineStr">
+        <is>
+          <t>Business
+Systems Engineer
+Intern, Finance
+Technology
+(Summer 2027)
+Toronto, Canada
+ID: 111178
+Cy Some
+¢2 Hearc e team
+At Lyft, our purpose is to serve and connect. We
+aim to achieve this by cultivating a work
+environment where all team members belong
+and have the opportunity to thrive.
+https://scontent-lga3-1.cdninstagram.com/v/t51.71878-15/829098229_2272315016887649_8525221502053528618_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5NjU4MzQ1ODc1MjE5NDcyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=ZKZk2VskEU0Q7kNvwGGkuT-&amp;_nc_oc=AdqhYENmNbZv6YeVxSljP6o6eA2ne_Jw_ATEQHBCjx6qrIILGSzUJI-FZjoX07t5EUw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=oyiZVGVdbUv3EPZ_Q74RPg&amp;_nc_ss=7e3ba&amp;oh=00_AQNZvCHWDkV1CqeI-6W9ynDAWNtSTae3vd-Ke-kjjMwf_w&amp;oe=6AC140D5
+https://scontent-lga3-1.cdninstagram.com/v/t51.71878-15/829098229_2272315016887649_8525221502053528618_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5NjU4MzQ1ODc1MjE5NDcyMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=ZKZk2VskEU0Q7kNvwGGkuT-&amp;_nc_oc=AdqhYENmNbZv6YeVxSljP6o6eA2ne_Jw_ATEQHBCjx6qrIILGSzUJI-FZjoX07t5EUw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=oyiZVGVdbUv3EPZ_Q74RPg&amp;_nc_ss=7e3ba&amp;oh=00_AQM867gHLdIGWLQ0GGKm5h6_UimAINQUSRgd5DrWaJ2Nwg&amp;oe=6AC140D5
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwEWn8JO&amp;_nc_oc=Adpg88I1HR43DnP7EVP4Jlkvp0Qngj5v2rId9ZanckodLXsyNyPXPKB3dlzSUnr69_w&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQOq35kRVkVPmxrA9PukJMVUzTkV8KB3R-VkwZNh4nfayQ&amp;oe=6AC16199
+https://l.instagram.com/?u=https%3A%2F%2Fapp.careerpuck.com%2Fjob-board%2Flyft%2Fjob%2F8802222002%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAads_51PCC5tCRq7CPHbPJxUYZONXk9cvraaxAHkfBr4SAK1bpT2Y7xdiEpzVg_aem_tbi_aFmoHHKcPizGCrUcHw&amp;e=AUCKf43eBDQK4h_qDgE5t3PyYmwMv0xYImB2LtdxBqbnLypP_DeHq0R4DIAHCNb0cAXMR79KpUVXS14wdrHS_gMJAvPjw8LFlfMyF3oVWQ
+https://scontent-lga3-2.cdninstagram.com/o1/v/t2/f2/m78/AQMLk0OLepP0O9uzwpIJl-NflvOc18DWAlnye7QEIEpj5XiwoS_245SGpWLJVnFE4OAX2zuaciSfshEbOp0AezVsUDMSvbUBxxFAAhk.mp4?_nc_cat=107&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ohc=IAAp8oDIsXYQ7kNvwGuBgfH&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg4ODQ3ODg2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=81bd5e39fe4e417&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzU4RTYzNjkzQzM0RDRFRTlBQ0Q4QzE5MEVGNDBCMzlGX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkxLKD1u-hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=oyiZVGVdbUv3EPZ_Q74RPg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQMPr5Pn3fcY8DRbmG_tNhiSIJpq-18WkvGekKk7WRVVGA&amp;oe=6ABD67DC</t>
+        </is>
+      </c>
+      <c r="O239" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P239" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q239" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R239" s="3" t="inlineStr"/>
+    </row>
+    <row r="240" ht="45" customHeight="1">
+      <c r="A240" s="3" t="inlineStr">
+        <is>
+          <t>27fb68c6226bc308d285</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T08:40:22.761524+00:00</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T05:22:46+00:00</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>Gitai</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>Gitai — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F240" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G240" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H240" s="3" t="inlineStr"/>
+      <c r="I240" s="3" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="J240" s="3" t="inlineStr"/>
+      <c r="K240" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitai/jobs/5437128008</t>
+        </is>
+      </c>
+      <c r="L240" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M240" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N240" s="3" t="inlineStr">
+        <is>
+          <t>@ job-boards.greenhouse.io
+Instagram
+&lt; Back to jobs
+Field-Deployed
+Software Engineering
+Intern
+© Los Angeles, California, United States
+Who We Are
+GITATI is a vertically intuS—-ed space and
+defense company building the next generation
+of hardware for low-Earth-orbit missions.
+At our core is the space robotics technology
+that has defined GITAI from the beginning. A
+small, highly capable engineering team
+that foundation across satellite buses, in
+servicing robotics, and mission hardwar
+annliantiann ciuinh ar Carth ahenein tian Tada.
+https://scontent-lga3-1.cdninstagram.com/v/t51.71878-15/825352441_1587026162905368_8815137211464303245_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5NjY2MjkxNjc5NTI2MzI0Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=D6jh6HejBRwQ7kNvwFNgCDK&amp;_nc_oc=AdqDjkE2guRPlCYBmIxRh--EMkzcFbaVX6vJXSDC0Z4TSzbdOcvJaW_L62JeA9MpO7U&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=oyiZVGVdbUv3EPZ_Q74RPg&amp;_nc_ss=7e3ba&amp;oh=00_AQN-66PbDzTq3o6HqhQxksxDsY352j1CjIQPzxpoDYd_3g&amp;oe=6AC1517F
+https://scontent-lga3-1.cdninstagram.com/v/t51.71878-15/825352441_1587026162905368_8815137211464303245_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5NjY2MjkxNjc5NTI2MzI0Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=D6jh6HejBRwQ7kNvwFNgCDK&amp;_nc_oc=AdqDjkE2guRPlCYBmIxRh--EMkzcFbaVX6vJXSDC0Z4TSzbdOcvJaW_L62JeA9MpO7U&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lga3-1.cdninstagram.com&amp;_nc_gid=oyiZVGVdbUv3EPZ_Q74RPg&amp;_nc_ss=7e3ba&amp;oh=00_AQPy1k51BE3S5QohNfgjzeoMjJxvfwCGMAFdLm__2kCENQ&amp;oe=6AC1517F
+https://scontent-lga3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwEWn8JO&amp;_nc_oc=Adpg88I1HR43DnP7EVP4Jlkvp0Qngj5v2rId9ZanckodLXsyNyPXPKB3dlzSUnr69_w&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQOq35kRVkVPmxrA9PukJMVUzTkV8KB3R-VkwZNh4nfayQ&amp;oe=6AC16199
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fgitai%2Fjobs%2F5437128008%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacouadWJhR9gLGFB5GiDpHUqVaJzBlz0T9bxrCcnS18x-PQZaUephMJ1H-3lg_aem_ot2PAe_3Cwy984q7Uq3afA&amp;e=AUCZq9VUdnsqXiWC4Tp1C87tSCZBXHy2hS5NQrEMa82RrxPEiesrcz7dQf3tMha1qnPmhwh1cX0f0JgwCLuKS9-h3nfY5IScG6KFg09_lA
+https://scontent-lga3-3.cdninstagram.com/o1/v/t2/f2/m78/AQNrqmTz9urOsp_K4xwygReWfKLGj41cBs3dZyaWM92p9TflyDHVV94jHdLU325BN0ngTNRDst73kzYqlLqj4M4MJbI8UnDVqtTs4qM.mp4?_nc_cat=1&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_ohc=Plt2wY24lt0Q7kNvwHPtx6y&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg5MDM3NTc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=d2d4954af3b2c456&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzA1NENFQzA3RUM5MzQ5QjdCRkQxRTBGREJCQTk4RUQ4X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkpdKt4_ChQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=oyiZVGVdbUv3EPZ_Q74RPg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQPIif6-az6cdQqUzYmuOHLsQBQ_WGOnpIJKZEBOq70hjg&amp;oe=6ABD459E</t>
+        </is>
+      </c>
+      <c r="O240" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P240" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q240" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R240" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R236"/>
+  <autoFilter ref="A1:R240"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -23515,6 +23871,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L235" r:id="rId453"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K236" r:id="rId454"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L236" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K237" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L237" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K238" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L238" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K239" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L239" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K240" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L240" r:id="rId463"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$240</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$241</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R240"/>
+  <dimension ref="A1:R241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23060,7 +23060,7 @@
     <row r="237" ht="45" customHeight="1">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>f2e5dd94d3cfaa1ad3cd</t>
+          <t>fa1af3054fca38cfd89a</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -23073,7 +23073,7 @@
           <t>2026-09-29T02:43:05+00:00</t>
         </is>
       </c>
-      <c r="D237" s="3" t="inlineStr"/>
+      <c r="D237" s="3" t="n"/>
       <c r="E237" s="3" t="inlineStr">
         <is>
           <t>Lyft Applied Scientist Intern (Summer</t>
@@ -23084,14 +23084,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G237" s="3" t="inlineStr"/>
+      <c r="G237" s="3" t="n"/>
       <c r="H237" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I237" s="3" t="inlineStr"/>
-      <c r="J237" s="3" t="inlineStr"/>
+      <c r="I237" s="3" t="n"/>
+      <c r="J237" s="3" t="n"/>
       <c r="K237" s="4" t="inlineStr">
         <is>
           <t>https://app.careerpuck.com/job-board/lyft/job/8843341002?gh_jid=8843341002</t>
@@ -23138,12 +23138,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R237" s="3" t="inlineStr"/>
+      <c r="R237" s="3" t="n"/>
     </row>
     <row r="238" ht="45" customHeight="1">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>10119cd6d23bda189362</t>
+          <t>23607f35089219d760ae</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -23156,7 +23156,7 @@
           <t>2026-09-29T02:44:12+00:00</t>
         </is>
       </c>
-      <c r="D238" s="3" t="inlineStr"/>
+      <c r="D238" s="3" t="n"/>
       <c r="E238" s="3" t="inlineStr">
         <is>
           <t>Lyft Industrialization Engineer Intern</t>
@@ -23167,14 +23167,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G238" s="3" t="inlineStr"/>
+      <c r="G238" s="3" t="n"/>
       <c r="H238" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I238" s="3" t="inlineStr"/>
-      <c r="J238" s="3" t="inlineStr"/>
+      <c r="I238" s="3" t="n"/>
+      <c r="J238" s="3" t="n"/>
       <c r="K238" s="4" t="inlineStr">
         <is>
           <t>https://app.careerpuck.com/job-board/lyft/job/8817930002?gh_jid=8817930002</t>
@@ -23221,12 +23221,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R238" s="3" t="inlineStr"/>
+      <c r="R238" s="3" t="n"/>
     </row>
     <row r="239" ht="45" customHeight="1">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>077f15ce0c1a41665f31</t>
+          <t>12dc4c53eb3f84ac041d</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -23239,7 +23239,7 @@
           <t>2026-09-29T02:44:54+00:00</t>
         </is>
       </c>
-      <c r="D239" s="3" t="inlineStr"/>
+      <c r="D239" s="3" t="n"/>
       <c r="E239" s="3" t="inlineStr">
         <is>
           <t>and have the opportunity to thrive.</t>
@@ -23250,14 +23250,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G239" s="3" t="inlineStr"/>
+      <c r="G239" s="3" t="n"/>
       <c r="H239" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I239" s="3" t="inlineStr"/>
-      <c r="J239" s="3" t="inlineStr"/>
+      <c r="I239" s="3" t="n"/>
+      <c r="J239" s="3" t="n"/>
       <c r="K239" s="4" t="inlineStr">
         <is>
           <t>https://app.careerpuck.com/job-board/lyft/job/8802222002</t>
@@ -23310,12 +23310,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R239" s="3" t="inlineStr"/>
+      <c r="R239" s="3" t="n"/>
     </row>
     <row r="240" ht="45" customHeight="1">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>27fb68c6226bc308d285</t>
+          <t>3bb13674b2b0870f95de</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -23348,13 +23348,13 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H240" s="3" t="inlineStr"/>
+      <c r="H240" s="3" t="n"/>
       <c r="I240" s="3" t="inlineStr">
         <is>
           <t>Los Angeles</t>
         </is>
       </c>
-      <c r="J240" s="3" t="inlineStr"/>
+      <c r="J240" s="3" t="n"/>
       <c r="K240" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitai/jobs/5437128008</t>
@@ -23411,10 +23411,112 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R240" s="3" t="inlineStr"/>
+      <c r="R240" s="3" t="n"/>
+    </row>
+    <row r="241" ht="45" customHeight="1">
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t>ebf53b8b5b9b3dc5cc0b</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T15:59:26.604759+00:00</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T14:50:43+00:00</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>NVIDIA — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G241" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H241" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I241" s="3" t="inlineStr"/>
+      <c r="J241" s="3" t="inlineStr"/>
+      <c r="K241" s="4" t="inlineStr">
+        <is>
+          <t>https://nvidia.eightfold.ai/events/candidate/landing?plannedEventId=vDKBy8oxN</t>
+        </is>
+      </c>
+      <c r="L241" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M241" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N241" s="3" t="inlineStr">
+        <is>
+          <t>@ nvidia.eightfold.ai CG:
+Instagram
+GA NVIDIA.
+Events &gt;... &gt;
+Stanford: Life, Culture &amp; Careers at
+NVIDIA - 10/5/2026
+Description
+Meet NVIDIA enginee are their career
+paths, what it means to ife's work, and the
+NVIDIA culture. Learn wha riences helped them
+succeed in their current roles and how they continue
+to grow both personally and professionally. Whether
+you're curious about our teams, emerging
+technology, exploring career opportunities, or
+entering to win NVIDIA prizes, this session is for you.
+Thank you to Stanford's SWE and SOLE in this
+partnership opportunity and platform to engage
+Powered by ¢f’ eightfold.ai #WhatsNextForYou
+https://scontent-hou1-1.cdninstagram.com/v/t51.71878-15/829340288_1396927832554591_8150523107126637860_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5Njk0ODc3NTUwNzU3NTc2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=msVdS0y2RAEQ7kNvwGlfcgQ&amp;_nc_oc=Adr_Xze90YcrOTRMta0KS0i8mEDWbhgQT5LPhK673eZCMVVz2jcB4Ukitr1G4yyh-oU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=JcwnSmXjd7w-XLn9Ah-rxQ&amp;_nc_ss=7e3ba&amp;oh=00_AQNT7mN3jVAM87S-HOQjgxsHDLhJyNkLw48hX5FB79RtDQ&amp;oe=6AC1976B
+https://scontent-hou1-1.cdninstagram.com/v/t51.71878-15/829340288_1396927832554591_8150523107126637860_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5Njk0ODc3NTUwNzU3NTc2NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=msVdS0y2RAEQ7kNvwGlfcgQ&amp;_nc_oc=Adr_Xze90YcrOTRMta0KS0i8mEDWbhgQT5LPhK673eZCMVVz2jcB4Ukitr1G4yyh-oU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_gid=JcwnSmXjd7w-XLn9Ah-rxQ&amp;_nc_ss=7e3ba&amp;oh=00_AQO1AzjjbfoY5zV6CM07mz_-tt3yaTLHKNVA5ZKYBctQPg&amp;oe=6AC1976B
+https://scontent-hou1-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwF7ZyjY&amp;_nc_oc=AdroHIbI3YIcCOFwRHOz8Xz5vafN0TX55rc7FV8Gttc4Fb0odl8mqpcPIo0zPuZYtuc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQNIw5_LTdsPGz3JtlfpB3TyOdCNLCJ3oh94UpeUycmS1w&amp;oe=6AC199D9
+https://l.instagram.com/?u=https%3A%2F%2Fnvidia.eightfold.ai%2Fevents%2Fcandidate%2Flanding%3FplannedEventId%3DvDKBy8oxN%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadomxnuzBb4m-7iQZeJiemh0wSSOGYsIZsjC4n-9jE7zuPvVAqOwU3-kHKs4g_aem_qM_07kfiAniNAUnNf1Txow&amp;e=AUAFbZu8-T2wV9yuSFS1BtrALxhXLmMkLNgRt5ZL3Ll0htTCvmKPijtkPBnuS4Qxg6PpQ_ideaW3l4sc43Db28upbfVAsB_72ajnv4X27w
+https://scontent-hou1-1.cdninstagram.com/o1/v/t2/f2/m78/AQN_KEy2nBmTFuxOGQI8gx-YfAoNfC0HX0d-mnTrEOmfx3jmBy_z3miGg_WvtTVIrrtMtMBm45GZn5wzQue3hRqI1s-GonNPl9MSoGA.mp4?_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-hou1-1.cdninstagram.com&amp;_nc_ohc=MpsPgoHqmuQQ7kNvwGZq4Y9&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg5ODAwOTg2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=b7c0f0c2a4491795&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzgzQUMxNUY5MTQ3QjQ2NzQ5RTVFMkI0NTE1RjUwQzZEX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkgoySnPWhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=JcwnSmXjd7w-XLn9Ah-rxQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQPohS0ekx-f1Z--27IriHtj4DiqbEH6gmThCiMHudym3w&amp;oe=6ABDBE45</t>
+        </is>
+      </c>
+      <c r="O241" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P241" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q241" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R241" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R240"/>
+  <autoFilter ref="A1:R241"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -23879,6 +23981,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L239" r:id="rId461"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K240" r:id="rId462"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L240" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K241" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L241" r:id="rId465"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$260</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R241"/>
+  <dimension ref="A1:R260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23416,7 +23416,7 @@
     <row r="241" ht="45" customHeight="1">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>ebf53b8b5b9b3dc5cc0b</t>
+          <t>78144c48bfac5b47042a</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -23454,8 +23454,8 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="I241" s="3" t="inlineStr"/>
-      <c r="J241" s="3" t="inlineStr"/>
+      <c r="I241" s="3" t="n"/>
+      <c r="J241" s="3" t="n"/>
       <c r="K241" s="4" t="inlineStr">
         <is>
           <t>https://nvidia.eightfold.ai/events/candidate/landing?plannedEventId=vDKBy8oxN</t>
@@ -23513,10 +23513,1820 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R241" s="3" t="inlineStr"/>
+      <c r="R241" s="3" t="n"/>
+    </row>
+    <row r="242" ht="45" customHeight="1">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>51d46c1be71c58bee683</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:53:25.463753+00:00</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T16:57:02+00:00</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr"/>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>2027 Internship</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G242" s="3" t="inlineStr"/>
+      <c r="H242" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I242" s="3" t="inlineStr"/>
+      <c r="J242" s="3" t="inlineStr"/>
+      <c r="K242" s="4" t="inlineStr">
+        <is>
+          <t>https://mycareer.verizon.com/jobs/r-1101384/verizon-network-and-technology-data-science-summer-2027-internship?source=zero2sudo</t>
+        </is>
+      </c>
+      <c r="L242" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M242" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N242" s="3" t="inlineStr">
+        <is>
+          <t>x @ mycareer .verizon.com G :
+Instagram At °
+Intern
+Verizon Network and
+Technology: Data
+Science Summer
+2027 Internship
+Irving, Texas
+Job ID: R-1101384
+@ MYCAREER.VERIZON.COM
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/825324829_1138770825281075_1895271968984414159_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5NzAxMjM1Nzg2ODM2ODIzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=JVx2Z-MCFN4Q7kNvwH8F4w5&amp;_nc_oc=AdpBiDTIU24I7AZITjDdcMpJqqGVzwYvo8_QB_9QMnWzG5fy8jY_ifQ3tiKbgX2CtXc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQP9o4qC0CSfjIURsSvjFnWRE33qDDvLfs4CLJF-rCkRcQ&amp;oe=6AC1F4E6
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/825324829_1138770825281075_1895271968984414159_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5NzAxMjM1Nzg2ODM2ODIzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=JVx2Z-MCFN4Q7kNvwH8F4w5&amp;_nc_oc=AdpBiDTIU24I7AZITjDdcMpJqqGVzwYvo8_QB_9QMnWzG5fy8jY_ifQ3tiKbgX2CtXc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQOk5I-rw8wp6V8VxHkTWyXPVqOTGH6fhOt_dBKwEGq2mg&amp;oe=6AC1F4E6
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwG-i5gH&amp;_nc_oc=AdqLIluHqu85V8LolXYTSzAm4CTUcCGacgklFopcBKDFO_Q4h9OwQ7j87geDJ4P1ch4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQNHzk9uZAjA805E7EJaTVCSVzLgg3XMu1Tthq10rgjPKQ&amp;oe=6AC20A59
+https://l.instagram.com/?u=https%3A%2F%2Fmycareer.verizon.com%2Fjobs%2Fr-1101384%2Fverizon-network-and-technology-data-science-summer-2027-internship%2F%3Fsource%3Dzero2sudo%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafLJYYA2HonLdKiKLt9fEQOzMytPXKMdjtwD_MHWmcZLEAVYnnUQ5Us1vXyKw_aem_jA-e2wzvzr_tf2oDtn0tMg&amp;e=AUBWQ3Ki5nGXf1QArhRWr0u0vaRSPQYBS_nvgTv8yeTVGy64L_GQGNQzZdPVuIl2oYQ0ioKIo8EKMIP7RE_t65ljvbS__6jOnOpfvuu_DA
+https://scontent-sjc6-1.cdninstagram.com/o1/v/t2/f2/m78/AQOX51sAssIehNCagLKZHWsSaNCtpdn_iMHU6zWc4iytS7UsbnfhM7-UY21iCaQNZAC9Py8e_k3uEhtka_MIGzbZU5U_INLA4qVJIXU.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ohc=fhxZBafLc_QQ7kNvwHfBkVV&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg5OTY0MzA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=66ef516c793d7678&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0Y4NUMwNDBFMkNGMjQzMDZCRjEwQTY3RDA2Qzk4RUUzX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkrsDplfahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQO3_hcPtx4xRYyaChxzXLnAg4AtMLgPbyu25HWMBN6cYQ&amp;oe=6ABE1251</t>
+        </is>
+      </c>
+      <c r="O242" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P242" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q242" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R242" s="3" t="inlineStr"/>
+    </row>
+    <row r="243" ht="45" customHeight="1">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>8d4e8aede174fdbcdd2d</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:53:27.179466+00:00</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T16:57:44+00:00</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr"/>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>2027 Internship</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G243" s="3" t="inlineStr"/>
+      <c r="H243" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I243" s="3" t="inlineStr"/>
+      <c r="J243" s="3" t="inlineStr"/>
+      <c r="K243" s="4" t="inlineStr">
+        <is>
+          <t>https://mycareer.verizon.com/jobs/r-1101387/verizon-network-and-technology-business-intelligence-summer-2027-internship?source=zero2sudo</t>
+        </is>
+      </c>
+      <c r="L243" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M243" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N243" s="3" t="inlineStr">
+        <is>
+          <t>x @ mycareer.verizon.com C+:
+Instagram °
+Intern
+Verizon Network and
+Technology:
+Business
+Intelligence Summer
+2027 Internship
+Irving, Texas
+Job ID: R-1101387
+—w
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/829406908_1561901888575978_5242097408384838084_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5NzAxMjcwNTE4ODgxNzA3Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=RcOv8ZaV7WYQ7kNvwETUrsH&amp;_nc_oc=AdqCvKCpEdxWV8-3U4a2YZcTv5yCzKdRQdCY2Inv-61xwETxQ1hKc4MjY9tGL2ZAkQ0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQPm_f_Omc_vAemfkOPalwUgIpQBuCOKNWCY7TivP1aw4A&amp;oe=6AC21192
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/829406908_1561901888575978_5242097408384838084_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5NzAxMjcwNTE4ODgxNzA3Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=RcOv8ZaV7WYQ7kNvwETUrsH&amp;_nc_oc=AdqCvKCpEdxWV8-3U4a2YZcTv5yCzKdRQdCY2Inv-61xwETxQ1hKc4MjY9tGL2ZAkQ0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQMwm4VJNYGF9zp-E01HozWYUSPPHoMA4dJ-NdgOlZU-AA&amp;oe=6AC21192
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwG-i5gH&amp;_nc_oc=AdqLIluHqu85V8LolXYTSzAm4CTUcCGacgklFopcBKDFO_Q4h9OwQ7j87geDJ4P1ch4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQNHzk9uZAjA805E7EJaTVCSVzLgg3XMu1Tthq10rgjPKQ&amp;oe=6AC20A59
+https://l.instagram.com/?u=https%3A%2F%2Fmycareer.verizon.com%2Fjobs%2Fr-1101387%2Fverizon-network-and-technology-business-intelligence-summer-2027-internship%2F%3Fsource%3Dzero2sudo%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadLJt7yITSeWN9BF25f9cpfBIJCmMlCjsTRIK_wX5_UxY5DvYZXwsJeZ3T6HQ_aem_pupDM0ZJpDDV3WrMaK6xhQ&amp;e=AUCvBe25JBSCC54yCHNkbHw5gyHd1Xz5O-E3kjybgAu-2X_4wUVTAvyGeFKUXfRS6xiyTOEEoDFSA6Y-5pKUeOQj0jVW-NVFq7c-vE1CWg
+https://scontent-sjc3-1.cdninstagram.com/o1/v/t2/f2/m78/AQNefZmE4fx0Rfmfdlw9CeQdlJZWWBJJU3TkOpDVZzkZziVqY992hEWwW8w4ZKfgkSVSRpJzgaVCa8bjGS-mSmgA9FW-ojHcepS-06w.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_ohc=WUvYq2c7j8YQ7kNvwEE9ESj&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg5OTY1NTM2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=a2d2adb6f2b89d4b&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzg2ODQwNTVEMTJCNzRDRjFCQzRDMUUzRDg4N0RFNDFDX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkgefelvahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQNCSffRVwz_6sYpGqsRTGuF6xFTKxZpzQ-wdPaT6V3G_A&amp;oe=6ABDF93C</t>
+        </is>
+      </c>
+      <c r="O243" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P243" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q243" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R243" s="3" t="inlineStr"/>
+    </row>
+    <row r="244" ht="45" customHeight="1">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t>d28453ccf88a2b9e506c</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:53:29.266750+00:00</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T16:58:44+00:00</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>Thecignagroup</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>Thecignagroup — Internship</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G244" s="3" t="inlineStr"/>
+      <c r="H244" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I244" s="3" t="inlineStr"/>
+      <c r="J244" s="3" t="inlineStr"/>
+      <c r="K244" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.thecignagroup.com/us/en/job/CIGNUS26010877EXTERNALENUS/AI-ML-Engineer-Intern</t>
+        </is>
+      </c>
+      <c r="L244" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M244" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N244" s="3" t="inlineStr">
+        <is>
+          <t>fl
+J
+@ jobs.thecignagroup.com Ee
+Instagram
+AI/ML Engineer
+Intern
+This job is available in 3 locations
+See all | Admin/Corporate
+Services | 09/29/2026 | 26010877
+LARA TLIFTARAIAARAILAARRAIIF ARAB
+f 1B, at f NE Fh sai Pg fF | Fi!
+Me =| | IN QIisahM ae AV
+Jee TE PLA IIIPAVI ‘ VJ IVI
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/829473171_1665754445163291_5221382130899568497_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5NzAxMzIxNDUyOTI5NTIyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=aExaFsjklOIQ7kNvwHlSZKZ&amp;_nc_oc=AdoTG8rx_3IwNQfVzlglO5VEVmaxtRsRMyu-O6afmpCs2dr8XKomiW4SZ_5CziK0CB4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQNtjVGX7OuvzzZwLXUROG2--qepTEYJfvQ9yeynCW5jQA&amp;oe=6AC2059C
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/829473171_1665754445163291_5221382130899568497_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5NzAxMzIxNDUyOTI5NTIyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=aExaFsjklOIQ7kNvwHlSZKZ&amp;_nc_oc=AdoTG8rx_3IwNQfVzlglO5VEVmaxtRsRMyu-O6afmpCs2dr8XKomiW4SZ_5CziK0CB4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQPaJtG5__ljIhYjMTd9xYnKp8YxU_7jWcklGrereiucyw&amp;oe=6AC2059C
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwG-i5gH&amp;_nc_oc=AdqLIluHqu85V8LolXYTSzAm4CTUcCGacgklFopcBKDFO_Q4h9OwQ7j87geDJ4P1ch4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQNHzk9uZAjA805E7EJaTVCSVzLgg3XMu1Tthq10rgjPKQ&amp;oe=6AC20A59
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.thecignagroup.com%2Fus%2Fen%2Fjob%2FCIGNUS26010877EXTERNALENUS%2FAI-ML-Engineer-Intern%3Futm_source%3Dzero2sudo%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeR2t0aocWk7d27ADSMHnHJ3lH8DffGlRgDgMmScuwIanAJHNouawuZM36cpA_aem_eCzIC6MIrjjIOUhA-3lTIg&amp;e=AUBXHcNBrC_O1Lk09b7PH6bMbHYByJhLTe6xkhnkl-1dybg9sT5RN4o0ZQYNlLKHQLZz5ltpuqtA1gaRjHZb_ZWuGfrWObCRID9GsRztew
+https://scontent-sjc6-1.cdninstagram.com/o1/v/t2/f2/m78/AQMJ1u-nlzMR8VgjXyJYfTqU_8NqfQeMdkrwSiDsvME92tPNj9hAlUgQSNI1ko-L_bSMyssFfPX-vHdtEX-DU7IjqU0QkPeaY6Zb4WQ.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ohc=-rUvSqETVToQ7kNvwGL0T-V&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg5OTY2NzM2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=cfe6217250edb59f&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzJDODE0NTMzNThCQjQ3MkI4Q0Y5QzVFMTNGNThGODg2X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkuZ_Rl_ahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQMFRULwqLBAw5cCXaJchzdq9vLp8ar0aIR04nSOMxW-RA&amp;oe=6ABE0336</t>
+        </is>
+      </c>
+      <c r="O244" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P244" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q244" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R244" s="3" t="inlineStr"/>
+    </row>
+    <row r="245" ht="45" customHeight="1">
+      <c r="A245" s="3" t="inlineStr">
+        <is>
+          <t>994f7bbf3ef4cd429dd8</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:53:30.871961+00:00</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T16:59:37+00:00</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr"/>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>Hybrid NewYork(US)  40hours — Internship</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G245" s="3" t="inlineStr"/>
+      <c r="H245" s="3" t="inlineStr"/>
+      <c r="I245" s="3" t="inlineStr"/>
+      <c r="J245" s="3" t="inlineStr"/>
+      <c r="K245" s="4" t="inlineStr">
+        <is>
+          <t>https://rabobank.jobs/en/job/gem-summer-commodities-intern/JR_00146162</t>
+        </is>
+      </c>
+      <c r="L245" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M245" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N245" s="3" t="inlineStr">
+        <is>
+          <t>@ rabobank.jobs C:
+Rabobank
+Corporate banking
+GEM Summer Commodities
+Intern
+Hybrid NewYork(US)  40hours — Internship
+Skills match v Apply
+Transform commodities data into clear
+@ RABOBANK.JOBS
+Our Shared
+“Use data, technology and thoughtful
+analysis to strengthen collaboration,
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/829941226_4398491560362848_8390972127212666595_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5NzAxMzY1NTk5NjQ3NzExOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=qdcD-LnUMGIQ7kNvwHzDy5E&amp;_nc_oc=AdrPv3E6v7UfCbiE-HgpUt4u14sn7tueafawjU0xt0EZBfnZWmxykGGADfCxDb3BmPI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQOFy6vB61_-ipbd-RjTWYabcwzMqAyXp-54cuNHTDWvKA&amp;oe=6AC1E845
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/829941226_4398491560362848_8390972127212666595_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5NzAxMzY1NTk5NjQ3NzExOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=qdcD-LnUMGIQ7kNvwHzDy5E&amp;_nc_oc=AdrPv3E6v7UfCbiE-HgpUt4u14sn7tueafawjU0xt0EZBfnZWmxykGGADfCxDb3BmPI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQOTrxmyvOfuDnHU3eRMwdhTwhyh8qzTGNKvz9V2fmrEgA&amp;oe=6AC1E845
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwG-i5gH&amp;_nc_oc=AdqLIluHqu85V8LolXYTSzAm4CTUcCGacgklFopcBKDFO_Q4h9OwQ7j87geDJ4P1ch4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQNHzk9uZAjA805E7EJaTVCSVzLgg3XMu1Tthq10rgjPKQ&amp;oe=6AC20A59
+https://l.instagram.com/?u=https%3A%2F%2Frabobank.jobs%2Fen%2Fjob%2Fgem-summer-commodities-intern%2FJR_00146162%2F%3Futm_source%3Dzero2sudo%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadpalVkkLUiXXgNNth8qJbXp8nWwR41-dhDX3Og0tEXVin4N1I5wIwjkftduA_aem_A6OSre_74aunHQAfqZmBzg&amp;e=AUCom4vIKVx-33-8TTGsCzZoh-GeW1_VqScx6vnzBpdNNKPy31EijYZFlA-U_LJn2ST1Vxnp48AO2Ks8BEiqj6KZMbvSt6_Dx5j49e5FYQ
+https://scontent-sjc3-1.cdninstagram.com/o1/v/t2/f2/m78/AQNckKJPYl7dq24czAjiKoG2LZymbIu0kTZ3b0QB_re5l0nstf6ZMBOybb0PrkYdTl2II4lWOV0uATX5TcsnzRarEoU5rHSQJXH2gFE.mp4?_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_ohc=0SxOK05qyt4Q7kNvwE3xR3G&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg5OTY4NjI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=48b6ecc22db648c1&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzIwQUM5QzBFRDAwMTQwOTJBREU4RTVFN0QzOUJFNzg1X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk3r6FmfahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQOrBl5ZoGUouElSPHCrhg84m5zShFITPLTu2u51RDFSSg&amp;oe=6ABE087E</t>
+        </is>
+      </c>
+      <c r="O245" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P245" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q245" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R245" s="3" t="inlineStr"/>
+    </row>
+    <row r="246" ht="45" customHeight="1">
+      <c r="A246" s="3" t="inlineStr">
+        <is>
+          <t>d084ecdd147b379efe41</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:53:33.238707+00:00</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T17:00:14+00:00</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>Workable — Other Opportunity</t>
+        </is>
+      </c>
+      <c r="F246" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G246" s="3" t="inlineStr"/>
+      <c r="H246" s="3" t="inlineStr"/>
+      <c r="I246" s="3" t="inlineStr"/>
+      <c r="J246" s="3" t="inlineStr"/>
+      <c r="K246" s="4" t="inlineStr">
+        <is>
+          <t>https://apply.workable.com/bestex-research/j/AE65B49EA3</t>
+        </is>
+      </c>
+      <c r="L246" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M246" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N246" s="3" t="inlineStr">
+        <is>
+          <t>@ apply.workable.com G
+BestEx
+= -RESEARCH
+7°
+Algorithmic Trading Analyst
+On-site - Full time
+Stamford, Connecticut, United States
+OVERVIEW APPLICATION
+Description Share this job &lt;
+BestEx Research is a financial technology and
+racaarch firm enarcializina in hiuildina
+@ APPLY.WORKABLE.COM
+multiple asset classes. rm provides high-
+performance algorit tion services to
+hedge funds, CTAs, as agers, and banks
+through a traditional electronic broker and ina
+broker-neutral Software as a Service (SaaS)
+model.
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/828599001_1807230340430851_5962884147000149155_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5NzAxMzk2MzYzOTk2NjU2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Wv2ZMeVSEqgQ7kNvwE90_yC&amp;_nc_oc=AdqDulLCGcoTrlYpEfkQVyC9g9bynO6GKWeByTT1Z4od-CRIMZTdCi2Aax_12BrR0L8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQO1D4QsQa8MZz9iNQ1z5bL9yuew4HYSBZGiO8bp30WlLw&amp;oe=6AC1E4B5
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/828599001_1807230340430851_5962884147000149155_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5NzAxMzk2MzYzOTk2NjU2MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Wv2ZMeVSEqgQ7kNvwE90_yC&amp;_nc_oc=AdqDulLCGcoTrlYpEfkQVyC9g9bynO6GKWeByTT1Z4od-CRIMZTdCi2Aax_12BrR0L8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQMWW4_rljBrYLslzKB0GZ67qnyxJYmr0FIJJU355IiEQQ&amp;oe=6AC1E4B5
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwG-i5gH&amp;_nc_oc=AdqLIluHqu85V8LolXYTSzAm4CTUcCGacgklFopcBKDFO_Q4h9OwQ7j87geDJ4P1ch4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQNHzk9uZAjA805E7EJaTVCSVzLgg3XMu1Tthq10rgjPKQ&amp;oe=6AC20A59
+https://l.instagram.com/?u=https%3A%2F%2Fapply.workable.com%2Fbestex-research%2Fj%2FAE65B49EA3%2F%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaefW9-HAxYX4OgrE5-cYNtYpdjsL8WY1z7RqRrxxNeJ0FfIy5M4k6H_vDALuA_aem_pBMgBwI7mQ2g6nG01YjrkQ%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUBIi-2ME8dE8g-z9tN4bqIERrme_wOTmB-6BU77_YL9sgk5YJ2vlkDOPc8Q5luQVAsgjXojgRe0iacJUtd7DppQoWs5MZC2gowff5pUPw
+https://scontent-sjc6-1.cdninstagram.com/o1/v/t2/f2/m78/AQOYDJJh0mtRh1f3swVfVqrTBYj93bFJX6Nl0ialvQgm9VmpeFKZrYmsCb8ipTb-XoudcThR81hKjEngNZqDjkCf-RpUQqV1mAMFPs8.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ohc=FUsGnda7r5UQ7kNvwHSh9rC&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg5OTY5NzA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=3a395a6bf32f9cf0&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0U3N0VGRkVBODIzOTQ5QUE5RTJDMTE5RkNENDEzOTc0X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkqr7smfahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQNw-rt402RXoqJAyeIPQgqz4EToEQKxldJwrqZ_m9ZtDg&amp;oe=6ABE1BCE</t>
+        </is>
+      </c>
+      <c r="O246" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P246" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q246" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R246" s="3" t="inlineStr"/>
+    </row>
+    <row r="247" ht="45" customHeight="1">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>7d8d80f7a1cba8ffe72a</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:53:35.931984+00:00</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T17:01:39+00:00</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>NVIDIA — Product Management</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G247" s="3" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="H247" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I247" s="3" t="inlineStr"/>
+      <c r="J247" s="3" t="inlineStr"/>
+      <c r="K247" s="4" t="inlineStr">
+        <is>
+          <t>https://nvidia.eightfold.ai/events/candidate/landing?plannedEventId=5eQmdl8bk</t>
+        </is>
+      </c>
+      <c r="L247" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M247" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N247" s="3" t="inlineStr">
+        <is>
+          <t>tagra
+@ nvidia.eightfold.ai C+:
+GSINVIDIA.
+&gt; i. oo
+' Events &gt; MIT: NVIDIA Career Connect 9/29/2026
+MIT: NVIDIA Career Connect 9/29/2026
+(3 Sep 29 2026, 10:00 AM - 4:00 PM EDT
+@ Happening
+Q MIT, Schwarzman College of Computing (45-801), 51
+Vassar Street, Cambridge, MA
+@ NVIDIA.EIGHTFOLD.AI
+Description
+NVIDIA will be on-camp to connect with
+EECS students interested in Summer 2027
+Internship and New College Grad (NCG)
+opportunities.
+Q. We're Looking For:
+e B.S., M.S., M.Eng., and Ph.D. students currently
+enrolled at MIT
+MIT students Only! Join NVIDIA rn!
+a Ctitdante caalinna Crimmar 9097 Intarnchine
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/829725831_2327041658097740_2659956642182832656_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5NzAxNDY4MDI1NDc3MjE4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=PzhEQRs0Lk4Q7kNvwHXURyI&amp;_nc_oc=AdoAHsBQF62jKIkYKjI_lmog72nVwecYvWVf4_q1VCA7wj7343AP3HVyUWJKSHrqbi0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQMUPYFpwBGW_roe1B_WqqoW79WIVaIWbc9m8HC3pVFuGg&amp;oe=6AC1DD7D
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/829725831_2327041658097740_2659956642182832656_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk5NzAxNDY4MDI1NDc3MjE4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=PzhEQRs0Lk4Q7kNvwHXURyI&amp;_nc_oc=AdoAHsBQF62jKIkYKjI_lmog72nVwecYvWVf4_q1VCA7wj7343AP3HVyUWJKSHrqbi0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQN9tDy-V_s206c33_bEsADIW7HCX4UCVgzsSrU1exBFHw&amp;oe=6AC1DD7D
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwG-i5gH&amp;_nc_oc=AdqLIluHqu85V8LolXYTSzAm4CTUcCGacgklFopcBKDFO_Q4h9OwQ7j87geDJ4P1ch4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQNHzk9uZAjA805E7EJaTVCSVzLgg3XMu1Tthq10rgjPKQ&amp;oe=6AC20A59
+https://l.instagram.com/?u=https%3A%2F%2Fnvidia.eightfold.ai%2Fevents%2Fcandidate%2Flanding%3FplannedEventId%3D5eQmdl8bk%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadmr4aeTw-3nOQTW-ZoT1a5Vmf_2L-pQ2AzdO88FWjbi33hk3tdOab7tw1_jQ_aem_eKIgHmnrGBiMsKjq-0UbxQ&amp;e=AUCKtPeayvaRjwOgI7mZEa0gHvVO2581SjvJeezwTgCerhjJuNSfZd75gQC3JQxWjDCUVefuZnMdKPYNCpe5vLQ1RThB5E6l_Z5TNX4ftw
+https://scontent-sjc6-1.cdninstagram.com/o1/v/t2/f2/m78/AQMZ_oy0qxOhKX0lUAqVtSKBgX4LHzOY8fdo-jQ1nK35P04LuwCT7T6jmtyYbvu1umY3jPqDHGfeIjz7tpz4w1CXP8ztkVOc012-yLc.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ohc=ASlQgLqEurgQ7kNvwHMgn7y&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODg5OTcyNDY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=417e3b35c1c7fbd1&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzUxQTk3NDVBOUJDNzRBQjM4MDIyNjREREVCRjIyQzE5X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk3tnzm_ahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQNKZDnrwLohXVQhrpXQPfpDkrl8EjjH0BIggciD0YFwlw&amp;oe=6ABE1355</t>
+        </is>
+      </c>
+      <c r="O247" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P247" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q247" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R247" s="3" t="inlineStr"/>
+    </row>
+    <row r="248" ht="45" customHeight="1">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t>de2cb56293a05bc8d9ad</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:53:41.585407+00:00</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T17:50:21+00:00</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>Thrivent</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>Thrivent — Internship</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G248" s="3" t="inlineStr"/>
+      <c r="H248" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I248" s="3" t="inlineStr"/>
+      <c r="J248" s="3" t="inlineStr"/>
+      <c r="K248" s="4" t="inlineStr">
+        <is>
+          <t>https://thrivent.wd5.myworkdayjobs.com/external/job/Mpls-Investments-Office/IT-Application-Engineer-Intern--Investments---Summer-2027_REQ-48511-2</t>
+        </is>
+      </c>
+      <c r="L248" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M248" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N248" s="3" t="inlineStr">
+        <is>
+          <t>2 Sign In
+thrivent
+Thrivent Careers
+IT Application Engineer Intern,
+Investments - Summer 2027
+© Mpls-Investments Office
+Full time
+©) Posted Today
+(2) THRIVENT.WD5.MYWORKDAYJOBS.C
+Our top-rated summe hip program is
+designed to give college students meaningful
+work experience in specific functions, providing
+a deeper understanding of the processes of a
+Fortune 500 financial services organization.
+The program offers interesting challenges,
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/829136271_972359378482902_3237795259043774865_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5NzAzOTE5MTM4OTA2OTk2Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=W-g1BoxFOH8Q7kNvwGy8VsA&amp;_nc_oc=AdoiH-w1ag8QmOKgbutZ-_m62xv6EClN5H5qRHNgTStOUmpOK40gaeDNFYiLc1OUNZY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQMiWGomKI6IKIdVN4J3edNPWGrpV0ffXjHC8YdiOlME6g&amp;oe=6AC20D31
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/829136271_972359378482902_3237795259043774865_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5NzAzOTE5MTM4OTA2OTk2Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=W-g1BoxFOH8Q7kNvwGy8VsA&amp;_nc_oc=AdoiH-w1ag8QmOKgbutZ-_m62xv6EClN5H5qRHNgTStOUmpOK40gaeDNFYiLc1OUNZY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQMK3vXYKTCdKoaTxi8J9nmNtLlqpjnTLhMPgLYkWDdSgQ&amp;oe=6AC20D31
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwG-i5gH&amp;_nc_oc=AdqLIluHqu85V8LolXYTSzAm4CTUcCGacgklFopcBKDFO_Q4h9OwQ7j87geDJ4P1ch4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQNHzk9uZAjA805E7EJaTVCSVzLgg3XMu1Tthq10rgjPKQ&amp;oe=6AC20A59
+https://l.instagram.com/?u=https%3A%2F%2Fthrivent.wd5.myworkdayjobs.com%2Fexternal%2Fjob%2FMpls-Investments-Office%2FIT-Application-Engineer-Intern--Investments---Summer-2027_REQ-48511-2%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacP4HQr8IiQg1Yv2QS5i2JC5OQuf2M89deqMAoKYEdC9_gGwT21mNqtl1eS2Q_aem_GiHB5hmLLUK5yjhwgP1-uw%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUA4JqENsd_o7Uee_KD2GeKiEvd_8408_aOK3U9WfYM5MHo6cO8Tbwj2eBPx2ABZS8fFvPjOcwI2Dq4MvH94t9LTp3O_-RIze-a8eNKYgg
+https://scontent-sjc6-1.cdninstagram.com/o1/v/t2/f2/m78/AQPv314FZP0NhHwNExeV21yDKr8ASIsdTEvSfVCS3Z1sdRUpKrFEhEiEerGrfcbS4bqO6pMPjbdzPRQ2jCTKjSpZQBspEyuUJqp6NqA.mp4?_nc_cat=104&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ohc=PiWPB1G-lioQ7kNvwFNzveZ&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwMDQ3NjE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=9359e04e2ba6fe61&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzIzRTNBNjUzQ0JEMjQyODU5M0NFMDMyREUwM0VDNzk4X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkkcjy0_ahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQPFdMNwvL1WLfv0DjhRIzMxY-cIoSFmhf5ZYhgTcX_AHg&amp;oe=6ABE0D09</t>
+        </is>
+      </c>
+      <c r="O248" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P248" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q248" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R248" s="3" t="inlineStr"/>
+    </row>
+    <row r="249" ht="45" customHeight="1">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>f5ca240c5e76c42a1d27</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:53:44.016285+00:00</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T17:51:03+00:00</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>Garmin</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>Garmin — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G249" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H249" s="3" t="inlineStr"/>
+      <c r="I249" s="3" t="inlineStr"/>
+      <c r="J249" s="3" t="inlineStr"/>
+      <c r="K249" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.garmin.com/jobs/20255?icims=1</t>
+        </is>
+      </c>
+      <c r="L249" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M249" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N249" s="3" t="inlineStr">
+        <is>
+          <t>CAREERS SEARCH JOBS MORE v
+&lt; BACK
+SOFTWARE ENGINEERING INTERN
+Req ID: 20255
+Location: Boulder, Colorado
+Shift: Core Business Hours
+Position Type: Intern
+Minimum Salary: USD $30.00/Hr.
+Maximum Salary: USD $36.00/Hr.
+Work Environment: On-site
+Overview
+We are seeking a full-time Software Engineering Intern
+at our office in Louisville, CO. In this role, you will be
+@ CAREERS. GARMIN.COM
+Essential Functions
+e Learn to develop soft , C++, Assembly
+language, or other selected languages for Garmin
+communication and navigation products in
+accordance with Garmin's software development
+©@00 G&amp;
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/825277255_1082959211129058_7442750718298659862_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5NzAzOTU0MTg5MDI4NDg1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=6i34R4rkjVAQ7kNvwEijfFH&amp;_nc_oc=AdrKVs6CC1-Wy_3udpCehxrSFNwVE-BnFc9REX3WSILL1-5irplw6rdabwy2UCiEg5k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQMdOLmkDXat4vNXkGrZ-_OeVtwpIjXSrskehlTqMXOrfA&amp;oe=6AC1DD0F
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/825277255_1082959211129058_7442750718298659862_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5NzAzOTU0MTg5MDI4NDg1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=6i34R4rkjVAQ7kNvwEijfFH&amp;_nc_oc=AdrKVs6CC1-Wy_3udpCehxrSFNwVE-BnFc9REX3WSILL1-5irplw6rdabwy2UCiEg5k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQO5cC2_IhCKki7na6amui31db8a5aPc__7IOlGtHNEhnQ&amp;oe=6AC1DD0F
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwG-i5gH&amp;_nc_oc=AdqLIluHqu85V8LolXYTSzAm4CTUcCGacgklFopcBKDFO_Q4h9OwQ7j87geDJ4P1ch4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQNHzk9uZAjA805E7EJaTVCSVzLgg3XMu1Tthq10rgjPKQ&amp;oe=6AC20A59
+https://l.instagram.com/?u=https%3A%2F%2Fcareers.garmin.com%2Fjobs%2F20255%3Ficims%3D1%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAac1MV0koU8oaOF-zKh7cHJ1VGswrJZWNp_6QcDuQ2JFVvBnNDh_iU-nhzN73Q_aem_uhsB7kJpyYhTfoNpepWvSg&amp;e=AUAOWnkQqqiM00Sh9tmFtGxhHlHY83Cfua-NWWbkrQHj1ZJ6ODUGrrl5PC1EO5YPkcS6kuZ0MQdPdOLcDF4sCXRYU9xKZEF9racoC8t6-A
+https://scontent-sjc6-1.cdninstagram.com/o1/v/t2/f2/m78/AQMVip_jpPzgf8pQJKh8V25iRCdB7jCyA59R3IhrzeqhFkvmPpvgcuo110jRm6nav9cYC98_NOSMbaTtfgWUcLLFeJ68ycN_yQsG1ro.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ohc=OnUZTX6A0UUQ7kNvwG0q3iD&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwMDQ4NjM2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=aba44134c2d9bcb3&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzYwOUYxODRCMDJCNDQ5Qzc5MjA0ODRENDRFRjkwRDNGX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkp-vT1PahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQMA69Ht3lTtzvTg5DuyMhKAml1ucYtBD07EWbcimX4ltQ&amp;oe=6ABE0BC9</t>
+        </is>
+      </c>
+      <c r="O249" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P249" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q249" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R249" s="3" t="inlineStr"/>
+    </row>
+    <row r="250" ht="45" customHeight="1">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>58746889ae25d01fa746</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:53:46.460932+00:00</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T17:51:40+00:00</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr"/>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>Summer Internship Program, open to students</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G250" s="3" t="inlineStr">
+        <is>
+          <t>Machine Learning / AI, Data Science</t>
+        </is>
+      </c>
+      <c r="H250" s="3" t="inlineStr">
+        <is>
+          <t>2026, 2027</t>
+        </is>
+      </c>
+      <c r="I250" s="3" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="J250" s="3" t="inlineStr"/>
+      <c r="K250" s="4" t="inlineStr">
+        <is>
+          <t>https://careers-hrblock.icims.com/jobs/76992/job?mobile=true&amp;needsRedirect=false</t>
+        </is>
+      </c>
+      <c r="L250" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M250" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N250" s="3" t="inlineStr">
+        <is>
+          <t>Returning Candidate or Current Associate?
+Log back in!
+Machine Learning Intern - S
+US-MO-KANSAS CITY 2026-76992
+Category Data Science &amp; Analytics
+Full-Time/Part-Time Full-Time Remote No
+About the Role
+Turn your classroom learning into real-world
+impact with H&amp;R Block’s Embark 2027
+Summer Internship Program, open to students
+studying Computer/Data Science, Machine
+Learning, or Applied/Computational
+(Z) CAREERS-HRBLOCK.ICIMS.CON
+valuable impact on ation.
+The Embark 2027 Sum ernship runs
+You'll work at our corporate headquarters in
+the heart of downtown Kansas City’s Power &amp;
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/829340311_1105528798838286_8819094482589723330_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5NzAzOTg1NTE3OTY0MzMyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=U_zADzKBE2kQ7kNvwFSzCAM&amp;_nc_oc=AdqVYvkjiIrJdDkH7p2KWTDUsMXGSmB9I7VpwmVfwxwX95nEs4l1Wflw5x1sxVTO6W8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQPkqZpYiTo-X05v0Lttnab42WABLuTGhBKcHLuKo4d5uA&amp;oe=6AC1E801
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/829340311_1105528798838286_8819094482589723330_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5NzAzOTg1NTE3OTY0MzMyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=U_zADzKBE2kQ7kNvwFSzCAM&amp;_nc_oc=AdqVYvkjiIrJdDkH7p2KWTDUsMXGSmB9I7VpwmVfwxwX95nEs4l1Wflw5x1sxVTO6W8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQPJIMT1uL7ncPD00ZiX8GwhYqSGhU6vpDECYMBjp9MtUA&amp;oe=6AC1E801
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwG-i5gH&amp;_nc_oc=AdqLIluHqu85V8LolXYTSzAm4CTUcCGacgklFopcBKDFO_Q4h9OwQ7j87geDJ4P1ch4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQNHzk9uZAjA805E7EJaTVCSVzLgg3XMu1Tthq10rgjPKQ&amp;oe=6AC20A59
+https://l.instagram.com/?u=https%3A%2F%2Fcareers-hrblock.icims.com%2Fjobs%2F76992%2Fjob%3Fmobile%3Dtrue%26needsRedirect%3Dfalse%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafoL5pHWLmIbxoifSGo5ZP8x8E-Yd4dFu7DzkDySwOhWpbaK4HXse5pIMqd_Q_aem_qA1bhX0CH_TmAmfnbRA2zg&amp;e=AUCZjUKUZZfJ3i2fM2r_-DvRAEbHP0HnjOqECbNmcn2-Y1q7wFkfEgwqYGzWTrFFDrGQBrrgrEd9-n8BdWp9mvj1zbVdM7ZniCtjm5uMHQ
+https://scontent-sjc3-1.cdninstagram.com/o1/v/t2/f2/m78/AQMlL46DG3RO7jDoJgFRuUO2QDqrx8t2gPWt50L_fpfVcudH8S0ztLM4rPvi0MhMBZUXgx5yFFjmruQssU_kHXlsZVlMeOqyMevFYOo.mp4?_nc_cat=110&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_ohc=3jOF0tVcvPYQ7kNvwEiVVLY&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwMDUwOTQ2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=8d021ee4955846dc&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0QxQ0Y3Rjg1MUJCNDQwRkI5MjI2QjAzMzVBNTlGMDJCX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkxpGw1vahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQORDHZuKCQAuIzZ2p1eYzJrtk-QB2uNBmX0XGg8zmErhg&amp;oe=6ABDF3F3</t>
+        </is>
+      </c>
+      <c r="O250" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P250" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q250" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R250" s="3" t="inlineStr"/>
+    </row>
+    <row r="251" ht="45" customHeight="1">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t>917e6998c557997b20f3</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:53:48.044529+00:00</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T17:52:48+00:00</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>EA — Internship</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G251" s="3" t="inlineStr"/>
+      <c r="H251" s="3" t="inlineStr"/>
+      <c r="I251" s="3" t="inlineStr"/>
+      <c r="J251" s="3" t="inlineStr"/>
+      <c r="K251" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ea.com/en_US/careers/JobDetail/AI-Engineer-Intern/216223</t>
+        </is>
+      </c>
+      <c r="L251" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M251" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N251" s="3">
+        <f>A) Electronic Arts
+Al Engineer Intern
+Home / ... / Role Detail
+f=] General Information
+Locations
+: Vancouver, British Columbia, Canada
+Role ID: 216223
+Worker Type: Intern - Temporary Employee
+patter © JOBS,EA.COM *
+Work Model: Hybrid
+FE) Description &amp; Requirements
+Apply
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/830562739_1762099505012786_9118617483631914332_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5NzA0MDQyNDU0ODAwNzc3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=4AieacfWAKUQ7kNvwGczdN3&amp;_nc_oc=Adq3K_GWKlvy-RWk1TQb1cYL5NgxYmY5iBx5q5mMDH_Kl10FGNR_N9cmfM5izy-ZAfs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQMMrAdNVddfd8DiD4kOAdppPog3MwyipAKbApCRWFUEpA&amp;oe=6AC1DCD6
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/830562739_1762099505012786_9118617483631914332_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5NzA0MDQyNDU0ODAwNzc3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=4AieacfWAKUQ7kNvwGczdN3&amp;_nc_oc=Adq3K_GWKlvy-RWk1TQb1cYL5NgxYmY5iBx5q5mMDH_Kl10FGNR_N9cmfM5izy-ZAfs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQPwHNRAKKTY98uZI8JFol82z098NBp-CJXGMtuLNUHGzw&amp;oe=6AC1DCD6
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwG-i5gH&amp;_nc_oc=AdqLIluHqu85V8LolXYTSzAm4CTUcCGacgklFopcBKDFO_Q4h9OwQ7j87geDJ4P1ch4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQNHzk9uZAjA805E7EJaTVCSVzLgg3XMu1Tthq10rgjPKQ&amp;oe=6AC20A59
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.ea.com%2Fen_US%2Fcareers%2FJobDetail%2FAI-Engineer-Intern%2F216223%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafceFZEd34Eku487MbT0QLts45ZOIQfGB1VbQe5girwuF9OIzuwQJisylAPNw_aem_rv8ndsTaqMuY_zbizzIKmw&amp;e=AUBPArYQwyLD79OoXl4v80aMmDBEG_3vQvhSdFxx0aHX-k-mh2h8BUaxQyC7ILAKtjFDpjNIHQQtl94SXSjJOEtgOmvilZTB368LtzmInQ
+https://scontent-sjc6-1.cdninstagram.com/o1/v/t2/f2/m78/AQMS9Kw9MdAGNOYfvNsjdexROt4-WG8wBrbS7Tc8wNljctt_1k-V6vBSt710oxflYpXZ5CVdNd1vDZVUQG2MVtws9VD3E8Sdl-0AsHU.mp4?_nc_cat=102&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ohc=pvfnmPHcINAQ7kNvwEf1Zvy&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwMDUyMDU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=eb3b7bcab508a721&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0YxNTE1REEzQkYzMTQ4NkQ5QUZCMkNBQUU4NDMxMjgyX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkrf-Z1_ahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQOcWC0Wlo4O1Noxkbq3g6ZDtiBA-Nl_qpMRxJziyfVQFw&amp;oe=6ABE1F1B</f>
+        <v/>
+      </c>
+      <c r="O251" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P251" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q251" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R251" s="3" t="inlineStr"/>
+    </row>
+    <row r="252" ht="45" customHeight="1">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>3b7af2886260d103435e</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:53:50.034931+00:00</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T17:54:14+00:00</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr"/>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>Scientific Join Talent Network English v</t>
+        </is>
+      </c>
+      <c r="F252" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G252" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H252" s="3" t="inlineStr"/>
+      <c r="I252" s="3" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="J252" s="3" t="inlineStr"/>
+      <c r="K252" s="4" t="inlineStr">
+        <is>
+          <t>https://bostonscientific.eightfold.ai/careers/job/563602813547669</t>
+        </is>
+      </c>
+      <c r="L252" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M252" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N252" s="3" t="inlineStr">
+        <is>
+          <t>Boston, ; ,
+Scientific Join Talent Network English v
+€ View All Jobs
+R&amp;D Firmware
+Engineer Intern
+Q Arden Hills US-MN, United States | N/A
+Apply Now
+9 PA
+Add to cart |
+Niche Firmware Eng SWE experience
+like this can pay $270k/yr+ new grad
+match with this job
+(2) BOSTONSCIENTIFIC.EIGHTFOLD.Al
+Job description y and benefits
+Work Mode Requisition ID v P
+Oncita AZL4a4
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/830695971_1417478556994289_3018851148769238681_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5NzA0MTE0NTQ4MTczMDM5Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=4Kp4gSGK9aYQ7kNvwHwjiiQ&amp;_nc_oc=Adoy7AoZKsXAzLCASYL1hBDXhvW0m2tMBz4y-yD4lSBfzuVv_Od1tUb7dyYvJ9XCyLE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQPndUQGvcTD5lgfBFPXssBkA8TegRlf-eYkj9XBzkaPwA&amp;oe=6AC1F1B2
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/830695971_1417478556994289_3018851148769238681_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5NzA0MTE0NTQ4MTczMDM5Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=4Kp4gSGK9aYQ7kNvwHwjiiQ&amp;_nc_oc=Adoy7AoZKsXAzLCASYL1hBDXhvW0m2tMBz4y-yD4lSBfzuVv_Od1tUb7dyYvJ9XCyLE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQMWesoBDAEkzQ7bcxSkpR19EY_ek7YMEib0K0p91Jo97A&amp;oe=6AC1F1B2
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwG-i5gH&amp;_nc_oc=AdqLIluHqu85V8LolXYTSzAm4CTUcCGacgklFopcBKDFO_Q4h9OwQ7j87geDJ4P1ch4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQNHzk9uZAjA805E7EJaTVCSVzLgg3XMu1Tthq10rgjPKQ&amp;oe=6AC20A59
+https://l.instagram.com/?u=https%3A%2F%2Fbostonscientific.eightfold.ai%2Fcareers%2Fjob%2F563602813547669%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeSL2iEvtpDsXkNdr1X-DCVAxo1VB7lk1lBTxtU0bzsqp9e5_xQrmbTdHxWNg_aem_w7ID_Dl6i_d88nG-CCqmkQ&amp;e=AUDqMFTDkBliRSUFZx7L2ppRqkw5j9USc-kOyAezRE39g1IhMrlm6UPJIbmSSymsgDAqPNGgV7NBsJUzfyDyQhPLREvBsK7zrYZZ_IOiJg
+https://scontent-sjc3-1.cdninstagram.com/o1/v/t2/f2/m78/AQMuadjtrjUHwEjzyeQV0iu1XXNJPIsMPYYi75A79fMoxxq0I44MNJxi8jAhtbi0nTs5pjF5RQRGVWSVhhZq6tnb4PEKlP_l0tw4mPc.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_ohc=zJO9UmDRYWQQ7kNvwFyA6AC&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwMDU1Nzc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=db338f3f4c3c93f3&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzEwRkNENEE0NzAwQTQyQzZCNjY0NzQyMkJBQjQxQUQ0X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkweH82fahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQOxqC0NFlGXDN7rOLK5gnDic9AQw5x-_FHobceF58meug&amp;oe=6ABDEACC</t>
+        </is>
+      </c>
+      <c r="O252" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P252" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q252" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R252" s="3" t="inlineStr"/>
+    </row>
+    <row r="253" ht="45" customHeight="1">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
+          <t>b973fac21a04af9eac77</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:53:51.569070+00:00</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T17:55:24+00:00</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq — Internship</t>
+        </is>
+      </c>
+      <c r="F253" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G253" s="3" t="inlineStr"/>
+      <c r="H253" s="3" t="inlineStr"/>
+      <c r="I253" s="3" t="inlineStr">
+        <is>
+          <t>New York, NYC</t>
+        </is>
+      </c>
+      <c r="J253" s="3" t="inlineStr"/>
+      <c r="K253" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/Perchwell/9d34fc9d-e235-44fc-bdf9-42e75223839a/application?embed=true</t>
+        </is>
+      </c>
+      <c r="L253" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M253" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N253" s="3" t="inlineStr">
+        <is>
+          <t>€ All Jobs
+Data Analytics Engineering Intern
+Location
+New York Office
+Employment Type
+Intern
+Department
+Internships
+5. 2 JOBS.ASHBYHO.COM
+Compensation
+$12K = 10 week internsSMp in NYC
+Overview Application
+Y Autofill from resume
+Upload your resume here to autofill key
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/830510919_2618400301928265_5329450049754210992_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5NzA0MTczMDUyMDA0MDM3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=5D0-0dbNdTYQ7kNvwFstMOf&amp;_nc_oc=AdoTeIQraMXn4VD-Mv7XnbpV72sVsT6P5pAV6cgWl5yVGB5hFGaOLh6NsHyr40x5qGY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQNHY-WaT0ahs52YNecgcYOwAacjAMGZPZwcPnIZq0ffmQ&amp;oe=6AC1FCD9
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/830510919_2618400301928265_5329450049754210992_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5NzA0MTczMDUyMDA0MDM3MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=5D0-0dbNdTYQ7kNvwFstMOf&amp;_nc_oc=AdoTeIQraMXn4VD-Mv7XnbpV72sVsT6P5pAV6cgWl5yVGB5hFGaOLh6NsHyr40x5qGY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQNLkSA0R4OKcfdXxp9OE_2ARvPFuJ83xk8TjrGuBXX6Yw&amp;oe=6AC1FCD9
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwG-i5gH&amp;_nc_oc=AdqLIluHqu85V8LolXYTSzAm4CTUcCGacgklFopcBKDFO_Q4h9OwQ7j87geDJ4P1ch4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQNHzk9uZAjA805E7EJaTVCSVzLgg3XMu1Tthq10rgjPKQ&amp;oe=6AC20A59
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.ashbyhq.com%2FPerchwell%2F9d34fc9d-e235-44fc-bdf9-42e75223839a%2Fapplication%3Fembed%3Dtrue%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaduogKyLOiGC3wOgn0AT8ynOMxBTuppFjK4JqNLIVSXpCDXf5QqS0gESM_umg_aem_IAK553yUD_9IFq9MgH0XeQ&amp;e=AUBmiZTj7mmSoGYuXX0qCLH6le8DO5okW8uHDvBt-vl3xm2JkvW1zZHrPNl5h186RL7YMEKt58B_HfVZJ1AlhgJrNpvl99g4PEFd8yxTpw
+https://scontent-sjc6-1.cdninstagram.com/o1/v/t2/f2/m78/AQMto_tTElMERD_6jRjPiUs-6Ddebb8erh4xKkm9jYH-9l33jcw62jr4YGsCJCQ2vUOOyHzghTr6jfK1hThnIiN6OepwFf_cxEx7Jps.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ohc=x2YrxdCuKHkQ7kNvwGKERb4&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwMDU3MzM2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=28d3e88813804b4b&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzdBM0E0Mjk1QjUzNzQ5MENBMDc2MkEwMUZEREU5QzMwX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkvcSR2_ahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQN3o-oQmCiD25IYhtNhjOZxjsPvVI2O4LkT7KuzsxDT6Q&amp;oe=6ABDF6D2</t>
+        </is>
+      </c>
+      <c r="O253" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P253" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q253" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R253" s="3" t="inlineStr"/>
+    </row>
+    <row r="254" ht="45" customHeight="1">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>cf30423d8c2e06e0f980</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:53:53.085114+00:00</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T17:55:56+00:00</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq</t>
+        </is>
+      </c>
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq — Software Engineering, Product Management</t>
+        </is>
+      </c>
+      <c r="F254" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G254" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering, Product Management</t>
+        </is>
+      </c>
+      <c r="H254" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I254" s="3" t="inlineStr">
+        <is>
+          <t>New York, NYC</t>
+        </is>
+      </c>
+      <c r="J254" s="3" t="inlineStr"/>
+      <c r="K254" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/Perchwell/194eec78-26db-4d8e-850f-a99ea2733e9f/application?embed=true</t>
+        </is>
+      </c>
+      <c r="L254" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M254" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N254" s="3" t="inlineStr">
+        <is>
+          <t>&lt; All Jobs
+Software Engineering Intern
+Location
+New York Office
+Employment Type
+Intern
+@ JOBS.ASHBYHQ.COM
+Deadline to Apply
+October 18, 2026 at 8:00 PM PDT
+Compensation
+$12K = 10 week internship in NYC
+Overview Application
+YA Autofill from resume
+Upload your resume here to autofill key
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/830095182_1657077196131986_4086183714195202247_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5NzA0MTk5OTc3NzU4MDQxMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=h8YDJ1r-iukQ7kNvwHVvSdJ&amp;_nc_oc=Adr3ZnelNNmMjxaKMpyI0ZwMnt1YDMtv12JNHck9dwUIvPy5Yb9PxwDPnQRi1eVvg1M&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQNlB5vJY5q_reFr_4wdP2uPDnxhy8MRwJ32KGhl8OAfAQ&amp;oe=6AC1E54B
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/830095182_1657077196131986_4086183714195202247_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5NzA0MTk5OTc3NzU4MDQxMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=h8YDJ1r-iukQ7kNvwHVvSdJ&amp;_nc_oc=Adr3ZnelNNmMjxaKMpyI0ZwMnt1YDMtv12JNHck9dwUIvPy5Yb9PxwDPnQRi1eVvg1M&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQN-z_NLNbVBggHYmrUvGIhGKhQHZCpzex6ZWMZX8Sw8mQ&amp;oe=6AC1E54B
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwG-i5gH&amp;_nc_oc=AdqLIluHqu85V8LolXYTSzAm4CTUcCGacgklFopcBKDFO_Q4h9OwQ7j87geDJ4P1ch4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQNHzk9uZAjA805E7EJaTVCSVzLgg3XMu1Tthq10rgjPKQ&amp;oe=6AC20A59
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.ashbyhq.com%2FPerchwell%2F194eec78-26db-4d8e-850f-a99ea2733e9f%2Fapplication%3Fembed%3Dtrue%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadktM2E4-BjApc0dCXZFMS7Qkxcd7PYFHddlYbHCH9zUhHQ5lWHTg5J-fh_HA_aem_ujtKDJDE_g2AMsH6HQ7quA&amp;e=AUDkfdEvZLHRmOhpb76YDo4riEaURSlh-C9lDwNXqXyXammerqfj0lXesolqGeP8VLAHJCZxjs_r4m7DVF9v_h5AeBTNQ6JTuOzF382QwQ
+https://scontent-sjc6-1.cdninstagram.com/o1/v/t2/f2/m78/AQMgGWc49bZBq9U8VR0y-ty4qMfWUNADdeA6cKvFap7GsZi6mpXSwBzAKiZR8izn3UyxENqhuve1UV4uORqr_4-7lrkp5Q4SbgJvzlo.mp4?_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ohc=LVNi-FUMcxsQ7kNvwF0kdRP&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwMDU4MzU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=56a7f550164fcd2f&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzU5RTE2QTEwNDQ3RDQ1RDVBRTIyRkE2RTE3QjhCRkVDX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk0-fy2_ahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQMGPgCJFeKj5tmbTM3REoru-FKFmtTBwLUSX9fSnO6o9A&amp;oe=6ABE196D</t>
+        </is>
+      </c>
+      <c r="O254" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P254" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q254" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R254" s="3" t="inlineStr"/>
+    </row>
+    <row r="255" ht="45" customHeight="1">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
+          <t>cf9720f4e17bd6a82c59</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:53:54.141738+00:00</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T17:58:18+00:00</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq</t>
+        </is>
+      </c>
+      <c r="E255" s="3" t="inlineStr">
+        <is>
+          <t>Ashbyhq — Other Opportunity</t>
+        </is>
+      </c>
+      <c r="F255" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G255" s="3" t="inlineStr"/>
+      <c r="H255" s="3" t="inlineStr"/>
+      <c r="I255" s="3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J255" s="3" t="inlineStr"/>
+      <c r="K255" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/plot/5f8cfeaa-c368-480f-aaa5-de52452a63d0/application?embed=true</t>
+        </is>
+      </c>
+      <c r="L255" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M255" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N255" s="3" t="inlineStr">
+        <is>
+          <t>&lt; All Jobs
+Co-op -- Applied Al
+Location
+New York City
+Employment Type
+Full time
+° @ JOBS.ASHBYHQ.COM
+Department Nay
+Engineering
+Overview Application
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/829671781_1787673985594278_3061227593875411804_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5NzA0MzE5MzE0MDkzODc5OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=0ZBjdE31D5wQ7kNvwHNGhXg&amp;_nc_oc=AdqURZ0ufuDQ-HotjSDB1_SRSy2KY9As-1uwBHf8-vixINiY6MyGuMIrLOy036izZtY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQNPgixoo_o0jYE_t9GDcOEgadCeFvhD0VFMKshW-m7myA&amp;oe=6AC1DF01
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/829671781_1787673985594278_3061227593875411804_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5NzA0MzE5MzE0MDkzODc5OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=0ZBjdE31D5wQ7kNvwHNGhXg&amp;_nc_oc=AdqURZ0ufuDQ-HotjSDB1_SRSy2KY9As-1uwBHf8-vixINiY6MyGuMIrLOy036izZtY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQOY-S1JIGd8G751UKXi9R2xQqFsEU_cetRv-OGHQhlkKA&amp;oe=6AC1DF01
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwG-i5gH&amp;_nc_oc=AdqLIluHqu85V8LolXYTSzAm4CTUcCGacgklFopcBKDFO_Q4h9OwQ7j87geDJ4P1ch4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQNHzk9uZAjA805E7EJaTVCSVzLgg3XMu1Tthq10rgjPKQ&amp;oe=6AC20A59
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.ashbyhq.com%2Fplot%2F5f8cfeaa-c368-480f-aaa5-de52452a63d0%2Fapplication%3Fembed%3Dtrue%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafaErF2Dwp5b1DQ0k0PmbK9qGT1oHzmP0UES7SzcUmvyp8J5Q0_MWEBn7nChw_aem_PL4kMtz8afg56KIfughKyA&amp;e=AUAXCPBp7IqgZPWkjQTNjZJAUvzJPRhg7KCCeCrKqAaycZSPR9MjysCOw0gFEc7PW3F918ADL6FBY8ShjRRsD0wZL7S63R3DTvbRW6paAg
+https://scontent-sjc3-1.cdninstagram.com/o1/v/t2/f2/m78/AQPrILKVDXKkeZaWRBDzCJnHNp-no54D65CpVCbGcjxrXrW5yfFMxCVMczKGS8mjfvmrLsH_ZpW1p7hYfuEb2q9i871YlDazOoBrMyE.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_ohc=ersXcwETCP4Q7kNvwGE1RZ1&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwMDYyNDM2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=1b84ec4df3b048dd&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzlDQ0UzOEIyRkMwMTQzRDU4MjIwN0NENDkyMzQzODQ3X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkq_T33vahQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQOJgxWyqZet_z9JHbt9nKpHg3LrvfEOZblzRaMuUgJe9w&amp;oe=6ABDFC94</t>
+        </is>
+      </c>
+      <c r="O255" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P255" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q255" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R255" s="3" t="inlineStr"/>
+    </row>
+    <row r="256" ht="45" customHeight="1">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>c859076de2d78f107030</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:53:56.936049+00:00</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T18:27:29+00:00</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F256" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G256" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H256" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I256" s="3" t="inlineStr">
+        <is>
+          <t>Redmond</t>
+        </is>
+      </c>
+      <c r="J256" s="3" t="inlineStr"/>
+      <c r="K256" s="4" t="inlineStr">
+        <is>
+          <t>https://apply.careers.microsoft.com/careers/job/1970393557008566?domain=microsoft.com&amp;hl=en</t>
+        </is>
+      </c>
+      <c r="L256" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M256" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N256" s="3" t="inlineStr">
+        <is>
+          <t>@ apply.careers.microsoft.com C:
+ye) B® Microsoft
+Careers ~
+€ View All Jobs
+Software Engineer
+9 United States, Washington, Redmond
+Apply now
+9 PA
+Microsoft New Grad SWE
+(2) APPLY.CAREERS.MICROSOFT.CC
+Job description dry and benefits
+Job number Date posted
+200058252 Sep 29, 2026
+Add to cart
+}
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/825325918_1424553909624954_7713901553694414363_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5NzA1Nzg3NTE0MjcxNzA2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=5neCpXRZYFcQ7kNvwG5-Lwp&amp;_nc_oc=AdrD_nMB4K72i669-qNWAIbAAQJ0RBVr4067cyRTwhMvQ0rJmiTt-NQCpjLPFXBAFWA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQOwx9-C3HeiDKd8aTBVihTiHUlqQN-sMYOOEvE4Hw0TCA&amp;oe=6AC202B7
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/825325918_1424553909624954_7713901553694414363_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5NzA1Nzg3NTE0MjcxNzA2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=5neCpXRZYFcQ7kNvwG5-Lwp&amp;_nc_oc=AdrD_nMB4K72i669-qNWAIbAAQJ0RBVr4067cyRTwhMvQ0rJmiTt-NQCpjLPFXBAFWA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQNnYBvH1T0NrqIgAuQDKmvnWUvfTctt9mUEDKxQ_IGqSg&amp;oe=6AC202B7
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwG-i5gH&amp;_nc_oc=AdqLIluHqu85V8LolXYTSzAm4CTUcCGacgklFopcBKDFO_Q4h9OwQ7j87geDJ4P1ch4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQNHzk9uZAjA805E7EJaTVCSVzLgg3XMu1Tthq10rgjPKQ&amp;oe=6AC20A59
+https://l.instagram.com/?u=https%3A%2F%2Fapply.careers.microsoft.com%2Fcareers%2Fjob%2F1970393557008566%3Fdomain%3Dmicrosoft.com%26hl%3Den%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaci_O7huQbH5-kFrPhu0udCOlXdBKHV4CCxWJUncB3CkwuaDWm_97W4cDrZLg_aem_389TtCGcyswu4AN3MSYJ0g&amp;e=AUC9mx2I_pkRXVX7VjgBoAKcL1rghOrxNCeR1b1kfRKRy5o2VoDOKCafyxTA_L4-VMSiGR_3qtBJRIWaU4kl4vqPwWe9xONrdDa_qwClWA
+https://scontent-sjc3-1.cdninstagram.com/o1/v/t2/f2/m78/AQO18yJhnsvmzlbeGFAulbGCu3jPvuzrF0LM-bJXN7fNfBKP1ffMloAxK2BA3ePn_S8BN-dq8PJEnxiGTxEvzHAGfhr0PyTPc15_EV4.mp4?_nc_cat=110&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_ohc=Qxd99rpp11cQ7kNvwEF0HP0&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwMTIyMjg2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDgyNiwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=5aa6821c9d3a94d1&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzQ4MDNENUJDQzc4NDRCQkU5MTdFRkMzQ0RCRkMzNDMyX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbklNPDi_ehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZZSpAQA&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQM1TTFQH27NTOKdKbzCtF4_mwYCm5jr-sgvbwPrdSMloQ&amp;oe=6ABE1BC3</t>
+        </is>
+      </c>
+      <c r="O256" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P256" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q256" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R256" s="3" t="inlineStr"/>
+    </row>
+    <row r="257" ht="45" customHeight="1">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>1b3e3b0dcabedafe5c04</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:53:59.456851+00:00</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T18:29:55+00:00</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>Embed</t>
+        </is>
+      </c>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>Embed — Fellowship</t>
+        </is>
+      </c>
+      <c r="F257" s="3" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="G257" s="3" t="inlineStr"/>
+      <c r="H257" s="3" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="I257" s="3" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="J257" s="3" t="inlineStr"/>
+      <c r="K257" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/embed/job_app?for=doordashusa&amp;token=7848317&amp;jr_id=6a41623bb526a24fc3131903</t>
+        </is>
+      </c>
+      <c r="L257" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M257" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N257" s="3" t="inlineStr">
+        <is>
+          <t>@ job-boards.greenhouse.io C+:
+a
+&lt; Back to jobs
+Al Research
+Fellowship, (Summer
+and Fall 2026)
+© San Francisco, CA
+(2) JOB-BOARDS.GREENHOUSE.|0
+About the Te
+The DoorDash Research Fellowship is a 3-
+month program (extendable to 6 months)
+looking for Summer and Fall 2026 cohorts,
+for researchers and engineers who want to
+work on the hardest applied ML and Al
+problems in local commerce. Fellows are
+given the resources, autonomy, and aci &gt; |
+to real-world operational dataneededt ~™&gt;
+pursue ambitious research directions — with
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/828480823_1090801470485806_465908367419965956_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5NzA1OTA5OTI1MDMzNDk1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=DiED_b2pVvsQ7kNvwHwjxNo&amp;_nc_oc=AdrMFnjYhelzjmWgxUh6A49IgZ6yLbH81ITwktJt-3YSp-hh1HhPgcMzEOthJOc8MDI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQNs_DHMsui94N0mossy0b2k-k1LrOSWrk039AThRtjesg&amp;oe=6AC1F3C9
+https://scontent-sjc6-1.cdninstagram.com/v/t51.71878-15/828480823_1090801470485806_465908367419965956_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5NzA1OTA5OTI1MDMzNDk1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=DiED_b2pVvsQ7kNvwHwjxNo&amp;_nc_oc=AdrMFnjYhelzjmWgxUh6A49IgZ6yLbH81ITwktJt-3YSp-hh1HhPgcMzEOthJOc8MDI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQPzCYDt0WLACzPmrN35WIhdIHEuLuRPb6i5AQWEcxcN7Q&amp;oe=6AC1F3C9
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwG-i5gH&amp;_nc_oc=AdqLIluHqu85V8LolXYTSzAm4CTUcCGacgklFopcBKDFO_Q4h9OwQ7j87geDJ4P1ch4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQNHzk9uZAjA805E7EJaTVCSVzLgg3XMu1Tthq10rgjPKQ&amp;oe=6AC20A59
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fembed%2Fjob_app%3Ffor%3Ddoordashusa%26token%3D7848317%26jr_id%3D6a41623bb526a24fc3131903%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeLZiEViuLUsfOKrB03yHmwsd9SuDiYmKzqj96DF5vIJhK9l5XW3t5Xp2HE5g_aem_gi02NEORJTlPQB61qvJ54A&amp;e=AUBYkuB3Cgk87qUVkEjULr0Qi94r4QicOUNOzfVjEed7Q6TwZFrF40YEZ83F9hTEbaoG-UOYjZ3fiYdlc6YI2vRxxnoyaW757589ztxtSQ
+https://scontent-sjc3-1.cdninstagram.com/o1/v/t2/f2/m78/AQN_OrLzGdnTaAa2ubn9RoBJumt-Sw1basdPzDaNUXiQRsxBOi6pQaFIGCCgd1rKQqmjgsW1XyBMyxWccy1-K_Rw-BtEIoKGGv9q81s.mp4?_nc_cat=110&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_ohc=VVC9g9rQVigQ7kNvwHqKh9j&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwMTI0MDg2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=1c9726f4fed275c&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0Q2QzNBRUFCMjY3RTREMTFBOUQ0ODA0RjcxRTJEMDQyX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk6KfvjPehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQOAuDNbM9V0IpaWNyudsuklSDvuRb2_8F2QBdRPGoLemw&amp;oe=6ABE12D7</t>
+        </is>
+      </c>
+      <c r="O257" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P257" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q257" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R257" s="3" t="inlineStr"/>
+    </row>
+    <row r="258" ht="45" customHeight="1">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>9033693172a982228fcf</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:54:01.341253+00:00</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T18:37:29+00:00</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="E258" s="3" t="inlineStr">
+        <is>
+          <t>EA — Internship</t>
+        </is>
+      </c>
+      <c r="F258" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G258" s="3" t="inlineStr"/>
+      <c r="H258" s="3" t="inlineStr"/>
+      <c r="I258" s="3" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="J258" s="3" t="inlineStr"/>
+      <c r="K258" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ea.com/en_US/careers/JobDetail/Software-Engineer-Intern/216241</t>
+        </is>
+      </c>
+      <c r="L258" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M258" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N258" s="3" t="inlineStr">
+        <is>
+          <t>@ jobs.ea.com
+Home / ... / Role Detail
+f=] General Information
+Locations
+: Austin, Texas, United States of America
+Role ID: 216241
+Worker Type: Intern - Temporary Employee
+Studio/Department: EA Studios - SPORTS
+=] Description ements
+TMlA Aten nin Aveta Aen Attn BA LAlnl Antanvtninnn ant
+Share this role: FT)
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/825277340_1071184042179246_1999624901487489417_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5NzA2MjkxMzU1MDQxNzkxMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=2jp0S7jsxo0Q7kNvwHyXv06&amp;_nc_oc=AdoGOtO-3ChiAei7yZ3w-Y5dDm88QmzVTJPHurXEMkNJWWNyIewTAlzFmZqYvJv6HEw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQN_EJEQkdmGqWxfsyafpSiw0yCGn2D0fQ2XZKdyjgd5BQ&amp;oe=6AC1F7D3
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/825277340_1071184042179246_1999624901487489417_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5NzA2MjkxMzU1MDQxNzkxMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=2jp0S7jsxo0Q7kNvwHyXv06&amp;_nc_oc=AdoGOtO-3ChiAei7yZ3w-Y5dDm88QmzVTJPHurXEMkNJWWNyIewTAlzFmZqYvJv6HEw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQPMAa5149z6d20OIOdHmAY3WM2ccaxGrD54fwTnyFLjQA&amp;oe=6AC1F7D3
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwG-i5gH&amp;_nc_oc=AdqLIluHqu85V8LolXYTSzAm4CTUcCGacgklFopcBKDFO_Q4h9OwQ7j87geDJ4P1ch4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQNHzk9uZAjA805E7EJaTVCSVzLgg3XMu1Tthq10rgjPKQ&amp;oe=6AC20A59
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.ea.com%2Fen_US%2Fcareers%2FJobDetail%2FSoftware-Engineer-Intern%2F216241%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeMlRCaMYybVj1ZzfEIGvmUAcfPirnT0zvXMpmI6OVBbkZA2GmT1wuOFKvFRA_aem_kxgLDBbfdtsFh_SLNfTSrg&amp;e=AUB4SpqkKS4lVHREtc_V-ti1R_pTYXxgCP1Od98gTxI1JqaPaq1347lE-24YD49IxSgWmuaUxpNRxqYVs0fPL5e89mYx1M7lDB5WunZ1xw
+https://scontent-sjc3-1.cdninstagram.com/o1/v/t2/f2/m78/AQPW8r9XawlmVbUJ6u8k4eYBc-ic5enY2XG0Ql_DzFZI8u_fwnL3AaOM-snhQjCFs3XoGOk7QGHJ8UWhCR2538knz1zaNA6Swp42WAg.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_ohc=lmowrnR_HJoQ7kNvwG6n54Q&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwMTMwNDE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=c13b1f43dfe15227&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0JCNTdGMkIxNjQzMzQ5NTI5RDcwRTI2RTQwNzUzMjM4X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkqf7KkfehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQNaxbHYuClm2rivXPllckhy0qgeV72eSyeYN6LMpdyciQ&amp;oe=6ABDF1D0</t>
+        </is>
+      </c>
+      <c r="O258" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P258" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q258" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R258" s="3" t="inlineStr"/>
+    </row>
+    <row r="259" ht="45" customHeight="1">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>a224e58e76da707eed5b</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:54:04.075866+00:00</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T19:04:02+00:00</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>Moog</t>
+        </is>
+      </c>
+      <c r="E259" s="3" t="inlineStr">
+        <is>
+          <t>Moog — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F259" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G259" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H259" s="3" t="inlineStr"/>
+      <c r="I259" s="3" t="inlineStr"/>
+      <c r="J259" s="3" t="inlineStr"/>
+      <c r="K259" s="4" t="inlineStr">
+        <is>
+          <t>https://moog.wd5.myworkdayjobs.com/en-US/MOOG_External_Career_Site/job/Intern--Software-Engineering_R-26-19948</t>
+        </is>
+      </c>
+      <c r="L259" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M259" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N259" s="3" t="inlineStr">
+        <is>
+          <t>x @ moog.wd5.myworkdayjobs.com oo
+Instagram
+moos Moog Careers
+A
+— ~~
+ey NZ
+MOOG
+Intern, Software Engineering
+Hybrid
+Torrance, CA
+Full time
+© i ©@
+Posted Today
+ers | iN 4V tver"tyv
+Moog is a perform that empowers
+people to achieve gr . Our people
+enjoy solving interesting technical challenges
+in a culture where everyone trusts each other
+to do the right thing. For you, working with us
+can mean deeper job satisfaction, better
+Ne ee ee ee ee ee ee St eee ee 2 are ee 2 ae ee |
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/825324039_1402063168127087_3911863695835655812_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5NzA3NjI3MzI5NzgzMjEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Sa5YGQaqIqsQ7kNvwFj0w_l&amp;_nc_oc=Adq1wS_8oCclOBoXOue_8MIpcaf1OxpDdoQmGB6XfOYaM56iiN0ZhO32QBIXDPKsv5w&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQPBpH3wd24jlqViQaBqTHGqrowTWADR95tyBzm0apYtJQ&amp;oe=6AC20D9C
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/825324039_1402063168127087_3911863695835655812_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5NzA3NjI3MzI5NzgzMjEzOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=Sa5YGQaqIqsQ7kNvwFj0w_l&amp;_nc_oc=Adq1wS_8oCclOBoXOue_8MIpcaf1OxpDdoQmGB6XfOYaM56iiN0ZhO32QBIXDPKsv5w&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQMh2ABrmc32MvbESVSQMkx8ZFooDo3ynFOM4VfC6OjoGw&amp;oe=6AC20D9C
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwG-i5gH&amp;_nc_oc=AdqLIluHqu85V8LolXYTSzAm4CTUcCGacgklFopcBKDFO_Q4h9OwQ7j87geDJ4P1ch4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQNHzk9uZAjA805E7EJaTVCSVzLgg3XMu1Tthq10rgjPKQ&amp;oe=6AC20A59
+https://l.instagram.com/?u=https%3A%2F%2Fmoog.wd5.myworkdayjobs.com%2Fen-US%2FMOOG_External_Career_Site%2Fjob%2FIntern--Software-Engineering_R-26-19948%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafvUCLDA7tqY4cU5tJTT4VvXPrIT02WCeUG4g9k57iI3zk_mrjxzbtNSkfasQ_aem_p8F5OBmbsIrn2DGXNoFRgw%26utm_id%3D97760_v0_s00_e0_tv6_a1denngsc6gtwx&amp;e=AUCMO5lmAMzg5ckCbj8v6_yjpJHGV-579C4XshsQVqEmsh68SDfom_xS6l88EB_8iIh9O1qjBY2iY_w1V-orO3kCHohTR7vfgtHnWRcR_w
+https://scontent-sjc6-1.cdninstagram.com/o1/v/t2/f2/m78/AQObuEl-WUfP8l2q-rwVc068_i6RwFgVMQOt5dSa1_qD6aOHTixUOMABzys9hC0-QSJ03s3YExMunFihX8VLnDZGq7Pq8R4jGv6gYEc.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ohc=b0JhPAawRboQ7kNvwHlURk_&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwMTU3MDg2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=6751857db5342d6&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0RBMjQwM0UzMDAwQzRBN0E5MUZCQTkyRTNFMTRENjlDX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk7Le6pfehQBUCKAJDMywXQAiHKwIMSboYEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQPiktboKA-C6u7SBQ0gVUMaSyZ0WBgQ6E8pJrIAfVXCbw&amp;oe=6ABE04B2</t>
+        </is>
+      </c>
+      <c r="O259" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P259" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q259" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R259" s="3" t="inlineStr"/>
+    </row>
+    <row r="260" ht="45" customHeight="1">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>1e9dcb051fbe42e708ed</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:54:06.033975+00:00</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:45:24+00:00</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="E260" s="3" t="inlineStr">
+        <is>
+          <t>Adobe — Software Engineering, Machine Learning / AI</t>
+        </is>
+      </c>
+      <c r="F260" s="3" t="inlineStr">
+        <is>
+          <t>Hackathon / Competition</t>
+        </is>
+      </c>
+      <c r="G260" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering, Machine Learning / AI</t>
+        </is>
+      </c>
+      <c r="H260" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I260" s="3" t="inlineStr"/>
+      <c r="J260" s="3" t="inlineStr"/>
+      <c r="K260" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.adobe.com/us/en/event/6a90701b41b49ecd36166e14/Adobe-University-Hackathon-2026</t>
+        </is>
+      </c>
+      <c r="L260" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M260" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N260" s="3" t="inlineStr">
+        <is>
+          <t>@ careers.adobe.com
+= Adobe
+Adobe University
+Hackathon 2026
+/@ CAREERS.ADOBE.COM |
+Description
+Build a real Adobe Express engineering
+challenge that tests how intelligently a
+design can adapt across canvas sizes.
+Open to undergraduate students in
+Software Engineering, Computer
+Engineering , Artificial Intelligence, or
+Machine Learning majors, form a team
+of 2-3 and compete for the chance to
+bring your solution to life.
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/828551693_28452257831062107_6966774494887335391_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5NzEyNzI5MDQ5NjYxNzMxMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=bky7FViHzcgQ7kNvwFzT7ne&amp;_nc_oc=AdrnWMvTKqYfVGAukh4GN8Iyrd_QkwcbXJyIwtenq_lTGt95DWnAGpoTgy1wiPALu2o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQO5HkPc4yRHeiHkGmWPpYcvj8N5RL41028fhm8ur4t63w&amp;oe=6AC212CD
+https://scontent-sjc3-1.cdninstagram.com/v/t51.71878-15/828551693_28452257831062107_6966774494887335391_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5NzEyNzI5MDQ5NjYxNzMxMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=bky7FViHzcgQ7kNvwFzT7ne&amp;_nc_oc=AdrnWMvTKqYfVGAukh4GN8Iyrd_QkwcbXJyIwtenq_lTGt95DWnAGpoTgy1wiPALu2o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-sjc3-1.cdninstagram.com&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;oh=00_AQOOFvB2XBtMeNpaz0MN38Dn5cik1QPAD61v0a-Dop-Y-w&amp;oe=6AC212CD
+https://scontent-sjc6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwG-i5gH&amp;_nc_oc=AdqLIluHqu85V8LolXYTSzAm4CTUcCGacgklFopcBKDFO_Q4h9OwQ7j87geDJ4P1ch4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQNHzk9uZAjA805E7EJaTVCSVzLgg3XMu1Tthq10rgjPKQ&amp;oe=6AC20A59
+https://l.instagram.com/?u=https%3A%2F%2Fcareers.adobe.com%2Fus%2Fen%2Fevent%2F6a90701b41b49ecd36166e14%2FAdobe-University-Hackathon-2026%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacOaHhkKzbXG9KVA9PCNojz_BLPnJXZXrpyyvxbvIEvacUKeAb4ljHu7A4PIA_aem_36V2003NMWCqnZDey4PNHQ&amp;e=AUD-FsH738zrGzlwwXO7Hq1s8JvoJBjEVBhCMk-JuAwKWBF4uCxvUaKxXO7QXxdTJRzlUMTlmscT8URBo4g5mNpo43RkAvnC3bkSwMxSKA
+https://scontent-sjc6-1.cdninstagram.com/o1/v/t2/f2/m78/AQNAPJRNcLS28iKA05ra_js3-zD91SKJMOlQIgBbTNcTWdTM-6tPRYAdTBVtkU4hiRfxGozlyfaKpHwOysZEzk8R4nBLqbD45Z-ci0o.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sjc6-1.cdninstagram.com&amp;_nc_ohc=7iQuZAt1ZcMQ7kNvwHiQHa1&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwMjQ0NjU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=9303cd70a957404f&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0MyNzIyMzRCRTY3MjQwN0I5RDlDQzkyRUNFQkE1NzdGX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkyeHZ5vehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=7ufTG6Y7EiOYiuLaaOWzuA&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQO8RX7cj5MuAgmBAOk_NW0twUlFMi4zFd7ymwAhZjFaOg&amp;oe=6ABE0DD1</t>
+        </is>
+      </c>
+      <c r="O260" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P260" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q260" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R260" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R241"/>
+  <autoFilter ref="A1:R260"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -23983,6 +25793,44 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L240" r:id="rId463"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K241" r:id="rId464"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L241" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K242" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L242" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K243" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L243" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K244" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L244" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K245" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L245" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K246" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L246" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K247" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L247" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K248" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L248" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K249" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L249" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K250" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L250" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K251" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L251" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K252" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L252" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K253" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L253" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K254" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L254" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K255" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L255" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K256" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L256" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K257" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L257" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K258" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L258" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K259" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L259" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K260" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L260" r:id="rId503"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$260</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$266</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R260"/>
+  <dimension ref="A1:R266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23518,7 +23518,7 @@
     <row r="242" ht="45" customHeight="1">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>51d46c1be71c58bee683</t>
+          <t>8a203f70893f4ffed861</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -23531,7 +23531,7 @@
           <t>2026-09-29T16:57:02+00:00</t>
         </is>
       </c>
-      <c r="D242" s="3" t="inlineStr"/>
+      <c r="D242" s="3" t="n"/>
       <c r="E242" s="3" t="inlineStr">
         <is>
           <t>2027 Internship</t>
@@ -23542,14 +23542,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G242" s="3" t="inlineStr"/>
+      <c r="G242" s="3" t="n"/>
       <c r="H242" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I242" s="3" t="inlineStr"/>
-      <c r="J242" s="3" t="inlineStr"/>
+      <c r="I242" s="3" t="n"/>
+      <c r="J242" s="3" t="n"/>
       <c r="K242" s="4" t="inlineStr">
         <is>
           <t>https://mycareer.verizon.com/jobs/r-1101384/verizon-network-and-technology-data-science-summer-2027-internship?source=zero2sudo</t>
@@ -23599,12 +23599,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R242" s="3" t="inlineStr"/>
+      <c r="R242" s="3" t="n"/>
     </row>
     <row r="243" ht="45" customHeight="1">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>8d4e8aede174fdbcdd2d</t>
+          <t>362202135748279c77ba</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -23617,7 +23617,7 @@
           <t>2026-09-29T16:57:44+00:00</t>
         </is>
       </c>
-      <c r="D243" s="3" t="inlineStr"/>
+      <c r="D243" s="3" t="n"/>
       <c r="E243" s="3" t="inlineStr">
         <is>
           <t>2027 Internship</t>
@@ -23628,14 +23628,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G243" s="3" t="inlineStr"/>
+      <c r="G243" s="3" t="n"/>
       <c r="H243" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I243" s="3" t="inlineStr"/>
-      <c r="J243" s="3" t="inlineStr"/>
+      <c r="I243" s="3" t="n"/>
+      <c r="J243" s="3" t="n"/>
       <c r="K243" s="4" t="inlineStr">
         <is>
           <t>https://mycareer.verizon.com/jobs/r-1101387/verizon-network-and-technology-business-intelligence-summer-2027-internship?source=zero2sudo</t>
@@ -23686,12 +23686,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R243" s="3" t="inlineStr"/>
+      <c r="R243" s="3" t="n"/>
     </row>
     <row r="244" ht="45" customHeight="1">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>d28453ccf88a2b9e506c</t>
+          <t>35938089e2098e6fd3b2</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -23719,14 +23719,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G244" s="3" t="inlineStr"/>
+      <c r="G244" s="3" t="n"/>
       <c r="H244" s="3" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="I244" s="3" t="inlineStr"/>
-      <c r="J244" s="3" t="inlineStr"/>
+      <c r="I244" s="3" t="n"/>
+      <c r="J244" s="3" t="n"/>
       <c r="K244" s="4" t="inlineStr">
         <is>
           <t>https://jobs.thecignagroup.com/us/en/job/CIGNUS26010877EXTERNALENUS/AI-ML-Engineer-Intern</t>
@@ -23779,12 +23779,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R244" s="3" t="inlineStr"/>
+      <c r="R244" s="3" t="n"/>
     </row>
     <row r="245" ht="45" customHeight="1">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>994f7bbf3ef4cd429dd8</t>
+          <t>6dbaa5dc21f7eafcc723</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -23797,7 +23797,7 @@
           <t>2026-09-29T16:59:37+00:00</t>
         </is>
       </c>
-      <c r="D245" s="3" t="inlineStr"/>
+      <c r="D245" s="3" t="n"/>
       <c r="E245" s="3" t="inlineStr">
         <is>
           <t>Hybrid NewYork(US)  40hours — Internship</t>
@@ -23808,10 +23808,10 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G245" s="3" t="inlineStr"/>
-      <c r="H245" s="3" t="inlineStr"/>
-      <c r="I245" s="3" t="inlineStr"/>
-      <c r="J245" s="3" t="inlineStr"/>
+      <c r="G245" s="3" t="n"/>
+      <c r="H245" s="3" t="n"/>
+      <c r="I245" s="3" t="n"/>
+      <c r="J245" s="3" t="n"/>
       <c r="K245" s="4" t="inlineStr">
         <is>
           <t>https://rabobank.jobs/en/job/gem-summer-commodities-intern/JR_00146162</t>
@@ -23863,12 +23863,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R245" s="3" t="inlineStr"/>
+      <c r="R245" s="3" t="n"/>
     </row>
     <row r="246" ht="45" customHeight="1">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>d084ecdd147b379efe41</t>
+          <t>18d1b9d8cbce00c32a6e</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -23896,10 +23896,10 @@
           <t>Other Opportunity</t>
         </is>
       </c>
-      <c r="G246" s="3" t="inlineStr"/>
-      <c r="H246" s="3" t="inlineStr"/>
-      <c r="I246" s="3" t="inlineStr"/>
-      <c r="J246" s="3" t="inlineStr"/>
+      <c r="G246" s="3" t="n"/>
+      <c r="H246" s="3" t="n"/>
+      <c r="I246" s="3" t="n"/>
+      <c r="J246" s="3" t="n"/>
       <c r="K246" s="4" t="inlineStr">
         <is>
           <t>https://apply.workable.com/bestex-research/j/AE65B49EA3</t>
@@ -23957,12 +23957,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R246" s="3" t="inlineStr"/>
+      <c r="R246" s="3" t="n"/>
     </row>
     <row r="247" ht="45" customHeight="1">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>7d8d80f7a1cba8ffe72a</t>
+          <t>fbe58a9d68aa588427fa</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -24000,8 +24000,8 @@
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I247" s="3" t="inlineStr"/>
-      <c r="J247" s="3" t="inlineStr"/>
+      <c r="I247" s="3" t="n"/>
+      <c r="J247" s="3" t="n"/>
       <c r="K247" s="4" t="inlineStr">
         <is>
           <t>https://nvidia.eightfold.ai/events/candidate/landing?plannedEventId=5eQmdl8bk</t>
@@ -24062,12 +24062,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R247" s="3" t="inlineStr"/>
+      <c r="R247" s="3" t="n"/>
     </row>
     <row r="248" ht="45" customHeight="1">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>de2cb56293a05bc8d9ad</t>
+          <t>1abc735f5c456a7b8303</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -24095,14 +24095,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G248" s="3" t="inlineStr"/>
+      <c r="G248" s="3" t="n"/>
       <c r="H248" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I248" s="3" t="inlineStr"/>
-      <c r="J248" s="3" t="inlineStr"/>
+      <c r="I248" s="3" t="n"/>
+      <c r="J248" s="3" t="n"/>
       <c r="K248" s="4" t="inlineStr">
         <is>
           <t>https://thrivent.wd5.myworkdayjobs.com/external/job/Mpls-Investments-Office/IT-Application-Engineer-Intern--Investments---Summer-2027_REQ-48511-2</t>
@@ -24157,12 +24157,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R248" s="3" t="inlineStr"/>
+      <c r="R248" s="3" t="n"/>
     </row>
     <row r="249" ht="45" customHeight="1">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>f5ca240c5e76c42a1d27</t>
+          <t>580d2a6e7cf39049614e</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -24195,9 +24195,9 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H249" s="3" t="inlineStr"/>
-      <c r="I249" s="3" t="inlineStr"/>
-      <c r="J249" s="3" t="inlineStr"/>
+      <c r="H249" s="3" t="n"/>
+      <c r="I249" s="3" t="n"/>
+      <c r="J249" s="3" t="n"/>
       <c r="K249" s="4" t="inlineStr">
         <is>
           <t>https://careers.garmin.com/jobs/20255?icims=1</t>
@@ -24257,12 +24257,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R249" s="3" t="inlineStr"/>
+      <c r="R249" s="3" t="n"/>
     </row>
     <row r="250" ht="45" customHeight="1">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>58746889ae25d01fa746</t>
+          <t>0b608d10eb1a1f66bd00</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -24275,7 +24275,7 @@
           <t>2026-09-29T17:51:40+00:00</t>
         </is>
       </c>
-      <c r="D250" s="3" t="inlineStr"/>
+      <c r="D250" s="3" t="n"/>
       <c r="E250" s="3" t="inlineStr">
         <is>
           <t>Summer Internship Program, open to students</t>
@@ -24301,7 +24301,7 @@
           <t>Remote</t>
         </is>
       </c>
-      <c r="J250" s="3" t="inlineStr"/>
+      <c r="J250" s="3" t="n"/>
       <c r="K250" s="4" t="inlineStr">
         <is>
           <t>https://careers-hrblock.icims.com/jobs/76992/job?mobile=true&amp;needsRedirect=false</t>
@@ -24358,12 +24358,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R250" s="3" t="inlineStr"/>
+      <c r="R250" s="3" t="n"/>
     </row>
     <row r="251" ht="45" customHeight="1">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>917e6998c557997b20f3</t>
+          <t>e82ec88172cdb10f831c</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -24391,10 +24391,10 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G251" s="3" t="inlineStr"/>
-      <c r="H251" s="3" t="inlineStr"/>
-      <c r="I251" s="3" t="inlineStr"/>
-      <c r="J251" s="3" t="inlineStr"/>
+      <c r="G251" s="3" t="n"/>
+      <c r="H251" s="3" t="n"/>
+      <c r="I251" s="3" t="n"/>
+      <c r="J251" s="3" t="n"/>
       <c r="K251" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ea.com/en_US/careers/JobDetail/AI-Engineer-Intern/216223</t>
@@ -24445,12 +24445,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R251" s="3" t="inlineStr"/>
+      <c r="R251" s="3" t="n"/>
     </row>
     <row r="252" ht="45" customHeight="1">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>3b7af2886260d103435e</t>
+          <t>cd61d5aecd6d3fcb4d05</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -24463,7 +24463,7 @@
           <t>2026-09-29T17:54:14+00:00</t>
         </is>
       </c>
-      <c r="D252" s="3" t="inlineStr"/>
+      <c r="D252" s="3" t="n"/>
       <c r="E252" s="3" t="inlineStr">
         <is>
           <t>Scientific Join Talent Network English v</t>
@@ -24479,13 +24479,13 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H252" s="3" t="inlineStr"/>
+      <c r="H252" s="3" t="n"/>
       <c r="I252" s="3" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="J252" s="3" t="inlineStr"/>
+      <c r="J252" s="3" t="n"/>
       <c r="K252" s="4" t="inlineStr">
         <is>
           <t>https://bostonscientific.eightfold.ai/careers/job/563602813547669</t>
@@ -24541,12 +24541,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R252" s="3" t="inlineStr"/>
+      <c r="R252" s="3" t="n"/>
     </row>
     <row r="253" ht="45" customHeight="1">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>b973fac21a04af9eac77</t>
+          <t>f2d29f72bf7ab5999330</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -24574,14 +24574,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G253" s="3" t="inlineStr"/>
-      <c r="H253" s="3" t="inlineStr"/>
+      <c r="G253" s="3" t="n"/>
+      <c r="H253" s="3" t="n"/>
       <c r="I253" s="3" t="inlineStr">
         <is>
           <t>New York, NYC</t>
         </is>
       </c>
-      <c r="J253" s="3" t="inlineStr"/>
+      <c r="J253" s="3" t="n"/>
       <c r="K253" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/Perchwell/9d34fc9d-e235-44fc-bdf9-42e75223839a/application?embed=true</t>
@@ -24635,12 +24635,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R253" s="3" t="inlineStr"/>
+      <c r="R253" s="3" t="n"/>
     </row>
     <row r="254" ht="45" customHeight="1">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>cf30423d8c2e06e0f980</t>
+          <t>425e03337ef402727589</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -24683,7 +24683,7 @@
           <t>New York, NYC</t>
         </is>
       </c>
-      <c r="J254" s="3" t="inlineStr"/>
+      <c r="J254" s="3" t="n"/>
       <c r="K254" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/Perchwell/194eec78-26db-4d8e-850f-a99ea2733e9f/application?embed=true</t>
@@ -24737,12 +24737,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R254" s="3" t="inlineStr"/>
+      <c r="R254" s="3" t="n"/>
     </row>
     <row r="255" ht="45" customHeight="1">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>cf9720f4e17bd6a82c59</t>
+          <t>1518ff0d353ae2598e4c</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -24770,14 +24770,14 @@
           <t>Other Opportunity</t>
         </is>
       </c>
-      <c r="G255" s="3" t="inlineStr"/>
-      <c r="H255" s="3" t="inlineStr"/>
+      <c r="G255" s="3" t="n"/>
+      <c r="H255" s="3" t="n"/>
       <c r="I255" s="3" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="J255" s="3" t="inlineStr"/>
+      <c r="J255" s="3" t="n"/>
       <c r="K255" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/plot/5f8cfeaa-c368-480f-aaa5-de52452a63d0/application?embed=true</t>
@@ -24827,12 +24827,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R255" s="3" t="inlineStr"/>
+      <c r="R255" s="3" t="n"/>
     </row>
     <row r="256" ht="45" customHeight="1">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>c859076de2d78f107030</t>
+          <t>4a2804981cc1b75f8d3d</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -24875,7 +24875,7 @@
           <t>Redmond</t>
         </is>
       </c>
-      <c r="J256" s="3" t="inlineStr"/>
+      <c r="J256" s="3" t="n"/>
       <c r="K256" s="4" t="inlineStr">
         <is>
           <t>https://apply.careers.microsoft.com/careers/job/1970393557008566?domain=microsoft.com&amp;hl=en</t>
@@ -24930,12 +24930,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R256" s="3" t="inlineStr"/>
+      <c r="R256" s="3" t="n"/>
     </row>
     <row r="257" ht="45" customHeight="1">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>1b3e3b0dcabedafe5c04</t>
+          <t>1670e742bba061e80055</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
@@ -24963,7 +24963,7 @@
           <t>Fellowship</t>
         </is>
       </c>
-      <c r="G257" s="3" t="inlineStr"/>
+      <c r="G257" s="3" t="n"/>
       <c r="H257" s="3" t="inlineStr">
         <is>
           <t>Fall 2026</t>
@@ -24974,7 +24974,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="J257" s="3" t="inlineStr"/>
+      <c r="J257" s="3" t="n"/>
       <c r="K257" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/embed/job_app?for=doordashusa&amp;token=7848317&amp;jr_id=6a41623bb526a24fc3131903</t>
@@ -25032,12 +25032,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R257" s="3" t="inlineStr"/>
+      <c r="R257" s="3" t="n"/>
     </row>
     <row r="258" ht="45" customHeight="1">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>9033693172a982228fcf</t>
+          <t>40f829e8878807858db0</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -25065,14 +25065,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G258" s="3" t="inlineStr"/>
-      <c r="H258" s="3" t="inlineStr"/>
+      <c r="G258" s="3" t="n"/>
+      <c r="H258" s="3" t="n"/>
       <c r="I258" s="3" t="inlineStr">
         <is>
           <t>Austin</t>
         </is>
       </c>
-      <c r="J258" s="3" t="inlineStr"/>
+      <c r="J258" s="3" t="n"/>
       <c r="K258" s="4" t="inlineStr">
         <is>
           <t>https://jobs.ea.com/en_US/careers/JobDetail/Software-Engineer-Intern/216241</t>
@@ -25123,12 +25123,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R258" s="3" t="inlineStr"/>
+      <c r="R258" s="3" t="n"/>
     </row>
     <row r="259" ht="45" customHeight="1">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>a224e58e76da707eed5b</t>
+          <t>d76b822eb5ea4496e053</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
@@ -25161,9 +25161,9 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H259" s="3" t="inlineStr"/>
-      <c r="I259" s="3" t="inlineStr"/>
-      <c r="J259" s="3" t="inlineStr"/>
+      <c r="H259" s="3" t="n"/>
+      <c r="I259" s="3" t="n"/>
+      <c r="J259" s="3" t="n"/>
       <c r="K259" s="4" t="inlineStr">
         <is>
           <t>https://moog.wd5.myworkdayjobs.com/en-US/MOOG_External_Career_Site/job/Intern--Software-Engineering_R-26-19948</t>
@@ -25224,12 +25224,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R259" s="3" t="inlineStr"/>
+      <c r="R259" s="3" t="n"/>
     </row>
     <row r="260" ht="45" customHeight="1">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>1e9dcb051fbe42e708ed</t>
+          <t>194590778091956df316</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -25267,8 +25267,8 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="I260" s="3" t="inlineStr"/>
-      <c r="J260" s="3" t="inlineStr"/>
+      <c r="I260" s="3" t="n"/>
+      <c r="J260" s="3" t="n"/>
       <c r="K260" s="4" t="inlineStr">
         <is>
           <t>https://careers.adobe.com/us/en/event/6a90701b41b49ecd36166e14/Adobe-University-Hackathon-2026</t>
@@ -25323,10 +25323,580 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R260" s="3" t="inlineStr"/>
+      <c r="R260" s="3" t="n"/>
+    </row>
+    <row r="261" ht="45" customHeight="1">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>4ea801c04dcf247aa6f9</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T00:33:35.658510+00:00</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:58:10+00:00</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="inlineStr"/>
+      <c r="E261" s="3" t="inlineStr">
+        <is>
+          <t>Job Type Intern/Apprentice</t>
+        </is>
+      </c>
+      <c r="F261" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G261" s="3" t="inlineStr"/>
+      <c r="H261" s="3" t="inlineStr">
+        <is>
+          <t>Spring 2027</t>
+        </is>
+      </c>
+      <c r="I261" s="3" t="inlineStr"/>
+      <c r="J261" s="3" t="inlineStr"/>
+      <c r="K261" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tesla.com/careers/search/job/285085</t>
+        </is>
+      </c>
+      <c r="L261" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M261" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N261" s="3" t="inlineStr">
+        <is>
+          <t>@ tesla.com
+TSE=SS5LA Careers Menu
+Go to search
+Internship, Al Software
+Engineer, Core
+Infrastructure
+(Winter/Spring 2027)
+Job Category Tesla Al
+Palo Alto,
+Eosatlen California
+Req. ID 285085
+Job Type Intern/Apprentice
+@ TESLA.COM
+https://scontent-dfw5-1.cdninstagram.com/v/t51.71878-15/828895840_1850228683002422_9023370776441248208_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5NzEzMzcyMTU4OTM5NjMzNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=RVV4ok2ly4gQ7kNvwGtHP7J&amp;_nc_oc=AdoLnF-SxBb9U9H9dhzYKLzrp9VX2DprzAEHPhIi8hc2K7-0KcKv-QLrWfy3N7VzIbM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_gid=_STxp7pVSqxr8qv36Er2zg&amp;_nc_ss=7e3ba&amp;oh=00_AQNyhU6tlcuNJfaZXu_Md-0PWrk_L2oXQZXhjqDZUEiEoQ&amp;oe=6AC2269C
+https://scontent-dfw5-1.cdninstagram.com/v/t51.71878-15/828895840_1850228683002422_9023370776441248208_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk5NzEzMzcyMTU4OTM5NjMzNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=RVV4ok2ly4gQ7kNvwGtHP7J&amp;_nc_oc=AdoLnF-SxBb9U9H9dhzYKLzrp9VX2DprzAEHPhIi8hc2K7-0KcKv-QLrWfy3N7VzIbM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_gid=_STxp7pVSqxr8qv36Er2zg&amp;_nc_ss=7e3ba&amp;oh=00_AQMfNhPWr_YRgJIh8SyH_NBezKXI2jl7ucvE-xuujfVSDw&amp;oe=6AC2269C
+https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwFVX6Xz&amp;_nc_oc=AdqtAod-C7eU8bbhbiLpjsSojKibiaoVPgRd4tXGxvRcbBFXuK5EuqedE_55BFQUSX8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQO1DJBd7QICXAB7CBzqiMh-ECJs5l7mW2zaKf8ALQ1FpQ&amp;oe=6AC24299
+https://l.instagram.com/?u=https%3A%2F%2Fwww.tesla.com%2Fcareers%2Fsearch%2Fjob%2F285085%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaf4gs736-c3o4MIcLhtMVQZDoAI7ft36cYh_SvXTI1ORlQQ7VjLpfpDKeSuUQ_aem_5qAtC_Ys9e52GvuJBpKp9Q&amp;e=AUDtZ7DVDs9BA9sW5fqxWJwXp065AHgfdkp_AsiPE_lKq3zIPCWfYCoVLdcLvZnIFcen6SA463cKkfXBNnPHYcpCc3V3GZ1fM27BKCPE6jjpPQCr75aPsvdwXsSy97LFgyqPuvmF_EkeSw
+https://scontent-dfw5-2.cdninstagram.com/o1/v/t2/f2/m78/AQNPz5lHNhAcXadNxMTIUGpDL3oQAbbWW2vjJ7DpHmOhbb2tZ0xNcxZtjJxXfvO7vSbnu6SaN4nyBglI5CpQEB5hoNtQAetDdx5KS14.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ohc=vQVpXYpgKcUQ7kNvwHW2PeB&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwMjU0Njc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=9a601c63ab01be4f&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzg2NTM4NkI3MzE5MzQ2NDhCMjlCQUJFMTZFQUZDRkJBX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkg6yV7vehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=_STxp7pVSqxr8qv36Er2zg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQNmK-ftysfZ1HEgxFzxxt39P-Ppbu8upNvhPgNhzS9aRg&amp;oe=6ABE4049</t>
+        </is>
+      </c>
+      <c r="O261" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P261" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q261" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R261" s="3" t="inlineStr"/>
+    </row>
+    <row r="262" ht="45" customHeight="1">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>64cc3ff78f0d84ce84bd</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T00:33:37.923054+00:00</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T21:11:15+00:00</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="inlineStr">
+        <is>
+          <t>SIG</t>
+        </is>
+      </c>
+      <c r="E262" s="3" t="inlineStr">
+        <is>
+          <t>SIG — Other Opportunity</t>
+        </is>
+      </c>
+      <c r="F262" s="3" t="inlineStr">
+        <is>
+          <t>Other Opportunity</t>
+        </is>
+      </c>
+      <c r="G262" s="3" t="inlineStr"/>
+      <c r="H262" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I262" s="3" t="inlineStr"/>
+      <c r="J262" s="3" t="inlineStr"/>
+      <c r="K262" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.sig.com/event-36238/talentcommunity/form</t>
+        </is>
+      </c>
+      <c r="L262" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M262" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N262" s="3" t="inlineStr">
+        <is>
+          <t>@ careers.sig.com
+Instagram
+SUSQUEHANNA
+= )
+Register for The Showdown, Presented by
+Susquehanna, our intercollegiate poker
+tournament for students attending U.S and
+Canada based universities. To earn your
+seat at the in-person finale at
+Susquehanna’'s office in April 2027, you
+must first qualify through a virtual round,
+which will be held using Poker Now. If you
+don't have a Poker Now account, visit
+https://www.pokernow.club/ to create one
+before registering below.
+|
+https://scontent-dfw6-2.cdninstagram.com/v/t51.71878-15/829586373_4580104355589580_8502356643241525832_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5NzE0MDMwNTM2MzI1NjYzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=EgkNhDHhZqAQ7kNvwHE0G2s&amp;_nc_oc=AdpMh2rLIoeyFY7sCJi7z78wZx_KjWk1asW2mB6jvUjWbipfUqi9oLg5Obya0sA1g3I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-2.cdninstagram.com&amp;_nc_gid=_STxp7pVSqxr8qv36Er2zg&amp;_nc_ss=7e3ba&amp;oh=00_AQNtSIowHtCfGd2X-4qtIoT6tiYoh-72-idD33buqZg-_w&amp;oe=6AC2418C
+https://scontent-dfw6-2.cdninstagram.com/v/t51.71878-15/829586373_4580104355589580_8502356643241525832_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5NzE0MDMwNTM2MzI1NjYzMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=EgkNhDHhZqAQ7kNvwHE0G2s&amp;_nc_oc=AdpMh2rLIoeyFY7sCJi7z78wZx_KjWk1asW2mB6jvUjWbipfUqi9oLg5Obya0sA1g3I&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-2.cdninstagram.com&amp;_nc_gid=_STxp7pVSqxr8qv36Er2zg&amp;_nc_ss=7e3ba&amp;oh=00_AQM08RVUzDOCYc54iAJhIm0UbUN-VRYRT6UiYcoqc8XC0A&amp;oe=6AC2418C
+https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwFVX6Xz&amp;_nc_oc=AdqtAod-C7eU8bbhbiLpjsSojKibiaoVPgRd4tXGxvRcbBFXuK5EuqedE_55BFQUSX8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQO1DJBd7QICXAB7CBzqiMh-ECJs5l7mW2zaKf8ALQ1FpQ&amp;oe=6AC24299
+https://l.instagram.com/?u=https%3A%2F%2Fcareers.sig.com%2Fevent-36238%2Ftalentcommunity%2Fform%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAactiayJ3p6Vs02_jERk7VDLQemgbbSY7cPr5CodRLdS0igPbiHsx6gPsAAHNg_aem_Rg7pMX5O3JEFORPiFztpdg&amp;e=AUA3prwc-jIXc-bkwqfR82IdXfsF3q02gakl3jReGcLupVau4SqahgsvYfJ52mPVKCV6TiqVnEM1ccUhfvGwPOU-pLE4uUZTmgwLRmco1XNtp5DVV-7DAFW4QwyUhggssTJly4-SelaFug
+https://scontent-dfw5-2.cdninstagram.com/o1/v/t2/f2/m78/AQO1fbYNcvYMsetHSHgfJfxJopzGS30Mnx03yjbc1QuVWhe8avXuVaWwAOjO02gX8U96CX1YwEt1HDSjdfqaBVdyUp-GVoFZsRVOf4U.mp4?_nc_cat=104&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ohc=Ttw-qkIQLhsQ7kNvwFTHqmr&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwMjY3MDY2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=925df5856360ab49&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzY0MkUxREU2MTE2QzRDNzg5NkUyMkY1QzNBMEYwRkIzX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkkvmy9_ehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=_STxp7pVSqxr8qv36Er2zg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQN3h6dCqQkZ6uqJ7OirmHjyr_F0bemOjgjXArAf1bm9VA&amp;oe=6ABE2291</t>
+        </is>
+      </c>
+      <c r="O262" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P262" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q262" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R262" s="3" t="inlineStr"/>
+    </row>
+    <row r="263" ht="45" customHeight="1">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>1dfadc9104e5c39cb56a</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T00:33:40.077315+00:00</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T21:15:29+00:00</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="inlineStr">
+        <is>
+          <t>Acuityinc</t>
+        </is>
+      </c>
+      <c r="E263" s="3" t="inlineStr">
+        <is>
+          <t>Acuityinc — Internship</t>
+        </is>
+      </c>
+      <c r="F263" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G263" s="3" t="inlineStr"/>
+      <c r="H263" s="3" t="inlineStr"/>
+      <c r="I263" s="3" t="inlineStr"/>
+      <c r="J263" s="3" t="inlineStr"/>
+      <c r="K263" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.acuityinc.com/job/Conyers-Intern-Program-Manager%2C-Early-Careers-GA-30012/1433760700</t>
+        </is>
+      </c>
+      <c r="L263" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M263" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N263" s="3" t="inlineStr">
+        <is>
+          <t>Intern Program Manager, Early
+Careers
+Req ID: 16554
+Work Flexibility: Hybrid
+Acuity
+Acuity Inc. (NYSE: AY1) is a market-leading
+industrial technology company. We use
+technology to solve problems in spaces, light
+@ CAREERS.ACUITYINC.COM
+design, manufacture to market
+products and service e a valuable
+difference in people's II
+We achieve growth through the development of
+innovative new products and services, including
+lighting, lighting controls, building management
+solutions, and an audio, video and control
+platform. We focus on customer outcomes and
+https://scontent-dfw6-2.cdninstagram.com/v/t51.71878-15/826395556_1714828049601580_593828503667019336_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5NzE0MjQzODU2OTQ0NjQ2Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=7il4YOttNosQ7kNvwHqpczP&amp;_nc_oc=AdpI45Pf4RTe6NOj3D4V1iIN5nrd_CeqinvdUX1i80-iK9AJLyLCVrI4u_Xip6tCrbk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-2.cdninstagram.com&amp;_nc_gid=_STxp7pVSqxr8qv36Er2zg&amp;_nc_ss=7e3ba&amp;oh=00_AQNh9CAhta1R-agyh-hbFzgwtOngj8rhzW4DrgQZzrX_bQ&amp;oe=6AC242A9
+https://scontent-dfw6-2.cdninstagram.com/v/t51.71878-15/826395556_1714828049601580_593828503667019336_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5NzE0MjQzODU2OTQ0NjQ2Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=7il4YOttNosQ7kNvwHqpczP&amp;_nc_oc=AdpI45Pf4RTe6NOj3D4V1iIN5nrd_CeqinvdUX1i80-iK9AJLyLCVrI4u_Xip6tCrbk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-2.cdninstagram.com&amp;_nc_gid=_STxp7pVSqxr8qv36Er2zg&amp;_nc_ss=7e3ba&amp;oh=00_AQOw8BaA9gUL4pno3H8c7rbEnTFge5bVbrpIo7NfHHj-ag&amp;oe=6AC242A9
+https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwFVX6Xz&amp;_nc_oc=AdqtAod-C7eU8bbhbiLpjsSojKibiaoVPgRd4tXGxvRcbBFXuK5EuqedE_55BFQUSX8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQO1DJBd7QICXAB7CBzqiMh-ECJs5l7mW2zaKf8ALQ1FpQ&amp;oe=6AC24299
+https://l.instagram.com/?u=https%3A%2F%2Fcareers.acuityinc.com%2Fjob%2FConyers-Intern-Program-Manager%252C-Early-Careers-GA-30012%2F1433760700%2F%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafpHyttVbPBJxRbgiRgHB63HhRSIwKyNUuQlj68F1OkmdiBie6M7iiMg83P1g_aem_h9Lr2uRULbYIOPtESHZu_w&amp;e=AUBSjAeM8bE9BKYNKYWvzBiadns7rQ4FjafVBzPz7OqvpDEDc2xV8qEIO6gp6rdaVviwaqIXHXGkilVbarUhszbbm6cnMjUgBy_Z2flna4UvRpP7hP8lERtUG-dMcqbtiruksbQwbCvXCg
+https://scontent-dfw6-2.cdninstagram.com/o1/v/t2/f2/m78/AQPPWH4dl6K_g8dgv9AmK2do8NwcrXj-_TWi1Y_6bvoMtU0Vki58M_wQIgFpmKg4T0kFVzxnS5bzIGvamkpSeAui8kNobHa-xvTIvME.mp4?_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-dfw6-2.cdninstagram.com&amp;_nc_ohc=hQsTOmWzE9oQ7kNvwFNmgXi&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwMjczMDM2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=692dcd58caab7e06&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0VCQUYyODdFQTg3QTQyRjE4REQ3QjVGN0I0RTJCREQ1X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkj6Xs-_ehQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=_STxp7pVSqxr8qv36Er2zg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQNEQuak0vFNTZKA8rrzKbeim-HnKEWJcQBur87hZ85RKw&amp;oe=6ABE260D</t>
+        </is>
+      </c>
+      <c r="O263" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P263" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q263" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R263" s="3" t="inlineStr"/>
+    </row>
+    <row r="264" ht="45" customHeight="1">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>69ff1a742c467d507486</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T00:33:42.102506+00:00</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T23:31:08+00:00</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>Robinhood</t>
+        </is>
+      </c>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>Robinhood — Data Science</t>
+        </is>
+      </c>
+      <c r="F264" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G264" s="3" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="H264" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I264" s="3" t="inlineStr">
+        <is>
+          <t>Menlo Park</t>
+        </is>
+      </c>
+      <c r="J264" s="3" t="inlineStr"/>
+      <c r="K264" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/robinhood/jobs/8241738?t=gh_src%3D&amp;gh_jid=8241738</t>
+        </is>
+      </c>
+      <c r="L264" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M264" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N264" s="3" t="inlineStr">
+        <is>
+          <t>@ job-boards.greenhouse.io C:
+@ Robinhood
+&lt; Back to jobs
+Data Science Intern
+(Summer 2027)
+© Menlo Park, CA
+Apply
+(7) JOB-BOARDS, GREENHOUSE. IO
+Our mission is to de e finance for all.
+An estimated $124 trillion of assets will be
+inherited by younger generations in the next
+two decades. The largest transfer of wealth
+in human history. If you’re ready to be at the
+epicenter of this historic cultural and
+financial shift, keep reading.
+https://scontent-dfw6-1.cdninstagram.com/v/t51.71878-15/825324619_1074995795316023_6251296652146274068_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5NzIxMDcxMTg1NTk1NTY2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=h-n2vPlMFaEQ7kNvwGyLxoX&amp;_nc_oc=Adr1NcG6aRiWwUHkA1wr1Y3ZgZTCteaInBILTYz00bcTh0UZOzW2pSOW7__oLiu-T0w&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=_STxp7pVSqxr8qv36Er2zg&amp;_nc_ss=7e3ba&amp;oh=00_AQP1Paxxa8USlt3xuUpVQgzjW_d13YOjOu-N2AxmxY1hHw&amp;oe=6AC23E94
+https://scontent-dfw6-1.cdninstagram.com/v/t51.71878-15/825324619_1074995795316023_6251296652146274068_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5NzIxMDcxMTg1NTk1NTY2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=h-n2vPlMFaEQ7kNvwGyLxoX&amp;_nc_oc=Adr1NcG6aRiWwUHkA1wr1Y3ZgZTCteaInBILTYz00bcTh0UZOzW2pSOW7__oLiu-T0w&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=_STxp7pVSqxr8qv36Er2zg&amp;_nc_ss=7e3ba&amp;oh=00_AQNa5AHnFibZnsw1cC43fLVs6wr8siI4a8zE9dWpbcSQAw&amp;oe=6AC23E94
+https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwFVX6Xz&amp;_nc_oc=AdqtAod-C7eU8bbhbiLpjsSojKibiaoVPgRd4tXGxvRcbBFXuK5EuqedE_55BFQUSX8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQO1DJBd7QICXAB7CBzqiMh-ECJs5l7mW2zaKf8ALQ1FpQ&amp;oe=6AC24299
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Frobinhood%2Fjobs%2F8241738%3Ft%3Dgh_src%253D%26gh_jid%3D8241738%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAad7b8TvFpW6AD66Pd6peB0862xVx6LzItGwfe8N_d6QrfqDIDEw2KGt1yDJQw_aem_FfCpOagRWmPoyL0OdZ00Dw&amp;e=AUDGbJDsReYOKilBvtaauOBT6EOQoWQt1mtzZ1ojIUMj5_txYi708Xju5-ah8C8Qk9ATACS7_1uDREed1xbdEVtDNHBJVsIJca0Ox5-kbbdZq_jS2L6ioodS7g992w5_jML42IF-7BBa-g
+https://scontent-dfw5-1.cdninstagram.com/o1/v/t2/f2/m78/AQM7HbwXR1boH9jI1Iv7Wmdhx1NFS6PMxR3Wl8RrgfoHWBkbmgRGHGH07DV-VxhcxTbhDzlbIvKkY5qeRlSzCHaVF7xSiGhHVlmowws.mp4?_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_ohc=GdONbA7kkeEQ7kNvwH9NNbQ&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwMzkzNTE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=1de928efc23b9067&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0VCNTI3OTMxQ0NCNjQ2QzFCMkUyNkY0Nzc4MTg1MEE3X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkn5TO1fihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=_STxp7pVSqxr8qv36Er2zg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQO-CABNhUotT6NYcD8cbFgtu7yV8ZVQtmfCtDdRknpo1A&amp;oe=6ABE3B03</t>
+        </is>
+      </c>
+      <c r="O264" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P264" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q264" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R264" s="3" t="inlineStr"/>
+    </row>
+    <row r="265" ht="45" customHeight="1">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>261caaeca4b405675dbb</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T00:33:43.782843+00:00</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T23:33:00+00:00</t>
+        </is>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>Enova</t>
+        </is>
+      </c>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>Enova — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F265" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G265" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H265" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I265" s="3" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="J265" s="3" t="inlineStr"/>
+      <c r="K265" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/enova/jobs/8239619</t>
+        </is>
+      </c>
+      <c r="L265" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M265" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N265" s="3" t="inlineStr">
+        <is>
+          <t>&lt; Back to jobs
+Software Engineer
+Internship Summer
+2027 (Hybrid)
+© Chicago, IL
+We are interested lified
+candidate who is eli ork in the
+United States. However, we are not able to
+sponsor visas or take over sponsorship at
+this time.
+About the role: _—
+As a Software Engineering Intern, you v Lo
+integrated into our core agile teams and
+https://scontent-dfw6-1.cdninstagram.com/v/t51.71878-15/829780645_2284533935724220_5735114928230085936_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5NzIxMTY0NTY5MjU1NDYwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=0HP8wgNBPooQ7kNvwHKPSNP&amp;_nc_oc=Adr6Z4Zx7AZAZkuspV5LsNoWMS_qLWxosoQTpOnCDEPvGLwvTSLtqWzVp-3pZeE6WEg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=_STxp7pVSqxr8qv36Er2zg&amp;_nc_ss=7e3ba&amp;oh=00_AQOw1Q_spYIQULYCvCfAYIdRWbS84AAuCjW-UIar7GLRIw&amp;oe=6AC24132
+https://scontent-dfw6-1.cdninstagram.com/v/t51.71878-15/829780645_2284533935724220_5735114928230085936_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5NzIxMTY0NTY5MjU1NDYwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=0HP8wgNBPooQ7kNvwHKPSNP&amp;_nc_oc=Adr6Z4Zx7AZAZkuspV5LsNoWMS_qLWxosoQTpOnCDEPvGLwvTSLtqWzVp-3pZeE6WEg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=_STxp7pVSqxr8qv36Er2zg&amp;_nc_ss=7e3ba&amp;oh=00_AQOrQ9dYyi4RjNHJDGqwUT2SHuF9FecOzCNO6p5KOfQ7LQ&amp;oe=6AC24132
+https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwFVX6Xz&amp;_nc_oc=AdqtAod-C7eU8bbhbiLpjsSojKibiaoVPgRd4tXGxvRcbBFXuK5EuqedE_55BFQUSX8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQO1DJBd7QICXAB7CBzqiMh-ECJs5l7mW2zaKf8ALQ1FpQ&amp;oe=6AC24299
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Fenova%2Fjobs%2F8239619%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaefXL7HMISmaWmaGQtQ2JWHVjpyIGl5SNC-aS2wltFvLgRkeitTIib4TFEtrg_aem_w4-q3Ll2BBCooujY1MfLqQ&amp;e=AUAbrayG_TVnW-Xz1rx6ErmizR3uJM9BIxfw3_-fI8KCzmlpGCSck1TrPVGoAg1i5hmuexKxmbqUhbrmTV1yZ5I1nhQzpU-vNeVxWs9LVhMcKS9Rbq9lu9_XXPd6T1dEUdgpV0PxS3s5_w
+https://scontent-dfw5-2.cdninstagram.com/o1/v/t2/f2/m78/AQPLKixT0WqG1AaDVKOvP65nm6RyMD8OZB4uFpVQ-CnhF-zpDg-fx_-7gKF69RRDFCrr_RJJ1bu5wfxYUrXWYhCAtpDCb_kjAjSpsQM.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ohc=wzmUrZ5lcvYQ7kNvwEjWw7g&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwMzk1MzE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=568eef1fdd6fdf83&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzUzNDU4RkM5N0Y2NjRDOEM5RjNGMDlFMzY2NzNBOTk4X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk8-j51vihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=_STxp7pVSqxr8qv36Er2zg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQN8IYiobdRVejdZqLjREDKywYUsUetBqMtC8INtdXqckQ&amp;oe=6ABE4A0D</t>
+        </is>
+      </c>
+      <c r="O265" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P265" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q265" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R265" s="3" t="inlineStr"/>
+    </row>
+    <row r="266" ht="45" customHeight="1">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>77748c2647796c15e682</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T00:33:44.945816+00:00</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29T23:47:51+00:00</t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="inlineStr"/>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>Job Type Intern/Apprentice</t>
+        </is>
+      </c>
+      <c r="F266" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G266" s="3" t="inlineStr"/>
+      <c r="H266" s="3" t="inlineStr">
+        <is>
+          <t>Spring 2027</t>
+        </is>
+      </c>
+      <c r="I266" s="3" t="inlineStr"/>
+      <c r="J266" s="3" t="inlineStr"/>
+      <c r="K266" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tesla.com/careers/search/job/285089</t>
+        </is>
+      </c>
+      <c r="L266" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M266" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N266" s="3" t="inlineStr">
+        <is>
+          <t>TESLA Careers Menu
+Go to search
+Internship, Al Hardware
+RTL Design Engineer, Al
+Hardware
+(Winter/Spring 2027)
+Job Category Tesla Al
+. Palo Alto,
+Eecaricn California
+Req. ID 285089
+Job Type Intern/Apprentice
+@ TESLA.COM
+https://scontent-dfw6-1.cdninstagram.com/v/t51.71878-15/831474538_27670891959254377_3140384873408221976_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5NzIxOTEyMzQzMTkyMzgwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=6iFDcTpPUrgQ7kNvwGVFbyn&amp;_nc_oc=AdpIvvJNM2Rzbxxqs96SorXg-NGSNGWViwHYV4nbYVg2GqyHykl7ELG-bJMfwvui_Y4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=_STxp7pVSqxr8qv36Er2zg&amp;_nc_ss=7e3ba&amp;oh=00_AQMyHDgF9YZlUuxu7RoRl9gxuOAh80-trl44Ku0XbAKBLQ&amp;oe=6AC23233
+https://scontent-dfw6-1.cdninstagram.com/v/t51.71878-15/831474538_27670891959254377_3140384873408221976_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5NzIxOTEyMzQzMTkyMzgwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=6iFDcTpPUrgQ7kNvwGVFbyn&amp;_nc_oc=AdpIvvJNM2Rzbxxqs96SorXg-NGSNGWViwHYV4nbYVg2GqyHykl7ELG-bJMfwvui_Y4&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=_STxp7pVSqxr8qv36Er2zg&amp;_nc_ss=7e3ba&amp;oh=00_AQNnnQvQD_Qwt20CF5pUGszjkiRa8u-ETc5GmxMDcQ2z8w&amp;oe=6AC23233
+https://scontent-dfw5-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=LyUynlmBnroQ7kNvwFVX6Xz&amp;_nc_oc=AdqtAod-C7eU8bbhbiLpjsSojKibiaoVPgRd4tXGxvRcbBFXuK5EuqedE_55BFQUSX8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQO1DJBd7QICXAB7CBzqiMh-ECJs5l7mW2zaKf8ALQ1FpQ&amp;oe=6AC24299
+https://l.instagram.com/?u=https%3A%2F%2Fwww.tesla.com%2Fcareers%2Fsearch%2Fjob%2F285089%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeQz8A9c2JBXjyhG5R6owbZdYq5MIHf6OzwLXLakZPDRl0ia5kpCGu_jh6WXw_aem_nnJupfK3MWow4qGoDA71uQ&amp;e=AUCqoAvxuVfrQTxFG3bAEoyh-SOp2yKmzLSKRLjw3Ja3Yq1fX1HSfYpSAYdQoHr3TcFAelzgMXdKlqtnd50j3KMZBwWtWfaNti9Ng8DrBCMUXBZsYmEtODPYFNDAU97XQnMmYIifqMKg-Q
+https://scontent-dfw6-1.cdninstagram.com/o1/v/t2/f2/m78/AQOAxn1mVSTSrjGe-QOGW2dMv7N8vQqsI35J1syNSq3zKgr07fluikIsEImlGvKaZxNhnmX4_GOzkEybRMGSJlw0iLuBiYa0MmAesWA.mp4?_nc_cat=102&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_ohc=ZC7HpUSeyRcQ7kNvwH_sQ8_&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwNDA5NDE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=6f73d572d7644016&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzM4NzVERkNFMkVENjQxMEU4Q0MwMTlFMDg3RTRDNjBFX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkhcC64fihQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=_STxp7pVSqxr8qv36Er2zg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQOZaGd_PmosjsSJqqPDJVXBZbZd8iPnmfNHeE5hJQ9ijg&amp;oe=6ABE3E2F</t>
+        </is>
+      </c>
+      <c r="O266" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P266" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q266" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R266" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R260"/>
+  <autoFilter ref="A1:R266"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -25831,6 +26401,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L259" r:id="rId501"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K260" r:id="rId502"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L260" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K261" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L261" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K262" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L262" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K263" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L263" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K264" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L264" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K265" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L265" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K266" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L266" r:id="rId515"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$266</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$270</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R266"/>
+  <dimension ref="A1:R270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25328,7 +25328,7 @@
     <row r="261" ht="45" customHeight="1">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>4ea801c04dcf247aa6f9</t>
+          <t>dec896c009ee46cb8cf9</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
@@ -25341,7 +25341,7 @@
           <t>2026-09-29T20:58:10+00:00</t>
         </is>
       </c>
-      <c r="D261" s="3" t="inlineStr"/>
+      <c r="D261" s="3" t="n"/>
       <c r="E261" s="3" t="inlineStr">
         <is>
           <t>Job Type Intern/Apprentice</t>
@@ -25352,14 +25352,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G261" s="3" t="inlineStr"/>
+      <c r="G261" s="3" t="n"/>
       <c r="H261" s="3" t="inlineStr">
         <is>
           <t>Spring 2027</t>
         </is>
       </c>
-      <c r="I261" s="3" t="inlineStr"/>
-      <c r="J261" s="3" t="inlineStr"/>
+      <c r="I261" s="3" t="n"/>
+      <c r="J261" s="3" t="n"/>
       <c r="K261" s="4" t="inlineStr">
         <is>
           <t>https://www.tesla.com/careers/search/job/285085</t>
@@ -25412,12 +25412,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R261" s="3" t="inlineStr"/>
+      <c r="R261" s="3" t="n"/>
     </row>
     <row r="262" ht="45" customHeight="1">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>64cc3ff78f0d84ce84bd</t>
+          <t>9d875f314bf2e2622965</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -25445,14 +25445,14 @@
           <t>Other Opportunity</t>
         </is>
       </c>
-      <c r="G262" s="3" t="inlineStr"/>
+      <c r="G262" s="3" t="n"/>
       <c r="H262" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="I262" s="3" t="inlineStr"/>
-      <c r="J262" s="3" t="inlineStr"/>
+      <c r="I262" s="3" t="n"/>
+      <c r="J262" s="3" t="n"/>
       <c r="K262" s="4" t="inlineStr">
         <is>
           <t>https://careers.sig.com/event-36238/talentcommunity/form</t>
@@ -25508,12 +25508,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R262" s="3" t="inlineStr"/>
+      <c r="R262" s="3" t="n"/>
     </row>
     <row r="263" ht="45" customHeight="1">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>1dfadc9104e5c39cb56a</t>
+          <t>e5d0d29b5b5efcb718b4</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
@@ -25541,10 +25541,10 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G263" s="3" t="inlineStr"/>
-      <c r="H263" s="3" t="inlineStr"/>
-      <c r="I263" s="3" t="inlineStr"/>
-      <c r="J263" s="3" t="inlineStr"/>
+      <c r="G263" s="3" t="n"/>
+      <c r="H263" s="3" t="n"/>
+      <c r="I263" s="3" t="n"/>
+      <c r="J263" s="3" t="n"/>
       <c r="K263" s="4" t="inlineStr">
         <is>
           <t>https://careers.acuityinc.com/job/Conyers-Intern-Program-Manager%2C-Early-Careers-GA-30012/1433760700</t>
@@ -25601,12 +25601,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R263" s="3" t="inlineStr"/>
+      <c r="R263" s="3" t="n"/>
     </row>
     <row r="264" ht="45" customHeight="1">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>69ff1a742c467d507486</t>
+          <t>b30665329ae8941f9065</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -25649,7 +25649,7 @@
           <t>Menlo Park</t>
         </is>
       </c>
-      <c r="J264" s="3" t="inlineStr"/>
+      <c r="J264" s="3" t="n"/>
       <c r="K264" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/robinhood/jobs/8241738?t=gh_src%3D&amp;gh_jid=8241738</t>
@@ -25704,12 +25704,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R264" s="3" t="inlineStr"/>
+      <c r="R264" s="3" t="n"/>
     </row>
     <row r="265" ht="45" customHeight="1">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>261caaeca4b405675dbb</t>
+          <t>a9d050ff8be7f298323b</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
@@ -25752,7 +25752,7 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="J265" s="3" t="inlineStr"/>
+      <c r="J265" s="3" t="n"/>
       <c r="K265" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/enova/jobs/8239619</t>
@@ -25805,12 +25805,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R265" s="3" t="inlineStr"/>
+      <c r="R265" s="3" t="n"/>
     </row>
     <row r="266" ht="45" customHeight="1">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>77748c2647796c15e682</t>
+          <t>f7fb890222ad9d5e2f4a</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -25823,7 +25823,7 @@
           <t>2026-09-29T23:47:51+00:00</t>
         </is>
       </c>
-      <c r="D266" s="3" t="inlineStr"/>
+      <c r="D266" s="3" t="n"/>
       <c r="E266" s="3" t="inlineStr">
         <is>
           <t>Job Type Intern/Apprentice</t>
@@ -25834,14 +25834,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G266" s="3" t="inlineStr"/>
+      <c r="G266" s="3" t="n"/>
       <c r="H266" s="3" t="inlineStr">
         <is>
           <t>Spring 2027</t>
         </is>
       </c>
-      <c r="I266" s="3" t="inlineStr"/>
-      <c r="J266" s="3" t="inlineStr"/>
+      <c r="I266" s="3" t="n"/>
+      <c r="J266" s="3" t="n"/>
       <c r="K266" s="4" t="inlineStr">
         <is>
           <t>https://www.tesla.com/careers/search/job/285089</t>
@@ -25893,10 +25893,391 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R266" s="3" t="inlineStr"/>
+      <c r="R266" s="3" t="n"/>
+    </row>
+    <row r="267" ht="45" customHeight="1">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>c90966ef561a66c5f8a3</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T06:50:07.717769+00:00</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T03:18:35+00:00</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="inlineStr"/>
+      <c r="E267" s="3" t="inlineStr">
+        <is>
+          <t>al 2 NEW GRAD PM!</t>
+        </is>
+      </c>
+      <c r="F267" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G267" s="3" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="H267" s="3" t="inlineStr"/>
+      <c r="I267" s="3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J267" s="3" t="inlineStr"/>
+      <c r="K267" s="4" t="inlineStr">
+        <is>
+          <t>https://www.demystifyd.com/jobs/product-manager-—-new-graduate</t>
+        </is>
+      </c>
+      <c r="L267" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M267" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N267" s="3" t="inlineStr">
+        <is>
+          <t>@ demystifyd.com C:
+D) DEMYSTIFYD
+HOME
+Product Manager —
+New Graduate
+New York, London, Toronto, San
+Francisco
+Job Type Full-time
+al 2 NEW GRAD PM!
+Own feature plangé ject definition,
+and issue prioritiz a deeply
+technical, engineering-led product
+organization.
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/825324752_1962619567745729_2040668614727993693_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5NzMyNTE4ODE0NDQyNjM3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=0AETek2Jut8Q7kNvwHMtUM0&amp;_nc_oc=AdoTbWe70iI-KKnclEICH_yqTBFYeGUrCs1T26gzdZvREG3y3GGVdAo7hU7jB_rKGRs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=8MjW_8NO19yWR7-Xa3JDJg&amp;_nc_ss=7e3ba&amp;oh=00_AQP53acx6lBcecNjynS1og-Z7eekfVnMdwtID702KinlYQ&amp;oe=6AC27C5A
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/825324752_1962619567745729_2040668614727993693_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5NzMyNTE4ODE0NDQyNjM3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=0AETek2Jut8Q7kNvwHMtUM0&amp;_nc_oc=AdoTbWe70iI-KKnclEICH_yqTBFYeGUrCs1T26gzdZvREG3y3GGVdAo7hU7jB_rKGRs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=8MjW_8NO19yWR7-Xa3JDJg&amp;_nc_ss=7e3ba&amp;oh=00_AQNlONebX0TIk0Ki6V-88S9EWYThTV62Xwr7dZuAnwtmFg&amp;oe=6AC27C5A
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=-f_j7BYj1KsQ7kNvwGzdcj3&amp;_nc_oc=AdpRxTchOp2IJm_xu6RC4bbcpkys9vTrccoEiRteYW3mhCALz5hhwHpFfvIS3pZAo_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQM9bwNkhXXwESu_50poqSZJhmhDToNNveNYyF5wM8q4vQ&amp;oe=6AC27AD9
+https://l.instagram.com/?u=https%3A%2F%2Fwww.demystifyd.com%2Fjobs%2Fproduct-manager-%E2%80%94-new-graduate%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeAmz_rtGiYE6fXWTa3MwTTUmt9ajCB9Esg0siEbWs7pSDuf_q6HkUe274GgQ_aem_boOcAMg4yKFYds_cShnyXQ&amp;e=AUCVKnyRzh8Ua2hNPtFF5zyKlecXQf5QlUZQujya7gZ2SaB1B8U_niOr3W73qSx8PYEPMTppVQ7taWNiz4skrVr9ob_nuX8C7s89P1TqRw
+https://scontent-lax3-2.cdninstagram.com/o1/v/t2/f2/m78/AQOO4F8N1l26T3fHvl8g6S-crfl6HqLfc7Xg2JTCSW7HINY6ajcxnnLGNjh6MwIUgojYpH7S-K82byfHLjwRGoB1lEyM3NQc-Nne7yg.mp4?_nc_cat=107&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ohc=cvaSi-cIvKcQ7kNvwEUzXN3&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwNjA2NTE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=974e4ceb3994e715&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzQ5RkYyMDc0Qjk0NDQ2RTU4QzdFQzlBQjZFOUZCMDY4X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk87Wn9PmhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=8MjW_8NO19yWR7-Xa3JDJg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQPTwnr8-pC5N58Lo3C6D_ot34H7-g7tryqVshfeKPHd-A&amp;oe=6ABE8CE4</t>
+        </is>
+      </c>
+      <c r="O267" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P267" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q267" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R267" s="3" t="inlineStr"/>
+    </row>
+    <row r="268" ht="45" customHeight="1">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>4796a062511603898286</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T06:50:11.374535+00:00</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T03:19:41+00:00</t>
+        </is>
+      </c>
+      <c r="D268" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E268" s="3" t="inlineStr">
+        <is>
+          <t>Amazon — Internship</t>
+        </is>
+      </c>
+      <c r="F268" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G268" s="3" t="inlineStr"/>
+      <c r="H268" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I268" s="3" t="inlineStr"/>
+      <c r="J268" s="3" t="inlineStr"/>
+      <c r="K268" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.jobs/en/jobs/10564599/2027-applied-science-internship-united-states-undergrad-student-science-recruiting-frontier-ai-robotics?jr_id=6abc6f9f2668e0eab35c23d1</t>
+        </is>
+      </c>
+      <c r="L268" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M268" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N268" s="3" t="inlineStr">
+        <is>
+          <t>amazon
+—?
+Impact the
+future, tocay.
+2027 Applied Science Internship
+- United States, Undergrad
+Student Science Recruiting,
+Frontier Al &amp; Robotics
+Are you a brilliant mind seeking
+to push the boundaries of what's
+possible with intelligent robotics?
+Join our elite team of researchers
+and engineers - led by Pieter Abeel,
+Rocky Duan, and Peter Chen - at
+the forefront of applied science,
+where we're harnessing the latest
+advancements in large lang...
+https://www.amazon.jobs/en
+_id=6abc6f9f2E ‘ab35c23d1
+Amazon undergrad research
+robotics and Ilm
+https://scontent-lax7-1.cdninstagram.com/v/t51.71878-15/829647802_1033045443074739_5467457875457086463_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5NzMyNTc0Njg3NTY5NjY1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=BU9ptfOgsboQ7kNvwHFUT8P&amp;_nc_oc=Adru8b-LiWg83Zr3-uaYXFT6thB_3yxq85ggxWJWj0KWAtD8nBk5GQtg5x2iJ73yC-E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_gid=8MjW_8NO19yWR7-Xa3JDJg&amp;_nc_ss=7e3ba&amp;oh=00_AQPY_t9xedcn9WBdjNHyxhcld1oP-V9nL_pYTjY9wIx87Q&amp;oe=6AC27098
+https://scontent-lax7-1.cdninstagram.com/v/t51.71878-15/829647802_1033045443074739_5467457875457086463_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5NzMyNTc0Njg3NTY5NjY1Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=BU9ptfOgsboQ7kNvwHFUT8P&amp;_nc_oc=Adru8b-LiWg83Zr3-uaYXFT6thB_3yxq85ggxWJWj0KWAtD8nBk5GQtg5x2iJ73yC-E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_gid=8MjW_8NO19yWR7-Xa3JDJg&amp;_nc_ss=7e3ba&amp;oh=00_AQPAZv3vTX6RfqyZa6BHewBUuoeYwDyu_Yc1Pv0oboMkFw&amp;oe=6AC27098
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=-f_j7BYj1KsQ7kNvwGzdcj3&amp;_nc_oc=AdpRxTchOp2IJm_xu6RC4bbcpkys9vTrccoEiRteYW3mhCALz5hhwHpFfvIS3pZAo_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQM9bwNkhXXwESu_50poqSZJhmhDToNNveNYyF5wM8q4vQ&amp;oe=6AC27AD9
+https://l.instagram.com/?u=https%3A%2F%2Fwww.amazon.jobs%2Fen%2Fjobs%2F10564599%2F2027-applied-science-internship-united-states-undergrad-student-science-recruiting-frontier-ai-robotics%3Fjr_id%3D6abc6f9f2668e0eab35c23d1%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafejvIbSlhDIZuyv4gfO-nx8QYLA8eY_OqwD_rofvyqZ7LquTVig4b-U6YDSw_aem_Qs_ZGWUAuU3W8Y0PXH163A&amp;e=AUBcEhj82D2fVPHFBZsxsxIzgFc5CwO8oPalIHvxe9gqqNBMwJQHee_R5uOtCRL2ipOoFG2LEuf0Rg40SBAxSN-HC8HvV7MwInH5cCd6Yw
+https://scontent-lax3-2.cdninstagram.com/o1/v/t2/f2/m78/AQMrY0pGtezH11XRWzCh4usC0YsvKneguWdaKtaYzRTa1pwcJ6AvNLNj0_GHofbTJJFQ4KO9F9Xpd1Hj1enjdvDIIvDntPXfQB1XK2E.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ohc=KjwRIEMJ2mYQ7kNvwF99Yz_&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwNjA4ODg2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=2bdb72f17c9e04e5&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzRGN0MwMzkyMzY3QjRBQ0M4MkQ1NTE3QTg0QkFFQUY4X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkyLiJ9vmhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=8MjW_8NO19yWR7-Xa3JDJg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQOL5E-udVz_JCvOyAbn1zYqq5-oMoTa1Lq_B-TrxO88mw&amp;oe=6ABE78AC</t>
+        </is>
+      </c>
+      <c r="O268" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P268" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q268" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R268" s="3" t="inlineStr"/>
+    </row>
+    <row r="269" ht="45" customHeight="1">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>ec6bca3e3a07b296df19</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T06:50:12.234568+00:00</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T03:20:25+00:00</t>
+        </is>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>Amca</t>
+        </is>
+      </c>
+      <c r="E269" s="3" t="inlineStr">
+        <is>
+          <t>Amca — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F269" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G269" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H269" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I269" s="3" t="inlineStr"/>
+      <c r="J269" s="3" t="inlineStr"/>
+      <c r="K269" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/amca/jobs/4425120009</t>
+        </is>
+      </c>
+      <c r="L269" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M269" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N269" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Internship
+(Summer 2027)
+El Segundo, CA
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/825324818_1901617081211995_1513383481815543570_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5NzMyNjExNDIxMzQzMjYwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=K-CyiKmA63EQ7kNvwF9dCiW&amp;_nc_oc=AdryoCzhHdDGwNOOJUeSaCTChYRO25z_4OS1-vbm1B4KaT2stg_iliyN_Hu4J6PKzQI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=8MjW_8NO19yWR7-Xa3JDJg&amp;_nc_ss=7e3ba&amp;oh=00_AQNYzQQsZcTefwUHAZ0PpsPhlAitLnjRYmIwS4ibBYGNFg&amp;oe=6AC28505
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/825324818_1901617081211995_1513383481815543570_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5NzMyNjExNDIxMzQzMjYwMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=K-CyiKmA63EQ7kNvwF9dCiW&amp;_nc_oc=AdryoCzhHdDGwNOOJUeSaCTChYRO25z_4OS1-vbm1B4KaT2stg_iliyN_Hu4J6PKzQI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=8MjW_8NO19yWR7-Xa3JDJg&amp;_nc_ss=7e3ba&amp;oh=00_AQNrBiFMF1OmbjNcOX1x6ww0Wn4i5-w2ENph_828jkSoXw&amp;oe=6AC28505
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=-f_j7BYj1KsQ7kNvwGzdcj3&amp;_nc_oc=AdpRxTchOp2IJm_xu6RC4bbcpkys9vTrccoEiRteYW3mhCALz5hhwHpFfvIS3pZAo_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQM9bwNkhXXwESu_50poqSZJhmhDToNNveNYyF5wM8q4vQ&amp;oe=6AC27AD9
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Famca%2Fjobs%2F4425120009%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadodtaKIKv4c18VxsTdLgMoCF9xM4s6hTLBoKOqr8OHu8AgMqsZYKtcpG9FqQ_aem_longQGT7soBZlzb0hJk99Q&amp;e=AUCRHk4rx5EVIY9w8wQ0Vq-MhsZ7Sqa8eqGFHX6vh-nRy_0OSFaFoep9TcB5MpaJj1Xe2CeHW17B7lwtw5FMUYztS4etm397CwD5YrIEQA
+https://scontent-lax3-2.cdninstagram.com/o1/v/t2/f2/m78/AQO5r4-MT6JnJPVtN6dR1FSxaVY9giRCtxBUvmyFmMCuy15FnhIsek7EVio9zltq5WAKRDDewFkP-DIh_JQkUtBOpkF0GSdOn4Kc2Xc.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ohc=mqVeQP58xBMQ7kNvwHDCJht&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwNjExNjQ2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=f3ea2ec1aee948d&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0IyNTQzQTY5RDEzNzQyQTE5QkNGMkRDRkY2RUYwNTBBX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk_NOQ-PmhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=8MjW_8NO19yWR7-Xa3JDJg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQP6CRY0F0find_qJn1znV9P42cSeDHnYLXfuBm2nTI7WA&amp;oe=6ABE987C</t>
+        </is>
+      </c>
+      <c r="O269" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P269" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q269" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R269" s="3" t="inlineStr"/>
+    </row>
+    <row r="270" ht="45" customHeight="1">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>140429e8f45ce994e92b</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T06:50:15.165475+00:00</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T04:22:44+00:00</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="inlineStr"/>
+      <c r="E270" s="3" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F270" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G270" s="3" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="H270" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I270" s="3" t="inlineStr"/>
+      <c r="J270" s="3" t="inlineStr"/>
+      <c r="K270" s="4" t="inlineStr">
+        <is>
+          <t>https://mycareer.verizon.com/jobs/r-1101384/verizon-network-and-technology-data-science-summer-2027-internship</t>
+        </is>
+      </c>
+      <c r="L270" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M270" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N270" s="3" t="inlineStr">
+        <is>
+          <t>La
+_.,
+. y
+&lt; )
+.
+Verizon Network and
+Technology: Data Science
+Summer 2027 Internship, Irving,
+United States of America |
+Verizon Careers
+When you join Verizon You want more
+out of a career. A place to share your
+ideas freely — even if they're daring
+or different. Where the true you can
+learn, grow, and thrive. At Verizon, we
+power and empower how people live,
+work and play by connecting them
+to what brings them joy. We do what
+We...
+Seen just now
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/829507796_1081260377882081_7232340071420331779_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5NzM1NzQ4MDg4ODE3NjA2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=St0kpXnYA-gQ7kNvwF20aTn&amp;_nc_oc=AdrtEDMfNJo-mmfpGXw0PchTk4dH5Z9T1AlYXZ7Imp1LMYxLsDU1mCvxviEbenMR0as&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=8MjW_8NO19yWR7-Xa3JDJg&amp;_nc_ss=7e3ba&amp;oh=00_AQMbr00V5TT1UQAS7hDFVY3u3V-cjGOrfcuUrKlr4bl1Pw&amp;oe=6AC28C96
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/829507796_1081260377882081_7232340071420331779_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk5NzM1NzQ4MDg4ODE3NjA2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=St0kpXnYA-gQ7kNvwF20aTn&amp;_nc_oc=AdrtEDMfNJo-mmfpGXw0PchTk4dH5Z9T1AlYXZ7Imp1LMYxLsDU1mCvxviEbenMR0as&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=8MjW_8NO19yWR7-Xa3JDJg&amp;_nc_ss=7e3ba&amp;oh=00_AQPvkMMlkVaDypkhohGyeqre4d6ZNtdc1g_WIviilwG-2A&amp;oe=6AC28C96
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=-f_j7BYj1KsQ7kNvwGzdcj3&amp;_nc_oc=AdpRxTchOp2IJm_xu6RC4bbcpkys9vTrccoEiRteYW3mhCALz5hhwHpFfvIS3pZAo_o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQM9bwNkhXXwESu_50poqSZJhmhDToNNveNYyF5wM8q4vQ&amp;oe=6AC27AD9
+https://l.instagram.com/?u=https%3A%2F%2Fmycareer.verizon.com%2Fjobs%2Fr-1101384%2Fverizon-network-and-technology-data-science-summer-2027-internship%2F%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaddMMXFNGS8luCVcaXIS4pPYOZXazGhLOdbTgrWAKdJd559pzGW4DCxk-royA_aem_Vg8PahZTI3tTo-K6NNXT3w&amp;e=AUCmfv6nyUZKutZMeaLyUVtPLvS1Po85DpHUf06lWmUxoYURZBuwc5xnKWSKLNHNp96yIdMnGj8y3G-qJcklVqdfGVu6LegU_sLQlH8VYg
+https://scontent-lax3-2.cdninstagram.com/o1/v/t2/f2/m78/AQMcLFfkWoRddKX377eT0cCGHa_TfrOjoZBQsxKUQ-hUa5G4RdeaZmo6Fm7DrCWabnhY57STU-0W8mRfeQ36-nYIpYmHV1xvYcJYVPA.mp4?_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ohc=7i5d0lewpIkQ7kNvwGMrLON&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwNjc5MzU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=9b917c7a3c98fe52&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0ZFNDJERTY5MUYyMDQyRDE5QzVCNEY0NzUwNjE2NjAzX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkh_7JqvqhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=8MjW_8NO19yWR7-Xa3JDJg&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQNhkV9Ly7MssACR7E-Kb5_9O6n5HzVFqrlax2bkMWmrog&amp;oe=6ABE945B</t>
+        </is>
+      </c>
+      <c r="O270" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P270" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q270" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R270" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R266"/>
+  <autoFilter ref="A1:R270"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -26413,6 +26794,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L265" r:id="rId513"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K266" r:id="rId514"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L266" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K267" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L267" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K268" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L268" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K269" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L269" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K270" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L270" r:id="rId523"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -25898,7 +25898,7 @@
     <row r="267" ht="45" customHeight="1">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>c90966ef561a66c5f8a3</t>
+          <t>b521fb340546063ed67b</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
@@ -25911,7 +25911,7 @@
           <t>2026-09-30T03:18:35+00:00</t>
         </is>
       </c>
-      <c r="D267" s="3" t="inlineStr"/>
+      <c r="D267" s="3" t="n"/>
       <c r="E267" s="3" t="inlineStr">
         <is>
           <t>al 2 NEW GRAD PM!</t>
@@ -25927,13 +25927,13 @@
           <t>Product Management</t>
         </is>
       </c>
-      <c r="H267" s="3" t="inlineStr"/>
+      <c r="H267" s="3" t="n"/>
       <c r="I267" s="3" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="J267" s="3" t="inlineStr"/>
+      <c r="J267" s="3" t="n"/>
       <c r="K267" s="4" t="inlineStr">
         <is>
           <t>https://www.demystifyd.com/jobs/product-manager-—-new-graduate</t>
@@ -25986,12 +25986,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R267" s="3" t="inlineStr"/>
+      <c r="R267" s="3" t="n"/>
     </row>
     <row r="268" ht="45" customHeight="1">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>4796a062511603898286</t>
+          <t>f7c5c5ee5a6f25237da6</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -26019,14 +26019,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G268" s="3" t="inlineStr"/>
+      <c r="G268" s="3" t="n"/>
       <c r="H268" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="I268" s="3" t="inlineStr"/>
-      <c r="J268" s="3" t="inlineStr"/>
+      <c r="I268" s="3" t="n"/>
+      <c r="J268" s="3" t="n"/>
       <c r="K268" s="4" t="inlineStr">
         <is>
           <t>https://www.amazon.jobs/en/jobs/10564599/2027-applied-science-internship-united-states-undergrad-student-science-recruiting-frontier-ai-robotics?jr_id=6abc6f9f2668e0eab35c23d1</t>
@@ -26087,12 +26087,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R268" s="3" t="inlineStr"/>
+      <c r="R268" s="3" t="n"/>
     </row>
     <row r="269" ht="45" customHeight="1">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>ec6bca3e3a07b296df19</t>
+          <t>2f8671fa446b29fd1834</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
@@ -26130,8 +26130,8 @@
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I269" s="3" t="inlineStr"/>
-      <c r="J269" s="3" t="inlineStr"/>
+      <c r="I269" s="3" t="n"/>
+      <c r="J269" s="3" t="n"/>
       <c r="K269" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/amca/jobs/4425120009</t>
@@ -26174,12 +26174,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R269" s="3" t="inlineStr"/>
+      <c r="R269" s="3" t="n"/>
     </row>
     <row r="270" ht="45" customHeight="1">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>140429e8f45ce994e92b</t>
+          <t>f296ef94a6ff81dacf8d</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
@@ -26192,7 +26192,7 @@
           <t>2026-09-30T04:22:44+00:00</t>
         </is>
       </c>
-      <c r="D270" s="3" t="inlineStr"/>
+      <c r="D270" s="3" t="n"/>
       <c r="E270" s="3" t="inlineStr">
         <is>
           <t>Data Science</t>
@@ -26213,8 +26213,8 @@
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I270" s="3" t="inlineStr"/>
-      <c r="J270" s="3" t="inlineStr"/>
+      <c r="I270" s="3" t="n"/>
+      <c r="J270" s="3" t="n"/>
       <c r="K270" s="4" t="inlineStr">
         <is>
           <t>https://mycareer.verizon.com/jobs/r-1101384/verizon-network-and-technology-data-science-summer-2027-internship</t>
@@ -26274,7 +26274,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R270" s="3" t="inlineStr"/>
+      <c r="R270" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:R270"/>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$270</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$280</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R270"/>
+  <dimension ref="A1:R280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26276,8 +26276,970 @@
       </c>
       <c r="R270" s="3" t="n"/>
     </row>
+    <row r="271" ht="45" customHeight="1">
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t>643ffde6cfeaa6121e34</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T19:27:14.522122+00:00</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T14:56:16+00:00</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="E271" s="3" t="inlineStr">
+        <is>
+          <t>Intuit — Internship</t>
+        </is>
+      </c>
+      <c r="F271" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G271" s="3" t="inlineStr"/>
+      <c r="H271" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I271" s="3" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="J271" s="3" t="inlineStr"/>
+      <c r="K271" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.intuit.com/job/-/-/27595/101313096144?cid=pjob_li_click_us_finance-fy27_cn_text_job_int-tm&amp;p_sid=fkSHJWb&amp;p_uid=1wdOF3YCer&amp;ss=paid</t>
+        </is>
+      </c>
+      <c r="L271" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M271" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N271" s="3" t="inlineStr">
+        <is>
+          <t>@ jobs.intuit.com C:
+Instagram 2
+intuit Careers
+Job Search v
+Summer 2027: Intelligent Automation
+Business Systems Analyst Intern
+Category: Finance, Internship
+Location: Mountain View, California
+Job ID: 24177
+Company Overview
+@ JOBS.INTUIT.COM
+people and commu we serve. With tens
+of millions of cust Idwide using
+products such as Tu ¥ Credit Karma,
+QuickBooks, and Mailchimp, we believe that
+everyone should have the opportunity to
+prosper. We never stop working to find new,
+innovative ways to make thatpe
+&amp;- Give Feedback
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/830999574_1776393827822955_128876854519723799_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5NzY3NjM1MDg1Mjc1MzY4Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=zikW3bpSIP8Q7kNvwFSLD8y&amp;_nc_oc=AdqiWsdCdKfYFLixpDPOWx832NahxJtT2JIOIeNHB2StWZxt9cRG0VRkn8Tu49dY0zQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=y2xDRYA51EwAn5EstlETNQ&amp;_nc_ss=7e3ba&amp;oh=00_AQP4gPqkt6Bk2p5mgg8QKhBOwd6-S5FhBLzyB86Y5PXx2w&amp;oe=6AC33F29
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=-f_j7BYj1KsQ7kNvwEaRPjJ&amp;_nc_oc=Adra88a0m78xJex2NLfKeSv1AqGWpSPUv3mGRLZCR3kGQgebvkU4RQ3jTzrws2-GdvM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQOYEejt81WsJtzdppWPTQanBJxM5YHOhP0mVFPhQidD4A&amp;oe=6AC32399
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.intuit.com%2Fjob%2F-%2F-%2F27595%2F101313096144%3Fcid%3Dpjob_li_click_us_finance-fy27_cn_text_job_int-tm%26p_sid%3DfkSHJWb%26p_uid%3D1wdOF3YCer%26ss%3Dpaid%26utm_content%3Dpj_board%26utm_medium%3Djobad%26utm_source%3Dzero2sudo%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafPSdA-gdLhSP-Ghz4q_LlHPwg9i8RQgxXIPlApNhtQj_xTyAtOh3ixJq1Sng_aem_o2MVslvNIEC3BVMgbetwuw&amp;e=AUCIzXu-J4fXmf-pgJ-LK1sG6PJ8s9ndCBGoxuTTQATSR-xYkc1WgvlrpDugAx8_sX0ZVQk_iWu8QMRtyWS2l8Qsm-Wlb-qJnEwc-l6GcQ
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQOMMve511X0jZ4mubjk5BBqZ5SgRjdz0D_cjPR6cgHrckr0cE0lwuk5fRmLNp9ESo5KbpvDhA3Tj6Q1D2WQVmt9C2kgWqLwbveuFXM.mp4?_nc_cat=110&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=vUC7SwKxmooQ7kNvwHbcsLK&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkxMzQyMTQ2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=9820d13b5f7c673&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0U3NjNCMzJBODVGNTQ2NkM4NDcxMzY1RkZDRjc4OTRFX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkpsiymP6hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=y2xDRYA51EwAn5EstlETNQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQMpkXGn_9P5EK3yHxVffy8KGgAzcF4QUwzA43zZwEeRjQ&amp;oe=6ABF5C8B</t>
+        </is>
+      </c>
+      <c r="O271" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P271" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q271" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R271" s="3" t="inlineStr"/>
+    </row>
+    <row r="272" ht="45" customHeight="1">
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t>c28ea01caaa1ba148d09</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T19:27:15.832790+00:00</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T14:57:00+00:00</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>Firstcitizens</t>
+        </is>
+      </c>
+      <c r="E272" s="3" t="inlineStr">
+        <is>
+          <t>Firstcitizens — Internship</t>
+        </is>
+      </c>
+      <c r="F272" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G272" s="3" t="inlineStr"/>
+      <c r="H272" s="3" t="inlineStr">
+        <is>
+          <t>2027, 2026</t>
+        </is>
+      </c>
+      <c r="I272" s="3" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="J272" s="3" t="inlineStr"/>
+      <c r="K272" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.firstcitizens.com/jobs/35706?lang=en-us&amp;iis=Social+Media%2FJob+Boards&amp;iisn=zero2sudo</t>
+        </is>
+      </c>
+      <c r="L272" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M272" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N272" s="3" t="inlineStr">
+        <is>
+          <t>@ jobs.firstcitizens.com C:
+Instagram &lt;
+FZ First Citizens Bank
+= Back
+2027 Summer Intern - Global
+Banking &amp; Market Solutions (San
+Francisco, CA)
+Req ID: 35706
+Address: 255 Battery St
+Location(s): San Francisco, California
+Category: FX Sales
+Work Hours: Monday - Friday
+Posted Date: 09/29/2026
+@ JOBS.FIRSTCITIZENS.COM
+Login or r
+https://scontent-lax7-1.cdninstagram.com/v/t51.71878-15/832706003_2187117765547426_3408883978375096907_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5NzY3NjcyMDY3NDA2MDcxOA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=qL3Rc5cyHswQ7kNvwGyx_OE&amp;_nc_oc=AdpXa-eYhGMHINFrcmIVNa9VLcHt6SHU_qmlYTTId-vReRNTlB42-q8bEUv0Y3eSNoc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_gid=y2xDRYA51EwAn5EstlETNQ&amp;_nc_ss=7e3ba&amp;oh=00_AQNDwTipScShfk6nv2ABrqVJ1aEqBjRowB0Xk9oEGRYvlg&amp;oe=6AC31B60
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=-f_j7BYj1KsQ7kNvwEaRPjJ&amp;_nc_oc=Adra88a0m78xJex2NLfKeSv1AqGWpSPUv3mGRLZCR3kGQgebvkU4RQ3jTzrws2-GdvM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQOYEejt81WsJtzdppWPTQanBJxM5YHOhP0mVFPhQidD4A&amp;oe=6AC32399
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.firstcitizens.com%2Fjobs%2F35706%3Flang%3Den-us%26iis%3DSocial%2BMedia%252FJob%2BBoards%26iisn%3Dzero2sudo%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaenU-yq7BzndFaQZNavR78r_294th4r0p33T2N6aZNObw6oBMjrA3VAd2Gzmg_aem_FMIRP-BtdhOc_18VYwEndA&amp;e=AUA9Bkan8hnXGV7pOHQdRRHmIHBg1V3s0f88VOqGOFHV4ZuLPQBsxRvpRZTnoGGK0Nl0HkfTz4X124ox8hZOwhKfjdwwt3WML6pcLzr_3w
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQMBu3JJlXPswV5fpiZUFWwPTn3yco8bM6SFjf6Slmuo2JImkv_vZkG5-HATOKbP2LDrn1mh8PHYGgnAGcuglOJtkjs9gKML0fHVc3s.mp4?_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=F-k_bVA-LBsQ7kNvwGQPgr8&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkxMzQzNjQ2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=e2a63dc74435ec2c&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzBBNjU1NjZCRUFGQTQ0RDlCMzkwRkMwMTc0MzJFNDRBX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk7M7Bmf6hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=y2xDRYA51EwAn5EstlETNQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQMEioanCiVUO7i8a7UAymnElL41F7ztOR8o-dpFrnyUiQ&amp;oe=6ABF3C49</t>
+        </is>
+      </c>
+      <c r="O272" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P272" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q272" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R272" s="3" t="inlineStr"/>
+    </row>
+    <row r="273" ht="45" customHeight="1">
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>62c25d6dd3b171c59bad</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T19:27:18.326071+00:00</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T14:58:34+00:00</t>
+        </is>
+      </c>
+      <c r="D273" s="3" t="inlineStr">
+        <is>
+          <t>Amca</t>
+        </is>
+      </c>
+      <c r="E273" s="3" t="inlineStr">
+        <is>
+          <t>Amca — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F273" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G273" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H273" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I273" s="3" t="inlineStr"/>
+      <c r="J273" s="3" t="inlineStr"/>
+      <c r="K273" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/amca/jobs/4425120009</t>
+        </is>
+      </c>
+      <c r="L273" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M273" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N273" s="3" t="inlineStr">
+        <is>
+          <t>&lt; Back to jobs
+Software Engineering
+Internship [Summer
+2027]
+© El Segundo, CA
+(2 JOB-BOARDS.GREENHOUSE.IO
+Amca is building A ew industrial
+base. Since the 1990s} bility to build new
+aviation and military systems and maintain
+the ones we already have has eroded. Today,
+the gap between what the nation needs to
+produce and what it is capable of producing is
+the largest it has been in generations.
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/830342574_1671180551233780_7620678743337664151_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk5NzY3NzUwMDUyODIyOTE3Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=F-ea-uwty3EQ7kNvwEIFeUN&amp;_nc_oc=AdrkPKVP9nE3tfGDRPQEA1TP5Dd_SxwWOzAxgF3XE4UjLFzh0e7WQI-R94H5tT-Ns6w&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=y2xDRYA51EwAn5EstlETNQ&amp;_nc_ss=7e3ba&amp;oh=00_AQNJoYlKvmDCj2wO3I3iXqKVlgPKWQs0eSfL1YmrBELTsA&amp;oe=6AC32122
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=-f_j7BYj1KsQ7kNvwEaRPjJ&amp;_nc_oc=Adra88a0m78xJex2NLfKeSv1AqGWpSPUv3mGRLZCR3kGQgebvkU4RQ3jTzrws2-GdvM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQOYEejt81WsJtzdppWPTQanBJxM5YHOhP0mVFPhQidD4A&amp;oe=6AC32399
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Famca%2Fjobs%2F4425120009%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafV_QijRas-e2d9rLVOPlz7wBi4J93CJliyEEf_cyA308xiWwWL_kRMb4qOyA_aem_xHpzkweUe7NdBODReiKVjg&amp;e=AUAZwVsT_e1bl7YVttSkB-QXK95FqQFp8z1DcWrdN8Y9-PIT6G785p0UUhnYuT7eYuhmKNxCiJYbLRMMvLulvICtKIGe_cWBbPbWz01-_w
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQO9Ow5CDQMdByRblVDnbnuh0Bcy2ch6tzP624lWyap7SRdomARruY5VJ5l2Lm5CSvqUgKS5MZaeLtkFeVmDHkSESH5MWuqdE5x46y4.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=lm6B2l7qno0Q7kNvwEG-7E6&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkxMzQ5Nzk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=427854343ed0ee55&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzMxRTlFODU0NkY3NzQ2RkI4NDE5RTFEQ0IwN0ZDQjkyX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbki5CMnv6hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=y2xDRYA51EwAn5EstlETNQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQM8pnxgxhrqP4uXKdRSEu36KMVQzmqjAh6ufLcbJ_20QA&amp;oe=6ABF318A</t>
+        </is>
+      </c>
+      <c r="O273" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P273" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q273" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R273" s="3" t="inlineStr"/>
+    </row>
+    <row r="274" ht="45" customHeight="1">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>e5f54c9d4dd71dbfaeb2</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T19:27:20.914948+00:00</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T15:12:32+00:00</t>
+        </is>
+      </c>
+      <c r="D274" s="3" t="inlineStr">
+        <is>
+          <t>ICF</t>
+        </is>
+      </c>
+      <c r="E274" s="3" t="inlineStr">
+        <is>
+          <t>ICF — Internship</t>
+        </is>
+      </c>
+      <c r="F274" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G274" s="3" t="inlineStr"/>
+      <c r="H274" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I274" s="3" t="inlineStr"/>
+      <c r="J274" s="3" t="inlineStr"/>
+      <c r="K274" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.icf.com/us/en/job/IIIIIIUSR2603312EXTERNALENUS/2027-Summer-Intern-AI-Engineer-Reston-VA</t>
+        </is>
+      </c>
+      <c r="L274" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M274" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N274" s="3" t="inlineStr">
+        <is>
+          <t>@ careers.icf.com
+instagram
+2027 Summer Intern, Al
+Engineer (Reston, VA)
+Reston, Virginia, United States of
+America °° Internship
+R2603312 [4 Part time
+SAVE JOB
+@ CAREERS.ICF.COM
+Description
+As an Al Engineer Intern, you will join our
+innovative Al research and development
+https://scontent-lax7-1.cdninstagram.com/v/t51.71878-15/825350314_4475063749373504_601165742026544801_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5NzY4NDUzODIzNTAwNzUwMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=aObA1pBRoG4Q7kNvwFY4JId&amp;_nc_oc=AdpykZ3TwqFwQisFasN0PxbF2p9W2LJVvM2rmLXA3r1y3J4p2cjKEWgrQQO7hfwZOzA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_gid=y2xDRYA51EwAn5EstlETNQ&amp;_nc_ss=7e3ba&amp;oh=00_AQMxHtJ1JCDa_Kypkkkqjd87gncei43PLTbRR9VqMCUH4Q&amp;oe=6AC34063
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=-f_j7BYj1KsQ7kNvwEaRPjJ&amp;_nc_oc=Adra88a0m78xJex2NLfKeSv1AqGWpSPUv3mGRLZCR3kGQgebvkU4RQ3jTzrws2-GdvM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQOYEejt81WsJtzdppWPTQanBJxM5YHOhP0mVFPhQidD4A&amp;oe=6AC32399
+https://l.instagram.com/?u=https%3A%2F%2Fcareers.icf.com%2Fus%2Fen%2Fjob%2FIIIIIIUSR2603312EXTERNALENUS%2F2027-Summer-Intern-AI-Engineer-Reston-VA%3Futm_source%3Dzero2sudo%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeLJ70iAzIndnmEwBxNK2i1YsPQoGzLmuViXucuj0Vd4dEWPFQjfd4xzT8KZQ_aem_IhaIN5oLmCNRUpwfykBb3g&amp;e=AUCqP3HQWdGLtOAA_S1zzz-3VBy9geJ2s3_AEn88zw7G5_KC9veWiu0Mpy3x0EflrJF920Q_REaI8n7mtBfewUTevwByK6VFKtRlHfn3EA
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQP7MypllEblJP_EUAjrAQ-Hdi8EpGubokW85tFaDlr7cXw-fdGWByPrklufpIR_vIbp90NCrkChayN4rwISwR_AzKMzPX2PCBp_Dio.mp4?_nc_cat=110&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=aTmvkWwdadkQ7kNvwGq-Zwq&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkxMzYzNjU2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=9ddb34d056664b24&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzZBMERFQzFCNjc5OTQ2MkY4Njk3RUM1RDM5MkU2QzcxX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkxfW1qP6hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=y2xDRYA51EwAn5EstlETNQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQOSnDn2SlLBrXbkjgcYsKRB4G0rFUg0SUjfaOZyXJUT-A&amp;oe=6ABF403B</t>
+        </is>
+      </c>
+      <c r="O274" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P274" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q274" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R274" s="3" t="inlineStr"/>
+    </row>
+    <row r="275" ht="45" customHeight="1">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t>b71a17fc83cbfae6312f</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T19:27:22.145785+00:00</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T15:20:29+00:00</t>
+        </is>
+      </c>
+      <c r="D275" s="3" t="inlineStr"/>
+      <c r="E275" s="3" t="inlineStr">
+        <is>
+          <t>epic games product intern</t>
+        </is>
+      </c>
+      <c r="F275" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G275" s="3" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="H275" s="3" t="inlineStr"/>
+      <c r="I275" s="3" t="inlineStr"/>
+      <c r="J275" s="3" t="inlineStr"/>
+      <c r="K275" s="4" t="inlineStr">
+        <is>
+          <t>https://www.epicgames.com/site/careers/jobs/6161289004</t>
+        </is>
+      </c>
+      <c r="L275" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M275" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N275" s="3" t="inlineStr">
+        <is>
+          <t>x @ epicgames.com C:
+Instagram
+i A
+PRODUCT MANAGEMENT
+Product Management
+Intern (R27422)
+epic games product intern
+Product Nv, «nent
+Location
+Cary, United States
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/831474587_1410416793856051_1268241322292813_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5NzY4ODU0NjA2OTAyNjE5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=gkFY-b0a9DsQ7kNvwFp47Nx&amp;_nc_oc=Adq4NKXa3NTjJW2WfZQX2EMI1cDipZz-X_U6s1-9PwXGk1UYSSco0Glu9Oiji-uvBBo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=y2xDRYA51EwAn5EstlETNQ&amp;_nc_ss=7e3ba&amp;oh=00_AQPQxr8VsF4RwmXUTtoRiGm8UAmPAm6MgwD4H_7WZxqwpg&amp;oe=6AC34702
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=-f_j7BYj1KsQ7kNvwEaRPjJ&amp;_nc_oc=Adra88a0m78xJex2NLfKeSv1AqGWpSPUv3mGRLZCR3kGQgebvkU4RQ3jTzrws2-GdvM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQOYEejt81WsJtzdppWPTQanBJxM5YHOhP0mVFPhQidD4A&amp;oe=6AC32399
+https://l.instagram.com/?u=https%3A%2F%2Fwww.epicgames.com%2Fsite%2Fcareers%2Fjobs%2F6161289004%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadd_ZYRRdAkd4nb4wKqDtVdAXPsJBdyx4cU5Mmr5S6-WGJVspdYktGf2jMTQw_aem_ne7qI9Itd4UcOiTPnTNU8w&amp;e=AUAyRX3l1PYhZUtQjxuqhTesHobbtbLKEIT5ExaP49sTmnl-r6nbOmxeYF7hYRS2_q2IGXvrpfbE7BcFwqz01dPdfi2t6u8Q_si2lwKNzg
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQMpUiSrgU1fDLAFhEijnz_71II1pY9TsYDKRWBRqHlYBGlFAZXBpe8KbY3FTfQrj9QZ6ISk7Biz0tUqxdrIV_s7BEXDnzM4L4c31Os.mp4?_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=SlQ4dCQvAdcQ7kNvwEpxFFj&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkxMzczNjE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=a7a8a8280e8c02cc&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzdCRTlCRjdEMDk0MzRDRDg5Njc1RDgxNUU0RjYxOTBGX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkyePrr_6hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=y2xDRYA51EwAn5EstlETNQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQOklSEtdTlLKcbg857vvR7m3NxOMGRDdTUyJFd4-7r78A&amp;oe=6ABF3E91</t>
+        </is>
+      </c>
+      <c r="O275" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P275" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q275" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R275" s="3" t="inlineStr"/>
+    </row>
+    <row r="276" ht="45" customHeight="1">
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t>02b1ae6aa3a124a966af</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T19:27:27.818961+00:00</t>
+        </is>
+      </c>
+      <c r="C276" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T17:09:19+00:00</t>
+        </is>
+      </c>
+      <c r="D276" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E276" s="3" t="inlineStr">
+        <is>
+          <t>Amazon — Software Engineering, Machine Learning / AI</t>
+        </is>
+      </c>
+      <c r="F276" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G276" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering, Machine Learning / AI</t>
+        </is>
+      </c>
+      <c r="H276" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I276" s="3" t="inlineStr"/>
+      <c r="J276" s="3" t="inlineStr"/>
+      <c r="K276" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.jobs/en/jobs/10565667/software-development-engineer-intern-aws-database-2027-us</t>
+        </is>
+      </c>
+      <c r="L276" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M276" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N276" s="3" t="inlineStr">
+        <is>
+          <t>Software Developm... &lt;
+amazon.jobs
+Vv
+= amazonjobs Q
+Software Development
+Engineer Intern, AWS
+Database - 2027 (US)
+Job ID: 10565667 | Amazon.com Services LLC
+Apply now
+AWS Database SWE Intern 2027
+re:  AMAZON.JOBS
+At Amazon, our tech.j tool, it's your
+playground. Our en on scalable
+systems, cloud service tomer-facing
+products that operate at global scale. This is an
+environment where you learn by building.
+Whether you're creating cloud-native solutions,
+optimizing machine learning models, or building
+products that drive experiences for millions of
+customers around the globe, your work reaches
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/825323679_1903748723670530_3998481007311736052_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk5Nzc0MzMxNzk5MTk4MjkwNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=faRNQBtEjp4Q7kNvwGHVODi&amp;_nc_oc=AdpDKmpu6xU34tldJXKFZO8bNu1RCSTSnzvkz46mCTRiKnk_yB55xHsKJDRDRS8aNGg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=y2xDRYA51EwAn5EstlETNQ&amp;_nc_ss=7e3ba&amp;oh=00_AQN06QrcX4QutIetxzI7yfD6Jst9V9f8oVwabSt37Udk-w&amp;oe=6AC33ED6
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=-f_j7BYj1KsQ7kNvwEaRPjJ&amp;_nc_oc=Adra88a0m78xJex2NLfKeSv1AqGWpSPUv3mGRLZCR3kGQgebvkU4RQ3jTzrws2-GdvM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQOYEejt81WsJtzdppWPTQanBJxM5YHOhP0mVFPhQidD4A&amp;oe=6AC32399
+https://l.instagram.com/?u=https%3A%2F%2Fwww.amazon.jobs%2Fen%2Fjobs%2F10565667%2Fsoftware-development-engineer-intern-aws-database-2027-us%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeb2_8U3cmiKQp_UC8c618mq2FEk81DeTtPU4D4kj0BhRf8YiU5LbbYWs8FGA_aem_NSVBepYtB06wFCAhPLbbDg&amp;e=AUDZi1RS9aD-sZVVskJz3S8l49lYT0tjMON6coVdd7AB1zka2uTVrVFH1oUn_QVeKhhvv1EoJX0zsfVWSdmT60oZTDa3D3JGnQog8XDunQ
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQOZ4x-wrcNdu71CbsWoEG5NFRYop8QjhXi7HP6jDWRrbHCZ0kxZR2xdY7E1FYNHrobH3IcTw03ZcYg3lqurWCrOJFkUNPfBCMLQWD0.mp4?_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=2bdqbjfgY_4Q7kNvwHZaIyV&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkxNTQyOTA2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=63fc2eabb1ac7ec5&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0IwMDU5QkNBOEM5MTQyNEFBOTBBQ0JGRTU0NUI0NURBX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk8sP8rf-hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=y2xDRYA51EwAn5EstlETNQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQMhJgBoxRTWBV6RWGfG06ODc7E6FKsomef3b5sh-mc67w&amp;oe=6ABF5405</t>
+        </is>
+      </c>
+      <c r="O276" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P276" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q276" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R276" s="3" t="inlineStr"/>
+    </row>
+    <row r="277" ht="45" customHeight="1">
+      <c r="A277" s="3" t="inlineStr">
+        <is>
+          <t>598558ff4c9066393ea4</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T19:27:37.598157+00:00</t>
+        </is>
+      </c>
+      <c r="C277" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T18:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="D277" s="3" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E277" s="3" t="inlineStr">
+        <is>
+          <t>Meta — Internship</t>
+        </is>
+      </c>
+      <c r="F277" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G277" s="3" t="inlineStr"/>
+      <c r="H277" s="3" t="inlineStr"/>
+      <c r="I277" s="3" t="inlineStr">
+        <is>
+          <t>Sunnyvale</t>
+        </is>
+      </c>
+      <c r="J277" s="3" t="inlineStr"/>
+      <c r="K277" s="4" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/profile/job_details/1683903403071591</t>
+        </is>
+      </c>
+      <c r="L277" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M277" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N277" s="3" t="inlineStr">
+        <is>
+          <t>@ metacareers.com C:
+Instagram
+= MMeta
+Do
+&lt;€ Back to Jobs al
+DFX Engineering Intern
+Sunnyvale, CA +1 location
+Engineering +3more
+Apply now
+Meta is at the forefront of developing
+innovative hardware that redefines how
+people experience the world — from virtual
+to augmented reality. The Design For
+Excellence (DFX) team is a critical pillar of
+this mission, ensuring our cutting-edge
+Meta manulapturing engineering Intern
+2% METACAREERS.COM
+scoped manufactuy ering project
+with direct mentors DFX er waa, %
+You'll get hands-on ex etohow “%*
+product moves from design intent to
+nroduction realitv — workina alonaside
+https://scontent-lax3-1.cdninstagram.com/v/t51.71878-15/830068124_4424141477914367_6505662530309979960_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk5Nzc4Mzk0MzA1NDk1NjI0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=9mRin6osOpAQ7kNvwGLMI2D&amp;_nc_oc=AdpnJEr2A8AyAeVbPSRfgf8rs45rA-vc88HiHQvcb-1_8pAlaWiuwjQ6Y4csXiaN38c&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_gid=y2xDRYA51EwAn5EstlETNQ&amp;_nc_ss=7e3ba&amp;oh=00_AQOsAwLUKxS0IvkgAe5zgSuKCoFJ73gg72tIuK39maZLsw&amp;oe=6AC32246
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=-f_j7BYj1KsQ7kNvwEaRPjJ&amp;_nc_oc=Adra88a0m78xJex2NLfKeSv1AqGWpSPUv3mGRLZCR3kGQgebvkU4RQ3jTzrws2-GdvM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQOYEejt81WsJtzdppWPTQanBJxM5YHOhP0mVFPhQidD4A&amp;oe=6AC32399
+https://l.instagram.com/?u=https%3A%2F%2Fwww.metacareers.com%2Fprofile%2Fjob_details%2F1683903403071591%2F%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAacfZw5y9jO5o4eC_Nv6ucVAc0eI1A7EJngMUNqp28fZA1pPgRKE2_B3CCz6Qg_aem_neyodBVy8N6IDXcq9VPczg&amp;e=AUD66248jX41Cxc4v1-Vp8YOvKvee597jLr-aFTYL1SmMF-ZIiecyya-feZ3-RM4qRAqbj0tHRyZv6yvwwZzgUEEm5vsLaqHPWLLugHwjA
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQOm5DpErUQTVkYsxkZZpACeBxd6zum99RkTTnn4TNZM1EyRjTz3YdJNJdRMsUeNXweGomQNphk9xLPlGRZRrFZ0UCIKbBHBHgtuFo8.mp4?_nc_cat=104&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=y3GGU5abxMwQ7kNvwFRA-9I&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkxNjM0MTk2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=91540434f57f9f2e&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzQwRTE3QjQzQzhFNzRGMjI4MjA5RUMwMDY4MkE0ODI2X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk48_-8f-hQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=y2xDRYA51EwAn5EstlETNQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQN_Ty1pK9iZbIcmyAWPFqFZUlSK1OI8U4F8ELxFjQrqPA&amp;oe=6ABF41C1</t>
+        </is>
+      </c>
+      <c r="O277" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P277" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q277" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R277" s="3" t="inlineStr"/>
+    </row>
+    <row r="278" ht="45" customHeight="1">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>2ee1e3f1bedcf99d166d</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T19:27:40.065437+00:00</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T18:53:49+00:00</t>
+        </is>
+      </c>
+      <c r="D278" s="3" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="E278" s="3" t="inlineStr">
+        <is>
+          <t>Apple — Internship</t>
+        </is>
+      </c>
+      <c r="F278" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G278" s="3" t="inlineStr"/>
+      <c r="H278" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I278" s="3" t="inlineStr"/>
+      <c r="J278" s="3" t="inlineStr"/>
+      <c r="K278" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.apple.com/en-us/details/200673612-0836/applied-data-solutions-program-internships-summer-2027?team=CORSV</t>
+        </is>
+      </c>
+      <c r="L278" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M278" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N278" s="3" t="inlineStr">
+        <is>
+          <t>4
+Join Apple.
+Applied Data Solutions Program,
+Internships - Summer 2027 -
+Jobs - Careers at Apple
+Apply for a Applied Data Solutions
+Program, Internships - Summer 2027
+job at Apple. Read about the role and
+find out if it’s right for you.
+Apple applied data solutions intern!
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/829339961_1096110986245143_1138230444254793670_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk5Nzc5NTkyMjk4NTQzMjY5MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=LSZhDLCupxwQ7kNvwFBOZNZ&amp;_nc_oc=Adq5ZKF28RN24a9bdxd6LGTICmruic3MWJWfrfdiEFhPRox_P3MxfVPnhsJ4ocjQFHY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=y2xDRYA51EwAn5EstlETNQ&amp;_nc_ss=7e3ba&amp;oh=00_AQMlRjwT8yFNUg4YSHnT9RSMKuAzHnz6NQvAgjQM2iarzQ&amp;oe=6AC3272E
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=-f_j7BYj1KsQ7kNvwEaRPjJ&amp;_nc_oc=Adra88a0m78xJex2NLfKeSv1AqGWpSPUv3mGRLZCR3kGQgebvkU4RQ3jTzrws2-GdvM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQOYEejt81WsJtzdppWPTQanBJxM5YHOhP0mVFPhQidD4A&amp;oe=6AC32399
+https://l.instagram.com/?u=https%3A%2F%2Fjobs.apple.com%2Fen-us%2Fdetails%2F200673612-0836%2Fapplied-data-solutions-program-internships-summer-2027%3Fteam%3DCORSV&amp;e=AUB6k_1_H7jItZhWkmBP-5_p94KMVm59VYIsrLQRHg9sgRj9_GLC4cCu63uj8y_beUcWxlstkPgjHCyXZxxxbcsbEPq7ifb3o0GO3XTbDg
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQPQ3oRdt-Z-Z8ErVdpD12-wVmt3O4JrTv-QQUMctt8cbnOnQqEdfMH12X7bNDDK6uHCqpNSLEYsf3OY1ePADMubN_kp-HAbVaviCZ8.mp4?_nc_cat=102&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=c458muGBXwEQ7kNvwFud32M&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkxNjYyMjc2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=369036cd81b50158&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0U1Mzg5OUZCN0MwMzQ5NzVBNDZCMEY4RENEOUE5MzJEX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkm8X0hoCiQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=y2xDRYA51EwAn5EstlETNQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQNyZTjuVn-k9MCu8ZIoJ3qqLQ_O4nhmb4ZC6J5RfBnmpg&amp;oe=6ABF5383</t>
+        </is>
+      </c>
+      <c r="O278" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P278" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q278" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R278" s="3" t="inlineStr"/>
+    </row>
+    <row r="279" ht="45" customHeight="1">
+      <c r="A279" s="3" t="inlineStr">
+        <is>
+          <t>5ca34312829eeb0dde98</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T19:27:41.846946+00:00</t>
+        </is>
+      </c>
+      <c r="C279" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T18:57:41+00:00</t>
+        </is>
+      </c>
+      <c r="D279" s="3" t="inlineStr"/>
+      <c r="E279" s="3" t="inlineStr">
+        <is>
+          <t>Intern - Winter '27</t>
+        </is>
+      </c>
+      <c r="F279" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G279" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H279" s="3" t="inlineStr"/>
+      <c r="I279" s="3" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="J279" s="3" t="inlineStr"/>
+      <c r="K279" s="4" t="inlineStr">
+        <is>
+          <t>https://vercel.com/careers/software-engineering-intern-winter-27-6181755004</t>
+        </is>
+      </c>
+      <c r="L279" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M279" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N279" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering
+Intern - Winter '27
+Careers / Engineering
+&amp;. Engineering
+@ San Francisco
+© Full Time
+About Vercel:
+Vercel is the agentic infrastructure
+company, freeing people and agents to
+ship what's next. For more than a decade
+Now we're scaling lucts for both
+agents and people
+software, built in the open and trusted by
+and run
+OnenAl PavPal. Ramn. Stinreme. and
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/825351979_1109114928340574_1290565017218151177_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk5Nzc5Nzg2NDk0ODE4ODc2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=03UrseaByUAQ7kNvwF5ddFB&amp;_nc_oc=AdpSimSZR3EZeAwX0d4Rdmx4Q5M5jC-dAwpj8LXC-DpqhVdxrwi3qpvE6ZnnjZ-DIzY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=y2xDRYA51EwAn5EstlETNQ&amp;_nc_ss=7e3ba&amp;oh=00_AQOW5iyHE0FHi5nee4pEvXoMLdmiCONHShNGKHL_JGhoyA&amp;oe=6AC34304
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=-f_j7BYj1KsQ7kNvwEaRPjJ&amp;_nc_oc=Adra88a0m78xJex2NLfKeSv1AqGWpSPUv3mGRLZCR3kGQgebvkU4RQ3jTzrws2-GdvM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQOYEejt81WsJtzdppWPTQanBJxM5YHOhP0mVFPhQidD4A&amp;oe=6AC32399
+https://l.instagram.com/?u=https%3A%2F%2Fvercel.com%2Fcareers%2Fsoftware-engineering-intern-winter-27-6181755004%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaessW8Vo1fNAtHDPOAjrVy2NXLbOyMwEQWPtR94KhPxb6lqW41wdRNs6F5KOg_aem_FLCDcFS0fQ0vJdchMgWFQQ&amp;e=AUDKxEh9JHedYvsZnFOoVCnEcch423uvP97mlHV0ndaj0b3lwljjct8HSRw_rJnv5opJcTKWM2FY3Wz6KngpgtGA4h4ERmE_1--Bk4FNuw
+https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m78/AQMWbmebnrnQx0gzAdUMUE1g2e8e-WkEfrU46Yl2BPo8akICzNBhU1VFyTceQH-94JSL8ouVLVhBXlHMjvSuTkgga91ZJdU40nAdg5E.mp4?_nc_cat=104&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=jSfDaD9K0ZkQ7kNvwFTsa2c&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkxNjY3NjE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=a4889a233acef6cf&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0Q3MDE4QUI1NDNCQTQ3NDk4Qjk2REY2OTA0QzFDOEI5X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk4ebxioCiQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=y2xDRYA51EwAn5EstlETNQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQPKUKqIJGgZPi-Vb5whoiDkmX14jOIuTYnAgSixGS6owQ&amp;oe=6ABF4411</t>
+        </is>
+      </c>
+      <c r="O279" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P279" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q279" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R279" s="3" t="inlineStr"/>
+    </row>
+    <row r="280" ht="45" customHeight="1">
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t>9c1b49a6c300439b05ff</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T19:27:43.417906+00:00</t>
+        </is>
+      </c>
+      <c r="C280" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T19:09:12+00:00</t>
+        </is>
+      </c>
+      <c r="D280" s="3" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E280" s="3" t="inlineStr">
+        <is>
+          <t>Meta — Design</t>
+        </is>
+      </c>
+      <c r="F280" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G280" s="3" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="H280" s="3" t="inlineStr"/>
+      <c r="I280" s="3" t="inlineStr">
+        <is>
+          <t>Redmond</t>
+        </is>
+      </c>
+      <c r="J280" s="3" t="inlineStr"/>
+      <c r="K280" s="4" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/profile/job_details/1613359540444032</t>
+        </is>
+      </c>
+      <c r="L280" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M280" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N280" s="3" t="inlineStr">
+        <is>
+          <t>@ metacareers.com C+:
+Instagran
+= MMeta
+Do
+&lt; Back to Jobs q
+Product Design
+Engineering Intern
+Redmond, WA
+Engineering + 2 more
+Apply now
+As an engineering intern on the AR Product
+Design Engineering team, you will help
+design solutions for next generation
+consumer augmented reality products. You
+(7) META PRODUCT DESIGN ENGINEER INT..
+COHAVOUTALION, Gevelo ya wuiorouygtl
+understanding of t t design
+process, manufactu validation.
+Our internships are twelve (12) to sixteen
+(16) weeks long.
+https://scontent-lax3-2.cdninstagram.com/v/t51.71878-15/829459189_1448679393849496_1605564559158838034_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk5NzgwMzY3MTUwOTE4OTg0Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=pGyJNTHR2joQ7kNvwGAn_r4&amp;_nc_oc=AdpeXLF79e0jf8_2Jl2Uw5U3klSoog5JlwGunS_oKq6TsCgjY0eSD3shGUS19b6Cm0o&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_gid=y2xDRYA51EwAn5EstlETNQ&amp;_nc_ss=7e3ba&amp;oh=00_AQPaCqIjFAw8l_97OjocNhxQCzZSW5Ty8L-7ShiVAEknXg&amp;oe=6AC34569
+https://scontent-lax3-2.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=-f_j7BYj1KsQ7kNvwEaRPjJ&amp;_nc_oc=Adra88a0m78xJex2NLfKeSv1AqGWpSPUv3mGRLZCR3kGQgebvkU4RQ3jTzrws2-GdvM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQOYEejt81WsJtzdppWPTQanBJxM5YHOhP0mVFPhQidD4A&amp;oe=6AC32399
+https://l.instagram.com/?u=https%3A%2F%2Fwww.metacareers.com%2Fprofile%2Fjob_details%2F1613359540444032%2F%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaeL9wKiWG7ocisN4NufJdkBPuD4TQlxRynGsn7u-tqNvkgyppbjmHw6DmqkwA_aem_HoHZWEfusRDkHiU-iR0_wQ&amp;e=AUBCdcZrup7YXVQbO3IYFwqKpn8QmWtBg9URktm8DiwRlf044NeGG6ApSZ6hXp7R7_QW7utM6RtD69D3e49AD2Fvu1GRQ5wVK6ToW5LbOg
+https://scontent-lax3-2.cdninstagram.com/o1/v/t2/f2/m78/AQMGQ1PWE-Tdyhx4TgLdon4rFKQdkCeCkCEv6xsqV8qTaFPi0_OLEy1jW-ngOf0R3TVQQirlws58nafSJEk6WHHXqwyZvvWSfUx1Hc4.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-2.cdninstagram.com&amp;_nc_ohc=pEFIGLhd_A0Q7kNvwFnh_UB&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkxNjc4MDI2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=a40855f92285d029&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0Q4Qzc2OTM4NTg5MTQyNzE5NUVEMEM0Njg4NTQ5NEJGX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk-snSkoCiQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=y2xDRYA51EwAn5EstlETNQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQMUA3CKJt0kXztHi1VfY5_ur9UnbgN_EXoQOtVGTwvBbQ&amp;oe=6ABF4231</t>
+        </is>
+      </c>
+      <c r="O280" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P280" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q280" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R280" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R270"/>
+  <autoFilter ref="A1:R280"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -26802,6 +27764,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L269" r:id="rId521"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K270" r:id="rId522"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L270" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K271" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L271" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K272" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L272" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K273" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L273" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K274" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L274" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K275" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L275" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K276" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L276" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K277" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L277" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K278" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L278" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K279" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L279" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K280" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L280" r:id="rId543"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zero2Sudo_Opportunity_Tracker.xlsx
+++ b/Zero2Sudo_Opportunity_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$280</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$R$283</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R280"/>
+  <dimension ref="A1:R283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26279,7 +26279,7 @@
     <row r="271" ht="45" customHeight="1">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>643ffde6cfeaa6121e34</t>
+          <t>0f58ab03c9b57d903938</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
@@ -26307,7 +26307,7 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G271" s="3" t="inlineStr"/>
+      <c r="G271" s="3" t="n"/>
       <c r="H271" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
@@ -26318,7 +26318,7 @@
           <t>Mountain View</t>
         </is>
       </c>
-      <c r="J271" s="3" t="inlineStr"/>
+      <c r="J271" s="3" t="n"/>
       <c r="K271" s="4" t="inlineStr">
         <is>
           <t>https://jobs.intuit.com/job/-/-/27595/101313096144?cid=pjob_li_click_us_finance-fy27_cn_text_job_int-tm&amp;p_sid=fkSHJWb&amp;p_uid=1wdOF3YCer&amp;ss=paid</t>
@@ -26376,12 +26376,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R271" s="3" t="inlineStr"/>
+      <c r="R271" s="3" t="n"/>
     </row>
     <row r="272" ht="45" customHeight="1">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>c28ea01caaa1ba148d09</t>
+          <t>d9f2aa6e7c25be9a097f</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
@@ -26409,7 +26409,7 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G272" s="3" t="inlineStr"/>
+      <c r="G272" s="3" t="n"/>
       <c r="H272" s="3" t="inlineStr">
         <is>
           <t>2027, 2026</t>
@@ -26420,7 +26420,7 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="J272" s="3" t="inlineStr"/>
+      <c r="J272" s="3" t="n"/>
       <c r="K272" s="4" t="inlineStr">
         <is>
           <t>https://jobs.firstcitizens.com/jobs/35706?lang=en-us&amp;iis=Social+Media%2FJob+Boards&amp;iisn=zero2sudo</t>
@@ -26474,12 +26474,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R272" s="3" t="inlineStr"/>
+      <c r="R272" s="3" t="n"/>
     </row>
     <row r="273" ht="45" customHeight="1">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>62c25d6dd3b171c59bad</t>
+          <t>01954b78a1443d22ca25</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
@@ -26517,8 +26517,8 @@
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I273" s="3" t="inlineStr"/>
-      <c r="J273" s="3" t="inlineStr"/>
+      <c r="I273" s="3" t="n"/>
+      <c r="J273" s="3" t="n"/>
       <c r="K273" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/amca/jobs/4425120009</t>
@@ -26570,12 +26570,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R273" s="3" t="inlineStr"/>
+      <c r="R273" s="3" t="n"/>
     </row>
     <row r="274" ht="45" customHeight="1">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>e5f54c9d4dd71dbfaeb2</t>
+          <t>02db01f1b0f379700e77</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
@@ -26603,14 +26603,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G274" s="3" t="inlineStr"/>
+      <c r="G274" s="3" t="n"/>
       <c r="H274" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="I274" s="3" t="inlineStr"/>
-      <c r="J274" s="3" t="inlineStr"/>
+      <c r="I274" s="3" t="n"/>
+      <c r="J274" s="3" t="n"/>
       <c r="K274" s="4" t="inlineStr">
         <is>
           <t>https://careers.icf.com/us/en/job/IIIIIIUSR2603312EXTERNALENUS/2027-Summer-Intern-AI-Engineer-Reston-VA</t>
@@ -26661,12 +26661,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R274" s="3" t="inlineStr"/>
+      <c r="R274" s="3" t="n"/>
     </row>
     <row r="275" ht="45" customHeight="1">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>b71a17fc83cbfae6312f</t>
+          <t>cd21738c8cd1bd8a33b6</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
@@ -26679,7 +26679,7 @@
           <t>2026-09-30T15:20:29+00:00</t>
         </is>
       </c>
-      <c r="D275" s="3" t="inlineStr"/>
+      <c r="D275" s="3" t="n"/>
       <c r="E275" s="3" t="inlineStr">
         <is>
           <t>epic games product intern</t>
@@ -26695,9 +26695,9 @@
           <t>Product Management</t>
         </is>
       </c>
-      <c r="H275" s="3" t="inlineStr"/>
-      <c r="I275" s="3" t="inlineStr"/>
-      <c r="J275" s="3" t="inlineStr"/>
+      <c r="H275" s="3" t="n"/>
+      <c r="I275" s="3" t="n"/>
+      <c r="J275" s="3" t="n"/>
       <c r="K275" s="4" t="inlineStr">
         <is>
           <t>https://www.epicgames.com/site/careers/jobs/6161289004</t>
@@ -26746,12 +26746,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R275" s="3" t="inlineStr"/>
+      <c r="R275" s="3" t="n"/>
     </row>
     <row r="276" ht="45" customHeight="1">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>02b1ae6aa3a124a966af</t>
+          <t>e362bb9613f0300bd079</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -26789,8 +26789,8 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="I276" s="3" t="inlineStr"/>
-      <c r="J276" s="3" t="inlineStr"/>
+      <c r="I276" s="3" t="n"/>
+      <c r="J276" s="3" t="n"/>
       <c r="K276" s="4" t="inlineStr">
         <is>
           <t>https://www.amazon.jobs/en/jobs/10565667/software-development-engineer-intern-aws-database-2027-us</t>
@@ -26849,12 +26849,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R276" s="3" t="inlineStr"/>
+      <c r="R276" s="3" t="n"/>
     </row>
     <row r="277" ht="45" customHeight="1">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>598558ff4c9066393ea4</t>
+          <t>ad0b270e53f888b036c2</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
@@ -26882,14 +26882,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G277" s="3" t="inlineStr"/>
-      <c r="H277" s="3" t="inlineStr"/>
+      <c r="G277" s="3" t="n"/>
+      <c r="H277" s="3" t="n"/>
       <c r="I277" s="3" t="inlineStr">
         <is>
           <t>Sunnyvale</t>
         </is>
       </c>
-      <c r="J277" s="3" t="inlineStr"/>
+      <c r="J277" s="3" t="n"/>
       <c r="K277" s="4" t="inlineStr">
         <is>
           <t>https://www.metacareers.com/profile/job_details/1683903403071591</t>
@@ -26950,12 +26950,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R277" s="3" t="inlineStr"/>
+      <c r="R277" s="3" t="n"/>
     </row>
     <row r="278" ht="45" customHeight="1">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>2ee1e3f1bedcf99d166d</t>
+          <t>0c702e7aa2e0eee0166c</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -26983,14 +26983,14 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="G278" s="3" t="inlineStr"/>
+      <c r="G278" s="3" t="n"/>
       <c r="H278" s="3" t="inlineStr">
         <is>
           <t>Summer 2027</t>
         </is>
       </c>
-      <c r="I278" s="3" t="inlineStr"/>
-      <c r="J278" s="3" t="inlineStr"/>
+      <c r="I278" s="3" t="n"/>
+      <c r="J278" s="3" t="n"/>
       <c r="K278" s="4" t="inlineStr">
         <is>
           <t>https://jobs.apple.com/en-us/details/200673612-0836/applied-data-solutions-program-internships-summer-2027?team=CORSV</t>
@@ -27039,12 +27039,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R278" s="3" t="inlineStr"/>
+      <c r="R278" s="3" t="n"/>
     </row>
     <row r="279" ht="45" customHeight="1">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>5ca34312829eeb0dde98</t>
+          <t>ed54a83eeb8b550b1f0f</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -27057,7 +27057,7 @@
           <t>2026-09-30T18:57:41+00:00</t>
         </is>
       </c>
-      <c r="D279" s="3" t="inlineStr"/>
+      <c r="D279" s="3" t="n"/>
       <c r="E279" s="3" t="inlineStr">
         <is>
           <t>Intern - Winter '27</t>
@@ -27073,13 +27073,13 @@
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="H279" s="3" t="inlineStr"/>
+      <c r="H279" s="3" t="n"/>
       <c r="I279" s="3" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="J279" s="3" t="inlineStr"/>
+      <c r="J279" s="3" t="n"/>
       <c r="K279" s="4" t="inlineStr">
         <is>
           <t>https://vercel.com/careers/software-engineering-intern-winter-27-6181755004</t>
@@ -27133,12 +27133,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R279" s="3" t="inlineStr"/>
+      <c r="R279" s="3" t="n"/>
     </row>
     <row r="280" ht="45" customHeight="1">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>9c1b49a6c300439b05ff</t>
+          <t>eab45bc621a44116c9d9</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -27171,13 +27171,13 @@
           <t>Design</t>
         </is>
       </c>
-      <c r="H280" s="3" t="inlineStr"/>
+      <c r="H280" s="3" t="n"/>
       <c r="I280" s="3" t="inlineStr">
         <is>
           <t>Redmond</t>
         </is>
       </c>
-      <c r="J280" s="3" t="inlineStr"/>
+      <c r="J280" s="3" t="n"/>
       <c r="K280" s="4" t="inlineStr">
         <is>
           <t>https://www.metacareers.com/profile/job_details/1613359540444032</t>
@@ -27236,10 +27236,291 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R280" s="3" t="inlineStr"/>
+      <c r="R280" s="3" t="n"/>
+    </row>
+    <row r="281" ht="45" customHeight="1">
+      <c r="A281" s="3" t="inlineStr">
+        <is>
+          <t>c90966ef561a66c5f8a3</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T23:55:54.227558+00:00</t>
+        </is>
+      </c>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T03:18:35+00:00</t>
+        </is>
+      </c>
+      <c r="D281" s="3" t="inlineStr"/>
+      <c r="E281" s="3" t="inlineStr">
+        <is>
+          <t>al 2 NEW GRAD PM!</t>
+        </is>
+      </c>
+      <c r="F281" s="3" t="inlineStr">
+        <is>
+          <t>New Grad / Early Career</t>
+        </is>
+      </c>
+      <c r="G281" s="3" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="H281" s="3" t="inlineStr"/>
+      <c r="I281" s="3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J281" s="3" t="inlineStr"/>
+      <c r="K281" s="4" t="inlineStr">
+        <is>
+          <t>https://www.demystifyd.com/jobs/product-manager-%E2%80%94-new-graduate</t>
+        </is>
+      </c>
+      <c r="L281" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M281" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N281" s="3" t="inlineStr">
+        <is>
+          <t>@ demystifyd.com C:
+D) DEMYSTIFYD
+HOME
+Product Manager —
+New Graduate
+New York, London, Toronto, San
+Francisco
+Job Type Full-time
+al 2 NEW GRAD PM!
+Own feature plangé ject definition,
+and issue prioritiz a deeply
+technical, engineering-led product
+organization.
+https://scontent-iad3-1.cdninstagram.com/v/t51.71878-15/825324752_1962619567745729_2040668614727993693_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=104&amp;cb=30a688f7-1209d890&amp;ig_cache_key=Mzk5NzMyNTE4ODE0NDQyNjM3NQ%3D%3D.3-ccb7-5-cb30a688f7-1209d890&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=BeCTxLSV0zYQ7kNvwEmh_CB&amp;_nc_oc=AdqvkU8t8dLsjHn5JYfD09Wv2XyONbr8r0pdKDUdJ8dCubsMBduB9LhQLlTrtJC2xi8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;_nc_gid=g_UJGnFxy8ZnD91xqrrgxQ&amp;_nc_ss=7e3ba&amp;oh=00_AQOL4urA3tuIORrsH4_gtK8RwPCl6ShU6kq45ZU29aVbsw&amp;oe=6AC35D5A
+https://scontent-iad3-1.cdninstagram.com/v/t51.71878-15/825324752_1962619567745729_2040668614727993693_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=104&amp;cb=30a688f7-1209d890&amp;ig_cache_key=Mzk5NzMyNTE4ODE0NDQyNjM3NQ%3D%3D.3-ccb7-5-cb30a688f7-1209d890&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=BeCTxLSV0zYQ7kNvwEmh_CB&amp;_nc_oc=AdqvkU8t8dLsjHn5JYfD09Wv2XyONbr8r0pdKDUdJ8dCubsMBduB9LhQLlTrtJC2xi8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;_nc_gid=g_UJGnFxy8ZnD91xqrrgxQ&amp;_nc_ss=7e3ba&amp;oh=00_AQOqPGl3lFVND2EbTh-d0z32INb57we1zM72V9Vd2ei15w&amp;oe=6AC35D5A
+https://scontent-iad6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=-f_j7BYj1KsQ7kNvwHETVJv&amp;_nc_oc=AdpkaPKrxGHeo1aowFWU77sb79zEmTuObkUuUSGgwcTrmRGSOMiu9_Lzy7EzW6Pv8Bo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQPJjkaMPQbr6KGpqaQXROHIa9QqHPoN0y3sHFy1NSJ1dA&amp;oe=6AC35BD9
+https://l.instagram.com/?u=https%3A%2F%2Fwww.demystifyd.com%2Fjobs%2Fproduct-manager-%25E2%2580%2594-new-graduate%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAaerCxPdWgUo5YyBnPVfFbU9QujDrYq0t61_XoU_GY-l8oGjIbblYc5e0uCP7Q_aem_uSU7V7xsz-o4lHo7TDgbbg&amp;e=AUBOBiKLeHjVP68MD0s_asu4VCead0Z-NHg81FbHUyEidXw2f1er2VResmrvd3gVqiy9As3thOpkDEpb1upt0bdYb-W3-w4Bw62ifuLGcuIQmLa-2AARrOakD0vni8snUzeo3iSoqGHUDA
+https://scontent-iad6-1.cdninstagram.com/o1/v/t2/f2/m78/AQOO4F8N1l26T3fHvl8g6S-crfl6HqLfc7Xg2JTCSW7HINY6ajcxnnLGNjh6MwIUgojYpH7S-K82byfHLjwRGoB1lEyM3NQc-Nne7yg.mp4?_nc_cat=107&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;_nc_ohc=jdxGthaP9DgQ7kNvwFX51Yk&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwNjA2NTE2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=974e4ceb3994e715&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzQ5RkYyMDc0Qjk0NDQ2RTU4QzdFQzlBQjZFOUZCMDY4X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk87Wn9PmhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=g_UJGnFxy8ZnD91xqrrgxQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQMzJDHURu4vc3PsPfF8_EG5qqgw3W3Yuqo6VkSZ5pdhYg&amp;oe=6ABF6DE4</t>
+        </is>
+      </c>
+      <c r="O281" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P281" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q281" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R281" s="3" t="inlineStr"/>
+    </row>
+    <row r="282" ht="45" customHeight="1">
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t>4796a062511603898286</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T23:55:57.700670+00:00</t>
+        </is>
+      </c>
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T03:19:41+00:00</t>
+        </is>
+      </c>
+      <c r="D282" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E282" s="3" t="inlineStr">
+        <is>
+          <t>Amazon — Internship</t>
+        </is>
+      </c>
+      <c r="F282" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G282" s="3" t="inlineStr"/>
+      <c r="H282" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="I282" s="3" t="inlineStr"/>
+      <c r="J282" s="3" t="inlineStr"/>
+      <c r="K282" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.jobs/en/jobs/10564599/2027-applied-science-internship-united-states-undergrad-student-science-recruiting-frontier-ai-robotics?jr_id=6abc6f9f2668e0eab35c23d1</t>
+        </is>
+      </c>
+      <c r="L282" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M282" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N282" s="3" t="inlineStr">
+        <is>
+          <t>amazon
+—?
+Impact the
+future, tocay.
+2027 Applied Science Internship
+- United States, Undergrad
+Student Science Recruiting,
+Frontier Al &amp; Robotics
+Are you a brilliant mind seeking
+to push the boundaries of what's
+possible with intelligent robotics?
+Join our elite team of researchers
+and engineers - led by Pieter Abeel,
+Rocky Duan, and Peter Chen - at
+the forefront of applied science,
+where we're harnessing the latest
+advancements in large lang...
+https://www.amazon.jobs/en
+_id=6abc6f9f2E ‘ab35c23d1
+Amazon undergrad research
+robotics and Ilm
+https://scontent-iad3-2.cdninstagram.com/v/t51.71878-15/829647802_1033045443074739_5467457875457086463_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;cb=30a688f7-1209d890&amp;ig_cache_key=Mzk5NzMyNTc0Njg3NTY5NjY1Mw%3D%3D.3-ccb7-5-cb30a688f7-1209d890&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=BU9ptfOgsboQ7kNvwFot9ZX&amp;_nc_oc=AdpiJVM9F8p_2qesp4CJntrzdlEHk_sAf3_IrPoeYuQodBuvM1aNlYv0W5w2-J5urFw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;_nc_gid=g_UJGnFxy8ZnD91xqrrgxQ&amp;_nc_ss=7e3ba&amp;oh=00_AQMkq69CUjB8UrtNZzQLr-cFScrH8pLc1l4RioRBlLWuZQ&amp;oe=6AC389D8
+https://scontent-iad3-2.cdninstagram.com/v/t51.71878-15/829647802_1033045443074739_5467457875457086463_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=105&amp;cb=30a688f7-1209d890&amp;ig_cache_key=Mzk5NzMyNTc0Njg3NTY5NjY1Mw%3D%3D.3-ccb7-5-cb30a688f7-1209d890&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=BU9ptfOgsboQ7kNvwFot9ZX&amp;_nc_oc=AdpiJVM9F8p_2qesp4CJntrzdlEHk_sAf3_IrPoeYuQodBuvM1aNlYv0W5w2-J5urFw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;_nc_gid=g_UJGnFxy8ZnD91xqrrgxQ&amp;_nc_ss=7e3ba&amp;oh=00_AQOVP3Ewx3a-AALLWSx_O7qdsU61ZroAoEFnY0umH2FAHQ&amp;oe=6AC389D8
+https://scontent-iad6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=-f_j7BYj1KsQ7kNvwHETVJv&amp;_nc_oc=AdpkaPKrxGHeo1aowFWU77sb79zEmTuObkUuUSGgwcTrmRGSOMiu9_Lzy7EzW6Pv8Bo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQPJjkaMPQbr6KGpqaQXROHIa9QqHPoN0y3sHFy1NSJ1dA&amp;oe=6AC35BD9
+https://l.instagram.com/?u=https%3A%2F%2Fwww.amazon.jobs%2Fen%2Fjobs%2F10564599%2F2027-applied-science-internship-united-states-undergrad-student-science-recruiting-frontier-ai-robotics%3Fjr_id%3D6abc6f9f2668e0eab35c23d1%26fbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAad0jYv416b_9mTL80q1NU1-kGn59K8xEZDwKGeEsOEaQUwUA_N4EG3M7FSjjw_aem_G4-G1xD6tfNlUjrom1eCtA&amp;e=AUBCtgO0xYDX7WVXUSWKEOdh9BAuwCBk0zAESbvJXiFeCoYeazuyqRRVGRmZruKeqPsRKvLRXTuUpP3UeYNVLPhy9LViBPwAcQ1M8mHaptnGVxA9PbdNFk49E-cbVrtgozadi12sEX7cwQ
+https://scontent-iad3-2.cdninstagram.com/o1/v/t2/f2/m78/AQMrY0pGtezH11XRWzCh4usC0YsvKneguWdaKtaYzRTa1pwcJ6AvNLNj0_GHofbTJJFQ4KO9F9Xpd1Hj1enjdvDIIvDntPXfQB1XK2E.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;_nc_ohc=KjwRIEMJ2mYQ7kNvwGid1Q0&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwNjA4ODg2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=2bdb72f17c9e04e5&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzRGN0MwMzkyMzY3QjRBQ0M4MkQ1NTE3QTg0QkFFQUY4X3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkyLiJ9vmhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=g_UJGnFxy8ZnD91xqrrgxQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQMvHZFSTA2Ej8Uu7N-rvFM-4iDvYpMe5CZV4U3DQG2qiw&amp;oe=6ABF91EC</t>
+        </is>
+      </c>
+      <c r="O282" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P282" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q282" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R282" s="3" t="inlineStr"/>
+    </row>
+    <row r="283" ht="45" customHeight="1">
+      <c r="A283" s="3" t="inlineStr">
+        <is>
+          <t>ec6bca3e3a07b296df19</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T23:55:58.553723+00:00</t>
+        </is>
+      </c>
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T03:20:25+00:00</t>
+        </is>
+      </c>
+      <c r="D283" s="3" t="inlineStr">
+        <is>
+          <t>Amca</t>
+        </is>
+      </c>
+      <c r="E283" s="3" t="inlineStr">
+        <is>
+          <t>Amca — Software Engineering</t>
+        </is>
+      </c>
+      <c r="F283" s="3" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G283" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="H283" s="3" t="inlineStr">
+        <is>
+          <t>Summer 2027</t>
+        </is>
+      </c>
+      <c r="I283" s="3" t="inlineStr"/>
+      <c r="J283" s="3" t="inlineStr"/>
+      <c r="K283" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/amca/jobs/4425120009</t>
+        </is>
+      </c>
+      <c r="L283" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stories/zero2sudo/</t>
+        </is>
+      </c>
+      <c r="M283" s="3" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="N283" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Internship
+(Summer 2027)
+El Segundo, CA
+https://scontent-iad3-2.cdninstagram.com/v/t51.71878-15/825324818_1901617081211995_1513383481815543570_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=103&amp;cb=30a688f7-1209d890&amp;ig_cache_key=Mzk5NzMyNjExNDIxMzQzMjYwMw%3D%3D.3-ccb7-5-cb30a688f7-1209d890&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=K-CyiKmA63EQ7kNvwHLwDKv&amp;_nc_oc=AdoQic-_pZ5uwzLfqNqxVoiW-Pi9yfc9zY3TVrkqr8wGbDMwQ9OlpunWHJEwcOegeew&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;_nc_gid=g_UJGnFxy8ZnD91xqrrgxQ&amp;_nc_ss=7e3ba&amp;oh=00_AQPlztC3bKoydjIHCoyRw3s5HjceWkgsFJfFSzefqiO1kw&amp;oe=6AC36605
+https://scontent-iad3-2.cdninstagram.com/v/t51.71878-15/825324818_1901617081211995_1513383481815543570_n.jpg?stp=dst-jpg_e15_p360x360_tt6&amp;_nc_cat=103&amp;cb=30a688f7-1209d890&amp;ig_cache_key=Mzk5NzMyNjExNDIxMzQzMjYwMw%3D%3D.3-ccb7-5-cb30a688f7-1209d890&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IlNUT1JZLnhwaWRzLjY0MC5zZHIudmlkZW9fZmlyc3RfZnJhbWVfdGh1bWJuYWlsLkMzIn0%3D&amp;_nc_ohc=K-CyiKmA63EQ7kNvwHLwDKv&amp;_nc_oc=AdoQic-_pZ5uwzLfqNqxVoiW-Pi9yfc9zY3TVrkqr8wGbDMwQ9OlpunWHJEwcOegeew&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;_nc_gid=g_UJGnFxy8ZnD91xqrrgxQ&amp;_nc_ss=7e3ba&amp;oh=00_AQORAOiluFN5DtI5bd28krYgyTbneU2Y3KrVkKayviuCYw&amp;oe=6AC36605
+https://scontent-iad6-1.cdninstagram.com/v/t51.2885-19/361942212_2508526442658147_3130876906989167533_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GMTMkhVjOYbTfekIAK0jkHT1G3MrbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=-f_j7BYj1KsQ7kNvwHETVJv&amp;_nc_oc=AdpkaPKrxGHeo1aowFWU77sb79zEmTuObkUuUSGgwcTrmRGSOMiu9_Lzy7EzW6Pv8Bo&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=24&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;_nc_ss=7e3ba&amp;oh=00_AQPJjkaMPQbr6KGpqaQXROHIa9QqHPoN0y3sHFy1NSJ1dA&amp;oe=6AC35BD9
+https://l.instagram.com/?u=https%3A%2F%2Fjob-boards.greenhouse.io%2Famca%2Fjobs%2F4425120009%3Ffbclid%3DPAZXh0bgNhZW0CMTEAcGRvZgJzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAadKLttoRuaDomkJwZjBOLUxDOqtFfg0jVaPHmfYYQfONPi3gw2RLAlV3UzyUw_aem_cb0bGZiidozMPZNpRK4-Zg&amp;e=AUD9nwd__8ikVJ2w-vLPMVbM1wLgFMZVYZTuQeGf5YXAlfZ8JSZ8T_48qhlVSCq6yFd9qn5N-uOx6DBVwm_8IXQ2AANvRDOZGv2-K8t9WptA_-lNUWF3OMRMnG7LMWCV-9CSVYXJpBHJFg
+https://scontent-iad3-2.cdninstagram.com/o1/v/t2/f2/m78/AQO5r4-MT6JnJPVtN6dR1FSxaVY9giRCtxBUvmyFmMCuy15FnhIsek7EVio9zltq5WAKRDDewFkP-DIh_JQkUtBOpkF0GSdOn4Kc2Xc.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;_nc_ohc=mqVeQP58xBMQ7kNvwFX0V4p&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uU1RPUlkuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgwODkwNjExNjQ2Nzg5NjIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDEwMCwiZHVyYXRpb25fcyI6MywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=f3ea2ec1aee948d&amp;_nc_vs=HBkcFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0IyNTQzQTY5RDEzNzQyQTE5QkNGMkRDRkY2RUYwNTBBX3ZpZGVvX2Rhc2hpbml0Lm1wNBUAAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbk_NOQ-PmhQBUCKAJDMywXQAhDlYEGJN0YEmRhc2hfYmFzZWxpbmVfMV92MREAdegHZeidAQA&amp;_nc_gid=g_UJGnFxy8ZnD91xqrrgxQ&amp;_nc_ss=7e3ba&amp;_nc_zt=28&amp;oh=00_AQPRsELhbq0W4aifdZ03lxpwvH7-mIHE8GaMBZydPLuo6w&amp;oe=6ABF797C</t>
+        </is>
+      </c>
+      <c r="O283" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="P283" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q283" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R283" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R280"/>
+  <autoFilter ref="A1:R283"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -27784,6 +28065,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L279" r:id="rId541"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K280" r:id="rId542"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L280" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K281" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L281" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K282" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L282" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K283" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L283" r:id="rId549"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
